--- a/TDA_Result.xlsx
+++ b/TDA_Result.xlsx
@@ -453,7 +453,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4606179852510911</v>
+        <v>0.467030199623675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -739,22 +739,22 @@
         <v>14.94856954517825</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.291324921466543</v>
+        <v>1.945053659492091</v>
       </c>
       <c r="Z2" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AA2" t="n">
-        <v>40</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.54237786061556</v>
+        <v>12.27306513849694</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.868927296035974</v>
+        <v>6.175054463322383</v>
       </c>
       <c r="AE2" t="n">
         <v>43</v>
@@ -763,10 +763,10 @@
         <v>53.48837209302326</v>
       </c>
       <c r="AG2" t="n">
-        <v>35.17183458348511</v>
+        <v>35.2995697192395</v>
       </c>
       <c r="AH2" t="n">
-        <v>18.31653750953814</v>
+        <v>18.18880237378376</v>
       </c>
       <c r="AI2" t="n">
         <v>38.91564047231397</v>
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7473463941583504</v>
+        <v>0.7539802635829748</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,22 +848,22 @@
         <v>12.13279917920569</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.771047956559557</v>
+        <v>0.8991122027144582</v>
       </c>
       <c r="Z3" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.26984126984127</v>
+        <v>44.26229508196721</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.95596430927363</v>
+        <v>10.50885197844632</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>8.377318369233233</v>
+        <v>9.183457383249415</v>
       </c>
       <c r="AE3" t="n">
         <v>38</v>
@@ -872,10 +872,10 @@
         <v>60.52631578947368</v>
       </c>
       <c r="AG3" t="n">
-        <v>31.17946845698509</v>
+        <v>31.40864168599064</v>
       </c>
       <c r="AH3" t="n">
-        <v>29.34684733248859</v>
+        <v>29.11767410348304</v>
       </c>
       <c r="AI3" t="n">
         <v>44.71786799604255</v>
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C4" t="n">
-        <v>1.334697536143082</v>
+        <v>1.385312471974113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -914,11 +914,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>5</v>
       </c>
@@ -926,25 +922,25 @@
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>27.76724590861524</v>
+        <v>27.63389482946404</v>
       </c>
       <c r="K4" t="n">
-        <v>3.341488363691547</v>
+        <v>7.260445775815549</v>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M4" t="n">
-        <v>76.92307692307692</v>
+        <v>56.25</v>
       </c>
       <c r="N4" t="n">
-        <v>14.87524842765284</v>
+        <v>18.41684522661439</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>1.604884604014623</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>53</v>
@@ -953,10 +949,10 @@
         <v>58.49056603773585</v>
       </c>
       <c r="S4" t="n">
-        <v>36.8860774877052</v>
+        <v>36.93324729902596</v>
       </c>
       <c r="T4" t="n">
-        <v>21.60448855003064</v>
+        <v>21.55731873870989</v>
       </c>
       <c r="U4" t="n">
         <v>45.09442218134437</v>
@@ -985,19 +981,19 @@
         <v>60</v>
       </c>
       <c r="AG4" t="n">
-        <v>38.65987904055164</v>
+        <v>38.55050898673715</v>
       </c>
       <c r="AH4" t="n">
-        <v>21.34012095944836</v>
+        <v>21.44949101326285</v>
       </c>
       <c r="AI4" t="n">
         <v>45.45185459035139</v>
       </c>
       <c r="AJ4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AK4" t="n">
-        <v>56.06060606060606</v>
+        <v>55.38461538461539</v>
       </c>
     </row>
     <row r="5">
@@ -1007,10 +1003,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2736761443396776</v>
+        <v>0.2739069011605809</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,43 +1045,43 @@
         <v>50</v>
       </c>
       <c r="R5" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="S5" t="n">
-        <v>43.90333485431293</v>
+        <v>44.74566289664097</v>
       </c>
       <c r="T5" t="n">
-        <v>20.09666514568707</v>
+        <v>17.25433710335903</v>
       </c>
       <c r="U5" t="n">
-        <v>50.1410168761127</v>
+        <v>48.15044693099298</v>
       </c>
       <c r="V5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W5" t="n">
-        <v>59.375</v>
+        <v>58.46153846153846</v>
       </c>
       <c r="X5" t="n">
-        <v>14.49567008868182</v>
+        <v>16.70098304122878</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.153613358628113</v>
+        <v>1.957825868118446</v>
       </c>
       <c r="Z5" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="AA5" t="n">
-        <v>52.63157894736842</v>
+        <v>43.13725490196079</v>
       </c>
       <c r="AB5" t="n">
-        <v>13.61927930816605</v>
+        <v>15.78456111954939</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>9.86153527692306</v>
+        <v>8.202770086538081</v>
       </c>
       <c r="AE5" t="n">
         <v>45</v>
@@ -1094,10 +1090,10 @@
         <v>48.88888888888889</v>
       </c>
       <c r="AG5" t="n">
-        <v>25.48093094006081</v>
+        <v>25.58886398670354</v>
       </c>
       <c r="AH5" t="n">
-        <v>23.40795794882807</v>
+        <v>23.30002490218535</v>
       </c>
       <c r="AI5" t="n">
         <v>34.9570237528785</v>
@@ -1116,10 +1112,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C6" t="n">
-        <v>1.982046877561934</v>
+        <v>2.029056747170189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,11 +1132,7 @@
           <t>SATMA_BEKLE</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.67: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>5</v>
       </c>
@@ -1151,16 +1143,16 @@
         <v>22.03360200065558</v>
       </c>
       <c r="K6" t="n">
-        <v>2.114972499464929</v>
+        <v>4.536919021817254</v>
       </c>
       <c r="L6" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M6" t="n">
-        <v>76.66666666666667</v>
+        <v>72</v>
       </c>
       <c r="N6" t="n">
-        <v>14.35938313558784</v>
+        <v>11.80010877058999</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
@@ -1175,10 +1167,10 @@
         <v>67.5</v>
       </c>
       <c r="S6" t="n">
-        <v>47.81821717059034</v>
+        <v>48.05915074208657</v>
       </c>
       <c r="T6" t="n">
-        <v>19.68178282940966</v>
+        <v>19.44084925791343</v>
       </c>
       <c r="U6" t="n">
         <v>52.01774618987768</v>
@@ -1193,7 +1185,7 @@
         <v>44.49622708587002</v>
       </c>
       <c r="Y6" t="n">
-        <v>20.38463412414608</v>
+        <v>18.49632965919758</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1235,19 +1227,19 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C7" t="n">
-        <v>2.126253121408264</v>
+        <v>2.150021772210852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1266,22 +1258,22 @@
         <v>11.35312764557068</v>
       </c>
       <c r="K7" t="n">
-        <v>1.865858236462281</v>
+        <v>3.004581556254426</v>
       </c>
       <c r="L7" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="M7" t="n">
-        <v>56.94444444444444</v>
+        <v>58.20895522388059</v>
       </c>
       <c r="N7" t="n">
-        <v>13.8900301664229</v>
+        <v>12.61338027889698</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.113367896930706</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1290,10 +1282,10 @@
         <v>58.8235294117647</v>
       </c>
       <c r="S7" t="n">
-        <v>51.83165142950381</v>
+        <v>51.89826781964963</v>
       </c>
       <c r="T7" t="n">
-        <v>6.991877982260888</v>
+        <v>6.925261592115078</v>
       </c>
       <c r="U7" t="n">
         <v>45.16533720637157</v>
@@ -1308,22 +1300,22 @@
         <v>13.79329344082609</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.699102676379356</v>
+        <v>8.689660068613092</v>
       </c>
       <c r="Z7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
-        <v>58.8235294117647</v>
+        <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.456095761480952</v>
+        <v>8.615798389642457</v>
       </c>
       <c r="AC7" t="n">
         <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.3332163162701351</v>
+        <v>1.435040032017765</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1354,10 +1346,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3237799330806628</v>
+        <v>0.3275522438928626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,22 +1377,22 @@
         <v>22.10694516187944</v>
       </c>
       <c r="K8" t="n">
-        <v>2.945117418805165</v>
+        <v>4.144515342596167</v>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N8" t="n">
-        <v>17.67912674615781</v>
+        <v>15.38993104685579</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>4.910269382306276</v>
+        <v>3.702052522613175</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1418,10 +1410,10 @@
         <v>37.55346297625253</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W8" t="n">
-        <v>50</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
@@ -1463,10 +1455,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5726147180025462</v>
+        <v>0.5785283806292564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,19 +1483,19 @@
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>13.88876160098961</v>
+        <v>12.72202042588303</v>
       </c>
       <c r="K9" t="n">
-        <v>3.030307392102904</v>
+        <v>4.094350035590177</v>
       </c>
       <c r="L9" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="M9" t="n">
-        <v>46.66666666666666</v>
+        <v>43.90243902439025</v>
       </c>
       <c r="N9" t="n">
-        <v>14.94294495595002</v>
+        <v>14.82625929286921</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1572,19 +1564,19 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C10" t="n">
-        <v>2.047308079771819</v>
+        <v>2.0721834724357</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1599,27 +1591,17 @@
       <c r="I10" t="n">
         <v>10</v>
       </c>
-      <c r="J10" t="n">
-        <v>10.35846261759502</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.7772020725388407</v>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>44</v>
-      </c>
-      <c r="M10" t="n">
-        <v>40.90909090909091</v>
-      </c>
-      <c r="N10" t="n">
-        <v>9.624545134931306</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
         <v>10</v>
       </c>
-      <c r="P10" t="n">
-        <v>9.151670951156831</v>
-      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
         <v>44</v>
       </c>
@@ -1627,10 +1609,10 @@
         <v>50</v>
       </c>
       <c r="S10" t="n">
-        <v>35.82026373426856</v>
+        <v>35.99804965802223</v>
       </c>
       <c r="T10" t="n">
-        <v>14.17973626573144</v>
+        <v>14.00195034197777</v>
       </c>
       <c r="U10" t="n">
         <v>35.8317605399894</v>
@@ -1659,10 +1641,10 @@
         <v>51.51515151515152</v>
       </c>
       <c r="AG10" t="n">
-        <v>36.55580514309054</v>
+        <v>36.33694992423531</v>
       </c>
       <c r="AH10" t="n">
-        <v>14.95934637206098</v>
+        <v>15.1782015909162</v>
       </c>
       <c r="AI10" t="n">
         <v>35.21837544891414</v>
@@ -1681,10 +1663,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C11" t="n">
-        <v>7.205050800019588</v>
+        <v>7.200048664376836</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1685,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1713,25 +1695,25 @@
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>20.34607119831284</v>
+        <v>19.38783055927281</v>
       </c>
       <c r="K11" t="n">
-        <v>1.729493789807468</v>
+        <v>1.658867677524722</v>
       </c>
       <c r="L11" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="M11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N11" t="n">
-        <v>16.41824258237483</v>
+        <v>15.00634405004488</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.248906450687381</v>
+        <v>1.319247747997276</v>
       </c>
       <c r="Q11" t="n">
         <v>49</v>
@@ -1794,10 +1776,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C12" t="n">
-        <v>6.220869280951902</v>
+        <v>6.248106510795969</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,16 +1807,16 @@
         <v>20.08266526523165</v>
       </c>
       <c r="K12" t="n">
-        <v>8.303505954800162</v>
+        <v>8.777698121744027</v>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>66.66666666666667</v>
+        <v>60</v>
       </c>
       <c r="N12" t="n">
-        <v>33.26223985018026</v>
+        <v>34.30134161376015</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -1903,10 +1885,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3136749574357124</v>
+        <v>0.3191372938337487</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1916,7 @@
         <v>38.11781916800814</v>
       </c>
       <c r="K13" t="n">
-        <v>10.22693361387461</v>
+        <v>12.14642567803277</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1970,7 +1952,7 @@
         <v>35.74308703619145</v>
       </c>
       <c r="Y13" t="n">
-        <v>18.79738701943163</v>
+        <v>17.3833245385582</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2002,10 +1984,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C14" t="n">
-        <v>8.215547332966091</v>
+        <v>8.25191844733912</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2065,16 +2047,16 @@
         <v>14.33662537827827</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.054636617891606</v>
+        <v>4.634303251068594</v>
       </c>
       <c r="Z14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AA14" t="n">
-        <v>44.44444444444444</v>
+        <v>44.82758620689656</v>
       </c>
       <c r="AB14" t="n">
-        <v>13.20714278594145</v>
+        <v>13.91848588751987</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2089,10 +2071,10 @@
         <v>52.63157894736842</v>
       </c>
       <c r="AG14" t="n">
-        <v>26.46533478916741</v>
+        <v>26.59691373653583</v>
       </c>
       <c r="AH14" t="n">
-        <v>26.16624415820101</v>
+        <v>26.03466521083259</v>
       </c>
       <c r="AI14" t="n">
         <v>37.25897138449667</v>
@@ -2111,10 +2093,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C15" t="n">
-        <v>10.97862379024168</v>
+        <v>11.13930100157059</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2139,25 +2121,25 @@
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>20.99141370769134</v>
+        <v>20.36228477344414</v>
       </c>
       <c r="K15" t="n">
-        <v>3.369672943508428</v>
+        <v>4.882535675839894</v>
       </c>
       <c r="L15" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M15" t="n">
-        <v>64.70588235294117</v>
+        <v>60</v>
       </c>
       <c r="N15" t="n">
-        <v>16.04542871885248</v>
+        <v>17.02443812528893</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>4.479386385426665</v>
+        <v>2.972338820826415</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2198,19 +2180,19 @@
         <v>58.06451612903226</v>
       </c>
       <c r="AG15" t="n">
-        <v>25.17408899208613</v>
+        <v>24.94292152949194</v>
       </c>
       <c r="AH15" t="n">
-        <v>32.89042713694612</v>
+        <v>33.12159459954032</v>
       </c>
       <c r="AI15" t="n">
         <v>40.76626249536972</v>
       </c>
       <c r="AJ15" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AK15" t="n">
-        <v>48.38709677419355</v>
+        <v>47.82608695652174</v>
       </c>
     </row>
     <row r="16">
@@ -2220,10 +2202,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C16" t="n">
-        <v>35.97788697511608</v>
+        <v>36.31054490785805</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,25 +2230,25 @@
         <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>19.3954730440369</v>
+        <v>19.01528411877121</v>
       </c>
       <c r="K16" t="n">
-        <v>3.701456310679618</v>
+        <v>4.660298393387308</v>
       </c>
       <c r="L16" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M16" t="n">
-        <v>60.41666666666666</v>
+        <v>65.90909090909091</v>
       </c>
       <c r="N16" t="n">
-        <v>16.46756258513066</v>
+        <v>15.89667251250147</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>6.073727325921596</v>
+        <v>5.101936157818243</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2275,10 +2257,10 @@
         <v>67.85714285714286</v>
       </c>
       <c r="S16" t="n">
-        <v>54.14549054741087</v>
+        <v>54.19064654084273</v>
       </c>
       <c r="T16" t="n">
-        <v>13.71165230973199</v>
+        <v>13.66649631630013</v>
       </c>
       <c r="U16" t="n">
         <v>49.33884318085762</v>
@@ -2329,10 +2311,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7486095436657887</v>
+        <v>0.752297233431801</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2360,22 +2342,22 @@
         <v>16.56354083790577</v>
       </c>
       <c r="K17" t="n">
-        <v>6.320928369942447</v>
+        <v>6.844670823909627</v>
       </c>
       <c r="L17" t="n">
         <v>38</v>
       </c>
       <c r="M17" t="n">
-        <v>73.68421052631579</v>
+        <v>71.05263157894737</v>
       </c>
       <c r="N17" t="n">
-        <v>17.18674544498326</v>
+        <v>17.76917220557955</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>1.579248465753835</v>
+        <v>1.081316613342809</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2402,22 +2384,22 @@
         <v>15.7396793517258</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.137875475842925</v>
+        <v>7.685357845847129</v>
       </c>
       <c r="Z17" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AA17" t="n">
-        <v>56</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="AB17" t="n">
-        <v>10.89047526644056</v>
+        <v>11.32671724855418</v>
       </c>
       <c r="AC17" t="n">
         <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.027086281536394</v>
+        <v>2.507340222678578</v>
       </c>
       <c r="AE17" t="n">
         <v>35</v>
@@ -2448,10 +2430,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1031548565101565</v>
+        <v>0.104976599501035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2479,22 +2461,22 @@
         <v>26.36599129766135</v>
       </c>
       <c r="K18" t="n">
-        <v>1.87110522084537</v>
+        <v>3.670176812698589</v>
       </c>
       <c r="L18" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="M18" t="n">
-        <v>54.54545454545455</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="N18" t="n">
-        <v>20.38192763618274</v>
+        <v>19.98491655925718</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>7.979588286130879</v>
+        <v>6.105732026229238</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2503,10 +2485,10 @@
         <v>77.19298245614036</v>
       </c>
       <c r="S18" t="n">
-        <v>42.03040872697647</v>
+        <v>41.98819088290104</v>
       </c>
       <c r="T18" t="n">
-        <v>35.16257372916389</v>
+        <v>35.20479157323932</v>
       </c>
       <c r="U18" t="n">
         <v>64.79398895432649</v>
@@ -2535,10 +2517,10 @@
         <v>59.52380952380953</v>
       </c>
       <c r="AG18" t="n">
-        <v>39.34635084038455</v>
+        <v>39.37236124454621</v>
       </c>
       <c r="AH18" t="n">
-        <v>20.17745868342498</v>
+        <v>20.15144827926331</v>
       </c>
       <c r="AI18" t="n">
         <v>44.49431275003934</v>
@@ -2557,10 +2539,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0252624143762631</v>
+        <v>0.02524487584296461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2588,7 +2570,7 @@
         <v>23.99412305210119</v>
       </c>
       <c r="K19" t="n">
-        <v>2.280152850989992</v>
+        <v>2.209144441428079</v>
       </c>
       <c r="L19" t="n">
         <v>19</v>
@@ -2597,13 +2579,13 @@
         <v>73.68421052631579</v>
       </c>
       <c r="N19" t="n">
-        <v>19.12805565057547</v>
+        <v>19.13887577281496</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>7.547746981036396</v>
+        <v>7.622464311925192</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2666,10 +2648,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C20" t="n">
-        <v>1.91678567514153</v>
+        <v>1.921766061284878</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,22 +2711,22 @@
         <v>20.34011802710127</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.242913135807257</v>
+        <v>2.991509099905532</v>
       </c>
       <c r="Z20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA20" t="n">
-        <v>46.66666666666666</v>
+        <v>40.625</v>
       </c>
       <c r="AB20" t="n">
-        <v>11.6658800826081</v>
+        <v>11.24895484505469</v>
       </c>
       <c r="AC20" t="n">
         <v>4</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.7824614079745773</v>
+        <v>1.039590339708596</v>
       </c>
       <c r="AE20" t="n">
         <v>40</v>
@@ -2775,10 +2757,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9439721810186589</v>
+        <v>0.9559392299348919</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2806,43 +2788,43 @@
         <v>15.77844025931157</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9000934570911001</v>
+        <v>2.179237459778216</v>
       </c>
       <c r="L21" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M21" t="n">
-        <v>55.10204081632653</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="N21" t="n">
-        <v>20.48153918688665</v>
+        <v>18.92892346628566</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>7.036570829271049</v>
+        <v>5.696619670422831</v>
       </c>
       <c r="Q21" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R21" t="n">
-        <v>72.5</v>
+        <v>70.73170731707317</v>
       </c>
       <c r="S21" t="n">
-        <v>45.70511029373566</v>
+        <v>44.95620516462016</v>
       </c>
       <c r="T21" t="n">
-        <v>26.79488970626434</v>
+        <v>25.77550215245302</v>
       </c>
       <c r="U21" t="n">
-        <v>57.16504419378943</v>
+        <v>55.52053227700284</v>
       </c>
       <c r="V21" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="W21" t="n">
-        <v>73.52941176470588</v>
+        <v>72.46376811594203</v>
       </c>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
@@ -2862,10 +2844,10 @@
         <v>61.53846153846154</v>
       </c>
       <c r="AG21" t="n">
-        <v>34.57934974104183</v>
+        <v>34.62938991928713</v>
       </c>
       <c r="AH21" t="n">
-        <v>26.95911179741971</v>
+        <v>26.90907161917441</v>
       </c>
       <c r="AI21" t="n">
         <v>45.89906145692508</v>
@@ -2884,10 +2866,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7961870533913079</v>
+        <v>0.7985795198705623</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2901,7 @@
         <v>22.47437017331863</v>
       </c>
       <c r="K22" t="n">
-        <v>6.060996456632761</v>
+        <v>6.379699678065465</v>
       </c>
       <c r="L22" t="n">
         <v>12</v>
@@ -2928,13 +2910,13 @@
         <v>83.33333333333333</v>
       </c>
       <c r="N22" t="n">
-        <v>12.17202745532379</v>
+        <v>13.57317947224143</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>3.713903956180409</v>
+        <v>3.403187199146629</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -2989,10 +2971,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7157683775037721</v>
+        <v>0.7182166749738363</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3009,11 +2991,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>5</v>
       </c>
@@ -3021,25 +2999,25 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>22.54470476538481</v>
+        <v>22.82612646819611</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>0.7079582571334564</v>
       </c>
       <c r="L23" t="n">
         <v>16</v>
       </c>
       <c r="M23" t="n">
-        <v>75</v>
+        <v>68.75</v>
       </c>
       <c r="N23" t="n">
-        <v>15.79634815583552</v>
+        <v>16.03529179982758</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>5.000000000000004</v>
+        <v>4.261869485932634</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3102,10 +3080,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1829419676436783</v>
+        <v>0.1842875908135932</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,22 +3111,22 @@
         <v>25.34703849055006</v>
       </c>
       <c r="K24" t="n">
-        <v>1.637419729694778</v>
+        <v>2.385010174250546</v>
       </c>
       <c r="L24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M24" t="n">
-        <v>66.66666666666667</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N24" t="n">
-        <v>17.32092515977939</v>
+        <v>12.38613097674726</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>8.22785573713456</v>
+        <v>7.43760225524166</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3211,10 +3189,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C25" t="n">
-        <v>4.008302785603856</v>
+        <v>3.950822968970396</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,22 +3220,22 @@
         <v>12.04001635695179</v>
       </c>
       <c r="K25" t="n">
-        <v>4.844201474997378</v>
+        <v>3.340715885657985</v>
       </c>
       <c r="L25" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="M25" t="n">
-        <v>56.25</v>
+        <v>56.36363636363637</v>
       </c>
       <c r="N25" t="n">
-        <v>18.45447962056389</v>
+        <v>17.26882469722056</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>3.009988612250725</v>
+        <v>4.508662509651384</v>
       </c>
       <c r="Q25" t="n">
         <v>44</v>
@@ -3298,10 +3276,10 @@
         <v>53.48837209302326</v>
       </c>
       <c r="AG25" t="n">
-        <v>50.59381580569994</v>
+        <v>50.48741665689312</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.894556287323319</v>
+        <v>3.000955436130134</v>
       </c>
       <c r="AI25" t="n">
         <v>38.91564047231397</v>
@@ -3320,19 +3298,19 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4404080739600113</v>
+        <v>0.4438890564042943</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3347,27 +3325,17 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
-      <c r="J26" t="n">
-        <v>10.42307529163454</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2.896758966079993</v>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>51</v>
-      </c>
-      <c r="M26" t="n">
-        <v>49.01960784313726</v>
-      </c>
-      <c r="N26" t="n">
-        <v>12.7602643829672</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
         <v>6</v>
       </c>
-      <c r="P26" t="n">
-        <v>3.015878308609321</v>
-      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="n">
         <v>36</v>
       </c>
@@ -3429,10 +3397,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C27" t="n">
-        <v>35.85157490849776</v>
+        <v>36.07913355560635</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3446,7 +3414,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3457,10 +3425,10 @@
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>58.05163224828907</v>
+        <v>58.38400783870043</v>
       </c>
       <c r="K27" t="n">
-        <v>1.117232921741063</v>
+        <v>2.571770334928236</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3471,7 +3439,7 @@
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>6.806720159743507</v>
+        <v>5.29212827988339</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -3484,23 +3452,17 @@
         <v>0</v>
       </c>
       <c r="W27" t="inlineStr"/>
-      <c r="X27" t="n">
-        <v>11.42857142857143</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>9.253765326642649</v>
-      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
         <v>5</v>
       </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="n">
         <v>0</v>
       </c>
@@ -3520,10 +3482,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C28" t="n">
-        <v>1.437852422547094</v>
+        <v>1.464202705696285</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3551,16 +3513,16 @@
         <v>25.72214510232956</v>
       </c>
       <c r="K28" t="n">
-        <v>3.120220313629152</v>
+        <v>5.010015789897526</v>
       </c>
       <c r="L28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M28" t="n">
-        <v>64.70588235294117</v>
+        <v>62.5</v>
       </c>
       <c r="N28" t="n">
-        <v>14.38810679374317</v>
+        <v>14.08273448953023</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
@@ -3575,10 +3537,10 @@
         <v>57.5</v>
       </c>
       <c r="S28" t="n">
-        <v>60.45024323790265</v>
+        <v>60.23282694082881</v>
       </c>
       <c r="T28" t="n">
-        <v>-2.950243237902647</v>
+        <v>-2.732826940828808</v>
       </c>
       <c r="U28" t="n">
         <v>42.19506854199106</v>
@@ -3629,10 +3591,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4366187054353385</v>
+        <v>0.4133848167099674</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3641,7 +3603,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3649,24 +3611,38 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H29" t="n">
         <v>5</v>
       </c>
       <c r="I29" t="n">
         <v>10</v>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>13.93943996887607</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.855922418188996</v>
+      </c>
       <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="M29" t="n">
+        <v>77.77777777777777</v>
+      </c>
+      <c r="N29" t="n">
+        <v>23.57395026752156</v>
+      </c>
       <c r="O29" t="n">
         <v>4</v>
       </c>
-      <c r="P29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
       <c r="Q29" t="n">
         <v>6</v>
       </c>
@@ -3692,10 +3668,10 @@
         <v>55.05052857749912</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.688577943954075</v>
+        <v>9.76040594110572</v>
       </c>
       <c r="Z29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
@@ -3703,7 +3679,7 @@
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>5.57270255911474</v>
+        <v>0.265508795105962</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3734,10 +3710,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3770415156978618</v>
+        <v>0.3877192085214907</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3762,25 +3738,25 @@
         <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>22.91017778822961</v>
+        <v>22.50856964296201</v>
       </c>
       <c r="K30" t="n">
-        <v>1.993168511183319</v>
+        <v>4.88158179759639</v>
       </c>
       <c r="L30" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="M30" t="n">
-        <v>55.55555555555556</v>
+        <v>60</v>
       </c>
       <c r="N30" t="n">
-        <v>10.64935866379255</v>
+        <v>11.91558704505633</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>2.948071456851542</v>
+        <v>0.1129065755626657</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3843,10 +3819,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1938890231011905</v>
+        <v>0.1960685210225771</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3874,22 +3850,22 @@
         <v>24.39894838979837</v>
       </c>
       <c r="K31" t="n">
-        <v>1.486200839940577</v>
+        <v>2.627002728785199</v>
       </c>
       <c r="L31" t="n">
         <v>9</v>
       </c>
       <c r="M31" t="n">
-        <v>66.66666666666667</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N31" t="n">
-        <v>11.96258778894206</v>
+        <v>12.87425769672796</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>8.389119988329252</v>
+        <v>7.184266396924399</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3952,10 +3928,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C32" t="n">
-        <v>2.292564041331953</v>
+        <v>2.282557429028157</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3983,16 +3959,16 @@
         <v>11.96252232646255</v>
       </c>
       <c r="K32" t="n">
-        <v>8.781351753940259</v>
+        <v>8.306541544384615</v>
       </c>
       <c r="L32" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M32" t="n">
-        <v>53.57142857142857</v>
+        <v>45.16129032258065</v>
       </c>
       <c r="N32" t="n">
-        <v>10.64869622622552</v>
+        <v>11.24042102953525</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4025,22 +4001,22 @@
         <v>12.36180984775317</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.186543629605409</v>
+        <v>3.609116219170316</v>
       </c>
       <c r="Z32" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA32" t="n">
-        <v>39.1304347826087</v>
+        <v>38.63636363636363</v>
       </c>
       <c r="AB32" t="n">
-        <v>11.65371273481513</v>
+        <v>10.84382070612624</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>4.97188774252515</v>
+        <v>4.555289471993563</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4071,19 +4047,19 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C33" t="n">
-        <v>1.844156140417789</v>
+        <v>1.858653874307141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4102,22 +4078,22 @@
         <v>12.57251846431013</v>
       </c>
       <c r="K33" t="n">
-        <v>3.362830053097343</v>
+        <v>4.175411358615566</v>
       </c>
       <c r="L33" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M33" t="n">
-        <v>59.61538461538461</v>
+        <v>56</v>
       </c>
       <c r="N33" t="n">
-        <v>11.61836319511857</v>
+        <v>11.09603008028689</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>0.6164401135063224</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>39</v>
@@ -4180,10 +4156,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8955525716916874</v>
+        <v>0.9029249831963908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4243,16 +4219,16 @@
         <v>14.68007915548277</v>
       </c>
       <c r="Y34" t="n">
-        <v>6.25014112273351</v>
+        <v>5.478368967754966</v>
       </c>
       <c r="Z34" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AA34" t="n">
-        <v>43.33333333333334</v>
+        <v>39.39393939393939</v>
       </c>
       <c r="AB34" t="n">
-        <v>11.54717462423103</v>
+        <v>11.06059041923906</v>
       </c>
       <c r="AC34" t="n">
         <v>2</v>
@@ -4267,10 +4243,10 @@
         <v>53.84615384615385</v>
       </c>
       <c r="AG34" t="n">
-        <v>27.63431526237328</v>
+        <v>28.02451055471287</v>
       </c>
       <c r="AH34" t="n">
-        <v>26.21183858378056</v>
+        <v>25.82164329144098</v>
       </c>
       <c r="AI34" t="n">
         <v>38.56944827051576</v>
@@ -4289,10 +4265,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C35" t="n">
-        <v>1.791526112660159</v>
+        <v>1.803956677780318</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4311,7 +4287,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4324,22 +4300,22 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>0.9977337948000375</v>
+        <v>1.698510020194011</v>
       </c>
       <c r="L35" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M35" t="n">
-        <v>76.47058823529412</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N35" t="n">
-        <v>15.68446000976045</v>
+        <v>16.49577743815318</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
       </c>
       <c r="P35" t="n">
-        <v>4.952849947468341</v>
+        <v>4.229648968261057</v>
       </c>
       <c r="Q35" t="n">
         <v>7</v>
@@ -4366,7 +4342,7 @@
         <v>42.52272358489104</v>
       </c>
       <c r="Y35" t="n">
-        <v>22.14004227023869</v>
+        <v>21.5998082943155</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -4408,10 +4384,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08273440510863563</v>
+        <v>0.08351846139832725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4436,19 +4412,19 @@
         <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>22.13853209156748</v>
+        <v>21.75644461318207</v>
       </c>
       <c r="K36" t="n">
-        <v>3.40684883253568</v>
+        <v>4.386813456900618</v>
       </c>
       <c r="L36" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M36" t="n">
         <v>50</v>
       </c>
       <c r="N36" t="n">
-        <v>12.89417180108945</v>
+        <v>11.75945115687612</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4517,10 +4493,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06252447360762513</v>
+        <v>0.06395368196261106</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4545,25 +4521,25 @@
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>15.38158724936403</v>
+        <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>1.779286592212626</v>
+        <v>4.105796490959812</v>
       </c>
       <c r="L37" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="M37" t="n">
-        <v>54.05405405405406</v>
+        <v>54.41176470588236</v>
       </c>
       <c r="N37" t="n">
-        <v>18.52733556386632</v>
+        <v>19.57056495175387</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>6.111964050908703</v>
+        <v>3.740621214476136</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4626,10 +4602,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C38" t="n">
-        <v>1.686266057144898</v>
+        <v>1.680887945360946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4654,19 +4630,19 @@
         <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>19.71082289641847</v>
+        <v>19.5673086238003</v>
       </c>
       <c r="K38" t="n">
-        <v>6.433353153471844</v>
+        <v>6.093898730858704</v>
       </c>
       <c r="L38" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M38" t="n">
-        <v>72.72727272727273</v>
+        <v>73.91304347826087</v>
       </c>
       <c r="N38" t="n">
-        <v>13.00612656255959</v>
+        <v>12.70337440081996</v>
       </c>
       <c r="O38" t="n">
         <v>6</v>
@@ -4681,10 +4657,10 @@
         <v>54.28571428571428</v>
       </c>
       <c r="S38" t="n">
-        <v>47.11769562479132</v>
+        <v>47.59013302528162</v>
       </c>
       <c r="T38" t="n">
-        <v>7.168018660922961</v>
+        <v>6.695581260432668</v>
       </c>
       <c r="U38" t="n">
         <v>38.18972506848375</v>
@@ -4713,10 +4689,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="AG38" t="n">
-        <v>20.0169623746369</v>
+        <v>20.29063847675367</v>
       </c>
       <c r="AH38" t="n">
-        <v>37.12589476822024</v>
+        <v>36.85221866610347</v>
       </c>
       <c r="AI38" t="n">
         <v>40.85741114397492</v>
@@ -4735,19 +4711,19 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C39" t="n">
-        <v>2.597818202326209</v>
+        <v>2.675956663691994</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4766,22 +4742,22 @@
         <v>19.12528796921053</v>
       </c>
       <c r="K39" t="n">
-        <v>2.833334608333327</v>
+        <v>5.926406531616113</v>
       </c>
       <c r="L39" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="M39" t="n">
-        <v>56.66666666666666</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N39" t="n">
-        <v>14.34839126097359</v>
+        <v>13.9922670744708</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
       </c>
       <c r="P39" t="n">
-        <v>2.106967939840687</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>43</v>
@@ -4790,10 +4766,10 @@
         <v>65.11627906976744</v>
       </c>
       <c r="S39" t="n">
-        <v>49.01102256104303</v>
+        <v>49.05308270843281</v>
       </c>
       <c r="T39" t="n">
-        <v>16.10525650872441</v>
+        <v>16.06319636133463</v>
       </c>
       <c r="U39" t="n">
         <v>50.17178199285205</v>
@@ -4844,31 +4820,27 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1962047369543223</v>
+        <v>0.19901376377796</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>5</v>
       </c>
@@ -4879,16 +4851,16 @@
         <v>14.73965458840789</v>
       </c>
       <c r="K40" t="n">
-        <v>7.155132274118148</v>
+        <v>8.689252425959948</v>
       </c>
       <c r="L40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M40" t="n">
-        <v>76.47058823529412</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N40" t="n">
-        <v>11.65394002153186</v>
+        <v>12.5552807609638</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4921,22 +4893,22 @@
         <v>14.17330472629232</v>
       </c>
       <c r="Y40" t="n">
-        <v>6.146946932121155</v>
+        <v>4.803270180782881</v>
       </c>
       <c r="Z40" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA40" t="n">
-        <v>36.36363636363637</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="AB40" t="n">
-        <v>12.33129410895796</v>
+        <v>10.90027840903963</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>0.2066560685337837</v>
       </c>
       <c r="AE40" t="n">
         <v>13</v>
@@ -4967,10 +4939,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C41" t="n">
-        <v>1.573637829953146</v>
+        <v>1.58727143832603</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4998,22 +4970,22 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>3.994858941003598</v>
+        <v>4.895844639623448</v>
       </c>
       <c r="L41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M41" t="n">
-        <v>58.33333333333334</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N41" t="n">
-        <v>18.43473608980998</v>
+        <v>18.77665382524726</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>5.774459545546518</v>
+        <v>4.86592712791647</v>
       </c>
       <c r="Q41" t="n">
         <v>10</v>
@@ -5040,7 +5012,7 @@
         <v>40.81782021738603</v>
       </c>
       <c r="Y41" t="n">
-        <v>19.29872200357227</v>
+        <v>18.59954612049928</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -5082,10 +5054,10 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C42" t="n">
-        <v>3.147275659906292</v>
+        <v>3.193476725237552</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5117,7 +5089,7 @@
         <v>22.36276267242437</v>
       </c>
       <c r="K42" t="n">
-        <v>2.397260273972601</v>
+        <v>3.900421427578271</v>
       </c>
       <c r="L42" t="n">
         <v>6</v>
@@ -5126,7 +5098,7 @@
         <v>100</v>
       </c>
       <c r="N42" t="n">
-        <v>13.23405911152248</v>
+        <v>13.52340132156805</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
@@ -5191,10 +5163,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C43" t="n">
-        <v>7.494515952686555</v>
+        <v>7.541906343839578</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5254,22 +5226,22 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>3.26583552690044</v>
+        <v>2.654152274615462</v>
       </c>
       <c r="Z43" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AA43" t="n">
-        <v>56.25</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="AB43" t="n">
-        <v>12.22985042288783</v>
+        <v>10.08100185628649</v>
       </c>
       <c r="AC43" t="n">
         <v>6</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.826472413332204</v>
+        <v>3.437072873229552</v>
       </c>
       <c r="AE43" t="n">
         <v>8</v>
@@ -5300,10 +5272,10 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C44" t="n">
-        <v>5.174584393338845</v>
+        <v>5.192029312865892</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5322,7 +5294,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %87.50: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -5335,22 +5307,22 @@
         <v>13.03201987649729</v>
       </c>
       <c r="K44" t="n">
-        <v>5.910007783291671</v>
+        <v>6.267058982469464</v>
       </c>
       <c r="L44" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M44" t="n">
-        <v>77.77777777777777</v>
+        <v>87.5</v>
       </c>
       <c r="N44" t="n">
-        <v>18.91879974651878</v>
+        <v>19.01122755073941</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>3.861761794104579</v>
+        <v>3.512792254979358</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5377,22 +5349,22 @@
         <v>12.1234692799834</v>
       </c>
       <c r="Y44" t="n">
-        <v>5.541624368735953</v>
+        <v>5.223179709940906</v>
       </c>
       <c r="Z44" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AA44" t="n">
-        <v>15.38461538461539</v>
+        <v>18.75</v>
       </c>
       <c r="AB44" t="n">
-        <v>8.55228327264183</v>
+        <v>7.420762629206091</v>
       </c>
       <c r="AC44" t="n">
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>4.719936799112601</v>
+        <v>5.040072325110612</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5402,10 +5374,10 @@
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK44" t="n">
-        <v>33.33333333333334</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45">
@@ -5415,10 +5387,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0206309713020313</v>
+        <v>0.02103739565924569</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5443,25 +5415,25 @@
         <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>10.57403875128903</v>
+        <v>10.51199238133264</v>
       </c>
       <c r="K45" t="n">
-        <v>1.030926772239371</v>
+        <v>3.021207737253273</v>
       </c>
       <c r="L45" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="M45" t="n">
-        <v>61.03896103896104</v>
+        <v>65.45454545454545</v>
       </c>
       <c r="N45" t="n">
-        <v>15.1445705774911</v>
+        <v>15.61808203515258</v>
       </c>
       <c r="O45" t="n">
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>8.877552165764268</v>
+        <v>6.774131672524697</v>
       </c>
       <c r="Q45" t="n">
         <v>37</v>
@@ -5524,10 +5496,10 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C46" t="n">
-        <v>8.389226424566271</v>
+        <v>8.530663939824125</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5555,22 +5527,22 @@
         <v>24.84932105129213</v>
       </c>
       <c r="K46" t="n">
-        <v>0.8860759493670933</v>
+        <v>2.586956958444331</v>
       </c>
       <c r="L46" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M46" t="n">
-        <v>60</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N46" t="n">
-        <v>12.41749205688389</v>
+        <v>11.66352812478545</v>
       </c>
       <c r="O46" t="n">
         <v>10</v>
       </c>
       <c r="P46" t="n">
-        <v>9.033877038895866</v>
+        <v>7.226106769653518</v>
       </c>
       <c r="Q46" t="n">
         <v>54</v>
@@ -5611,10 +5583,10 @@
         <v>58.97435897435897</v>
       </c>
       <c r="AG46" t="n">
-        <v>17.0218379070037</v>
+        <v>16.96892785409365</v>
       </c>
       <c r="AH46" t="n">
-        <v>41.95252106735527</v>
+        <v>42.00543112026533</v>
       </c>
       <c r="AI46" t="n">
         <v>43.41862288289698</v>
@@ -5633,10 +5605,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7881872668570162</v>
+        <v>0.8069945103214758</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5661,25 +5633,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>28.65609902232038</v>
+        <v>27.74248530779953</v>
       </c>
       <c r="K47" t="n">
-        <v>5.73893781612671</v>
+        <v>8.262015808887547</v>
       </c>
       <c r="L47" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M47" t="n">
-        <v>72.22222222222223</v>
+        <v>56.25</v>
       </c>
       <c r="N47" t="n">
-        <v>11.90651980820221</v>
+        <v>9.174193745483864</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>4.029794768019146</v>
+        <v>1.605349926404931</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5729,10 +5701,10 @@
         <v>42.22414699362943</v>
       </c>
       <c r="AJ47" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK47" t="n">
-        <v>52.56410256410256</v>
+        <v>53.24675324675324</v>
       </c>
     </row>
     <row r="48">
@@ -5742,10 +5714,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C48" t="n">
-        <v>0.06126135420456268</v>
+        <v>0.06184994450042606</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5762,11 +5734,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>5</v>
       </c>
@@ -5774,25 +5742,25 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>36.05053321517423</v>
+        <v>35.39957983385757</v>
       </c>
       <c r="K48" t="n">
-        <v>4.386458190842468</v>
+        <v>5.389388294305686</v>
       </c>
       <c r="L48" t="n">
         <v>5</v>
       </c>
       <c r="M48" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="N48" t="n">
-        <v>9.43803645849119</v>
+        <v>12.66074525724039</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>5.377653295693485</v>
+        <v>4.374834867452626</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5833,10 +5801,10 @@
         <v>60.37735849056604</v>
       </c>
       <c r="AG48" t="n">
-        <v>23.42012128370161</v>
+        <v>23.3257816610601</v>
       </c>
       <c r="AH48" t="n">
-        <v>36.95723720686443</v>
+        <v>37.05157682950594</v>
       </c>
       <c r="AI48" t="n">
         <v>46.94147867320552</v>
@@ -5855,19 +5823,19 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C49" t="n">
-        <v>0.262518584139103</v>
+        <v>0.2699097846251305</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5886,22 +5854,22 @@
         <v>24.46536626635938</v>
       </c>
       <c r="K49" t="n">
-        <v>3.888686127562191</v>
+        <v>6.813668029003206</v>
       </c>
       <c r="L49" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M49" t="n">
-        <v>56.25</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N49" t="n">
-        <v>12.53629562180559</v>
+        <v>11.48773357364777</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>1.069715975686969</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>53</v>
@@ -5964,10 +5932,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7271364828672704</v>
+        <v>0.7333636255141159</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5992,25 +5960,25 @@
         <v>10</v>
       </c>
       <c r="J50" t="n">
-        <v>12.2094861546159</v>
+        <v>11.86078125763058</v>
       </c>
       <c r="K50" t="n">
-        <v>1.76783239310343</v>
+        <v>2.639364525108689</v>
       </c>
       <c r="L50" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M50" t="n">
-        <v>46.7741935483871</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N50" t="n">
-        <v>13.92523339466475</v>
+        <v>12.72852381361679</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>2.193392110656611</v>
+        <v>1.325646822918958</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6073,10 +6041,10 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1810473034860125</v>
+        <v>0.1821838432534583</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6095,7 +6063,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -6108,16 +6076,16 @@
         <v>27.30972539236674</v>
       </c>
       <c r="K51" t="n">
-        <v>4.935236810370625</v>
+        <v>5.593976638829568</v>
       </c>
       <c r="L51" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M51" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N51" t="n">
-        <v>17.95969937536291</v>
+        <v>19.55687804064408</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
@@ -6150,7 +6118,7 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>17.81079079536082</v>
+        <v>17.29484107991414</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6192,10 +6160,10 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C52" t="n">
-        <v>4.145140857773695</v>
+        <v>4.165404340530646</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6227,50 +6195,50 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="R52" t="n">
-        <v>56.66666666666666</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="S52" t="n">
-        <v>31.9621842201604</v>
+        <v>36.84351968588739</v>
       </c>
       <c r="T52" t="n">
-        <v>24.70448244650627</v>
+        <v>24.26759142522372</v>
       </c>
       <c r="U52" t="n">
-        <v>39.19730700081361</v>
+        <v>44.86445909660515</v>
       </c>
       <c r="V52" t="n">
         <v>55</v>
       </c>
       <c r="W52" t="n">
-        <v>63.63636363636363</v>
+        <v>69.09090909090909</v>
       </c>
       <c r="X52" t="n">
         <v>12.1710603868542</v>
       </c>
       <c r="Y52" t="n">
-        <v>4.890073098508152</v>
+        <v>4.425129100243563</v>
       </c>
       <c r="Z52" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AA52" t="n">
-        <v>51.85185185185185</v>
+        <v>46.875</v>
       </c>
       <c r="AB52" t="n">
-        <v>13.44360014086126</v>
+        <v>13.28027921400272</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.269823669103322</v>
+        <v>3.740387892865615</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6279,10 +6247,10 @@
         <v>68.42105263157895</v>
       </c>
       <c r="AG52" t="n">
-        <v>36.62274507751766</v>
+        <v>36.35958718278081</v>
       </c>
       <c r="AH52" t="n">
-        <v>31.79830755406129</v>
+        <v>32.06146544879813</v>
       </c>
       <c r="AI52" t="n">
         <v>52.54424010939046</v>
@@ -6301,10 +6269,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C53" t="n">
-        <v>1.543112478062354</v>
+        <v>1.552559863816388</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6332,7 +6300,7 @@
         <v>27.64453042428524</v>
       </c>
       <c r="K53" t="n">
-        <v>0.0682635494880568</v>
+        <v>0.6809107161258598</v>
       </c>
       <c r="L53" t="n">
         <v>10</v>
@@ -6347,7 +6315,7 @@
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>7.926325659272937</v>
+        <v>7.269589867448301</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6378,7 +6346,7 @@
       <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AD53" t="inlineStr"/>
       <c r="AE53" t="n">
@@ -6389,10 +6357,10 @@
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="inlineStr"/>
       <c r="AJ53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK53" t="n">
-        <v>83.33333333333333</v>
+        <v>71.42857142857143</v>
       </c>
     </row>
     <row r="54">
@@ -6402,10 +6370,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C54" t="n">
-        <v>0.09704977392183173</v>
+        <v>0.09466828046660558</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6433,7 +6401,7 @@
         <v>42.39442432818535</v>
       </c>
       <c r="K54" t="n">
-        <v>20.06653654879791</v>
+        <v>17.12023735171848</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -6471,7 +6439,7 @@
         <v>114.7400208810756</v>
       </c>
       <c r="Y54" t="n">
-        <v>30.83498043185524</v>
+        <v>32.5322130453469</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -6513,24 +6481,24 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8673428734452758</v>
+        <v>0.8747349500098697</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -6544,49 +6512,49 @@
         <v>11.62878088168478</v>
       </c>
       <c r="K55" t="n">
-        <v>2.58964370987167</v>
+        <v>3.463981326811383</v>
       </c>
       <c r="L55" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="M55" t="n">
-        <v>64.61538461538461</v>
+        <v>66.12903225806451</v>
       </c>
       <c r="N55" t="n">
-        <v>13.36138772136001</v>
+        <v>12.14663030481262</v>
       </c>
       <c r="O55" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.451112590746063</v>
       </c>
       <c r="Q55" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R55" t="n">
-        <v>72.09302325581395</v>
+        <v>70.45454545454545</v>
       </c>
       <c r="S55" t="n">
-        <v>54.67715886916449</v>
+        <v>58.62867820553725</v>
       </c>
       <c r="T55" t="n">
-        <v>17.41586438664945</v>
+        <v>11.8258672490082</v>
       </c>
       <c r="U55" t="n">
-        <v>57.30897131812112</v>
+        <v>55.77979987383978</v>
       </c>
       <c r="V55" t="n">
         <v>78</v>
       </c>
       <c r="W55" t="n">
-        <v>70.51282051282051</v>
+        <v>73.07692307692308</v>
       </c>
       <c r="X55" t="n">
         <v>25.41488056506582</v>
       </c>
       <c r="Y55" t="n">
-        <v>9.340281164450403</v>
+        <v>8.567618353150774</v>
       </c>
       <c r="Z55" t="n">
         <v>16</v>
@@ -6595,7 +6563,7 @@
         <v>50</v>
       </c>
       <c r="AB55" t="n">
-        <v>10.78082928863532</v>
+        <v>10.86223550521618</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6610,10 +6578,10 @@
         <v>53.19148936170212</v>
       </c>
       <c r="AG55" t="n">
-        <v>40.7661853155541</v>
+        <v>40.70451402354052</v>
       </c>
       <c r="AH55" t="n">
-        <v>12.42530404614803</v>
+        <v>12.48697533816161</v>
       </c>
       <c r="AI55" t="n">
         <v>39.23238322019481</v>
@@ -6632,10 +6600,10 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C56" t="n">
-        <v>3.275693056052178</v>
+        <v>0.9757144331858283</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6660,10 +6628,10 @@
         <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>30.29575178666555</v>
+        <v>30.29575178666554</v>
       </c>
       <c r="K56" t="n">
-        <v>10.63291795373509</v>
+        <v>10.55611060323638</v>
       </c>
       <c r="L56" t="n">
         <v>2</v>
@@ -6690,10 +6658,10 @@
         <v>100</v>
       </c>
       <c r="X56" t="n">
-        <v>17.75189696236841</v>
+        <v>17.75189696236843</v>
       </c>
       <c r="Y56" t="n">
-        <v>6.045744648095508</v>
+        <v>6.11097276966307</v>
       </c>
       <c r="Z56" t="n">
         <v>8</v>
@@ -6708,7 +6676,7 @@
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>4.208702774657603</v>
+        <v>4.142153076946919</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6731,10 +6699,10 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C57" t="n">
-        <v>1.492587619415972</v>
+        <v>1.459995290938866</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6762,10 +6730,10 @@
         <v>32.76213282665623</v>
       </c>
       <c r="K57" t="n">
-        <v>27.80613468767126</v>
+        <v>25.01534407079624</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -6800,16 +6768,16 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>7.981148382269598</v>
+        <v>9.990483445081322</v>
       </c>
       <c r="Z57" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AA57" t="n">
-        <v>50</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB57" t="n">
-        <v>14.96901650574739</v>
+        <v>13.75807019707077</v>
       </c>
       <c r="AC57" t="n">
         <v>6</v>
@@ -6846,10 +6814,10 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7768192419122002</v>
+        <v>0.7809081043611865</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6866,7 +6834,11 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6874,25 +6846,25 @@
         <v>10</v>
       </c>
       <c r="J58" t="n">
-        <v>12.62277775428285</v>
+        <v>13.34780199539933</v>
       </c>
       <c r="K58" t="n">
-        <v>0.271745358872999</v>
+        <v>1.642931167695849</v>
       </c>
       <c r="L58" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="M58" t="n">
-        <v>72.72727272727273</v>
+        <v>75</v>
       </c>
       <c r="N58" t="n">
-        <v>16.93858212044188</v>
+        <v>18.31342452521605</v>
       </c>
       <c r="O58" t="n">
         <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>4.715440650010194</v>
+        <v>3.302806003071179</v>
       </c>
       <c r="Q58" t="n">
         <v>24</v>
@@ -6919,7 +6891,7 @@
         <v>41.32985472592288</v>
       </c>
       <c r="Y58" t="n">
-        <v>12.38533420811797</v>
+        <v>11.92416602688824</v>
       </c>
       <c r="Z58" t="n">
         <v>1</v>
@@ -6961,10 +6933,10 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8235546518257472</v>
+        <v>0.8229828956796779</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6992,22 +6964,22 @@
         <v>12.06710605756499</v>
       </c>
       <c r="K59" t="n">
-        <v>3.094130713183008</v>
+        <v>3.022557196199949</v>
       </c>
       <c r="L59" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M59" t="n">
-        <v>68.42105263157895</v>
+        <v>69.49152542372882</v>
       </c>
       <c r="N59" t="n">
-        <v>13.52119263018851</v>
+        <v>13.36391853238126</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>4.758631022813087</v>
+        <v>4.831410653417234</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7034,16 +7006,16 @@
         <v>10.2478061424703</v>
       </c>
       <c r="Y59" t="n">
-        <v>6.488723612370828</v>
+        <v>6.553644194001784</v>
       </c>
       <c r="Z59" t="n">
         <v>23</v>
       </c>
       <c r="AA59" t="n">
-        <v>47.82608695652174</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="AB59" t="n">
-        <v>16.13404301226775</v>
+        <v>16.81170246459129</v>
       </c>
       <c r="AC59" t="n">
         <v>6</v>
@@ -7080,10 +7052,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C60" t="n">
-        <v>13.1680329449591</v>
+        <v>13.29563405664327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7111,43 +7083,43 @@
         <v>17.06238107085701</v>
       </c>
       <c r="K60" t="n">
-        <v>3.630982958483164</v>
+        <v>4.635189789199501</v>
       </c>
       <c r="L60" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="M60" t="n">
-        <v>42.85714285714285</v>
+        <v>48.38709677419355</v>
       </c>
       <c r="N60" t="n">
-        <v>11.69086490015707</v>
+        <v>12.4349075064265</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>4.215937084440435</v>
+        <v>3.215753913744823</v>
       </c>
       <c r="Q60" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R60" t="n">
-        <v>67.39130434782609</v>
+        <v>65.95744680851064</v>
       </c>
       <c r="S60" t="n">
-        <v>50.97325605675668</v>
+        <v>50.84616550235759</v>
       </c>
       <c r="T60" t="n">
-        <v>16.41804829106942</v>
+        <v>15.11128130615305</v>
       </c>
       <c r="U60" t="n">
-        <v>52.96773241932241</v>
+        <v>51.67092456194193</v>
       </c>
       <c r="V60" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="W60" t="n">
-        <v>70.96774193548387</v>
+        <v>69.84126984126983</v>
       </c>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
@@ -7189,10 +7161,10 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C61" t="n">
-        <v>0.648822975669943</v>
+        <v>0.6551044879960993</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7217,25 +7189,25 @@
         <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>40.00382173229804</v>
+        <v>39.02052765309554</v>
       </c>
       <c r="K61" t="n">
-        <v>4.758666234510756</v>
+        <v>5.772876393366988</v>
       </c>
       <c r="L61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M61" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="N61" t="n">
-        <v>38.6612144818804</v>
+        <v>48.06650734995709</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>5.003245988027483</v>
+        <v>3.996415480763171</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7290,10 +7262,10 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C62" t="n">
-        <v>8.52606449673611</v>
+        <v>8.593776126801863</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7321,22 +7293,22 @@
         <v>15.79076798430271</v>
       </c>
       <c r="K62" t="n">
-        <v>2.466420005153247</v>
+        <v>3.280179780042003</v>
       </c>
       <c r="L62" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M62" t="n">
-        <v>62.22222222222222</v>
+        <v>67.39130434782609</v>
       </c>
       <c r="N62" t="n">
-        <v>14.33151242201165</v>
+        <v>14.45431345993661</v>
       </c>
       <c r="O62" t="n">
         <v>6</v>
       </c>
       <c r="P62" t="n">
-        <v>3.448524887147464</v>
+        <v>2.633438696321466</v>
       </c>
       <c r="Q62" t="n">
         <v>29</v>
@@ -7399,10 +7371,10 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1037864111592051</v>
+        <v>0.104135104516161</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7427,10 +7399,10 @@
         <v>10</v>
       </c>
       <c r="J63" t="n">
-        <v>34.29674249354652</v>
+        <v>33.30512547687425</v>
       </c>
       <c r="K63" t="n">
-        <v>4.008440278890557</v>
+        <v>4.357879591682301</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
@@ -7441,7 +7413,7 @@
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>0.953345438553499</v>
+        <v>0.615306108968583</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7504,24 +7476,24 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1650477702057303</v>
+        <v>0.1670369227966545</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AL_BEKLE_EŞİK</t>
-        </is>
-      </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -7535,22 +7507,22 @@
         <v>21.14278085376978</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1277168595424483</v>
+        <v>1.334454200896529</v>
       </c>
       <c r="L64" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M64" t="n">
-        <v>62.5</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N64" t="n">
-        <v>14.63450155664174</v>
+        <v>14.42105333595837</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.866068350776764</v>
+        <v>3.617274921949543</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7559,10 +7531,10 @@
         <v>70.37037037037037</v>
       </c>
       <c r="S64" t="n">
-        <v>74.52373898919379</v>
+        <v>73.86269274864564</v>
       </c>
       <c r="T64" t="n">
-        <v>-4.153368618823421</v>
+        <v>-3.492322378275276</v>
       </c>
       <c r="U64" t="n">
         <v>57.17242709884697</v>
@@ -7573,17 +7545,27 @@
       <c r="W64" t="n">
         <v>71.84466019417475</v>
       </c>
-      <c r="X64" t="inlineStr"/>
-      <c r="Y64" t="inlineStr"/>
+      <c r="X64" t="n">
+        <v>11.49424813787225</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>9.112392887220743</v>
+      </c>
       <c r="Z64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA64" t="inlineStr"/>
-      <c r="AB64" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>17.18726889310038</v>
+      </c>
       <c r="AC64" t="n">
         <v>2</v>
       </c>
-      <c r="AD64" t="inlineStr"/>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
       <c r="AE64" t="n">
         <v>54</v>
       </c>
@@ -7591,10 +7573,10 @@
         <v>59.25925925925926</v>
       </c>
       <c r="AG64" t="n">
-        <v>38.10864571025153</v>
+        <v>37.92255864916446</v>
       </c>
       <c r="AH64" t="n">
-        <v>21.15061354900773</v>
+        <v>21.33670061009479</v>
       </c>
       <c r="AI64" t="n">
         <v>45.96684934349057</v>
@@ -7613,10 +7595,10 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C65" t="n">
-        <v>6.420863386430897</v>
+        <v>6.184994323818231</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7633,7 +7615,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %82.35: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H65" t="n">
         <v>5</v>
       </c>
@@ -7641,25 +7627,25 @@
         <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>24.62463409641153</v>
+        <v>28.12426974452364</v>
       </c>
       <c r="K65" t="n">
-        <v>0.8807898736318265</v>
+        <v>1.906412478336228</v>
       </c>
       <c r="L65" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M65" t="n">
-        <v>70</v>
+        <v>82.35294117647059</v>
       </c>
       <c r="N65" t="n">
-        <v>12.10738652377501</v>
+        <v>15.35336073609163</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>9.039590330122671</v>
+        <v>7.942176870748296</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7668,10 +7654,10 @@
         <v>68</v>
       </c>
       <c r="S65" t="n">
-        <v>45.44970347936523</v>
+        <v>45.47819350785525</v>
       </c>
       <c r="T65" t="n">
-        <v>22.55029652063477</v>
+        <v>22.52180649214475</v>
       </c>
       <c r="U65" t="n">
         <v>54.18970269185592</v>
@@ -7722,10 +7708,10 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4273558093924296</v>
+        <v>0.4337911161650584</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7750,25 +7736,25 @@
         <v>10</v>
       </c>
       <c r="J66" t="n">
-        <v>11.63994709715769</v>
+        <v>11.2547528069613</v>
       </c>
       <c r="K66" t="n">
-        <v>2.422934164415214</v>
+        <v>3.965262564812644</v>
       </c>
       <c r="L66" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="M66" t="n">
         <v>50</v>
       </c>
       <c r="N66" t="n">
-        <v>18.7588075265043</v>
+        <v>18.77237618853692</v>
       </c>
       <c r="O66" t="n">
         <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>3.492446164296248</v>
+        <v>1.957132012165008</v>
       </c>
       <c r="Q66" t="n">
         <v>35</v>
@@ -7831,10 +7817,10 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02778865570862936</v>
+        <v>0.02819011081451109</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7859,25 +7845,25 @@
         <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>18.46026050404527</v>
+        <v>17.88062675770013</v>
       </c>
       <c r="K67" t="n">
-        <v>0.7633672105359146</v>
+        <v>2.219068007172265</v>
       </c>
       <c r="L67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M67" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N67" t="n">
-        <v>11.81759600692333</v>
+        <v>13.30779001380697</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>3.212112575298764</v>
+        <v>1.742269840205135</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7920,10 +7906,10 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C68" t="n">
-        <v>3.263061720973079</v>
+        <v>3.191372857343514</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7932,7 +7918,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7947,17 +7933,27 @@
       <c r="I68" t="n">
         <v>10</v>
       </c>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+      <c r="J68" t="n">
+        <v>12.46006389776357</v>
+      </c>
+      <c r="K68" t="n">
+        <v>10.65305008314123</v>
+      </c>
       <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="M68" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="N68" t="n">
+        <v>13.04645653865888</v>
+      </c>
       <c r="O68" t="n">
         <v>2</v>
       </c>
-      <c r="P68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
       <c r="Q68" t="n">
         <v>5</v>
       </c>
@@ -7983,7 +7979,7 @@
         <v>83.80957438533017</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.9584664536741117</v>
+        <v>3.134390662042497</v>
       </c>
       <c r="Z68" t="n">
         <v>1</v>
@@ -7994,7 +7990,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>7.109677419354843</v>
+        <v>5.02305139172946</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8025,19 +8021,19 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C69" t="n">
-        <v>0.3999882109579903</v>
+        <v>0.4043387300548991</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -8045,11 +8041,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>5</v>
       </c>
@@ -8060,22 +8052,22 @@
         <v>29.4573350207784</v>
       </c>
       <c r="K69" t="n">
-        <v>2.315564443609319</v>
+        <v>3.428411784676744</v>
       </c>
       <c r="L69" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M69" t="n">
-        <v>80</v>
+        <v>62.5</v>
       </c>
       <c r="N69" t="n">
-        <v>16.19449547156433</v>
+        <v>15.74456577461902</v>
       </c>
       <c r="O69" t="n">
         <v>3</v>
       </c>
       <c r="P69" t="n">
-        <v>0.6689456878947286</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8122,10 +8114,10 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4025144699740459</v>
+        <v>0.3988690023448942</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8150,25 +8142,25 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>19.88694746486775</v>
+        <v>19.94256627542972</v>
       </c>
       <c r="K70" t="n">
-        <v>2.245989641339441</v>
+        <v>1.390365291086737</v>
       </c>
       <c r="L70" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M70" t="n">
-        <v>44</v>
+        <v>51.72413793103448</v>
       </c>
       <c r="N70" t="n">
-        <v>11.38277499878724</v>
+        <v>14.53893495737219</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>5.627614715104823</v>
+        <v>6.518996839529412</v>
       </c>
       <c r="Q70" t="n">
         <v>30</v>
@@ -8218,10 +8210,10 @@
         <v>34.61744754671859</v>
       </c>
       <c r="AJ70" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AK70" t="n">
-        <v>48.27586206896552</v>
+        <v>49.12280701754386</v>
       </c>
     </row>
     <row r="71">
@@ -8231,10 +8223,10 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C71" t="n">
-        <v>3.220957698766975</v>
+        <v>3.317597231298988</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8253,7 +8245,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %82.14: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -8263,25 +8255,25 @@
         <v>10</v>
       </c>
       <c r="J71" t="n">
-        <v>21.94103653262863</v>
+        <v>21.33797260620418</v>
       </c>
       <c r="K71" t="n">
-        <v>2.814294281332996</v>
+        <v>5.899067900297461</v>
       </c>
       <c r="L71" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M71" t="n">
-        <v>82.14285714285714</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="N71" t="n">
-        <v>12.44656920241869</v>
+        <v>11.1036158799086</v>
       </c>
       <c r="O71" t="n">
         <v>6</v>
       </c>
       <c r="P71" t="n">
-        <v>3.098504678687863</v>
+        <v>0.09530971490472329</v>
       </c>
       <c r="Q71" t="n">
         <v>43</v>
@@ -8322,10 +8314,10 @@
         <v>54.83870967741935</v>
       </c>
       <c r="AG71" t="n">
-        <v>14.73735711723767</v>
+        <v>14.78870579909084</v>
       </c>
       <c r="AH71" t="n">
-        <v>40.10135256018168</v>
+        <v>40.05000387832852</v>
       </c>
       <c r="AI71" t="n">
         <v>37.77216763735451</v>
@@ -8344,10 +8336,10 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07347151896017202</v>
+        <v>0.07363088480735989</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8364,11 +8356,7 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>5</v>
       </c>
@@ -8379,16 +8367,16 @@
         <v>29.15235727667785</v>
       </c>
       <c r="K72" t="n">
-        <v>12.81610002443463</v>
+        <v>13.06080754663206</v>
       </c>
       <c r="L72" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M72" t="n">
-        <v>75</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N72" t="n">
-        <v>16.91845715896132</v>
+        <v>17.1591378756031</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
@@ -8421,7 +8409,7 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>18.20147984426843</v>
+        <v>18.0240520375778</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -8463,10 +8451,10 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07178735975608873</v>
+        <v>0.07257901607626739</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8483,7 +8471,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H73" t="n">
         <v>5</v>
       </c>
@@ -8494,22 +8486,22 @@
         <v>20.52993807340809</v>
       </c>
       <c r="K73" t="n">
-        <v>2.095813828929116</v>
+        <v>3.221705581405776</v>
       </c>
       <c r="L73" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="M73" t="n">
-        <v>72.72727272727273</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="N73" t="n">
-        <v>12.99141199558474</v>
+        <v>15.61518280627299</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>7.741929737016529</v>
+        <v>6.566733595821606</v>
       </c>
       <c r="Q73" t="n">
         <v>12</v>
@@ -8572,10 +8564,10 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C74" t="n">
-        <v>5.084060681387087</v>
+        <v>5.124709710920363</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8603,22 +8595,22 @@
         <v>17.41018086324394</v>
       </c>
       <c r="K74" t="n">
-        <v>6.327323019235687</v>
+        <v>7.177451049655614</v>
       </c>
       <c r="L74" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="M74" t="n">
-        <v>57.14285714285715</v>
+        <v>65.21739130434783</v>
       </c>
       <c r="N74" t="n">
-        <v>20.95563015685226</v>
+        <v>22.39330437546893</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>1.573139371205379</v>
+        <v>0.7674645574126338</v>
       </c>
       <c r="Q74" t="n">
         <v>35</v>
@@ -8645,7 +8637,7 @@
         <v>95.98093909010421</v>
       </c>
       <c r="Y74" t="n">
-        <v>12.18445622545886</v>
+        <v>11.48233702270417</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
@@ -8687,19 +8679,19 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1381011915729012</v>
+        <v>0.138426061754845</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8722,7 +8714,7 @@
         <v>19.1703426786477</v>
       </c>
       <c r="K75" t="n">
-        <v>5.97738087905606</v>
+        <v>6.226682790328297</v>
       </c>
       <c r="L75" t="n">
         <v>3</v>
@@ -8737,7 +8729,7 @@
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>0.02134334775620861</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8800,10 +8792,10 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C76" t="n">
-        <v>1.778894938207904</v>
+        <v>1.824994073439563</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8828,25 +8820,25 @@
         <v>10</v>
       </c>
       <c r="J76" t="n">
-        <v>21.50878665648681</v>
+        <v>21.37762355327298</v>
       </c>
       <c r="K76" t="n">
-        <v>2.638314383068185</v>
+        <v>5.298132809141887</v>
       </c>
       <c r="L76" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="M76" t="n">
-        <v>63.63636363636363</v>
+        <v>62.5</v>
       </c>
       <c r="N76" t="n">
-        <v>11.89453471173047</v>
+        <v>12.11418143995526</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>7.172453738334439</v>
+        <v>4.465290186465598</v>
       </c>
       <c r="Q76" t="n">
         <v>42</v>
@@ -8855,10 +8847,10 @@
         <v>64.28571428571429</v>
       </c>
       <c r="S76" t="n">
-        <v>29.15803201671905</v>
+        <v>29.26507262252812</v>
       </c>
       <c r="T76" t="n">
-        <v>35.12768226899524</v>
+        <v>35.02064166318617</v>
       </c>
       <c r="U76" t="n">
         <v>49.16636571945582</v>
@@ -8909,10 +8901,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C77" t="n">
-        <v>0.500195788650481</v>
+        <v>0.5124709710920362</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8940,16 +8932,16 @@
         <v>22.11886481778794</v>
       </c>
       <c r="K77" t="n">
-        <v>3.018341919589784</v>
+        <v>5.546489838030411</v>
       </c>
       <c r="L77" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M77" t="n">
-        <v>65.38461538461539</v>
+        <v>70.83333333333333</v>
       </c>
       <c r="N77" t="n">
-        <v>20.13004691355972</v>
+        <v>16.85356364151541</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -8964,10 +8956,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="S77" t="n">
-        <v>39.01412091389712</v>
+        <v>39.11478618000358</v>
       </c>
       <c r="T77" t="n">
-        <v>18.12873622896002</v>
+        <v>18.02807096285357</v>
       </c>
       <c r="U77" t="n">
         <v>39.07078562746877</v>
@@ -8996,10 +8988,10 @@
         <v>50</v>
       </c>
       <c r="AG77" t="n">
-        <v>25.48896966546818</v>
+        <v>25.49777093285068</v>
       </c>
       <c r="AH77" t="n">
-        <v>24.51103033453182</v>
+        <v>24.50222906714932</v>
       </c>
       <c r="AI77" t="n">
         <v>36.11893708270325</v>
@@ -9018,31 +9010,27 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05199846805609908</v>
+        <v>0.05280386289433271</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>5</v>
       </c>
@@ -9050,19 +9038,19 @@
         <v>10</v>
       </c>
       <c r="J78" t="n">
-        <v>20.97958707767719</v>
+        <v>20.92476038411055</v>
       </c>
       <c r="K78" t="n">
-        <v>10.27462966115</v>
+        <v>11.98265339410685</v>
       </c>
       <c r="L78" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="M78" t="n">
-        <v>75</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N78" t="n">
-        <v>18.73221693929225</v>
+        <v>18.16221833390237</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
@@ -9095,22 +9083,22 @@
         <v>23.16536029857119</v>
       </c>
       <c r="Y78" t="n">
-        <v>10.46619813084794</v>
+        <v>9.079425316790202</v>
       </c>
       <c r="Z78" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AA78" t="n">
-        <v>38.46153846153846</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="AB78" t="n">
-        <v>8.780932770684695</v>
+        <v>16.34038047129173</v>
       </c>
       <c r="AC78" t="n">
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>0</v>
+        <v>1.0125042504596</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9141,10 +9129,10 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8787109788087741</v>
+        <v>0.8898818203976717</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9169,25 +9157,25 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>16.73024428816069</v>
+        <v>14.97695523729659</v>
       </c>
       <c r="K79" t="n">
-        <v>1.755244300160586</v>
+        <v>3.048834277217249</v>
       </c>
       <c r="L79" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M79" t="n">
-        <v>60.46511627906977</v>
+        <v>44.68085106382978</v>
       </c>
       <c r="N79" t="n">
-        <v>13.60227008828606</v>
+        <v>11.56750774009771</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>3.188784737490225</v>
+        <v>1.893437937913811</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9228,10 +9216,10 @@
         <v>55.26315789473684</v>
       </c>
       <c r="AG79" t="n">
-        <v>26.81224337856242</v>
+        <v>26.48329601014137</v>
       </c>
       <c r="AH79" t="n">
-        <v>28.45091451617442</v>
+        <v>28.77986188459547</v>
       </c>
       <c r="AI79" t="n">
         <v>39.70629712199248</v>
@@ -9250,10 +9238,10 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C80" t="n">
-        <v>0.146732512967351</v>
+        <v>0.13295634414279</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9278,10 +9266,10 @@
         <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>65.44295223334754</v>
+        <v>68.88556557298216</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>0.6369420169175521</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9292,7 +9280,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>10.00000000000001</v>
+        <v>9.303798183283906</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9355,14 +9343,14 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C81" t="n">
-        <v>1.073652566255658</v>
+        <v>1.084477730245694</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9386,7 +9374,7 @@
         <v>11.07045147382514</v>
       </c>
       <c r="K81" t="n">
-        <v>1.391651631364921</v>
+        <v>2.413938813109318</v>
       </c>
       <c r="L81" t="n">
         <v>48</v>
@@ -9395,13 +9383,13 @@
         <v>54.16666666666666</v>
       </c>
       <c r="N81" t="n">
-        <v>11.39001113621812</v>
+        <v>12.30981727638644</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>8.490194439215681</v>
+        <v>7.407254593277735</v>
       </c>
       <c r="Q81" t="n">
         <v>31</v>
@@ -9428,22 +9416,22 @@
         <v>27.31228182970742</v>
       </c>
       <c r="Y81" t="n">
-        <v>9.832861960995166</v>
+        <v>8.923746585628923</v>
       </c>
       <c r="Z81" t="n">
         <v>9</v>
       </c>
       <c r="AA81" t="n">
-        <v>55.55555555555556</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB81" t="n">
-        <v>9.529724010146259</v>
+        <v>11.50734464839207</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.1853646934346864</v>
+        <v>1.181705849794268</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9474,10 +9462,10 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C82" t="n">
-        <v>5.117744027569239</v>
+        <v>5.105775862334871</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9505,7 +9493,7 @@
         <v>17.26584051182517</v>
       </c>
       <c r="K82" t="n">
-        <v>12.572754224857</v>
+        <v>12.30949578203666</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
@@ -9547,7 +9535,7 @@
         <v>15.04024401260009</v>
       </c>
       <c r="Y82" t="n">
-        <v>2.144892692919553</v>
+        <v>2.373732995789124</v>
       </c>
       <c r="Z82" t="n">
         <v>11</v>
@@ -9562,7 +9550,7 @@
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>1.895769529186564</v>
+        <v>1.665808858737505</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9593,10 +9581,10 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C83" t="n">
-        <v>5.720884017254414</v>
+        <v>5.911508180248037</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9621,25 +9609,25 @@
         <v>10</v>
       </c>
       <c r="J83" t="n">
-        <v>17.35592939855059</v>
+        <v>15.63345941387357</v>
       </c>
       <c r="K83" t="n">
-        <v>5.701701725979591</v>
+        <v>9.223762015568671</v>
       </c>
       <c r="L83" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="M83" t="n">
-        <v>59.45945945945946</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N83" t="n">
-        <v>12.17224449245908</v>
+        <v>10.57317693140836</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>4.06644188677614</v>
+        <v>0.710685999188243</v>
       </c>
       <c r="Q83" t="n">
         <v>44</v>
@@ -9648,10 +9636,10 @@
         <v>63.63636363636363</v>
       </c>
       <c r="S83" t="n">
-        <v>55.48442273100814</v>
+        <v>55.17171937866284</v>
       </c>
       <c r="T83" t="n">
-        <v>8.151940905355495</v>
+        <v>8.464644257700797</v>
       </c>
       <c r="U83" t="n">
         <v>48.86637687904344</v>
@@ -9702,10 +9690,10 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C84" t="n">
-        <v>2.104148445541426</v>
+        <v>2.128984376551607</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9730,25 +9718,25 @@
         <v>10</v>
       </c>
       <c r="J84" t="n">
-        <v>16.33687114000013</v>
+        <v>15.40292259784146</v>
       </c>
       <c r="K84" t="n">
-        <v>0.7309549522502179</v>
+        <v>1.919914340113182</v>
       </c>
       <c r="L84" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="M84" t="n">
-        <v>63.1578947368421</v>
+        <v>60.41666666666666</v>
       </c>
       <c r="N84" t="n">
-        <v>12.5966385525712</v>
+        <v>13.04640963468292</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>4.238066689403919</v>
+        <v>3.022064608108277</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9779,29 +9767,29 @@
       <c r="AA84" t="inlineStr"/>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD84" t="inlineStr"/>
       <c r="AE84" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF84" t="n">
-        <v>45</v>
+        <v>41.02564102564103</v>
       </c>
       <c r="AG84" t="n">
-        <v>29.28345209410173</v>
+        <v>26.40911098078695</v>
       </c>
       <c r="AH84" t="n">
-        <v>15.71654790589827</v>
+        <v>14.61653004485408</v>
       </c>
       <c r="AI84" t="n">
-        <v>30.70530781090492</v>
+        <v>27.07931000072518</v>
       </c>
       <c r="AJ84" t="n">
         <v>59</v>
       </c>
       <c r="AK84" t="n">
-        <v>50.84745762711864</v>
+        <v>45.76271186440678</v>
       </c>
     </row>
     <row r="85">
@@ -9811,10 +9799,10 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C85" t="n">
-        <v>6.610331486358366</v>
+        <v>6.758263355532677</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9842,22 +9830,22 @@
         <v>15.13449360257271</v>
       </c>
       <c r="K85" t="n">
-        <v>2.581708173913877</v>
+        <v>4.877372750581066</v>
       </c>
       <c r="L85" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M85" t="n">
-        <v>55.10204081632653</v>
+        <v>60.97560975609756</v>
       </c>
       <c r="N85" t="n">
-        <v>13.0699515953862</v>
+        <v>13.03001069684921</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>5.281927862714197</v>
+        <v>2.977407964676204</v>
       </c>
       <c r="Q85" t="n">
         <v>34</v>
@@ -9920,10 +9908,10 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C86" t="n">
-        <v>3.252535715421553</v>
+        <v>3.309182401363403</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9980,25 +9968,25 @@
         <v>68.35443037974683</v>
       </c>
       <c r="X86" t="n">
-        <v>27.76399696217335</v>
+        <v>29.73457526325705</v>
       </c>
       <c r="Y86" t="n">
-        <v>0.3225806451612967</v>
+        <v>0.1269821904761992</v>
       </c>
       <c r="Z86" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA86" t="n">
-        <v>44</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="AB86" t="n">
-        <v>13.86001431575128</v>
+        <v>12.51003871173557</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>5.695792880258899</v>
+        <v>5.880484978159695</v>
       </c>
       <c r="AE86" t="n">
         <v>51</v>
@@ -10029,10 +10017,10 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C87" t="n">
-        <v>5.736673025581704</v>
+        <v>5.727430968229638</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10064,7 +10052,7 @@
         <v>29.54558799520699</v>
       </c>
       <c r="K87" t="n">
-        <v>5.6201550387597</v>
+        <v>5.449995867049995</v>
       </c>
       <c r="L87" t="n">
         <v>6</v>
@@ -10073,7 +10061,7 @@
         <v>83.33333333333333</v>
       </c>
       <c r="N87" t="n">
-        <v>8.337490203764601</v>
+        <v>9.497966602573221</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
@@ -10120,10 +10108,10 @@
         <v>53.19148936170212</v>
       </c>
       <c r="AG87" t="n">
-        <v>46.21705077683674</v>
+        <v>45.96992190329986</v>
       </c>
       <c r="AH87" t="n">
-        <v>6.974438584865389</v>
+        <v>7.221567458402262</v>
       </c>
       <c r="AI87" t="n">
         <v>39.23238322019481</v>
@@ -10142,10 +10130,10 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9296568071529799</v>
+        <v>0.9344810766852593</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10164,7 +10152,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %82.76: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %82.14: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H88" t="n">
@@ -10177,22 +10165,22 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>4.150939284176003</v>
+        <v>4.691409917296685</v>
       </c>
       <c r="L88" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M88" t="n">
-        <v>82.75862068965517</v>
+        <v>82.14285714285714</v>
       </c>
       <c r="N88" t="n">
-        <v>13.0696020440587</v>
+        <v>12.25028825824852</v>
       </c>
       <c r="O88" t="n">
         <v>10</v>
       </c>
       <c r="P88" t="n">
-        <v>5.615946198876642</v>
+        <v>5.070702636345192</v>
       </c>
       <c r="Q88" t="n">
         <v>44</v>
@@ -10255,10 +10243,10 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C89" t="n">
-        <v>1.914680345613957</v>
+        <v>1.941751683512434</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10286,16 +10274,16 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>4.002287160743001</v>
+        <v>5.472757709204235</v>
       </c>
       <c r="L89" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M89" t="n">
-        <v>63.63636363636363</v>
+        <v>67.5</v>
       </c>
       <c r="N89" t="n">
-        <v>14.35120412673499</v>
+        <v>13.78300315643509</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
@@ -10328,7 +10316,7 @@
         <v>28.7873334490923</v>
       </c>
       <c r="Y89" t="n">
-        <v>16.50087984422584</v>
+        <v>15.3203000669588</v>
       </c>
       <c r="Z89" t="n">
         <v>2</v>
@@ -10360,7 +10348,7 @@
         <v>88</v>
       </c>
       <c r="AK89" t="n">
-        <v>48.86363636363637</v>
+        <v>47.72727272727273</v>
       </c>
     </row>
     <row r="90">
@@ -10370,10 +10358,10 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C90" t="n">
-        <v>2.620975382329989</v>
+        <v>2.625467042437919</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10401,22 +10389,22 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>3.319502074688785</v>
+        <v>3.496564434361726</v>
       </c>
       <c r="L90" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M90" t="n">
-        <v>74.07407407407408</v>
+        <v>74.50980392156863</v>
       </c>
       <c r="N90" t="n">
-        <v>14.38112257649603</v>
+        <v>14.26636743751452</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>4.530120481927735</v>
+        <v>4.351289910202172</v>
       </c>
       <c r="Q90" t="n">
         <v>42</v>
@@ -10443,7 +10431,7 @@
         <v>33.24184775233741</v>
       </c>
       <c r="Y90" t="n">
-        <v>13.81781026676451</v>
+        <v>13.67011673776437</v>
       </c>
       <c r="Z90" t="n">
         <v>2</v>
@@ -10485,19 +10473,19 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2303089926255455</v>
+        <v>0.234146216001518</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -10513,40 +10501,40 @@
         <v>10</v>
       </c>
       <c r="J91" t="n">
-        <v>15.46353424996684</v>
+        <v>15.33687628212038</v>
       </c>
       <c r="K91" t="n">
-        <v>1.578450443260238</v>
+        <v>3.270868963668039</v>
       </c>
       <c r="L91" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="M91" t="n">
-        <v>57.4074074074074</v>
+        <v>56.25</v>
       </c>
       <c r="N91" t="n">
-        <v>16.18525307284902</v>
+        <v>13.58921776104736</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>1.399459777675793</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R91" t="n">
-        <v>60.8695652173913</v>
+        <v>61.70212765957447</v>
       </c>
       <c r="S91" t="n">
-        <v>34.92823342494342</v>
+        <v>31.66621822688545</v>
       </c>
       <c r="T91" t="n">
-        <v>25.94133179244788</v>
+        <v>30.03590943268901</v>
       </c>
       <c r="U91" t="n">
-        <v>46.45684323162075</v>
+        <v>47.42656695641357</v>
       </c>
       <c r="V91" t="n">
         <v>81</v>
@@ -10594,10 +10582,10 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C92" t="n">
-        <v>1.073652566255658</v>
+        <v>1.093944574280776</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10625,22 +10613,22 @@
         <v>23.70319776773422</v>
       </c>
       <c r="K92" t="n">
-        <v>1.898103445405774</v>
+        <v>3.82397518254467</v>
       </c>
       <c r="L92" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M92" t="n">
-        <v>68</v>
+        <v>56.25</v>
       </c>
       <c r="N92" t="n">
-        <v>16.08046557361654</v>
+        <v>16.47744676738716</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>5.98823368470589</v>
+        <v>4.022216265667922</v>
       </c>
       <c r="Q92" t="n">
         <v>56</v>
@@ -10703,10 +10691,10 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04189350230559383</v>
+        <v>0.04228516506470987</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10734,22 +10722,22 @@
         <v>20.06295203850619</v>
       </c>
       <c r="K93" t="n">
-        <v>1.015227395707208</v>
+        <v>1.959619735739704</v>
       </c>
       <c r="L93" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M93" t="n">
-        <v>62.22222222222222</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N93" t="n">
-        <v>14.33054855153099</v>
+        <v>14.40452539607959</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>4.934674437514186</v>
+        <v>3.962725905345876</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10812,10 +10800,10 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C94" t="n">
-        <v>6.215606278176139</v>
+        <v>6.121882136840495</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10843,22 +10831,22 @@
         <v>11.31569733043036</v>
       </c>
       <c r="K94" t="n">
-        <v>3.324584426946631</v>
+        <v>1.766569404618124</v>
       </c>
       <c r="L94" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="M94" t="n">
-        <v>40.47619047619047</v>
+        <v>42.5925925925926</v>
       </c>
       <c r="N94" t="n">
-        <v>12.52117568515545</v>
+        <v>12.39447518301613</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>4.524978831498738</v>
+        <v>6.125224257681428</v>
       </c>
       <c r="Q94" t="n">
         <v>40</v>
@@ -10885,7 +10873,7 @@
         <v>46.65531127586331</v>
       </c>
       <c r="Y94" t="n">
-        <v>8.367312814731632</v>
+        <v>9.749027572770819</v>
       </c>
       <c r="Z94" t="n">
         <v>2</v>
@@ -10905,10 +10893,10 @@
         <v>54.05405405405406</v>
       </c>
       <c r="AG94" t="n">
-        <v>21.42430611577617</v>
+        <v>21.16476085623091</v>
       </c>
       <c r="AH94" t="n">
-        <v>32.62974793827789</v>
+        <v>32.88929319782315</v>
       </c>
       <c r="AI94" t="n">
         <v>38.38404689217949</v>
@@ -10927,10 +10915,10 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1410484703905671</v>
+        <v>0.1428439156847824</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10947,7 +10935,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H95" t="n">
         <v>5</v>
       </c>
@@ -10958,22 +10950,22 @@
         <v>23.34731360730358</v>
       </c>
       <c r="K95" t="n">
-        <v>1.66919055381205</v>
+        <v>2.963366018750135</v>
       </c>
       <c r="L95" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="M95" t="n">
-        <v>65.38461538461539</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="N95" t="n">
-        <v>19.69125565142667</v>
+        <v>17.8824332376777</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>4.259706822290199</v>
+        <v>2.949237285712747</v>
       </c>
       <c r="Q95" t="n">
         <v>22</v>
@@ -11036,10 +11028,10 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1324171489961174</v>
+        <v>0.134218586620101</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11067,22 +11059,22 @@
         <v>12.45241464719801</v>
       </c>
       <c r="K96" t="n">
-        <v>1.944892681427635</v>
+        <v>3.331777738548736</v>
       </c>
       <c r="L96" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M96" t="n">
-        <v>58.9041095890411</v>
+        <v>58.73015873015873</v>
       </c>
       <c r="N96" t="n">
-        <v>13.05039313719298</v>
+        <v>14.43137887764547</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>7.901432927831076</v>
+        <v>6.453215465162399</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11109,16 +11101,16 @@
         <v>16.74415231729489</v>
       </c>
       <c r="Y96" t="n">
-        <v>10.74970806690475</v>
+        <v>9.535523687776394</v>
       </c>
       <c r="Z96" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AA96" t="n">
-        <v>36.8421052631579</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB96" t="n">
-        <v>18.11843988336842</v>
+        <v>16.88679887629387</v>
       </c>
       <c r="AC96" t="n">
         <v>8</v>
@@ -11155,10 +11147,10 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C97" t="n">
-        <v>1.816788622402032</v>
+        <v>1.842875827562707</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11183,25 +11175,25 @@
         <v>10</v>
       </c>
       <c r="J97" t="n">
-        <v>25.18755369673152</v>
+        <v>24.72840729454471</v>
       </c>
       <c r="K97" t="n">
-        <v>1.649000582768312</v>
+        <v>3.108575075850672</v>
       </c>
       <c r="L97" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M97" t="n">
-        <v>52.17391304347826</v>
+        <v>45</v>
       </c>
       <c r="N97" t="n">
-        <v>12.30389391293941</v>
+        <v>11.68685273681049</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>2.31286033679925</v>
+        <v>0.8645497462200114</v>
       </c>
       <c r="Q97" t="n">
         <v>51</v>
@@ -11210,10 +11202,10 @@
         <v>54.90196078431372</v>
       </c>
       <c r="S97" t="n">
-        <v>34.22272913178863</v>
+        <v>34.32405195756966</v>
       </c>
       <c r="T97" t="n">
-        <v>20.6792316525251</v>
+        <v>20.57790882674406</v>
       </c>
       <c r="U97" t="n">
         <v>41.38470855036881</v>
@@ -11242,10 +11234,10 @@
         <v>55</v>
       </c>
       <c r="AG97" t="n">
-        <v>58.02188141754571</v>
+        <v>57.80938255798803</v>
       </c>
       <c r="AH97" t="n">
-        <v>-3.021881417545714</v>
+        <v>-2.80938255798803</v>
       </c>
       <c r="AI97" t="n">
         <v>39.82909179893205</v>
@@ -11264,10 +11256,10 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6151397499052953</v>
+        <v>0.6349086075176275</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11295,22 +11287,22 @@
         <v>21.12557680400878</v>
       </c>
       <c r="K98" t="n">
-        <v>2.454413880468787</v>
+        <v>5.747009945134995</v>
       </c>
       <c r="L98" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="M98" t="n">
-        <v>52.77777777777778</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N98" t="n">
-        <v>14.12784715713754</v>
+        <v>18.51513166406675</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>7.364822884384936</v>
+        <v>4.021853721511004</v>
       </c>
       <c r="Q98" t="n">
         <v>48</v>
@@ -11319,10 +11311,10 @@
         <v>68.75</v>
       </c>
       <c r="S98" t="n">
-        <v>40.11919104718147</v>
+        <v>40.1712743805148</v>
       </c>
       <c r="T98" t="n">
-        <v>28.63080895281853</v>
+        <v>28.5787256194852</v>
       </c>
       <c r="U98" t="n">
         <v>54.66692858410841</v>
@@ -11373,10 +11365,10 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4799858371500599</v>
+        <v>0.4830185849818769</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11404,22 +11396,22 @@
         <v>28.77817890954801</v>
       </c>
       <c r="K99" t="n">
-        <v>3.260866497321979</v>
+        <v>3.913311100355954</v>
       </c>
       <c r="L99" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M99" t="n">
-        <v>60</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N99" t="n">
-        <v>12.90306316279074</v>
+        <v>12.77959199349419</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>0.7157924659650261</v>
+        <v>0.08342424923821756</v>
       </c>
       <c r="Q99" t="n">
         <v>35</v>
@@ -11460,19 +11452,19 @@
         <v>52.5</v>
       </c>
       <c r="AG99" t="n">
-        <v>37.91929917934884</v>
+        <v>37.78906518920106</v>
       </c>
       <c r="AH99" t="n">
-        <v>14.58070082065116</v>
+        <v>14.71093481079894</v>
       </c>
       <c r="AI99" t="n">
         <v>37.49736210669248</v>
       </c>
       <c r="AJ99" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK99" t="n">
-        <v>50</v>
+        <v>49.35064935064935</v>
       </c>
     </row>
     <row r="100">
@@ -11482,19 +11474,19 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C100" t="n">
-        <v>315.9949011707013</v>
+        <v>325.7851091790787</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -11502,7 +11494,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H100" t="n">
         <v>5</v>
       </c>
@@ -11513,22 +11509,22 @@
         <v>25.87300653788257</v>
       </c>
       <c r="K100" t="n">
-        <v>3.102656148023497</v>
+        <v>6.297000253468688</v>
       </c>
       <c r="L100" t="n">
         <v>13</v>
       </c>
       <c r="M100" t="n">
-        <v>69.23076923076923</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="N100" t="n">
-        <v>15.02972702183852</v>
+        <v>12.40411229835558</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
       </c>
       <c r="P100" t="n">
-        <v>1.840247305804144</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>47</v>
@@ -11591,19 +11587,19 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C101" t="n">
-        <v>321.0094943271166</v>
+        <v>324.3791783837299</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -11622,22 +11618,22 @@
         <v>14.83975271775182</v>
       </c>
       <c r="K101" t="n">
-        <v>1.653769629014823</v>
+        <v>2.72084425723278</v>
       </c>
       <c r="L101" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="M101" t="n">
-        <v>55.88235294117647</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N101" t="n">
-        <v>11.66874870423401</v>
+        <v>9.643846868652336</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
       </c>
       <c r="P101" t="n">
-        <v>0.3405976701589486</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
         <v>29</v>
@@ -11700,10 +11696,10 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C102" t="n">
-        <v>388.9590541177647</v>
+        <v>390.0573113018389</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11799,31 +11795,27 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C103" t="n">
-        <v>0.6896638483686088</v>
+        <v>0.7173751597930625</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>BAND</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>5</v>
       </c>
@@ -11834,22 +11826,22 @@
         <v>31.6668549372698</v>
       </c>
       <c r="K103" t="n">
-        <v>6.069156736335612</v>
+        <v>10.33111050091629</v>
       </c>
       <c r="L103" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M103" t="n">
-        <v>83.33333333333333</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N103" t="n">
-        <v>26.0378402285978</v>
+        <v>14.21207955224867</v>
       </c>
       <c r="O103" t="n">
         <v>10</v>
       </c>
       <c r="P103" t="n">
-        <v>3.705924874500144</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
         <v>43</v>
@@ -11872,17 +11864,27 @@
       <c r="W103" t="n">
         <v>68.18181818181819</v>
       </c>
-      <c r="X103" t="inlineStr"/>
-      <c r="Y103" t="inlineStr"/>
+      <c r="X103" t="n">
+        <v>10.84879266873253</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>0.4670165144363025</v>
+      </c>
       <c r="Z103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA103" t="inlineStr"/>
-      <c r="AB103" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>34.61538461538461</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>10.78940398518989</v>
+      </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
-      <c r="AD103" t="inlineStr"/>
+      <c r="AD103" t="n">
+        <v>7.568328831071646</v>
+      </c>
       <c r="AE103" t="n">
         <v>34</v>
       </c>
@@ -11912,10 +11914,10 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04905118418595056</v>
+        <v>0.04985862539829875</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11932,11 +11934,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.19: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>5</v>
       </c>
@@ -11947,22 +11945,22 @@
         <v>27.65580276361549</v>
       </c>
       <c r="K104" t="n">
-        <v>1.304346550094504</v>
+        <v>2.971937368788291</v>
       </c>
       <c r="L104" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M104" t="n">
-        <v>76.19047619047619</v>
+        <v>65</v>
       </c>
       <c r="N104" t="n">
-        <v>15.30180212803625</v>
+        <v>14.25029794564913</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>2.660945499088241</v>
+        <v>0.9983910738027291</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>
@@ -12003,10 +12001,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="AG104" t="n">
-        <v>34.61910331345534</v>
+        <v>34.47252163831823</v>
       </c>
       <c r="AH104" t="n">
-        <v>27.08302434611912</v>
+        <v>27.22960602125623</v>
       </c>
       <c r="AI104" t="n">
         <v>47.42656695641357</v>

--- a/TDA_Result.xlsx
+++ b/TDA_Result.xlsx
@@ -453,7 +453,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -679,7 +679,7 @@
         <v>46237</v>
       </c>
       <c r="C2" t="n">
-        <v>0.467030199623675</v>
+        <v>0.4725207813133375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -739,22 +739,22 @@
         <v>14.94856954517825</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.945053659492091</v>
+        <v>0.7922830391085545</v>
       </c>
       <c r="Z2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AA2" t="n">
-        <v>41.66666666666666</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB2" t="n">
-        <v>12.27306513849694</v>
+        <v>11.03336785576561</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.175054463322383</v>
+        <v>7.265278530432051</v>
       </c>
       <c r="AE2" t="n">
         <v>43</v>
@@ -788,7 +788,7 @@
         <v>46237</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7539802635829748</v>
+        <v>0.751489028332933</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>12.13279917920569</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.8991122027144582</v>
+        <v>1.226552637053979</v>
       </c>
       <c r="Z3" t="n">
         <v>61</v>
@@ -857,13 +857,13 @@
         <v>44.26229508196721</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.50885197844632</v>
+        <v>10.50485684922246</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>9.183457383249415</v>
+        <v>8.882394608247013</v>
       </c>
       <c r="AE3" t="n">
         <v>38</v>
@@ -897,7 +897,7 @@
         <v>46237</v>
       </c>
       <c r="C4" t="n">
-        <v>1.385312471974113</v>
+        <v>1.390633312610751</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>27.63389482946404</v>
       </c>
       <c r="K4" t="n">
-        <v>7.260445775815549</v>
+        <v>7.672421954572184</v>
       </c>
       <c r="L4" t="n">
         <v>16</v>
@@ -1006,7 +1006,7 @@
         <v>46237</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2739069011605809</v>
+        <v>0.2671867354724948</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,25 +1063,25 @@
         <v>58.46153846153846</v>
       </c>
       <c r="X5" t="n">
-        <v>16.70098304122878</v>
+        <v>16.70614361206606</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.957825868118446</v>
+        <v>4.367469365904886</v>
       </c>
       <c r="Z5" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="AA5" t="n">
-        <v>43.13725490196079</v>
+        <v>43.24324324324324</v>
       </c>
       <c r="AB5" t="n">
-        <v>15.78456111954939</v>
+        <v>15.89552284580699</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>8.202770086538081</v>
+        <v>5.88976428496496</v>
       </c>
       <c r="AE5" t="n">
         <v>45</v>
@@ -1115,16 +1115,16 @@
         <v>46237</v>
       </c>
       <c r="C6" t="n">
-        <v>2.029056747170189</v>
+        <v>1.954460512247084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1132,7 +1132,11 @@
           <t>SATMA_BEKLE</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
@@ -1143,22 +1147,22 @@
         <v>22.03360200065558</v>
       </c>
       <c r="K6" t="n">
-        <v>4.536919021817254</v>
+        <v>0.6937241085332335</v>
       </c>
       <c r="L6" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M6" t="n">
-        <v>72</v>
+        <v>81.25</v>
       </c>
       <c r="N6" t="n">
-        <v>11.80010877058999</v>
+        <v>14.70472042945921</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.297276372516309</v>
       </c>
       <c r="Q6" t="n">
         <v>40</v>
@@ -1185,7 +1189,7 @@
         <v>44.49622708587002</v>
       </c>
       <c r="Y6" t="n">
-        <v>18.49632965919758</v>
+        <v>21.49273030117917</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1230,7 +1234,7 @@
         <v>46237</v>
       </c>
       <c r="C7" t="n">
-        <v>2.150021772210852</v>
+        <v>2.150116847156821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,7 +1262,7 @@
         <v>11.35312764557068</v>
       </c>
       <c r="K7" t="n">
-        <v>3.004581556254426</v>
+        <v>3.009136465954687</v>
       </c>
       <c r="L7" t="n">
         <v>67</v>
@@ -1300,7 +1304,7 @@
         <v>13.79329344082609</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.689660068613092</v>
+        <v>8.68562228362525</v>
       </c>
       <c r="Z7" t="n">
         <v>20</v>
@@ -1315,7 +1319,7 @@
         <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.435040032017765</v>
+        <v>1.439398426890937</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1349,7 +1353,7 @@
         <v>46237</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3275522438928626</v>
+        <v>0.3242005996182086</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,22 +1381,22 @@
         <v>22.10694516187944</v>
       </c>
       <c r="K8" t="n">
-        <v>4.144515342596167</v>
+        <v>3.078867418966613</v>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N8" t="n">
-        <v>15.38993104685579</v>
+        <v>17.67912674615781</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>3.702052522613175</v>
+        <v>4.774143046247614</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1458,7 +1462,7 @@
         <v>46237</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5785283806292564</v>
+        <v>0.5680348004475569</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,16 +1490,16 @@
         <v>12.72202042588303</v>
       </c>
       <c r="K9" t="n">
-        <v>4.094350035590177</v>
+        <v>2.206244896526388</v>
       </c>
       <c r="L9" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="M9" t="n">
-        <v>43.90243902439025</v>
+        <v>51.11111111111111</v>
       </c>
       <c r="N9" t="n">
-        <v>14.82625929286921</v>
+        <v>14.25664128597968</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1567,16 +1571,16 @@
         <v>46237</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0721834724357</v>
+        <v>2.02704267237144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1591,17 +1595,27 @@
       <c r="I10" t="n">
         <v>10</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>10.04653454191088</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1559267409103837</v>
+      </c>
       <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="M10" t="n">
+        <v>43.58974358974359</v>
+      </c>
+      <c r="N10" t="n">
+        <v>10.34069535415989</v>
+      </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>9.828747613263955</v>
+      </c>
       <c r="Q10" t="n">
         <v>44</v>
       </c>
@@ -1666,7 +1680,7 @@
         <v>46237</v>
       </c>
       <c r="C11" t="n">
-        <v>7.200048664376836</v>
+        <v>7.07939667965196</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,7 +1699,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1695,25 +1709,25 @@
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>19.38783055927281</v>
+        <v>20.20204115522435</v>
       </c>
       <c r="K11" t="n">
-        <v>1.658867677524722</v>
+        <v>0.9752438109527528</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="M11" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="N11" t="n">
-        <v>15.00634405004488</v>
+        <v>16.4703946183538</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.319247747997276</v>
+        <v>2.005200594353629</v>
       </c>
       <c r="Q11" t="n">
         <v>49</v>
@@ -1779,16 +1793,16 @@
         <v>46237</v>
       </c>
       <c r="C12" t="n">
-        <v>6.248106510795969</v>
+        <v>6.085335778868735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1807,22 +1821,22 @@
         <v>20.08266526523165</v>
       </c>
       <c r="K12" t="n">
-        <v>8.777698121744027</v>
+        <v>5.943907514934987</v>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N12" t="n">
-        <v>34.30134161376015</v>
+        <v>23.02355388202442</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.05294545611989054</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1888,7 +1902,7 @@
         <v>46237</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3191372938337487</v>
+        <v>0.3164164213336986</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1930,7 @@
         <v>38.11781916800814</v>
       </c>
       <c r="K13" t="n">
-        <v>12.14642567803277</v>
+        <v>11.19029760556367</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1952,7 +1966,7 @@
         <v>35.74308703619145</v>
       </c>
       <c r="Y13" t="n">
-        <v>17.3833245385582</v>
+        <v>18.08769047964968</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -1987,7 +2001,7 @@
         <v>46237</v>
       </c>
       <c r="C14" t="n">
-        <v>8.25191844733912</v>
+        <v>8.105015069348937</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2047,16 +2061,16 @@
         <v>14.33662537827827</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.634303251068594</v>
+        <v>6.332034885985916</v>
       </c>
       <c r="Z14" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA14" t="n">
-        <v>44.82758620689656</v>
+        <v>40.74074074074074</v>
       </c>
       <c r="AB14" t="n">
-        <v>13.91848588751987</v>
+        <v>10.75804611379783</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2096,7 +2110,7 @@
         <v>46237</v>
       </c>
       <c r="C15" t="n">
-        <v>11.13930100157059</v>
+        <v>11.15031274952612</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,22 +2138,22 @@
         <v>20.36228477344414</v>
       </c>
       <c r="K15" t="n">
-        <v>4.882535675839894</v>
+        <v>4.986217230691148</v>
       </c>
       <c r="L15" t="n">
         <v>30</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="N15" t="n">
-        <v>17.02443812528893</v>
+        <v>17.4192324468736</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>2.972338820826415</v>
+        <v>2.870646117943787</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2205,7 +2219,7 @@
         <v>46237</v>
       </c>
       <c r="C16" t="n">
-        <v>36.31054490785805</v>
+        <v>35.9755373616786</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,22 +2247,22 @@
         <v>19.01528411877121</v>
       </c>
       <c r="K16" t="n">
-        <v>4.660298393387308</v>
+        <v>3.694683863609516</v>
       </c>
       <c r="L16" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M16" t="n">
-        <v>65.90909090909091</v>
+        <v>62</v>
       </c>
       <c r="N16" t="n">
-        <v>15.89667251250147</v>
+        <v>17.16738140147843</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>5.101936157818243</v>
+        <v>6.080655151698933</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2314,11 +2328,11 @@
         <v>46237</v>
       </c>
       <c r="C17" t="n">
-        <v>0.752297233431801</v>
+        <v>0.7296091502078541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2328,7 +2342,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2342,22 +2356,22 @@
         <v>16.56354083790577</v>
       </c>
       <c r="K17" t="n">
-        <v>6.844670823909627</v>
+        <v>3.622406171107562</v>
       </c>
       <c r="L17" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="M17" t="n">
-        <v>71.05263157894737</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N17" t="n">
-        <v>17.76917220557955</v>
+        <v>16.94507464850981</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>1.081316613342809</v>
+        <v>4.224562998145309</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2384,22 +2398,22 @@
         <v>15.7396793517258</v>
       </c>
       <c r="Y17" t="n">
-        <v>7.685357845847129</v>
+        <v>10.46942003683505</v>
       </c>
       <c r="Z17" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AA17" t="n">
-        <v>55.17241379310344</v>
+        <v>40.90909090909091</v>
       </c>
       <c r="AB17" t="n">
-        <v>11.32671724855418</v>
+        <v>8.774516751473181</v>
       </c>
       <c r="AC17" t="n">
         <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.507340222678578</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>35</v>
@@ -2433,7 +2447,7 @@
         <v>46237</v>
       </c>
       <c r="C18" t="n">
-        <v>0.104976599501035</v>
+        <v>0.1020358787173026</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2461,22 +2475,22 @@
         <v>26.36599129766135</v>
       </c>
       <c r="K18" t="n">
-        <v>3.670176812698589</v>
+        <v>0.7660529883857015</v>
       </c>
       <c r="L18" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="M18" t="n">
-        <v>38.46153846153846</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N18" t="n">
-        <v>19.98491655925718</v>
+        <v>20.02563322973904</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>6.105732026229238</v>
+        <v>9.16374784738132</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2542,7 +2556,7 @@
         <v>46237</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02524487584296461</v>
+        <v>0.02503560913387707</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,22 +2584,22 @@
         <v>23.99412305210119</v>
       </c>
       <c r="K19" t="n">
-        <v>2.209144441428079</v>
+        <v>1.361884529002255</v>
       </c>
       <c r="L19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M19" t="n">
-        <v>73.68421052631579</v>
+        <v>65</v>
       </c>
       <c r="N19" t="n">
-        <v>19.13887577281496</v>
+        <v>23.79065269649551</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>7.622464311925192</v>
+        <v>8.522054923442312</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2651,11 +2665,11 @@
         <v>46237</v>
       </c>
       <c r="C20" t="n">
-        <v>1.921766061284878</v>
+        <v>1.872411008882688</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2665,7 +2679,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2711,22 +2725,22 @@
         <v>20.34011802710127</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.991509099905532</v>
+        <v>5.482894106793657</v>
       </c>
       <c r="Z20" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="AA20" t="n">
-        <v>40.625</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="AB20" t="n">
-        <v>11.24895484505469</v>
+        <v>12.18607979866391</v>
       </c>
       <c r="AC20" t="n">
         <v>4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.039590339708596</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>40</v>
@@ -2760,7 +2774,7 @@
         <v>46237</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9559392299348919</v>
+        <v>0.9500907964076463</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,22 +2802,22 @@
         <v>15.77844025931157</v>
       </c>
       <c r="K21" t="n">
-        <v>2.179237459778216</v>
+        <v>1.554105171621289</v>
       </c>
       <c r="L21" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M21" t="n">
-        <v>45.83333333333334</v>
+        <v>50</v>
       </c>
       <c r="N21" t="n">
-        <v>18.92892346628566</v>
+        <v>21.84859522686849</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>5.696619670422831</v>
+        <v>6.347251858982439</v>
       </c>
       <c r="Q21" t="n">
         <v>41</v>
@@ -2869,7 +2883,7 @@
         <v>46237</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7985795198705623</v>
+        <v>0.7965110330165086</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2901,7 +2915,7 @@
         <v>22.47437017331863</v>
       </c>
       <c r="K22" t="n">
-        <v>6.379699678065465</v>
+        <v>6.104154156489949</v>
       </c>
       <c r="L22" t="n">
         <v>12</v>
@@ -2910,13 +2924,13 @@
         <v>83.33333333333333</v>
       </c>
       <c r="N22" t="n">
-        <v>13.57317947224143</v>
+        <v>12.10085352258792</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>3.403187199146629</v>
+        <v>3.671718486878639</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -2974,7 +2988,7 @@
         <v>46237</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7182166749738363</v>
+        <v>0.7157238582415516</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2999,25 +3013,25 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>22.82612646819611</v>
+        <v>24.64401357803806</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7079582571334564</v>
+        <v>2.779462333914706</v>
       </c>
       <c r="L23" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M23" t="n">
-        <v>68.75</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N23" t="n">
-        <v>16.03529179982758</v>
+        <v>18.61926909781184</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.261869485932634</v>
+        <v>2.160487723579552</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3083,7 +3097,7 @@
         <v>46237</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1842875908135932</v>
+        <v>0.180298446805362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3111,22 +3125,22 @@
         <v>25.34703849055006</v>
       </c>
       <c r="K24" t="n">
-        <v>2.385010174250546</v>
+        <v>0.1687537889661472</v>
       </c>
       <c r="L24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M24" t="n">
-        <v>61.53846153846154</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N24" t="n">
-        <v>12.38613097674726</v>
+        <v>15.69950398939818</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>7.43760225524166</v>
+        <v>9.814683560650227</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3192,7 +3206,7 @@
         <v>46237</v>
       </c>
       <c r="C25" t="n">
-        <v>3.950822968970396</v>
+        <v>3.967828401089686</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3220,22 +3234,22 @@
         <v>12.04001635695179</v>
       </c>
       <c r="K25" t="n">
-        <v>3.340715885657985</v>
+        <v>3.785522839286259</v>
       </c>
       <c r="L25" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="M25" t="n">
-        <v>56.36363636363637</v>
+        <v>54.90196078431372</v>
       </c>
       <c r="N25" t="n">
-        <v>17.26882469722056</v>
+        <v>18.10702151244897</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>4.508662509651384</v>
+        <v>4.060756303400748</v>
       </c>
       <c r="Q25" t="n">
         <v>44</v>
@@ -3301,7 +3315,7 @@
         <v>46237</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4438890564042943</v>
+        <v>0.4363348752086788</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3400,7 +3414,7 @@
         <v>46237</v>
       </c>
       <c r="C27" t="n">
-        <v>36.07913355560635</v>
+        <v>34.986736042381</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3425,10 +3439,10 @@
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>58.38400783870043</v>
+        <v>59.27824529244716</v>
       </c>
       <c r="K27" t="n">
-        <v>2.571770334928236</v>
+        <v>1.650366748166254</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3439,7 +3453,7 @@
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>5.29212827988339</v>
+        <v>6.246542393265186</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -3485,16 +3499,16 @@
         <v>46237</v>
       </c>
       <c r="C28" t="n">
-        <v>1.464202705696285</v>
+        <v>1.410619818611661</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3513,22 +3527,22 @@
         <v>25.72214510232956</v>
       </c>
       <c r="K28" t="n">
-        <v>5.010015789897526</v>
+        <v>1.167146358681093</v>
       </c>
       <c r="L28" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M28" t="n">
-        <v>62.5</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="N28" t="n">
-        <v>14.08273448953023</v>
+        <v>17.7683328440831</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>0.8232451653485295</v>
       </c>
       <c r="Q28" t="n">
         <v>40</v>
@@ -3594,28 +3608,24 @@
         <v>46237</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4133848167099674</v>
+        <v>0.39909702861282</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>AL_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>5</v>
       </c>
@@ -3623,25 +3633,25 @@
         <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>13.93943996887607</v>
+        <v>13.93563433155613</v>
       </c>
       <c r="K29" t="n">
-        <v>4.855922418188996</v>
+        <v>1.227318798414245</v>
       </c>
       <c r="L29" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M29" t="n">
-        <v>77.77777777777777</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N29" t="n">
-        <v>23.57395026752156</v>
+        <v>24.20466013684741</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.739064152343418</v>
       </c>
       <c r="Q29" t="n">
         <v>6</v>
@@ -3668,10 +3678,10 @@
         <v>55.05052857749912</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.76040594110572</v>
+        <v>12.87935019297134</v>
       </c>
       <c r="Z29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
@@ -3679,7 +3689,7 @@
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.265508795105962</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3713,7 +3723,7 @@
         <v>46237</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3877192085214907</v>
+        <v>0.3822663840583294</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3741,22 +3751,22 @@
         <v>22.50856964296201</v>
       </c>
       <c r="K30" t="n">
-        <v>4.88158179759639</v>
+        <v>3.406543052052058</v>
       </c>
       <c r="L30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M30" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="N30" t="n">
-        <v>11.91558704505633</v>
+        <v>12.10566919354135</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>0.1129065755626657</v>
+        <v>1.540963367420423</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3822,7 +3832,7 @@
         <v>46237</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1960685210225771</v>
+        <v>0.1918695302814034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3850,22 +3860,22 @@
         <v>24.39894838979837</v>
       </c>
       <c r="K31" t="n">
-        <v>2.627002728785199</v>
+        <v>0.4291494884735458</v>
       </c>
       <c r="L31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M31" t="n">
-        <v>55.55555555555556</v>
+        <v>50</v>
       </c>
       <c r="N31" t="n">
-        <v>12.87425769672796</v>
+        <v>12.57353257398547</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>7.184266396924399</v>
+        <v>9.529952767970951</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3931,7 +3941,7 @@
         <v>46237</v>
       </c>
       <c r="C32" t="n">
-        <v>2.282557429028157</v>
+        <v>2.291073727327118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3959,16 +3969,16 @@
         <v>11.96252232646255</v>
       </c>
       <c r="K32" t="n">
-        <v>8.306541544384615</v>
+        <v>8.710636882267764</v>
       </c>
       <c r="L32" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M32" t="n">
-        <v>45.16129032258065</v>
+        <v>50</v>
       </c>
       <c r="N32" t="n">
-        <v>11.24042102953525</v>
+        <v>10.65025967437194</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4001,22 +4011,22 @@
         <v>12.36180984775317</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.609116219170316</v>
+        <v>3.249478599919897</v>
       </c>
       <c r="Z32" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA32" t="n">
-        <v>38.63636363636363</v>
+        <v>34.78260869565217</v>
       </c>
       <c r="AB32" t="n">
-        <v>10.84382070612624</v>
+        <v>11.99054819348334</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>4.555289471993563</v>
+        <v>4.91007317721408</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4050,16 +4060,16 @@
         <v>46237</v>
       </c>
       <c r="C33" t="n">
-        <v>1.858653874307141</v>
+        <v>1.828230556592072</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4078,22 +4088,22 @@
         <v>12.57251846431013</v>
       </c>
       <c r="K33" t="n">
-        <v>4.175411358615566</v>
+        <v>2.470219401321949</v>
       </c>
       <c r="L33" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M33" t="n">
-        <v>56</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N33" t="n">
-        <v>11.09603008028689</v>
+        <v>11.05697725973216</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.492902628310677</v>
       </c>
       <c r="Q33" t="n">
         <v>39</v>
@@ -4159,7 +4169,7 @@
         <v>46237</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9029249831963908</v>
+        <v>0.8634129160355463</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4168,7 +4178,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4183,17 +4193,27 @@
       <c r="I34" t="n">
         <v>10</v>
       </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="J34" t="n">
+        <v>10.18726434397186</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.6375727017615906</v>
+      </c>
       <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="M34" t="n">
+        <v>46</v>
+      </c>
+      <c r="N34" t="n">
+        <v>13.98077476539812</v>
+      </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
-      <c r="P34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>3.341125196056671</v>
+      </c>
       <c r="Q34" t="n">
         <v>35</v>
       </c>
@@ -4219,16 +4239,16 @@
         <v>14.68007915548277</v>
       </c>
       <c r="Y34" t="n">
-        <v>5.478368967754966</v>
+        <v>9.614642858723721</v>
       </c>
       <c r="Z34" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="n">
-        <v>39.39393939393939</v>
+        <v>50</v>
       </c>
       <c r="AB34" t="n">
-        <v>11.06059041923906</v>
+        <v>10.91246972399142</v>
       </c>
       <c r="AC34" t="n">
         <v>2</v>
@@ -4268,7 +4288,7 @@
         <v>46237</v>
       </c>
       <c r="C35" t="n">
-        <v>1.803956677780318</v>
+        <v>1.802984469105537</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4300,7 +4320,7 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>1.698510020194011</v>
+        <v>1.643701512389062</v>
       </c>
       <c r="L35" t="n">
         <v>18</v>
@@ -4315,7 +4335,7 @@
         <v>6</v>
       </c>
       <c r="P35" t="n">
-        <v>4.229648968261057</v>
+        <v>4.285851875514357</v>
       </c>
       <c r="Q35" t="n">
         <v>7</v>
@@ -4342,7 +4362,7 @@
         <v>42.52272358489104</v>
       </c>
       <c r="Y35" t="n">
-        <v>21.5998082943155</v>
+        <v>21.64206060969514</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -4387,7 +4407,7 @@
         <v>46237</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08351846139832725</v>
+        <v>0.08247023937767434</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4415,16 +4435,16 @@
         <v>21.75644461318207</v>
       </c>
       <c r="K36" t="n">
-        <v>4.386813456900618</v>
+        <v>3.07667729419705</v>
       </c>
       <c r="L36" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M36" t="n">
-        <v>50</v>
+        <v>43.75</v>
       </c>
       <c r="N36" t="n">
-        <v>11.75945115687612</v>
+        <v>13.56470521880246</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4496,7 +4516,7 @@
         <v>46237</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06395368196261106</v>
+        <v>0.0626942117294228</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,22 +4544,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>4.105796490959812</v>
+        <v>2.055591596433581</v>
       </c>
       <c r="L37" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="M37" t="n">
-        <v>54.41176470588236</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N37" t="n">
-        <v>19.57056495175387</v>
+        <v>19.72675281368874</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>3.740621214476136</v>
+        <v>5.824676836006071</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4605,16 +4625,16 @@
         <v>46237</v>
       </c>
       <c r="C38" t="n">
-        <v>1.680887945360946</v>
+        <v>1.673598892892937</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4622,7 +4642,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %77.27: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H38" t="n">
         <v>5</v>
       </c>
@@ -4633,22 +4657,22 @@
         <v>19.5673086238003</v>
       </c>
       <c r="K38" t="n">
-        <v>6.093898730858704</v>
+        <v>5.633829993665906</v>
       </c>
       <c r="L38" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M38" t="n">
-        <v>73.91304347826087</v>
+        <v>77.27272727272727</v>
       </c>
       <c r="N38" t="n">
-        <v>12.70337440081996</v>
+        <v>12.11464618607974</v>
       </c>
       <c r="O38" t="n">
         <v>6</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>0.3466408501481499</v>
       </c>
       <c r="Q38" t="n">
         <v>35</v>
@@ -4714,7 +4738,7 @@
         <v>46237</v>
       </c>
       <c r="C39" t="n">
-        <v>2.675956663691994</v>
+        <v>2.686594158690625</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4742,16 +4766,16 @@
         <v>19.12528796921053</v>
       </c>
       <c r="K39" t="n">
-        <v>5.926406531616113</v>
+        <v>6.347486452300766</v>
       </c>
       <c r="L39" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M39" t="n">
-        <v>61.90476190476191</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N39" t="n">
-        <v>13.9922670744708</v>
+        <v>14.25905874162124</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4823,24 +4847,28 @@
         <v>46237</v>
       </c>
       <c r="C40" t="n">
-        <v>0.19901376377796</v>
+        <v>0.1956564352625516</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>ÇELİŞKİLİ_BEKLE</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H40" t="n">
         <v>5</v>
       </c>
@@ -4851,16 +4879,16 @@
         <v>14.73965458840789</v>
       </c>
       <c r="K40" t="n">
-        <v>8.689252425959948</v>
+        <v>6.855683131249091</v>
       </c>
       <c r="L40" t="n">
         <v>18</v>
       </c>
       <c r="M40" t="n">
-        <v>61.11111111111111</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N40" t="n">
-        <v>12.5552807609638</v>
+        <v>11.2474596513414</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4893,22 +4921,22 @@
         <v>14.17330472629232</v>
       </c>
       <c r="Y40" t="n">
-        <v>4.803270180782881</v>
+        <v>6.4092229024865</v>
       </c>
       <c r="Z40" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA40" t="n">
-        <v>58.33333333333334</v>
+        <v>34.78260869565217</v>
       </c>
       <c r="AB40" t="n">
-        <v>10.90027840903963</v>
+        <v>12.33129410895796</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.2066560685337837</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>13</v>
@@ -4942,7 +4970,7 @@
         <v>46237</v>
       </c>
       <c r="C41" t="n">
-        <v>1.58727143832603</v>
+        <v>1.592601209680515</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4970,7 +4998,7 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>4.895844639623448</v>
+        <v>5.24806597648213</v>
       </c>
       <c r="L41" t="n">
         <v>11</v>
@@ -4979,13 +5007,13 @@
         <v>63.63636363636363</v>
       </c>
       <c r="N41" t="n">
-        <v>18.77665382524726</v>
+        <v>17.82717538896454</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>4.86592712791647</v>
+        <v>4.51498465024498</v>
       </c>
       <c r="Q41" t="n">
         <v>10</v>
@@ -5012,7 +5040,7 @@
         <v>40.81782021738603</v>
       </c>
       <c r="Y41" t="n">
-        <v>18.59954612049928</v>
+        <v>18.32621807032874</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -5057,7 +5085,7 @@
         <v>46237</v>
       </c>
       <c r="C42" t="n">
-        <v>3.193476725237552</v>
+        <v>3.166268054346567</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5076,7 +5104,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -5089,16 +5117,16 @@
         <v>22.36276267242437</v>
       </c>
       <c r="K42" t="n">
-        <v>3.900421427578271</v>
+        <v>3.01518172950368</v>
       </c>
       <c r="L42" t="n">
         <v>6</v>
       </c>
       <c r="M42" t="n">
-        <v>100</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N42" t="n">
-        <v>13.52340132156805</v>
+        <v>12.3779784972871</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
@@ -5166,7 +5194,7 @@
         <v>46237</v>
       </c>
       <c r="C43" t="n">
-        <v>7.541906343839578</v>
+        <v>7.542239850387006</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5226,7 +5254,7 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.654152274615462</v>
+        <v>2.649847596712929</v>
       </c>
       <c r="Z43" t="n">
         <v>13</v>
@@ -5241,7 +5269,7 @@
         <v>6</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.437072873229552</v>
+        <v>3.441342741209674</v>
       </c>
       <c r="AE43" t="n">
         <v>8</v>
@@ -5275,7 +5303,7 @@
         <v>46237</v>
       </c>
       <c r="C44" t="n">
-        <v>5.192029312865892</v>
+        <v>5.059717389171757</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5294,7 +5322,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %87.50: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %78.26: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -5307,22 +5335,22 @@
         <v>13.03201987649729</v>
       </c>
       <c r="K44" t="n">
-        <v>6.267058982469464</v>
+        <v>3.558985096128575</v>
       </c>
       <c r="L44" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="M44" t="n">
-        <v>87.5</v>
+        <v>78.26086956521739</v>
       </c>
       <c r="N44" t="n">
-        <v>19.01122755073941</v>
+        <v>19.86668303814072</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>3.512792254979358</v>
+        <v>6.21965819565784</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5349,22 +5377,22 @@
         <v>12.1234692799834</v>
       </c>
       <c r="Y44" t="n">
-        <v>5.223179709940906</v>
+        <v>7.638440229198096</v>
       </c>
       <c r="Z44" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AA44" t="n">
-        <v>18.75</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="AB44" t="n">
-        <v>7.420762629206091</v>
+        <v>9.691917834769438</v>
       </c>
       <c r="AC44" t="n">
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>5.040072325110612</v>
+        <v>2.556864323926733</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5390,7 +5418,7 @@
         <v>46237</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02103739565924569</v>
+        <v>0.02061755984441858</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5415,25 +5443,25 @@
         <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>10.51199238133264</v>
+        <v>11.49212697867188</v>
       </c>
       <c r="K45" t="n">
-        <v>3.021207737253273</v>
+        <v>2.083337543402863</v>
       </c>
       <c r="L45" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="M45" t="n">
-        <v>65.45454545454545</v>
+        <v>56.16438356164384</v>
       </c>
       <c r="N45" t="n">
-        <v>15.61808203515258</v>
+        <v>16.28901498856858</v>
       </c>
       <c r="O45" t="n">
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>6.774131672524697</v>
+        <v>7.755097596834748</v>
       </c>
       <c r="Q45" t="n">
         <v>37</v>
@@ -5499,7 +5527,7 @@
         <v>46237</v>
       </c>
       <c r="C46" t="n">
-        <v>8.530663939824125</v>
+        <v>8.52578158819898</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5524,25 +5552,25 @@
         <v>10</v>
       </c>
       <c r="J46" t="n">
-        <v>24.84932105129213</v>
+        <v>25.37350183746037</v>
       </c>
       <c r="K46" t="n">
-        <v>2.586956958444331</v>
+        <v>3.248407643312112</v>
       </c>
       <c r="L46" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M46" t="n">
-        <v>61.11111111111111</v>
+        <v>56.25</v>
       </c>
       <c r="N46" t="n">
-        <v>11.66352812478545</v>
+        <v>17.39270412847368</v>
       </c>
       <c r="O46" t="n">
         <v>10</v>
       </c>
       <c r="P46" t="n">
-        <v>7.226106769653518</v>
+        <v>6.539173349784089</v>
       </c>
       <c r="Q46" t="n">
         <v>54</v>
@@ -5608,7 +5636,7 @@
         <v>46237</v>
       </c>
       <c r="C47" t="n">
-        <v>0.8069945103214758</v>
+        <v>0.7973525854094685</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5636,22 +5664,22 @@
         <v>27.74248530779953</v>
       </c>
       <c r="K47" t="n">
-        <v>8.262015808887547</v>
+        <v>6.968507347676312</v>
       </c>
       <c r="L47" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M47" t="n">
-        <v>56.25</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N47" t="n">
-        <v>9.174193745483864</v>
+        <v>12.77877075447891</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>1.605349926404931</v>
+        <v>2.834004818325209</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5717,7 +5745,7 @@
         <v>46237</v>
       </c>
       <c r="C48" t="n">
-        <v>0.06184994450042606</v>
+        <v>0.06122153038613047</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5734,7 +5762,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H48" t="n">
         <v>5</v>
       </c>
@@ -5745,22 +5777,22 @@
         <v>35.39957983385757</v>
       </c>
       <c r="K48" t="n">
-        <v>5.389388294305686</v>
+        <v>4.318600282512652</v>
       </c>
       <c r="L48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M48" t="n">
-        <v>60</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N48" t="n">
-        <v>12.66074525724039</v>
+        <v>10.89490514088561</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>4.374834867452626</v>
+        <v>5.446200104392851</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5826,7 +5858,7 @@
         <v>46237</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2699097846251305</v>
+        <v>0.2692905760613089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5854,7 +5886,7 @@
         <v>24.46536626635938</v>
       </c>
       <c r="K49" t="n">
-        <v>6.813668029003206</v>
+        <v>6.568623418750885</v>
       </c>
       <c r="L49" t="n">
         <v>14</v>
@@ -5935,7 +5967,7 @@
         <v>46237</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7333636255141159</v>
+        <v>0.7279260454219343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5963,22 +5995,22 @@
         <v>11.86078125763058</v>
       </c>
       <c r="K50" t="n">
-        <v>2.639364525108689</v>
+        <v>1.878337190511004</v>
       </c>
       <c r="L50" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M50" t="n">
-        <v>53.33333333333334</v>
+        <v>47.61904761904762</v>
       </c>
       <c r="N50" t="n">
-        <v>12.72852381361679</v>
+        <v>13.63160196619841</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>1.325646822918958</v>
+        <v>2.082545581325612</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6044,7 +6076,7 @@
         <v>46237</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1821838432534583</v>
+        <v>0.180719223001842</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6063,7 +6095,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -6076,16 +6108,16 @@
         <v>27.30972539236674</v>
       </c>
       <c r="K51" t="n">
-        <v>5.593976638829568</v>
+        <v>4.745080963603465</v>
       </c>
       <c r="L51" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M51" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="N51" t="n">
-        <v>19.55687804064408</v>
+        <v>18.09582420420059</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
@@ -6118,7 +6150,7 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>17.29484107991414</v>
+        <v>17.95972797934672</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6163,7 +6195,7 @@
         <v>46237</v>
       </c>
       <c r="C52" t="n">
-        <v>4.165404340530646</v>
+        <v>4.110888760831124</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6223,22 +6255,22 @@
         <v>12.1710603868542</v>
       </c>
       <c r="Y52" t="n">
-        <v>4.425129100243563</v>
+        <v>5.675984735339834</v>
       </c>
       <c r="Z52" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AA52" t="n">
-        <v>46.875</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="AB52" t="n">
-        <v>13.28027921400272</v>
+        <v>13.67485347556112</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.740387892865615</v>
+        <v>2.463863797718213</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6272,7 +6304,7 @@
         <v>46237</v>
       </c>
       <c r="C53" t="n">
-        <v>1.552559863816388</v>
+        <v>1.550524557795511</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6297,25 +6329,25 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>27.64453042428524</v>
+        <v>28.82678537432798</v>
       </c>
       <c r="K53" t="n">
-        <v>0.6809107161258598</v>
+        <v>2.219138022125944</v>
       </c>
       <c r="L53" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M53" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N53" t="n">
-        <v>10.49707132013907</v>
+        <v>18.3375126485811</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>7.269589867448301</v>
+        <v>5.655361696185279</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6373,7 +6405,7 @@
         <v>46237</v>
       </c>
       <c r="C54" t="n">
-        <v>0.09466828046660558</v>
+        <v>0.09446207864301949</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6401,7 +6433,7 @@
         <v>42.39442432818535</v>
       </c>
       <c r="K54" t="n">
-        <v>17.12023735171848</v>
+        <v>16.86513177251363</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -6439,7 +6471,7 @@
         <v>114.7400208810756</v>
       </c>
       <c r="Y54" t="n">
-        <v>32.5322130453469</v>
+        <v>32.67916808281876</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -6484,7 +6516,7 @@
         <v>46237</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8747349500098697</v>
+        <v>0.848686071676284</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6509,25 +6541,25 @@
         <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>11.62878088168478</v>
+        <v>11.95011127641994</v>
       </c>
       <c r="K55" t="n">
-        <v>3.463981326811383</v>
+        <v>0.7492488089583249</v>
       </c>
       <c r="L55" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="M55" t="n">
-        <v>66.12903225806451</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N55" t="n">
-        <v>12.14663030481262</v>
+        <v>15.12173145603583</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>2.451112590746063</v>
+        <v>5.211702571597532</v>
       </c>
       <c r="Q55" t="n">
         <v>44</v>
@@ -6554,16 +6586,16 @@
         <v>25.41488056506582</v>
       </c>
       <c r="Y55" t="n">
-        <v>8.567618353150774</v>
+        <v>11.29039853386937</v>
       </c>
       <c r="Z55" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AA55" t="n">
         <v>50</v>
       </c>
       <c r="AB55" t="n">
-        <v>10.86223550521618</v>
+        <v>9.686169325397467</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6603,7 +6635,7 @@
         <v>46237</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9757144331858283</v>
+        <v>0.9686045457480569</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6631,7 +6663,7 @@
         <v>30.29575178666554</v>
       </c>
       <c r="K56" t="n">
-        <v>10.55611060323638</v>
+        <v>10.56099944500437</v>
       </c>
       <c r="L56" t="n">
         <v>2</v>
@@ -6658,10 +6690,10 @@
         <v>100</v>
       </c>
       <c r="X56" t="n">
-        <v>17.75189696236843</v>
+        <v>17.75189696236841</v>
       </c>
       <c r="Y56" t="n">
-        <v>6.11097276966307</v>
+        <v>6.106820953943637</v>
       </c>
       <c r="Z56" t="n">
         <v>8</v>
@@ -6670,13 +6702,13 @@
         <v>37.5</v>
       </c>
       <c r="AB56" t="n">
-        <v>10.81948936760916</v>
+        <v>10.81948936760917</v>
       </c>
       <c r="AC56" t="n">
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>4.142153076946919</v>
+        <v>4.146391767336666</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6702,7 +6734,7 @@
         <v>46237</v>
       </c>
       <c r="C57" t="n">
-        <v>1.459995290938866</v>
+        <v>1.448488708952631</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6730,7 +6762,7 @@
         <v>32.76213282665623</v>
       </c>
       <c r="K57" t="n">
-        <v>25.01534407079624</v>
+        <v>24.0300673955798</v>
       </c>
       <c r="L57" t="n">
         <v>1</v>
@@ -6768,16 +6800,16 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>9.990483445081322</v>
+        <v>10.69987058366207</v>
       </c>
       <c r="Z57" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA57" t="n">
-        <v>66.66666666666667</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="AB57" t="n">
-        <v>13.75807019707077</v>
+        <v>14.39928291782675</v>
       </c>
       <c r="AC57" t="n">
         <v>6</v>
@@ -6817,7 +6849,7 @@
         <v>46237</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7809081043611865</v>
+        <v>0.7565381815371161</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6836,7 +6868,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %89.19: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -6846,25 +6878,25 @@
         <v>10</v>
       </c>
       <c r="J58" t="n">
-        <v>13.34780199539933</v>
+        <v>16.33375063430099</v>
       </c>
       <c r="K58" t="n">
-        <v>1.642931167695849</v>
+        <v>1.985254660670122</v>
       </c>
       <c r="L58" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="M58" t="n">
-        <v>75</v>
+        <v>89.18918918918919</v>
       </c>
       <c r="N58" t="n">
-        <v>18.31342452521605</v>
+        <v>19.01585258090028</v>
       </c>
       <c r="O58" t="n">
         <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>3.302806003071179</v>
+        <v>2.956060020010409</v>
       </c>
       <c r="Q58" t="n">
         <v>24</v>
@@ -6891,10 +6923,10 @@
         <v>41.32985472592288</v>
       </c>
       <c r="Y58" t="n">
-        <v>11.92416602688824</v>
+        <v>14.67276251936057</v>
       </c>
       <c r="Z58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="inlineStr"/>
       <c r="AB58" t="inlineStr"/>
@@ -6936,7 +6968,7 @@
         <v>46237</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8229828956796779</v>
+        <v>0.8204947117575823</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,22 +6996,22 @@
         <v>12.06710605756499</v>
       </c>
       <c r="K59" t="n">
-        <v>3.022557196199949</v>
+        <v>2.711081621465117</v>
       </c>
       <c r="L59" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M59" t="n">
-        <v>69.49152542372882</v>
+        <v>68.85245901639344</v>
       </c>
       <c r="N59" t="n">
-        <v>13.36391853238126</v>
+        <v>13.5467393731803</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>4.831410653417234</v>
+        <v>5.149316213051724</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7006,16 +7038,16 @@
         <v>10.2478061424703</v>
       </c>
       <c r="Y59" t="n">
-        <v>6.553644194001784</v>
+        <v>6.836167344015598</v>
       </c>
       <c r="Z59" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA59" t="n">
-        <v>43.47826086956522</v>
+        <v>50</v>
       </c>
       <c r="AB59" t="n">
-        <v>16.81170246459129</v>
+        <v>15.44866820059028</v>
       </c>
       <c r="AC59" t="n">
         <v>6</v>
@@ -7055,7 +7087,7 @@
         <v>46237</v>
       </c>
       <c r="C60" t="n">
-        <v>13.29563405664327</v>
+        <v>12.9806471065238</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7083,22 +7115,22 @@
         <v>17.06238107085701</v>
       </c>
       <c r="K60" t="n">
-        <v>4.635189789199501</v>
+        <v>2.156276849323291</v>
       </c>
       <c r="L60" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="M60" t="n">
-        <v>48.38709677419355</v>
+        <v>51.16279069767442</v>
       </c>
       <c r="N60" t="n">
-        <v>12.4349075064265</v>
+        <v>12.73109490548113</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>3.215753913744823</v>
+        <v>5.720376007140504</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7164,7 +7196,7 @@
         <v>46237</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6551044879960993</v>
+        <v>0.6378820360547829</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7181,7 +7213,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H61" t="n">
         <v>5</v>
       </c>
@@ -7192,22 +7228,22 @@
         <v>39.02052765309554</v>
       </c>
       <c r="K61" t="n">
-        <v>5.772876393366988</v>
+        <v>2.992147038341697</v>
       </c>
       <c r="L61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M61" t="n">
-        <v>60</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N61" t="n">
-        <v>48.06650734995709</v>
+        <v>33.49457775007936</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>3.996415480763171</v>
+        <v>6.804259512183441</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7265,7 +7301,7 @@
         <v>46237</v>
       </c>
       <c r="C62" t="n">
-        <v>8.593776126801863</v>
+        <v>8.483704936313975</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7293,22 +7329,22 @@
         <v>15.79076798430271</v>
       </c>
       <c r="K62" t="n">
-        <v>3.280179780042003</v>
+        <v>1.957341929200407</v>
       </c>
       <c r="L62" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M62" t="n">
-        <v>67.39130434782609</v>
+        <v>60.37735849056604</v>
       </c>
       <c r="N62" t="n">
-        <v>14.45431345993661</v>
+        <v>14.33317049238344</v>
       </c>
       <c r="O62" t="n">
         <v>6</v>
       </c>
       <c r="P62" t="n">
-        <v>2.633438696321466</v>
+        <v>3.965048513727276</v>
       </c>
       <c r="Q62" t="n">
         <v>29</v>
@@ -7374,7 +7410,7 @@
         <v>46237</v>
       </c>
       <c r="C63" t="n">
-        <v>0.104135104516161</v>
+        <v>0.1028774111238529</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7402,7 +7438,7 @@
         <v>33.30512547687425</v>
       </c>
       <c r="K63" t="n">
-        <v>4.357879591682301</v>
+        <v>3.09749562983237</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
@@ -7413,7 +7449,7 @@
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>0.615306108968583</v>
+        <v>1.845344892759093</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7479,11 +7515,11 @@
         <v>46237</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1670369227966545</v>
+        <v>0.1653612446430489</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7493,7 +7529,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -7504,25 +7540,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>21.14278085376978</v>
+        <v>21.49597893333038</v>
       </c>
       <c r="K64" t="n">
-        <v>1.334454200896529</v>
+        <v>0.7692299812623427</v>
       </c>
       <c r="L64" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M64" t="n">
-        <v>61.90476190476191</v>
+        <v>60.97560975609756</v>
       </c>
       <c r="N64" t="n">
-        <v>14.42105333595837</v>
+        <v>15.08628706395872</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>3.617274921949543</v>
+        <v>4.198474097226268</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7545,27 +7581,17 @@
       <c r="W64" t="n">
         <v>71.84466019417475</v>
       </c>
-      <c r="X64" t="n">
-        <v>11.49424813787225</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>9.112392887220743</v>
-      </c>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>17.18726889310038</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
         <v>2</v>
       </c>
-      <c r="AD64" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD64" t="inlineStr"/>
       <c r="AE64" t="n">
         <v>54</v>
       </c>
@@ -7598,7 +7624,7 @@
         <v>46237</v>
       </c>
       <c r="C65" t="n">
-        <v>6.184994323818231</v>
+        <v>6.295719038293756</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7617,7 +7643,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %82.35: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -7627,25 +7653,25 @@
         <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>28.12426974452364</v>
+        <v>28.12109136686307</v>
       </c>
       <c r="K65" t="n">
-        <v>1.906412478336228</v>
+        <v>3.72616984402081</v>
       </c>
       <c r="L65" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M65" t="n">
-        <v>82.35294117647059</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="N65" t="n">
-        <v>15.35336073609163</v>
+        <v>13.19135185717638</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>7.942176870748296</v>
+        <v>6.048454469507103</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7711,7 +7737,7 @@
         <v>46237</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4337911161650584</v>
+        <v>0.4296026174289592</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7739,22 +7765,22 @@
         <v>11.2547528069613</v>
       </c>
       <c r="K66" t="n">
-        <v>3.965262564812644</v>
+        <v>2.961419114304431</v>
       </c>
       <c r="L66" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="M66" t="n">
-        <v>50</v>
+        <v>53.7037037037037</v>
       </c>
       <c r="N66" t="n">
-        <v>18.77237618853692</v>
+        <v>18.17474417697341</v>
       </c>
       <c r="O66" t="n">
         <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>1.957132012165008</v>
+        <v>2.951183959811443</v>
       </c>
       <c r="Q66" t="n">
         <v>35</v>
@@ -7820,7 +7846,7 @@
         <v>46237</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02819011081451109</v>
+        <v>0.02798097434506084</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7848,22 +7874,22 @@
         <v>17.88062675770013</v>
       </c>
       <c r="K67" t="n">
-        <v>2.219068007172265</v>
+        <v>1.460726362679332</v>
       </c>
       <c r="L67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M67" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N67" t="n">
-        <v>13.30779001380697</v>
+        <v>11.54719770132041</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>1.742269840205135</v>
+        <v>2.502715807734157</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7909,7 +7935,7 @@
         <v>46237</v>
       </c>
       <c r="C68" t="n">
-        <v>3.191372857343514</v>
+        <v>3.263044482015865</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7918,7 +7944,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7933,27 +7959,17 @@
       <c r="I68" t="n">
         <v>10</v>
       </c>
-      <c r="J68" t="n">
-        <v>12.46006389776357</v>
-      </c>
-      <c r="K68" t="n">
-        <v>10.65305008314123</v>
-      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="n">
-        <v>12</v>
-      </c>
-      <c r="M68" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N68" t="n">
-        <v>13.04645653865888</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
         <v>2</v>
       </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
+      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="n">
         <v>5</v>
       </c>
@@ -7976,10 +7992,10 @@
         <v>80</v>
       </c>
       <c r="X68" t="n">
-        <v>83.80957438533017</v>
+        <v>84.86382491664126</v>
       </c>
       <c r="Y68" t="n">
-        <v>3.134390662042497</v>
+        <v>1.523805650793641</v>
       </c>
       <c r="Z68" t="n">
         <v>1</v>
@@ -7990,7 +8006,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>5.02305139172946</v>
+        <v>6.576405995383139</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8024,16 +8040,16 @@
         <v>46237</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4043387300548991</v>
+        <v>0.39909702861282</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -8041,7 +8057,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H69" t="n">
         <v>5</v>
       </c>
@@ -8052,22 +8072,22 @@
         <v>29.4573350207784</v>
       </c>
       <c r="K69" t="n">
-        <v>3.428411784676744</v>
+        <v>2.087603163325857</v>
       </c>
       <c r="L69" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M69" t="n">
-        <v>62.5</v>
+        <v>80</v>
       </c>
       <c r="N69" t="n">
-        <v>15.74456577461902</v>
+        <v>16.53833303572285</v>
       </c>
       <c r="O69" t="n">
         <v>3</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>0.8937391107267434</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8117,7 +8137,7 @@
         <v>46237</v>
       </c>
       <c r="C70" t="n">
-        <v>0.3988690023448942</v>
+        <v>0.3967828401089686</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8142,25 +8162,25 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>19.94256627542972</v>
+        <v>20.66685340467635</v>
       </c>
       <c r="K70" t="n">
-        <v>1.390365291086737</v>
+        <v>1.780895346528988</v>
       </c>
       <c r="L70" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M70" t="n">
-        <v>51.72413793103448</v>
+        <v>58.06451612903226</v>
       </c>
       <c r="N70" t="n">
-        <v>14.53893495737219</v>
+        <v>13.60436768229634</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>6.518996839529412</v>
+        <v>6.110286839487022</v>
       </c>
       <c r="Q70" t="n">
         <v>30</v>
@@ -8226,7 +8246,7 @@
         <v>46237</v>
       </c>
       <c r="C71" t="n">
-        <v>3.317597231298988</v>
+        <v>3.284082807958367</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8243,11 +8263,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>5</v>
       </c>
@@ -8258,22 +8274,22 @@
         <v>21.33797260620418</v>
       </c>
       <c r="K71" t="n">
-        <v>5.899067900297461</v>
+        <v>4.829273725313166</v>
       </c>
       <c r="L71" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M71" t="n">
-        <v>76.92307692307692</v>
+        <v>70</v>
       </c>
       <c r="N71" t="n">
-        <v>11.1036158799086</v>
+        <v>11.59837148247931</v>
       </c>
       <c r="O71" t="n">
         <v>6</v>
       </c>
       <c r="P71" t="n">
-        <v>0.09530971490472329</v>
+        <v>1.116793270698913</v>
       </c>
       <c r="Q71" t="n">
         <v>43</v>
@@ -8339,7 +8355,7 @@
         <v>46237</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07363088480735989</v>
+        <v>0.0723718425045068</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8367,16 +8383,16 @@
         <v>29.15235727667785</v>
       </c>
       <c r="K72" t="n">
-        <v>13.06080754663206</v>
+        <v>11.12753810584826</v>
       </c>
       <c r="L72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M72" t="n">
-        <v>71.42857142857143</v>
+        <v>62.5</v>
       </c>
       <c r="N72" t="n">
-        <v>17.1591378756031</v>
+        <v>20.36965270753011</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
@@ -8409,7 +8425,7 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>18.0240520375778</v>
+        <v>19.42578972647294</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -8454,7 +8470,7 @@
         <v>46237</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07257901607626739</v>
+        <v>0.07047838980354947</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8471,11 +8487,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>5</v>
       </c>
@@ -8486,22 +8498,22 @@
         <v>20.52993807340809</v>
       </c>
       <c r="K73" t="n">
-        <v>3.221705581405776</v>
+        <v>0.2341998479137963</v>
       </c>
       <c r="L73" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="M73" t="n">
-        <v>76.92307692307692</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N73" t="n">
-        <v>15.61518280627299</v>
+        <v>15.48311115261322</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>6.566733595821606</v>
+        <v>9.742982102819141</v>
       </c>
       <c r="Q73" t="n">
         <v>12</v>
@@ -8567,7 +8579,7 @@
         <v>46237</v>
       </c>
       <c r="C74" t="n">
-        <v>5.124709710920363</v>
+        <v>4.981875647351393</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8595,22 +8607,22 @@
         <v>17.41018086324394</v>
       </c>
       <c r="K74" t="n">
-        <v>7.177451049655614</v>
+        <v>4.190239730394918</v>
       </c>
       <c r="L74" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="M74" t="n">
-        <v>65.21739130434783</v>
+        <v>62.5</v>
       </c>
       <c r="N74" t="n">
-        <v>22.39330437546893</v>
+        <v>19.22643583577678</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>0.7674645574126338</v>
+        <v>3.656542378118433</v>
       </c>
       <c r="Q74" t="n">
         <v>35</v>
@@ -8637,7 +8649,7 @@
         <v>95.98093909010421</v>
       </c>
       <c r="Y74" t="n">
-        <v>11.48233702270417</v>
+        <v>13.9494694485143</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
@@ -8682,16 +8694,16 @@
         <v>46237</v>
       </c>
       <c r="C75" t="n">
-        <v>0.138426061754845</v>
+        <v>0.1375906508224307</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8714,7 +8726,7 @@
         <v>19.1703426786477</v>
       </c>
       <c r="K75" t="n">
-        <v>6.226682790328297</v>
+        <v>5.585597354593652</v>
       </c>
       <c r="L75" t="n">
         <v>3</v>
@@ -8729,7 +8741,7 @@
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>0.3924802774138314</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8795,7 +8807,7 @@
         <v>46237</v>
       </c>
       <c r="C76" t="n">
-        <v>1.824994073439563</v>
+        <v>1.809296031055181</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8823,22 +8835,22 @@
         <v>21.37762355327298</v>
       </c>
       <c r="K76" t="n">
-        <v>5.298132809141887</v>
+        <v>4.392390387349332</v>
       </c>
       <c r="L76" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M76" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="N76" t="n">
-        <v>12.11418143995526</v>
+        <v>11.01737898992127</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>4.465290186465598</v>
+        <v>5.371665110688206</v>
       </c>
       <c r="Q76" t="n">
         <v>42</v>
@@ -8904,7 +8916,7 @@
         <v>46237</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5124709710920362</v>
+        <v>0.5015536936249991</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8932,16 +8944,16 @@
         <v>22.11886481778794</v>
       </c>
       <c r="K77" t="n">
-        <v>5.546489838030411</v>
+        <v>3.298010645583349</v>
       </c>
       <c r="L77" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M77" t="n">
-        <v>70.83333333333333</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N77" t="n">
-        <v>16.85356364151541</v>
+        <v>19.15179104564679</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -9013,7 +9025,7 @@
         <v>46237</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05280386289433271</v>
+        <v>0.05343734705242231</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9030,7 +9042,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H78" t="n">
         <v>5</v>
       </c>
@@ -9041,16 +9057,16 @@
         <v>20.92476038411055</v>
       </c>
       <c r="K78" t="n">
-        <v>11.98265339410685</v>
+        <v>13.32610125980493</v>
       </c>
       <c r="L78" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M78" t="n">
-        <v>73.33333333333333</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N78" t="n">
-        <v>18.16221833390237</v>
+        <v>16.75776347050931</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
@@ -9083,22 +9099,22 @@
         <v>23.16536029857119</v>
       </c>
       <c r="Y78" t="n">
-        <v>9.079425316790202</v>
+        <v>7.988657699627899</v>
       </c>
       <c r="Z78" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA78" t="n">
-        <v>41.1764705882353</v>
+        <v>50</v>
       </c>
       <c r="AB78" t="n">
-        <v>16.34038047129173</v>
+        <v>15.27678857792912</v>
       </c>
       <c r="AC78" t="n">
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.0125042504596</v>
+        <v>2.18597213135534</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9132,7 +9148,7 @@
         <v>46237</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8898818203976717</v>
+        <v>0.8848720179641453</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9160,22 +9176,22 @@
         <v>14.97695523729659</v>
       </c>
       <c r="K79" t="n">
-        <v>3.048834277217249</v>
+        <v>2.468696230905243</v>
       </c>
       <c r="L79" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M79" t="n">
-        <v>44.68085106382978</v>
+        <v>46.93877551020408</v>
       </c>
       <c r="N79" t="n">
-        <v>11.56750774009771</v>
+        <v>12.10364544634033</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>1.893437937913811</v>
+        <v>2.47031909471227</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9241,7 +9257,7 @@
         <v>46237</v>
       </c>
       <c r="C80" t="n">
-        <v>0.13295634414279</v>
+        <v>0.1373802728225872</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9266,10 +9282,10 @@
         <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>68.88556557298216</v>
+        <v>68.8841896784632</v>
       </c>
       <c r="K80" t="n">
-        <v>0.6369420169175521</v>
+        <v>3.980891586626245</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9280,7 +9296,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>9.303798183283906</v>
+        <v>5.78866782302907</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9346,11 +9362,11 @@
         <v>46237</v>
       </c>
       <c r="C81" t="n">
-        <v>1.084477730245694</v>
+        <v>1.077162304245236</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9374,22 +9390,22 @@
         <v>11.07045147382514</v>
       </c>
       <c r="K81" t="n">
-        <v>2.413938813109318</v>
+        <v>1.723097895026959</v>
       </c>
       <c r="L81" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M81" t="n">
-        <v>54.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="N81" t="n">
-        <v>12.30981727638644</v>
+        <v>11.72548731552414</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>7.407254593277735</v>
+        <v>8.136698818899912</v>
       </c>
       <c r="Q81" t="n">
         <v>31</v>
@@ -9416,22 +9432,22 @@
         <v>27.31228182970742</v>
       </c>
       <c r="Y81" t="n">
-        <v>8.923746585628923</v>
+        <v>9.538108295113634</v>
       </c>
       <c r="Z81" t="n">
         <v>9</v>
       </c>
       <c r="AA81" t="n">
-        <v>33.33333333333334</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB81" t="n">
-        <v>11.50734464839207</v>
+        <v>9.438232199299446</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.181705849794268</v>
+        <v>0.5105925779146814</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9465,7 +9481,7 @@
         <v>46237</v>
       </c>
       <c r="C82" t="n">
-        <v>5.105775862334871</v>
+        <v>5.053405827222113</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9493,7 +9509,7 @@
         <v>17.26584051182517</v>
       </c>
       <c r="K82" t="n">
-        <v>12.30949578203666</v>
+        <v>11.1575352580759</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
@@ -9535,22 +9551,22 @@
         <v>15.04024401260009</v>
       </c>
       <c r="Y82" t="n">
-        <v>2.373732995789124</v>
+        <v>3.375087377334585</v>
       </c>
       <c r="Z82" t="n">
         <v>11</v>
       </c>
       <c r="AA82" t="n">
-        <v>45.45454545454545</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB82" t="n">
-        <v>9.120545575431816</v>
+        <v>9.943255098757476</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>1.665808858737505</v>
+        <v>0.6467406859199887</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9584,7 +9600,7 @@
         <v>46237</v>
       </c>
       <c r="C83" t="n">
-        <v>5.911508180248037</v>
+        <v>5.885471682414964</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9612,22 +9628,22 @@
         <v>15.63345941387357</v>
       </c>
       <c r="K83" t="n">
-        <v>9.223762015568671</v>
+        <v>8.742699627371287</v>
       </c>
       <c r="L83" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M83" t="n">
-        <v>53.33333333333334</v>
+        <v>58.62068965517241</v>
       </c>
       <c r="N83" t="n">
-        <v>10.57317693140836</v>
+        <v>11.02630084398797</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>0.710685999188243</v>
+        <v>1.156215890296197</v>
       </c>
       <c r="Q83" t="n">
         <v>44</v>
@@ -9693,7 +9709,7 @@
         <v>46237</v>
       </c>
       <c r="C84" t="n">
-        <v>2.128984376551607</v>
+        <v>2.162739971056111</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9721,22 +9737,22 @@
         <v>15.40292259784146</v>
       </c>
       <c r="K84" t="n">
-        <v>1.919914340113182</v>
+        <v>3.535880778519429</v>
       </c>
       <c r="L84" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="M84" t="n">
-        <v>60.41666666666666</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N84" t="n">
-        <v>13.04640963468292</v>
+        <v>12.81407370694672</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>3.022064608108277</v>
+        <v>1.414117705351425</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9802,7 +9818,7 @@
         <v>46237</v>
       </c>
       <c r="C85" t="n">
-        <v>6.758263355532677</v>
+        <v>6.711225975658173</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9830,22 +9846,22 @@
         <v>15.13449360257271</v>
       </c>
       <c r="K85" t="n">
-        <v>4.877372750581066</v>
+        <v>4.147428301424538</v>
       </c>
       <c r="L85" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M85" t="n">
-        <v>60.97560975609756</v>
+        <v>54.76190476190476</v>
       </c>
       <c r="N85" t="n">
-        <v>13.03001069684921</v>
+        <v>13.1498215264233</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>2.977407964676204</v>
+        <v>3.699152020753993</v>
       </c>
       <c r="Q85" t="n">
         <v>34</v>
@@ -9911,7 +9927,7 @@
         <v>46237</v>
       </c>
       <c r="C86" t="n">
-        <v>3.309182401363403</v>
+        <v>3.332470700958546</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9968,25 +9984,25 @@
         <v>68.35443037974683</v>
       </c>
       <c r="X86" t="n">
-        <v>29.73457526325705</v>
+        <v>30.48168037312833</v>
       </c>
       <c r="Y86" t="n">
-        <v>0.1269821904761992</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA86" t="n">
-        <v>39.1304347826087</v>
+        <v>35</v>
       </c>
       <c r="AB86" t="n">
-        <v>12.51003871173557</v>
+        <v>10.79079935884037</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>5.880484978159695</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="AE86" t="n">
         <v>51</v>
@@ -10020,7 +10036,7 @@
         <v>46237</v>
       </c>
       <c r="C87" t="n">
-        <v>5.727430968229638</v>
+        <v>5.769760889731203</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10052,7 +10068,7 @@
         <v>29.54558799520699</v>
       </c>
       <c r="K87" t="n">
-        <v>5.449995867049995</v>
+        <v>6.229348786736488</v>
       </c>
       <c r="L87" t="n">
         <v>6</v>
@@ -10061,7 +10077,7 @@
         <v>83.33333333333333</v>
       </c>
       <c r="N87" t="n">
-        <v>9.497966602573221</v>
+        <v>8.337490203764601</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
@@ -10133,7 +10149,7 @@
         <v>46237</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9344810766852593</v>
+        <v>0.9442000908105034</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10150,11 +10166,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %82.14: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>5</v>
       </c>
@@ -10165,22 +10177,22 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>4.691409917296685</v>
+        <v>5.780246617326124</v>
       </c>
       <c r="L88" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M88" t="n">
-        <v>82.14285714285714</v>
+        <v>74.07407407407408</v>
       </c>
       <c r="N88" t="n">
-        <v>12.25028825824852</v>
+        <v>11.4800387843004</v>
       </c>
       <c r="O88" t="n">
         <v>10</v>
       </c>
       <c r="P88" t="n">
-        <v>5.070702636345192</v>
+        <v>3.989169544990179</v>
       </c>
       <c r="Q88" t="n">
         <v>44</v>
@@ -10246,7 +10258,7 @@
         <v>46237</v>
       </c>
       <c r="C89" t="n">
-        <v>1.941751683512434</v>
+        <v>1.917643441847706</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10274,16 +10286,16 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>5.472757709204235</v>
+        <v>4.163237674541942</v>
       </c>
       <c r="L89" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M89" t="n">
-        <v>67.5</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N89" t="n">
-        <v>13.78300315643509</v>
+        <v>13.76877936814122</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
@@ -10316,7 +10328,7 @@
         <v>28.7873334490923</v>
       </c>
       <c r="Y89" t="n">
-        <v>15.3203000669588</v>
+        <v>16.37165935631426</v>
       </c>
       <c r="Z89" t="n">
         <v>2</v>
@@ -10361,7 +10373,7 @@
         <v>46237</v>
       </c>
       <c r="C90" t="n">
-        <v>2.625467042437919</v>
+        <v>2.596129453493399</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10389,22 +10401,22 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>3.496564434361726</v>
+        <v>2.340069374448173</v>
       </c>
       <c r="L90" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="M90" t="n">
-        <v>74.50980392156863</v>
+        <v>63.49206349206349</v>
       </c>
       <c r="N90" t="n">
-        <v>14.26636743751452</v>
+        <v>14.87933638741587</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>4.351289910202172</v>
+        <v>5.530512789514463</v>
       </c>
       <c r="Q90" t="n">
         <v>42</v>
@@ -10431,7 +10443,7 @@
         <v>33.24184775233741</v>
       </c>
       <c r="Y90" t="n">
-        <v>13.67011673776437</v>
+        <v>14.63478724698701</v>
       </c>
       <c r="Z90" t="n">
         <v>2</v>
@@ -10476,7 +10488,7 @@
         <v>46237</v>
       </c>
       <c r="C91" t="n">
-        <v>0.234146216001518</v>
+        <v>0.2349981024608146</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10504,16 +10516,16 @@
         <v>15.33687628212038</v>
       </c>
       <c r="K91" t="n">
-        <v>3.270868963668039</v>
+        <v>3.646595962003873</v>
       </c>
       <c r="L91" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="M91" t="n">
-        <v>56.25</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N91" t="n">
-        <v>13.58921776104736</v>
+        <v>13.56657022385137</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
@@ -10585,7 +10597,7 @@
         <v>46237</v>
       </c>
       <c r="C92" t="n">
-        <v>1.093944574280776</v>
+        <v>1.103460211673363</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10613,7 +10625,7 @@
         <v>23.70319776773422</v>
       </c>
       <c r="K92" t="n">
-        <v>3.82397518254467</v>
+        <v>4.727084283061633</v>
       </c>
       <c r="L92" t="n">
         <v>16</v>
@@ -10622,13 +10634,13 @@
         <v>56.25</v>
       </c>
       <c r="N92" t="n">
-        <v>16.47744676738716</v>
+        <v>16.16576288577387</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>4.022216265667922</v>
+        <v>3.125185561446719</v>
       </c>
       <c r="Q92" t="n">
         <v>56</v>
@@ -10694,7 +10706,7 @@
         <v>46237</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04228516506470987</v>
+        <v>0.04186626883596245</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10719,25 +10731,25 @@
         <v>10</v>
       </c>
       <c r="J93" t="n">
-        <v>20.06295203850619</v>
+        <v>20.11491625845134</v>
       </c>
       <c r="K93" t="n">
-        <v>1.959619735739704</v>
+        <v>1.015227395707186</v>
       </c>
       <c r="L93" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="M93" t="n">
-        <v>58.33333333333334</v>
+        <v>62.22222222222222</v>
       </c>
       <c r="N93" t="n">
-        <v>14.40452539607959</v>
+        <v>14.33054855153099</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>3.962725905345876</v>
+        <v>4.934674437514208</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10803,7 +10815,7 @@
         <v>46237</v>
       </c>
       <c r="C94" t="n">
-        <v>6.121882136840495</v>
+        <v>6.164229501153118</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10831,22 +10843,22 @@
         <v>11.31569733043036</v>
       </c>
       <c r="K94" t="n">
-        <v>1.766569404618124</v>
+        <v>2.470527091664887</v>
       </c>
       <c r="L94" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="M94" t="n">
-        <v>42.5925925925926</v>
+        <v>31.25</v>
       </c>
       <c r="N94" t="n">
-        <v>12.39447518301613</v>
+        <v>11.62002772702134</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>6.125224257681428</v>
+        <v>5.396159330173766</v>
       </c>
       <c r="Q94" t="n">
         <v>40</v>
@@ -10873,7 +10885,7 @@
         <v>46.65531127586331</v>
       </c>
       <c r="Y94" t="n">
-        <v>9.749027572770819</v>
+        <v>9.124727606924555</v>
       </c>
       <c r="Z94" t="n">
         <v>2</v>
@@ -10918,7 +10930,7 @@
         <v>46237</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1428439156847824</v>
+        <v>0.1411671679157222</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10935,11 +10947,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>5</v>
       </c>
@@ -10950,22 +10958,22 @@
         <v>23.34731360730358</v>
       </c>
       <c r="K95" t="n">
-        <v>2.963366018750135</v>
+        <v>1.754748952778318</v>
       </c>
       <c r="L95" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="M95" t="n">
-        <v>78.57142857142857</v>
+        <v>65.38461538461539</v>
       </c>
       <c r="N95" t="n">
-        <v>17.8824332376777</v>
+        <v>19.65396541550904</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>2.949237285712747</v>
+        <v>4.172042180745583</v>
       </c>
       <c r="Q95" t="n">
         <v>22</v>
@@ -11031,7 +11039,7 @@
         <v>46237</v>
       </c>
       <c r="C96" t="n">
-        <v>0.134218586620101</v>
+        <v>0.1308583829443147</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11056,25 +11064,25 @@
         <v>10</v>
       </c>
       <c r="J96" t="n">
-        <v>12.45241464719801</v>
+        <v>12.79292615761875</v>
       </c>
       <c r="K96" t="n">
-        <v>3.331777738548736</v>
+        <v>1.138206322956004</v>
       </c>
       <c r="L96" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="M96" t="n">
-        <v>58.73015873015873</v>
+        <v>56.52173913043478</v>
       </c>
       <c r="N96" t="n">
-        <v>14.43137887764547</v>
+        <v>12.43485955793264</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>6.453215465162399</v>
+        <v>8.762063318333336</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11101,16 +11109,16 @@
         <v>16.74415231729489</v>
       </c>
       <c r="Y96" t="n">
-        <v>9.535523687776394</v>
+        <v>11.80032972907986</v>
       </c>
       <c r="Z96" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AA96" t="n">
-        <v>42.85714285714285</v>
+        <v>40</v>
       </c>
       <c r="AB96" t="n">
-        <v>16.88679887629387</v>
+        <v>16.42948776937994</v>
       </c>
       <c r="AC96" t="n">
         <v>8</v>
@@ -11150,7 +11158,7 @@
         <v>46237</v>
       </c>
       <c r="C97" t="n">
-        <v>1.842875827562707</v>
+        <v>1.84611310145456</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11178,22 +11186,22 @@
         <v>24.72840729454471</v>
       </c>
       <c r="K97" t="n">
-        <v>3.108575075850672</v>
+        <v>3.28969997484112</v>
       </c>
       <c r="L97" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M97" t="n">
-        <v>45</v>
+        <v>47.61904761904762</v>
       </c>
       <c r="N97" t="n">
-        <v>11.68685273681049</v>
+        <v>13.47471292030109</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>0.8645497462200114</v>
+        <v>0.6876774986585232</v>
       </c>
       <c r="Q97" t="n">
         <v>51</v>
@@ -11259,7 +11267,7 @@
         <v>46237</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6349086075176275</v>
+        <v>0.6383028122512628</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11276,7 +11284,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H98" t="n">
         <v>5</v>
       </c>
@@ -11287,22 +11299,22 @@
         <v>21.12557680400878</v>
       </c>
       <c r="K98" t="n">
-        <v>5.747009945134995</v>
+        <v>6.31233068181063</v>
       </c>
       <c r="L98" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M98" t="n">
-        <v>66.66666666666667</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="N98" t="n">
-        <v>18.51513166406675</v>
+        <v>16.92060910488019</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>4.021853721511004</v>
+        <v>3.468712702034971</v>
       </c>
       <c r="Q98" t="n">
         <v>48</v>
@@ -11368,7 +11380,7 @@
         <v>46237</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4830185849818769</v>
+        <v>0.4826192082713111</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11396,7 +11408,7 @@
         <v>28.77817890954801</v>
       </c>
       <c r="K99" t="n">
-        <v>3.913311100355954</v>
+        <v>3.827391929413859</v>
       </c>
       <c r="L99" t="n">
         <v>18</v>
@@ -11405,13 +11417,13 @@
         <v>66.66666666666667</v>
       </c>
       <c r="N99" t="n">
-        <v>12.77959199349419</v>
+        <v>12.82986200275538</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>0.08342424923821756</v>
+        <v>0.1662452146573123</v>
       </c>
       <c r="Q99" t="n">
         <v>35</v>
@@ -11477,7 +11489,7 @@
         <v>46237</v>
       </c>
       <c r="C100" t="n">
-        <v>325.7851091790787</v>
+        <v>326.7237226297649</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11509,7 +11521,7 @@
         <v>25.87300653788257</v>
       </c>
       <c r="K100" t="n">
-        <v>6.297000253468688</v>
+        <v>6.603250574291852</v>
       </c>
       <c r="L100" t="n">
         <v>13</v>
@@ -11590,16 +11602,16 @@
         <v>46237</v>
       </c>
       <c r="C101" t="n">
-        <v>324.3791783837299</v>
+        <v>321.4056693904869</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -11618,22 +11630,22 @@
         <v>14.83975271775182</v>
       </c>
       <c r="K101" t="n">
-        <v>2.72084425723278</v>
+        <v>1.779226007521717</v>
       </c>
       <c r="L101" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="M101" t="n">
-        <v>55.17241379310344</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N101" t="n">
-        <v>9.643846868652336</v>
+        <v>11.35964129654057</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>0.2169145916495419</v>
       </c>
       <c r="Q101" t="n">
         <v>29</v>
@@ -11699,7 +11711,7 @@
         <v>46237</v>
       </c>
       <c r="C102" t="n">
-        <v>390.0573113018389</v>
+        <v>386.4782387927601</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11798,7 +11810,7 @@
         <v>46237</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7173751597930625</v>
+        <v>0.7178276586471632</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11826,7 +11838,7 @@
         <v>31.6668549372698</v>
       </c>
       <c r="K103" t="n">
-        <v>10.33111050091629</v>
+        <v>10.40070407464377</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
@@ -11865,25 +11877,25 @@
         <v>68.18181818181819</v>
       </c>
       <c r="X103" t="n">
-        <v>10.84879266873253</v>
+        <v>10.9184091346022</v>
       </c>
       <c r="Y103" t="n">
-        <v>0.4670165144363025</v>
+        <v>0.4667440364477082</v>
       </c>
       <c r="Z103" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA103" t="n">
-        <v>34.61538461538461</v>
+        <v>35.84905660377358</v>
       </c>
       <c r="AB103" t="n">
-        <v>10.78940398518989</v>
+        <v>11.64874872800553</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>7.568328831071646</v>
+        <v>7.56858186806515</v>
       </c>
       <c r="AE103" t="n">
         <v>34</v>
@@ -11917,7 +11929,7 @@
         <v>46237</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04985862539829875</v>
+        <v>0.0492296808120056</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11934,7 +11946,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.19: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H104" t="n">
         <v>5</v>
       </c>
@@ -11945,22 +11961,22 @@
         <v>27.65580276361549</v>
       </c>
       <c r="K104" t="n">
-        <v>2.971937368788291</v>
+        <v>1.672991759460962</v>
       </c>
       <c r="L104" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M104" t="n">
-        <v>65</v>
+        <v>76.19047619047619</v>
       </c>
       <c r="N104" t="n">
-        <v>14.25029794564913</v>
+        <v>15.96576789787374</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>0.9983910738027291</v>
+        <v>2.288718174089244</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>

--- a/TDA_Result.xlsx
+++ b/TDA_Result.xlsx
@@ -679,7 +679,7 @@
         <v>46237</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4725207813133375</v>
+        <v>0.4607877745041246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -739,22 +739,22 @@
         <v>14.94856954517825</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.7922830391085545</v>
+        <v>3.255676956712206</v>
       </c>
       <c r="Z2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AA2" t="n">
-        <v>44.44444444444444</v>
+        <v>40</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.03336785576561</v>
+        <v>13.55541461777871</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>7.265278530432051</v>
+        <v>4.903980816698638</v>
       </c>
       <c r="AE2" t="n">
         <v>43</v>
@@ -788,7 +788,7 @@
         <v>46237</v>
       </c>
       <c r="C3" t="n">
-        <v>0.751489028332933</v>
+        <v>0.739364492965886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,22 +848,22 @@
         <v>12.13279917920569</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.226552637053979</v>
+        <v>2.820164933076241</v>
       </c>
       <c r="Z3" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="AA3" t="n">
-        <v>44.26229508196721</v>
+        <v>44.82758620689656</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.50485684922246</v>
+        <v>10.79236473985161</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>8.882394608247013</v>
+        <v>7.388194332681564</v>
       </c>
       <c r="AE3" t="n">
         <v>38</v>
@@ -897,7 +897,7 @@
         <v>46237</v>
       </c>
       <c r="C4" t="n">
-        <v>1.390633312610751</v>
+        <v>1.38867550890269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>27.63389482946404</v>
       </c>
       <c r="K4" t="n">
-        <v>7.672421954572184</v>
+        <v>7.520835288952377</v>
       </c>
       <c r="L4" t="n">
         <v>16</v>
@@ -1006,7 +1006,7 @@
         <v>46237</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2671867354724948</v>
+        <v>0.2649003767482757</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,25 +1063,25 @@
         <v>58.46153846153846</v>
       </c>
       <c r="X5" t="n">
-        <v>16.70614361206606</v>
+        <v>16.71841465953139</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.367469365904886</v>
+        <v>5.195780075516621</v>
       </c>
       <c r="Z5" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="AA5" t="n">
-        <v>43.24324324324324</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB5" t="n">
-        <v>15.89552284580699</v>
+        <v>17.13495178814146</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.88976428496496</v>
+        <v>5.067516961070084</v>
       </c>
       <c r="AE5" t="n">
         <v>45</v>
@@ -1115,7 +1115,7 @@
         <v>46237</v>
       </c>
       <c r="C6" t="n">
-        <v>1.954460512247084</v>
+        <v>1.922053115357382</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1144,25 +1144,25 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>22.03360200065558</v>
+        <v>23.72415549749964</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6937241085332335</v>
+        <v>1.218834869806096</v>
       </c>
       <c r="L6" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="M6" t="n">
-        <v>81.25</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N6" t="n">
-        <v>14.70472042945921</v>
+        <v>14.31557485845824</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.297276372516309</v>
+        <v>0.7717586664563791</v>
       </c>
       <c r="Q6" t="n">
         <v>40</v>
@@ -1189,7 +1189,7 @@
         <v>44.49622708587002</v>
       </c>
       <c r="Y6" t="n">
-        <v>21.49273030117917</v>
+        <v>22.79447890746409</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1234,7 +1234,7 @@
         <v>46237</v>
       </c>
       <c r="C7" t="n">
-        <v>2.150116847156821</v>
+        <v>2.162967371979649</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,16 +1262,16 @@
         <v>11.35312764557068</v>
       </c>
       <c r="K7" t="n">
-        <v>3.009136465954687</v>
+        <v>3.624787409243768</v>
       </c>
       <c r="L7" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="M7" t="n">
-        <v>58.20895522388059</v>
+        <v>50.81967213114754</v>
       </c>
       <c r="N7" t="n">
-        <v>12.61338027889698</v>
+        <v>12.67331044452345</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1304,22 +1304,22 @@
         <v>13.79329344082609</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.68562228362525</v>
+        <v>8.139866977778931</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>60</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.615798389642457</v>
+        <v>8.654336102227296</v>
       </c>
       <c r="AC7" t="n">
         <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.439398426890937</v>
+        <v>2.02496225622828</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1353,7 +1353,7 @@
         <v>46237</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3242005996182086</v>
+        <v>0.3206577944891157</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,22 +1381,22 @@
         <v>22.10694516187944</v>
       </c>
       <c r="K8" t="n">
-        <v>3.078867418966613</v>
+        <v>1.952440322215221</v>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M8" t="n">
-        <v>60</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N8" t="n">
-        <v>17.67912674615781</v>
+        <v>17.10466508226268</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>4.774143046247614</v>
+        <v>5.931745879423578</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1462,7 +1462,7 @@
         <v>46237</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5680348004475569</v>
+        <v>0.5685153468082034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>12.72202042588303</v>
       </c>
       <c r="K9" t="n">
-        <v>2.206244896526388</v>
+        <v>2.292709385993685</v>
       </c>
       <c r="L9" t="n">
         <v>45</v>
@@ -1571,7 +1571,7 @@
         <v>46237</v>
       </c>
       <c r="C10" t="n">
-        <v>2.02704267237144</v>
+        <v>2.026203874890748</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,25 +1596,25 @@
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>10.04653454191088</v>
+        <v>10.22410665907629</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1559267409103837</v>
+        <v>0.3125031770833342</v>
       </c>
       <c r="L10" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M10" t="n">
-        <v>43.58974358974359</v>
+        <v>43.90243902439025</v>
       </c>
       <c r="N10" t="n">
-        <v>10.34069535415989</v>
+        <v>10.11800639229653</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>9.828747613263955</v>
+        <v>9.657317399223086</v>
       </c>
       <c r="Q10" t="n">
         <v>44</v>
@@ -1680,7 +1680,7 @@
         <v>46237</v>
       </c>
       <c r="C11" t="n">
-        <v>7.07939667965196</v>
+        <v>7.053840369085257</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,11 +1697,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>5</v>
       </c>
@@ -1709,25 +1705,25 @@
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>20.20204115522435</v>
+        <v>20.55286918845752</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9752438109527528</v>
+        <v>1.055011303692543</v>
       </c>
       <c r="L11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M11" t="n">
-        <v>75</v>
+        <v>73.91304347826087</v>
       </c>
       <c r="N11" t="n">
-        <v>16.4703946183538</v>
+        <v>16.70337383836244</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.005200594353629</v>
+        <v>1.924683072334088</v>
       </c>
       <c r="Q11" t="n">
         <v>49</v>
@@ -1793,16 +1789,16 @@
         <v>46237</v>
       </c>
       <c r="C12" t="n">
-        <v>6.085335778868735</v>
+        <v>6.091235754959528</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1821,7 +1817,7 @@
         <v>20.08266526523165</v>
       </c>
       <c r="K12" t="n">
-        <v>5.943907514934987</v>
+        <v>6.046624364755138</v>
       </c>
       <c r="L12" t="n">
         <v>10</v>
@@ -1836,7 +1832,7 @@
         <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>0.05294545611989054</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1902,7 +1898,7 @@
         <v>46237</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3164164213336986</v>
+        <v>0.3101375254822771</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1930,7 +1926,7 @@
         <v>38.11781916800814</v>
       </c>
       <c r="K13" t="n">
-        <v>11.19029760556367</v>
+        <v>8.983862505226025</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1966,7 +1962,7 @@
         <v>35.74308703619145</v>
       </c>
       <c r="Y13" t="n">
-        <v>18.08769047964968</v>
+        <v>19.71313981081847</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2001,7 +1997,7 @@
         <v>46237</v>
       </c>
       <c r="C14" t="n">
-        <v>8.105015069348937</v>
+        <v>7.990144310693889</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,16 +2057,16 @@
         <v>14.33662537827827</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.332034885985916</v>
+        <v>7.659572234437217</v>
       </c>
       <c r="Z14" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AA14" t="n">
-        <v>40.74074074074074</v>
+        <v>40.90909090909091</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.75804611379783</v>
+        <v>11.26258837364468</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2110,7 +2106,7 @@
         <v>46237</v>
       </c>
       <c r="C15" t="n">
-        <v>11.15031274952612</v>
+        <v>11.30928918235146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,22 +2134,22 @@
         <v>20.36228477344414</v>
       </c>
       <c r="K15" t="n">
-        <v>4.986217230691148</v>
+        <v>6.483066214758493</v>
       </c>
       <c r="L15" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M15" t="n">
-        <v>56.66666666666666</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N15" t="n">
-        <v>17.4192324468736</v>
+        <v>15.0289238728392</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>2.870646117943787</v>
+        <v>1.424577483693157</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2219,7 +2215,7 @@
         <v>46237</v>
       </c>
       <c r="C16" t="n">
-        <v>35.9755373616786</v>
+        <v>36.21076592153833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,22 +2243,22 @@
         <v>19.01528411877121</v>
       </c>
       <c r="K16" t="n">
-        <v>3.694683863609516</v>
+        <v>4.372698785391571</v>
       </c>
       <c r="L16" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="M16" t="n">
-        <v>62</v>
+        <v>63.04347826086956</v>
       </c>
       <c r="N16" t="n">
-        <v>17.16738140147843</v>
+        <v>16.46890478610655</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>6.080655151698933</v>
+        <v>5.391545183840796</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2328,7 +2324,7 @@
         <v>46237</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7296091502078541</v>
+        <v>0.7191655958300509</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,22 +2352,22 @@
         <v>16.56354083790577</v>
       </c>
       <c r="K17" t="n">
-        <v>3.622406171107562</v>
+        <v>2.139165132671472</v>
       </c>
       <c r="L17" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M17" t="n">
-        <v>71.42857142857143</v>
+        <v>62.26415094339622</v>
       </c>
       <c r="N17" t="n">
-        <v>16.94507464850981</v>
+        <v>18.04154495657372</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>4.224562998145309</v>
+        <v>5.738087696052463</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2398,16 +2394,16 @@
         <v>15.7396793517258</v>
       </c>
       <c r="Y17" t="n">
-        <v>10.46942003683505</v>
+        <v>11.75095204620636</v>
       </c>
       <c r="Z17" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA17" t="n">
-        <v>40.90909090909091</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.774516751473181</v>
+        <v>9.196941783233198</v>
       </c>
       <c r="AC17" t="n">
         <v>10</v>
@@ -2447,7 +2443,7 @@
         <v>46237</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1020358787173026</v>
+        <v>0.101836207142278</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2472,25 +2468,25 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>26.36599129766135</v>
+        <v>27.32413099353592</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7660529883857015</v>
+        <v>1.894740000000006</v>
       </c>
       <c r="L18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M18" t="n">
-        <v>57.14285714285715</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N18" t="n">
-        <v>20.02563322973904</v>
+        <v>20.39831773620558</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>9.16374784738132</v>
+        <v>7.954542108846829</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2556,7 +2552,7 @@
         <v>46237</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02503560913387707</v>
+        <v>0.02482783380411211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,7 +2569,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>5</v>
       </c>
@@ -2584,22 +2584,22 @@
         <v>23.99412305210119</v>
       </c>
       <c r="K19" t="n">
-        <v>1.361884529002255</v>
+        <v>0.5206627767776251</v>
       </c>
       <c r="L19" t="n">
         <v>20</v>
       </c>
       <c r="M19" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="N19" t="n">
-        <v>23.79065269649551</v>
+        <v>20.99582487684433</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>8.522054923442312</v>
+        <v>9.430237486866533</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2665,7 +2665,7 @@
         <v>46237</v>
       </c>
       <c r="C20" t="n">
-        <v>1.872411008882688</v>
+        <v>1.839994985122424</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>20.34011802710127</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.482894106793657</v>
+        <v>7.119216867047995</v>
       </c>
       <c r="Z20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA20" t="n">
-        <v>42.10526315789474</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB20" t="n">
-        <v>12.18607979866391</v>
+        <v>12.96967327390692</v>
       </c>
       <c r="AC20" t="n">
         <v>4</v>
@@ -2774,7 +2774,7 @@
         <v>46237</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9500907964076463</v>
+        <v>0.9501906935415783</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>15.77844025931157</v>
       </c>
       <c r="K21" t="n">
-        <v>1.554105171621289</v>
+        <v>1.564783060602037</v>
       </c>
       <c r="L21" t="n">
         <v>50</v>
@@ -2817,7 +2817,7 @@
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>6.347251858982439</v>
+        <v>6.336071171006363</v>
       </c>
       <c r="Q21" t="n">
         <v>41</v>
@@ -2883,7 +2883,7 @@
         <v>46237</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7965110330165086</v>
+        <v>0.7928074788779208</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2915,22 +2915,22 @@
         <v>22.47437017331863</v>
       </c>
       <c r="K22" t="n">
-        <v>6.104154156489949</v>
+        <v>5.610799434510239</v>
       </c>
       <c r="L22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M22" t="n">
-        <v>83.33333333333333</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="N22" t="n">
-        <v>12.10085352258792</v>
+        <v>12.40298813286815</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>3.671718486878639</v>
+        <v>4.156014904717709</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -2988,7 +2988,7 @@
         <v>46237</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7157238582415516</v>
+        <v>0.71664075357138</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3013,25 +3013,25 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>24.64401357803806</v>
+        <v>24.63609028576259</v>
       </c>
       <c r="K23" t="n">
-        <v>2.779462333914706</v>
+        <v>2.900311010195633</v>
       </c>
       <c r="L23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M23" t="n">
-        <v>69.23076923076923</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N23" t="n">
-        <v>18.61926909781184</v>
+        <v>18.61486514700509</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.160487723579552</v>
+        <v>2.040507914107592</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3097,7 +3097,7 @@
         <v>46237</v>
       </c>
       <c r="C24" t="n">
-        <v>0.180298446805362</v>
+        <v>0.1758988906405579</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,10 +3122,10 @@
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>25.34703849055006</v>
+        <v>27.39484163531333</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1687537889661472</v>
+        <v>0.4807688881055761</v>
       </c>
       <c r="L24" t="n">
         <v>15</v>
@@ -3134,13 +3134,13 @@
         <v>73.33333333333333</v>
       </c>
       <c r="N24" t="n">
-        <v>15.69950398939818</v>
+        <v>16.83448322139268</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>9.814683560650227</v>
+        <v>9.473684583857999</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3206,7 +3206,7 @@
         <v>46237</v>
       </c>
       <c r="C25" t="n">
-        <v>3.967828401089686</v>
+        <v>3.9556211465713</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3234,22 +3234,22 @@
         <v>12.04001635695179</v>
       </c>
       <c r="K25" t="n">
-        <v>3.785522839286259</v>
+        <v>3.46622065064448</v>
       </c>
       <c r="L25" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="M25" t="n">
-        <v>54.90196078431372</v>
+        <v>50.90909090909091</v>
       </c>
       <c r="N25" t="n">
-        <v>18.10702151244897</v>
+        <v>18.38827790074306</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>4.060756303400748</v>
+        <v>4.381893260278558</v>
       </c>
       <c r="Q25" t="n">
         <v>44</v>
@@ -3315,7 +3315,7 @@
         <v>46237</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4363348752086788</v>
+        <v>0.4376431746936753</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>46237</v>
       </c>
       <c r="C27" t="n">
-        <v>34.986736042381</v>
+        <v>34.35919857633475</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3439,10 +3439,10 @@
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>59.27824529244716</v>
+        <v>59.57268759382546</v>
       </c>
       <c r="K27" t="n">
-        <v>1.650366748166254</v>
+        <v>0.5541871921182384</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3453,7 +3453,7 @@
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>6.246542393265186</v>
+        <v>7.404776484996933</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -3499,7 +3499,7 @@
         <v>46237</v>
       </c>
       <c r="C28" t="n">
-        <v>1.410619818611661</v>
+        <v>1.411820068525712</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>25.72214510232956</v>
       </c>
       <c r="K28" t="n">
-        <v>1.167146358681093</v>
+        <v>1.253226149365827</v>
       </c>
       <c r="L28" t="n">
         <v>19</v>
@@ -3542,7 +3542,7 @@
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>0.8232451653485295</v>
+        <v>0.7375309202815483</v>
       </c>
       <c r="Q28" t="n">
         <v>40</v>
@@ -3608,7 +3608,7 @@
         <v>46237</v>
       </c>
       <c r="C29" t="n">
-        <v>0.39909702861282</v>
+        <v>0.3985078011305299</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3633,10 +3633,10 @@
         <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>13.93563433155613</v>
+        <v>13.92658510858031</v>
       </c>
       <c r="K29" t="n">
-        <v>1.227318798414245</v>
+        <v>1.067239927719577</v>
       </c>
       <c r="L29" t="n">
         <v>14</v>
@@ -3651,7 +3651,7 @@
         <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>2.739064152343418</v>
+        <v>2.9017910001083</v>
       </c>
       <c r="Q29" t="n">
         <v>6</v>
@@ -3678,7 +3678,7 @@
         <v>55.05052857749912</v>
       </c>
       <c r="Y29" t="n">
-        <v>12.87935019297134</v>
+        <v>13.00797525770735</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3723,7 +3723,7 @@
         <v>46237</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3822663840583294</v>
+        <v>0.3835689983106866</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,22 +3751,22 @@
         <v>22.50856964296201</v>
       </c>
       <c r="K30" t="n">
-        <v>3.406543052052058</v>
+        <v>3.758912086798349</v>
       </c>
       <c r="L30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M30" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="N30" t="n">
-        <v>12.10566919354135</v>
+        <v>11.60016023263135</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>1.540963367420423</v>
+        <v>1.196126567097622</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3832,7 +3832,7 @@
         <v>46237</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1918695302814034</v>
+        <v>0.1874711905457825</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3857,25 +3857,25 @@
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>24.39894838979837</v>
+        <v>26.14803348293122</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4291494884735458</v>
+        <v>0.4509578409927162</v>
       </c>
       <c r="L31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M31" t="n">
         <v>50</v>
       </c>
       <c r="N31" t="n">
-        <v>12.57353257398547</v>
+        <v>14.664321271725</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>9.529952767970951</v>
+        <v>9.506173325019752</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3941,7 +3941,7 @@
         <v>46237</v>
       </c>
       <c r="C32" t="n">
-        <v>2.291073727327118</v>
+        <v>2.289210600061713</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>11.96252232646255</v>
       </c>
       <c r="K32" t="n">
-        <v>8.710636882267764</v>
+        <v>8.622232153428566</v>
       </c>
       <c r="L32" t="n">
         <v>30</v>
@@ -3978,7 +3978,7 @@
         <v>50</v>
       </c>
       <c r="N32" t="n">
-        <v>10.65025967437194</v>
+        <v>10.88144950943727</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4011,7 +4011,7 @@
         <v>12.36180984775317</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.249478599919897</v>
+        <v>3.328157226544881</v>
       </c>
       <c r="Z32" t="n">
         <v>46</v>
@@ -4020,13 +4020,13 @@
         <v>34.78260869565217</v>
       </c>
       <c r="AB32" t="n">
-        <v>11.99054819348334</v>
+        <v>11.98597638064313</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>4.91007317721408</v>
+        <v>4.832682029661218</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4060,7 +4060,7 @@
         <v>46237</v>
       </c>
       <c r="C33" t="n">
-        <v>1.828230556592072</v>
+        <v>1.828422785580565</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4088,22 +4088,22 @@
         <v>12.57251846431013</v>
       </c>
       <c r="K33" t="n">
-        <v>2.470219401321949</v>
+        <v>2.480993614976357</v>
       </c>
       <c r="L33" t="n">
         <v>54</v>
       </c>
       <c r="M33" t="n">
-        <v>61.11111111111111</v>
+        <v>59.25925925925926</v>
       </c>
       <c r="N33" t="n">
-        <v>11.05697725973216</v>
+        <v>11.20201978105696</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>1.492902628310677</v>
+        <v>1.482232296391062</v>
       </c>
       <c r="Q33" t="n">
         <v>39</v>
@@ -4169,7 +4169,7 @@
         <v>46237</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8634129160355463</v>
+        <v>0.8580331145282969</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4194,25 +4194,25 @@
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>10.18726434397186</v>
+        <v>10.30997185104549</v>
       </c>
       <c r="K34" t="n">
-        <v>0.6375727017615906</v>
+        <v>0.1473417441120617</v>
       </c>
       <c r="L34" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M34" t="n">
-        <v>46</v>
+        <v>48.97959183673469</v>
       </c>
       <c r="N34" t="n">
-        <v>13.98077476539812</v>
+        <v>13.7460313909748</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>3.341125196056671</v>
+        <v>3.846990033676501</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4239,16 +4239,16 @@
         <v>14.68007915548277</v>
       </c>
       <c r="Y34" t="n">
-        <v>9.614642858723721</v>
+        <v>10.17782099927622</v>
       </c>
       <c r="Z34" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA34" t="n">
-        <v>50</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="AB34" t="n">
-        <v>10.91246972399142</v>
+        <v>10.49224721614327</v>
       </c>
       <c r="AC34" t="n">
         <v>2</v>
@@ -4288,16 +4288,16 @@
         <v>46237</v>
       </c>
       <c r="C35" t="n">
-        <v>1.802984469105537</v>
+        <v>1.935729497258296</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4320,22 +4320,22 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>1.643701512389062</v>
+        <v>9.127235757976027</v>
       </c>
       <c r="L35" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="M35" t="n">
-        <v>77.77777777777777</v>
+        <v>100</v>
       </c>
       <c r="N35" t="n">
-        <v>16.49577743815318</v>
+        <v>12.38992893736071</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
       </c>
       <c r="P35" t="n">
-        <v>4.285851875514357</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>7</v>
@@ -4362,7 +4362,7 @@
         <v>42.52272358489104</v>
       </c>
       <c r="Y35" t="n">
-        <v>21.64206060969514</v>
+        <v>15.87294443116339</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -4407,7 +4407,7 @@
         <v>46237</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08247023937767434</v>
+        <v>0.08184769497725783</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4435,16 +4435,16 @@
         <v>21.75644461318207</v>
       </c>
       <c r="K36" t="n">
-        <v>3.07667729419705</v>
+        <v>2.298580749949442</v>
       </c>
       <c r="L36" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M36" t="n">
-        <v>43.75</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="N36" t="n">
-        <v>13.56470521880246</v>
+        <v>14.96518048865908</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4516,7 +4516,7 @@
         <v>46237</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0626942117294228</v>
+        <v>0.06291120887129999</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4544,22 +4544,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>2.055591596433581</v>
+        <v>2.408826306275524</v>
       </c>
       <c r="L37" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="M37" t="n">
-        <v>54.54545454545455</v>
+        <v>58.10810810810811</v>
       </c>
       <c r="N37" t="n">
-        <v>19.72675281368874</v>
+        <v>19.21787917365839</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>5.824676836006071</v>
+        <v>5.459659968177832</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4625,7 +4625,7 @@
         <v>46237</v>
       </c>
       <c r="C38" t="n">
-        <v>1.673598892892937</v>
+        <v>1.661150412006168</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.27: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %76.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -4657,22 +4657,22 @@
         <v>19.5673086238003</v>
       </c>
       <c r="K38" t="n">
-        <v>5.633829993665906</v>
+        <v>4.848109640206966</v>
       </c>
       <c r="L38" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="M38" t="n">
-        <v>77.27272727272727</v>
+        <v>76</v>
       </c>
       <c r="N38" t="n">
-        <v>12.11464618607974</v>
+        <v>12.75247762912281</v>
       </c>
       <c r="O38" t="n">
         <v>6</v>
       </c>
       <c r="P38" t="n">
-        <v>0.3466408501481499</v>
+        <v>1.098627685082576</v>
       </c>
       <c r="Q38" t="n">
         <v>35</v>
@@ -4738,7 +4738,7 @@
         <v>46237</v>
       </c>
       <c r="C39" t="n">
-        <v>2.686594158690625</v>
+        <v>2.686876640172928</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>19.12528796921053</v>
       </c>
       <c r="K39" t="n">
-        <v>6.347486452300766</v>
+        <v>6.358668340534646</v>
       </c>
       <c r="L39" t="n">
         <v>18</v>
@@ -4847,28 +4847,24 @@
         <v>46237</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1956564352625516</v>
+        <v>0.1986226700120861</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>5</v>
       </c>
@@ -4879,16 +4875,16 @@
         <v>14.73965458840789</v>
       </c>
       <c r="K40" t="n">
-        <v>6.855683131249091</v>
+        <v>8.475660721374556</v>
       </c>
       <c r="L40" t="n">
         <v>18</v>
       </c>
       <c r="M40" t="n">
-        <v>77.77777777777777</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N40" t="n">
-        <v>11.2474596513414</v>
+        <v>11.87432800207371</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4921,22 +4917,22 @@
         <v>14.17330472629232</v>
       </c>
       <c r="Y40" t="n">
-        <v>6.4092229024865</v>
+        <v>4.990346927923939</v>
       </c>
       <c r="Z40" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA40" t="n">
-        <v>34.78260869565217</v>
+        <v>56</v>
       </c>
       <c r="AB40" t="n">
-        <v>12.33129410895796</v>
+        <v>10.90744550176035</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>0.01016009612070379</v>
       </c>
       <c r="AE40" t="n">
         <v>13</v>
@@ -4970,7 +4966,7 @@
         <v>46237</v>
       </c>
       <c r="C41" t="n">
-        <v>1.592601209680515</v>
+        <v>1.644318077960891</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4987,7 +4983,11 @@
           <t>SATMA_BEKLE</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H41" t="n">
         <v>5</v>
       </c>
@@ -4998,22 +4998,22 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>5.24806597648213</v>
+        <v>8.665808178223822</v>
       </c>
       <c r="L41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M41" t="n">
-        <v>63.63636363636363</v>
+        <v>75</v>
       </c>
       <c r="N41" t="n">
-        <v>17.82717538896454</v>
+        <v>14.51550197500303</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>4.51498465024498</v>
+        <v>1.227793584885473</v>
       </c>
       <c r="Q41" t="n">
         <v>10</v>
@@ -5040,7 +5040,7 @@
         <v>40.81782021738603</v>
       </c>
       <c r="Y41" t="n">
-        <v>18.32621807032874</v>
+        <v>15.67400846735836</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -5085,7 +5085,7 @@
         <v>46237</v>
       </c>
       <c r="C42" t="n">
-        <v>3.166268054346567</v>
+        <v>3.149768476473825</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -5117,16 +5117,16 @@
         <v>22.36276267242437</v>
       </c>
       <c r="K42" t="n">
-        <v>3.01518172950368</v>
+        <v>2.478364573202785</v>
       </c>
       <c r="L42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M42" t="n">
-        <v>83.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="N42" t="n">
-        <v>12.3779784972871</v>
+        <v>13.14793523296843</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
@@ -5194,7 +5194,7 @@
         <v>46237</v>
       </c>
       <c r="C43" t="n">
-        <v>7.542239850387006</v>
+        <v>7.343147766773317</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5211,7 +5211,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %81.82: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H43" t="n">
         <v>5</v>
       </c>
@@ -5254,22 +5258,22 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.649847596712929</v>
+        <v>5.219594126463778</v>
       </c>
       <c r="Z43" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AA43" t="n">
-        <v>53.84615384615385</v>
+        <v>81.81818181818181</v>
       </c>
       <c r="AB43" t="n">
-        <v>10.08100185628649</v>
+        <v>11.13754853734093</v>
       </c>
       <c r="AC43" t="n">
         <v>6</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.441342741209674</v>
+        <v>0.8233831310846096</v>
       </c>
       <c r="AE43" t="n">
         <v>8</v>
@@ -5303,7 +5307,7 @@
         <v>46237</v>
       </c>
       <c r="C44" t="n">
-        <v>5.059717389171757</v>
+        <v>5.026584403120183</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5320,11 +5324,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.26: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>5</v>
       </c>
@@ -5335,22 +5335,22 @@
         <v>13.03201987649729</v>
       </c>
       <c r="K44" t="n">
-        <v>3.558985096128575</v>
+        <v>2.880840815570873</v>
       </c>
       <c r="L44" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M44" t="n">
-        <v>78.26086956521739</v>
+        <v>70.83333333333333</v>
       </c>
       <c r="N44" t="n">
-        <v>19.86668303814072</v>
+        <v>17.94687033846331</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>6.21965819565784</v>
+        <v>6.919810460327858</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5377,13 +5377,13 @@
         <v>12.1234692799834</v>
       </c>
       <c r="Y44" t="n">
-        <v>7.638440229198096</v>
+        <v>8.243259438693219</v>
       </c>
       <c r="Z44" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA44" t="n">
-        <v>11.11111111111111</v>
+        <v>14.28571428571429</v>
       </c>
       <c r="AB44" t="n">
         <v>9.691917834769438</v>
@@ -5392,7 +5392,7 @@
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.556864323926733</v>
+        <v>1.914562952607302</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5418,7 +5418,7 @@
         <v>46237</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02061755984441858</v>
+        <v>0.02040932250448295</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5443,25 +5443,25 @@
         <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>11.49212697867188</v>
+        <v>11.4828208335343</v>
       </c>
       <c r="K45" t="n">
-        <v>2.083337543402863</v>
+        <v>1.041671896701502</v>
       </c>
       <c r="L45" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="M45" t="n">
-        <v>56.16438356164384</v>
+        <v>59.30232558139535</v>
       </c>
       <c r="N45" t="n">
-        <v>16.28901498856858</v>
+        <v>14.86013625887492</v>
       </c>
       <c r="O45" t="n">
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>7.755097596834748</v>
+        <v>8.86597374641318</v>
       </c>
       <c r="Q45" t="n">
         <v>37</v>
@@ -5527,7 +5527,7 @@
         <v>46237</v>
       </c>
       <c r="C46" t="n">
-        <v>8.52578158819898</v>
+        <v>8.484596954015302</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5552,25 +5552,25 @@
         <v>10</v>
       </c>
       <c r="J46" t="n">
-        <v>25.37350183746037</v>
+        <v>25.36565524710288</v>
       </c>
       <c r="K46" t="n">
-        <v>3.248407643312112</v>
+        <v>2.738853503184724</v>
       </c>
       <c r="L46" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M46" t="n">
-        <v>56.25</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N46" t="n">
-        <v>17.39270412847368</v>
+        <v>16.4590755360719</v>
       </c>
       <c r="O46" t="n">
         <v>10</v>
       </c>
       <c r="P46" t="n">
-        <v>6.539173349784089</v>
+        <v>7.067575945443272</v>
       </c>
       <c r="Q46" t="n">
         <v>54</v>
@@ -5636,7 +5636,7 @@
         <v>46237</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7973525854094685</v>
+        <v>0.7869161539035476</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5653,7 +5653,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %78.95: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H47" t="n">
         <v>5</v>
       </c>
@@ -5664,22 +5668,22 @@
         <v>27.74248530779953</v>
       </c>
       <c r="K47" t="n">
-        <v>6.968507347676312</v>
+        <v>5.568412181933136</v>
       </c>
       <c r="L47" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M47" t="n">
-        <v>64.70588235294117</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="N47" t="n">
-        <v>12.77877075447891</v>
+        <v>12.87809202591376</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>2.834004818325209</v>
+        <v>4.197835059250132</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5745,7 +5749,7 @@
         <v>46237</v>
       </c>
       <c r="C48" t="n">
-        <v>0.06122153038613047</v>
+        <v>0.06164877785291165</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5762,11 +5766,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>5</v>
       </c>
@@ -5777,22 +5777,22 @@
         <v>35.39957983385757</v>
       </c>
       <c r="K48" t="n">
-        <v>4.318600282512652</v>
+        <v>5.046609814906811</v>
       </c>
       <c r="L48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M48" t="n">
-        <v>83.33333333333333</v>
+        <v>60</v>
       </c>
       <c r="N48" t="n">
-        <v>10.89490514088561</v>
+        <v>9.470969877799496</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>5.446200104392851</v>
+        <v>4.715421272348652</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5858,7 +5858,7 @@
         <v>46237</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2692905760613089</v>
+        <v>0.2674252389954578</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5886,16 +5886,16 @@
         <v>24.46536626635938</v>
       </c>
       <c r="K49" t="n">
-        <v>6.568623418750885</v>
+        <v>5.83043790098341</v>
       </c>
       <c r="L49" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M49" t="n">
-        <v>64.28571428571429</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N49" t="n">
-        <v>11.48773357364777</v>
+        <v>12.38347478478886</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
@@ -5967,7 +5967,7 @@
         <v>46237</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7279260454219343</v>
+        <v>0.7275818430171396</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>11.86078125763058</v>
       </c>
       <c r="K50" t="n">
-        <v>1.878337190511004</v>
+        <v>1.830163658490802</v>
       </c>
       <c r="L50" t="n">
         <v>63</v>
@@ -6010,7 +6010,7 @@
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>2.082545581325612</v>
+        <v>2.130838509487432</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6076,7 +6076,7 @@
         <v>46237</v>
       </c>
       <c r="C51" t="n">
-        <v>0.180719223001842</v>
+        <v>0.1815798453724928</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -6108,16 +6108,16 @@
         <v>27.30972539236674</v>
       </c>
       <c r="K51" t="n">
-        <v>4.745080963603465</v>
+        <v>5.243898734040586</v>
       </c>
       <c r="L51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M51" t="n">
-        <v>75</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N51" t="n">
-        <v>18.09582420420059</v>
+        <v>16.77127889385772</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
@@ -6150,7 +6150,7 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>17.95972797934672</v>
+        <v>17.56903521173489</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6195,7 +6195,7 @@
         <v>46237</v>
       </c>
       <c r="C52" t="n">
-        <v>4.110888760831124</v>
+        <v>4.121841268532068</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6255,22 +6255,22 @@
         <v>12.1710603868542</v>
       </c>
       <c r="Y52" t="n">
-        <v>5.675984735339834</v>
+        <v>5.424680318296627</v>
       </c>
       <c r="Z52" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA52" t="n">
-        <v>58.33333333333334</v>
+        <v>56</v>
       </c>
       <c r="AB52" t="n">
-        <v>13.67485347556112</v>
+        <v>13.70881130418631</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.463863797718213</v>
+        <v>2.723035661281081</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6304,7 +6304,7 @@
         <v>46237</v>
       </c>
       <c r="C53" t="n">
-        <v>1.550524557795511</v>
+        <v>1.538063296607775</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6329,25 +6329,25 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>28.82678537432798</v>
+        <v>28.81930187887606</v>
       </c>
       <c r="K53" t="n">
-        <v>2.219138022125944</v>
+        <v>1.386962581443174</v>
       </c>
       <c r="L53" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M53" t="n">
-        <v>50</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N53" t="n">
-        <v>18.3375126485811</v>
+        <v>13.05014890266504</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>5.655361696185279</v>
+        <v>6.522571788502529</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6405,7 +6405,7 @@
         <v>46237</v>
       </c>
       <c r="C54" t="n">
-        <v>0.09446207864301949</v>
+        <v>0.09047431745651388</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6433,10 +6433,10 @@
         <v>42.39442432818535</v>
       </c>
       <c r="K54" t="n">
-        <v>16.86513177251363</v>
+        <v>11.93161513564749</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -6471,7 +6471,7 @@
         <v>114.7400208810756</v>
       </c>
       <c r="Y54" t="n">
-        <v>32.67916808281876</v>
+        <v>35.52114874235025</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -6516,7 +6516,7 @@
         <v>46237</v>
       </c>
       <c r="C55" t="n">
-        <v>0.848686071676284</v>
+        <v>0.8576122940893759</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6541,25 +6541,25 @@
         <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>11.95011127641994</v>
+        <v>11.94085328596284</v>
       </c>
       <c r="K55" t="n">
-        <v>0.7492488089583249</v>
+        <v>1.798195263378144</v>
       </c>
       <c r="L55" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M55" t="n">
-        <v>66.66666666666667</v>
+        <v>62.0253164556962</v>
       </c>
       <c r="N55" t="n">
-        <v>15.12173145603583</v>
+        <v>15.15093636570434</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>5.211702571597532</v>
+        <v>4.127582739311553</v>
       </c>
       <c r="Q55" t="n">
         <v>44</v>
@@ -6586,16 +6586,16 @@
         <v>25.41488056506582</v>
       </c>
       <c r="Y55" t="n">
-        <v>11.29039853386937</v>
+        <v>10.35737788077981</v>
       </c>
       <c r="Z55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA55" t="n">
-        <v>50</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="AB55" t="n">
-        <v>9.686169325397467</v>
+        <v>8.985280448705707</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6635,7 +6635,7 @@
         <v>46237</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9686045457480569</v>
+        <v>0.9211547285693282</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6660,10 +6660,10 @@
         <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>30.29575178666554</v>
+        <v>30.29575178666553</v>
       </c>
       <c r="K56" t="n">
-        <v>10.56099944500437</v>
+        <v>10.57262436233963</v>
       </c>
       <c r="L56" t="n">
         <v>2</v>
@@ -6690,25 +6690,25 @@
         <v>100</v>
       </c>
       <c r="X56" t="n">
-        <v>17.75189696236841</v>
+        <v>21.48339906035102</v>
       </c>
       <c r="Y56" t="n">
-        <v>6.106820953943637</v>
+        <v>8.981288622481742</v>
       </c>
       <c r="Z56" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA56" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="AB56" t="n">
-        <v>10.81948936760917</v>
+        <v>17.32231848970716</v>
       </c>
       <c r="AC56" t="n">
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>4.146391767336666</v>
+        <v>1.119232916068158</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6734,7 +6734,7 @@
         <v>46237</v>
       </c>
       <c r="C57" t="n">
-        <v>1.448488708952631</v>
+        <v>1.398143686835204</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6751,7 +6751,11 @@
           <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %100.00: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>5</v>
       </c>
@@ -6762,7 +6766,7 @@
         <v>32.76213282665623</v>
       </c>
       <c r="K57" t="n">
-        <v>24.0300673955798</v>
+        <v>19.71916290066553</v>
       </c>
       <c r="L57" t="n">
         <v>1</v>
@@ -6800,16 +6804,16 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>10.69987058366207</v>
+        <v>13.80366902045174</v>
       </c>
       <c r="Z57" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AA57" t="n">
-        <v>71.42857142857143</v>
+        <v>100</v>
       </c>
       <c r="AB57" t="n">
-        <v>14.39928291782675</v>
+        <v>11.48120296715095</v>
       </c>
       <c r="AC57" t="n">
         <v>6</v>
@@ -6849,7 +6853,7 @@
         <v>46237</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7565381815371161</v>
+        <v>0.7528304244599112</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6868,7 +6872,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %89.19: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %91.89: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -6878,25 +6882,25 @@
         <v>10</v>
       </c>
       <c r="J58" t="n">
-        <v>16.33375063430099</v>
+        <v>16.32495356085277</v>
       </c>
       <c r="K58" t="n">
-        <v>1.985254660670122</v>
+        <v>1.474760308496803</v>
       </c>
       <c r="L58" t="n">
         <v>37</v>
       </c>
       <c r="M58" t="n">
-        <v>89.18918918918919</v>
+        <v>91.89189189189189</v>
       </c>
       <c r="N58" t="n">
-        <v>19.01585258090028</v>
+        <v>18.72122528472824</v>
       </c>
       <c r="O58" t="n">
         <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>2.956060020010409</v>
+        <v>3.474006423652543</v>
       </c>
       <c r="Q58" t="n">
         <v>24</v>
@@ -6923,7 +6927,7 @@
         <v>41.32985472592288</v>
       </c>
       <c r="Y58" t="n">
-        <v>14.67276251936057</v>
+        <v>15.09094718785197</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -6968,7 +6972,7 @@
         <v>46237</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8204947117575823</v>
+        <v>0.8104815339654904</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6996,22 +7000,22 @@
         <v>12.06710605756499</v>
       </c>
       <c r="K59" t="n">
-        <v>2.711081621465117</v>
+        <v>1.457613065536556</v>
       </c>
       <c r="L59" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M59" t="n">
-        <v>68.85245901639344</v>
+        <v>60.9375</v>
       </c>
       <c r="N59" t="n">
-        <v>13.5467393731803</v>
+        <v>14.3457197144375</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>5.149316213051724</v>
+        <v>6.448394296677762</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7038,16 +7042,16 @@
         <v>10.2478061424703</v>
       </c>
       <c r="Y59" t="n">
-        <v>6.836167344015598</v>
+        <v>7.97312289876716</v>
       </c>
       <c r="Z59" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AA59" t="n">
-        <v>50</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="AB59" t="n">
-        <v>15.44866820059028</v>
+        <v>13.8254719095032</v>
       </c>
       <c r="AC59" t="n">
         <v>6</v>
@@ -7087,7 +7091,7 @@
         <v>46237</v>
       </c>
       <c r="C60" t="n">
-        <v>12.9806471065238</v>
+        <v>12.85576872635672</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7115,22 +7119,22 @@
         <v>17.06238107085701</v>
       </c>
       <c r="K60" t="n">
-        <v>2.156276849323291</v>
+        <v>1.17349761866139</v>
       </c>
       <c r="L60" t="n">
         <v>43</v>
       </c>
       <c r="M60" t="n">
-        <v>51.16279069767442</v>
+        <v>55.81395348837209</v>
       </c>
       <c r="N60" t="n">
-        <v>12.73109490548113</v>
+        <v>13.84009050337867</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>5.720376007140504</v>
+        <v>6.747322710013215</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7196,7 +7200,7 @@
         <v>46237</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6378820360547829</v>
+        <v>0.6295328990524627</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7228,7 +7232,7 @@
         <v>39.02052765309554</v>
       </c>
       <c r="K61" t="n">
-        <v>2.992147038341697</v>
+        <v>1.644099127940324</v>
       </c>
       <c r="L61" t="n">
         <v>6</v>
@@ -7237,13 +7241,13 @@
         <v>83.33333333333333</v>
       </c>
       <c r="N61" t="n">
-        <v>33.49457775007936</v>
+        <v>25.04311802372403</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>6.804259512183441</v>
+        <v>8.220743696633125</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7301,7 +7305,7 @@
         <v>46237</v>
       </c>
       <c r="C62" t="n">
-        <v>8.483704936313975</v>
+        <v>8.447776012491365</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7329,22 +7333,22 @@
         <v>15.79076798430271</v>
       </c>
       <c r="K62" t="n">
-        <v>1.957341929200407</v>
+        <v>1.525547377311898</v>
       </c>
       <c r="L62" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M62" t="n">
-        <v>60.37735849056604</v>
+        <v>63.46153846153846</v>
       </c>
       <c r="N62" t="n">
-        <v>14.33317049238344</v>
+        <v>14.29118651923218</v>
       </c>
       <c r="O62" t="n">
         <v>6</v>
       </c>
       <c r="P62" t="n">
-        <v>3.965048513727276</v>
+        <v>4.407218417704417</v>
       </c>
       <c r="Q62" t="n">
         <v>29</v>
@@ -7410,7 +7414,7 @@
         <v>46237</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1028774111238529</v>
+        <v>0.1020466072622803</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7438,18 +7442,22 @@
         <v>33.30512547687425</v>
       </c>
       <c r="K63" t="n">
-        <v>3.09749562983237</v>
+        <v>2.264914438761978</v>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
-      </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M63" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="N63" t="n">
+        <v>10.8811033182065</v>
+      </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>1.845344892759093</v>
+        <v>2.674510193694868</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7515,7 +7523,7 @@
         <v>46237</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1653612446430489</v>
+        <v>0.163695390164921</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7540,25 +7548,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>21.49597893333038</v>
+        <v>21.89035128217772</v>
       </c>
       <c r="K64" t="n">
-        <v>0.7692299812623427</v>
+        <v>0.2577316933919604</v>
       </c>
       <c r="L64" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M64" t="n">
-        <v>60.97560975609756</v>
+        <v>62.5</v>
       </c>
       <c r="N64" t="n">
-        <v>15.08628706395872</v>
+        <v>15.58003045770035</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.198474097226268</v>
+        <v>4.730077398031352</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7624,7 +7632,7 @@
         <v>46237</v>
       </c>
       <c r="C65" t="n">
-        <v>6.295719038293756</v>
+        <v>6.185918176021075</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7643,7 +7651,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %82.35: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -7653,25 +7661,25 @@
         <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>28.12109136686307</v>
+        <v>28.1135336713357</v>
       </c>
       <c r="K65" t="n">
-        <v>3.72616984402081</v>
+        <v>1.906412478336228</v>
       </c>
       <c r="L65" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M65" t="n">
-        <v>78.57142857142857</v>
+        <v>82.35294117647059</v>
       </c>
       <c r="N65" t="n">
-        <v>13.19135185717638</v>
+        <v>15.35336073609163</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>6.048454469507103</v>
+        <v>7.942176870748296</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7737,7 +7745,7 @@
         <v>46237</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4296026174289592</v>
+        <v>0.4283853667931945</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7765,7 +7773,7 @@
         <v>11.2547528069613</v>
       </c>
       <c r="K66" t="n">
-        <v>2.961419114304431</v>
+        <v>2.669684735156141</v>
       </c>
       <c r="L66" t="n">
         <v>54</v>
@@ -7774,13 +7782,13 @@
         <v>53.7037037037037</v>
       </c>
       <c r="N66" t="n">
-        <v>18.17474417697341</v>
+        <v>17.63499988006323</v>
       </c>
       <c r="O66" t="n">
         <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>2.951183959811443</v>
+        <v>3.243718214811553</v>
       </c>
       <c r="Q66" t="n">
         <v>35</v>
@@ -7846,7 +7854,7 @@
         <v>46237</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02798097434506084</v>
+        <v>0.02714229319602197</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7871,10 +7879,10 @@
         <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>17.88062675770013</v>
+        <v>19.80495045311466</v>
       </c>
       <c r="K67" t="n">
-        <v>1.460726362679332</v>
+        <v>0.7812492370605328</v>
       </c>
       <c r="L67" t="n">
         <v>5</v>
@@ -7883,13 +7891,13 @@
         <v>60</v>
       </c>
       <c r="N67" t="n">
-        <v>11.54719770132041</v>
+        <v>13.17502365156353</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>2.502715807734157</v>
+        <v>3.193799230815486</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7935,7 +7943,7 @@
         <v>46237</v>
       </c>
       <c r="C68" t="n">
-        <v>3.263044482015865</v>
+        <v>3.372798307766084</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7992,10 +8000,10 @@
         <v>80</v>
       </c>
       <c r="X68" t="n">
-        <v>84.86382491664126</v>
+        <v>88.17007952573587</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.523805650793641</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
         <v>1</v>
@@ -8006,7 +8014,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>6.576405995383139</v>
+        <v>7.999999999999996</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8040,7 +8048,7 @@
         <v>46237</v>
       </c>
       <c r="C69" t="n">
-        <v>0.39909702861282</v>
+        <v>0.3953517286342882</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8059,7 +8067,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %90.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H69" t="n">
@@ -8072,22 +8080,22 @@
         <v>29.4573350207784</v>
       </c>
       <c r="K69" t="n">
-        <v>2.087603163325857</v>
+        <v>1.129568724269925</v>
       </c>
       <c r="L69" t="n">
         <v>10</v>
       </c>
       <c r="M69" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N69" t="n">
-        <v>16.53833303572285</v>
+        <v>16.18279183771334</v>
       </c>
       <c r="O69" t="n">
         <v>3</v>
       </c>
       <c r="P69" t="n">
-        <v>0.8937391107267434</v>
+        <v>1.849539456486582</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8137,7 +8145,7 @@
         <v>46237</v>
       </c>
       <c r="C70" t="n">
-        <v>0.3967828401089686</v>
+        <v>0.3959829188948367</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8162,25 +8170,25 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>20.66685340467635</v>
+        <v>20.65851193457618</v>
       </c>
       <c r="K70" t="n">
-        <v>1.780895346528988</v>
+        <v>1.565024226666645</v>
       </c>
       <c r="L70" t="n">
         <v>31</v>
       </c>
       <c r="M70" t="n">
-        <v>58.06451612903226</v>
+        <v>64.51612903225806</v>
       </c>
       <c r="N70" t="n">
-        <v>13.60436768229634</v>
+        <v>13.66554107566214</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>6.110286839487022</v>
+        <v>6.335818676094807</v>
       </c>
       <c r="Q70" t="n">
         <v>30</v>
@@ -8246,7 +8254,7 @@
         <v>46237</v>
       </c>
       <c r="C71" t="n">
-        <v>3.284082807958367</v>
+        <v>3.286531973562727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8274,22 +8282,22 @@
         <v>21.33797260620418</v>
       </c>
       <c r="K71" t="n">
-        <v>4.829273725313166</v>
+        <v>4.907452098561182</v>
       </c>
       <c r="L71" t="n">
         <v>30</v>
       </c>
       <c r="M71" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="N71" t="n">
-        <v>11.59837148247931</v>
+        <v>11.55469196476905</v>
       </c>
       <c r="O71" t="n">
         <v>6</v>
       </c>
       <c r="P71" t="n">
-        <v>1.116793270698913</v>
+        <v>1.041439744826111</v>
       </c>
       <c r="Q71" t="n">
         <v>43</v>
@@ -8355,7 +8363,7 @@
         <v>46237</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0723718425045068</v>
+        <v>0.07511471923598968</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8383,17 +8391,13 @@
         <v>29.15235727667785</v>
       </c>
       <c r="K72" t="n">
-        <v>11.12753810584826</v>
+        <v>15.33924707924528</v>
       </c>
       <c r="L72" t="n">
-        <v>8</v>
-      </c>
-      <c r="M72" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="N72" t="n">
-        <v>20.36965270753011</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
         <v>5</v>
       </c>
@@ -8425,7 +8429,7 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>19.42578972647294</v>
+        <v>16.37204508119735</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -8470,7 +8474,7 @@
         <v>46237</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07047838980354947</v>
+        <v>0.07090661079163273</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8495,25 +8499,25 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>20.52993807340809</v>
+        <v>20.57324828822117</v>
       </c>
       <c r="K73" t="n">
-        <v>0.2341998479137963</v>
+        <v>0.898203018215038</v>
       </c>
       <c r="L73" t="n">
         <v>26</v>
       </c>
       <c r="M73" t="n">
-        <v>69.23076923076923</v>
+        <v>73.07692307692308</v>
       </c>
       <c r="N73" t="n">
-        <v>15.48311115261322</v>
+        <v>14.93643632280392</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>9.742982102819141</v>
+        <v>9.020772134209199</v>
       </c>
       <c r="Q73" t="n">
         <v>12</v>
@@ -8579,7 +8583,7 @@
         <v>46237</v>
       </c>
       <c r="C74" t="n">
-        <v>4.981875647351393</v>
+        <v>4.927693938629543</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8607,22 +8611,22 @@
         <v>17.41018086324394</v>
       </c>
       <c r="K74" t="n">
-        <v>4.190239730394918</v>
+        <v>3.057091169424031</v>
       </c>
       <c r="L74" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M74" t="n">
-        <v>62.5</v>
+        <v>62.7906976744186</v>
       </c>
       <c r="N74" t="n">
-        <v>19.22643583577678</v>
+        <v>20.67372893071872</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>3.656542378118433</v>
+        <v>4.796282113619843</v>
       </c>
       <c r="Q74" t="n">
         <v>35</v>
@@ -8649,10 +8653,10 @@
         <v>95.98093909010421</v>
       </c>
       <c r="Y74" t="n">
-        <v>13.9494694485143</v>
+        <v>14.88533479557089</v>
       </c>
       <c r="Z74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="inlineStr"/>
       <c r="AB74" t="inlineStr"/>
@@ -8694,16 +8698,16 @@
         <v>46237</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1375906508224307</v>
+        <v>0.1407612005739323</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8711,11 +8715,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>5</v>
       </c>
@@ -8726,22 +8726,18 @@
         <v>19.1703426786477</v>
       </c>
       <c r="K75" t="n">
-        <v>5.585597354593652</v>
+        <v>8.018643404261528</v>
       </c>
       <c r="L75" t="n">
-        <v>3</v>
-      </c>
-      <c r="M75" t="n">
-        <v>100</v>
-      </c>
-      <c r="N75" t="n">
-        <v>7.445930190134614</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>0.3924802774138314</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8807,7 +8803,7 @@
         <v>46237</v>
       </c>
       <c r="C76" t="n">
-        <v>1.809296031055181</v>
+        <v>1.818954447108747</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8835,22 +8831,22 @@
         <v>21.37762355327298</v>
       </c>
       <c r="K76" t="n">
-        <v>4.392390387349332</v>
+        <v>4.94965969092438</v>
       </c>
       <c r="L76" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M76" t="n">
-        <v>60</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N76" t="n">
-        <v>11.01737898992127</v>
+        <v>11.96395971167433</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>5.371665110688206</v>
+        <v>4.812155012173291</v>
       </c>
       <c r="Q76" t="n">
         <v>42</v>
@@ -8916,7 +8912,7 @@
         <v>46237</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5015536936249991</v>
+        <v>0.5066561536861022</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8944,16 +8940,16 @@
         <v>22.11886481778794</v>
       </c>
       <c r="K77" t="n">
-        <v>3.298010645583349</v>
+        <v>4.348893094281991</v>
       </c>
       <c r="L77" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="M77" t="n">
         <v>66.66666666666667</v>
       </c>
       <c r="N77" t="n">
-        <v>19.15179104564679</v>
+        <v>15.56210585085078</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -9025,7 +9021,7 @@
         <v>46237</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05343734705242231</v>
+        <v>0.05344296571311838</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9057,7 +9053,7 @@
         <v>20.92476038411055</v>
       </c>
       <c r="K78" t="n">
-        <v>13.32610125980493</v>
+        <v>13.33801691329652</v>
       </c>
       <c r="L78" t="n">
         <v>12</v>
@@ -9099,7 +9095,7 @@
         <v>23.16536029857119</v>
       </c>
       <c r="Y78" t="n">
-        <v>7.988657699627899</v>
+        <v>7.978983182813504</v>
       </c>
       <c r="Z78" t="n">
         <v>18</v>
@@ -9114,7 +9110,7 @@
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>2.18597213135534</v>
+        <v>2.196255689286231</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9148,7 +9144,7 @@
         <v>46237</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8848720179641453</v>
+        <v>0.8845442374522813</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9176,7 +9172,7 @@
         <v>14.97695523729659</v>
       </c>
       <c r="K79" t="n">
-        <v>2.468696230905243</v>
+        <v>2.430739056287079</v>
       </c>
       <c r="L79" t="n">
         <v>49</v>
@@ -9191,7 +9187,7 @@
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>2.47031909471227</v>
+        <v>2.508290936279467</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9257,7 +9253,7 @@
         <v>46237</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1373802728225872</v>
+        <v>0.1346594453915874</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9282,10 +9278,10 @@
         <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>68.8841896784632</v>
+        <v>68.88091801192056</v>
       </c>
       <c r="K80" t="n">
-        <v>3.980891586626245</v>
+        <v>1.910826209988303</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9296,7 +9292,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>5.78866782302907</v>
+        <v>7.937501922851542</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9362,11 +9358,11 @@
         <v>46237</v>
       </c>
       <c r="C81" t="n">
-        <v>1.077162304245236</v>
+        <v>1.054130922293201</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9376,7 +9372,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -9387,25 +9383,25 @@
         <v>10</v>
       </c>
       <c r="J81" t="n">
-        <v>11.07045147382514</v>
+        <v>11.75504511642799</v>
       </c>
       <c r="K81" t="n">
-        <v>1.723097895026959</v>
+        <v>0.3203841497582349</v>
       </c>
       <c r="L81" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M81" t="n">
-        <v>52</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N81" t="n">
-        <v>11.72548731552414</v>
+        <v>10.94116300280899</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>8.136698818899912</v>
+        <v>9.648702935379561</v>
       </c>
       <c r="Q81" t="n">
         <v>31</v>
@@ -9432,22 +9428,22 @@
         <v>27.31228182970742</v>
       </c>
       <c r="Y81" t="n">
-        <v>9.538108295113634</v>
+        <v>11.47232226801971</v>
       </c>
       <c r="Z81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA81" t="n">
-        <v>55.55555555555556</v>
+        <v>50</v>
       </c>
       <c r="AB81" t="n">
-        <v>9.438232199299446</v>
+        <v>9.529724010146259</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.5105925779146814</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9481,7 +9477,7 @@
         <v>46237</v>
       </c>
       <c r="C82" t="n">
-        <v>5.053405827222113</v>
+        <v>5.135995457485868</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9509,17 +9505,13 @@
         <v>17.26584051182517</v>
       </c>
       <c r="K82" t="n">
-        <v>11.1575352580759</v>
+        <v>12.97422286478676</v>
       </c>
       <c r="L82" t="n">
-        <v>3</v>
-      </c>
-      <c r="M82" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="N82" t="n">
-        <v>6.884527306048893</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="O82" t="n">
         <v>4</v>
       </c>
@@ -9551,22 +9543,22 @@
         <v>15.04024401260009</v>
       </c>
       <c r="Y82" t="n">
-        <v>3.375087377334585</v>
+        <v>1.795911652957749</v>
       </c>
       <c r="Z82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA82" t="n">
-        <v>36.36363636363637</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB82" t="n">
-        <v>9.943255098757476</v>
+        <v>9.536932908011476</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.6467406859199887</v>
+        <v>2.24439571115741</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9600,7 +9592,7 @@
         <v>46237</v>
       </c>
       <c r="C83" t="n">
-        <v>5.885471682414964</v>
+        <v>5.85452970230566</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9628,22 +9620,22 @@
         <v>15.63345941387357</v>
       </c>
       <c r="K83" t="n">
-        <v>8.742699627371287</v>
+        <v>8.171001277525258</v>
       </c>
       <c r="L83" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M83" t="n">
-        <v>58.62068965517241</v>
+        <v>61.29032258064516</v>
       </c>
       <c r="N83" t="n">
-        <v>11.02630084398797</v>
+        <v>10.87572382585771</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>1.156215890296197</v>
+        <v>1.690840152049855</v>
       </c>
       <c r="Q83" t="n">
         <v>44</v>
@@ -9709,16 +9701,16 @@
         <v>46237</v>
       </c>
       <c r="C84" t="n">
-        <v>2.162739971056111</v>
+        <v>2.200840244038604</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -9737,22 +9729,22 @@
         <v>15.40292259784146</v>
       </c>
       <c r="K84" t="n">
-        <v>3.535880778519429</v>
+        <v>5.359838061381406</v>
       </c>
       <c r="L84" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="M84" t="n">
-        <v>61.90476190476191</v>
+        <v>69.6969696969697</v>
       </c>
       <c r="N84" t="n">
-        <v>12.81407370694672</v>
+        <v>10.76769305697522</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>1.414117705351425</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9818,7 +9810,7 @@
         <v>46237</v>
       </c>
       <c r="C85" t="n">
-        <v>6.711225975658173</v>
+        <v>6.711931626363003</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9846,13 +9838,13 @@
         <v>15.13449360257271</v>
       </c>
       <c r="K85" t="n">
-        <v>4.147428301424538</v>
+        <v>4.158378864921253</v>
       </c>
       <c r="L85" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M85" t="n">
-        <v>54.76190476190476</v>
+        <v>56.09756097560975</v>
       </c>
       <c r="N85" t="n">
         <v>13.1498215264233</v>
@@ -9861,7 +9853,7 @@
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>3.699152020753993</v>
+        <v>3.688249737508675</v>
       </c>
       <c r="Q85" t="n">
         <v>34</v>
@@ -9927,7 +9919,7 @@
         <v>46237</v>
       </c>
       <c r="C86" t="n">
-        <v>3.332470700958546</v>
+        <v>3.572683418896017</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9984,25 +9976,25 @@
         <v>68.35443037974683</v>
       </c>
       <c r="X86" t="n">
-        <v>30.48168037312833</v>
+        <v>39.96949805432428</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>0.05885276844616039</v>
       </c>
       <c r="Z86" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AA86" t="n">
-        <v>35</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB86" t="n">
-        <v>10.79079935884037</v>
+        <v>12.3031665129609</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>6.000000000000005</v>
+        <v>5.944645820193351</v>
       </c>
       <c r="AE86" t="n">
         <v>51</v>
@@ -10036,7 +10028,7 @@
         <v>46237</v>
       </c>
       <c r="C87" t="n">
-        <v>5.769760889731203</v>
+        <v>5.754587146740694</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10068,7 +10060,7 @@
         <v>29.54558799520699</v>
       </c>
       <c r="K87" t="n">
-        <v>6.229348786736488</v>
+        <v>5.949979005675399</v>
       </c>
       <c r="L87" t="n">
         <v>6</v>
@@ -10149,7 +10141,7 @@
         <v>46237</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9442000908105034</v>
+        <v>0.9447201890061261</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10177,22 +10169,22 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>5.780246617326124</v>
+        <v>5.838514050186649</v>
       </c>
       <c r="L88" t="n">
         <v>27</v>
       </c>
       <c r="M88" t="n">
-        <v>74.07407407407408</v>
+        <v>70.37037037037037</v>
       </c>
       <c r="N88" t="n">
-        <v>11.4800387843004</v>
+        <v>11.83803676381896</v>
       </c>
       <c r="O88" t="n">
         <v>10</v>
       </c>
       <c r="P88" t="n">
-        <v>3.989169544990179</v>
+        <v>3.931920234481057</v>
       </c>
       <c r="Q88" t="n">
         <v>44</v>
@@ -10258,7 +10250,7 @@
         <v>46237</v>
       </c>
       <c r="C89" t="n">
-        <v>1.917643441847706</v>
+        <v>1.918897002673713</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10286,7 +10278,7 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>4.163237674541942</v>
+        <v>4.231329036788645</v>
       </c>
       <c r="L89" t="n">
         <v>44</v>
@@ -10295,7 +10287,7 @@
         <v>63.63636363636363</v>
       </c>
       <c r="N89" t="n">
-        <v>13.76877936814122</v>
+        <v>13.75903325537547</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
@@ -10328,7 +10320,7 @@
         <v>28.7873334490923</v>
       </c>
       <c r="Y89" t="n">
-        <v>16.37165935631426</v>
+        <v>16.31699162743037</v>
       </c>
       <c r="Z89" t="n">
         <v>2</v>
@@ -10373,7 +10365,7 @@
         <v>46237</v>
       </c>
       <c r="C90" t="n">
-        <v>2.596129453493399</v>
+        <v>2.609026713695964</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10401,22 +10393,22 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>2.340069374448173</v>
+        <v>2.848482582462397</v>
       </c>
       <c r="L90" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M90" t="n">
-        <v>63.49206349206349</v>
+        <v>64.91228070175438</v>
       </c>
       <c r="N90" t="n">
-        <v>14.87933638741587</v>
+        <v>14.67949900638165</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>5.530512789514463</v>
+        <v>5.008841441493517</v>
       </c>
       <c r="Q90" t="n">
         <v>42</v>
@@ -10443,7 +10435,7 @@
         <v>33.24184775233741</v>
       </c>
       <c r="Y90" t="n">
-        <v>14.63478724698701</v>
+        <v>14.21070309369433</v>
       </c>
       <c r="Z90" t="n">
         <v>2</v>
@@ -10488,7 +10480,7 @@
         <v>46237</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2349981024608146</v>
+        <v>0.2341811904066856</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10516,16 +10508,16 @@
         <v>15.33687628212038</v>
       </c>
       <c r="K91" t="n">
-        <v>3.646595962003873</v>
+        <v>3.28629452669793</v>
       </c>
       <c r="L91" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M91" t="n">
-        <v>55.55555555555556</v>
+        <v>57.4468085106383</v>
       </c>
       <c r="N91" t="n">
-        <v>13.56657022385137</v>
+        <v>15.19244190628366</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
@@ -10597,7 +10589,7 @@
         <v>46237</v>
       </c>
       <c r="C92" t="n">
-        <v>1.103460211673363</v>
+        <v>1.111992401830813</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10625,22 +10617,22 @@
         <v>23.70319776773422</v>
       </c>
       <c r="K92" t="n">
-        <v>4.727084283061633</v>
+        <v>5.536856478094632</v>
       </c>
       <c r="L92" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M92" t="n">
-        <v>56.25</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N92" t="n">
-        <v>16.16576288577387</v>
+        <v>13.96884097780217</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>3.125185561446719</v>
+        <v>2.333917840746591</v>
       </c>
       <c r="Q92" t="n">
         <v>56</v>
@@ -10706,7 +10698,7 @@
         <v>46237</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04186626883596245</v>
+        <v>0.04144986051816008</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10731,25 +10723,25 @@
         <v>10</v>
       </c>
       <c r="J93" t="n">
-        <v>20.11491625845134</v>
+        <v>20.51206701965846</v>
       </c>
       <c r="K93" t="n">
-        <v>1.015227395707186</v>
+        <v>0.5102035610162536</v>
       </c>
       <c r="L93" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M93" t="n">
-        <v>62.22222222222222</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N93" t="n">
-        <v>14.33054855153099</v>
+        <v>13.31844194410766</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>4.934674437514208</v>
+        <v>5.461929480275196</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10815,7 +10807,7 @@
         <v>46237</v>
       </c>
       <c r="C94" t="n">
-        <v>6.164229501153118</v>
+        <v>6.117536427476624</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10843,22 +10835,22 @@
         <v>11.31569733043036</v>
       </c>
       <c r="K94" t="n">
-        <v>2.470527091664887</v>
+        <v>1.694328887126084</v>
       </c>
       <c r="L94" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="M94" t="n">
-        <v>31.25</v>
+        <v>40.74074074074074</v>
       </c>
       <c r="N94" t="n">
-        <v>11.62002772702134</v>
+        <v>12.70505029324409</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>5.396159330173766</v>
+        <v>6.200612346704992</v>
       </c>
       <c r="Q94" t="n">
         <v>40</v>
@@ -10885,7 +10877,7 @@
         <v>46.65531127586331</v>
       </c>
       <c r="Y94" t="n">
-        <v>9.124727606924555</v>
+        <v>9.813093571953523</v>
       </c>
       <c r="Z94" t="n">
         <v>2</v>
@@ -10930,7 +10922,7 @@
         <v>46237</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1411671679157222</v>
+        <v>0.1390779590056758</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10955,25 +10947,25 @@
         <v>10</v>
       </c>
       <c r="J95" t="n">
-        <v>23.34731360730358</v>
+        <v>23.38908838680146</v>
       </c>
       <c r="K95" t="n">
-        <v>1.754748952778318</v>
+        <v>0.3034898261724761</v>
       </c>
       <c r="L95" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M95" t="n">
-        <v>65.38461538461539</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="N95" t="n">
-        <v>19.65396541550904</v>
+        <v>20.35553191478007</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>4.172042180745583</v>
+        <v>5.67927415456797</v>
       </c>
       <c r="Q95" t="n">
         <v>22</v>
@@ -11039,7 +11031,7 @@
         <v>46237</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1308583829443147</v>
+        <v>0.1327657936038704</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11064,25 +11056,25 @@
         <v>10</v>
       </c>
       <c r="J96" t="n">
-        <v>12.79292615761875</v>
+        <v>12.78375678478788</v>
       </c>
       <c r="K96" t="n">
-        <v>1.138206322956004</v>
+        <v>2.601623372331341</v>
       </c>
       <c r="L96" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M96" t="n">
-        <v>56.52173913043478</v>
+        <v>57.35294117647059</v>
       </c>
       <c r="N96" t="n">
-        <v>12.43485955793264</v>
+        <v>13.98386424925724</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>8.762063318333336</v>
+        <v>7.210779307867954</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11109,16 +11101,16 @@
         <v>16.74415231729489</v>
       </c>
       <c r="Y96" t="n">
-        <v>11.80032972907986</v>
+        <v>10.51471861683158</v>
       </c>
       <c r="Z96" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AA96" t="n">
-        <v>40</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="AB96" t="n">
-        <v>16.42948776937994</v>
+        <v>19.477453049894</v>
       </c>
       <c r="AC96" t="n">
         <v>8</v>
@@ -11158,7 +11150,7 @@
         <v>46237</v>
       </c>
       <c r="C97" t="n">
-        <v>1.84611310145456</v>
+        <v>1.852619436277912</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11186,22 +11178,22 @@
         <v>24.72840729454471</v>
       </c>
       <c r="K97" t="n">
-        <v>3.28969997484112</v>
+        <v>3.653728252041666</v>
       </c>
       <c r="L97" t="n">
         <v>21</v>
       </c>
       <c r="M97" t="n">
-        <v>47.61904761904762</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N97" t="n">
-        <v>13.47471292030109</v>
+        <v>11.91267637188544</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>0.6876774986585232</v>
+        <v>0.3340658882200032</v>
       </c>
       <c r="Q97" t="n">
         <v>51</v>
@@ -11267,7 +11259,7 @@
         <v>46237</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6383028122512628</v>
+        <v>0.6396323476203802</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11286,7 +11278,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H98" t="n">
@@ -11299,22 +11291,22 @@
         <v>21.12557680400878</v>
       </c>
       <c r="K98" t="n">
-        <v>6.31233068181063</v>
+        <v>6.533771040683956</v>
       </c>
       <c r="L98" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M98" t="n">
-        <v>76.47058823529412</v>
+        <v>75</v>
       </c>
       <c r="N98" t="n">
-        <v>16.92060910488019</v>
+        <v>15.92523016905886</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>3.468712702034971</v>
+        <v>3.253643352202684</v>
       </c>
       <c r="Q98" t="n">
         <v>48</v>
@@ -11380,7 +11372,7 @@
         <v>46237</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4826192082713111</v>
+        <v>0.4776202289012797</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11408,22 +11400,22 @@
         <v>28.77817890954801</v>
       </c>
       <c r="K99" t="n">
-        <v>3.827391929413859</v>
+        <v>2.75194573621651</v>
       </c>
       <c r="L99" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M99" t="n">
-        <v>66.66666666666667</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="N99" t="n">
-        <v>12.82986200275538</v>
+        <v>12.20882658747631</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>0.1662452146573123</v>
+        <v>1.214628350676183</v>
       </c>
       <c r="Q99" t="n">
         <v>35</v>
@@ -11489,7 +11481,7 @@
         <v>46237</v>
       </c>
       <c r="C100" t="n">
-        <v>326.7237226297649</v>
+        <v>325.3443736970872</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11521,7 +11513,7 @@
         <v>25.87300653788257</v>
       </c>
       <c r="K100" t="n">
-        <v>6.603250574291852</v>
+        <v>6.153197303852553</v>
       </c>
       <c r="L100" t="n">
         <v>13</v>
@@ -11530,7 +11522,7 @@
         <v>76.92307692307692</v>
       </c>
       <c r="N100" t="n">
-        <v>12.40411229835558</v>
+        <v>12.27301201847957</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11602,7 +11594,7 @@
         <v>46237</v>
       </c>
       <c r="C101" t="n">
-        <v>321.4056693904869</v>
+        <v>320.1555592203123</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11630,7 +11622,7 @@
         <v>14.83975271775182</v>
       </c>
       <c r="K101" t="n">
-        <v>1.779226007521717</v>
+        <v>1.383354815249982</v>
       </c>
       <c r="L101" t="n">
         <v>34</v>
@@ -11639,13 +11631,13 @@
         <v>58.8235294117647</v>
       </c>
       <c r="N101" t="n">
-        <v>11.35964129654057</v>
+        <v>11.41220571101113</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
       </c>
       <c r="P101" t="n">
-        <v>0.2169145916495419</v>
+        <v>0.6082311893049086</v>
       </c>
       <c r="Q101" t="n">
         <v>29</v>
@@ -11711,7 +11703,7 @@
         <v>46237</v>
       </c>
       <c r="C102" t="n">
-        <v>386.4782387927601</v>
+        <v>384.8747952851122</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11810,7 +11802,7 @@
         <v>46237</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7178276586471632</v>
+        <v>0.7153782924650223</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11838,7 +11830,7 @@
         <v>31.6668549372698</v>
       </c>
       <c r="K103" t="n">
-        <v>10.40070407464377</v>
+        <v>10.02399561574348</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
@@ -11877,25 +11869,25 @@
         <v>68.18181818181819</v>
       </c>
       <c r="X103" t="n">
-        <v>10.9184091346022</v>
+        <v>10.930071631718</v>
       </c>
       <c r="Y103" t="n">
-        <v>0.4667440364477082</v>
+        <v>0.8167992706095473</v>
       </c>
       <c r="Z103" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA103" t="n">
-        <v>35.84905660377358</v>
+        <v>35.18518518518518</v>
       </c>
       <c r="AB103" t="n">
-        <v>11.64874872800553</v>
+        <v>11.50048915914395</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>7.56858186806515</v>
+        <v>7.242356242352932</v>
       </c>
       <c r="AE103" t="n">
         <v>34</v>
@@ -11929,7 +11921,7 @@
         <v>46237</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0492296808120056</v>
+        <v>0.04860364154916188</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11948,7 +11940,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.19: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -11961,22 +11953,22 @@
         <v>27.65580276361549</v>
       </c>
       <c r="K104" t="n">
-        <v>1.672991759460962</v>
+        <v>0.3800464516236834</v>
       </c>
       <c r="L104" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M104" t="n">
-        <v>76.19047619047619</v>
+        <v>75</v>
       </c>
       <c r="N104" t="n">
-        <v>15.96576789787374</v>
+        <v>14.95533509217345</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>2.288718174089244</v>
+        <v>3.606248130320289</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>

--- a/TDA_Result.xlsx
+++ b/TDA_Result.xlsx
@@ -453,7 +453,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4607877745041246</v>
+        <v>0.4613459941311895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,37 +715,37 @@
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R2" t="n">
-        <v>58.8235294117647</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="S2" t="n">
-        <v>49.81660369379443</v>
+        <v>49.5316690073753</v>
       </c>
       <c r="T2" t="n">
-        <v>9.006925717970276</v>
+        <v>8.160638684932394</v>
       </c>
       <c r="U2" t="n">
-        <v>45.16533720637157</v>
+        <v>44.19432537390302</v>
       </c>
       <c r="V2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W2" t="n">
-        <v>65.51724137931035</v>
+        <v>64.40677966101696</v>
       </c>
       <c r="X2" t="n">
         <v>14.94856954517825</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.255676956712206</v>
+        <v>3.138476408177704</v>
       </c>
       <c r="Z2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AA2" t="n">
-        <v>40</v>
+        <v>39.02439024390244</v>
       </c>
       <c r="AB2" t="n">
         <v>13.55541461777871</v>
@@ -754,7 +754,7 @@
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.903980816698638</v>
+        <v>5.019045139439382</v>
       </c>
       <c r="AE2" t="n">
         <v>43</v>
@@ -763,10 +763,10 @@
         <v>53.48837209302326</v>
       </c>
       <c r="AG2" t="n">
-        <v>35.2995697192395</v>
+        <v>35.37001391759068</v>
       </c>
       <c r="AH2" t="n">
-        <v>18.18880237378376</v>
+        <v>18.11835817543258</v>
       </c>
       <c r="AI2" t="n">
         <v>38.91564047231397</v>
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C3" t="n">
-        <v>0.739364492965886</v>
+        <v>0.7435366563275064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,22 +848,22 @@
         <v>12.13279917920569</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.820164933076241</v>
+        <v>2.271788386444806</v>
       </c>
       <c r="Z3" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="AA3" t="n">
-        <v>44.82758620689656</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.79236473985161</v>
+        <v>10.3002809707242</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>7.388194332681564</v>
+        <v>7.907861492559299</v>
       </c>
       <c r="AE3" t="n">
         <v>38</v>
@@ -872,10 +872,10 @@
         <v>60.52631578947368</v>
       </c>
       <c r="AG3" t="n">
-        <v>31.40864168599064</v>
+        <v>31.67720124076367</v>
       </c>
       <c r="AH3" t="n">
-        <v>29.11767410348304</v>
+        <v>28.84911454871001</v>
       </c>
       <c r="AI3" t="n">
         <v>44.71786799604255</v>
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C4" t="n">
-        <v>1.38867550890269</v>
+        <v>1.386771475426517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>27.63389482946404</v>
       </c>
       <c r="K4" t="n">
-        <v>7.520835288952377</v>
+        <v>7.373411885526737</v>
       </c>
       <c r="L4" t="n">
         <v>16</v>
@@ -949,10 +949,10 @@
         <v>58.49056603773585</v>
       </c>
       <c r="S4" t="n">
-        <v>36.93324729902596</v>
+        <v>37.34056829450487</v>
       </c>
       <c r="T4" t="n">
-        <v>21.55731873870989</v>
+        <v>21.14999774323098</v>
       </c>
       <c r="U4" t="n">
         <v>45.09442218134437</v>
@@ -981,10 +981,10 @@
         <v>60</v>
       </c>
       <c r="AG4" t="n">
-        <v>38.55050898673715</v>
+        <v>38.7582984030571</v>
       </c>
       <c r="AH4" t="n">
-        <v>21.44949101326285</v>
+        <v>21.2417015969429</v>
       </c>
       <c r="AI4" t="n">
         <v>45.45185459035139</v>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2649003767482757</v>
+        <v>0.26326581217916</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
         <v>62</v>
       </c>
       <c r="S5" t="n">
-        <v>44.74566289664097</v>
+        <v>44.84124694222501</v>
       </c>
       <c r="T5" t="n">
-        <v>17.25433710335903</v>
+        <v>17.15875305777499</v>
       </c>
       <c r="U5" t="n">
         <v>48.15044693099298</v>
@@ -1063,25 +1063,25 @@
         <v>58.46153846153846</v>
       </c>
       <c r="X5" t="n">
-        <v>16.71841465953139</v>
+        <v>16.70172291026088</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.195780075516621</v>
+        <v>5.767292269863844</v>
       </c>
       <c r="Z5" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="AA5" t="n">
-        <v>36.36363636363637</v>
+        <v>37.93103448275862</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.13495178814146</v>
+        <v>17.56925120345615</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.067516961070084</v>
+        <v>4.491760697631431</v>
       </c>
       <c r="AE5" t="n">
         <v>45</v>
@@ -1090,10 +1090,10 @@
         <v>48.88888888888889</v>
       </c>
       <c r="AG5" t="n">
-        <v>25.58886398670354</v>
+        <v>25.702862759323</v>
       </c>
       <c r="AH5" t="n">
-        <v>23.30002490218535</v>
+        <v>23.18602612956589</v>
       </c>
       <c r="AI5" t="n">
         <v>34.9570237528785</v>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C6" t="n">
-        <v>1.922053115357382</v>
+        <v>1.917718880641212</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,10 +1144,10 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>23.72415549749964</v>
+        <v>23.73506360720576</v>
       </c>
       <c r="K6" t="n">
-        <v>1.218834869806096</v>
+        <v>1.005030735562906</v>
       </c>
       <c r="L6" t="n">
         <v>27</v>
@@ -1156,13 +1156,13 @@
         <v>77.77777777777777</v>
       </c>
       <c r="N6" t="n">
-        <v>14.31557485845824</v>
+        <v>14.44735332283513</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7717586664563791</v>
+        <v>0.9850690180392974</v>
       </c>
       <c r="Q6" t="n">
         <v>40</v>
@@ -1171,10 +1171,10 @@
         <v>67.5</v>
       </c>
       <c r="S6" t="n">
-        <v>48.05915074208657</v>
+        <v>47.37539610276927</v>
       </c>
       <c r="T6" t="n">
-        <v>19.44084925791343</v>
+        <v>20.12460389723073</v>
       </c>
       <c r="U6" t="n">
         <v>52.01774618987768</v>
@@ -1189,7 +1189,7 @@
         <v>44.49622708587002</v>
       </c>
       <c r="Y6" t="n">
-        <v>22.79447890746409</v>
+        <v>22.96857755600068</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C7" t="n">
-        <v>2.162967371979649</v>
+        <v>2.161639401008327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,16 +1262,16 @@
         <v>11.35312764557068</v>
       </c>
       <c r="K7" t="n">
-        <v>3.624787409243768</v>
+        <v>3.561166149223083</v>
       </c>
       <c r="L7" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M7" t="n">
-        <v>50.81967213114754</v>
+        <v>52.38095238095238</v>
       </c>
       <c r="N7" t="n">
-        <v>12.67331044452345</v>
+        <v>12.78180602736253</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1286,10 +1286,10 @@
         <v>58.8235294117647</v>
       </c>
       <c r="S7" t="n">
-        <v>51.89826781964963</v>
+        <v>51.70218938827708</v>
       </c>
       <c r="T7" t="n">
-        <v>6.925261592115078</v>
+        <v>7.121340023487626</v>
       </c>
       <c r="U7" t="n">
         <v>45.16533720637157</v>
@@ -1304,13 +1304,13 @@
         <v>13.79329344082609</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.139866977778931</v>
+        <v>8.196265234939748</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA7" t="n">
-        <v>57.14285714285715</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="AB7" t="n">
         <v>8.654336102227296</v>
@@ -1319,7 +1319,7 @@
         <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.02496225622828</v>
+        <v>1.96477275099568</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3206577944891157</v>
+        <v>0.3221431320117004</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>22.10694516187944</v>
       </c>
       <c r="K8" t="n">
-        <v>1.952440322215221</v>
+        <v>2.424700119831957</v>
       </c>
       <c r="L8" t="n">
         <v>11</v>
@@ -1390,13 +1390,13 @@
         <v>72.72727272727273</v>
       </c>
       <c r="N8" t="n">
-        <v>17.10466508226268</v>
+        <v>16.69353349408749</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>5.931745879423578</v>
+        <v>5.443315795550507</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5685153468082034</v>
+        <v>0.5723718021223878</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,19 +1487,19 @@
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>12.72202042588303</v>
+        <v>11.07138721870453</v>
       </c>
       <c r="K9" t="n">
-        <v>2.292709385993685</v>
+        <v>2.986599647582411</v>
       </c>
       <c r="L9" t="n">
+        <v>40</v>
+      </c>
+      <c r="M9" t="n">
         <v>45</v>
       </c>
-      <c r="M9" t="n">
-        <v>51.11111111111111</v>
-      </c>
       <c r="N9" t="n">
-        <v>14.25664128597968</v>
+        <v>15.45282043738036</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C10" t="n">
-        <v>2.026203874890748</v>
+        <v>2.028113885685852</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,10 +1596,10 @@
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>10.22410665907629</v>
+        <v>10.23694539327734</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3125031770833342</v>
+        <v>0.4214243768458692</v>
       </c>
       <c r="L10" t="n">
         <v>41</v>
@@ -1608,13 +1608,13 @@
         <v>43.90243902439025</v>
       </c>
       <c r="N10" t="n">
-        <v>10.11800639229653</v>
+        <v>9.822220633184779</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>9.657317399223086</v>
+        <v>9.538378570701367</v>
       </c>
       <c r="Q10" t="n">
         <v>44</v>
@@ -1623,10 +1623,10 @@
         <v>50</v>
       </c>
       <c r="S10" t="n">
-        <v>35.99804965802223</v>
+        <v>36.14225028498147</v>
       </c>
       <c r="T10" t="n">
-        <v>14.00195034197777</v>
+        <v>13.85774971501853</v>
       </c>
       <c r="U10" t="n">
         <v>35.8317605399894</v>
@@ -1645,23 +1645,23 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AF10" t="n">
-        <v>51.51515151515152</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="AG10" t="n">
-        <v>36.33694992423531</v>
+        <v>39.46550909050909</v>
       </c>
       <c r="AH10" t="n">
-        <v>15.1782015909162</v>
+        <v>13.86782424282425</v>
       </c>
       <c r="AI10" t="n">
-        <v>35.21837544891414</v>
+        <v>36.1422996198733</v>
       </c>
       <c r="AJ10" t="n">
         <v>55</v>
@@ -1677,19 +1677,19 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C11" t="n">
-        <v>7.053840369085257</v>
+        <v>7.217730567918579</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1705,25 +1705,25 @@
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>20.55286918845752</v>
+        <v>20.56423081971027</v>
       </c>
       <c r="K11" t="n">
-        <v>1.055011303692543</v>
+        <v>3.417731290746562</v>
       </c>
       <c r="L11" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="M11" t="n">
-        <v>73.91304347826087</v>
+        <v>62.5</v>
       </c>
       <c r="N11" t="n">
-        <v>16.70337383836244</v>
+        <v>12.53796400267027</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.924683072334088</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>49</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C12" t="n">
-        <v>6.091235754959528</v>
+        <v>6.218918617514697</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1817,16 +1817,16 @@
         <v>20.08266526523165</v>
       </c>
       <c r="K12" t="n">
-        <v>6.046624364755138</v>
+        <v>8.269545477631146</v>
       </c>
       <c r="L12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M12" t="n">
-        <v>50</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N12" t="n">
-        <v>23.02355388202442</v>
+        <v>33.26223985018026</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3101375254822771</v>
+        <v>0.3025874590717458</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>38.11781916800814</v>
       </c>
       <c r="K13" t="n">
-        <v>8.983862505226025</v>
+        <v>6.330731774557008</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1962,7 +1962,7 @@
         <v>35.74308703619145</v>
       </c>
       <c r="Y13" t="n">
-        <v>19.71313981081847</v>
+        <v>21.66766345441414</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C14" t="n">
-        <v>7.990144310693889</v>
+        <v>7.964211078220427</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,10 +2039,10 @@
         <v>60.97560975609756</v>
       </c>
       <c r="S14" t="n">
-        <v>34.46629652895422</v>
+        <v>34.4990901342012</v>
       </c>
       <c r="T14" t="n">
-        <v>26.50931322714334</v>
+        <v>26.47651962189637</v>
       </c>
       <c r="U14" t="n">
         <v>45.72685693412379</v>
@@ -2057,16 +2057,16 @@
         <v>14.33662537827827</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.659572234437217</v>
+        <v>7.959277181785707</v>
       </c>
       <c r="Z14" t="n">
         <v>22</v>
       </c>
       <c r="AA14" t="n">
-        <v>40.90909090909091</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.26258837364468</v>
+        <v>10.47267774674982</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2081,10 +2081,10 @@
         <v>52.63157894736842</v>
       </c>
       <c r="AG14" t="n">
-        <v>26.59691373653583</v>
+        <v>26.68358875742138</v>
       </c>
       <c r="AH14" t="n">
-        <v>26.03466521083259</v>
+        <v>25.94799018994704</v>
       </c>
       <c r="AI14" t="n">
         <v>37.25897138449667</v>
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C15" t="n">
-        <v>11.30928918235146</v>
+        <v>11.23926289454474</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,25 +2131,25 @@
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>20.36228477344414</v>
+        <v>19.49276356151121</v>
       </c>
       <c r="K15" t="n">
-        <v>6.483066214758493</v>
+        <v>5.823730891285361</v>
       </c>
       <c r="L15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M15" t="n">
-        <v>63.63636363636363</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N15" t="n">
-        <v>15.0289238728392</v>
+        <v>18.42435090586761</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>1.424577483693157</v>
+        <v>2.056503858241743</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2158,10 +2158,10 @@
         <v>76.92307692307692</v>
       </c>
       <c r="S15" t="n">
-        <v>53.32217477086338</v>
+        <v>53.33079360301163</v>
       </c>
       <c r="T15" t="n">
-        <v>23.60090215221354</v>
+        <v>23.59228332006529</v>
       </c>
       <c r="U15" t="n">
         <v>61.66374277165825</v>
@@ -2190,10 +2190,10 @@
         <v>58.06451612903226</v>
       </c>
       <c r="AG15" t="n">
-        <v>24.94292152949194</v>
+        <v>25.06124739654446</v>
       </c>
       <c r="AH15" t="n">
-        <v>33.12159459954032</v>
+        <v>33.0032687324878</v>
       </c>
       <c r="AI15" t="n">
         <v>40.76626249536972</v>
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C16" t="n">
-        <v>36.21076592153833</v>
+        <v>36.02031307456526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,25 +2240,25 @@
         <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>19.01528411877121</v>
+        <v>18.2920442587057</v>
       </c>
       <c r="K16" t="n">
-        <v>4.372698785391571</v>
+        <v>3.823743878637798</v>
       </c>
       <c r="L16" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="M16" t="n">
-        <v>63.04347826086956</v>
+        <v>61.22448979591837</v>
       </c>
       <c r="N16" t="n">
-        <v>16.46890478610655</v>
+        <v>16.59012435820357</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>5.391545183840796</v>
+        <v>5.948789641588914</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2267,10 +2267,10 @@
         <v>67.85714285714286</v>
       </c>
       <c r="S16" t="n">
-        <v>54.19064654084273</v>
+        <v>54.02219122768298</v>
       </c>
       <c r="T16" t="n">
-        <v>13.66649631630013</v>
+        <v>13.83495162945988</v>
       </c>
       <c r="U16" t="n">
         <v>49.33884318085762</v>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7191655958300509</v>
+        <v>0.7174623721905614</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,25 +2349,25 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>16.56354083790577</v>
+        <v>14.16674936134154</v>
       </c>
       <c r="K17" t="n">
-        <v>2.139165132671472</v>
+        <v>1.89726557354295</v>
       </c>
       <c r="L17" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="M17" t="n">
-        <v>62.26415094339622</v>
+        <v>70</v>
       </c>
       <c r="N17" t="n">
-        <v>18.04154495657372</v>
+        <v>16.68447139999035</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>5.738087696052463</v>
+        <v>5.989105195421063</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2394,13 +2394,13 @@
         <v>15.7396793517258</v>
       </c>
       <c r="Y17" t="n">
-        <v>11.75095204620636</v>
+        <v>11.95995518193599</v>
       </c>
       <c r="Z17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA17" t="n">
-        <v>63.1578947368421</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB17" t="n">
         <v>9.196941783233198</v>
@@ -2418,10 +2418,10 @@
         <v>60</v>
       </c>
       <c r="AG17" t="n">
-        <v>42.73545695777331</v>
+        <v>42.73923624726688</v>
       </c>
       <c r="AH17" t="n">
-        <v>17.26454304222669</v>
+        <v>17.26076375273312</v>
       </c>
       <c r="AI17" t="n">
         <v>43.5727090128925</v>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C18" t="n">
-        <v>0.101836207142278</v>
+        <v>0.102825059107988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,25 +2468,25 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>27.32413099353592</v>
+        <v>27.33452427541018</v>
       </c>
       <c r="K18" t="n">
-        <v>1.894740000000006</v>
+        <v>2.898875767547082</v>
       </c>
       <c r="L18" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="M18" t="n">
-        <v>52.63157894736842</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N18" t="n">
-        <v>20.39831773620558</v>
+        <v>20.90509599778342</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>7.954542108846829</v>
+        <v>6.901070764363526</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2527,10 +2527,10 @@
         <v>59.52380952380953</v>
       </c>
       <c r="AG18" t="n">
-        <v>39.37236124454621</v>
+        <v>39.39994803683889</v>
       </c>
       <c r="AH18" t="n">
-        <v>20.15144827926331</v>
+        <v>20.12386148697064</v>
       </c>
       <c r="AI18" t="n">
         <v>44.49431275003934</v>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02482783380411211</v>
+        <v>0.02502286907177551</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2569,11 +2569,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>5</v>
       </c>
@@ -2584,22 +2580,22 @@
         <v>23.99412305210119</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5206627767776251</v>
+        <v>1.310303730759044</v>
       </c>
       <c r="L19" t="n">
         <v>20</v>
       </c>
       <c r="M19" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="N19" t="n">
-        <v>20.99582487684433</v>
+        <v>23.79065269649551</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>9.430237486866533</v>
+        <v>8.577307489211151</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2662,10 +2658,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C20" t="n">
-        <v>1.839994985122424</v>
+        <v>1.830454385874408</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,7 +2721,7 @@
         <v>20.34011802710127</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.119216867047995</v>
+        <v>7.600815097955349</v>
       </c>
       <c r="Z20" t="n">
         <v>18</v>
@@ -2734,7 +2730,7 @@
         <v>44.44444444444444</v>
       </c>
       <c r="AB20" t="n">
-        <v>12.96967327390692</v>
+        <v>13.15851961577055</v>
       </c>
       <c r="AC20" t="n">
         <v>4</v>
@@ -2771,10 +2767,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9501906935415783</v>
+        <v>0.9777843303953793</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2799,25 +2795,25 @@
         <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>15.77844025931157</v>
+        <v>14.08722322280853</v>
       </c>
       <c r="K21" t="n">
-        <v>1.564783060602037</v>
+        <v>4.514234954793528</v>
       </c>
       <c r="L21" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="M21" t="n">
-        <v>50</v>
+        <v>53.48837209302326</v>
       </c>
       <c r="N21" t="n">
-        <v>21.84859522686849</v>
+        <v>15.49973924911641</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>6.336071171006363</v>
+        <v>3.335206009702141</v>
       </c>
       <c r="Q21" t="n">
         <v>41</v>
@@ -2858,10 +2854,10 @@
         <v>61.53846153846154</v>
       </c>
       <c r="AG21" t="n">
-        <v>34.62938991928713</v>
+        <v>34.67662338757323</v>
       </c>
       <c r="AH21" t="n">
-        <v>26.90907161917441</v>
+        <v>26.86183815088831</v>
       </c>
       <c r="AI21" t="n">
         <v>45.89906145692508</v>
@@ -2880,10 +2876,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7928074788779208</v>
+        <v>0.7860124584173873</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2900,11 +2896,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>5</v>
       </c>
@@ -2912,25 +2904,25 @@
         <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>22.47437017331863</v>
+        <v>20.35908649698318</v>
       </c>
       <c r="K22" t="n">
-        <v>5.610799434510239</v>
+        <v>4.705626915166117</v>
       </c>
       <c r="L22" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M22" t="n">
-        <v>76.92307692307692</v>
+        <v>68.75</v>
       </c>
       <c r="N22" t="n">
-        <v>12.40298813286815</v>
+        <v>15.69529022497824</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>4.156014904717709</v>
+        <v>5.056436068257786</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -2985,27 +2977,31 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C23" t="n">
-        <v>0.71664075357138</v>
+        <v>0.7780219403146028</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BAND</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>5</v>
       </c>
@@ -3013,25 +3009,25 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>24.63609028576259</v>
+        <v>24.64686798085608</v>
       </c>
       <c r="K23" t="n">
-        <v>2.900311010195633</v>
+        <v>11.72983110515275</v>
       </c>
       <c r="L23" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>64.28571428571429</v>
+        <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>18.61486514700509</v>
+        <v>12.41985142387837</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.040507914107592</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3054,17 +3050,27 @@
       <c r="W23" t="n">
         <v>87.5</v>
       </c>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
+      <c r="X23" t="n">
+        <v>13.36048547240214</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.438468052120656</v>
+      </c>
       <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>13.40010890158462</v>
+      </c>
       <c r="AC23" t="n">
         <v>6</v>
       </c>
-      <c r="AD23" t="inlineStr"/>
+      <c r="AD23" t="n">
+        <v>4.628105770810819</v>
+      </c>
       <c r="AE23" t="n">
         <v>10</v>
       </c>
@@ -3094,10 +3100,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1758988906405579</v>
+        <v>0.1781039471494759</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,25 +3128,25 @@
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>27.39484163531333</v>
+        <v>23.34450349594161</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4807688881055761</v>
+        <v>1.754940803300054</v>
       </c>
       <c r="L24" t="n">
         <v>15</v>
       </c>
       <c r="M24" t="n">
-        <v>73.33333333333333</v>
+        <v>60</v>
       </c>
       <c r="N24" t="n">
-        <v>16.83448322139268</v>
+        <v>14.52787507022096</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>9.473684583857999</v>
+        <v>8.102858821016135</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3203,19 +3209,19 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C25" t="n">
-        <v>3.9556211465713</v>
+        <v>3.95108967132919</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3230,27 +3236,17 @@
       <c r="I25" t="n">
         <v>10</v>
       </c>
-      <c r="J25" t="n">
-        <v>12.04001635695179</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.46622065064448</v>
-      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>55</v>
-      </c>
-      <c r="M25" t="n">
-        <v>50.90909090909091</v>
-      </c>
-      <c r="N25" t="n">
-        <v>18.38827790074306</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
         <v>8</v>
       </c>
-      <c r="P25" t="n">
-        <v>4.381893260278558</v>
-      </c>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="n">
         <v>44</v>
       </c>
@@ -3258,10 +3254,10 @@
         <v>68.18181818181819</v>
       </c>
       <c r="S25" t="n">
-        <v>36.91307030616539</v>
+        <v>36.9404339161862</v>
       </c>
       <c r="T25" t="n">
-        <v>31.26874787565279</v>
+        <v>31.24138426563199</v>
       </c>
       <c r="U25" t="n">
         <v>53.44310393781777</v>
@@ -3290,10 +3286,10 @@
         <v>53.48837209302326</v>
       </c>
       <c r="AG25" t="n">
-        <v>50.48741665689312</v>
+        <v>50.65061301365994</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.000955436130134</v>
+        <v>2.837759079363316</v>
       </c>
       <c r="AI25" t="n">
         <v>38.91564047231397</v>
@@ -3312,10 +3308,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4376431746936753</v>
+        <v>0.4356922720671197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3411,10 +3407,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C27" t="n">
-        <v>34.35919857633475</v>
+        <v>34.085772033783</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3439,10 +3435,10 @@
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>59.57268759382546</v>
+        <v>60.11995427672586</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5541871921182384</v>
+        <v>1.122894572676225</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3453,7 +3449,7 @@
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>7.404776484996933</v>
+        <v>6.800740283775464</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -3496,10 +3492,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C28" t="n">
-        <v>1.411820068525712</v>
+        <v>1.408850540569686</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3524,25 +3520,25 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>25.72214510232956</v>
+        <v>24.87361787048376</v>
       </c>
       <c r="K28" t="n">
-        <v>1.253226149365827</v>
+        <v>1.040256881970225</v>
       </c>
       <c r="L28" t="n">
         <v>19</v>
       </c>
       <c r="M28" t="n">
-        <v>68.42105263157895</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="N28" t="n">
-        <v>17.7683328440831</v>
+        <v>16.11094891522698</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>0.7375309202815483</v>
+        <v>0.9498621120400452</v>
       </c>
       <c r="Q28" t="n">
         <v>40</v>
@@ -3551,10 +3547,10 @@
         <v>57.5</v>
       </c>
       <c r="S28" t="n">
-        <v>60.23282694082881</v>
+        <v>59.75202829605958</v>
       </c>
       <c r="T28" t="n">
-        <v>-2.732826940828808</v>
+        <v>-2.252028296059578</v>
       </c>
       <c r="U28" t="n">
         <v>42.19506854199106</v>
@@ -3605,10 +3601,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3985078011305299</v>
+        <v>0.3864876380930803</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3625,7 +3621,11 @@
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %88.89: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H29" t="n">
         <v>5</v>
       </c>
@@ -3633,25 +3633,25 @@
         <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>13.92658510858031</v>
+        <v>17.83520922572316</v>
       </c>
       <c r="K29" t="n">
-        <v>1.067239927719577</v>
+        <v>2.68156173290468</v>
       </c>
       <c r="L29" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="M29" t="n">
-        <v>57.14285714285715</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N29" t="n">
-        <v>24.20466013684741</v>
+        <v>28.21742727075513</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>2.9017910001083</v>
+        <v>1.284006831260354</v>
       </c>
       <c r="Q29" t="n">
         <v>6</v>
@@ -3678,7 +3678,7 @@
         <v>55.05052857749912</v>
       </c>
       <c r="Y29" t="n">
-        <v>13.00797525770735</v>
+        <v>15.63190963839896</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3720,10 +3720,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3835689983106866</v>
+        <v>0.3818615762002674</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3748,25 +3748,25 @@
         <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>22.50856964296201</v>
+        <v>21.77845247058357</v>
       </c>
       <c r="K30" t="n">
-        <v>3.758912086798349</v>
+        <v>3.297038834709998</v>
       </c>
       <c r="L30" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M30" t="n">
-        <v>50</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N30" t="n">
-        <v>11.60016023263135</v>
+        <v>11.64030685510427</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>1.196126567097622</v>
+        <v>1.648605985709795</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1874711905457825</v>
+        <v>0.1863047061259438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3857,25 +3857,25 @@
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>26.14803348293122</v>
+        <v>26.85904908752153</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4509578409927162</v>
+        <v>0.7963560900858146</v>
       </c>
       <c r="L31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M31" t="n">
-        <v>50</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N31" t="n">
-        <v>14.664321271725</v>
+        <v>15.87753653145509</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>9.506173325019752</v>
+        <v>9.130929199155302</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3938,19 +3938,19 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C32" t="n">
-        <v>2.289210600061713</v>
+        <v>2.319346551072098</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3965,27 +3965,17 @@
       <c r="I32" t="n">
         <v>10</v>
       </c>
-      <c r="J32" t="n">
-        <v>11.96252232646255</v>
-      </c>
-      <c r="K32" t="n">
-        <v>8.622232153428566</v>
-      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
-        <v>30</v>
-      </c>
-      <c r="M32" t="n">
-        <v>50</v>
-      </c>
-      <c r="N32" t="n">
-        <v>10.88144950943727</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
         <v>3</v>
       </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
+      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="n">
         <v>33</v>
       </c>
@@ -4011,22 +4001,22 @@
         <v>12.36180984775317</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.328157226544881</v>
+        <v>2.055536036591477</v>
       </c>
       <c r="Z32" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="AA32" t="n">
-        <v>34.78260869565217</v>
+        <v>45.09803921568628</v>
       </c>
       <c r="AB32" t="n">
-        <v>11.98597638064313</v>
+        <v>10.84413756618767</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>4.832682029661218</v>
+        <v>6.069218945982835</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4057,10 +4047,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C33" t="n">
-        <v>1.828422785580565</v>
+        <v>1.828351495605076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4088,7 +4078,7 @@
         <v>12.57251846431013</v>
       </c>
       <c r="K33" t="n">
-        <v>2.480993614976357</v>
+        <v>2.476997893865995</v>
       </c>
       <c r="L33" t="n">
         <v>54</v>
@@ -4103,7 +4093,7 @@
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>1.482232296391062</v>
+        <v>1.486189230203006</v>
       </c>
       <c r="Q33" t="n">
         <v>39</v>
@@ -4166,10 +4156,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8580331145282969</v>
+        <v>0.8638146684298388</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4194,25 +4184,25 @@
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>10.30997185104549</v>
+        <v>10.40906379693826</v>
       </c>
       <c r="K34" t="n">
-        <v>0.1473417441120617</v>
+        <v>0.9336635452190434</v>
       </c>
       <c r="L34" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M34" t="n">
-        <v>48.97959183673469</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="N34" t="n">
-        <v>13.7460313909748</v>
+        <v>13.73200290307858</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>3.846990033676501</v>
+        <v>3.037972017539237</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4239,16 +4229,16 @@
         <v>14.68007915548277</v>
       </c>
       <c r="Y34" t="n">
-        <v>10.17782099927622</v>
+        <v>9.57258588578982</v>
       </c>
       <c r="Z34" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="n">
-        <v>47.36842105263158</v>
+        <v>50</v>
       </c>
       <c r="AB34" t="n">
-        <v>10.49224721614327</v>
+        <v>11.00516569549747</v>
       </c>
       <c r="AC34" t="n">
         <v>2</v>
@@ -4263,10 +4253,10 @@
         <v>53.84615384615385</v>
       </c>
       <c r="AG34" t="n">
-        <v>28.02451055471287</v>
+        <v>28.41426498030814</v>
       </c>
       <c r="AH34" t="n">
-        <v>25.82164329144098</v>
+        <v>25.4318888658457</v>
       </c>
       <c r="AI34" t="n">
         <v>38.56944827051576</v>
@@ -4285,10 +4275,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C35" t="n">
-        <v>1.935729497258296</v>
+        <v>1.931386865608722</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4307,7 +4297,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %88.89: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4320,16 +4310,16 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>9.127235757976027</v>
+        <v>8.882418809892979</v>
       </c>
       <c r="L35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M35" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N35" t="n">
-        <v>12.38992893736071</v>
+        <v>12.48259706892392</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4362,7 +4352,7 @@
         <v>42.52272358489104</v>
       </c>
       <c r="Y35" t="n">
-        <v>15.87294443116339</v>
+        <v>16.06167576713577</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -4404,10 +4394,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08184769497725783</v>
+        <v>0.08179744393583781</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4432,19 +4422,19 @@
         <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>21.75644461318207</v>
+        <v>20.39128953068605</v>
       </c>
       <c r="K36" t="n">
-        <v>2.298580749949442</v>
+        <v>2.235773725024615</v>
       </c>
       <c r="L36" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M36" t="n">
-        <v>41.1764705882353</v>
+        <v>50</v>
       </c>
       <c r="N36" t="n">
-        <v>14.96518048865908</v>
+        <v>13.04871975908602</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4513,10 +4503,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06291120887129999</v>
+        <v>0.06287258403569951</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4544,22 +4534,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>2.408826306275524</v>
+        <v>2.345951595217133</v>
       </c>
       <c r="L37" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M37" t="n">
-        <v>58.10810810810811</v>
+        <v>56.57894736842105</v>
       </c>
       <c r="N37" t="n">
-        <v>19.21787917365839</v>
+        <v>19.24752808895938</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>5.459659968177832</v>
+        <v>5.524447539600685</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4568,10 +4558,10 @@
         <v>55.55555555555556</v>
       </c>
       <c r="S37" t="n">
-        <v>35.41760949006174</v>
+        <v>35.35742430487655</v>
       </c>
       <c r="T37" t="n">
-        <v>20.13794606549381</v>
+        <v>20.198131250679</v>
       </c>
       <c r="U37" t="n">
         <v>39.5810617556973</v>
@@ -4622,10 +4612,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C38" t="n">
-        <v>1.661150412006168</v>
+        <v>1.653822345841002</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4642,11 +4632,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>5</v>
       </c>
@@ -4654,25 +4640,25 @@
         <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>19.5673086238003</v>
+        <v>18.01910891260425</v>
       </c>
       <c r="K38" t="n">
-        <v>4.848109640206966</v>
+        <v>4.385578445450133</v>
       </c>
       <c r="L38" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M38" t="n">
-        <v>76</v>
+        <v>67.74193548387096</v>
       </c>
       <c r="N38" t="n">
-        <v>12.75247762912281</v>
+        <v>14.79177455291849</v>
       </c>
       <c r="O38" t="n">
         <v>6</v>
       </c>
       <c r="P38" t="n">
-        <v>1.098627685082576</v>
+        <v>1.546594442060334</v>
       </c>
       <c r="Q38" t="n">
         <v>35</v>
@@ -4681,10 +4667,10 @@
         <v>54.28571428571428</v>
       </c>
       <c r="S38" t="n">
-        <v>47.59013302528162</v>
+        <v>48.14378228525551</v>
       </c>
       <c r="T38" t="n">
-        <v>6.695581260432668</v>
+        <v>6.141932000458773</v>
       </c>
       <c r="U38" t="n">
         <v>38.18972506848375</v>
@@ -4713,10 +4699,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="AG38" t="n">
-        <v>20.29063847675367</v>
+        <v>20.3581137714274</v>
       </c>
       <c r="AH38" t="n">
-        <v>36.85221866610347</v>
+        <v>36.78474337142975</v>
       </c>
       <c r="AI38" t="n">
         <v>40.85741114397492</v>
@@ -4735,10 +4721,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C39" t="n">
-        <v>2.686876640172928</v>
+        <v>2.674713200947313</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4763,19 +4749,19 @@
         <v>10</v>
       </c>
       <c r="J39" t="n">
-        <v>19.12528796921053</v>
+        <v>18.47027414490581</v>
       </c>
       <c r="K39" t="n">
-        <v>6.358668340534646</v>
+        <v>5.877184680609626</v>
       </c>
       <c r="L39" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M39" t="n">
-        <v>61.11111111111111</v>
+        <v>70</v>
       </c>
       <c r="N39" t="n">
-        <v>14.25905874162124</v>
+        <v>14.53711661926971</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4790,10 +4776,10 @@
         <v>65.11627906976744</v>
       </c>
       <c r="S39" t="n">
-        <v>49.05308270843281</v>
+        <v>49.51062611645727</v>
       </c>
       <c r="T39" t="n">
-        <v>16.06319636133463</v>
+        <v>15.60565295331017</v>
       </c>
       <c r="U39" t="n">
         <v>50.17178199285205</v>
@@ -4844,24 +4830,24 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1986226700120861</v>
+        <v>0.1970287971666329</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4875,16 +4861,16 @@
         <v>14.73965458840789</v>
       </c>
       <c r="K40" t="n">
-        <v>8.475660721374556</v>
+        <v>7.605184002851528</v>
       </c>
       <c r="L40" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M40" t="n">
-        <v>61.11111111111111</v>
+        <v>68.75</v>
       </c>
       <c r="N40" t="n">
-        <v>11.87432800207371</v>
+        <v>12.21407746678665</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4917,22 +4903,22 @@
         <v>14.17330472629232</v>
       </c>
       <c r="Y40" t="n">
-        <v>4.990346927923939</v>
+        <v>5.752763957552542</v>
       </c>
       <c r="Z40" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA40" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="AB40" t="n">
-        <v>10.90744550176035</v>
+        <v>12.58136924216362</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.01016009612070379</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>13</v>
@@ -4963,10 +4949,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C41" t="n">
-        <v>1.644318077960891</v>
+        <v>1.626486375485432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4998,7 +4984,7 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>8.665808178223822</v>
+        <v>7.487388755205426</v>
       </c>
       <c r="L41" t="n">
         <v>12</v>
@@ -5007,13 +4993,13 @@
         <v>75</v>
       </c>
       <c r="N41" t="n">
-        <v>14.51550197500303</v>
+        <v>17.56011838426139</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>1.227793584885473</v>
+        <v>2.337587017316856</v>
       </c>
       <c r="Q41" t="n">
         <v>10</v>
@@ -5040,7 +5026,7 @@
         <v>40.81782021738603</v>
       </c>
       <c r="Y41" t="n">
-        <v>15.67400846735836</v>
+        <v>16.58847630184379</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -5082,10 +5068,10 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C42" t="n">
-        <v>3.149768476473825</v>
+        <v>3.177273511553252</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5104,7 +5090,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -5114,19 +5100,19 @@
         <v>10</v>
       </c>
       <c r="J42" t="n">
-        <v>22.36276267242437</v>
+        <v>21.13784986389697</v>
       </c>
       <c r="K42" t="n">
-        <v>2.478364573202785</v>
+        <v>3.373246541043096</v>
       </c>
       <c r="L42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M42" t="n">
-        <v>100</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N42" t="n">
-        <v>13.14793523296843</v>
+        <v>13.42476118611086</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
@@ -5191,14 +5177,14 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C43" t="n">
-        <v>7.343147766773317</v>
+        <v>7.212473662916453</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5208,14 +5194,10 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %81.82: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>BAZ_ORAN_YETERSİZ</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>5</v>
       </c>
@@ -5258,22 +5240,22 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>5.219594126463778</v>
+        <v>6.906247451997549</v>
       </c>
       <c r="Z43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA43" t="n">
-        <v>81.81818181818181</v>
+        <v>60</v>
       </c>
       <c r="AB43" t="n">
-        <v>11.13754853734093</v>
+        <v>13.09070057304151</v>
       </c>
       <c r="AC43" t="n">
         <v>6</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.8233831310846096</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
         <v>8</v>
@@ -5304,10 +5286,10 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C44" t="n">
-        <v>5.026584403120183</v>
+        <v>4.979340482147699</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5335,22 +5317,22 @@
         <v>13.03201987649729</v>
       </c>
       <c r="K44" t="n">
-        <v>2.880840815570873</v>
+        <v>1.913883151424911</v>
       </c>
       <c r="L44" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="M44" t="n">
-        <v>70.83333333333333</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N44" t="n">
-        <v>17.94687033846331</v>
+        <v>17.42717636190461</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>6.919810460327858</v>
+        <v>7.934264300930072</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5377,7 +5359,7 @@
         <v>12.1234692799834</v>
       </c>
       <c r="Y44" t="n">
-        <v>8.243259438693219</v>
+        <v>9.105663777727147</v>
       </c>
       <c r="Z44" t="n">
         <v>7</v>
@@ -5386,13 +5368,13 @@
         <v>14.28571428571429</v>
       </c>
       <c r="AB44" t="n">
-        <v>9.691917834769438</v>
+        <v>8.805992909897132</v>
       </c>
       <c r="AC44" t="n">
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.914562952607302</v>
+        <v>0.983929537794126</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5415,10 +5397,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02040932250448295</v>
+        <v>0.02039679203907629</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5443,19 +5425,19 @@
         <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>11.4828208335343</v>
+        <v>10.66683965345718</v>
       </c>
       <c r="K45" t="n">
         <v>1.041671896701502</v>
       </c>
       <c r="L45" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="M45" t="n">
-        <v>59.30232558139535</v>
+        <v>61.03896103896104</v>
       </c>
       <c r="N45" t="n">
-        <v>14.86013625887492</v>
+        <v>15.1445705774911</v>
       </c>
       <c r="O45" t="n">
         <v>10</v>
@@ -5524,10 +5506,10 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C46" t="n">
-        <v>8.484596954015302</v>
+        <v>8.531956818450002</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5552,25 +5534,25 @@
         <v>10</v>
       </c>
       <c r="J46" t="n">
-        <v>25.36565524710288</v>
+        <v>23.79638976838147</v>
       </c>
       <c r="K46" t="n">
-        <v>2.738853503184724</v>
+        <v>3.327104463812081</v>
       </c>
       <c r="L46" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M46" t="n">
-        <v>55.55555555555556</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="N46" t="n">
-        <v>16.4590755360719</v>
+        <v>10.19857950124049</v>
       </c>
       <c r="O46" t="n">
         <v>10</v>
       </c>
       <c r="P46" t="n">
-        <v>7.067575945443272</v>
+        <v>6.458030127540204</v>
       </c>
       <c r="Q46" t="n">
         <v>54</v>
@@ -5605,19 +5587,19 @@
       </c>
       <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AF46" t="n">
-        <v>58.97435897435897</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="AG46" t="n">
-        <v>16.96892785409365</v>
+        <v>17.61095990167152</v>
       </c>
       <c r="AH46" t="n">
-        <v>42.00543112026533</v>
+        <v>40.28377694043374</v>
       </c>
       <c r="AI46" t="n">
-        <v>43.41862288289698</v>
+        <v>42.19234534367055</v>
       </c>
       <c r="AJ46" t="n">
         <v>81</v>
@@ -5633,10 +5615,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7869161539035476</v>
+        <v>0.7801246701431945</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5653,11 +5635,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.95: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>5</v>
       </c>
@@ -5665,25 +5643,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>27.74248530779953</v>
+        <v>25.38434003813299</v>
       </c>
       <c r="K47" t="n">
-        <v>5.568412181933136</v>
+        <v>4.657303478187114</v>
       </c>
       <c r="L47" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M47" t="n">
-        <v>78.94736842105263</v>
+        <v>50</v>
       </c>
       <c r="N47" t="n">
-        <v>12.87809202591376</v>
+        <v>16.45845198786146</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>4.197835059250132</v>
+        <v>5.104943796804817</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5746,10 +5724,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C48" t="n">
-        <v>0.06164877785291165</v>
+        <v>0.06161092809684655</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5774,25 +5752,25 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>35.39957983385757</v>
+        <v>34.60463024804744</v>
       </c>
       <c r="K48" t="n">
-        <v>5.046609814906811</v>
+        <v>4.982115615744487</v>
       </c>
       <c r="L48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M48" t="n">
-        <v>60</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N48" t="n">
-        <v>9.470969877799496</v>
+        <v>11.58233814173376</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>4.715421272348652</v>
+        <v>4.779751631813167</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5833,10 +5811,10 @@
         <v>60.37735849056604</v>
       </c>
       <c r="AG48" t="n">
-        <v>23.3257816610601</v>
+        <v>23.36181717488015</v>
       </c>
       <c r="AH48" t="n">
-        <v>37.05157682950594</v>
+        <v>37.01554131568589</v>
       </c>
       <c r="AI48" t="n">
         <v>46.94147867320552</v>
@@ -5855,19 +5833,19 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2674252389954578</v>
+        <v>0.2626349690698471</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5883,25 +5861,25 @@
         <v>10</v>
       </c>
       <c r="J49" t="n">
-        <v>24.46536626635938</v>
+        <v>24.14896896188847</v>
       </c>
       <c r="K49" t="n">
-        <v>5.83043790098341</v>
+        <v>3.934744114579414</v>
       </c>
       <c r="L49" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M49" t="n">
-        <v>53.33333333333334</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N49" t="n">
-        <v>12.38347478478886</v>
+        <v>11.28436287108054</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.024927606735848</v>
       </c>
       <c r="Q49" t="n">
         <v>53</v>
@@ -5910,10 +5888,10 @@
         <v>73.58490566037736</v>
       </c>
       <c r="S49" t="n">
-        <v>38.25740629602495</v>
+        <v>38.35174591866646</v>
       </c>
       <c r="T49" t="n">
-        <v>35.32749936435241</v>
+        <v>35.2331597417109</v>
       </c>
       <c r="U49" t="n">
         <v>60.41933558938148</v>
@@ -5942,10 +5920,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="AG49" t="n">
-        <v>34.77726740496033</v>
+        <v>34.86482632230648</v>
       </c>
       <c r="AH49" t="n">
-        <v>26.92486025461414</v>
+        <v>26.83730133726798</v>
       </c>
       <c r="AI49" t="n">
         <v>47.42656695641357</v>
@@ -5964,10 +5942,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7275818430171396</v>
+        <v>0.7258734523662211</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5995,22 +5973,22 @@
         <v>11.86078125763058</v>
       </c>
       <c r="K50" t="n">
-        <v>1.830163658490802</v>
+        <v>1.591062447753799</v>
       </c>
       <c r="L50" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M50" t="n">
-        <v>47.61904761904762</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="N50" t="n">
-        <v>13.63160196619841</v>
+        <v>13.16142843703877</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>2.130838509487432</v>
+        <v>2.371210118493505</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6073,10 +6051,10 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1815798453724928</v>
+        <v>0.1827300090422888</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6095,7 +6073,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -6108,16 +6086,16 @@
         <v>27.30972539236674</v>
       </c>
       <c r="K51" t="n">
-        <v>5.243898734040586</v>
+        <v>5.910534992834959</v>
       </c>
       <c r="L51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M51" t="n">
-        <v>83.33333333333333</v>
+        <v>75</v>
       </c>
       <c r="N51" t="n">
-        <v>16.77127889385772</v>
+        <v>22.94220322121633</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
@@ -6150,7 +6128,7 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>17.56903521173489</v>
+        <v>17.04690071618444</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6192,10 +6170,10 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C52" t="n">
-        <v>4.121841268532068</v>
+        <v>4.138235681807588</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6255,22 +6233,22 @@
         <v>12.1710603868542</v>
       </c>
       <c r="Y52" t="n">
-        <v>5.424680318296627</v>
+        <v>5.048511811187062</v>
       </c>
       <c r="Z52" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA52" t="n">
-        <v>56</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="AB52" t="n">
-        <v>13.70881130418631</v>
+        <v>13.74275314443207</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.723035661281081</v>
+        <v>3.108416987571427</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6279,10 +6257,10 @@
         <v>68.42105263157895</v>
       </c>
       <c r="AG52" t="n">
-        <v>36.35958718278081</v>
+        <v>35.82556534658112</v>
       </c>
       <c r="AH52" t="n">
-        <v>32.06146544879813</v>
+        <v>32.59548728499783</v>
       </c>
       <c r="AI52" t="n">
         <v>52.54424010939046</v>
@@ -6301,10 +6279,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C53" t="n">
-        <v>1.538063296607775</v>
+        <v>1.561300785631331</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6329,25 +6307,25 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>28.81930187887606</v>
+        <v>28.17598592067425</v>
       </c>
       <c r="K53" t="n">
-        <v>1.386962581443174</v>
+        <v>2.933465455497863</v>
       </c>
       <c r="L53" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M53" t="n">
-        <v>66.66666666666667</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N53" t="n">
-        <v>13.05014890266504</v>
+        <v>17.02235577422501</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>6.522571788502529</v>
+        <v>4.922145117801957</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6402,19 +6380,19 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C54" t="n">
-        <v>0.09047431745651388</v>
+        <v>0.08810572909728384</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6433,18 +6411,22 @@
         <v>42.39442432818535</v>
       </c>
       <c r="K54" t="n">
-        <v>11.93161513564749</v>
+        <v>9.001281665405614</v>
       </c>
       <c r="L54" t="n">
-        <v>2</v>
-      </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M54" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="N54" t="n">
+        <v>25.55854552237183</v>
+      </c>
       <c r="O54" t="n">
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>0.9162445792702645</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6462,16 +6444,16 @@
         <v>35.42021355803963</v>
       </c>
       <c r="V54" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="W54" t="n">
-        <v>71.15384615384616</v>
+        <v>69.81132075471699</v>
       </c>
       <c r="X54" t="n">
         <v>114.7400208810756</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.52114874235025</v>
+        <v>37.20918420698695</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -6513,10 +6495,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8576122940893759</v>
+        <v>0.8478336322242699</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6541,25 +6523,25 @@
         <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>11.94085328596284</v>
+        <v>12.34658621941707</v>
       </c>
       <c r="K55" t="n">
-        <v>1.798195263378144</v>
+        <v>1.103306439805984</v>
       </c>
       <c r="L55" t="n">
         <v>79</v>
       </c>
       <c r="M55" t="n">
-        <v>62.0253164556962</v>
+        <v>64.55696202531645</v>
       </c>
       <c r="N55" t="n">
-        <v>15.15093636570434</v>
+        <v>15.77836033789633</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>4.127582739311553</v>
+        <v>4.843257587336547</v>
       </c>
       <c r="Q55" t="n">
         <v>44</v>
@@ -6586,16 +6568,16 @@
         <v>25.41488056506582</v>
       </c>
       <c r="Y55" t="n">
-        <v>10.35737788077981</v>
+        <v>11.37950046046611</v>
       </c>
       <c r="Z55" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA55" t="n">
-        <v>53.84615384615385</v>
+        <v>50</v>
       </c>
       <c r="AB55" t="n">
-        <v>8.985280448705707</v>
+        <v>9.686169325397467</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6604,25 +6586,25 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF55" t="n">
-        <v>53.19148936170212</v>
+        <v>54.16666666666666</v>
       </c>
       <c r="AG55" t="n">
-        <v>40.70451402354052</v>
+        <v>41.10326832506873</v>
       </c>
       <c r="AH55" t="n">
-        <v>12.48697533816161</v>
+        <v>13.06339834159793</v>
       </c>
       <c r="AI55" t="n">
-        <v>39.23238322019481</v>
+        <v>40.2910745456498</v>
       </c>
       <c r="AJ55" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AK55" t="n">
-        <v>54.28571428571428</v>
+        <v>54.92957746478874</v>
       </c>
     </row>
     <row r="56">
@@ -6632,24 +6614,24 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9211547285693282</v>
+        <v>0.7839096482632872</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -6660,13 +6642,13 @@
         <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>30.29575178666553</v>
+        <v>34.40959858154028</v>
       </c>
       <c r="K56" t="n">
-        <v>10.57262436233963</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
@@ -6674,7 +6656,7 @@
         <v>4</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>4.000000000000004</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -6684,32 +6666,22 @@
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W56" t="n">
         <v>100</v>
       </c>
-      <c r="X56" t="n">
-        <v>21.48339906035102</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>8.981288622481742</v>
-      </c>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>17.32231848970716</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
         <v>10</v>
       </c>
-      <c r="AD56" t="n">
-        <v>1.119232916068158</v>
-      </c>
+      <c r="AD56" t="inlineStr"/>
       <c r="AE56" t="n">
         <v>0</v>
       </c>
@@ -6718,10 +6690,10 @@
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="inlineStr"/>
       <c r="AJ56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK56" t="n">
-        <v>50</v>
+        <v>33.33333333333334</v>
       </c>
     </row>
     <row r="57">
@@ -6731,10 +6703,10 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C57" t="n">
-        <v>1.398143686835204</v>
+        <v>1.368898030381272</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6751,11 +6723,7 @@
           <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %100.00: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>5</v>
       </c>
@@ -6766,13 +6734,17 @@
         <v>32.76213282665623</v>
       </c>
       <c r="K57" t="n">
-        <v>19.71916290066553</v>
+        <v>17.21493851935709</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M57" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="N57" t="n">
+        <v>17.10890341118185</v>
+      </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
@@ -6804,17 +6776,13 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>13.80366902045174</v>
+        <v>15.60667990349154</v>
       </c>
       <c r="Z57" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>11.48120296715095</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
         <v>6</v>
       </c>
@@ -6850,10 +6818,10 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7528304244599112</v>
+        <v>0.7712931084304441</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6872,7 +6840,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %91.89: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %84.62: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -6882,25 +6850,25 @@
         <v>10</v>
       </c>
       <c r="J58" t="n">
-        <v>16.32495356085277</v>
+        <v>16.33691982084211</v>
       </c>
       <c r="K58" t="n">
-        <v>1.474760308496803</v>
+        <v>3.978233602764591</v>
       </c>
       <c r="L58" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="M58" t="n">
-        <v>91.89189189189189</v>
+        <v>84.61538461538461</v>
       </c>
       <c r="N58" t="n">
-        <v>18.72122528472824</v>
+        <v>20.44222564624019</v>
       </c>
       <c r="O58" t="n">
         <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>3.474006423652543</v>
+        <v>0.9826733555976075</v>
       </c>
       <c r="Q58" t="n">
         <v>24</v>
@@ -6927,7 +6895,7 @@
         <v>41.32985472592288</v>
       </c>
       <c r="Y58" t="n">
-        <v>15.09094718785197</v>
+        <v>13.00860705204698</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -6969,10 +6937,10 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8104815339654904</v>
+        <v>0.8091428082544818</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6981,7 +6949,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6989,34 +6957,28 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H59" t="n">
         <v>5</v>
       </c>
       <c r="I59" t="n">
         <v>10</v>
       </c>
-      <c r="J59" t="n">
-        <v>12.06710605756499</v>
-      </c>
-      <c r="K59" t="n">
-        <v>1.457613065536556</v>
-      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="n">
-        <v>64</v>
-      </c>
-      <c r="M59" t="n">
-        <v>60.9375</v>
-      </c>
-      <c r="N59" t="n">
-        <v>14.3457197144375</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="n">
         <v>8</v>
       </c>
-      <c r="P59" t="n">
-        <v>6.448394296677762</v>
-      </c>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="n">
         <v>45</v>
       </c>
@@ -7042,13 +7004,13 @@
         <v>10.2478061424703</v>
       </c>
       <c r="Y59" t="n">
-        <v>7.97312289876716</v>
+        <v>8.125129750640102</v>
       </c>
       <c r="Z59" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA59" t="n">
-        <v>70.58823529411765</v>
+        <v>75</v>
       </c>
       <c r="AB59" t="n">
         <v>13.8254719095032</v>
@@ -7088,10 +7050,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C60" t="n">
-        <v>12.85576872635672</v>
+        <v>12.83736201519095</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7119,22 +7081,22 @@
         <v>17.06238107085701</v>
       </c>
       <c r="K60" t="n">
-        <v>1.17349761866139</v>
+        <v>1.028638809519911</v>
       </c>
       <c r="L60" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M60" t="n">
-        <v>55.81395348837209</v>
+        <v>56.09756097560975</v>
       </c>
       <c r="N60" t="n">
-        <v>13.84009050337867</v>
+        <v>12.75109754658648</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>6.747322710013215</v>
+        <v>6.900381191539107</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7197,10 +7159,10 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6295328990524627</v>
+        <v>0.6304080381822081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7219,7 +7181,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -7229,25 +7191,25 @@
         <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>39.02052765309554</v>
+        <v>36.10328933244122</v>
       </c>
       <c r="K61" t="n">
-        <v>1.644099127940324</v>
+        <v>1.785398698762553</v>
       </c>
       <c r="L61" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M61" t="n">
-        <v>83.33333333333333</v>
+        <v>75</v>
       </c>
       <c r="N61" t="n">
-        <v>25.04311802372403</v>
+        <v>19.46927000780446</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>8.220743696633125</v>
+        <v>8.07051051158021</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7302,10 +7264,10 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C62" t="n">
-        <v>8.447776012491365</v>
+        <v>8.447846338415992</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7330,25 +7292,25 @@
         <v>10</v>
       </c>
       <c r="J62" t="n">
-        <v>15.79076798430271</v>
+        <v>14.45999953470718</v>
       </c>
       <c r="K62" t="n">
-        <v>1.525547377311898</v>
+        <v>1.526392555733058</v>
       </c>
       <c r="L62" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="M62" t="n">
-        <v>63.46153846153846</v>
+        <v>55.93220338983051</v>
       </c>
       <c r="N62" t="n">
-        <v>14.29118651923218</v>
+        <v>14.85340212793895</v>
       </c>
       <c r="O62" t="n">
         <v>6</v>
       </c>
       <c r="P62" t="n">
-        <v>4.407218417704417</v>
+        <v>4.406349257225073</v>
       </c>
       <c r="Q62" t="n">
         <v>29</v>
@@ -7411,24 +7373,24 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1020466072622803</v>
+        <v>0.1070305889974221</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -7439,25 +7401,21 @@
         <v>10</v>
       </c>
       <c r="J63" t="n">
-        <v>33.30512547687425</v>
+        <v>33.28434552774222</v>
       </c>
       <c r="K63" t="n">
-        <v>2.264914438761978</v>
+        <v>7.259558350819129</v>
       </c>
       <c r="L63" t="n">
-        <v>3</v>
-      </c>
-      <c r="M63" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N63" t="n">
-        <v>10.8811033182065</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>2.674510193694868</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7480,17 +7438,27 @@
       <c r="W63" t="n">
         <v>66.66666666666667</v>
       </c>
-      <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
+      <c r="X63" t="n">
+        <v>10.20972019420772</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>2.676861748845671</v>
+      </c>
       <c r="Z63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA63" t="inlineStr"/>
-      <c r="AB63" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>64.28571428571429</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>11.24234270242617</v>
+      </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
-      <c r="AD63" t="inlineStr"/>
+      <c r="AD63" t="n">
+        <v>7.524560328352814</v>
+      </c>
       <c r="AE63" t="n">
         <v>1</v>
       </c>
@@ -7520,10 +7488,10 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C64" t="n">
-        <v>0.163695390164921</v>
+        <v>0.1612818471474259</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7548,25 +7516,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>21.89035128217772</v>
+        <v>22.40226642575713</v>
       </c>
       <c r="K64" t="n">
-        <v>0.2577316933919604</v>
+        <v>0.3926729124407835</v>
       </c>
       <c r="L64" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M64" t="n">
-        <v>62.5</v>
+        <v>63.88888888888889</v>
       </c>
       <c r="N64" t="n">
-        <v>15.58003045770035</v>
+        <v>16.19270505080708</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.730077398031352</v>
+        <v>4.589306125535253</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7575,10 +7543,10 @@
         <v>70.37037037037037</v>
       </c>
       <c r="S64" t="n">
-        <v>73.86269274864564</v>
+        <v>73.98949442717146</v>
       </c>
       <c r="T64" t="n">
-        <v>-3.492322378275276</v>
+        <v>-3.619124056801098</v>
       </c>
       <c r="U64" t="n">
         <v>57.17242709884697</v>
@@ -7607,10 +7575,10 @@
         <v>59.25925925925926</v>
       </c>
       <c r="AG64" t="n">
-        <v>37.92255864916446</v>
+        <v>38.6780251892314</v>
       </c>
       <c r="AH64" t="n">
-        <v>21.33670061009479</v>
+        <v>20.58123407002786</v>
       </c>
       <c r="AI64" t="n">
         <v>45.96684934349057</v>
@@ -7629,10 +7597,10 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C65" t="n">
-        <v>6.185918176021075</v>
+        <v>6.234689332521074</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7651,7 +7619,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %82.35: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -7661,25 +7629,25 @@
         <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>28.1135336713357</v>
+        <v>28.12381406175567</v>
       </c>
       <c r="K65" t="n">
-        <v>1.906412478336228</v>
+        <v>2.724555834461184</v>
       </c>
       <c r="L65" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M65" t="n">
-        <v>82.35294117647059</v>
+        <v>81.25</v>
       </c>
       <c r="N65" t="n">
-        <v>15.35336073609163</v>
+        <v>14.72106682780091</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>7.942176870748296</v>
+        <v>7.082478095367062</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7688,10 +7656,10 @@
         <v>68</v>
       </c>
       <c r="S65" t="n">
-        <v>45.47819350785525</v>
+        <v>45.53332171298345</v>
       </c>
       <c r="T65" t="n">
-        <v>22.52180649214475</v>
+        <v>22.46667828701655</v>
       </c>
       <c r="U65" t="n">
         <v>54.18970269185592</v>
@@ -7742,19 +7710,19 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4283853667931945</v>
+        <v>0.4314867722471822</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7769,47 +7737,37 @@
       <c r="I66" t="n">
         <v>10</v>
       </c>
-      <c r="J66" t="n">
-        <v>11.2547528069613</v>
-      </c>
-      <c r="K66" t="n">
-        <v>2.669684735156141</v>
-      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="n">
-        <v>54</v>
-      </c>
-      <c r="M66" t="n">
-        <v>53.7037037037037</v>
-      </c>
-      <c r="N66" t="n">
-        <v>17.63499988006323</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
         <v>6</v>
       </c>
-      <c r="P66" t="n">
-        <v>3.243718214811553</v>
-      </c>
+      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R66" t="n">
-        <v>60</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="S66" t="n">
-        <v>24.72850398572462</v>
+        <v>24.52771220834338</v>
       </c>
       <c r="T66" t="n">
-        <v>35.27149601427539</v>
+        <v>33.80562112498995</v>
       </c>
       <c r="U66" t="n">
-        <v>43.5727090128925</v>
+        <v>42.20025157487166</v>
       </c>
       <c r="V66" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="W66" t="n">
-        <v>66.66666666666667</v>
+        <v>65.71428571428571</v>
       </c>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
@@ -7851,10 +7809,10 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02714229319602197</v>
+        <v>0.02712562896986379</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7879,7 +7837,7 @@
         <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>19.80495045311466</v>
+        <v>18.7880380179217</v>
       </c>
       <c r="K67" t="n">
         <v>0.7812492370605328</v>
@@ -7940,10 +7898,10 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C68" t="n">
-        <v>3.372798307766084</v>
+        <v>3.625161561197397</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8000,13 +7958,13 @@
         <v>80</v>
       </c>
       <c r="X68" t="n">
-        <v>88.17007952573587</v>
+        <v>107.0594361964295</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2.322949631728055</v>
       </c>
       <c r="Z68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="inlineStr"/>
       <c r="AB68" t="inlineStr"/>
@@ -8014,7 +7972,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>7.999999999999996</v>
+        <v>5.812061632561328</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8045,10 +8003,10 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C69" t="n">
-        <v>0.3953517286342882</v>
+        <v>0.3984734151421189</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8067,7 +8025,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %90.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H69" t="n">
@@ -8080,22 +8038,22 @@
         <v>29.4573350207784</v>
       </c>
       <c r="K69" t="n">
-        <v>1.129568724269925</v>
+        <v>1.928085051287987</v>
       </c>
       <c r="L69" t="n">
         <v>10</v>
       </c>
       <c r="M69" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="N69" t="n">
-        <v>16.18279183771334</v>
+        <v>16.55531405137488</v>
       </c>
       <c r="O69" t="n">
         <v>3</v>
       </c>
       <c r="P69" t="n">
-        <v>1.849539456486582</v>
+        <v>1.051638464680904</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8142,10 +8100,10 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C70" t="n">
-        <v>0.3959829188948367</v>
+        <v>0.4054125282729914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8170,25 +8128,25 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>20.65851193457618</v>
+        <v>20.66985845799666</v>
       </c>
       <c r="K70" t="n">
-        <v>1.565024226666645</v>
+        <v>3.998482311486296</v>
       </c>
       <c r="L70" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="M70" t="n">
-        <v>64.51612903225806</v>
+        <v>40.90909090909091</v>
       </c>
       <c r="N70" t="n">
-        <v>13.66554107566214</v>
+        <v>12.02462524087466</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>6.335818676094807</v>
+        <v>3.847669311681634</v>
       </c>
       <c r="Q70" t="n">
         <v>30</v>
@@ -8229,10 +8187,10 @@
         <v>48.83720930232558</v>
       </c>
       <c r="AG70" t="n">
-        <v>34.90792638477132</v>
+        <v>34.79867517086895</v>
       </c>
       <c r="AH70" t="n">
-        <v>13.92928291755426</v>
+        <v>14.03853413145664</v>
       </c>
       <c r="AI70" t="n">
         <v>34.61744754671859</v>
@@ -8251,10 +8209,10 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C71" t="n">
-        <v>3.286531973562727</v>
+        <v>3.309747261069855</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8279,25 +8237,25 @@
         <v>10</v>
       </c>
       <c r="J71" t="n">
-        <v>21.33797260620418</v>
+        <v>20.51701021225919</v>
       </c>
       <c r="K71" t="n">
-        <v>4.907452098561182</v>
+        <v>5.648493622483541</v>
       </c>
       <c r="L71" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M71" t="n">
-        <v>60</v>
+        <v>72.41379310344827</v>
       </c>
       <c r="N71" t="n">
-        <v>11.55469196476905</v>
+        <v>12.00056970406572</v>
       </c>
       <c r="O71" t="n">
         <v>6</v>
       </c>
       <c r="P71" t="n">
-        <v>1.041439744826111</v>
+        <v>0.3327130993201921</v>
       </c>
       <c r="Q71" t="n">
         <v>43</v>
@@ -8338,10 +8296,10 @@
         <v>54.83870967741935</v>
       </c>
       <c r="AG71" t="n">
-        <v>14.78870579909084</v>
+        <v>14.81145187022401</v>
       </c>
       <c r="AH71" t="n">
-        <v>40.05000387832852</v>
+        <v>40.02725780719535</v>
       </c>
       <c r="AI71" t="n">
         <v>37.77216763735451</v>
@@ -8360,10 +8318,10 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07511471923598968</v>
+        <v>0.07548915393803918</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8388,16 +8346,20 @@
         <v>10</v>
       </c>
       <c r="J72" t="n">
-        <v>29.15235727667785</v>
+        <v>20.36571476939619</v>
       </c>
       <c r="K72" t="n">
-        <v>15.33924707924528</v>
+        <v>5.538495734182591</v>
       </c>
       <c r="L72" t="n">
-        <v>2</v>
-      </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="M72" t="n">
+        <v>50</v>
+      </c>
+      <c r="N72" t="n">
+        <v>13.54970683032341</v>
+      </c>
       <c r="O72" t="n">
         <v>5</v>
       </c>
@@ -8429,7 +8391,7 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>16.37204508119735</v>
+        <v>15.95517327895241</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -8471,10 +8433,10 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07090661079163273</v>
+        <v>0.07065280112580734</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8499,10 +8461,10 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>20.57324828822117</v>
+        <v>20.48362439310756</v>
       </c>
       <c r="K73" t="n">
-        <v>0.898203018215038</v>
+        <v>0.5988021119437636</v>
       </c>
       <c r="L73" t="n">
         <v>26</v>
@@ -8511,34 +8473,34 @@
         <v>73.07692307692308</v>
       </c>
       <c r="N73" t="n">
-        <v>14.93643632280392</v>
+        <v>14.86908195608804</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>9.020772134209199</v>
+        <v>9.345238403132106</v>
       </c>
       <c r="Q73" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R73" t="n">
-        <v>83.33333333333333</v>
+        <v>84.61538461538461</v>
       </c>
       <c r="S73" t="n">
-        <v>52.60146630285622</v>
+        <v>51.51377954583177</v>
       </c>
       <c r="T73" t="n">
-        <v>30.73186703047711</v>
+        <v>33.10160506955284</v>
       </c>
       <c r="U73" t="n">
-        <v>55.19691377470266</v>
+        <v>57.76536898051745</v>
       </c>
       <c r="V73" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W73" t="n">
-        <v>76.19047619047619</v>
+        <v>77.27272727272727</v>
       </c>
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
@@ -8580,10 +8542,10 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C74" t="n">
-        <v>4.927693938629543</v>
+        <v>4.809016631810345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8608,25 +8570,25 @@
         <v>10</v>
       </c>
       <c r="J74" t="n">
-        <v>17.41018086324394</v>
+        <v>18.27906859558925</v>
       </c>
       <c r="K74" t="n">
-        <v>3.057091169424031</v>
+        <v>1.644443088888914</v>
       </c>
       <c r="L74" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="M74" t="n">
-        <v>62.7906976744186</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N74" t="n">
-        <v>20.67372893071872</v>
+        <v>22.85638561467399</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>4.796282113619843</v>
+        <v>6.252734254791581</v>
       </c>
       <c r="Q74" t="n">
         <v>35</v>
@@ -8653,7 +8615,7 @@
         <v>95.98093909010421</v>
       </c>
       <c r="Y74" t="n">
-        <v>14.88533479557089</v>
+        <v>16.93521438693378</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -8695,14 +8657,14 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1407612005739323</v>
+        <v>0.1478241730755747</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -8712,7 +8674,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -8726,10 +8688,10 @@
         <v>19.1703426786477</v>
       </c>
       <c r="K75" t="n">
-        <v>8.018643404261528</v>
+        <v>13.43869314039821</v>
       </c>
       <c r="L75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
@@ -8760,17 +8722,27 @@
       <c r="W75" t="n">
         <v>100</v>
       </c>
-      <c r="X75" t="inlineStr"/>
-      <c r="Y75" t="inlineStr"/>
+      <c r="X75" t="n">
+        <v>14.084147344171</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.565770283425604</v>
+      </c>
       <c r="Z75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA75" t="inlineStr"/>
-      <c r="AB75" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>53.33333333333334</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>12.1869143909037</v>
+      </c>
       <c r="AC75" t="n">
         <v>10</v>
       </c>
-      <c r="AD75" t="inlineStr"/>
+      <c r="AD75" t="n">
+        <v>9.487909488981373</v>
+      </c>
       <c r="AE75" t="n">
         <v>4</v>
       </c>
@@ -8800,10 +8772,10 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C76" t="n">
-        <v>1.818954447108747</v>
+        <v>1.816786400906899</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8828,25 +8800,25 @@
         <v>10</v>
       </c>
       <c r="J76" t="n">
-        <v>21.37762355327298</v>
+        <v>20.88959101184773</v>
       </c>
       <c r="K76" t="n">
-        <v>4.94965969092438</v>
+        <v>4.824568206945878</v>
       </c>
       <c r="L76" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M76" t="n">
-        <v>66.66666666666667</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="N76" t="n">
-        <v>11.96395971167433</v>
+        <v>11.67635417336743</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>4.812155012173291</v>
+        <v>4.937231682974108</v>
       </c>
       <c r="Q76" t="n">
         <v>42</v>
@@ -8855,10 +8827,10 @@
         <v>64.28571428571429</v>
       </c>
       <c r="S76" t="n">
-        <v>29.26507262252812</v>
+        <v>29.74204478885298</v>
       </c>
       <c r="T76" t="n">
-        <v>35.02064166318617</v>
+        <v>34.54366949686131</v>
       </c>
       <c r="U76" t="n">
         <v>49.16636571945582</v>
@@ -8909,10 +8881,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5066561536861022</v>
+        <v>0.5059245262599383</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8937,19 +8909,19 @@
         <v>10</v>
       </c>
       <c r="J77" t="n">
-        <v>22.11886481778794</v>
+        <v>21.60005234598619</v>
       </c>
       <c r="K77" t="n">
-        <v>4.348893094281991</v>
+        <v>4.19821000966496</v>
       </c>
       <c r="L77" t="n">
         <v>24</v>
       </c>
       <c r="M77" t="n">
-        <v>66.66666666666667</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N77" t="n">
-        <v>15.56210585085078</v>
+        <v>16.78554035367463</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -8964,19 +8936,19 @@
         <v>57.14285714285715</v>
       </c>
       <c r="S77" t="n">
-        <v>39.11478618000358</v>
+        <v>39.18919094190834</v>
       </c>
       <c r="T77" t="n">
-        <v>18.02807096285357</v>
+        <v>17.95366620094881</v>
       </c>
       <c r="U77" t="n">
         <v>39.07078562746877</v>
       </c>
       <c r="V77" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W77" t="n">
-        <v>61.03896103896104</v>
+        <v>61.8421052631579</v>
       </c>
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
@@ -8996,19 +8968,19 @@
         <v>50</v>
       </c>
       <c r="AG77" t="n">
-        <v>25.49777093285068</v>
+        <v>25.56139577050298</v>
       </c>
       <c r="AH77" t="n">
-        <v>24.50222906714932</v>
+        <v>24.43860422949702</v>
       </c>
       <c r="AI77" t="n">
         <v>36.11893708270325</v>
       </c>
       <c r="AJ77" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK77" t="n">
-        <v>45.78313253012048</v>
+        <v>45.1219512195122</v>
       </c>
     </row>
     <row r="78">
@@ -9018,10 +8990,10 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05344296571311838</v>
+        <v>0.05319987799068343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9038,11 +9010,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>5</v>
       </c>
@@ -9050,19 +9018,19 @@
         <v>10</v>
       </c>
       <c r="J78" t="n">
-        <v>20.92476038411055</v>
+        <v>20.32485186011925</v>
       </c>
       <c r="K78" t="n">
-        <v>13.33801691329652</v>
+        <v>12.82249386869903</v>
       </c>
       <c r="L78" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M78" t="n">
-        <v>83.33333333333333</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N78" t="n">
-        <v>16.75776347050931</v>
+        <v>16.51077214169325</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
@@ -9095,22 +9063,22 @@
         <v>23.16536029857119</v>
       </c>
       <c r="Y78" t="n">
-        <v>7.978983182813504</v>
+        <v>8.397544898013132</v>
       </c>
       <c r="Z78" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA78" t="n">
-        <v>50</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="AB78" t="n">
-        <v>15.27678857792912</v>
+        <v>15.78157380146375</v>
       </c>
       <c r="AC78" t="n">
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>2.196255689286231</v>
+        <v>1.749358246132982</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9141,10 +9109,10 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8845442374522813</v>
+        <v>0.8886271862329258</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9169,25 +9137,25 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>14.97695523729659</v>
+        <v>12.92020537241256</v>
       </c>
       <c r="K79" t="n">
-        <v>2.430739056287079</v>
+        <v>2.903546908537602</v>
       </c>
       <c r="L79" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="M79" t="n">
-        <v>46.93877551020408</v>
+        <v>46.55172413793103</v>
       </c>
       <c r="N79" t="n">
-        <v>12.10364544634033</v>
+        <v>10.20772267382851</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>2.508290936279467</v>
+        <v>2.037299154834549</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9228,10 +9196,10 @@
         <v>55.26315789473684</v>
       </c>
       <c r="AG79" t="n">
-        <v>26.48329601014137</v>
+        <v>26.54908548382558</v>
       </c>
       <c r="AH79" t="n">
-        <v>28.77986188459547</v>
+        <v>28.71407241091126</v>
       </c>
       <c r="AI79" t="n">
         <v>39.70629712199248</v>
@@ -9250,24 +9218,24 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1346594453915874</v>
+        <v>0.1341562179672859</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AL_BEKLE_EŞİK</t>
-        </is>
-      </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -9278,10 +9246,10 @@
         <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>68.88091801192056</v>
+        <v>68.88536831152055</v>
       </c>
       <c r="K80" t="n">
-        <v>1.910826209988303</v>
+        <v>1.544503358116223</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9292,7 +9260,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>7.937501922851542</v>
+        <v>8.326887583529619</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9315,31 +9283,41 @@
       <c r="W80" t="n">
         <v>75.9493670886076</v>
       </c>
-      <c r="X80" t="inlineStr"/>
-      <c r="Y80" t="inlineStr"/>
+      <c r="X80" t="n">
+        <v>10.5095514001583</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>8.11246442362199</v>
+      </c>
       <c r="Z80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA80" t="inlineStr"/>
-      <c r="AB80" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>57.89473684210526</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>10.08160658985287</v>
+      </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
-      <c r="AD80" t="inlineStr"/>
+      <c r="AD80" t="n">
+        <v>0</v>
+      </c>
       <c r="AE80" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AF80" t="n">
-        <v>46.42857142857143</v>
+        <v>50</v>
       </c>
       <c r="AG80" t="n">
-        <v>38.12750883933075</v>
+        <v>39.74534888579511</v>
       </c>
       <c r="AH80" t="n">
-        <v>8.301062589240679</v>
+        <v>10.25465111420489</v>
       </c>
       <c r="AI80" t="n">
-        <v>29.53156998279538</v>
+        <v>32.06059352575905</v>
       </c>
       <c r="AJ80" t="n">
         <v>72</v>
@@ -9355,10 +9333,10 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C81" t="n">
-        <v>1.054130922293201</v>
+        <v>1.060843445409956</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9383,25 +9361,25 @@
         <v>10</v>
       </c>
       <c r="J81" t="n">
-        <v>11.75504511642799</v>
+        <v>11.87985607284572</v>
       </c>
       <c r="K81" t="n">
-        <v>0.3203841497582349</v>
+        <v>1.102202831936472</v>
       </c>
       <c r="L81" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="M81" t="n">
-        <v>53.33333333333334</v>
+        <v>51.92307692307692</v>
       </c>
       <c r="N81" t="n">
-        <v>10.94116300280899</v>
+        <v>12.31903901763035</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>9.648702935379561</v>
+        <v>8.800794561177327</v>
       </c>
       <c r="Q81" t="n">
         <v>31</v>
@@ -9428,13 +9406,13 @@
         <v>27.31228182970742</v>
       </c>
       <c r="Y81" t="n">
-        <v>11.47232226801971</v>
+        <v>10.90859335097414</v>
       </c>
       <c r="Z81" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA81" t="n">
-        <v>50</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB81" t="n">
         <v>9.529724010146259</v>
@@ -9474,10 +9452,10 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C82" t="n">
-        <v>5.135995457485868</v>
+        <v>5.130739282074678</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9494,7 +9472,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H82" t="n">
         <v>5</v>
       </c>
@@ -9502,16 +9484,20 @@
         <v>10</v>
       </c>
       <c r="J82" t="n">
-        <v>17.26584051182517</v>
+        <v>15.23084223335499</v>
       </c>
       <c r="K82" t="n">
-        <v>12.97422286478676</v>
+        <v>12.85860509657892</v>
       </c>
       <c r="L82" t="n">
-        <v>2</v>
-      </c>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M82" t="n">
+        <v>80</v>
+      </c>
+      <c r="N82" t="n">
+        <v>8.430896867829917</v>
+      </c>
       <c r="O82" t="n">
         <v>4</v>
       </c>
@@ -9543,7 +9529,7 @@
         <v>15.04024401260009</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.795911652957749</v>
+        <v>1.896413672229535</v>
       </c>
       <c r="Z82" t="n">
         <v>12</v>
@@ -9558,7 +9544,7 @@
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>2.24439571115741</v>
+        <v>2.144250181376905</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9589,10 +9575,10 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C83" t="n">
-        <v>5.85452970230566</v>
+        <v>5.850935267365898</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9617,25 +9603,25 @@
         <v>10</v>
       </c>
       <c r="J83" t="n">
-        <v>15.63345941387357</v>
+        <v>14.0949513048101</v>
       </c>
       <c r="K83" t="n">
-        <v>8.171001277525258</v>
+        <v>8.104588833446646</v>
       </c>
       <c r="L83" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M83" t="n">
-        <v>61.29032258064516</v>
+        <v>60</v>
       </c>
       <c r="N83" t="n">
-        <v>10.87572382585771</v>
+        <v>11.46594952641528</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>1.690840152049855</v>
+        <v>1.753312405150131</v>
       </c>
       <c r="Q83" t="n">
         <v>44</v>
@@ -9644,10 +9630,10 @@
         <v>63.63636363636363</v>
       </c>
       <c r="S83" t="n">
-        <v>55.17171937866284</v>
+        <v>54.36087535210635</v>
       </c>
       <c r="T83" t="n">
-        <v>8.464644257700797</v>
+        <v>9.275488284257278</v>
       </c>
       <c r="U83" t="n">
         <v>48.86637687904344</v>
@@ -9698,10 +9684,10 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C84" t="n">
-        <v>2.200840244038604</v>
+        <v>2.199489020717132</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9726,19 +9712,19 @@
         <v>10</v>
       </c>
       <c r="J84" t="n">
-        <v>15.40292259784146</v>
+        <v>14.10735630446007</v>
       </c>
       <c r="K84" t="n">
-        <v>5.359838061381406</v>
+        <v>5.29515155325313</v>
       </c>
       <c r="L84" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="M84" t="n">
-        <v>69.6969696969697</v>
+        <v>65.85365853658537</v>
       </c>
       <c r="N84" t="n">
-        <v>10.76769305697522</v>
+        <v>11.13597975333524</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
@@ -9807,10 +9793,10 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C85" t="n">
-        <v>6.711931626363003</v>
+        <v>6.686783162703883</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9838,22 +9824,22 @@
         <v>15.13449360257271</v>
       </c>
       <c r="K85" t="n">
-        <v>4.158378864921253</v>
+        <v>3.768115174601649</v>
       </c>
       <c r="L85" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="M85" t="n">
-        <v>56.09756097560975</v>
+        <v>50</v>
       </c>
       <c r="N85" t="n">
-        <v>13.1498215264233</v>
+        <v>14.0272000326463</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>3.688249737508675</v>
+        <v>4.07821306022349</v>
       </c>
       <c r="Q85" t="n">
         <v>34</v>
@@ -9862,10 +9848,10 @@
         <v>61.76470588235294</v>
       </c>
       <c r="S85" t="n">
-        <v>64.87048354695413</v>
+        <v>65.42887171084101</v>
       </c>
       <c r="T85" t="n">
-        <v>-3.105777664601192</v>
+        <v>-3.664165828488066</v>
       </c>
       <c r="U85" t="n">
         <v>45.0410173444307</v>
@@ -9894,10 +9880,10 @@
         <v>41.93548387096774</v>
       </c>
       <c r="AG85" t="n">
-        <v>22.41966956750239</v>
+        <v>22.56170152360549</v>
       </c>
       <c r="AH85" t="n">
-        <v>19.51581430346536</v>
+        <v>19.37378234736226</v>
       </c>
       <c r="AI85" t="n">
         <v>26.41554306731223</v>
@@ -9916,10 +9902,10 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C86" t="n">
-        <v>3.572683418896017</v>
+        <v>3.482174001676542</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9976,25 +9962,25 @@
         <v>68.35443037974683</v>
       </c>
       <c r="X86" t="n">
-        <v>39.96949805432428</v>
+        <v>39.94948119773951</v>
       </c>
       <c r="Y86" t="n">
-        <v>0.05885276844616039</v>
+        <v>2.576803005653405</v>
       </c>
       <c r="Z86" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA86" t="n">
-        <v>66.66666666666667</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB86" t="n">
-        <v>12.3031665129609</v>
+        <v>17.9558912884659</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>5.944645820193351</v>
+        <v>3.513739129855542</v>
       </c>
       <c r="AE86" t="n">
         <v>51</v>
@@ -10025,19 +10011,19 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C87" t="n">
-        <v>5.754587146740694</v>
+        <v>5.635402162278745</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -10045,11 +10031,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>5</v>
       </c>
@@ -10060,22 +10042,22 @@
         <v>29.54558799520699</v>
       </c>
       <c r="K87" t="n">
-        <v>5.949979005675399</v>
+        <v>3.755617137563405</v>
       </c>
       <c r="L87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M87" t="n">
-        <v>83.33333333333333</v>
+        <v>60</v>
       </c>
       <c r="N87" t="n">
-        <v>8.337490203764601</v>
+        <v>9.533690881227427</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>1.199340235032054</v>
       </c>
       <c r="Q87" t="n">
         <v>47</v>
@@ -10116,19 +10098,19 @@
         <v>53.19148936170212</v>
       </c>
       <c r="AG87" t="n">
-        <v>45.96992190329986</v>
+        <v>46.42511283856881</v>
       </c>
       <c r="AH87" t="n">
-        <v>7.221567458402262</v>
+        <v>6.76637652313331</v>
       </c>
       <c r="AI87" t="n">
         <v>39.23238322019481</v>
       </c>
       <c r="AJ87" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AK87" t="n">
-        <v>49.23076923076923</v>
+        <v>48.4375</v>
       </c>
     </row>
     <row r="88">
@@ -10138,10 +10120,10 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9447201890061261</v>
+        <v>0.9605416885069691</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10169,22 +10151,22 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>5.838514050186649</v>
+        <v>7.611021949035135</v>
       </c>
       <c r="L88" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="M88" t="n">
-        <v>70.37037037037037</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="N88" t="n">
-        <v>11.83803676381896</v>
+        <v>12.1999542095487</v>
       </c>
       <c r="O88" t="n">
         <v>10</v>
       </c>
       <c r="P88" t="n">
-        <v>3.931920234481057</v>
+        <v>2.220012418520012</v>
       </c>
       <c r="Q88" t="n">
         <v>44</v>
@@ -10247,10 +10229,10 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C89" t="n">
-        <v>1.918897002673713</v>
+        <v>1.949260310653967</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10278,16 +10260,16 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>4.231329036788645</v>
+        <v>5.880613985551109</v>
       </c>
       <c r="L89" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M89" t="n">
-        <v>63.63636363636363</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N89" t="n">
-        <v>13.75903325537547</v>
+        <v>13.55774842129218</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
@@ -10311,22 +10293,26 @@
         <v>54.89463582227039</v>
       </c>
       <c r="V89" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W89" t="n">
-        <v>75</v>
+        <v>75.82417582417582</v>
       </c>
       <c r="X89" t="n">
         <v>28.7873334490923</v>
       </c>
       <c r="Y89" t="n">
-        <v>16.31699162743037</v>
+        <v>14.99284918914936</v>
       </c>
       <c r="Z89" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA89" t="inlineStr"/>
-      <c r="AB89" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>36.07037617635147</v>
+      </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
@@ -10362,10 +10348,10 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C90" t="n">
-        <v>2.609026713695964</v>
+        <v>2.659993931075602</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10393,22 +10379,22 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>2.848482582462397</v>
+        <v>4.857622980078546</v>
       </c>
       <c r="L90" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="M90" t="n">
-        <v>64.91228070175438</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N90" t="n">
-        <v>14.67949900638165</v>
+        <v>14.51148757910913</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>5.008841441493517</v>
+        <v>2.996803599599485</v>
       </c>
       <c r="Q90" t="n">
         <v>42</v>
@@ -10435,13 +10421,17 @@
         <v>33.24184775233741</v>
       </c>
       <c r="Y90" t="n">
-        <v>14.21070309369433</v>
+        <v>12.53481310708858</v>
       </c>
       <c r="Z90" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA90" t="inlineStr"/>
-      <c r="AB90" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>10.631003022771</v>
+      </c>
       <c r="AC90" t="n">
         <v>3</v>
       </c>
@@ -10477,10 +10467,10 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2341811904066856</v>
+        <v>0.2348785171771856</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10505,19 +10495,19 @@
         <v>10</v>
       </c>
       <c r="J91" t="n">
-        <v>15.33687628212038</v>
+        <v>14.9000517126033</v>
       </c>
       <c r="K91" t="n">
-        <v>3.28629452669793</v>
+        <v>3.593852525161179</v>
       </c>
       <c r="L91" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M91" t="n">
-        <v>57.4468085106383</v>
+        <v>60.41666666666666</v>
       </c>
       <c r="N91" t="n">
-        <v>15.19244190628366</v>
+        <v>14.54651963345206</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
@@ -10532,10 +10522,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="S91" t="n">
-        <v>31.66621822688545</v>
+        <v>32.19411737547947</v>
       </c>
       <c r="T91" t="n">
-        <v>30.03590943268901</v>
+        <v>29.50801028409499</v>
       </c>
       <c r="U91" t="n">
         <v>47.42656695641357</v>
@@ -10586,10 +10576,10 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C92" t="n">
-        <v>1.111992401830813</v>
+        <v>1.10710422561993</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10614,25 +10604,25 @@
         <v>10</v>
       </c>
       <c r="J92" t="n">
-        <v>23.70319776773422</v>
+        <v>23.07989300517391</v>
       </c>
       <c r="K92" t="n">
-        <v>5.536856478094632</v>
+        <v>5.072929970720819</v>
       </c>
       <c r="L92" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="M92" t="n">
-        <v>57.14285714285715</v>
+        <v>65</v>
       </c>
       <c r="N92" t="n">
-        <v>13.96884097780217</v>
+        <v>14.6092261303582</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>2.333917840746591</v>
+        <v>2.785750840006873</v>
       </c>
       <c r="Q92" t="n">
         <v>56</v>
@@ -10673,10 +10663,10 @@
         <v>52.94117647058823</v>
       </c>
       <c r="AG92" t="n">
-        <v>40.29534387271291</v>
+        <v>40.31765720771973</v>
       </c>
       <c r="AH92" t="n">
-        <v>12.64583259787533</v>
+        <v>12.6235192628685</v>
       </c>
       <c r="AI92" t="n">
         <v>39.52330421009647</v>
@@ -10695,10 +10685,10 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04144986051816008</v>
+        <v>0.0416346880373879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10723,25 +10713,25 @@
         <v>10</v>
       </c>
       <c r="J93" t="n">
-        <v>20.51206701965846</v>
+        <v>19.49655531533526</v>
       </c>
       <c r="K93" t="n">
-        <v>0.5102035610162536</v>
+        <v>0.9728248348112922</v>
       </c>
       <c r="L93" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="M93" t="n">
-        <v>61.90476190476191</v>
+        <v>61.22448979591837</v>
       </c>
       <c r="N93" t="n">
-        <v>13.31844194410766</v>
+        <v>14.688601813055</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>5.461929480275196</v>
+        <v>4.978740738820608</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10804,10 +10794,10 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C94" t="n">
-        <v>6.117536427476624</v>
+        <v>6.176863377497692</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10835,22 +10825,22 @@
         <v>11.31569733043036</v>
       </c>
       <c r="K94" t="n">
-        <v>1.694328887126084</v>
+        <v>2.680545224182063</v>
       </c>
       <c r="L94" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M94" t="n">
-        <v>40.74074074074074</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="N94" t="n">
-        <v>12.70505029324409</v>
+        <v>11.46351092365998</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>6.200612346704992</v>
+        <v>5.180586803667619</v>
       </c>
       <c r="Q94" t="n">
         <v>40</v>
@@ -10877,7 +10867,7 @@
         <v>46.65531127586331</v>
       </c>
       <c r="Y94" t="n">
-        <v>9.813093571953523</v>
+        <v>8.938474490622051</v>
       </c>
       <c r="Z94" t="n">
         <v>2</v>
@@ -10906,10 +10896,10 @@
         <v>38.38404689217949</v>
       </c>
       <c r="AJ94" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AK94" t="n">
-        <v>58.92857142857143</v>
+        <v>58.18181818181818</v>
       </c>
     </row>
     <row r="95">
@@ -10919,10 +10909,10 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1390779590056758</v>
+        <v>0.1392028421432502</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10947,10 +10937,10 @@
         <v>10</v>
       </c>
       <c r="J95" t="n">
-        <v>23.38908838680146</v>
+        <v>23.400044414021</v>
       </c>
       <c r="K95" t="n">
-        <v>0.3034898261724761</v>
+        <v>0.4079151691108285</v>
       </c>
       <c r="L95" t="n">
         <v>23</v>
@@ -10965,7 +10955,7 @@
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>5.67927415456797</v>
+        <v>5.56936653994935</v>
       </c>
       <c r="Q95" t="n">
         <v>22</v>
@@ -11028,10 +11018,10 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1327657936038704</v>
+        <v>0.132894562028433</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11056,25 +11046,25 @@
         <v>10</v>
       </c>
       <c r="J96" t="n">
-        <v>12.78375678478788</v>
+        <v>12.79622946674051</v>
       </c>
       <c r="K96" t="n">
-        <v>2.601623372331341</v>
+        <v>2.715825079417811</v>
       </c>
       <c r="L96" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="M96" t="n">
-        <v>57.35294117647059</v>
+        <v>57.8125</v>
       </c>
       <c r="N96" t="n">
-        <v>13.98386424925724</v>
+        <v>13.90716148726076</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>7.210779307867954</v>
+        <v>7.091580012086962</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11101,16 +11091,16 @@
         <v>16.74415231729489</v>
       </c>
       <c r="Y96" t="n">
-        <v>10.51471861683158</v>
+        <v>10.42792759640029</v>
       </c>
       <c r="Z96" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA96" t="n">
-        <v>31.57894736842105</v>
+        <v>35</v>
       </c>
       <c r="AB96" t="n">
-        <v>19.477453049894</v>
+        <v>19.38302326887769</v>
       </c>
       <c r="AC96" t="n">
         <v>8</v>
@@ -11147,10 +11137,10 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C97" t="n">
-        <v>1.852619436277912</v>
+        <v>1.843070925917527</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11175,25 +11165,25 @@
         <v>10</v>
       </c>
       <c r="J97" t="n">
-        <v>24.72840729454471</v>
+        <v>23.59665213438843</v>
       </c>
       <c r="K97" t="n">
-        <v>3.653728252041666</v>
+        <v>3.119490794134161</v>
       </c>
       <c r="L97" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M97" t="n">
-        <v>57.14285714285715</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N97" t="n">
-        <v>11.91267637188544</v>
+        <v>12.07307419524786</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>0.3340658882200032</v>
+        <v>0.8538727248214251</v>
       </c>
       <c r="Q97" t="n">
         <v>51</v>
@@ -11202,10 +11192,10 @@
         <v>54.90196078431372</v>
       </c>
       <c r="S97" t="n">
-        <v>34.32405195756966</v>
+        <v>34.57993301552077</v>
       </c>
       <c r="T97" t="n">
-        <v>20.57790882674406</v>
+        <v>20.32202776879296</v>
       </c>
       <c r="U97" t="n">
         <v>41.38470855036881</v>
@@ -11234,10 +11224,10 @@
         <v>55</v>
       </c>
       <c r="AG97" t="n">
-        <v>57.80938255798803</v>
+        <v>58.11993765047036</v>
       </c>
       <c r="AH97" t="n">
-        <v>-2.80938255798803</v>
+        <v>-3.119937650470362</v>
       </c>
       <c r="AI97" t="n">
         <v>39.82909179893205</v>
@@ -11256,10 +11246,10 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6396323476203802</v>
+        <v>0.637136870276643</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11276,11 +11266,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>5</v>
       </c>
@@ -11288,25 +11274,25 @@
         <v>10</v>
       </c>
       <c r="J98" t="n">
-        <v>21.12557680400878</v>
+        <v>19.60032989595409</v>
       </c>
       <c r="K98" t="n">
-        <v>6.533771040683956</v>
+        <v>6.118137570982229</v>
       </c>
       <c r="L98" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="M98" t="n">
-        <v>75</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N98" t="n">
-        <v>15.92523016905886</v>
+        <v>18.01422758014704</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>3.253643352202684</v>
+        <v>3.658057442273899</v>
       </c>
       <c r="Q98" t="n">
         <v>48</v>
@@ -11315,10 +11301,10 @@
         <v>68.75</v>
       </c>
       <c r="S98" t="n">
-        <v>40.1712743805148</v>
+        <v>39.59359234758559</v>
       </c>
       <c r="T98" t="n">
-        <v>28.5787256194852</v>
+        <v>29.15640765241441</v>
       </c>
       <c r="U98" t="n">
         <v>54.66692858410841</v>
@@ -11369,10 +11355,10 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4776202289012797</v>
+        <v>0.4756447822555336</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11400,22 +11386,22 @@
         <v>28.77817890954801</v>
       </c>
       <c r="K99" t="n">
-        <v>2.75194573621651</v>
+        <v>2.326961670915439</v>
       </c>
       <c r="L99" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M99" t="n">
-        <v>68.42105263157895</v>
+        <v>70</v>
       </c>
       <c r="N99" t="n">
-        <v>12.20882658747631</v>
+        <v>13.56231575344962</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>1.214628350676183</v>
+        <v>1.634992676187408</v>
       </c>
       <c r="Q99" t="n">
         <v>35</v>
@@ -11456,10 +11442,10 @@
         <v>52.5</v>
       </c>
       <c r="AG99" t="n">
-        <v>37.78906518920106</v>
+        <v>38.08333281435104</v>
       </c>
       <c r="AH99" t="n">
-        <v>14.71093481079894</v>
+        <v>14.41666718564896</v>
       </c>
       <c r="AI99" t="n">
         <v>37.49736210669248</v>
@@ -11478,10 +11464,10 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C100" t="n">
-        <v>325.3443736970872</v>
+        <v>323.2641119175578</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11500,7 +11486,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -11513,16 +11499,16 @@
         <v>25.87300653788257</v>
       </c>
       <c r="K100" t="n">
-        <v>6.153197303852553</v>
+        <v>5.474450545097653</v>
       </c>
       <c r="L100" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M100" t="n">
-        <v>76.92307692307692</v>
+        <v>75</v>
       </c>
       <c r="N100" t="n">
-        <v>12.27301201847957</v>
+        <v>11.45661960612005</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11591,10 +11577,10 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C101" t="n">
-        <v>320.1555592203123</v>
+        <v>321.1859711241724</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11619,25 +11605,25 @@
         <v>10</v>
       </c>
       <c r="J101" t="n">
-        <v>14.83975271775182</v>
+        <v>14.61847018515478</v>
       </c>
       <c r="K101" t="n">
-        <v>1.383354815249982</v>
+        <v>1.709654367596736</v>
       </c>
       <c r="L101" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M101" t="n">
-        <v>58.8235294117647</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N101" t="n">
-        <v>11.41220571101113</v>
+        <v>11.18629778942283</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
       </c>
       <c r="P101" t="n">
-        <v>0.6082311893049086</v>
+        <v>0.2854651647462125</v>
       </c>
       <c r="Q101" t="n">
         <v>29</v>
@@ -11700,10 +11686,10 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C102" t="n">
-        <v>384.8747952851122</v>
+        <v>386.8011808561735</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11799,19 +11785,19 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7153782924650223</v>
+        <v>0.7094719344132854</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -11827,25 +11813,21 @@
         <v>10</v>
       </c>
       <c r="J103" t="n">
-        <v>31.6668549372698</v>
+        <v>31.27238030517686</v>
       </c>
       <c r="K103" t="n">
-        <v>10.02399561574348</v>
+        <v>9.115607537388293</v>
       </c>
       <c r="L103" t="n">
-        <v>3</v>
-      </c>
-      <c r="M103" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N103" t="n">
-        <v>14.21207955224867</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="O103" t="n">
         <v>10</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>0.8105095893900183</v>
       </c>
       <c r="Q103" t="n">
         <v>43</v>
@@ -11869,25 +11851,25 @@
         <v>68.18181818181819</v>
       </c>
       <c r="X103" t="n">
-        <v>10.930071631718</v>
+        <v>10.91420766588502</v>
       </c>
       <c r="Y103" t="n">
-        <v>0.8167992706095473</v>
+        <v>1.621613827792734</v>
       </c>
       <c r="Z103" t="n">
         <v>54</v>
       </c>
       <c r="AA103" t="n">
-        <v>35.18518518518518</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB103" t="n">
-        <v>11.50048915914395</v>
+        <v>11.46966802156439</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>7.242356242352932</v>
+        <v>6.48352389217095</v>
       </c>
       <c r="AE103" t="n">
         <v>34</v>
@@ -11918,10 +11900,10 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04860364154916188</v>
+        <v>0.04878407694779304</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11940,7 +11922,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -11953,22 +11935,22 @@
         <v>27.65580276361549</v>
       </c>
       <c r="K104" t="n">
-        <v>0.3800464516236834</v>
+        <v>0.7526957659305999</v>
       </c>
       <c r="L104" t="n">
         <v>20</v>
       </c>
       <c r="M104" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N104" t="n">
-        <v>14.95533509217345</v>
+        <v>14.63571482376176</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>3.606248130320289</v>
+        <v>3.223044514474882</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>
@@ -12009,10 +11991,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="AG104" t="n">
-        <v>34.47252163831823</v>
+        <v>34.6524603607966</v>
       </c>
       <c r="AH104" t="n">
-        <v>27.22960602125623</v>
+        <v>27.04966729877786</v>
       </c>
       <c r="AI104" t="n">
         <v>47.42656695641357</v>

--- a/TDA_Result.xlsx
+++ b/TDA_Result.xlsx
@@ -453,7 +453,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -679,7 +679,7 @@
         <v>46238</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4613459941311895</v>
+        <v>0.4529521035802819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -739,22 +739,22 @@
         <v>14.94856954517825</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.138476408177704</v>
+        <v>4.900808883080954</v>
       </c>
       <c r="Z2" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.02439024390244</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.55541461777871</v>
+        <v>10.73616807324932</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.019045139439382</v>
+        <v>3.258903761977072</v>
       </c>
       <c r="AE2" t="n">
         <v>43</v>
@@ -788,7 +788,7 @@
         <v>46238</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7435366563275064</v>
+        <v>0.7515556291312734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,22 +848,22 @@
         <v>12.13279917920569</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.271788386444806</v>
+        <v>1.217798829345296</v>
       </c>
       <c r="Z3" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AA3" t="n">
-        <v>44.44444444444444</v>
+        <v>44.26229508196721</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.3002809707242</v>
+        <v>10.50485684922246</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>7.907861492559299</v>
+        <v>8.890469200501716</v>
       </c>
       <c r="AE3" t="n">
         <v>38</v>
@@ -897,7 +897,7 @@
         <v>46238</v>
       </c>
       <c r="C4" t="n">
-        <v>1.386771475426517</v>
+        <v>1.38366984791598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>27.63389482946404</v>
       </c>
       <c r="K4" t="n">
-        <v>7.373411885526737</v>
+        <v>7.133262492417836</v>
       </c>
       <c r="L4" t="n">
         <v>16</v>
@@ -1006,7 +1006,7 @@
         <v>46238</v>
       </c>
       <c r="C5" t="n">
-        <v>0.26326581217916</v>
+        <v>0.2618037772819932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,22 +1066,22 @@
         <v>16.70172291026088</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.767292269863844</v>
+        <v>6.290609391884305</v>
       </c>
       <c r="Z5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA5" t="n">
-        <v>37.93103448275862</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.56925120345615</v>
+        <v>17.00985318049628</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.491760697631431</v>
+        <v>3.95839796208689</v>
       </c>
       <c r="AE5" t="n">
         <v>45</v>
@@ -1115,16 +1115,16 @@
         <v>46238</v>
       </c>
       <c r="C6" t="n">
-        <v>1.917718880641212</v>
+        <v>1.958796998116376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1147,22 +1147,22 @@
         <v>23.73506360720576</v>
       </c>
       <c r="K6" t="n">
-        <v>1.005030735562906</v>
+        <v>3.168588992209287</v>
       </c>
       <c r="L6" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="M6" t="n">
-        <v>77.77777777777777</v>
+        <v>80</v>
       </c>
       <c r="N6" t="n">
-        <v>14.44735332283513</v>
+        <v>12.86926775044043</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9850690180392974</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>40</v>
@@ -1189,7 +1189,7 @@
         <v>44.49622708587002</v>
       </c>
       <c r="Y6" t="n">
-        <v>22.96857755600068</v>
+        <v>21.31854122774828</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1234,16 +1234,16 @@
         <v>46238</v>
       </c>
       <c r="C7" t="n">
-        <v>2.161639401008327</v>
+        <v>2.142795639576391</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1262,22 +1262,22 @@
         <v>11.35312764557068</v>
       </c>
       <c r="K7" t="n">
-        <v>3.561166149223083</v>
+        <v>2.65838749538343</v>
       </c>
       <c r="L7" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M7" t="n">
-        <v>52.38095238095238</v>
+        <v>54.41176470588236</v>
       </c>
       <c r="N7" t="n">
-        <v>12.78180602736253</v>
+        <v>12.8575295178231</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.3327662872475434</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1304,22 +1304,22 @@
         <v>13.79329344082609</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.196265234939748</v>
+        <v>8.996550275852023</v>
       </c>
       <c r="Z7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA7" t="n">
-        <v>63.1578947368421</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.654336102227296</v>
+        <v>8.263093745287698</v>
       </c>
       <c r="AC7" t="n">
         <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.96477275099568</v>
+        <v>1.102650204129252</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1353,7 +1353,7 @@
         <v>46238</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3221431320117004</v>
+        <v>0.3299358408260801</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,22 +1381,22 @@
         <v>22.10694516187944</v>
       </c>
       <c r="K8" t="n">
-        <v>2.424700119831957</v>
+        <v>4.902374743685245</v>
       </c>
       <c r="L8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>72.72727272727273</v>
+        <v>50</v>
       </c>
       <c r="N8" t="n">
-        <v>16.69353349408749</v>
+        <v>17.20097034198387</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>5.443315795550507</v>
+        <v>2.952864760100415</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1462,7 +1462,7 @@
         <v>46238</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5723718021223878</v>
+        <v>0.5711317799376231</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,16 +1490,16 @@
         <v>11.07138721870453</v>
       </c>
       <c r="K9" t="n">
-        <v>2.986599647582411</v>
+        <v>2.76348301635958</v>
       </c>
       <c r="L9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M9" t="n">
-        <v>45</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="N9" t="n">
-        <v>15.45282043738036</v>
+        <v>14.53643886531697</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1571,7 +1571,7 @@
         <v>46238</v>
       </c>
       <c r="C10" t="n">
-        <v>2.028113885685852</v>
+        <v>2.035550749088603</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,22 +1599,22 @@
         <v>10.23694539327734</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4214243768458692</v>
+        <v>0.7896583409596314</v>
       </c>
       <c r="L10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M10" t="n">
-        <v>43.90243902439025</v>
+        <v>40.47619047619047</v>
       </c>
       <c r="N10" t="n">
-        <v>9.822220633184779</v>
+        <v>9.764403333337537</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>9.538378570701367</v>
+        <v>9.138181248598798</v>
       </c>
       <c r="Q10" t="n">
         <v>44</v>
@@ -1680,7 +1680,7 @@
         <v>46238</v>
       </c>
       <c r="C11" t="n">
-        <v>7.217730567918579</v>
+        <v>7.275831993733152</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,16 +1708,16 @@
         <v>20.56423081971027</v>
       </c>
       <c r="K11" t="n">
-        <v>3.417731290746562</v>
+        <v>4.250225325534762</v>
       </c>
       <c r="L11" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M11" t="n">
-        <v>62.5</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="N11" t="n">
-        <v>12.53796400267027</v>
+        <v>14.43081743608645</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1789,7 +1789,7 @@
         <v>46238</v>
       </c>
       <c r="C12" t="n">
-        <v>6.218918617514697</v>
+        <v>6.198125665181637</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,7 +1806,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>5</v>
       </c>
@@ -1817,16 +1821,16 @@
         <v>20.08266526523165</v>
       </c>
       <c r="K12" t="n">
-        <v>8.269545477631146</v>
+        <v>7.907546288270773</v>
       </c>
       <c r="L12" t="n">
         <v>6</v>
       </c>
       <c r="M12" t="n">
-        <v>66.66666666666667</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N12" t="n">
-        <v>33.26223985018026</v>
+        <v>28.65873508979989</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -1898,7 +1902,7 @@
         <v>46238</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3025874590717458</v>
+        <v>0.3011269129906093</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1926,7 +1930,7 @@
         <v>38.11781916800814</v>
       </c>
       <c r="K13" t="n">
-        <v>6.330731774557008</v>
+        <v>5.817488647845415</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1962,7 +1966,7 @@
         <v>35.74308703619145</v>
       </c>
       <c r="Y13" t="n">
-        <v>21.66766345441414</v>
+        <v>22.04576236016157</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -1997,7 +2001,7 @@
         <v>46238</v>
       </c>
       <c r="C14" t="n">
-        <v>7.964211078220427</v>
+        <v>8.043369183823499</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,16 +2061,16 @@
         <v>14.33662537827827</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.959277181785707</v>
+        <v>7.044463500296083</v>
       </c>
       <c r="Z14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>45.45454545454545</v>
+        <v>37.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.47267774674982</v>
+        <v>11.56978199300831</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2106,7 +2110,7 @@
         <v>46238</v>
       </c>
       <c r="C15" t="n">
-        <v>11.23926289454474</v>
+        <v>11.34483052202033</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2134,22 +2138,22 @@
         <v>19.49276356151121</v>
       </c>
       <c r="K15" t="n">
-        <v>5.823730891285361</v>
+        <v>6.817707124925354</v>
       </c>
       <c r="L15" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M15" t="n">
-        <v>58.33333333333334</v>
+        <v>55</v>
       </c>
       <c r="N15" t="n">
-        <v>18.42435090586761</v>
+        <v>16.64539778417854</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>2.056503858241743</v>
+        <v>1.106832291103133</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2215,7 +2219,7 @@
         <v>46238</v>
       </c>
       <c r="C16" t="n">
-        <v>36.02031307456526</v>
+        <v>36.10579055849659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2243,22 +2247,22 @@
         <v>18.2920442587057</v>
       </c>
       <c r="K16" t="n">
-        <v>3.823743878637798</v>
+        <v>4.070121315188846</v>
       </c>
       <c r="L16" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M16" t="n">
-        <v>61.22448979591837</v>
+        <v>63.82978723404256</v>
       </c>
       <c r="N16" t="n">
-        <v>16.59012435820357</v>
+        <v>16.47506314968796</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>5.948789641588914</v>
+        <v>5.697964612582518</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2324,7 +2328,7 @@
         <v>46238</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7174623721905614</v>
+        <v>0.7183306931056348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2352,22 +2356,22 @@
         <v>14.16674936134154</v>
       </c>
       <c r="K17" t="n">
-        <v>1.89726557354295</v>
+        <v>2.020588454736227</v>
       </c>
       <c r="L17" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="M17" t="n">
-        <v>70</v>
+        <v>62.90322580645162</v>
       </c>
       <c r="N17" t="n">
-        <v>16.68447139999035</v>
+        <v>16.8725548240452</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>5.989105195421063</v>
+        <v>5.860985155870457</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2394,7 +2398,7 @@
         <v>15.7396793517258</v>
       </c>
       <c r="Y17" t="n">
-        <v>11.95995518193599</v>
+        <v>11.85340323546092</v>
       </c>
       <c r="Z17" t="n">
         <v>18</v>
@@ -2443,7 +2447,7 @@
         <v>46238</v>
       </c>
       <c r="C18" t="n">
-        <v>0.102825059107988</v>
+        <v>0.1026186732073968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,22 +2475,22 @@
         <v>27.33452427541018</v>
       </c>
       <c r="K18" t="n">
-        <v>2.898875767547082</v>
+        <v>2.692341705429024</v>
       </c>
       <c r="L18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M18" t="n">
-        <v>54.54545454545455</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N18" t="n">
-        <v>20.90509599778342</v>
+        <v>19.64929478594908</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>6.901070764363526</v>
+        <v>7.116069390581092</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2552,7 +2556,7 @@
         <v>46238</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02502286907177551</v>
+        <v>0.02502381650026696</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2580,7 +2584,7 @@
         <v>23.99412305210119</v>
       </c>
       <c r="K19" t="n">
-        <v>1.310303730759044</v>
+        <v>1.314139592584374</v>
       </c>
       <c r="L19" t="n">
         <v>20</v>
@@ -2595,7 +2599,7 @@
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>8.577307489211151</v>
+        <v>8.573196636070923</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2661,7 +2665,7 @@
         <v>46238</v>
       </c>
       <c r="C20" t="n">
-        <v>1.830454385874408</v>
+        <v>1.818957998433288</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2721,7 +2725,7 @@
         <v>20.34011802710127</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.600815097955349</v>
+        <v>8.181139216969191</v>
       </c>
       <c r="Z20" t="n">
         <v>18</v>
@@ -2730,7 +2734,7 @@
         <v>44.44444444444444</v>
       </c>
       <c r="AB20" t="n">
-        <v>13.15851961577055</v>
+        <v>12.89733152444661</v>
       </c>
       <c r="AC20" t="n">
         <v>4</v>
@@ -2770,7 +2774,7 @@
         <v>46238</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9777843303953793</v>
+        <v>0.955110623816726</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2798,22 +2802,22 @@
         <v>14.08722322280853</v>
       </c>
       <c r="K21" t="n">
-        <v>4.514234954793528</v>
+        <v>2.090668711203603</v>
       </c>
       <c r="L21" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="M21" t="n">
-        <v>53.48837209302326</v>
+        <v>54.23728813559322</v>
       </c>
       <c r="N21" t="n">
-        <v>15.49973924911641</v>
+        <v>16.1506378427643</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>3.335206009702141</v>
+        <v>5.788316761361267</v>
       </c>
       <c r="Q21" t="n">
         <v>41</v>
@@ -2879,7 +2883,7 @@
         <v>46238</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7860124584173873</v>
+        <v>0.7809953636098027</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2896,7 +2900,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>5</v>
       </c>
@@ -2907,22 +2915,22 @@
         <v>20.35908649698318</v>
       </c>
       <c r="K22" t="n">
-        <v>4.705626915166117</v>
+        <v>4.037293924390517</v>
       </c>
       <c r="L22" t="n">
         <v>16</v>
       </c>
       <c r="M22" t="n">
-        <v>68.75</v>
+        <v>81.25</v>
       </c>
       <c r="N22" t="n">
-        <v>15.69529022497824</v>
+        <v>14.50436328333056</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>5.056436068257786</v>
+        <v>5.731316002839248</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -2980,7 +2988,7 @@
         <v>46238</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7780219403146028</v>
+        <v>0.7755280107341586</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3012,7 +3020,7 @@
         <v>24.64686798085608</v>
       </c>
       <c r="K23" t="n">
-        <v>11.72983110515275</v>
+        <v>11.37168396768449</v>
       </c>
       <c r="L23" t="n">
         <v>7</v>
@@ -3051,25 +3059,25 @@
         <v>87.5</v>
       </c>
       <c r="X23" t="n">
-        <v>13.36048547240214</v>
+        <v>16.44501523256388</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.438468052120656</v>
+        <v>4.356847096242733</v>
       </c>
       <c r="Z23" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="AA23" t="n">
-        <v>28.57142857142857</v>
+        <v>50</v>
       </c>
       <c r="AB23" t="n">
-        <v>13.40010890158462</v>
+        <v>10.96308432487421</v>
       </c>
       <c r="AC23" t="n">
         <v>6</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.628105770810819</v>
+        <v>1.718003697986337</v>
       </c>
       <c r="AE23" t="n">
         <v>10</v>
@@ -3103,7 +3111,7 @@
         <v>46238</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1781039471494759</v>
+        <v>0.1861014910674987</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,22 +3139,22 @@
         <v>23.34450349594161</v>
       </c>
       <c r="K24" t="n">
-        <v>1.754940803300054</v>
+        <v>6.324124254732566</v>
       </c>
       <c r="L24" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M24" t="n">
-        <v>60</v>
+        <v>37.5</v>
       </c>
       <c r="N24" t="n">
-        <v>14.52787507022096</v>
+        <v>13.73901262125115</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>8.102858821016135</v>
+        <v>3.45723585407649</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3212,7 +3220,7 @@
         <v>46238</v>
       </c>
       <c r="C25" t="n">
-        <v>3.95108967132919</v>
+        <v>3.911285407035741</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3311,7 +3319,7 @@
         <v>46238</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4356922720671197</v>
+        <v>0.4315031094170144</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3410,7 +3418,7 @@
         <v>46238</v>
       </c>
       <c r="C27" t="n">
-        <v>34.085772033783</v>
+        <v>33.7506079478084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3435,10 +3443,10 @@
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>60.11995427672586</v>
+        <v>60.26772025973355</v>
       </c>
       <c r="K27" t="n">
-        <v>1.122894572676225</v>
+        <v>0.5009392611145858</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3449,7 +3457,7 @@
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>6.800740283775464</v>
+        <v>7.461682242990664</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -3495,16 +3503,16 @@
         <v>46238</v>
       </c>
       <c r="C28" t="n">
-        <v>1.408850540569686</v>
+        <v>1.448857906070049</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3523,22 +3531,22 @@
         <v>24.87361787048376</v>
       </c>
       <c r="K28" t="n">
-        <v>1.040256881970225</v>
+        <v>3.909514032336903</v>
       </c>
       <c r="L28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M28" t="n">
-        <v>57.89473684210526</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="N28" t="n">
-        <v>16.11094891522698</v>
+        <v>14.1693939144707</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>0.9498621120400452</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>40</v>
@@ -3604,7 +3612,7 @@
         <v>46238</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3864876380930803</v>
+        <v>0.3791423579980717</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3623,7 +3631,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %88.89: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3633,25 +3641,25 @@
         <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>17.83520922572316</v>
+        <v>17.9698042307806</v>
       </c>
       <c r="K29" t="n">
-        <v>2.68156173290468</v>
+        <v>0.8953544626694177</v>
       </c>
       <c r="L29" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M29" t="n">
-        <v>88.88888888888889</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="N29" t="n">
-        <v>28.21742727075513</v>
+        <v>23.93140568417198</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>1.284006831260354</v>
+        <v>3.077094633211575</v>
       </c>
       <c r="Q29" t="n">
         <v>6</v>
@@ -3678,7 +3686,7 @@
         <v>55.05052857749912</v>
       </c>
       <c r="Y29" t="n">
-        <v>15.63190963839896</v>
+        <v>17.23534321222443</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3723,7 +3731,7 @@
         <v>46238</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3818615762002674</v>
+        <v>0.3816657454376894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3759,7 @@
         <v>21.77845247058357</v>
       </c>
       <c r="K30" t="n">
-        <v>3.297038834709998</v>
+        <v>3.24406482750994</v>
       </c>
       <c r="L30" t="n">
         <v>26</v>
@@ -3766,7 +3774,7 @@
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>1.648605985709795</v>
+        <v>1.700761371051884</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3832,7 +3840,7 @@
         <v>46238</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1863047061259438</v>
+        <v>0.185260355261961</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3857,25 +3865,25 @@
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>26.85904908752153</v>
+        <v>26.85627978794248</v>
       </c>
       <c r="K31" t="n">
-        <v>0.7963560900858146</v>
+        <v>0.2275365198067814</v>
       </c>
       <c r="L31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M31" t="n">
-        <v>42.85714285714285</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="N31" t="n">
-        <v>15.87753653145509</v>
+        <v>16.48034815138524</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>9.130929199155302</v>
+        <v>9.750278036876626</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3941,7 +3949,7 @@
         <v>46238</v>
       </c>
       <c r="C32" t="n">
-        <v>2.319346551072098</v>
+        <v>2.30471437971425</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4001,22 +4009,22 @@
         <v>12.36180984775317</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.055536036591477</v>
+        <v>2.673442911958013</v>
       </c>
       <c r="Z32" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA32" t="n">
-        <v>45.09803921568628</v>
+        <v>39.58333333333334</v>
       </c>
       <c r="AB32" t="n">
-        <v>10.84413756618767</v>
+        <v>12.02327185494637</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>6.069218945982835</v>
+        <v>5.472871174538274</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4050,7 +4058,7 @@
         <v>46238</v>
       </c>
       <c r="C33" t="n">
-        <v>1.828351495605076</v>
+        <v>1.813700894391573</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4078,22 +4086,22 @@
         <v>12.57251846431013</v>
       </c>
       <c r="K33" t="n">
-        <v>2.476997893865995</v>
+        <v>1.655848550696004</v>
       </c>
       <c r="L33" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M33" t="n">
-        <v>59.25925925925926</v>
+        <v>61.40350877192982</v>
       </c>
       <c r="N33" t="n">
-        <v>11.20201978105696</v>
+        <v>12.49758808778181</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>1.486189230203006</v>
+        <v>2.305968109778722</v>
       </c>
       <c r="Q33" t="n">
         <v>39</v>
@@ -4159,7 +4167,7 @@
         <v>46238</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8638146684298388</v>
+        <v>0.8697353054886147</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4184,25 +4192,25 @@
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>10.40906379693826</v>
+        <v>10.40567165971804</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9336635452190434</v>
+        <v>1.62162122279037</v>
       </c>
       <c r="L34" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M34" t="n">
-        <v>46.15384615384615</v>
+        <v>42.5925925925926</v>
       </c>
       <c r="N34" t="n">
-        <v>13.73200290307858</v>
+        <v>13.33836126749276</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>3.037972017539237</v>
+        <v>2.340425933567225</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4229,16 +4237,16 @@
         <v>14.68007915548277</v>
       </c>
       <c r="Y34" t="n">
-        <v>9.57258588578982</v>
+        <v>8.952791016935546</v>
       </c>
       <c r="Z34" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA34" t="n">
-        <v>50</v>
+        <v>47.82608695652174</v>
       </c>
       <c r="AB34" t="n">
-        <v>11.00516569549747</v>
+        <v>10.32245985978625</v>
       </c>
       <c r="AC34" t="n">
         <v>2</v>
@@ -4278,7 +4286,7 @@
         <v>46238</v>
       </c>
       <c r="C35" t="n">
-        <v>1.931386865608722</v>
+        <v>1.948282790032946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4297,7 +4305,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %88.89: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4310,16 +4318,16 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>8.882418809892979</v>
+        <v>9.834930785663776</v>
       </c>
       <c r="L35" t="n">
         <v>9</v>
       </c>
       <c r="M35" t="n">
-        <v>88.88888888888889</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N35" t="n">
-        <v>12.48259706892392</v>
+        <v>11.33742913819006</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4352,7 +4360,7 @@
         <v>42.52272358489104</v>
       </c>
       <c r="Y35" t="n">
-        <v>16.06167576713577</v>
+        <v>15.3273766954231</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -4397,7 +4405,7 @@
         <v>46238</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08179744393583781</v>
+        <v>0.08243139305635987</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4425,16 +4433,16 @@
         <v>20.39128953068605</v>
       </c>
       <c r="K36" t="n">
-        <v>2.235773725024615</v>
+        <v>3.028124631364815</v>
       </c>
       <c r="L36" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M36" t="n">
-        <v>50</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="N36" t="n">
-        <v>13.04871975908602</v>
+        <v>14.11464947818691</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4506,7 +4514,7 @@
         <v>46238</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06287258403569951</v>
+        <v>0.06392638430611416</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4534,22 +4542,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>2.345951595217133</v>
+        <v>4.061360515035761</v>
       </c>
       <c r="L37" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="M37" t="n">
-        <v>56.57894736842105</v>
+        <v>57.35294117647059</v>
       </c>
       <c r="N37" t="n">
-        <v>19.24752808895938</v>
+        <v>18.90646061917947</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>5.524447539600685</v>
+        <v>3.784920229247968</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4615,7 +4623,7 @@
         <v>46238</v>
       </c>
       <c r="C38" t="n">
-        <v>1.653822345841002</v>
+        <v>1.670707600320264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4632,7 +4640,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %85.19: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H38" t="n">
         <v>5</v>
       </c>
@@ -4643,22 +4655,22 @@
         <v>18.01910891260425</v>
       </c>
       <c r="K38" t="n">
-        <v>4.385578445450133</v>
+        <v>5.451338054061572</v>
       </c>
       <c r="L38" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M38" t="n">
-        <v>67.74193548387096</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="N38" t="n">
-        <v>14.79177455291849</v>
+        <v>12.89404370622258</v>
       </c>
       <c r="O38" t="n">
         <v>6</v>
       </c>
       <c r="P38" t="n">
-        <v>1.546594442060334</v>
+        <v>0.5202987046566854</v>
       </c>
       <c r="Q38" t="n">
         <v>35</v>
@@ -4724,7 +4736,7 @@
         <v>46238</v>
       </c>
       <c r="C39" t="n">
-        <v>2.674713200947313</v>
+        <v>2.67060885319107</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4741,7 +4753,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H39" t="n">
         <v>5</v>
       </c>
@@ -4752,16 +4768,16 @@
         <v>18.47027414490581</v>
       </c>
       <c r="K39" t="n">
-        <v>5.877184680609626</v>
+        <v>5.714716126886832</v>
       </c>
       <c r="L39" t="n">
         <v>20</v>
       </c>
       <c r="M39" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="N39" t="n">
-        <v>14.53711661926971</v>
+        <v>13.90751191027973</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4833,7 +4849,7 @@
         <v>46238</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1970287971666329</v>
+        <v>0.1949334275398527</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4850,7 +4866,11 @@
           <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %78.95: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H40" t="n">
         <v>5</v>
       </c>
@@ -4861,16 +4881,16 @@
         <v>14.73965458840789</v>
       </c>
       <c r="K40" t="n">
-        <v>7.605184002851528</v>
+        <v>6.460820145963275</v>
       </c>
       <c r="L40" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M40" t="n">
-        <v>68.75</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="N40" t="n">
-        <v>12.21407746678665</v>
+        <v>11.77088649714645</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4903,16 +4923,16 @@
         <v>14.17330472629232</v>
       </c>
       <c r="Y40" t="n">
-        <v>5.752763957552542</v>
+        <v>6.75506818237257</v>
       </c>
       <c r="Z40" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA40" t="n">
-        <v>50</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="AB40" t="n">
-        <v>12.58136924216362</v>
+        <v>11.50844416173121</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
@@ -4952,7 +4972,7 @@
         <v>46238</v>
       </c>
       <c r="C41" t="n">
-        <v>1.626486375485432</v>
+        <v>1.647576374499912</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4971,7 +4991,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -4984,22 +5004,22 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>7.487388755205426</v>
+        <v>8.881134781660638</v>
       </c>
       <c r="L41" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M41" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N41" t="n">
-        <v>17.56011838426139</v>
+        <v>12.63199731055526</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>2.337587017316856</v>
+        <v>1.027602458941157</v>
       </c>
       <c r="Q41" t="n">
         <v>10</v>
@@ -5026,7 +5046,7 @@
         <v>40.81782021738603</v>
       </c>
       <c r="Y41" t="n">
-        <v>16.58847630184379</v>
+        <v>15.50691239875521</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -5071,7 +5091,7 @@
         <v>46238</v>
       </c>
       <c r="C42" t="n">
-        <v>3.177273511553252</v>
+        <v>3.156365394918847</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5090,7 +5110,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -5103,16 +5123,16 @@
         <v>21.13784986389697</v>
       </c>
       <c r="K42" t="n">
-        <v>3.373246541043096</v>
+        <v>2.692996670297587</v>
       </c>
       <c r="L42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M42" t="n">
-        <v>83.33333333333333</v>
+        <v>75</v>
       </c>
       <c r="N42" t="n">
-        <v>13.42476118611086</v>
+        <v>16.84474117966856</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
@@ -5180,7 +5200,7 @@
         <v>46238</v>
       </c>
       <c r="C43" t="n">
-        <v>7.212473662916453</v>
+        <v>7.239032265441149</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5240,16 +5260,16 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>6.906247451997549</v>
+        <v>6.563446897429559</v>
       </c>
       <c r="Z43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA43" t="n">
-        <v>60</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="AB43" t="n">
-        <v>13.09070057304151</v>
+        <v>12.2110825576475</v>
       </c>
       <c r="AC43" t="n">
         <v>6</v>
@@ -5289,7 +5309,7 @@
         <v>46238</v>
       </c>
       <c r="C44" t="n">
-        <v>4.979340482147699</v>
+        <v>5.019482874892531</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5317,22 +5337,22 @@
         <v>13.03201987649729</v>
       </c>
       <c r="K44" t="n">
-        <v>1.913883151424911</v>
+        <v>2.735491382129962</v>
       </c>
       <c r="L44" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="M44" t="n">
-        <v>66.66666666666667</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N44" t="n">
-        <v>17.42717636190461</v>
+        <v>18.54409624254036</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>7.934264300930072</v>
+        <v>7.071079838270622</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5359,7 +5379,7 @@
         <v>12.1234692799834</v>
       </c>
       <c r="Y44" t="n">
-        <v>9.105663777727147</v>
+        <v>8.372892810166899</v>
       </c>
       <c r="Z44" t="n">
         <v>7</v>
@@ -5368,13 +5388,13 @@
         <v>14.28571428571429</v>
       </c>
       <c r="AB44" t="n">
-        <v>8.805992909897132</v>
+        <v>9.691917834769438</v>
       </c>
       <c r="AC44" t="n">
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.983929537794126</v>
+        <v>1.775792382555585</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5400,7 +5420,7 @@
         <v>46238</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02039679203907629</v>
+        <v>0.02039756431270554</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5425,10 +5445,10 @@
         <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>10.66683965345718</v>
+        <v>10.66345727627647</v>
       </c>
       <c r="K45" t="n">
-        <v>1.041671896701502</v>
+        <v>1.041671896701479</v>
       </c>
       <c r="L45" t="n">
         <v>77</v>
@@ -5443,7 +5463,7 @@
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>8.86597374641318</v>
+        <v>8.865973746413204</v>
       </c>
       <c r="Q45" t="n">
         <v>37</v>
@@ -5509,7 +5529,7 @@
         <v>46238</v>
       </c>
       <c r="C46" t="n">
-        <v>8.531956818450002</v>
+        <v>8.542794067786396</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5537,22 +5557,22 @@
         <v>23.79638976838147</v>
       </c>
       <c r="K46" t="n">
-        <v>3.327104463812081</v>
+        <v>3.458350040660352</v>
       </c>
       <c r="L46" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M46" t="n">
-        <v>47.05882352941177</v>
+        <v>43.75</v>
       </c>
       <c r="N46" t="n">
-        <v>10.19857950124049</v>
+        <v>10.87915030095106</v>
       </c>
       <c r="O46" t="n">
         <v>10</v>
       </c>
       <c r="P46" t="n">
-        <v>6.458030127540204</v>
+        <v>6.322979205418133</v>
       </c>
       <c r="Q46" t="n">
         <v>54</v>
@@ -5618,7 +5638,7 @@
         <v>46238</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7801246701431945</v>
+        <v>0.7671166120939383</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5646,22 +5666,22 @@
         <v>25.38434003813299</v>
       </c>
       <c r="K47" t="n">
-        <v>4.657303478187114</v>
+        <v>2.912212813802673</v>
       </c>
       <c r="L47" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M47" t="n">
-        <v>50</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N47" t="n">
-        <v>16.45845198786146</v>
+        <v>13.07077433982179</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>5.104943796804817</v>
+        <v>6.88721677671158</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5727,7 +5747,7 @@
         <v>46238</v>
       </c>
       <c r="C48" t="n">
-        <v>0.06161092809684655</v>
+        <v>0.0618235447922699</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5755,7 +5775,7 @@
         <v>34.60463024804744</v>
       </c>
       <c r="K48" t="n">
-        <v>4.982115615744487</v>
+        <v>5.344404436742045</v>
       </c>
       <c r="L48" t="n">
         <v>7</v>
@@ -5764,13 +5784,13 @@
         <v>71.42857142857143</v>
       </c>
       <c r="N48" t="n">
-        <v>11.58233814173376</v>
+        <v>13.44205386179763</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>4.779751631813167</v>
+        <v>4.419404702272134</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5836,7 +5856,7 @@
         <v>46238</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2626349690698471</v>
+        <v>0.2599112166727135</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5864,22 +5884,22 @@
         <v>24.14896896188847</v>
       </c>
       <c r="K49" t="n">
-        <v>3.934744114579414</v>
+        <v>2.856850681613632</v>
       </c>
       <c r="L49" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M49" t="n">
-        <v>52.94117647058823</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N49" t="n">
-        <v>11.28436287108054</v>
+        <v>9.908482851676821</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>1.024927606735848</v>
+        <v>2.083623311606475</v>
       </c>
       <c r="Q49" t="n">
         <v>53</v>
@@ -5945,7 +5965,7 @@
         <v>46238</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7258734523662211</v>
+        <v>0.7200130048809851</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5973,22 +5993,22 @@
         <v>11.86078125763058</v>
       </c>
       <c r="K50" t="n">
-        <v>1.591062447753799</v>
+        <v>0.7708518662762787</v>
       </c>
       <c r="L50" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="M50" t="n">
-        <v>46.66666666666666</v>
+        <v>41.50943396226415</v>
       </c>
       <c r="N50" t="n">
-        <v>13.16142843703877</v>
+        <v>13.61476274983396</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>2.371210118493505</v>
+        <v>3.204446597324417</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6054,7 +6074,7 @@
         <v>46238</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1827300090422888</v>
+        <v>0.1829472166562726</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6086,7 +6106,7 @@
         <v>27.30972539236674</v>
       </c>
       <c r="K51" t="n">
-        <v>5.910534992834959</v>
+        <v>6.036428789492221</v>
       </c>
       <c r="L51" t="n">
         <v>4</v>
@@ -6095,7 +6115,7 @@
         <v>75</v>
       </c>
       <c r="N51" t="n">
-        <v>22.94220322121633</v>
+        <v>22.48074903415539</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
@@ -6128,7 +6148,7 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>17.04690071618444</v>
+        <v>16.94829597762813</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6173,7 +6193,7 @@
         <v>46238</v>
       </c>
       <c r="C52" t="n">
-        <v>4.138235681807588</v>
+        <v>4.096335533440767</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6233,22 +6253,22 @@
         <v>12.1710603868542</v>
       </c>
       <c r="Y52" t="n">
-        <v>5.048511811187062</v>
+        <v>6.009907378929091</v>
       </c>
       <c r="Z52" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AA52" t="n">
-        <v>53.84615384615385</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="AB52" t="n">
-        <v>13.74275314443207</v>
+        <v>12.94443432089259</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.108416987571427</v>
+        <v>2.117342972619607</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6282,7 +6302,7 @@
         <v>46238</v>
       </c>
       <c r="C53" t="n">
-        <v>1.561300785631331</v>
+        <v>1.569771299029488</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6299,7 +6319,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H53" t="n">
         <v>5</v>
       </c>
@@ -6310,22 +6334,22 @@
         <v>28.17598592067425</v>
       </c>
       <c r="K53" t="n">
-        <v>2.933465455497863</v>
+        <v>3.491909610707133</v>
       </c>
       <c r="L53" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M53" t="n">
-        <v>57.14285714285715</v>
+        <v>75</v>
       </c>
       <c r="N53" t="n">
-        <v>17.02235577422501</v>
+        <v>14.69167149600774</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>4.922145117801957</v>
+        <v>4.355983386769458</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6383,7 +6407,7 @@
         <v>46238</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08810572909728384</v>
+        <v>0.08810906500084342</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6411,7 +6435,7 @@
         <v>42.39442432818535</v>
       </c>
       <c r="K54" t="n">
-        <v>9.001281665405614</v>
+        <v>9.005408726917196</v>
       </c>
       <c r="L54" t="n">
         <v>3</v>
@@ -6426,7 +6450,7 @@
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>0.9162445792702645</v>
+        <v>0.9124237821762415</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6453,7 +6477,7 @@
         <v>114.7400208810756</v>
       </c>
       <c r="Y54" t="n">
-        <v>37.20918420698695</v>
+        <v>37.20680678944488</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -6498,7 +6522,7 @@
         <v>46238</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8478336322242699</v>
+        <v>0.8579593636262435</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6523,25 +6547,25 @@
         <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>12.34658621941707</v>
+        <v>12.34326744164818</v>
       </c>
       <c r="K55" t="n">
-        <v>1.103306439805984</v>
+        <v>2.306916111624857</v>
       </c>
       <c r="L55" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="M55" t="n">
-        <v>64.55696202531645</v>
+        <v>62.31884057971015</v>
       </c>
       <c r="N55" t="n">
-        <v>15.77836033789633</v>
+        <v>14.02210064666208</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>4.843257587336547</v>
+        <v>3.609808631457234</v>
       </c>
       <c r="Q55" t="n">
         <v>44</v>
@@ -6568,16 +6592,16 @@
         <v>25.41488056506582</v>
       </c>
       <c r="Y55" t="n">
-        <v>11.37950046046611</v>
+        <v>10.32110015533564</v>
       </c>
       <c r="Z55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA55" t="n">
-        <v>50</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="AB55" t="n">
-        <v>9.686169325397467</v>
+        <v>8.985280448705707</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6617,16 +6641,16 @@
         <v>46238</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7839096482632872</v>
+        <v>0.8638473746165619</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6642,13 +6666,13 @@
         <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>34.40959858154028</v>
+        <v>34.40711516467502</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>10.19314156211462</v>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
@@ -6656,7 +6680,7 @@
         <v>4</v>
       </c>
       <c r="P56" t="n">
-        <v>4.000000000000004</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -6706,7 +6730,7 @@
         <v>46238</v>
       </c>
       <c r="C57" t="n">
-        <v>1.368898030381272</v>
+        <v>1.378412743874265</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6734,17 +6758,13 @@
         <v>32.76213282665623</v>
       </c>
       <c r="K57" t="n">
-        <v>17.21493851935709</v>
+        <v>18.02965702457682</v>
       </c>
       <c r="L57" t="n">
-        <v>3</v>
-      </c>
-      <c r="M57" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N57" t="n">
-        <v>17.10890341118185</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
         <v>10</v>
       </c>
@@ -6776,10 +6796,10 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>15.60667990349154</v>
+        <v>15.02009255832818</v>
       </c>
       <c r="Z57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr"/>
@@ -6821,7 +6841,7 @@
         <v>46238</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7712931084304441</v>
+        <v>0.7486115833666973</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6840,7 +6860,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %84.62: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %91.67: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -6853,22 +6873,22 @@
         <v>16.33691982084211</v>
       </c>
       <c r="K58" t="n">
-        <v>3.978233602764591</v>
+        <v>0.9205310435592251</v>
       </c>
       <c r="L58" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="M58" t="n">
-        <v>84.61538461538461</v>
+        <v>91.66666666666667</v>
       </c>
       <c r="N58" t="n">
-        <v>20.44222564624019</v>
+        <v>17.74346149259786</v>
       </c>
       <c r="O58" t="n">
         <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>0.9826733555976075</v>
+        <v>4.042258710152846</v>
       </c>
       <c r="Q58" t="n">
         <v>24</v>
@@ -6895,7 +6915,7 @@
         <v>41.32985472592288</v>
       </c>
       <c r="Y58" t="n">
-        <v>13.00860705204698</v>
+        <v>15.56677519579512</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -6940,7 +6960,7 @@
         <v>46238</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8091428082544818</v>
+        <v>0.8205288085039025</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6957,11 +6977,7 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>5</v>
       </c>
@@ -7004,16 +7020,16 @@
         <v>10.2478061424703</v>
       </c>
       <c r="Y59" t="n">
-        <v>8.125129750640102</v>
+        <v>6.832295797346521</v>
       </c>
       <c r="Z59" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AA59" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AB59" t="n">
-        <v>13.8254719095032</v>
+        <v>15.44866820059028</v>
       </c>
       <c r="AC59" t="n">
         <v>6</v>
@@ -7053,7 +7069,7 @@
         <v>46238</v>
       </c>
       <c r="C60" t="n">
-        <v>12.83736201519095</v>
+        <v>13.00607539920218</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7081,22 +7097,22 @@
         <v>17.06238107085701</v>
       </c>
       <c r="K60" t="n">
-        <v>1.028638809519911</v>
+        <v>2.356394739081846</v>
       </c>
       <c r="L60" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M60" t="n">
-        <v>56.09756097560975</v>
+        <v>53.48837209302326</v>
       </c>
       <c r="N60" t="n">
-        <v>12.75109754658648</v>
+        <v>12.06861578740512</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>6.900381191539107</v>
+        <v>5.513681167946904</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7162,7 +7178,7 @@
         <v>46238</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6304080381822081</v>
+        <v>0.6308524850057646</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7194,7 +7210,7 @@
         <v>36.10328933244122</v>
       </c>
       <c r="K61" t="n">
-        <v>1.785398698762553</v>
+        <v>1.857158883271848</v>
       </c>
       <c r="L61" t="n">
         <v>8</v>
@@ -7209,7 +7225,7 @@
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>8.07051051158021</v>
+        <v>7.994372910066971</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7267,7 +7283,7 @@
         <v>46238</v>
       </c>
       <c r="C62" t="n">
-        <v>8.447846338415992</v>
+        <v>8.432394882910387</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7295,22 +7311,22 @@
         <v>14.45999953470718</v>
       </c>
       <c r="K62" t="n">
-        <v>1.526392555733058</v>
+        <v>1.340696642907835</v>
       </c>
       <c r="L62" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M62" t="n">
-        <v>55.93220338983051</v>
+        <v>56.14035087719298</v>
       </c>
       <c r="N62" t="n">
-        <v>14.85340212793895</v>
+        <v>14.40118179846843</v>
       </c>
       <c r="O62" t="n">
         <v>6</v>
       </c>
       <c r="P62" t="n">
-        <v>4.406349257225073</v>
+        <v>4.597662648314005</v>
       </c>
       <c r="Q62" t="n">
         <v>29</v>
@@ -7376,7 +7392,7 @@
         <v>46238</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1070305889974221</v>
+        <v>0.1072449203481384</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7404,7 +7420,7 @@
         <v>33.28434552774222</v>
       </c>
       <c r="K63" t="n">
-        <v>7.259558350819129</v>
+        <v>7.474348218219662</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
@@ -7439,16 +7455,16 @@
         <v>66.66666666666667</v>
       </c>
       <c r="X63" t="n">
-        <v>10.20972019420772</v>
+        <v>10.21389301022846</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.676861748845671</v>
+        <v>2.485661940781414</v>
       </c>
       <c r="Z63" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA63" t="n">
-        <v>64.28571428571429</v>
+        <v>60</v>
       </c>
       <c r="AB63" t="n">
         <v>11.24234270242617</v>
@@ -7457,7 +7473,7 @@
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>7.524560328352814</v>
+        <v>7.705880190311365</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7491,7 +7507,7 @@
         <v>46238</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1612818471474259</v>
+        <v>0.1583439781524143</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7516,25 +7532,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>22.40226642575713</v>
+        <v>24.02447184067135</v>
       </c>
       <c r="K64" t="n">
-        <v>0.3926729124407835</v>
+        <v>0.6684517361806197</v>
       </c>
       <c r="L64" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M64" t="n">
-        <v>63.88888888888889</v>
+        <v>69.6969696969697</v>
       </c>
       <c r="N64" t="n">
-        <v>16.19270505080708</v>
+        <v>16.28257099681413</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.589306125535253</v>
+        <v>4.302786214663334</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7600,7 +7616,7 @@
         <v>46238</v>
       </c>
       <c r="C65" t="n">
-        <v>6.234689332521074</v>
+        <v>6.255953809640499</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7619,7 +7635,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -7632,22 +7648,22 @@
         <v>28.12381406175567</v>
       </c>
       <c r="K65" t="n">
-        <v>2.724555834461184</v>
+        <v>3.074915547775325</v>
       </c>
       <c r="L65" t="n">
         <v>16</v>
       </c>
       <c r="M65" t="n">
-        <v>81.25</v>
+        <v>75</v>
       </c>
       <c r="N65" t="n">
-        <v>14.72106682780091</v>
+        <v>15.2018122320435</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>7.082478095367062</v>
+        <v>6.718496362982607</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7713,7 +7729,7 @@
         <v>46238</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4314867722471822</v>
+        <v>0.4285591038167132</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7812,16 +7828,16 @@
         <v>46238</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02712562896986379</v>
+        <v>0.02880893014859659</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7837,25 +7853,21 @@
         <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>18.7880380179217</v>
+        <v>18.78496312965017</v>
       </c>
       <c r="K67" t="n">
-        <v>0.7812492370605328</v>
+        <v>7.031252508544994</v>
       </c>
       <c r="L67" t="n">
-        <v>5</v>
-      </c>
-      <c r="M67" t="n">
-        <v>60</v>
-      </c>
-      <c r="N67" t="n">
-        <v>13.17502365156353</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>3.193799230815486</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7901,7 +7913,7 @@
         <v>46238</v>
       </c>
       <c r="C68" t="n">
-        <v>3.625161561197397</v>
+        <v>3.68628141818702</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7958,13 +7970,13 @@
         <v>80</v>
       </c>
       <c r="X68" t="n">
-        <v>107.0594361964295</v>
+        <v>108.240461684886</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.322949631728055</v>
+        <v>1.239434901408454</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA68" t="inlineStr"/>
       <c r="AB68" t="inlineStr"/>
@@ -7972,7 +7984,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>5.812061632561328</v>
+        <v>6.845409492992016</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8006,16 +8018,16 @@
         <v>46238</v>
       </c>
       <c r="C69" t="n">
-        <v>0.3984734151421189</v>
+        <v>0.4029044506027525</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -8025,7 +8037,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H69" t="n">
@@ -8038,22 +8050,22 @@
         <v>29.4573350207784</v>
       </c>
       <c r="K69" t="n">
-        <v>1.928085051287987</v>
+        <v>3.061528192370933</v>
       </c>
       <c r="L69" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M69" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="N69" t="n">
-        <v>16.55531405137488</v>
+        <v>14.18660243657942</v>
       </c>
       <c r="O69" t="n">
         <v>3</v>
       </c>
       <c r="P69" t="n">
-        <v>1.051638464680904</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8103,7 +8115,7 @@
         <v>46238</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4054125282729914</v>
+        <v>0.4167832019083328</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8131,22 +8143,22 @@
         <v>20.66985845799666</v>
       </c>
       <c r="K70" t="n">
-        <v>3.998482311486296</v>
+        <v>6.915345305267429</v>
       </c>
       <c r="L70" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="M70" t="n">
-        <v>40.90909090909091</v>
+        <v>62.5</v>
       </c>
       <c r="N70" t="n">
-        <v>12.02462524087466</v>
+        <v>8.782275786017548</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>3.847669311681634</v>
+        <v>1.014498612557113</v>
       </c>
       <c r="Q70" t="n">
         <v>30</v>
@@ -8212,7 +8224,7 @@
         <v>46238</v>
       </c>
       <c r="C71" t="n">
-        <v>3.309747261069855</v>
+        <v>3.269918713946546</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8229,7 +8241,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.67: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H71" t="n">
         <v>5</v>
       </c>
@@ -8240,22 +8256,22 @@
         <v>20.51701021225919</v>
       </c>
       <c r="K71" t="n">
-        <v>5.648493622483541</v>
+        <v>4.377150019833476</v>
       </c>
       <c r="L71" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M71" t="n">
-        <v>72.41379310344827</v>
+        <v>76.66666666666667</v>
       </c>
       <c r="N71" t="n">
-        <v>12.00056970406572</v>
+        <v>11.83084085922615</v>
       </c>
       <c r="O71" t="n">
         <v>6</v>
       </c>
       <c r="P71" t="n">
-        <v>0.3327130993201921</v>
+        <v>1.554794301107254</v>
       </c>
       <c r="Q71" t="n">
         <v>43</v>
@@ -8321,7 +8337,7 @@
         <v>46238</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07548915393803918</v>
+        <v>0.079066844577105</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8349,16 +8365,16 @@
         <v>20.36571476939619</v>
       </c>
       <c r="K72" t="n">
-        <v>5.538495734182591</v>
+        <v>10.54032803129894</v>
       </c>
       <c r="L72" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="M72" t="n">
-        <v>50</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N72" t="n">
-        <v>13.54970683032341</v>
+        <v>15.39469661418315</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
@@ -8391,10 +8407,10 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>15.95517327895241</v>
+        <v>11.97199988071029</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr"/>
@@ -8436,7 +8452,7 @@
         <v>46238</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07065280112580734</v>
+        <v>0.07002462415336658</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8461,10 +8477,10 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>20.48362439310756</v>
+        <v>21.1948589936776</v>
       </c>
       <c r="K73" t="n">
-        <v>0.5988021119437636</v>
+        <v>0.6042290139739448</v>
       </c>
       <c r="L73" t="n">
         <v>26</v>
@@ -8473,13 +8489,13 @@
         <v>73.07692307692308</v>
       </c>
       <c r="N73" t="n">
-        <v>14.86908195608804</v>
+        <v>15.33662112876341</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>9.345238403132106</v>
+        <v>9.33933998412828</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8545,7 +8561,7 @@
         <v>46238</v>
       </c>
       <c r="C74" t="n">
-        <v>4.809016631810345</v>
+        <v>4.752422053710093</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8570,25 +8586,25 @@
         <v>10</v>
       </c>
       <c r="J74" t="n">
-        <v>18.27906859558925</v>
+        <v>18.3849409116933</v>
       </c>
       <c r="K74" t="n">
-        <v>1.644443088888914</v>
+        <v>0.5785505418984371</v>
       </c>
       <c r="L74" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="M74" t="n">
-        <v>66.66666666666667</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="N74" t="n">
-        <v>22.85638561467399</v>
+        <v>21.34949645792945</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>6.252734254791581</v>
+        <v>7.378759604424778</v>
       </c>
       <c r="Q74" t="n">
         <v>35</v>
@@ -8615,7 +8631,7 @@
         <v>95.98093909010421</v>
       </c>
       <c r="Y74" t="n">
-        <v>16.93521438693378</v>
+        <v>17.91275654506719</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -8660,7 +8676,7 @@
         <v>46238</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1478241730755747</v>
+        <v>0.146357777362474</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8688,13 +8704,17 @@
         <v>19.1703426786477</v>
       </c>
       <c r="K75" t="n">
-        <v>13.43869314039821</v>
+        <v>12.31339671654617</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M75" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="N75" t="n">
+        <v>9.794958843326418</v>
+      </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
@@ -8723,25 +8743,25 @@
         <v>100</v>
       </c>
       <c r="X75" t="n">
-        <v>14.084147344171</v>
+        <v>14.08846685570693</v>
       </c>
       <c r="Y75" t="n">
-        <v>0.565770283425604</v>
+        <v>1.555871674045539</v>
       </c>
       <c r="Z75" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA75" t="n">
-        <v>53.33333333333334</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="AB75" t="n">
-        <v>12.1869143909037</v>
+        <v>12.90413460503942</v>
       </c>
       <c r="AC75" t="n">
         <v>10</v>
       </c>
       <c r="AD75" t="n">
-        <v>9.487909488981373</v>
+        <v>8.577584534036852</v>
       </c>
       <c r="AE75" t="n">
         <v>4</v>
@@ -8775,7 +8795,7 @@
         <v>46238</v>
       </c>
       <c r="C76" t="n">
-        <v>1.816786400906899</v>
+        <v>1.805289495751353</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8803,22 +8823,22 @@
         <v>20.88959101184773</v>
       </c>
       <c r="K76" t="n">
-        <v>4.824568206945878</v>
+        <v>4.161222137179665</v>
       </c>
       <c r="L76" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M76" t="n">
-        <v>57.89473684210526</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N76" t="n">
-        <v>11.67635417336743</v>
+        <v>11.23672238262284</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>4.937231682974108</v>
+        <v>5.605519734715392</v>
       </c>
       <c r="Q76" t="n">
         <v>42</v>
@@ -8884,7 +8904,7 @@
         <v>46238</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5059245262599383</v>
+        <v>0.5051025660010202</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8912,16 +8932,16 @@
         <v>21.60005234598619</v>
       </c>
       <c r="K77" t="n">
-        <v>4.19821000966496</v>
+        <v>4.028922332881435</v>
       </c>
       <c r="L77" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M77" t="n">
-        <v>58.33333333333334</v>
+        <v>64</v>
       </c>
       <c r="N77" t="n">
-        <v>16.78554035367463</v>
+        <v>16.74808530813116</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -8993,7 +9013,7 @@
         <v>46238</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05319987799068343</v>
+        <v>0.0529916083199159</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9010,7 +9030,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H78" t="n">
         <v>5</v>
       </c>
@@ -9021,16 +9045,16 @@
         <v>20.32485186011925</v>
       </c>
       <c r="K78" t="n">
-        <v>12.82249386869903</v>
+        <v>12.38081045624231</v>
       </c>
       <c r="L78" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M78" t="n">
-        <v>73.33333333333333</v>
+        <v>75</v>
       </c>
       <c r="N78" t="n">
-        <v>16.51077214169325</v>
+        <v>15.49144004111212</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
@@ -9063,22 +9087,22 @@
         <v>23.16536029857119</v>
       </c>
       <c r="Y78" t="n">
-        <v>8.397544898013132</v>
+        <v>8.756154990482312</v>
       </c>
       <c r="Z78" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA78" t="n">
-        <v>46.66666666666666</v>
+        <v>43.75</v>
       </c>
       <c r="AB78" t="n">
-        <v>15.78157380146375</v>
+        <v>16.0191368974861</v>
       </c>
       <c r="AC78" t="n">
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.749358246132982</v>
+        <v>1.363209769807416</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9112,7 +9136,7 @@
         <v>46238</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8886271862329258</v>
+        <v>0.8798289355756355</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9140,22 +9164,22 @@
         <v>12.92020537241256</v>
       </c>
       <c r="K79" t="n">
-        <v>2.903546908537602</v>
+        <v>1.884704346378752</v>
       </c>
       <c r="L79" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="M79" t="n">
-        <v>46.55172413793103</v>
+        <v>58.06451612903226</v>
       </c>
       <c r="N79" t="n">
-        <v>10.20772267382851</v>
+        <v>12.35163766441931</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>2.037299154834549</v>
+        <v>3.057667658366214</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9221,11 +9245,11 @@
         <v>46238</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1341562179672859</v>
+        <v>0.1328995937493785</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -9235,7 +9259,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -9246,10 +9270,10 @@
         <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>68.88536831152055</v>
+        <v>69.29504130463948</v>
       </c>
       <c r="K80" t="n">
-        <v>1.544503358116223</v>
+        <v>1.935489736732765</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9260,7 +9284,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>8.326887583529619</v>
+        <v>7.911386195421577</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9283,27 +9307,17 @@
       <c r="W80" t="n">
         <v>75.9493670886076</v>
       </c>
-      <c r="X80" t="n">
-        <v>10.5095514001583</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>8.11246442362199</v>
-      </c>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA80" t="n">
-        <v>57.89473684210526</v>
-      </c>
-      <c r="AB80" t="n">
-        <v>10.08160658985287</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
-      <c r="AD80" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD80" t="inlineStr"/>
       <c r="AE80" t="n">
         <v>26</v>
       </c>
@@ -9336,11 +9350,11 @@
         <v>46238</v>
       </c>
       <c r="C81" t="n">
-        <v>1.060843445409956</v>
+        <v>1.075603519108305</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9350,7 +9364,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -9361,25 +9375,25 @@
         <v>10</v>
       </c>
       <c r="J81" t="n">
-        <v>11.87985607284572</v>
+        <v>11.87651962350458</v>
       </c>
       <c r="K81" t="n">
-        <v>1.102202831936472</v>
+        <v>2.50500994323315</v>
       </c>
       <c r="L81" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M81" t="n">
-        <v>51.92307692307692</v>
+        <v>51.02040816326531</v>
       </c>
       <c r="N81" t="n">
-        <v>12.31903901763035</v>
+        <v>13.07620610710466</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>8.800794561177327</v>
+        <v>7.311828037397938</v>
       </c>
       <c r="Q81" t="n">
         <v>31</v>
@@ -9406,7 +9420,7 @@
         <v>27.31228182970742</v>
       </c>
       <c r="Y81" t="n">
-        <v>10.90859335097414</v>
+        <v>9.669017677750247</v>
       </c>
       <c r="Z81" t="n">
         <v>9</v>
@@ -9415,13 +9429,13 @@
         <v>55.55555555555556</v>
       </c>
       <c r="AB81" t="n">
-        <v>9.529724010146259</v>
+        <v>9.276812191444455</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>0.3664106309272608</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9455,7 +9469,7 @@
         <v>46238</v>
       </c>
       <c r="C82" t="n">
-        <v>5.130739282074678</v>
+        <v>5.12672792561685</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9472,11 +9486,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>5</v>
       </c>
@@ -9487,13 +9497,13 @@
         <v>15.23084223335499</v>
       </c>
       <c r="K82" t="n">
-        <v>12.85860509657892</v>
+        <v>12.77036906089546</v>
       </c>
       <c r="L82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M82" t="n">
-        <v>80</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N82" t="n">
         <v>8.430896867829917</v>
@@ -9529,7 +9539,7 @@
         <v>15.04024401260009</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.896413672229535</v>
+        <v>1.973113818722438</v>
       </c>
       <c r="Z82" t="n">
         <v>12</v>
@@ -9544,7 +9554,7 @@
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>2.144250181376905</v>
+        <v>2.067683938801568</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9578,7 +9588,7 @@
         <v>46238</v>
       </c>
       <c r="C83" t="n">
-        <v>5.850935267365898</v>
+        <v>5.803842862053034</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9606,22 +9616,22 @@
         <v>14.0949513048101</v>
       </c>
       <c r="K83" t="n">
-        <v>8.104588833446646</v>
+        <v>7.234487750305263</v>
       </c>
       <c r="L83" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="M83" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N83" t="n">
-        <v>11.46594952641528</v>
+        <v>11.55732548563121</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>1.753312405150131</v>
+        <v>2.578939208563402</v>
       </c>
       <c r="Q83" t="n">
         <v>44</v>
@@ -9687,7 +9697,7 @@
         <v>46238</v>
       </c>
       <c r="C84" t="n">
-        <v>2.199489020717132</v>
+        <v>2.226909304243826</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9715,16 +9725,16 @@
         <v>14.10735630446007</v>
       </c>
       <c r="K84" t="n">
-        <v>5.29515155325313</v>
+        <v>6.607830490215938</v>
       </c>
       <c r="L84" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M84" t="n">
-        <v>65.85365853658537</v>
+        <v>63.88888888888889</v>
       </c>
       <c r="N84" t="n">
-        <v>11.13597975333524</v>
+        <v>9.240299333392311</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
@@ -9796,7 +9806,7 @@
         <v>46238</v>
       </c>
       <c r="C85" t="n">
-        <v>6.686783162703883</v>
+        <v>6.655493716810817</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9824,22 +9834,22 @@
         <v>15.13449360257271</v>
       </c>
       <c r="K85" t="n">
-        <v>3.768115174601649</v>
+        <v>3.282553321289172</v>
       </c>
       <c r="L85" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M85" t="n">
-        <v>50</v>
+        <v>52.08333333333334</v>
       </c>
       <c r="N85" t="n">
-        <v>14.0272000326463</v>
+        <v>13.46665735539501</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>4.07821306022349</v>
+        <v>4.567515545472522</v>
       </c>
       <c r="Q85" t="n">
         <v>34</v>
@@ -9905,7 +9915,7 @@
         <v>46238</v>
       </c>
       <c r="C86" t="n">
-        <v>3.482174001676542</v>
+        <v>3.505436910878696</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9965,22 +9975,22 @@
         <v>39.94948119773951</v>
       </c>
       <c r="Y86" t="n">
-        <v>2.576803005653405</v>
+        <v>1.925960461664544</v>
       </c>
       <c r="Z86" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AA86" t="n">
-        <v>33.33333333333334</v>
+        <v>37.5</v>
       </c>
       <c r="AB86" t="n">
-        <v>17.9558912884659</v>
+        <v>14.29736215071794</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>3.513739129855542</v>
+        <v>4.154044798718615</v>
       </c>
       <c r="AE86" t="n">
         <v>51</v>
@@ -10014,7 +10024,7 @@
         <v>46238</v>
       </c>
       <c r="C87" t="n">
-        <v>5.635402162278745</v>
+        <v>5.688186573135311</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10031,7 +10041,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H87" t="n">
         <v>5</v>
       </c>
@@ -10042,22 +10056,22 @@
         <v>29.54558799520699</v>
       </c>
       <c r="K87" t="n">
-        <v>3.755617137563405</v>
+        <v>4.727451793894488</v>
       </c>
       <c r="L87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M87" t="n">
-        <v>60</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N87" t="n">
-        <v>9.533690881227427</v>
+        <v>9.637889717228306</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>1.199340235032054</v>
+        <v>0.2602452379361742</v>
       </c>
       <c r="Q87" t="n">
         <v>47</v>
@@ -10123,7 +10137,7 @@
         <v>46238</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9605416885069691</v>
+        <v>0.9584752473674266</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10151,22 +10165,22 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>7.611021949035135</v>
+        <v>7.379515242471113</v>
       </c>
       <c r="L88" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M88" t="n">
-        <v>60.8695652173913</v>
+        <v>60</v>
       </c>
       <c r="N88" t="n">
-        <v>12.1999542095487</v>
+        <v>12.0185275795009</v>
       </c>
       <c r="O88" t="n">
         <v>10</v>
       </c>
       <c r="P88" t="n">
-        <v>2.220012418520012</v>
+        <v>2.440395406527629</v>
       </c>
       <c r="Q88" t="n">
         <v>44</v>
@@ -10232,7 +10246,7 @@
         <v>46238</v>
       </c>
       <c r="C89" t="n">
-        <v>1.949260310653967</v>
+        <v>1.949334114531143</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10260,7 +10274,7 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>5.880613985551109</v>
+        <v>5.884622890768787</v>
       </c>
       <c r="L89" t="n">
         <v>39</v>
@@ -10302,7 +10316,7 @@
         <v>28.7873334490923</v>
       </c>
       <c r="Y89" t="n">
-        <v>14.99284918914936</v>
+        <v>14.98963060552393</v>
       </c>
       <c r="Z89" t="n">
         <v>3</v>
@@ -10351,7 +10365,7 @@
         <v>46238</v>
       </c>
       <c r="C90" t="n">
-        <v>2.659993931075602</v>
+        <v>2.641169038383991</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10379,22 +10393,22 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>4.857622980078546</v>
+        <v>4.115541023636204</v>
       </c>
       <c r="L90" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="M90" t="n">
         <v>66.66666666666667</v>
       </c>
       <c r="N90" t="n">
-        <v>14.51148757910913</v>
+        <v>15.20642055656773</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>2.996803599599485</v>
+        <v>3.73091177183813</v>
       </c>
       <c r="Q90" t="n">
         <v>42</v>
@@ -10421,13 +10435,13 @@
         <v>33.24184775233741</v>
       </c>
       <c r="Y90" t="n">
-        <v>12.53481310708858</v>
+        <v>13.15380803721796</v>
       </c>
       <c r="Z90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA90" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AB90" t="n">
         <v>10.631003022771</v>
@@ -10470,16 +10484,16 @@
         <v>46238</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2348785171771856</v>
+        <v>0.2329948494465224</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -10498,22 +10512,22 @@
         <v>14.9000517126033</v>
       </c>
       <c r="K91" t="n">
-        <v>3.593852525161179</v>
+        <v>2.763055398876868</v>
       </c>
       <c r="L91" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M91" t="n">
-        <v>60.41666666666666</v>
+        <v>56</v>
       </c>
       <c r="N91" t="n">
-        <v>14.54651963345206</v>
+        <v>15.9752496989453</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>0.2305737214638448</v>
       </c>
       <c r="Q91" t="n">
         <v>47</v>
@@ -10579,7 +10593,7 @@
         <v>46238</v>
       </c>
       <c r="C92" t="n">
-        <v>1.10710422561993</v>
+        <v>1.101889039316879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10607,7 +10621,7 @@
         <v>23.07989300517391</v>
       </c>
       <c r="K92" t="n">
-        <v>5.072929970720819</v>
+        <v>4.577967624336554</v>
       </c>
       <c r="L92" t="n">
         <v>20</v>
@@ -10616,13 +10630,13 @@
         <v>65</v>
       </c>
       <c r="N92" t="n">
-        <v>14.6092261303582</v>
+        <v>14.80197958437172</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>2.785750840006873</v>
+        <v>3.272230713027469</v>
       </c>
       <c r="Q92" t="n">
         <v>56</v>
@@ -10688,7 +10702,7 @@
         <v>46238</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0416346880373879</v>
+        <v>0.04142598047956436</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10716,22 +10730,22 @@
         <v>19.49655531533526</v>
       </c>
       <c r="K93" t="n">
-        <v>0.9728248348112922</v>
+        <v>0.4666653636776763</v>
       </c>
       <c r="L93" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M93" t="n">
-        <v>61.22448979591837</v>
+        <v>62.5</v>
       </c>
       <c r="N93" t="n">
-        <v>14.688601813055</v>
+        <v>15.54303520799231</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>4.978740738820608</v>
+        <v>5.507632423443432</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10797,7 +10811,7 @@
         <v>46238</v>
       </c>
       <c r="C94" t="n">
-        <v>6.176863377497692</v>
+        <v>6.14555462476449</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10825,22 +10839,22 @@
         <v>11.31569733043036</v>
       </c>
       <c r="K94" t="n">
-        <v>2.680545224182063</v>
+        <v>2.160086926100568</v>
       </c>
       <c r="L94" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="M94" t="n">
-        <v>36.36363636363637</v>
+        <v>32.69230769230769</v>
       </c>
       <c r="N94" t="n">
-        <v>11.46351092365998</v>
+        <v>13.21428865713718</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>5.180586803667619</v>
+        <v>5.71643314881265</v>
       </c>
       <c r="Q94" t="n">
         <v>40</v>
@@ -10867,7 +10881,7 @@
         <v>46.65531127586331</v>
       </c>
       <c r="Y94" t="n">
-        <v>8.938474490622051</v>
+        <v>9.400039302961527</v>
       </c>
       <c r="Z94" t="n">
         <v>2</v>
@@ -10912,7 +10926,7 @@
         <v>46238</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1392028421432502</v>
+        <v>0.1392081127114796</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10940,7 +10954,7 @@
         <v>23.400044414021</v>
       </c>
       <c r="K95" t="n">
-        <v>0.4079151691108285</v>
+        <v>0.4117168642452373</v>
       </c>
       <c r="L95" t="n">
         <v>23</v>
@@ -10955,7 +10969,7 @@
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>5.56936653994935</v>
+        <v>5.565369570674727</v>
       </c>
       <c r="Q95" t="n">
         <v>22</v>
@@ -11021,7 +11035,7 @@
         <v>46238</v>
       </c>
       <c r="C96" t="n">
-        <v>0.132894562028433</v>
+        <v>0.1314276010428676</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11049,22 +11063,22 @@
         <v>12.79622946674051</v>
       </c>
       <c r="K96" t="n">
-        <v>2.715825079417811</v>
+        <v>1.581993072360799</v>
       </c>
       <c r="L96" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="M96" t="n">
-        <v>57.8125</v>
+        <v>60.27397260273973</v>
       </c>
       <c r="N96" t="n">
-        <v>13.90716148726076</v>
+        <v>12.88642560075273</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>7.091580012086962</v>
+        <v>8.286908607554832</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11091,16 +11105,16 @@
         <v>16.74415231729489</v>
       </c>
       <c r="Y96" t="n">
-        <v>10.42792759640029</v>
+        <v>11.41667185806693</v>
       </c>
       <c r="Z96" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AA96" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="AB96" t="n">
-        <v>19.38302326887769</v>
+        <v>16.42948776937994</v>
       </c>
       <c r="AC96" t="n">
         <v>8</v>
@@ -11140,7 +11154,7 @@
         <v>46238</v>
       </c>
       <c r="C97" t="n">
-        <v>1.843070925917527</v>
+        <v>1.832626501115223</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11168,22 +11182,22 @@
         <v>23.59665213438843</v>
       </c>
       <c r="K97" t="n">
-        <v>3.119490794134161</v>
+        <v>2.535127082403932</v>
       </c>
       <c r="L97" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M97" t="n">
-        <v>54.54545454545455</v>
+        <v>54.16666666666666</v>
       </c>
       <c r="N97" t="n">
-        <v>12.07307419524786</v>
+        <v>11.73441643678193</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>0.8538727248214251</v>
+        <v>1.428654705249266</v>
       </c>
       <c r="Q97" t="n">
         <v>51</v>
@@ -11249,7 +11263,7 @@
         <v>46238</v>
       </c>
       <c r="C98" t="n">
-        <v>0.637136870276643</v>
+        <v>0.6316936409985818</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11277,22 +11291,22 @@
         <v>19.60032989595409</v>
       </c>
       <c r="K98" t="n">
-        <v>6.118137570982229</v>
+        <v>5.211542174754591</v>
       </c>
       <c r="L98" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M98" t="n">
-        <v>54.54545454545455</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="N98" t="n">
-        <v>18.01422758014704</v>
+        <v>18.85960633705799</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>3.658057442273899</v>
+        <v>4.551266644577723</v>
       </c>
       <c r="Q98" t="n">
         <v>48</v>
@@ -11358,7 +11372,7 @@
         <v>46238</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4756447822555336</v>
+        <v>0.4773450629692915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11386,22 +11400,22 @@
         <v>28.77817890954801</v>
       </c>
       <c r="K99" t="n">
-        <v>2.326961670915439</v>
+        <v>2.692748421695002</v>
       </c>
       <c r="L99" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M99" t="n">
-        <v>70</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="N99" t="n">
-        <v>13.56231575344962</v>
+        <v>12.20882658747631</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>1.634992676187408</v>
+        <v>1.272973601735661</v>
       </c>
       <c r="Q99" t="n">
         <v>35</v>
@@ -11467,7 +11481,7 @@
         <v>46238</v>
       </c>
       <c r="C100" t="n">
-        <v>323.2641119175578</v>
+        <v>322.0503989509643</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11499,7 +11513,7 @@
         <v>25.87300653788257</v>
       </c>
       <c r="K100" t="n">
-        <v>5.474450545097653</v>
+        <v>5.07844089369669</v>
       </c>
       <c r="L100" t="n">
         <v>12</v>
@@ -11508,7 +11522,7 @@
         <v>75</v>
       </c>
       <c r="N100" t="n">
-        <v>11.45661960612005</v>
+        <v>12.43291671760379</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11580,7 +11594,7 @@
         <v>46238</v>
       </c>
       <c r="C101" t="n">
-        <v>321.1859711241724</v>
+        <v>321.2044364472218</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11608,7 +11622,7 @@
         <v>14.61847018515478</v>
       </c>
       <c r="K101" t="n">
-        <v>1.709654367596736</v>
+        <v>1.715501763790805</v>
       </c>
       <c r="L101" t="n">
         <v>35</v>
@@ -11623,7 +11637,7 @@
         <v>2</v>
       </c>
       <c r="P101" t="n">
-        <v>0.2854651647462125</v>
+        <v>0.2796999781506937</v>
       </c>
       <c r="Q101" t="n">
         <v>29</v>
@@ -11689,7 +11703,7 @@
         <v>46238</v>
       </c>
       <c r="C102" t="n">
-        <v>386.8011808561735</v>
+        <v>386.6263650163695</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11788,7 +11802,7 @@
         <v>46238</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7094719344132854</v>
+        <v>0.7094987967975557</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11816,7 +11830,7 @@
         <v>31.27238030517686</v>
       </c>
       <c r="K103" t="n">
-        <v>9.115607537388293</v>
+        <v>9.119738927563681</v>
       </c>
       <c r="L103" t="n">
         <v>1</v>
@@ -11827,7 +11841,7 @@
         <v>10</v>
       </c>
       <c r="P103" t="n">
-        <v>0.8105095893900183</v>
+        <v>0.8066927955359793</v>
       </c>
       <c r="Q103" t="n">
         <v>43</v>
@@ -11854,7 +11868,7 @@
         <v>10.91420766588502</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.621613827792734</v>
+        <v>1.617888975709003</v>
       </c>
       <c r="Z103" t="n">
         <v>54</v>
@@ -11869,7 +11883,7 @@
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>6.48352389217095</v>
+        <v>6.48706452610599</v>
       </c>
       <c r="AE103" t="n">
         <v>34</v>
@@ -11903,7 +11917,7 @@
         <v>46238</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04878407694779304</v>
+        <v>0.04899620798650776</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11922,7 +11936,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %76.19: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -11932,25 +11946,25 @@
         <v>10</v>
       </c>
       <c r="J104" t="n">
-        <v>27.65580276361549</v>
+        <v>27.73688559743085</v>
       </c>
       <c r="K104" t="n">
-        <v>0.7526957659305999</v>
+        <v>1.304346550094482</v>
       </c>
       <c r="L104" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M104" t="n">
-        <v>80</v>
+        <v>76.19047619047619</v>
       </c>
       <c r="N104" t="n">
-        <v>14.63571482376176</v>
+        <v>15.30180212803625</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>3.223044514474882</v>
+        <v>2.660945499088263</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>

--- a/TDA_Result.xlsx
+++ b/TDA_Result.xlsx
@@ -453,7 +453,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -679,7 +679,7 @@
         <v>46238</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4529521035802819</v>
+        <v>0.4530646230418026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>14.94856954517825</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.900808883080954</v>
+        <v>4.877184950901469</v>
       </c>
       <c r="Z2" t="n">
         <v>34</v>
@@ -754,7 +754,7 @@
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.258903761977072</v>
+        <v>3.282929597370154</v>
       </c>
       <c r="AE2" t="n">
         <v>43</v>
@@ -788,7 +788,7 @@
         <v>46238</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7515556291312734</v>
+        <v>0.7479562640643116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,22 +848,22 @@
         <v>12.13279917920569</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.217798829345296</v>
+        <v>1.690888498758369</v>
       </c>
       <c r="Z3" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="AA3" t="n">
-        <v>44.26229508196721</v>
+        <v>42.1875</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.50485684922246</v>
+        <v>10.77839607848096</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>8.890469200501716</v>
+        <v>8.452025833980493</v>
       </c>
       <c r="AE3" t="n">
         <v>38</v>
@@ -897,7 +897,7 @@
         <v>46238</v>
       </c>
       <c r="C4" t="n">
-        <v>1.38366984791598</v>
+        <v>1.428184182163316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -925,16 +925,16 @@
         <v>27.63389482946404</v>
       </c>
       <c r="K4" t="n">
-        <v>7.133262492417836</v>
+        <v>10.57986925542409</v>
       </c>
       <c r="L4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>56.25</v>
+        <v>50</v>
       </c>
       <c r="N4" t="n">
-        <v>18.41684522661439</v>
+        <v>15.39789546009553</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -963,17 +963,27 @@
       <c r="W4" t="n">
         <v>61.64383561643836</v>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>11.23129951738115</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.5856537366582315</v>
+      </c>
       <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>33.92857142857143</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>12.42949452781888</v>
+      </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AD4" t="n">
+        <v>9.469806539192859</v>
+      </c>
       <c r="AE4" t="n">
         <v>45</v>
       </c>
@@ -1006,7 +1016,7 @@
         <v>46238</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2618037772819932</v>
+        <v>0.2633411813657943</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,22 +1076,22 @@
         <v>16.70172291026088</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.290609391884305</v>
+        <v>5.74031481131283</v>
       </c>
       <c r="Z5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AA5" t="n">
-        <v>55.55555555555556</v>
+        <v>37.93103448275862</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.00985318049628</v>
+        <v>17.56925120345615</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.95839796208689</v>
+        <v>4.519095496829017</v>
       </c>
       <c r="AE5" t="n">
         <v>45</v>
@@ -1115,7 +1125,7 @@
         <v>46238</v>
       </c>
       <c r="C6" t="n">
-        <v>1.958796998116376</v>
+        <v>1.98767897162422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,11 +1142,7 @@
           <t>SATMA_BEKLE</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>5</v>
       </c>
@@ -1147,16 +1153,16 @@
         <v>23.73506360720576</v>
       </c>
       <c r="K6" t="n">
-        <v>3.168588992209287</v>
+        <v>4.689784122169161</v>
       </c>
       <c r="L6" t="n">
         <v>20</v>
       </c>
       <c r="M6" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="N6" t="n">
-        <v>12.86926775044043</v>
+        <v>9.966151438936262</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
@@ -1189,7 +1195,7 @@
         <v>44.49622708587002</v>
       </c>
       <c r="Y6" t="n">
-        <v>21.31854122774828</v>
+        <v>20.1584027294741</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1234,16 +1240,16 @@
         <v>46238</v>
       </c>
       <c r="C7" t="n">
-        <v>2.142795639576391</v>
+        <v>2.176981730826526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1262,22 +1268,22 @@
         <v>11.35312764557068</v>
       </c>
       <c r="K7" t="n">
-        <v>2.65838749538343</v>
+        <v>4.296196037500311</v>
       </c>
       <c r="L7" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="M7" t="n">
-        <v>54.41176470588236</v>
+        <v>51.85185185185185</v>
       </c>
       <c r="N7" t="n">
-        <v>12.8575295178231</v>
+        <v>13.8868159829741</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3327662872475434</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1304,22 +1310,22 @@
         <v>13.79329344082609</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.996550275852023</v>
+        <v>7.544684228111742</v>
       </c>
       <c r="Z7" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AA7" t="n">
-        <v>61.11111111111111</v>
+        <v>56.52173913043478</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.263093745287698</v>
+        <v>8.960300666112964</v>
       </c>
       <c r="AC7" t="n">
         <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.102650204129252</v>
+        <v>2.655678314858789</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1353,7 +1359,7 @@
         <v>46238</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3299358408260801</v>
+        <v>0.3319108321222949</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1387,7 @@
         <v>22.10694516187944</v>
       </c>
       <c r="K8" t="n">
-        <v>4.902374743685245</v>
+        <v>5.530318881407026</v>
       </c>
       <c r="L8" t="n">
         <v>4</v>
@@ -1396,7 +1402,7 @@
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.952864760100415</v>
+        <v>2.340257420588632</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1462,7 +1468,7 @@
         <v>46238</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5711317799376231</v>
+        <v>0.5796871048094565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,16 +1496,16 @@
         <v>11.07138721870453</v>
       </c>
       <c r="K9" t="n">
-        <v>2.76348301635958</v>
+        <v>4.302838753597849</v>
       </c>
       <c r="L9" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M9" t="n">
-        <v>46.15384615384615</v>
+        <v>40.54054054054054</v>
       </c>
       <c r="N9" t="n">
-        <v>14.53643886531697</v>
+        <v>15.33035988439627</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1571,7 +1577,7 @@
         <v>46238</v>
       </c>
       <c r="C10" t="n">
-        <v>2.035550749088603</v>
+        <v>2.04552148138048</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,22 +1605,22 @@
         <v>10.23694539327734</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7896583409596314</v>
+        <v>1.283356030175908</v>
       </c>
       <c r="L10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>40.47619047619047</v>
+        <v>41.86046511627907</v>
       </c>
       <c r="N10" t="n">
-        <v>9.764403333337537</v>
+        <v>9.946203451885726</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>9.138181248598798</v>
+        <v>8.606195836586528</v>
       </c>
       <c r="Q10" t="n">
         <v>44</v>
@@ -1680,7 +1686,7 @@
         <v>46238</v>
       </c>
       <c r="C11" t="n">
-        <v>7.275831993733152</v>
+        <v>7.367032378956433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1703,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>5</v>
       </c>
@@ -1708,16 +1718,16 @@
         <v>20.56423081971027</v>
       </c>
       <c r="K11" t="n">
-        <v>4.250225325534762</v>
+        <v>5.556970824536367</v>
       </c>
       <c r="L11" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M11" t="n">
-        <v>68.42105263157895</v>
+        <v>81.25</v>
       </c>
       <c r="N11" t="n">
-        <v>14.43081743608645</v>
+        <v>14.50308943650603</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1789,11 +1799,11 @@
         <v>46238</v>
       </c>
       <c r="C12" t="n">
-        <v>6.198125665181637</v>
+        <v>6.336384023299431</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1803,14 +1813,10 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BAND</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>5</v>
       </c>
@@ -1821,16 +1827,16 @@
         <v>20.08266526523165</v>
       </c>
       <c r="K12" t="n">
-        <v>7.907546288270773</v>
+        <v>10.31458367090165</v>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>83.33333333333333</v>
+        <v>50</v>
       </c>
       <c r="N12" t="n">
-        <v>28.65873508979989</v>
+        <v>30.74991940184407</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -1859,17 +1865,27 @@
       <c r="W12" t="n">
         <v>70.58823529411765</v>
       </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>10.86386790494764</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4954582989265099</v>
+      </c>
       <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>31.57894736842105</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>14.5203734855606</v>
+      </c>
       <c r="AC12" t="n">
         <v>2</v>
       </c>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>1.512033195020746</v>
+      </c>
       <c r="AE12" t="n">
         <v>5</v>
       </c>
@@ -1902,7 +1918,7 @@
         <v>46238</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3011269129906093</v>
+        <v>0.3012017170103529</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1930,7 +1946,7 @@
         <v>38.11781916800814</v>
       </c>
       <c r="K13" t="n">
-        <v>5.817488647845415</v>
+        <v>5.843775150873043</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1966,7 +1982,7 @@
         <v>35.74308703619145</v>
       </c>
       <c r="Y13" t="n">
-        <v>22.04576236016157</v>
+        <v>22.02639746755335</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2001,7 +2017,7 @@
         <v>46238</v>
       </c>
       <c r="C14" t="n">
-        <v>8.043369183823499</v>
+        <v>8.087434545920766</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,16 +2077,16 @@
         <v>14.33662537827827</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.044463500296083</v>
+        <v>6.535209320711344</v>
       </c>
       <c r="Z14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA14" t="n">
-        <v>37.5</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.56978199300831</v>
+        <v>11.18997592652526</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2110,21 +2126,21 @@
         <v>46238</v>
       </c>
       <c r="C15" t="n">
-        <v>11.34483052202033</v>
+        <v>11.63160287098617</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -2138,22 +2154,22 @@
         <v>19.49276356151121</v>
       </c>
       <c r="K15" t="n">
-        <v>6.817707124925354</v>
+        <v>9.517823686728777</v>
       </c>
       <c r="L15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M15" t="n">
-        <v>55</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N15" t="n">
-        <v>16.64539778417854</v>
+        <v>14.71720560319735</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>1.106832291103133</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2176,17 +2192,27 @@
       <c r="W15" t="n">
         <v>79.56989247311827</v>
       </c>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
+      <c r="X15" t="n">
+        <v>10.11195292915226</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.5395683453237488</v>
+      </c>
       <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>22.72727272727273</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>9.342950854998504</v>
+      </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
-      <c r="AD15" t="inlineStr"/>
+      <c r="AD15" t="n">
+        <v>9.511754068716083</v>
+      </c>
       <c r="AE15" t="n">
         <v>31</v>
       </c>
@@ -2219,7 +2245,7 @@
         <v>46238</v>
       </c>
       <c r="C16" t="n">
-        <v>36.10579055849659</v>
+        <v>36.49336524622245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,22 +2273,22 @@
         <v>18.2920442587057</v>
       </c>
       <c r="K16" t="n">
-        <v>4.070121315188846</v>
+        <v>5.187253612984044</v>
       </c>
       <c r="L16" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M16" t="n">
-        <v>63.82978723404256</v>
+        <v>54.76190476190476</v>
       </c>
       <c r="N16" t="n">
-        <v>16.47506314968796</v>
+        <v>17.84367448638176</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>5.697964612582518</v>
+        <v>4.575408351969656</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2328,7 +2354,7 @@
         <v>46238</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7183306931056348</v>
+        <v>0.7323913351933847</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,22 +2382,22 @@
         <v>14.16674936134154</v>
       </c>
       <c r="K17" t="n">
-        <v>2.020588454736227</v>
+        <v>4.017544722387623</v>
       </c>
       <c r="L17" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="M17" t="n">
-        <v>62.90322580645162</v>
+        <v>67.27272727272727</v>
       </c>
       <c r="N17" t="n">
-        <v>16.8725548240452</v>
+        <v>14.63779299529553</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>5.860985155870457</v>
+        <v>3.828638032402276</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2398,16 +2424,16 @@
         <v>15.7396793517258</v>
       </c>
       <c r="Y17" t="n">
-        <v>11.85340323546092</v>
+        <v>10.12801719772811</v>
       </c>
       <c r="Z17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="n">
-        <v>66.66666666666667</v>
+        <v>38.09523809523809</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.196941783233198</v>
+        <v>9.372889596389378</v>
       </c>
       <c r="AC17" t="n">
         <v>10</v>
@@ -2447,7 +2473,7 @@
         <v>46238</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1026186732073968</v>
+        <v>0.1043268548017279</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2475,22 +2501,22 @@
         <v>27.33452427541018</v>
       </c>
       <c r="K18" t="n">
-        <v>2.692341705429024</v>
+        <v>4.401749579232339</v>
       </c>
       <c r="L18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M18" t="n">
-        <v>53.84615384615385</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="N18" t="n">
-        <v>19.64929478594908</v>
+        <v>19.38924952671559</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>7.116069390581092</v>
+        <v>5.362218969825849</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2556,7 +2582,7 @@
         <v>46238</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02502381650026696</v>
+        <v>0.02524036894532288</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,22 +2610,22 @@
         <v>23.99412305210119</v>
       </c>
       <c r="K19" t="n">
-        <v>1.314139592584374</v>
+        <v>2.190897326452679</v>
       </c>
       <c r="L19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M19" t="n">
-        <v>65</v>
+        <v>73.68421052631579</v>
       </c>
       <c r="N19" t="n">
-        <v>23.79065269649551</v>
+        <v>19.13887577281496</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>8.573196636070923</v>
+        <v>7.641681282630142</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2665,7 +2691,7 @@
         <v>46238</v>
       </c>
       <c r="C20" t="n">
-        <v>1.818957998433288</v>
+        <v>1.832030004098632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,7 +2751,7 @@
         <v>20.34011802710127</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.181139216969191</v>
+        <v>7.52127974282245</v>
       </c>
       <c r="Z20" t="n">
         <v>18</v>
@@ -2734,7 +2760,7 @@
         <v>44.44444444444444</v>
       </c>
       <c r="AB20" t="n">
-        <v>12.89733152444661</v>
+        <v>13.15851961577055</v>
       </c>
       <c r="AC20" t="n">
         <v>4</v>
@@ -2774,7 +2800,7 @@
         <v>46238</v>
       </c>
       <c r="C21" t="n">
-        <v>0.955110623816726</v>
+        <v>0.959975312724288</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2802,22 +2828,22 @@
         <v>14.08722322280853</v>
       </c>
       <c r="K21" t="n">
-        <v>2.090668711203603</v>
+        <v>2.610649675984811</v>
       </c>
       <c r="L21" t="n">
         <v>59</v>
       </c>
       <c r="M21" t="n">
-        <v>54.23728813559322</v>
+        <v>55.93220338983051</v>
       </c>
       <c r="N21" t="n">
-        <v>16.1506378427643</v>
+        <v>16.09406398265327</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>5.788316761361267</v>
+        <v>5.252232922248545</v>
       </c>
       <c r="Q21" t="n">
         <v>41</v>
@@ -2883,7 +2909,7 @@
         <v>46238</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7809953636098027</v>
+        <v>0.816946577312556</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2900,11 +2926,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>5</v>
       </c>
@@ -2915,22 +2937,22 @@
         <v>20.35908649698318</v>
       </c>
       <c r="K22" t="n">
-        <v>4.037293924390517</v>
+        <v>8.82639660183051</v>
       </c>
       <c r="L22" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="M22" t="n">
-        <v>81.25</v>
+        <v>62.5</v>
       </c>
       <c r="N22" t="n">
-        <v>14.50436328333056</v>
+        <v>14.03695461188192</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>5.731316002839248</v>
+        <v>1.078417952643806</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -2988,7 +3010,7 @@
         <v>46238</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7755280107341586</v>
+        <v>0.7816100559513667</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,16 +3042,16 @@
         <v>24.64686798085608</v>
       </c>
       <c r="K23" t="n">
-        <v>11.37168396768449</v>
+        <v>12.24511163042854</v>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>12.41985142387837</v>
+        <v>13.98850448712136</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
@@ -3059,25 +3081,25 @@
         <v>87.5</v>
       </c>
       <c r="X23" t="n">
-        <v>16.44501523256388</v>
+        <v>16.47394175770236</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.356847096242733</v>
+        <v>3.630709207103966</v>
       </c>
       <c r="Z23" t="n">
         <v>16</v>
       </c>
       <c r="AA23" t="n">
-        <v>50</v>
+        <v>43.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>10.96308432487421</v>
+        <v>11.61243051167745</v>
       </c>
       <c r="AC23" t="n">
         <v>6</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.718003697986337</v>
+        <v>2.458553729515145</v>
       </c>
       <c r="AE23" t="n">
         <v>10</v>
@@ -3111,7 +3133,7 @@
         <v>46238</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1861014910674987</v>
+        <v>0.1859373799715338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3161,7 @@
         <v>23.34450349594161</v>
       </c>
       <c r="K24" t="n">
-        <v>6.324124254732566</v>
+        <v>6.230363756313895</v>
       </c>
       <c r="L24" t="n">
         <v>8</v>
@@ -3148,13 +3170,13 @@
         <v>37.5</v>
       </c>
       <c r="N24" t="n">
-        <v>13.73901262125115</v>
+        <v>14.06352044548723</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>3.45723585407649</v>
+        <v>3.548548748579483</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3220,7 +3242,7 @@
         <v>46238</v>
       </c>
       <c r="C25" t="n">
-        <v>3.911285407035741</v>
+        <v>3.94801414721106</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3319,7 +3341,7 @@
         <v>46238</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4315031094170144</v>
+        <v>0.4345549974138045</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3440,7 @@
         <v>46238</v>
       </c>
       <c r="C27" t="n">
-        <v>33.7506079478084</v>
+        <v>34.24276577570613</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3443,10 +3465,10 @@
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>60.26772025973355</v>
+        <v>60.4569342526416</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5009392611145858</v>
+        <v>2.45437382001259</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3457,7 +3479,7 @@
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>7.461682242990664</v>
+        <v>5.412776412776421</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -3503,7 +3525,7 @@
         <v>46238</v>
       </c>
       <c r="C28" t="n">
-        <v>1.448857906070049</v>
+        <v>1.464993052008209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3531,16 +3553,16 @@
         <v>24.87361787048376</v>
       </c>
       <c r="K28" t="n">
-        <v>3.909514032336903</v>
+        <v>5.066698022741223</v>
       </c>
       <c r="L28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M28" t="n">
-        <v>47.05882352941177</v>
+        <v>50</v>
       </c>
       <c r="N28" t="n">
-        <v>14.1693939144707</v>
+        <v>12.81456999130203</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
@@ -3612,7 +3634,7 @@
         <v>46238</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3791423579980717</v>
+        <v>0.3729264259530697</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,11 +3651,7 @@
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>5</v>
       </c>
@@ -3641,25 +3659,25 @@
         <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>17.9698042307806</v>
+        <v>19.41872247596972</v>
       </c>
       <c r="K29" t="n">
-        <v>0.8953544626694177</v>
+        <v>1.025642779458047</v>
       </c>
       <c r="L29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M29" t="n">
-        <v>76.92307692307692</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N29" t="n">
-        <v>23.93140568417198</v>
+        <v>20.28444810421354</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>3.077094633211575</v>
+        <v>2.944160649425487</v>
       </c>
       <c r="Q29" t="n">
         <v>6</v>
@@ -3686,7 +3704,7 @@
         <v>55.05052857749912</v>
       </c>
       <c r="Y29" t="n">
-        <v>17.23534321222443</v>
+        <v>18.59224642144944</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3731,7 +3749,7 @@
         <v>46238</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3816657454376894</v>
+        <v>0.388070672350295</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3759,22 +3777,22 @@
         <v>21.77845247058357</v>
       </c>
       <c r="K30" t="n">
-        <v>3.24406482750994</v>
+        <v>4.976655968541399</v>
       </c>
       <c r="L30" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M30" t="n">
-        <v>53.84615384615385</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N30" t="n">
-        <v>11.64030685510427</v>
+        <v>11.12474155731627</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>1.700761371051884</v>
+        <v>0.02223735481305944</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3840,7 +3858,7 @@
         <v>46238</v>
       </c>
       <c r="C31" t="n">
-        <v>0.185260355261961</v>
+        <v>0.185727038734683</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3865,10 +3883,10 @@
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>26.85627978794248</v>
+        <v>27.00457192147066</v>
       </c>
       <c r="K31" t="n">
-        <v>0.2275365198067814</v>
+        <v>0.6841443198738473</v>
       </c>
       <c r="L31" t="n">
         <v>6</v>
@@ -3877,13 +3895,13 @@
         <v>33.33333333333334</v>
       </c>
       <c r="N31" t="n">
-        <v>16.48034815138524</v>
+        <v>16.05012874702525</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>9.750278036876626</v>
+        <v>9.252554851665273</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3949,7 +3967,7 @@
         <v>46238</v>
       </c>
       <c r="C32" t="n">
-        <v>2.30471437971425</v>
+        <v>2.273736442237348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4009,22 +4027,22 @@
         <v>12.36180984775317</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.673442911958013</v>
+        <v>3.981620631007676</v>
       </c>
       <c r="Z32" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AA32" t="n">
-        <v>39.58333333333334</v>
+        <v>40.47619047619047</v>
       </c>
       <c r="AB32" t="n">
-        <v>12.02327185494637</v>
+        <v>9.523041492863745</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>5.472871174538274</v>
+        <v>4.185010615051055</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4058,7 +4076,7 @@
         <v>46238</v>
       </c>
       <c r="C33" t="n">
-        <v>1.813700894391573</v>
+        <v>1.815203188503609</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4086,22 +4104,22 @@
         <v>12.57251846431013</v>
       </c>
       <c r="K33" t="n">
-        <v>1.655848550696004</v>
+        <v>1.740050407354921</v>
       </c>
       <c r="L33" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M33" t="n">
-        <v>61.40350877192982</v>
+        <v>63.79310344827586</v>
       </c>
       <c r="N33" t="n">
-        <v>12.49758808778181</v>
+        <v>12.3710183755118</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>2.305968109778722</v>
+        <v>2.221297889667362</v>
       </c>
       <c r="Q33" t="n">
         <v>39</v>
@@ -4167,7 +4185,7 @@
         <v>46238</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8697353054886147</v>
+        <v>0.8800474970466582</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4192,25 +4210,25 @@
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>10.40567165971804</v>
+        <v>10.38341521030434</v>
       </c>
       <c r="K34" t="n">
-        <v>1.62162122279037</v>
+        <v>2.800981249907952</v>
       </c>
       <c r="L34" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="M34" t="n">
-        <v>42.5925925925926</v>
+        <v>38.09523809523809</v>
       </c>
       <c r="N34" t="n">
-        <v>13.33836126749276</v>
+        <v>9.538689121041216</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>2.340425933567225</v>
+        <v>1.16634951876311</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4237,16 +4255,16 @@
         <v>14.68007915548277</v>
       </c>
       <c r="Y34" t="n">
-        <v>8.952791016935546</v>
+        <v>7.873271473537091</v>
       </c>
       <c r="Z34" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AA34" t="n">
-        <v>47.82608695652174</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="AB34" t="n">
-        <v>10.32245985978625</v>
+        <v>11.84984593704369</v>
       </c>
       <c r="AC34" t="n">
         <v>2</v>
@@ -4286,7 +4304,7 @@
         <v>46238</v>
       </c>
       <c r="C35" t="n">
-        <v>1.948282790032946</v>
+        <v>1.936146617993971</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4305,7 +4323,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4318,16 +4336,16 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>9.834930785663776</v>
+        <v>9.150751044035399</v>
       </c>
       <c r="L35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M35" t="n">
-        <v>77.77777777777777</v>
+        <v>100</v>
       </c>
       <c r="N35" t="n">
-        <v>11.33742913819006</v>
+        <v>12.38992893736071</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4360,7 +4378,7 @@
         <v>42.52272358489104</v>
       </c>
       <c r="Y35" t="n">
-        <v>15.3273766954231</v>
+        <v>15.85481630977101</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -4405,7 +4423,7 @@
         <v>46238</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08243139305635987</v>
+        <v>0.08329321489036053</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4433,16 +4451,16 @@
         <v>20.39128953068605</v>
       </c>
       <c r="K36" t="n">
-        <v>3.028124631364815</v>
+        <v>4.105285698662819</v>
       </c>
       <c r="L36" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M36" t="n">
-        <v>41.1764705882353</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N36" t="n">
-        <v>14.11464947818691</v>
+        <v>12.60275160796857</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4514,7 +4532,7 @@
         <v>46238</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06392638430611416</v>
+        <v>0.06373192830043403</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4542,22 +4560,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>4.061360515035761</v>
+        <v>3.744818969146091</v>
       </c>
       <c r="L37" t="n">
         <v>68</v>
       </c>
       <c r="M37" t="n">
-        <v>57.35294117647059</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N37" t="n">
-        <v>18.90646061917947</v>
+        <v>20.65527448243167</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>3.784920229247968</v>
+        <v>4.101584130306701</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4623,16 +4641,16 @@
         <v>46238</v>
       </c>
       <c r="C38" t="n">
-        <v>1.670707600320264</v>
+        <v>1.692156266716906</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4642,7 +4660,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.19: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %86.36: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -4655,22 +4673,22 @@
         <v>18.01910891260425</v>
       </c>
       <c r="K38" t="n">
-        <v>5.451338054061572</v>
+        <v>6.805130046488927</v>
       </c>
       <c r="L38" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M38" t="n">
-        <v>85.18518518518519</v>
+        <v>86.36363636363636</v>
       </c>
       <c r="N38" t="n">
-        <v>12.89404370622258</v>
+        <v>13.64361758037937</v>
       </c>
       <c r="O38" t="n">
         <v>6</v>
       </c>
       <c r="P38" t="n">
-        <v>0.5202987046566854</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>35</v>
@@ -4736,7 +4754,7 @@
         <v>46238</v>
       </c>
       <c r="C39" t="n">
-        <v>2.67060885319107</v>
+        <v>2.761716984515142</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,14 +4768,10 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>BAND</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>5</v>
       </c>
@@ -4768,16 +4782,16 @@
         <v>18.47027414490581</v>
       </c>
       <c r="K39" t="n">
-        <v>5.714716126886832</v>
+        <v>9.321185950525312</v>
       </c>
       <c r="L39" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M39" t="n">
-        <v>75</v>
+        <v>56.25</v>
       </c>
       <c r="N39" t="n">
-        <v>13.90751191027973</v>
+        <v>15.20010515213887</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4806,17 +4820,27 @@
       <c r="W39" t="n">
         <v>69.23076923076923</v>
       </c>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
+      <c r="X39" t="n">
+        <v>10.23704506296521</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.8308088373710998</v>
+      </c>
       <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>44.89795918367347</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>11.70848058084654</v>
+      </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
-      <c r="AD39" t="inlineStr"/>
+      <c r="AD39" t="n">
+        <v>5.212497048757692</v>
+      </c>
       <c r="AE39" t="n">
         <v>42</v>
       </c>
@@ -4849,7 +4873,7 @@
         <v>46238</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1949334275398527</v>
+        <v>0.1970852036558122</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4866,11 +4890,7 @@
           <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.95: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>5</v>
       </c>
@@ -4881,16 +4901,16 @@
         <v>14.73965458840789</v>
       </c>
       <c r="K40" t="n">
-        <v>6.460820145963275</v>
+        <v>7.635989807558174</v>
       </c>
       <c r="L40" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M40" t="n">
-        <v>78.94736842105263</v>
+        <v>68.75</v>
       </c>
       <c r="N40" t="n">
-        <v>11.77088649714645</v>
+        <v>12.21407746678665</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4923,16 +4943,16 @@
         <v>14.17330472629232</v>
       </c>
       <c r="Y40" t="n">
-        <v>6.75506818237257</v>
+        <v>5.725782339756257</v>
       </c>
       <c r="Z40" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA40" t="n">
-        <v>39.1304347826087</v>
+        <v>50</v>
       </c>
       <c r="AB40" t="n">
-        <v>11.50844416173121</v>
+        <v>12.58136924216362</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
@@ -4972,16 +4992,16 @@
         <v>46238</v>
       </c>
       <c r="C41" t="n">
-        <v>1.647576374499912</v>
+        <v>1.686897856739064</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4991,7 +5011,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -5004,22 +5024,22 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>8.881134781660638</v>
+        <v>11.4797199967438</v>
       </c>
       <c r="L41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M41" t="n">
-        <v>80</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N41" t="n">
-        <v>12.63199731055526</v>
+        <v>13.38516228592029</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>1.027602458941157</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>10</v>
@@ -5046,13 +5066,17 @@
         <v>40.81782021738603</v>
       </c>
       <c r="Y41" t="n">
-        <v>15.50691239875521</v>
+        <v>13.49037860107198</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>22.19906898574699</v>
+      </c>
       <c r="AC41" t="n">
         <v>3</v>
       </c>
@@ -5091,7 +5115,7 @@
         <v>46238</v>
       </c>
       <c r="C42" t="n">
-        <v>3.156365394918847</v>
+        <v>3.203423422653857</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5110,7 +5134,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -5123,16 +5147,16 @@
         <v>21.13784986389697</v>
       </c>
       <c r="K42" t="n">
-        <v>2.692996670297587</v>
+        <v>4.22403927179158</v>
       </c>
       <c r="L42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M42" t="n">
-        <v>75</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N42" t="n">
-        <v>16.84474117966856</v>
+        <v>12.69257812864195</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
@@ -5200,7 +5224,7 @@
         <v>46238</v>
       </c>
       <c r="C43" t="n">
-        <v>7.239032265441149</v>
+        <v>7.18824643970981</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5260,16 +5284,16 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>6.563446897429559</v>
+        <v>7.21895613247715</v>
       </c>
       <c r="Z43" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA43" t="n">
-        <v>63.63636363636363</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB43" t="n">
-        <v>12.2110825576475</v>
+        <v>12.88450323174313</v>
       </c>
       <c r="AC43" t="n">
         <v>6</v>
@@ -5309,7 +5333,7 @@
         <v>46238</v>
       </c>
       <c r="C44" t="n">
-        <v>5.019482874892531</v>
+        <v>5.048073578728177</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5326,7 +5350,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %78.26: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H44" t="n">
         <v>5</v>
       </c>
@@ -5337,22 +5365,22 @@
         <v>13.03201987649729</v>
       </c>
       <c r="K44" t="n">
-        <v>2.735491382129962</v>
+        <v>3.320667202174765</v>
       </c>
       <c r="L44" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M44" t="n">
-        <v>69.23076923076923</v>
+        <v>78.26086956521739</v>
       </c>
       <c r="N44" t="n">
-        <v>18.54409624254036</v>
+        <v>19.74854765260397</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>7.071079838270622</v>
+        <v>6.464662858550185</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5379,13 +5407,13 @@
         <v>12.1234692799834</v>
       </c>
       <c r="Y44" t="n">
-        <v>8.372892810166899</v>
+        <v>7.850989747585457</v>
       </c>
       <c r="Z44" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA44" t="n">
-        <v>14.28571428571429</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="AB44" t="n">
         <v>9.691917834769438</v>
@@ -5394,7 +5422,7 @@
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.775792382555585</v>
+        <v>2.332103455618217</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5420,7 +5448,7 @@
         <v>46238</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02039756431270554</v>
+        <v>0.02061296753381285</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5445,25 +5473,25 @@
         <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>10.66345727627647</v>
+        <v>10.64126486431516</v>
       </c>
       <c r="K45" t="n">
-        <v>1.041671896701479</v>
+        <v>2.083337543402886</v>
       </c>
       <c r="L45" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="M45" t="n">
-        <v>61.03896103896104</v>
+        <v>53.73134328358209</v>
       </c>
       <c r="N45" t="n">
-        <v>15.1445705774911</v>
+        <v>15.98905578121075</v>
       </c>
       <c r="O45" t="n">
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>8.865973746413204</v>
+        <v>7.755097596834726</v>
       </c>
       <c r="Q45" t="n">
         <v>37</v>
@@ -5529,7 +5557,7 @@
         <v>46238</v>
       </c>
       <c r="C46" t="n">
-        <v>8.542794067786396</v>
+        <v>8.660601233505529</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5557,22 +5585,22 @@
         <v>23.79638976838147</v>
       </c>
       <c r="K46" t="n">
-        <v>3.458350040660352</v>
+        <v>4.885065339139549</v>
       </c>
       <c r="L46" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M46" t="n">
-        <v>43.75</v>
+        <v>40</v>
       </c>
       <c r="N46" t="n">
-        <v>10.87915030095106</v>
+        <v>11.14792574694933</v>
       </c>
       <c r="O46" t="n">
         <v>10</v>
       </c>
       <c r="P46" t="n">
-        <v>6.322979205418133</v>
+        <v>4.876704461518555</v>
       </c>
       <c r="Q46" t="n">
         <v>54</v>
@@ -5638,7 +5666,7 @@
         <v>46238</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7671166120939383</v>
+        <v>0.7853961174455049</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5666,22 +5694,22 @@
         <v>25.38434003813299</v>
       </c>
       <c r="K47" t="n">
-        <v>2.912212813802673</v>
+        <v>5.364492317614422</v>
       </c>
       <c r="L47" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M47" t="n">
-        <v>52.63157894736842</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N47" t="n">
-        <v>13.07077433982179</v>
+        <v>14.24479087190473</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>6.88721677671158</v>
+        <v>4.399497003613084</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5747,7 +5775,7 @@
         <v>46238</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0618235447922699</v>
+        <v>0.06204923879021584</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5775,22 +5803,22 @@
         <v>34.60463024804744</v>
       </c>
       <c r="K48" t="n">
-        <v>5.344404436742045</v>
+        <v>5.728976364450955</v>
       </c>
       <c r="L48" t="n">
         <v>7</v>
       </c>
       <c r="M48" t="n">
-        <v>71.42857142857143</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N48" t="n">
-        <v>13.44205386179763</v>
+        <v>18.164645185499</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>4.419404702272134</v>
+        <v>4.039596128148171</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5856,7 +5884,7 @@
         <v>46238</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2599112166727135</v>
+        <v>0.2639721848840525</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5884,22 +5912,22 @@
         <v>24.14896896188847</v>
       </c>
       <c r="K49" t="n">
-        <v>2.856850681613632</v>
+        <v>4.463931769854823</v>
       </c>
       <c r="L49" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M49" t="n">
-        <v>52.63157894736842</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N49" t="n">
-        <v>9.908482851676821</v>
+        <v>9.480322112836159</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>2.083623311606475</v>
+        <v>0.5131610701061939</v>
       </c>
       <c r="Q49" t="n">
         <v>53</v>
@@ -5965,7 +5993,7 @@
         <v>46238</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7200130048809851</v>
+        <v>0.7361773968978591</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5993,22 +6021,22 @@
         <v>11.86078125763058</v>
       </c>
       <c r="K50" t="n">
-        <v>0.7708518662762787</v>
+        <v>3.033171494391995</v>
       </c>
       <c r="L50" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M50" t="n">
-        <v>41.50943396226415</v>
+        <v>58.92857142857143</v>
       </c>
       <c r="N50" t="n">
-        <v>13.61476274983396</v>
+        <v>12.55373909038889</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>3.204446597324417</v>
+        <v>0.9383662480588972</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6074,7 +6102,7 @@
         <v>46238</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1829472166562726</v>
+        <v>0.183834007987614</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6106,7 +6134,7 @@
         <v>27.30972539236674</v>
       </c>
       <c r="K51" t="n">
-        <v>6.036428789492221</v>
+        <v>6.550414121302883</v>
       </c>
       <c r="L51" t="n">
         <v>4</v>
@@ -6148,7 +6176,7 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>16.94829597762813</v>
+        <v>16.54572340764726</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6193,7 +6221,7 @@
         <v>46238</v>
       </c>
       <c r="C52" t="n">
-        <v>4.096335533440767</v>
+        <v>4.156247374791403</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6253,22 +6281,22 @@
         <v>12.1710603868542</v>
       </c>
       <c r="Y52" t="n">
-        <v>6.009907378929091</v>
+        <v>4.635234949955658</v>
       </c>
       <c r="Z52" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="AA52" t="n">
-        <v>59.09090909090909</v>
+        <v>45.16129032258065</v>
       </c>
       <c r="AB52" t="n">
-        <v>12.94443432089259</v>
+        <v>13.71435399424619</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.117342972619607</v>
+        <v>3.528310533013546</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6302,7 +6330,7 @@
         <v>46238</v>
       </c>
       <c r="C53" t="n">
-        <v>1.569771299029488</v>
+        <v>1.594349969434251</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6319,11 +6347,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>5</v>
       </c>
@@ -6334,22 +6358,22 @@
         <v>28.17598592067425</v>
       </c>
       <c r="K53" t="n">
-        <v>3.491909610707133</v>
+        <v>5.112332622297266</v>
       </c>
       <c r="L53" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M53" t="n">
-        <v>75</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N53" t="n">
-        <v>14.69167149600774</v>
+        <v>12.79930778909531</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>4.355983386769458</v>
+        <v>2.747220336246436</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6407,7 +6431,7 @@
         <v>46238</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08810906500084342</v>
+        <v>0.08855162486820237</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6435,22 +6459,18 @@
         <v>42.39442432818535</v>
       </c>
       <c r="K54" t="n">
-        <v>9.005408726917196</v>
+        <v>9.55292809086834</v>
       </c>
       <c r="L54" t="n">
-        <v>3</v>
-      </c>
-      <c r="M54" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N54" t="n">
-        <v>25.55854552237183</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>0.9124237821762415</v>
+        <v>0.4080875946655071</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6477,7 +6497,7 @@
         <v>114.7400208810756</v>
       </c>
       <c r="Y54" t="n">
-        <v>37.20680678944488</v>
+        <v>36.89140510792615</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -6522,7 +6542,7 @@
         <v>46238</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8579593636262435</v>
+        <v>0.8674273452813068</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6547,25 +6567,25 @@
         <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>12.34326744164818</v>
+        <v>12.32149231737306</v>
       </c>
       <c r="K55" t="n">
-        <v>2.306916111624857</v>
+        <v>3.410232130166801</v>
       </c>
       <c r="L55" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="M55" t="n">
-        <v>62.31884057971015</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N55" t="n">
-        <v>14.02210064666208</v>
+        <v>12.0241634893214</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>3.609808631457234</v>
+        <v>2.504363268978405</v>
       </c>
       <c r="Q55" t="n">
         <v>44</v>
@@ -6592,16 +6612,16 @@
         <v>25.41488056506582</v>
       </c>
       <c r="Y55" t="n">
-        <v>10.32110015533564</v>
+        <v>9.331451677129355</v>
       </c>
       <c r="Z55" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AA55" t="n">
-        <v>53.84615384615385</v>
+        <v>50</v>
       </c>
       <c r="AB55" t="n">
-        <v>8.985280448705707</v>
+        <v>10.78082928863532</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6641,7 +6661,7 @@
         <v>46238</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8638473746165619</v>
+        <v>0.8552277956411526</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6666,10 +6686,10 @@
         <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>34.40711516467502</v>
+        <v>34.39082100018626</v>
       </c>
       <c r="K56" t="n">
-        <v>10.19314156211462</v>
+        <v>9.066526772026883</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6730,7 +6750,7 @@
         <v>46238</v>
       </c>
       <c r="C57" t="n">
-        <v>1.378412743874265</v>
+        <v>1.385065155982075</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6758,10 +6778,10 @@
         <v>32.76213282665623</v>
       </c>
       <c r="K57" t="n">
-        <v>18.02965702457682</v>
+        <v>18.59928460743274</v>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -6796,10 +6816,10 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>15.02009255832818</v>
+        <v>14.60996767541642</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr"/>
@@ -6841,7 +6861,7 @@
         <v>46238</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7486115833666973</v>
+        <v>0.7559489895984578</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6860,7 +6880,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %91.67: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %89.19: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -6873,22 +6893,22 @@
         <v>16.33691982084211</v>
       </c>
       <c r="K58" t="n">
-        <v>0.9205310435592251</v>
+        <v>1.909688772139106</v>
       </c>
       <c r="L58" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M58" t="n">
-        <v>91.66666666666667</v>
+        <v>89.18918918918919</v>
       </c>
       <c r="N58" t="n">
-        <v>17.74346149259786</v>
+        <v>19.01585258090028</v>
       </c>
       <c r="O58" t="n">
         <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>4.042258710152846</v>
+        <v>3.032401791325801</v>
       </c>
       <c r="Q58" t="n">
         <v>24</v>
@@ -6915,7 +6935,7 @@
         <v>41.32985472592288</v>
       </c>
       <c r="Y58" t="n">
-        <v>15.56677519579512</v>
+        <v>14.73921537223499</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -6960,7 +6980,7 @@
         <v>46238</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8205288085039025</v>
+        <v>0.8270427147945381</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7020,16 +7040,16 @@
         <v>10.2478061424703</v>
       </c>
       <c r="Y59" t="n">
-        <v>6.832295797346521</v>
+        <v>6.092668269098866</v>
       </c>
       <c r="Z59" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AA59" t="n">
         <v>50</v>
       </c>
       <c r="AB59" t="n">
-        <v>15.44866820059028</v>
+        <v>15.12318601205643</v>
       </c>
       <c r="AC59" t="n">
         <v>6</v>
@@ -7069,7 +7089,7 @@
         <v>46238</v>
       </c>
       <c r="C60" t="n">
-        <v>13.00607539920218</v>
+        <v>13.26170996411715</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7097,22 +7117,22 @@
         <v>17.06238107085701</v>
       </c>
       <c r="K60" t="n">
-        <v>2.356394739081846</v>
+        <v>4.368210881328327</v>
       </c>
       <c r="L60" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="M60" t="n">
-        <v>53.48837209302326</v>
+        <v>48.38709677419355</v>
       </c>
       <c r="N60" t="n">
-        <v>12.06861578740512</v>
+        <v>12.20601152229256</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>5.513681167946904</v>
+        <v>3.479784781211981</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7178,7 +7198,7 @@
         <v>46238</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6308524850057646</v>
+        <v>0.6377399555922313</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7195,11 +7215,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>5</v>
       </c>
@@ -7210,22 +7226,22 @@
         <v>36.10328933244122</v>
       </c>
       <c r="K61" t="n">
-        <v>1.857158883271848</v>
+        <v>2.969206790673184</v>
       </c>
       <c r="L61" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M61" t="n">
-        <v>75</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N61" t="n">
-        <v>19.46927000780446</v>
+        <v>43.93076393964234</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>7.994372910066971</v>
+        <v>6.828054161492925</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7283,7 +7299,7 @@
         <v>46238</v>
       </c>
       <c r="C62" t="n">
-        <v>8.432394882910387</v>
+        <v>8.613275543704953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7311,22 +7327,22 @@
         <v>14.45999953470718</v>
       </c>
       <c r="K62" t="n">
-        <v>1.340696642907835</v>
+        <v>3.514524176921996</v>
       </c>
       <c r="L62" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M62" t="n">
-        <v>56.14035087719298</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N62" t="n">
-        <v>14.40118179846843</v>
+        <v>15.01384110579671</v>
       </c>
       <c r="O62" t="n">
         <v>6</v>
       </c>
       <c r="P62" t="n">
-        <v>4.597662648314005</v>
+        <v>2.401088970693577</v>
       </c>
       <c r="Q62" t="n">
         <v>29</v>
@@ -7392,7 +7408,7 @@
         <v>46238</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1072449203481384</v>
+        <v>0.106219885548797</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7420,7 +7436,7 @@
         <v>33.28434552774222</v>
       </c>
       <c r="K63" t="n">
-        <v>7.474348218219662</v>
+        <v>6.447120573287002</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
@@ -7455,25 +7471,25 @@
         <v>66.66666666666667</v>
       </c>
       <c r="X63" t="n">
-        <v>10.21389301022846</v>
+        <v>10.24127163987956</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.485661940781414</v>
+        <v>3.441679336743098</v>
       </c>
       <c r="Z63" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA63" t="n">
-        <v>60</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB63" t="n">
-        <v>11.24234270242617</v>
+        <v>11.68557514107501</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>7.705880190311365</v>
+        <v>6.792082358317697</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7507,7 +7523,7 @@
         <v>46238</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1583439781524143</v>
+        <v>0.1606970061884738</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7532,25 +7548,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>24.02447184067135</v>
+        <v>24.00559848640348</v>
       </c>
       <c r="K64" t="n">
-        <v>0.6684517361806197</v>
+        <v>2.139035422088131</v>
       </c>
       <c r="L64" t="n">
         <v>33</v>
       </c>
       <c r="M64" t="n">
-        <v>69.6969696969697</v>
+        <v>57.57575757575758</v>
       </c>
       <c r="N64" t="n">
-        <v>16.28257099681413</v>
+        <v>16.23377088890027</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.302786214663334</v>
+        <v>2.801049144520484</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7616,7 +7632,7 @@
         <v>46238</v>
       </c>
       <c r="C65" t="n">
-        <v>6.255953809640499</v>
+        <v>6.27854151354317</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7635,7 +7651,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -7648,22 +7664,22 @@
         <v>28.12381406175567</v>
       </c>
       <c r="K65" t="n">
-        <v>3.074915547775325</v>
+        <v>3.447077130649912</v>
       </c>
       <c r="L65" t="n">
         <v>16</v>
       </c>
       <c r="M65" t="n">
-        <v>75</v>
+        <v>81.25</v>
       </c>
       <c r="N65" t="n">
-        <v>15.2018122320435</v>
+        <v>14.24622363239263</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>6.718496362982607</v>
+        <v>6.334565510317902</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7729,7 +7745,7 @@
         <v>46238</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4285591038167132</v>
+        <v>0.4324516254298847</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7828,7 +7844,7 @@
         <v>46238</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02880893014859659</v>
+        <v>0.02944709545524157</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7853,13 +7869,13 @@
         <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>18.78496312965017</v>
+        <v>18.76478821017455</v>
       </c>
       <c r="K67" t="n">
-        <v>7.031252508544994</v>
+        <v>9.375001000976591</v>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
@@ -7913,7 +7929,7 @@
         <v>46238</v>
       </c>
       <c r="C68" t="n">
-        <v>3.68628141818702</v>
+        <v>3.621992728584865</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7970,10 +7986,10 @@
         <v>80</v>
       </c>
       <c r="X68" t="n">
-        <v>108.240461684886</v>
+        <v>108.2921914471068</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.239434901408454</v>
+        <v>2.985917211267608</v>
       </c>
       <c r="Z68" t="n">
         <v>1</v>
@@ -7984,7 +8000,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>6.845409492992016</v>
+        <v>5.168407147291754</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8018,7 +8034,7 @@
         <v>46238</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4029044506027525</v>
+        <v>0.4112076442816664</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8035,11 +8051,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>5</v>
       </c>
@@ -8050,16 +8062,16 @@
         <v>29.4573350207784</v>
       </c>
       <c r="K69" t="n">
-        <v>3.061528192370933</v>
+        <v>5.185455659902982</v>
       </c>
       <c r="L69" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M69" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="N69" t="n">
-        <v>14.18660243657942</v>
+        <v>14.20304940810647</v>
       </c>
       <c r="O69" t="n">
         <v>3</v>
@@ -8115,7 +8127,7 @@
         <v>46238</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4167832019083328</v>
+        <v>0.4141523810026533</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8143,22 +8155,22 @@
         <v>20.66985845799666</v>
       </c>
       <c r="K70" t="n">
-        <v>6.915345305267429</v>
+        <v>6.240473755072617</v>
       </c>
       <c r="L70" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M70" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="N70" t="n">
-        <v>8.782275786017548</v>
+        <v>8.731453063316346</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>1.014498612557113</v>
+        <v>1.656173191568988</v>
       </c>
       <c r="Q70" t="n">
         <v>30</v>
@@ -8224,16 +8236,16 @@
         <v>46238</v>
       </c>
       <c r="C71" t="n">
-        <v>3.269918713946546</v>
+        <v>3.350658902033429</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8241,11 +8253,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.67: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>5</v>
       </c>
@@ -8256,22 +8264,22 @@
         <v>20.51701021225919</v>
       </c>
       <c r="K71" t="n">
-        <v>4.377150019833476</v>
+        <v>6.954410025909552</v>
       </c>
       <c r="L71" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="M71" t="n">
-        <v>76.66666666666667</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N71" t="n">
-        <v>11.83084085922615</v>
+        <v>12.05814941002346</v>
       </c>
       <c r="O71" t="n">
         <v>6</v>
       </c>
       <c r="P71" t="n">
-        <v>1.554794301107254</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>43</v>
@@ -8337,7 +8345,7 @@
         <v>46238</v>
       </c>
       <c r="C72" t="n">
-        <v>0.079066844577105</v>
+        <v>0.07971749442273686</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8354,7 +8362,11 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H72" t="n">
         <v>5</v>
       </c>
@@ -8365,16 +8377,16 @@
         <v>20.36571476939619</v>
       </c>
       <c r="K72" t="n">
-        <v>10.54032803129894</v>
+        <v>11.44997666789682</v>
       </c>
       <c r="L72" t="n">
         <v>9</v>
       </c>
       <c r="M72" t="n">
-        <v>66.66666666666667</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N72" t="n">
-        <v>15.39469661418315</v>
+        <v>15.59377252623562</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
@@ -8407,7 +8419,7 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>11.97199988071029</v>
+        <v>11.24760769084564</v>
       </c>
       <c r="Z72" t="n">
         <v>2</v>
@@ -8452,7 +8464,7 @@
         <v>46238</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07002462415336658</v>
+        <v>0.07067302799883049</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8477,25 +8489,25 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>21.1948589936776</v>
+        <v>21.17528272510304</v>
       </c>
       <c r="K73" t="n">
-        <v>0.6042290139739448</v>
+        <v>1.510572837049651</v>
       </c>
       <c r="L73" t="n">
         <v>26</v>
       </c>
       <c r="M73" t="n">
-        <v>73.07692307692308</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N73" t="n">
-        <v>15.33662112876341</v>
+        <v>15.58923191844779</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>9.33933998412828</v>
+        <v>8.363096498901701</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8561,7 +8573,7 @@
         <v>46238</v>
       </c>
       <c r="C74" t="n">
-        <v>4.752422053710093</v>
+        <v>4.825116867362479</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8586,25 +8598,25 @@
         <v>10</v>
       </c>
       <c r="J74" t="n">
-        <v>18.3849409116933</v>
+        <v>18.36466662125948</v>
       </c>
       <c r="K74" t="n">
-        <v>0.5785505418984371</v>
+        <v>2.091676463638681</v>
       </c>
       <c r="L74" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="M74" t="n">
-        <v>70.58823529411765</v>
+        <v>67.5</v>
       </c>
       <c r="N74" t="n">
-        <v>21.34949645792945</v>
+        <v>20.79005760883963</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>7.378759604424778</v>
+        <v>5.787272519190778</v>
       </c>
       <c r="Q74" t="n">
         <v>35</v>
@@ -8631,7 +8643,7 @@
         <v>95.98093909010421</v>
       </c>
       <c r="Y74" t="n">
-        <v>17.91275654506719</v>
+        <v>16.6571195669634</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -8676,7 +8688,7 @@
         <v>46238</v>
       </c>
       <c r="C75" t="n">
-        <v>0.146357777362474</v>
+        <v>0.1493388412673446</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8704,17 +8716,13 @@
         <v>19.1703426786477</v>
       </c>
       <c r="K75" t="n">
-        <v>12.31339671654617</v>
+        <v>14.60103334931557</v>
       </c>
       <c r="L75" t="n">
-        <v>3</v>
-      </c>
-      <c r="M75" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="N75" t="n">
-        <v>9.794958843326418</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="n">
         <v>6</v>
       </c>
@@ -8743,25 +8751,25 @@
         <v>100</v>
       </c>
       <c r="X75" t="n">
-        <v>14.08846685570693</v>
+        <v>17.02218358940229</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.555871674045539</v>
+        <v>2.068966896551716</v>
       </c>
       <c r="Z75" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="AA75" t="n">
-        <v>47.05882352941177</v>
+        <v>20</v>
       </c>
       <c r="AB75" t="n">
-        <v>12.90413460503942</v>
+        <v>11.24142221425521</v>
       </c>
       <c r="AC75" t="n">
         <v>10</v>
       </c>
       <c r="AD75" t="n">
-        <v>8.577584534036852</v>
+        <v>8.098590254909732</v>
       </c>
       <c r="AE75" t="n">
         <v>4</v>
@@ -8795,7 +8803,7 @@
         <v>46238</v>
       </c>
       <c r="C76" t="n">
-        <v>1.805289495751353</v>
+        <v>1.864632210324189</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8823,22 +8831,22 @@
         <v>20.88959101184773</v>
       </c>
       <c r="K76" t="n">
-        <v>4.161222137179665</v>
+        <v>7.585165881045453</v>
       </c>
       <c r="L76" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="M76" t="n">
-        <v>61.90476190476191</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N76" t="n">
-        <v>11.23672238262284</v>
+        <v>10.34072670763836</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>5.605519734715392</v>
+        <v>2.244579072940778</v>
       </c>
       <c r="Q76" t="n">
         <v>42</v>
@@ -8904,7 +8912,7 @@
         <v>46238</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5051025660010202</v>
+        <v>0.5170068673387196</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8932,16 +8940,16 @@
         <v>21.60005234598619</v>
       </c>
       <c r="K77" t="n">
-        <v>4.028922332881435</v>
+        <v>6.480685049296242</v>
       </c>
       <c r="L77" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M77" t="n">
-        <v>64</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="N77" t="n">
-        <v>16.74808530813116</v>
+        <v>10.83008970198139</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -9013,7 +9021,7 @@
         <v>46238</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0529916083199159</v>
+        <v>0.05300477215597307</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9045,7 +9053,7 @@
         <v>20.32485186011925</v>
       </c>
       <c r="K78" t="n">
-        <v>12.38081045624231</v>
+        <v>12.40872737765157</v>
       </c>
       <c r="L78" t="n">
         <v>16</v>
@@ -9087,7 +9095,7 @@
         <v>23.16536029857119</v>
       </c>
       <c r="Y78" t="n">
-        <v>8.756154990482312</v>
+        <v>8.733488778698762</v>
       </c>
       <c r="Z78" t="n">
         <v>16</v>
@@ -9102,7 +9110,7 @@
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.363209769807416</v>
+        <v>1.387706404411826</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9136,7 +9144,7 @@
         <v>46238</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8798289355756355</v>
+        <v>0.891826364423447</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9164,22 +9172,22 @@
         <v>12.92020537241256</v>
       </c>
       <c r="K79" t="n">
-        <v>1.884704346378752</v>
+        <v>3.274013610544135</v>
       </c>
       <c r="L79" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="M79" t="n">
-        <v>58.06451612903226</v>
+        <v>49.12280701754386</v>
       </c>
       <c r="N79" t="n">
-        <v>12.35163766441931</v>
+        <v>10.39232662290731</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>3.057667658366214</v>
+        <v>1.671268820794292</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9245,7 +9253,7 @@
         <v>46238</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1328995937493785</v>
+        <v>0.1356669734319282</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9270,10 +9278,10 @@
         <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>69.29504130463948</v>
+        <v>69.28741377539056</v>
       </c>
       <c r="K80" t="n">
-        <v>1.935489736732765</v>
+        <v>4.032258188085325</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9284,7 +9292,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>7.911386195421577</v>
+        <v>5.736433982933731</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9350,11 +9358,11 @@
         <v>46238</v>
       </c>
       <c r="C81" t="n">
-        <v>1.075603519108305</v>
+        <v>1.088490865413263</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9375,25 +9383,25 @@
         <v>10</v>
       </c>
       <c r="J81" t="n">
-        <v>11.87651962350458</v>
+        <v>11.85462855272487</v>
       </c>
       <c r="K81" t="n">
-        <v>2.50500994323315</v>
+        <v>3.70741164985291</v>
       </c>
       <c r="L81" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M81" t="n">
-        <v>51.02040816326531</v>
+        <v>43.18181818181818</v>
       </c>
       <c r="N81" t="n">
-        <v>13.07620610710466</v>
+        <v>14.02911596425254</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>7.311828037397938</v>
+        <v>6.067636102415475</v>
       </c>
       <c r="Q81" t="n">
         <v>31</v>
@@ -9420,22 +9428,22 @@
         <v>27.31228182970742</v>
       </c>
       <c r="Y81" t="n">
-        <v>9.669017677750247</v>
+        <v>8.586716782882464</v>
       </c>
       <c r="Z81" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA81" t="n">
-        <v>55.55555555555556</v>
+        <v>25</v>
       </c>
       <c r="AB81" t="n">
-        <v>9.276812191444455</v>
+        <v>15.30045963659641</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.3664106309272608</v>
+        <v>1.546037039016324</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9469,7 +9477,7 @@
         <v>46238</v>
       </c>
       <c r="C82" t="n">
-        <v>5.12672792561685</v>
+        <v>5.201619214233761</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9497,17 +9505,13 @@
         <v>15.23084223335499</v>
       </c>
       <c r="K82" t="n">
-        <v>12.77036906089546</v>
+        <v>14.41771964772396</v>
       </c>
       <c r="L82" t="n">
-        <v>6</v>
-      </c>
-      <c r="M82" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N82" t="n">
-        <v>8.430896867829917</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="O82" t="n">
         <v>4</v>
       </c>
@@ -9539,22 +9543,22 @@
         <v>15.04024401260009</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.973113818722438</v>
+        <v>0.5411361651909585</v>
       </c>
       <c r="Z82" t="n">
         <v>12</v>
       </c>
       <c r="AA82" t="n">
-        <v>41.66666666666666</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="AB82" t="n">
-        <v>9.536932908011476</v>
+        <v>11.30341333058647</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>2.067683938801568</v>
+        <v>3.477682834336282</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9588,21 +9592,21 @@
         <v>46238</v>
       </c>
       <c r="C83" t="n">
-        <v>5.803842862053034</v>
+        <v>5.99458737473971</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -9616,22 +9620,22 @@
         <v>14.0949513048101</v>
       </c>
       <c r="K83" t="n">
-        <v>7.234487750305263</v>
+        <v>10.758771676542</v>
       </c>
       <c r="L83" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="M83" t="n">
-        <v>50</v>
+        <v>65.38461538461539</v>
       </c>
       <c r="N83" t="n">
-        <v>11.55732548563121</v>
+        <v>11.17763364443807</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>2.578939208563402</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
         <v>44</v>
@@ -9654,17 +9658,27 @@
       <c r="W83" t="n">
         <v>62.12121212121212</v>
       </c>
-      <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="inlineStr"/>
+      <c r="X83" t="n">
+        <v>11.1473989455825</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>0.3496503496503545</v>
+      </c>
       <c r="Z83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA83" t="inlineStr"/>
-      <c r="AB83" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>56.14035087719298</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>11.88823380124909</v>
+      </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
-      <c r="AD83" t="inlineStr"/>
+      <c r="AD83" t="n">
+        <v>5.670175438596492</v>
+      </c>
       <c r="AE83" t="n">
         <v>35</v>
       </c>
@@ -9697,7 +9711,7 @@
         <v>46238</v>
       </c>
       <c r="C84" t="n">
-        <v>2.226909304243826</v>
+        <v>2.2442893143903</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9725,16 +9739,16 @@
         <v>14.10735630446007</v>
       </c>
       <c r="K84" t="n">
-        <v>6.607830490215938</v>
+        <v>7.439855922092575</v>
       </c>
       <c r="L84" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M84" t="n">
-        <v>63.88888888888889</v>
+        <v>54.05405405405406</v>
       </c>
       <c r="N84" t="n">
-        <v>9.240299333392311</v>
+        <v>8.93109574327298</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
@@ -9806,7 +9820,7 @@
         <v>46238</v>
       </c>
       <c r="C85" t="n">
-        <v>6.655493716810817</v>
+        <v>6.814899331283039</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9834,22 +9848,22 @@
         <v>15.13449360257271</v>
       </c>
       <c r="K85" t="n">
-        <v>3.282553321289172</v>
+        <v>5.756271962906223</v>
       </c>
       <c r="L85" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="M85" t="n">
-        <v>52.08333333333334</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N85" t="n">
-        <v>13.46665735539501</v>
+        <v>13.02129877713198</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>4.567515545472522</v>
+        <v>2.121602809411405</v>
       </c>
       <c r="Q85" t="n">
         <v>34</v>
@@ -9915,7 +9929,7 @@
         <v>46238</v>
       </c>
       <c r="C86" t="n">
-        <v>3.505436910878696</v>
+        <v>3.504204537539013</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9975,7 +9989,7 @@
         <v>39.94948119773951</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.925960461664544</v>
+        <v>1.960439425261629</v>
       </c>
       <c r="Z86" t="n">
         <v>16</v>
@@ -9984,13 +9998,13 @@
         <v>37.5</v>
       </c>
       <c r="AB86" t="n">
-        <v>14.29736215071794</v>
+        <v>14.11117846209332</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>4.154044798718615</v>
+        <v>4.12033729145379</v>
       </c>
       <c r="AE86" t="n">
         <v>51</v>
@@ -10024,16 +10038,16 @@
         <v>46238</v>
       </c>
       <c r="C87" t="n">
-        <v>5.688186573135311</v>
+        <v>5.752700515758985</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -10056,7 +10070,7 @@
         <v>29.54558799520699</v>
       </c>
       <c r="K87" t="n">
-        <v>4.727451793894488</v>
+        <v>5.915243496801104</v>
       </c>
       <c r="L87" t="n">
         <v>6</v>
@@ -10065,13 +10079,13 @@
         <v>83.33333333333333</v>
       </c>
       <c r="N87" t="n">
-        <v>9.637889717228306</v>
+        <v>8.337490203764601</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>0.2602452379361742</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
         <v>47</v>
@@ -10137,7 +10151,7 @@
         <v>46238</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9584752473674266</v>
+        <v>0.9780642558785843</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10165,22 +10179,22 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>7.379515242471113</v>
+        <v>9.574103202656993</v>
       </c>
       <c r="L88" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M88" t="n">
-        <v>60</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="N88" t="n">
-        <v>12.0185275795009</v>
+        <v>11.63023150978318</v>
       </c>
       <c r="O88" t="n">
         <v>10</v>
       </c>
       <c r="P88" t="n">
-        <v>2.440395406527629</v>
+        <v>0.3886838083952293</v>
       </c>
       <c r="Q88" t="n">
         <v>44</v>
@@ -10246,7 +10260,7 @@
         <v>46238</v>
       </c>
       <c r="C89" t="n">
-        <v>1.949334114531143</v>
+        <v>1.984523893456046</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10274,16 +10288,16 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>5.884622890768787</v>
+        <v>7.796073802799341</v>
       </c>
       <c r="L89" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="M89" t="n">
-        <v>69.23076923076923</v>
+        <v>68.57142857142857</v>
       </c>
       <c r="N89" t="n">
-        <v>13.55774842129218</v>
+        <v>16.05252990993683</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
@@ -10316,16 +10330,16 @@
         <v>28.7873334490923</v>
       </c>
       <c r="Y89" t="n">
-        <v>14.98963060552393</v>
+        <v>13.45500599550143</v>
       </c>
       <c r="Z89" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AA89" t="n">
         <v>33.33333333333334</v>
       </c>
       <c r="AB89" t="n">
-        <v>36.07037617635147</v>
+        <v>24.68761358108778</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
@@ -10365,7 +10379,7 @@
         <v>46238</v>
       </c>
       <c r="C90" t="n">
-        <v>2.641169038383991</v>
+        <v>2.675478932573332</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10393,22 +10407,22 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>4.115541023636204</v>
+        <v>5.468045594177662</v>
       </c>
       <c r="L90" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="M90" t="n">
-        <v>66.66666666666667</v>
+        <v>67.5</v>
       </c>
       <c r="N90" t="n">
-        <v>15.20642055656773</v>
+        <v>15.6798363091836</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>3.73091177183813</v>
+        <v>2.400683914789559</v>
       </c>
       <c r="Q90" t="n">
         <v>42</v>
@@ -10435,16 +10449,16 @@
         <v>33.24184775233741</v>
       </c>
       <c r="Y90" t="n">
-        <v>13.15380803721796</v>
+        <v>12.02563955815183</v>
       </c>
       <c r="Z90" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA90" t="n">
-        <v>25</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AB90" t="n">
-        <v>10.631003022771</v>
+        <v>8.158989511032161</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
@@ -10484,16 +10498,16 @@
         <v>46238</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2329948494465224</v>
+        <v>0.2372594525211416</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -10512,22 +10526,22 @@
         <v>14.9000517126033</v>
       </c>
       <c r="K91" t="n">
-        <v>2.763055398876868</v>
+        <v>4.643970977278489</v>
       </c>
       <c r="L91" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M91" t="n">
-        <v>56</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="N91" t="n">
-        <v>15.9752496989453</v>
+        <v>16.21885791524035</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>0.2305737214638448</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>47</v>
@@ -10593,7 +10607,7 @@
         <v>46238</v>
       </c>
       <c r="C92" t="n">
-        <v>1.101889039316879</v>
+        <v>1.129506479225996</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10621,22 +10635,22 @@
         <v>23.07989300517391</v>
       </c>
       <c r="K92" t="n">
-        <v>4.577967624336554</v>
+        <v>7.19908067077657</v>
       </c>
       <c r="L92" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M92" t="n">
-        <v>65</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N92" t="n">
-        <v>14.80197958437172</v>
+        <v>13.10328592465721</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>3.272230713027469</v>
+        <v>0.7471326472315409</v>
       </c>
       <c r="Q92" t="n">
         <v>56</v>
@@ -10702,7 +10716,7 @@
         <v>46238</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04142598047956436</v>
+        <v>0.04185694363395753</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10730,22 +10744,22 @@
         <v>19.49655531533526</v>
       </c>
       <c r="K93" t="n">
-        <v>0.4666653636776763</v>
+        <v>1.511841132971847</v>
       </c>
       <c r="L93" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M93" t="n">
-        <v>62.5</v>
+        <v>61.22448979591837</v>
       </c>
       <c r="N93" t="n">
-        <v>15.54303520799231</v>
+        <v>14.67814716503741</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>5.507632423443432</v>
+        <v>4.421315599181241</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10811,7 +10825,7 @@
         <v>46238</v>
       </c>
       <c r="C94" t="n">
-        <v>6.14555462476449</v>
+        <v>6.073463524407338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10836,25 +10850,25 @@
         <v>10</v>
       </c>
       <c r="J94" t="n">
-        <v>11.31569733043036</v>
+        <v>12.24582326961634</v>
       </c>
       <c r="K94" t="n">
-        <v>2.160086926100568</v>
+        <v>2.031802120141357</v>
       </c>
       <c r="L94" t="n">
         <v>52</v>
       </c>
       <c r="M94" t="n">
-        <v>32.69230769230769</v>
+        <v>36.53846153846154</v>
       </c>
       <c r="N94" t="n">
-        <v>13.21428865713718</v>
+        <v>12.66321508749038</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>5.71643314881265</v>
+        <v>5.849350649350638</v>
       </c>
       <c r="Q94" t="n">
         <v>40</v>
@@ -10881,7 +10895,7 @@
         <v>46.65531127586331</v>
       </c>
       <c r="Y94" t="n">
-        <v>9.400039302961527</v>
+        <v>10.46283204629581</v>
       </c>
       <c r="Z94" t="n">
         <v>2</v>
@@ -10926,7 +10940,7 @@
         <v>46238</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1392081127114796</v>
+        <v>0.14092538340977</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10954,22 +10968,22 @@
         <v>23.400044414021</v>
       </c>
       <c r="K95" t="n">
-        <v>0.4117168642452373</v>
+        <v>1.650395385039394</v>
       </c>
       <c r="L95" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M95" t="n">
-        <v>60.8695652173913</v>
+        <v>65.38461538461539</v>
       </c>
       <c r="N95" t="n">
-        <v>20.35553191478007</v>
+        <v>19.29680295145889</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>5.565369570674727</v>
+        <v>4.278984453021395</v>
       </c>
       <c r="Q95" t="n">
         <v>22</v>
@@ -11035,7 +11049,7 @@
         <v>46238</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1314276010428676</v>
+        <v>0.1323015942011554</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11063,22 +11077,22 @@
         <v>12.79622946674051</v>
       </c>
       <c r="K96" t="n">
-        <v>1.581993072360799</v>
+        <v>2.257513025901758</v>
       </c>
       <c r="L96" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M96" t="n">
-        <v>60.27397260273973</v>
+        <v>59.72222222222222</v>
       </c>
       <c r="N96" t="n">
-        <v>12.88642560075273</v>
+        <v>13.57796746080097</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>8.286908607554832</v>
+        <v>7.571558064527828</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11105,16 +11119,16 @@
         <v>16.74415231729489</v>
       </c>
       <c r="Y96" t="n">
-        <v>11.41667185806693</v>
+        <v>10.82759298787469</v>
       </c>
       <c r="Z96" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AA96" t="n">
-        <v>40</v>
+        <v>36.8421052631579</v>
       </c>
       <c r="AB96" t="n">
-        <v>16.42948776937994</v>
+        <v>18.11843988336842</v>
       </c>
       <c r="AC96" t="n">
         <v>8</v>
@@ -11154,7 +11168,7 @@
         <v>46238</v>
       </c>
       <c r="C97" t="n">
-        <v>1.832626501115223</v>
+        <v>1.855166976030003</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11182,22 +11196,22 @@
         <v>23.59665213438843</v>
       </c>
       <c r="K97" t="n">
-        <v>2.535127082403932</v>
+        <v>3.796262648477167</v>
       </c>
       <c r="L97" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M97" t="n">
-        <v>54.16666666666666</v>
+        <v>56.52173913043478</v>
       </c>
       <c r="N97" t="n">
-        <v>11.73441643678193</v>
+        <v>12.9157255095876</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>1.428654705249266</v>
+        <v>0.1962858260251776</v>
       </c>
       <c r="Q97" t="n">
         <v>51</v>
@@ -11263,7 +11277,7 @@
         <v>46238</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6316936409985818</v>
+        <v>0.6528842021997929</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11280,7 +11294,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H98" t="n">
         <v>5</v>
       </c>
@@ -11291,22 +11309,22 @@
         <v>19.60032989595409</v>
       </c>
       <c r="K98" t="n">
-        <v>5.211542174754591</v>
+        <v>8.740929648093033</v>
       </c>
       <c r="L98" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="M98" t="n">
-        <v>53.57142857142857</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="N98" t="n">
-        <v>18.85960633705799</v>
+        <v>16.5293966310366</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>4.551266644577723</v>
+        <v>1.157862412967758</v>
       </c>
       <c r="Q98" t="n">
         <v>48</v>
@@ -11372,7 +11390,7 @@
         <v>46238</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4773450629692915</v>
+        <v>0.4829323530140469</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11400,22 +11418,22 @@
         <v>28.77817890954801</v>
       </c>
       <c r="K99" t="n">
-        <v>2.692748421695002</v>
+        <v>3.894759745235188</v>
       </c>
       <c r="L99" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M99" t="n">
-        <v>68.42105263157895</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N99" t="n">
-        <v>12.20882658747631</v>
+        <v>12.77959199349419</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>1.272973601735661</v>
+        <v>0.1012950557110592</v>
       </c>
       <c r="Q99" t="n">
         <v>35</v>
@@ -11481,7 +11499,7 @@
         <v>46238</v>
       </c>
       <c r="C100" t="n">
-        <v>322.0503989509643</v>
+        <v>331.1723393095031</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11498,11 +11516,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>5</v>
       </c>
@@ -11513,16 +11527,16 @@
         <v>25.87300653788257</v>
       </c>
       <c r="K100" t="n">
-        <v>5.07844089369669</v>
+        <v>8.054742969156891</v>
       </c>
       <c r="L100" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M100" t="n">
-        <v>75</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N100" t="n">
-        <v>12.43291671760379</v>
+        <v>13.39481695000269</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11594,16 +11608,16 @@
         <v>46238</v>
       </c>
       <c r="C101" t="n">
-        <v>321.2044364472218</v>
+        <v>325.7803739343845</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -11622,22 +11636,22 @@
         <v>14.61847018515478</v>
       </c>
       <c r="K101" t="n">
-        <v>1.715501763790805</v>
+        <v>3.164559512477827</v>
       </c>
       <c r="L101" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="M101" t="n">
-        <v>57.14285714285715</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N101" t="n">
-        <v>11.18629778942283</v>
+        <v>9.217090275853739</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
       </c>
       <c r="P101" t="n">
-        <v>0.2796999781506937</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
         <v>29</v>
@@ -11703,7 +11717,7 @@
         <v>46238</v>
       </c>
       <c r="C102" t="n">
-        <v>386.6263650163695</v>
+        <v>388.837973408214</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11802,16 +11816,16 @@
         <v>46238</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7094987967975557</v>
+        <v>0.7328120176670864</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -11830,18 +11844,22 @@
         <v>31.27238030517686</v>
       </c>
       <c r="K103" t="n">
-        <v>9.119738927563681</v>
+        <v>12.70527365479126</v>
       </c>
       <c r="L103" t="n">
-        <v>1</v>
-      </c>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M103" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="N103" t="n">
+        <v>15.31498501728872</v>
+      </c>
       <c r="O103" t="n">
         <v>10</v>
       </c>
       <c r="P103" t="n">
-        <v>0.8066927955359793</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
         <v>43</v>
@@ -11865,25 +11883,25 @@
         <v>68.18181818181819</v>
       </c>
       <c r="X103" t="n">
-        <v>10.91420766588502</v>
+        <v>14.2580428648073</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.617888975709003</v>
+        <v>1.35900210705806</v>
       </c>
       <c r="Z103" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="AA103" t="n">
-        <v>33.33333333333334</v>
+        <v>46.55172413793103</v>
       </c>
       <c r="AB103" t="n">
-        <v>11.46966802156439</v>
+        <v>10.43347479087641</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>6.48706452610599</v>
+        <v>6.732492609360675</v>
       </c>
       <c r="AE103" t="n">
         <v>34</v>
@@ -11917,7 +11935,7 @@
         <v>46238</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04899620798650776</v>
+        <v>0.04942905168834941</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11934,11 +11952,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.19: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>5</v>
       </c>
@@ -11946,25 +11960,25 @@
         <v>10</v>
       </c>
       <c r="J104" t="n">
-        <v>27.73688559743085</v>
+        <v>27.71893445721953</v>
       </c>
       <c r="K104" t="n">
-        <v>1.304346550094482</v>
+        <v>2.173910916824151</v>
       </c>
       <c r="L104" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M104" t="n">
-        <v>76.19047619047619</v>
+        <v>70</v>
       </c>
       <c r="N104" t="n">
-        <v>15.30180212803625</v>
+        <v>13.71309755213932</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>2.660945499088263</v>
+        <v>1.787236161158989</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>

--- a/TDA_Result.xlsx
+++ b/TDA_Result.xlsx
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4530646230418026</v>
+        <v>0.4481496029691159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -739,22 +739,22 @@
         <v>14.94856954517825</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.877184950901469</v>
+        <v>5.90911399934021</v>
       </c>
       <c r="Z2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA2" t="n">
-        <v>44.11764705882353</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.73616807324932</v>
+        <v>11.6279462467923</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.282929597370154</v>
+        <v>2.222198227196126</v>
       </c>
       <c r="AE2" t="n">
         <v>43</v>
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7479562640643116</v>
+        <v>0.748317327017355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>12.13279917920569</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.690888498758369</v>
+        <v>1.643431475112589</v>
       </c>
       <c r="Z3" t="n">
         <v>64</v>
@@ -863,7 +863,7 @@
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>8.452025833980493</v>
+        <v>8.496197712278796</v>
       </c>
       <c r="AE3" t="n">
         <v>38</v>
@@ -872,10 +872,10 @@
         <v>60.52631578947368</v>
       </c>
       <c r="AG3" t="n">
-        <v>31.67720124076367</v>
+        <v>31.9061389697014</v>
       </c>
       <c r="AH3" t="n">
-        <v>28.84911454871001</v>
+        <v>28.62017681977228</v>
       </c>
       <c r="AI3" t="n">
         <v>44.71786799604255</v>
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C4" t="n">
-        <v>1.428184182163316</v>
+        <v>1.422013216104769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         <v>27.63389482946404</v>
       </c>
       <c r="K4" t="n">
-        <v>10.57986925542409</v>
+        <v>10.10207050337513</v>
       </c>
       <c r="L4" t="n">
         <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N4" t="n">
-        <v>15.39789546009553</v>
+        <v>13.69615600604336</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -949,10 +949,10 @@
         <v>58.49056603773585</v>
       </c>
       <c r="S4" t="n">
-        <v>37.34056829450487</v>
+        <v>37.63323703111325</v>
       </c>
       <c r="T4" t="n">
-        <v>21.14999774323098</v>
+        <v>20.85732900662259</v>
       </c>
       <c r="U4" t="n">
         <v>45.09442218134437</v>
@@ -964,25 +964,25 @@
         <v>61.64383561643836</v>
       </c>
       <c r="X4" t="n">
-        <v>11.23129951738115</v>
+        <v>11.23805603488277</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5856537366582315</v>
+        <v>1.021220229838793</v>
       </c>
       <c r="Z4" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AA4" t="n">
-        <v>33.92857142857143</v>
+        <v>37.93103448275862</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.42949452781888</v>
+        <v>12.16310113391574</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>9.469806539192859</v>
+        <v>9.071418935463582</v>
       </c>
       <c r="AE4" t="n">
         <v>45</v>
@@ -991,10 +991,10 @@
         <v>60</v>
       </c>
       <c r="AG4" t="n">
-        <v>38.7582984030571</v>
+        <v>38.92068184220413</v>
       </c>
       <c r="AH4" t="n">
-        <v>21.2417015969429</v>
+        <v>21.07931815779587</v>
       </c>
       <c r="AI4" t="n">
         <v>45.45185459035139</v>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2633411813657943</v>
+        <v>0.2631722944139569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
         <v>62</v>
       </c>
       <c r="S5" t="n">
-        <v>44.84124694222501</v>
+        <v>44.94124694222501</v>
       </c>
       <c r="T5" t="n">
-        <v>17.15875305777499</v>
+        <v>17.05875305777499</v>
       </c>
       <c r="U5" t="n">
         <v>48.15044693099298</v>
@@ -1076,7 +1076,7 @@
         <v>16.70172291026088</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.74031481131283</v>
+        <v>5.800765785331031</v>
       </c>
       <c r="Z5" t="n">
         <v>29</v>
@@ -1085,28 +1085,28 @@
         <v>37.93103448275862</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.56925120345615</v>
+        <v>17.33713608175451</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.519095496829017</v>
+        <v>4.457822029741143</v>
       </c>
       <c r="AE5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AF5" t="n">
-        <v>48.88888888888889</v>
+        <v>50</v>
       </c>
       <c r="AG5" t="n">
-        <v>25.702862759323</v>
+        <v>26.09501963826463</v>
       </c>
       <c r="AH5" t="n">
-        <v>23.18602612956589</v>
+        <v>23.90498036173537</v>
       </c>
       <c r="AI5" t="n">
-        <v>34.9570237528785</v>
+        <v>35.8317605399894</v>
       </c>
       <c r="AJ5" t="n">
         <v>66</v>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C6" t="n">
-        <v>1.98767897162422</v>
+        <v>2.003220410450814</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,16 +1153,16 @@
         <v>23.73506360720576</v>
       </c>
       <c r="K6" t="n">
-        <v>4.689784122169161</v>
+        <v>5.508341796185579</v>
       </c>
       <c r="L6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M6" t="n">
-        <v>70</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="N6" t="n">
-        <v>9.966151438936262</v>
+        <v>10.09994808370767</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
@@ -1177,10 +1177,10 @@
         <v>67.5</v>
       </c>
       <c r="S6" t="n">
-        <v>47.37539610276927</v>
+        <v>47.77901735896405</v>
       </c>
       <c r="T6" t="n">
-        <v>20.12460389723073</v>
+        <v>19.72098264103595</v>
       </c>
       <c r="U6" t="n">
         <v>52.01774618987768</v>
@@ -1195,7 +1195,7 @@
         <v>44.49622708587002</v>
       </c>
       <c r="Y6" t="n">
-        <v>20.1584027294741</v>
+        <v>19.53413024004713</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1215,10 +1215,10 @@
         <v>45.83333333333334</v>
       </c>
       <c r="AG6" t="n">
-        <v>41.31848933822723</v>
+        <v>41.65634683346627</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.514843995106105</v>
+        <v>4.176986499867063</v>
       </c>
       <c r="AI6" t="n">
         <v>32.57524229286744</v>
@@ -1237,10 +1237,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C7" t="n">
-        <v>2.176981730826526</v>
+        <v>2.173483597863762</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,16 +1268,16 @@
         <v>11.35312764557068</v>
       </c>
       <c r="K7" t="n">
-        <v>4.296196037500311</v>
+        <v>4.128605305762179</v>
       </c>
       <c r="L7" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M7" t="n">
-        <v>51.85185185185185</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="N7" t="n">
-        <v>13.8868159829741</v>
+        <v>13.18265863947417</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1292,10 +1292,10 @@
         <v>58.8235294117647</v>
       </c>
       <c r="S7" t="n">
-        <v>51.70218938827708</v>
+        <v>51.42401469059773</v>
       </c>
       <c r="T7" t="n">
-        <v>7.121340023487626</v>
+        <v>7.399514721166973</v>
       </c>
       <c r="U7" t="n">
         <v>45.16533720637157</v>
@@ -1310,22 +1310,22 @@
         <v>13.79329344082609</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.544684228111742</v>
+        <v>7.693248170153499</v>
       </c>
       <c r="Z7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>56.52173913043478</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.960300666112964</v>
+        <v>8.839646921407008</v>
       </c>
       <c r="AC7" t="n">
         <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.655678314858789</v>
+        <v>2.499006610154197</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3319108321222949</v>
+        <v>0.3327489813462158</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>22.10694516187944</v>
       </c>
       <c r="K8" t="n">
-        <v>5.530318881407026</v>
+        <v>5.796806583254588</v>
       </c>
       <c r="L8" t="n">
         <v>4</v>
@@ -1402,7 +1402,7 @@
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.340257420588632</v>
+        <v>2.082476293848878</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5796871048094565</v>
+        <v>0.585621406830838</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,19 +1493,19 @@
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>11.07138721870453</v>
+        <v>10.57037035785485</v>
       </c>
       <c r="K9" t="n">
-        <v>4.302838753597849</v>
+        <v>5.370595034039449</v>
       </c>
       <c r="L9" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="M9" t="n">
-        <v>40.54054054054054</v>
+        <v>37.5</v>
       </c>
       <c r="N9" t="n">
-        <v>15.33035988439627</v>
+        <v>16.04479078410657</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C10" t="n">
-        <v>2.04552148138048</v>
+        <v>2.041056585148209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,37 +1605,37 @@
         <v>10.23694539327734</v>
       </c>
       <c r="K10" t="n">
-        <v>1.283356030175908</v>
+        <v>1.062278090468438</v>
       </c>
       <c r="L10" t="n">
         <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>41.86046511627907</v>
+        <v>39.53488372093023</v>
       </c>
       <c r="N10" t="n">
-        <v>9.946203451885726</v>
+        <v>9.789932158108417</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>8.606195836586528</v>
+        <v>8.843776410354366</v>
       </c>
       <c r="Q10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R10" t="n">
-        <v>50</v>
+        <v>51.16279069767442</v>
       </c>
       <c r="S10" t="n">
-        <v>36.14225028498147</v>
+        <v>37.07477737648844</v>
       </c>
       <c r="T10" t="n">
-        <v>13.85774971501853</v>
+        <v>14.08801332118598</v>
       </c>
       <c r="U10" t="n">
-        <v>35.8317605399894</v>
+        <v>36.75230846944931</v>
       </c>
       <c r="V10" t="n">
         <v>54</v>
@@ -1661,10 +1661,10 @@
         <v>53.33333333333334</v>
       </c>
       <c r="AG10" t="n">
-        <v>39.46550909050909</v>
+        <v>39.64895902395903</v>
       </c>
       <c r="AH10" t="n">
-        <v>13.86782424282425</v>
+        <v>13.68437430937431</v>
       </c>
       <c r="AI10" t="n">
         <v>36.1422996198733</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C11" t="n">
-        <v>7.367032378956433</v>
+        <v>7.446388328339105</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,11 +1703,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>5</v>
       </c>
@@ -1718,16 +1714,16 @@
         <v>20.56423081971027</v>
       </c>
       <c r="K11" t="n">
-        <v>5.556970824536367</v>
+        <v>6.694005820835192</v>
       </c>
       <c r="L11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M11" t="n">
-        <v>81.25</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N11" t="n">
-        <v>14.50308943650603</v>
+        <v>14.54874782819977</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1742,10 +1738,10 @@
         <v>61.22448979591837</v>
       </c>
       <c r="S11" t="n">
-        <v>51.13990211420917</v>
+        <v>51.19092252237243</v>
       </c>
       <c r="T11" t="n">
-        <v>10.08458768170919</v>
+        <v>10.03356727354593</v>
       </c>
       <c r="U11" t="n">
         <v>47.24599944352045</v>
@@ -1796,10 +1792,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C12" t="n">
-        <v>6.336384023299431</v>
+        <v>6.479461403558304</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,16 +1823,16 @@
         <v>20.08266526523165</v>
       </c>
       <c r="K12" t="n">
-        <v>10.31458367090165</v>
+        <v>12.80551881276546</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>50</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N12" t="n">
-        <v>30.74991940184407</v>
+        <v>22.33927009741701</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -1866,25 +1862,25 @@
         <v>70.58823529411765</v>
       </c>
       <c r="X12" t="n">
-        <v>10.86386790494764</v>
+        <v>13.26296211695348</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4954582989265099</v>
+        <v>0.4038772213247221</v>
       </c>
       <c r="Z12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AA12" t="n">
-        <v>31.57894736842105</v>
+        <v>40</v>
       </c>
       <c r="AB12" t="n">
-        <v>14.5203734855606</v>
+        <v>14.22529094583299</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.512033195020746</v>
+        <v>1.602595296025955</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -1915,10 +1911,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3012017170103529</v>
+        <v>0.2993269388366395</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1946,10 +1942,10 @@
         <v>38.11781916800814</v>
       </c>
       <c r="K13" t="n">
-        <v>5.843775150873043</v>
+        <v>5.18496881521906</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1982,7 +1978,7 @@
         <v>35.74308703619145</v>
       </c>
       <c r="Y13" t="n">
-        <v>22.02639746755335</v>
+        <v>22.51173071732565</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2014,10 +2010,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C14" t="n">
-        <v>8.087434545920766</v>
+        <v>8.045462618692428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,10 +2055,10 @@
         <v>60.97560975609756</v>
       </c>
       <c r="S14" t="n">
-        <v>34.4990901342012</v>
+        <v>34.77464671535319</v>
       </c>
       <c r="T14" t="n">
-        <v>26.47651962189637</v>
+        <v>26.20096304074437</v>
       </c>
       <c r="U14" t="n">
         <v>45.72685693412379</v>
@@ -2077,16 +2073,16 @@
         <v>14.33662537827827</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.535209320711344</v>
+        <v>7.020270111068116</v>
       </c>
       <c r="Z14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>38.46153846153846</v>
+        <v>37.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.18997592652526</v>
+        <v>11.56978199300831</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2101,10 +2097,10 @@
         <v>52.63157894736842</v>
       </c>
       <c r="AG14" t="n">
-        <v>26.68358875742138</v>
+        <v>26.75224893688489</v>
       </c>
       <c r="AH14" t="n">
-        <v>25.94799018994704</v>
+        <v>25.87933001048353</v>
       </c>
       <c r="AI14" t="n">
         <v>37.25897138449667</v>
@@ -2123,10 +2119,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C15" t="n">
-        <v>11.63160287098617</v>
+        <v>11.79230445221803</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,19 +2147,19 @@
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>19.49276356151121</v>
+        <v>16.27559902090345</v>
       </c>
       <c r="K15" t="n">
-        <v>9.517823686728777</v>
+        <v>11.03091587485958</v>
       </c>
       <c r="L15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M15" t="n">
-        <v>61.90476190476191</v>
+        <v>70.83333333333333</v>
       </c>
       <c r="N15" t="n">
-        <v>14.71720560319735</v>
+        <v>14.06653819062704</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
@@ -2178,10 +2174,10 @@
         <v>76.92307692307692</v>
       </c>
       <c r="S15" t="n">
-        <v>53.33079360301163</v>
+        <v>53.33993478862341</v>
       </c>
       <c r="T15" t="n">
-        <v>23.59228332006529</v>
+        <v>23.58314213445351</v>
       </c>
       <c r="U15" t="n">
         <v>61.66374277165825</v>
@@ -2193,25 +2189,25 @@
         <v>79.56989247311827</v>
       </c>
       <c r="X15" t="n">
-        <v>10.11195292915226</v>
+        <v>11.12987391039868</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.5395683453237488</v>
+        <v>0.08904719501335867</v>
       </c>
       <c r="Z15" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.72727272727273</v>
+        <v>26.08695652173913</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.342950854998504</v>
+        <v>11.6548836476784</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>9.511754068716083</v>
+        <v>9.919786096256678</v>
       </c>
       <c r="AE15" t="n">
         <v>31</v>
@@ -2220,10 +2216,10 @@
         <v>58.06451612903226</v>
       </c>
       <c r="AG15" t="n">
-        <v>25.06124739654446</v>
+        <v>25.2719114250453</v>
       </c>
       <c r="AH15" t="n">
-        <v>33.0032687324878</v>
+        <v>32.79260470398695</v>
       </c>
       <c r="AI15" t="n">
         <v>40.76626249536972</v>
@@ -2242,10 +2238,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C16" t="n">
-        <v>36.49336524622245</v>
+        <v>36.59608208789945</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,25 +2266,25 @@
         <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>18.2920442587057</v>
+        <v>17.40096492560246</v>
       </c>
       <c r="K16" t="n">
-        <v>5.187253612984044</v>
+        <v>5.483321196855973</v>
       </c>
       <c r="L16" t="n">
         <v>42</v>
       </c>
       <c r="M16" t="n">
-        <v>54.76190476190476</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N16" t="n">
-        <v>17.84367448638176</v>
+        <v>15.42901561708397</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>4.575408351969656</v>
+        <v>4.281889072031464</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2297,10 +2293,10 @@
         <v>67.85714285714286</v>
       </c>
       <c r="S16" t="n">
-        <v>54.02219122768298</v>
+        <v>54.06943234635268</v>
       </c>
       <c r="T16" t="n">
-        <v>13.83495162945988</v>
+        <v>13.78771051079018</v>
       </c>
       <c r="U16" t="n">
         <v>49.33884318085762</v>
@@ -2351,14 +2347,14 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7323913351933847</v>
+        <v>0.7365460942150444</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2368,7 +2364,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2382,22 +2378,22 @@
         <v>14.16674936134154</v>
       </c>
       <c r="K17" t="n">
-        <v>4.017544722387623</v>
+        <v>4.607622473965778</v>
       </c>
       <c r="L17" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="M17" t="n">
-        <v>67.27272727272727</v>
+        <v>74.50980392156863</v>
       </c>
       <c r="N17" t="n">
-        <v>14.63779299529553</v>
+        <v>15.78087961695294</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>3.828638032402276</v>
+        <v>3.242954428945666</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2406,10 +2402,10 @@
         <v>65.21739130434783</v>
       </c>
       <c r="S17" t="n">
-        <v>46.04461306455928</v>
+        <v>46.09896089064624</v>
       </c>
       <c r="T17" t="n">
-        <v>19.17277823978855</v>
+        <v>19.11843041370159</v>
       </c>
       <c r="U17" t="n">
         <v>50.77005884206276</v>
@@ -2424,22 +2420,22 @@
         <v>15.7396793517258</v>
       </c>
       <c r="Y17" t="n">
-        <v>10.12801719772811</v>
+        <v>9.618185345002017</v>
       </c>
       <c r="Z17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA17" t="n">
-        <v>38.09523809523809</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.372889596389378</v>
+        <v>11.00132337973763</v>
       </c>
       <c r="AC17" t="n">
         <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>0.4224463255749322</v>
       </c>
       <c r="AE17" t="n">
         <v>35</v>
@@ -2448,10 +2444,10 @@
         <v>60</v>
       </c>
       <c r="AG17" t="n">
-        <v>42.73923624726688</v>
+        <v>42.74330625133689</v>
       </c>
       <c r="AH17" t="n">
-        <v>17.26076375273312</v>
+        <v>17.25669374866311</v>
       </c>
       <c r="AI17" t="n">
         <v>43.5727090128925</v>
@@ -2470,10 +2466,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1043268548017279</v>
+        <v>0.1044701437631723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2498,25 +2494,25 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>27.33452427541018</v>
+        <v>25.10069993473878</v>
       </c>
       <c r="K18" t="n">
-        <v>4.401749579232339</v>
+        <v>4.545141405801068</v>
       </c>
       <c r="L18" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="M18" t="n">
-        <v>45.45454545454545</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="N18" t="n">
-        <v>19.38924952671559</v>
+        <v>22.19834958948873</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>5.362218969825849</v>
+        <v>5.217706457563076</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2525,10 +2521,10 @@
         <v>77.19298245614036</v>
       </c>
       <c r="S18" t="n">
-        <v>41.98819088290104</v>
+        <v>41.9297113507373</v>
       </c>
       <c r="T18" t="n">
-        <v>35.20479157323932</v>
+        <v>35.26327110540306</v>
       </c>
       <c r="U18" t="n">
         <v>64.79398895432649</v>
@@ -2557,10 +2553,10 @@
         <v>59.52380952380953</v>
       </c>
       <c r="AG18" t="n">
-        <v>39.39994803683889</v>
+        <v>39.49419406858492</v>
       </c>
       <c r="AH18" t="n">
-        <v>20.12386148697064</v>
+        <v>20.02961545522461</v>
       </c>
       <c r="AI18" t="n">
         <v>44.49431275003934</v>
@@ -2579,10 +2575,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02524036894532288</v>
+        <v>0.02522418169746321</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2607,25 +2603,25 @@
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>23.99412305210119</v>
+        <v>22.96673379938283</v>
       </c>
       <c r="K19" t="n">
-        <v>2.190897326452679</v>
+        <v>2.125359877788258</v>
       </c>
       <c r="L19" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M19" t="n">
-        <v>73.68421052631579</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N19" t="n">
-        <v>19.13887577281496</v>
+        <v>19.55780077327282</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>7.641681282630142</v>
+        <v>7.710758749477309</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2688,10 +2684,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C20" t="n">
-        <v>1.832030004098632</v>
+        <v>1.839263172137394</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2751,7 +2747,7 @@
         <v>20.34011802710127</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.52127974282245</v>
+        <v>7.156157925967211</v>
       </c>
       <c r="Z20" t="n">
         <v>18</v>
@@ -2760,7 +2756,7 @@
         <v>44.44444444444444</v>
       </c>
       <c r="AB20" t="n">
-        <v>13.15851961577055</v>
+        <v>12.96967327390692</v>
       </c>
       <c r="AC20" t="n">
         <v>4</v>
@@ -2797,10 +2793,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C21" t="n">
-        <v>0.959975312724288</v>
+        <v>0.9694493203538858</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,25 +2821,25 @@
         <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>14.08722322280853</v>
+        <v>13.7580634602656</v>
       </c>
       <c r="K21" t="n">
-        <v>2.610649675984811</v>
+        <v>3.623315382094949</v>
       </c>
       <c r="L21" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M21" t="n">
-        <v>55.93220338983051</v>
+        <v>50</v>
       </c>
       <c r="N21" t="n">
-        <v>16.09406398265327</v>
+        <v>14.21383982371403</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>5.252232922248545</v>
+        <v>4.223648511695188</v>
       </c>
       <c r="Q21" t="n">
         <v>41</v>
@@ -2852,10 +2848,10 @@
         <v>70.73170731707317</v>
       </c>
       <c r="S21" t="n">
-        <v>44.95620516462016</v>
+        <v>45.01718077437626</v>
       </c>
       <c r="T21" t="n">
-        <v>25.77550215245302</v>
+        <v>25.71452654269692</v>
       </c>
       <c r="U21" t="n">
         <v>55.52053227700284</v>
@@ -2884,10 +2880,10 @@
         <v>61.53846153846154</v>
       </c>
       <c r="AG21" t="n">
-        <v>34.67662338757323</v>
+        <v>34.72910501900224</v>
       </c>
       <c r="AH21" t="n">
-        <v>26.86183815088831</v>
+        <v>26.8093565194593</v>
       </c>
       <c r="AI21" t="n">
         <v>45.89906145692508</v>
@@ -2906,10 +2902,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C22" t="n">
-        <v>0.816946577312556</v>
+        <v>0.3247613218292883</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,7 +2919,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2937,7 +2933,7 @@
         <v>20.35908649698318</v>
       </c>
       <c r="K22" t="n">
-        <v>8.82639660183051</v>
+        <v>9.484721073664048</v>
       </c>
       <c r="L22" t="n">
         <v>8</v>
@@ -2946,13 +2942,13 @@
         <v>62.5</v>
       </c>
       <c r="N22" t="n">
-        <v>14.03695461188192</v>
+        <v>13.73609705603676</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>1.078417952643806</v>
+        <v>0.470640032036318</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -2975,17 +2971,27 @@
       <c r="W22" t="n">
         <v>72.22222222222223</v>
       </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
+      <c r="X22" t="n">
+        <v>13.73655091481325</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>3.738314382624219</v>
+      </c>
       <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>38.70967741935484</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>13.95240582378237</v>
+      </c>
       <c r="AC22" t="n">
         <v>6</v>
       </c>
-      <c r="AD22" t="inlineStr"/>
+      <c r="AD22" t="n">
+        <v>2.34951798617532</v>
+      </c>
       <c r="AE22" t="n">
         <v>0</v>
       </c>
@@ -3007,10 +3013,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7816100559513667</v>
+        <v>0.8479528758847078</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,11 +3033,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>5</v>
       </c>
@@ -3039,20 +3041,16 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>24.64686798085608</v>
+        <v>23.56853924970225</v>
       </c>
       <c r="K23" t="n">
-        <v>12.24511163042854</v>
+        <v>21.77244200776267</v>
       </c>
       <c r="L23" t="n">
-        <v>5</v>
-      </c>
-      <c r="M23" t="n">
-        <v>100</v>
-      </c>
-      <c r="N23" t="n">
-        <v>13.98850448712136</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
         <v>5</v>
       </c>
@@ -3081,25 +3079,25 @@
         <v>87.5</v>
       </c>
       <c r="X23" t="n">
-        <v>16.47394175770236</v>
+        <v>23.76475220013776</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.630709207103966</v>
+        <v>1.609755731707319</v>
       </c>
       <c r="Z23" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AA23" t="n">
-        <v>43.75</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB23" t="n">
-        <v>11.61243051167745</v>
+        <v>10.3788617544537</v>
       </c>
       <c r="AC23" t="n">
         <v>6</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.458553729515145</v>
+        <v>4.462072739977419</v>
       </c>
       <c r="AE23" t="n">
         <v>10</v>
@@ -3130,10 +3128,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1859373799715338</v>
+        <v>0.1828753056929751</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3158,25 +3156,25 @@
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>23.34450349594161</v>
+        <v>23.26504282616538</v>
       </c>
       <c r="K24" t="n">
-        <v>6.230363756313895</v>
+        <v>4.480929271919476</v>
       </c>
       <c r="L24" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M24" t="n">
-        <v>37.5</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N24" t="n">
-        <v>14.06352044548723</v>
+        <v>12.73592039462029</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>3.548548748579483</v>
+        <v>5.282371401690678</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3194,10 +3192,10 @@
         <v>51.01091635454027</v>
       </c>
       <c r="V24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W24" t="n">
-        <v>74.07407407407408</v>
+        <v>75</v>
       </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
@@ -3239,10 +3237,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C25" t="n">
-        <v>3.94801414721106</v>
+        <v>3.955992267274341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3284,10 +3282,10 @@
         <v>68.18181818181819</v>
       </c>
       <c r="S25" t="n">
-        <v>36.9404339161862</v>
+        <v>37.02646258844482</v>
       </c>
       <c r="T25" t="n">
-        <v>31.24138426563199</v>
+        <v>31.15535559337336</v>
       </c>
       <c r="U25" t="n">
         <v>53.44310393781777</v>
@@ -3316,10 +3314,10 @@
         <v>53.48837209302326</v>
       </c>
       <c r="AG25" t="n">
-        <v>50.65061301365994</v>
+        <v>50.76681922686738</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.837759079363316</v>
+        <v>2.721552866155882</v>
       </c>
       <c r="AI25" t="n">
         <v>38.91564047231397</v>
@@ -3338,10 +3336,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4345549974138045</v>
+        <v>0.4338558942967459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3437,10 +3435,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C27" t="n">
-        <v>34.24276577570613</v>
+        <v>34.01060357163774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,10 +3463,10 @@
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>60.4569342526416</v>
+        <v>60.45453229009195</v>
       </c>
       <c r="K27" t="n">
-        <v>2.45437382001259</v>
+        <v>1.75356356736398</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3479,7 +3477,7 @@
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>5.412776412776421</v>
+        <v>6.138788867576794</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -3522,10 +3520,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C28" t="n">
-        <v>1.464993052008209</v>
+        <v>1.475614503706198</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3553,16 +3551,16 @@
         <v>24.87361787048376</v>
       </c>
       <c r="K28" t="n">
-        <v>5.066698022741223</v>
+        <v>5.828449661485213</v>
       </c>
       <c r="L28" t="n">
         <v>16</v>
       </c>
       <c r="M28" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="N28" t="n">
-        <v>12.81456999130203</v>
+        <v>16.04159935017336</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
@@ -3577,10 +3575,10 @@
         <v>57.5</v>
       </c>
       <c r="S28" t="n">
-        <v>59.75202829605958</v>
+        <v>59.09887512108735</v>
       </c>
       <c r="T28" t="n">
-        <v>-2.252028296059578</v>
+        <v>-1.598875121087346</v>
       </c>
       <c r="U28" t="n">
         <v>42.19506854199106</v>
@@ -3631,10 +3629,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3729264259530697</v>
+        <v>0.3794137012484565</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3651,7 +3649,11 @@
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H29" t="n">
         <v>5</v>
       </c>
@@ -3659,25 +3661,25 @@
         <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>19.41872247596972</v>
+        <v>19.41382773128674</v>
       </c>
       <c r="K29" t="n">
-        <v>1.025642779458047</v>
+        <v>2.776800498666154</v>
       </c>
       <c r="L29" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M29" t="n">
-        <v>63.63636363636363</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N29" t="n">
-        <v>20.28444810421354</v>
+        <v>22.76363899904027</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>2.944160649425487</v>
+        <v>1.190151372098525</v>
       </c>
       <c r="Q29" t="n">
         <v>6</v>
@@ -3704,7 +3706,7 @@
         <v>55.05052857749912</v>
       </c>
       <c r="Y29" t="n">
-        <v>18.59224642144944</v>
+        <v>17.17611049787314</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3733,7 +3735,7 @@
         <v>23.07242812760128</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -3746,10 +3748,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C30" t="n">
-        <v>0.388070672350295</v>
+        <v>0.3874013809447285</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3774,25 +3776,25 @@
         <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>21.77845247058357</v>
+        <v>21.6314445059014</v>
       </c>
       <c r="K30" t="n">
-        <v>4.976655968541399</v>
+        <v>4.795606539582176</v>
       </c>
       <c r="L30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M30" t="n">
-        <v>61.90476190476191</v>
+        <v>65</v>
       </c>
       <c r="N30" t="n">
-        <v>11.12474155731627</v>
+        <v>11.12294608260836</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>0.02223735481305944</v>
+        <v>0.1950401044156669</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3855,10 +3857,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C31" t="n">
-        <v>0.185727038734683</v>
+        <v>0.1858181339152461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3883,25 +3885,25 @@
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>27.00457192147066</v>
+        <v>27.21774887994811</v>
       </c>
       <c r="K31" t="n">
-        <v>0.6841443198738473</v>
+        <v>1.028573142857137</v>
       </c>
       <c r="L31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M31" t="n">
-        <v>33.33333333333334</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N31" t="n">
-        <v>16.05012874702525</v>
+        <v>13.69665025578728</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>9.252554851665273</v>
+        <v>8.88008865022476</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3964,10 +3966,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C32" t="n">
-        <v>2.273736442237348</v>
+        <v>2.293298391612765</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4027,22 +4029,22 @@
         <v>12.36180984775317</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.981620631007676</v>
+        <v>3.155532505121961</v>
       </c>
       <c r="Z32" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AA32" t="n">
-        <v>40.47619047619047</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="AB32" t="n">
-        <v>9.523041492863745</v>
+        <v>11.65371273481513</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>4.185010615051055</v>
+        <v>5.002317241441023</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4073,10 +4075,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C33" t="n">
-        <v>1.815203188503609</v>
+        <v>1.799324853953008</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4104,22 +4106,22 @@
         <v>12.57251846431013</v>
       </c>
       <c r="K33" t="n">
-        <v>1.740050407354921</v>
+        <v>0.8500880230916774</v>
       </c>
       <c r="L33" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M33" t="n">
-        <v>63.79310344827586</v>
+        <v>62.96296296296296</v>
       </c>
       <c r="N33" t="n">
-        <v>12.3710183755118</v>
+        <v>11.8035712977734</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>2.221297889667362</v>
+        <v>3.123360662002694</v>
       </c>
       <c r="Q33" t="n">
         <v>39</v>
@@ -4182,10 +4184,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8800474970466582</v>
+        <v>0.8803239270528644</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4210,10 +4212,10 @@
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>10.38341521030434</v>
+        <v>10.37797163438468</v>
       </c>
       <c r="K34" t="n">
-        <v>2.800981249907952</v>
+        <v>2.827025848908571</v>
       </c>
       <c r="L34" t="n">
         <v>42</v>
@@ -4228,7 +4230,7 @@
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>1.16634951876311</v>
+        <v>1.140725545067278</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4255,7 +4257,7 @@
         <v>14.68007915548277</v>
       </c>
       <c r="Y34" t="n">
-        <v>7.873271473537091</v>
+        <v>7.844333726172559</v>
       </c>
       <c r="Z34" t="n">
         <v>26</v>
@@ -4279,10 +4281,10 @@
         <v>53.84615384615385</v>
       </c>
       <c r="AG34" t="n">
-        <v>28.41426498030814</v>
+        <v>27.93582805228828</v>
       </c>
       <c r="AH34" t="n">
-        <v>25.4318888658457</v>
+        <v>25.91032579386557</v>
       </c>
       <c r="AI34" t="n">
         <v>38.56944827051576</v>
@@ -4301,10 +4303,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C35" t="n">
-        <v>1.936146617993971</v>
+        <v>1.930700794819965</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4323,7 +4325,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %88.89: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4336,16 +4338,16 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>9.150751044035399</v>
+        <v>8.843741397156691</v>
       </c>
       <c r="L35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M35" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N35" t="n">
-        <v>12.38992893736071</v>
+        <v>12.48259706892392</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4378,7 +4380,7 @@
         <v>42.52272358489104</v>
       </c>
       <c r="Y35" t="n">
-        <v>15.85481630977101</v>
+        <v>16.09149249279481</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -4420,10 +4422,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08329321489036053</v>
+        <v>0.08302959567892415</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4448,19 +4450,19 @@
         <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>20.39128953068605</v>
+        <v>19.86910865198848</v>
       </c>
       <c r="K36" t="n">
-        <v>4.105285698662819</v>
+        <v>3.775797236026768</v>
       </c>
       <c r="L36" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M36" t="n">
-        <v>53.33333333333334</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N36" t="n">
-        <v>12.60275160796857</v>
+        <v>13.72841217631283</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4529,10 +4531,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06373192830043403</v>
+        <v>0.06369105550169608</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4560,7 +4562,7 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>3.744818969146091</v>
+        <v>3.67828495363911</v>
       </c>
       <c r="L37" t="n">
         <v>68</v>
@@ -4569,13 +4571,13 @@
         <v>52.94117647058823</v>
       </c>
       <c r="N37" t="n">
-        <v>20.65527448243167</v>
+        <v>20.71797764396541</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>4.101584130306701</v>
+        <v>4.168389791838667</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4584,10 +4586,10 @@
         <v>55.55555555555556</v>
       </c>
       <c r="S37" t="n">
-        <v>35.35742430487655</v>
+        <v>35.29200562532744</v>
       </c>
       <c r="T37" t="n">
-        <v>20.198131250679</v>
+        <v>20.26354993022812</v>
       </c>
       <c r="U37" t="n">
         <v>39.5810617556973</v>
@@ -4638,19 +4640,19 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C38" t="n">
-        <v>1.692156266716906</v>
+        <v>1.662693875451374</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4658,11 +4660,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %86.36: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>5</v>
       </c>
@@ -4670,40 +4668,40 @@
         <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>18.01910891260425</v>
+        <v>16.52414407302303</v>
       </c>
       <c r="K38" t="n">
-        <v>6.805130046488927</v>
+        <v>4.945529610944654</v>
       </c>
       <c r="L38" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M38" t="n">
-        <v>86.36363636363636</v>
+        <v>65.625</v>
       </c>
       <c r="N38" t="n">
-        <v>13.64361758037937</v>
+        <v>12.37025528795528</v>
       </c>
       <c r="O38" t="n">
         <v>6</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.004778758051428</v>
       </c>
       <c r="Q38" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R38" t="n">
-        <v>54.28571428571428</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="S38" t="n">
-        <v>48.14378228525551</v>
+        <v>48.79049758232556</v>
       </c>
       <c r="T38" t="n">
-        <v>6.141932000458773</v>
+        <v>4.150678888262675</v>
       </c>
       <c r="U38" t="n">
-        <v>38.18972506848375</v>
+        <v>36.73671298006892</v>
       </c>
       <c r="V38" t="n">
         <v>68</v>
@@ -4729,10 +4727,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="AG38" t="n">
-        <v>20.3581137714274</v>
+        <v>19.47451786828455</v>
       </c>
       <c r="AH38" t="n">
-        <v>36.78474337142975</v>
+        <v>37.6683392745726</v>
       </c>
       <c r="AI38" t="n">
         <v>40.85741114397492</v>
@@ -4751,10 +4749,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C39" t="n">
-        <v>2.761716984515142</v>
+        <v>2.743129645302055</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4782,16 +4780,16 @@
         <v>18.47027414490581</v>
       </c>
       <c r="K39" t="n">
-        <v>9.321185950525312</v>
+        <v>8.585415421599807</v>
       </c>
       <c r="L39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M39" t="n">
-        <v>56.25</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N39" t="n">
-        <v>15.20010515213887</v>
+        <v>13.62657385415175</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4806,10 +4804,10 @@
         <v>65.11627906976744</v>
       </c>
       <c r="S39" t="n">
-        <v>49.51062611645727</v>
+        <v>49.81801559321186</v>
       </c>
       <c r="T39" t="n">
-        <v>15.60565295331017</v>
+        <v>15.29826347655558</v>
       </c>
       <c r="U39" t="n">
         <v>50.17178199285205</v>
@@ -4821,25 +4819,25 @@
         <v>69.23076923076923</v>
       </c>
       <c r="X39" t="n">
-        <v>10.23704506296521</v>
+        <v>10.2437411865161</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.8308088373710998</v>
+        <v>1.504235748050908</v>
       </c>
       <c r="Z39" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AA39" t="n">
-        <v>44.89795918367347</v>
+        <v>40.38461538461539</v>
       </c>
       <c r="AB39" t="n">
-        <v>11.70848058084654</v>
+        <v>11.74839789809693</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>5.212497048757692</v>
+        <v>4.564423948677709</v>
       </c>
       <c r="AE39" t="n">
         <v>42</v>
@@ -4870,10 +4868,10 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1970852036558122</v>
+        <v>0.1977996134162674</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4901,16 +4899,16 @@
         <v>14.73965458840789</v>
       </c>
       <c r="K40" t="n">
-        <v>7.635989807558174</v>
+        <v>8.026157107124021</v>
       </c>
       <c r="L40" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M40" t="n">
-        <v>68.75</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N40" t="n">
-        <v>12.21407746678665</v>
+        <v>11.37077883851085</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4943,16 +4941,16 @@
         <v>14.17330472629232</v>
       </c>
       <c r="Y40" t="n">
-        <v>5.725782339756257</v>
+        <v>5.384049830128723</v>
       </c>
       <c r="Z40" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AA40" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AB40" t="n">
-        <v>12.58136924216362</v>
+        <v>11.69010824049992</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
@@ -4989,10 +4987,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C41" t="n">
-        <v>1.686897856739064</v>
+        <v>1.691071046728007</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5024,7 +5022,7 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>11.4797199967438</v>
+        <v>11.7555079169205</v>
       </c>
       <c r="L41" t="n">
         <v>9</v>
@@ -5066,7 +5064,7 @@
         <v>40.81782021738603</v>
       </c>
       <c r="Y41" t="n">
-        <v>13.49037860107198</v>
+        <v>13.27636381379426</v>
       </c>
       <c r="Z41" t="n">
         <v>4</v>
@@ -5112,10 +5110,10 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C42" t="n">
-        <v>3.203423422653857</v>
+        <v>3.218185175699889</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5144,10 +5142,10 @@
         <v>10</v>
       </c>
       <c r="J42" t="n">
-        <v>21.13784986389697</v>
+        <v>21.11518617286606</v>
       </c>
       <c r="K42" t="n">
-        <v>4.22403927179158</v>
+        <v>4.704315940280046</v>
       </c>
       <c r="L42" t="n">
         <v>6</v>
@@ -5156,7 +5154,7 @@
         <v>83.33333333333333</v>
       </c>
       <c r="N42" t="n">
-        <v>12.69257812864195</v>
+        <v>12.46777111330014</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
@@ -5221,10 +5219,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C43" t="n">
-        <v>7.18824643970981</v>
+        <v>7.104810882085017</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5238,7 +5236,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -5284,43 +5282,43 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>7.21895613247715</v>
+        <v>8.295886117700313</v>
       </c>
       <c r="Z43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA43" t="n">
-        <v>55.55555555555556</v>
+        <v>37.5</v>
       </c>
       <c r="AB43" t="n">
-        <v>12.88450323174313</v>
+        <v>15.48463828947013</v>
       </c>
       <c r="AC43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF43" t="n">
-        <v>37.5</v>
+        <v>60</v>
       </c>
       <c r="AG43" t="n">
-        <v>54.70182391138273</v>
+        <v>47.68111236589498</v>
       </c>
       <c r="AH43" t="n">
-        <v>-17.20182391138273</v>
+        <v>12.31888763410502</v>
       </c>
       <c r="AI43" t="n">
-        <v>13.68442858235974</v>
+        <v>31.26737697336582</v>
       </c>
       <c r="AJ43" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK43" t="n">
-        <v>42.85714285714285</v>
+        <v>36.36363636363637</v>
       </c>
     </row>
     <row r="44">
@@ -5330,10 +5328,10 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C44" t="n">
-        <v>5.048073578728177</v>
+        <v>5.017509869479351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5350,11 +5348,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.26: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>5</v>
       </c>
@@ -5365,22 +5359,22 @@
         <v>13.03201987649729</v>
       </c>
       <c r="K44" t="n">
-        <v>3.320667202174765</v>
+        <v>2.695109198212875</v>
       </c>
       <c r="L44" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M44" t="n">
-        <v>78.26086956521739</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N44" t="n">
-        <v>19.74854765260397</v>
+        <v>18.54409624254036</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>6.464662858550185</v>
+        <v>7.113182758964598</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5407,13 +5401,13 @@
         <v>12.1234692799834</v>
       </c>
       <c r="Y44" t="n">
-        <v>7.850989747585457</v>
+        <v>8.408908627530042</v>
       </c>
       <c r="Z44" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA44" t="n">
-        <v>11.11111111111111</v>
+        <v>14.28571428571429</v>
       </c>
       <c r="AB44" t="n">
         <v>9.691917834769438</v>
@@ -5422,7 +5416,7 @@
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.332103455618217</v>
+        <v>1.737168264541722</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5445,10 +5439,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02061296753381285</v>
+        <v>0.02080994924352745</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5473,25 +5467,25 @@
         <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>10.64126486431516</v>
+        <v>10.6275101427813</v>
       </c>
       <c r="K45" t="n">
-        <v>2.083337543402886</v>
+        <v>3.052606957600967</v>
       </c>
       <c r="L45" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="M45" t="n">
-        <v>53.73134328358209</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N45" t="n">
-        <v>15.98905578121075</v>
+        <v>15.59634768604025</v>
       </c>
       <c r="O45" t="n">
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>7.755097596834726</v>
+        <v>6.741598536422688</v>
       </c>
       <c r="Q45" t="n">
         <v>37</v>
@@ -5554,10 +5548,10 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C46" t="n">
-        <v>8.660601233505529</v>
+        <v>8.923053903683698</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5574,7 +5568,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.19: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H46" t="n">
         <v>5</v>
       </c>
@@ -5582,25 +5580,25 @@
         <v>10</v>
       </c>
       <c r="J46" t="n">
-        <v>23.79638976838147</v>
+        <v>20.98614247885408</v>
       </c>
       <c r="K46" t="n">
-        <v>4.885065339139549</v>
+        <v>8.063524284180556</v>
       </c>
       <c r="L46" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="M46" t="n">
-        <v>40</v>
+        <v>76.19047619047619</v>
       </c>
       <c r="N46" t="n">
-        <v>11.14792574694933</v>
+        <v>14.40054871052415</v>
       </c>
       <c r="O46" t="n">
         <v>10</v>
       </c>
       <c r="P46" t="n">
-        <v>4.876704461518555</v>
+        <v>1.791979049958603</v>
       </c>
       <c r="Q46" t="n">
         <v>54</v>
@@ -5641,10 +5639,10 @@
         <v>57.89473684210526</v>
       </c>
       <c r="AG46" t="n">
-        <v>17.61095990167152</v>
+        <v>17.68276374282521</v>
       </c>
       <c r="AH46" t="n">
-        <v>40.28377694043374</v>
+        <v>40.21197309928006</v>
       </c>
       <c r="AI46" t="n">
         <v>42.19234534367055</v>
@@ -5663,10 +5661,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7853961174455049</v>
+        <v>0.7911984534548681</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5691,25 +5689,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>25.38434003813299</v>
+        <v>25.31303456031801</v>
       </c>
       <c r="K47" t="n">
-        <v>5.364492317614422</v>
+        <v>6.142902312651333</v>
       </c>
       <c r="L47" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M47" t="n">
-        <v>57.14285714285715</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N47" t="n">
-        <v>14.24479087190473</v>
+        <v>14.52324590656573</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>4.399497003613084</v>
+        <v>3.633872452429587</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5772,10 +5770,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C48" t="n">
-        <v>0.06204923879021584</v>
+        <v>0.06221964643539671</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5800,25 +5798,25 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>34.60463024804744</v>
+        <v>30.07074365952763</v>
       </c>
       <c r="K48" t="n">
-        <v>5.728976364450955</v>
+        <v>6.01934295461275</v>
       </c>
       <c r="L48" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M48" t="n">
-        <v>57.14285714285715</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N48" t="n">
-        <v>18.164645185499</v>
+        <v>10.60849138278571</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>4.039596128148171</v>
+        <v>3.754651683788857</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5859,10 +5857,10 @@
         <v>60.37735849056604</v>
       </c>
       <c r="AG48" t="n">
-        <v>23.36181717488015</v>
+        <v>23.4089869862009</v>
       </c>
       <c r="AH48" t="n">
-        <v>37.01554131568589</v>
+        <v>36.96837150436514</v>
       </c>
       <c r="AI48" t="n">
         <v>46.94147867320552</v>
@@ -5881,10 +5879,10 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2639721848840525</v>
+        <v>0.2625416753938916</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5909,25 +5907,25 @@
         <v>10</v>
       </c>
       <c r="J49" t="n">
-        <v>24.14896896188847</v>
+        <v>23.59168796028241</v>
       </c>
       <c r="K49" t="n">
-        <v>4.463931769854823</v>
+        <v>3.897824223933144</v>
       </c>
       <c r="L49" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M49" t="n">
-        <v>52.94117647058823</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N49" t="n">
-        <v>9.480322112836159</v>
+        <v>9.357882125142343</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>0.5131610701061939</v>
+        <v>1.060826619132382</v>
       </c>
       <c r="Q49" t="n">
         <v>53</v>
@@ -5936,10 +5934,10 @@
         <v>73.58490566037736</v>
       </c>
       <c r="S49" t="n">
-        <v>38.35174591866646</v>
+        <v>38.5102534828344</v>
       </c>
       <c r="T49" t="n">
-        <v>35.2331597417109</v>
+        <v>35.07465217754296</v>
       </c>
       <c r="U49" t="n">
         <v>60.41933558938148</v>
@@ -5968,19 +5966,19 @@
         <v>61.70212765957447</v>
       </c>
       <c r="AG49" t="n">
-        <v>34.86482632230648</v>
+        <v>34.9341277788763</v>
       </c>
       <c r="AH49" t="n">
-        <v>26.83730133726798</v>
+        <v>26.76799988069816</v>
       </c>
       <c r="AI49" t="n">
         <v>47.42656695641357</v>
       </c>
       <c r="AJ49" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AK49" t="n">
-        <v>56.71641791044776</v>
+        <v>56.06060606060606</v>
       </c>
     </row>
     <row r="50">
@@ -5990,10 +5988,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7361773968978591</v>
+        <v>0.7319216352417425</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6021,22 +6019,22 @@
         <v>11.86078125763058</v>
       </c>
       <c r="K50" t="n">
-        <v>3.033171494391995</v>
+        <v>2.437547909096338</v>
       </c>
       <c r="L50" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M50" t="n">
-        <v>58.92857142857143</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N50" t="n">
-        <v>12.55373909038889</v>
+        <v>13.52691631999766</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>0.9383662480588972</v>
+        <v>1.52527283481072</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6099,10 +6097,10 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C51" t="n">
-        <v>0.183834007987614</v>
+        <v>0.1830855120329969</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6132,7 @@
         <v>27.30972539236674</v>
       </c>
       <c r="K51" t="n">
-        <v>6.550414121302883</v>
+        <v>6.116584957669891</v>
       </c>
       <c r="L51" t="n">
         <v>4</v>
@@ -6176,7 +6174,7 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>16.54572340764726</v>
+        <v>16.88551466340381</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6218,10 +6216,10 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C52" t="n">
-        <v>4.156247374791403</v>
+        <v>4.24817255209683</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6253,50 +6251,50 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="R52" t="n">
-        <v>61.11111111111111</v>
+        <v>54.83870967741935</v>
       </c>
       <c r="S52" t="n">
-        <v>36.84351968588739</v>
+        <v>31.11035748904411</v>
       </c>
       <c r="T52" t="n">
-        <v>24.26759142522372</v>
+        <v>23.72835218837524</v>
       </c>
       <c r="U52" t="n">
-        <v>44.86445909660515</v>
+        <v>37.77216763735451</v>
       </c>
       <c r="V52" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="W52" t="n">
-        <v>69.09090909090909</v>
+        <v>62.5</v>
       </c>
       <c r="X52" t="n">
         <v>12.1710603868542</v>
       </c>
       <c r="Y52" t="n">
-        <v>4.635234949955658</v>
+        <v>2.526019076741259</v>
       </c>
       <c r="Z52" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="AA52" t="n">
-        <v>45.16129032258065</v>
+        <v>37.73584905660378</v>
       </c>
       <c r="AB52" t="n">
-        <v>13.71435399424619</v>
+        <v>12.13128424788364</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.528310533013546</v>
+        <v>5.615838064076195</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6305,19 +6303,19 @@
         <v>68.42105263157895</v>
       </c>
       <c r="AG52" t="n">
-        <v>35.82556534658112</v>
+        <v>36.16335835852274</v>
       </c>
       <c r="AH52" t="n">
-        <v>32.59548728499783</v>
+        <v>32.25769427305621</v>
       </c>
       <c r="AI52" t="n">
         <v>52.54424010939046</v>
       </c>
       <c r="AJ52" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AK52" t="n">
-        <v>57.4074074074074</v>
+        <v>56.60377358490566</v>
       </c>
     </row>
     <row r="53">
@@ -6327,10 +6325,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C53" t="n">
-        <v>1.594349969434251</v>
+        <v>1.610143499104591</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6347,7 +6345,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H53" t="n">
         <v>5</v>
       </c>
@@ -6358,22 +6360,22 @@
         <v>28.17598592067425</v>
       </c>
       <c r="K53" t="n">
-        <v>5.112332622297266</v>
+        <v>6.153568722159308</v>
       </c>
       <c r="L53" t="n">
         <v>7</v>
       </c>
       <c r="M53" t="n">
-        <v>71.42857142857143</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N53" t="n">
-        <v>12.79930778909531</v>
+        <v>11.95683582355183</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>2.747220336246436</v>
+        <v>1.739396329362641</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6428,19 +6430,19 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08855162486820237</v>
+        <v>0.08912543344950878</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6459,7 +6461,7 @@
         <v>42.39442432818535</v>
       </c>
       <c r="K54" t="n">
-        <v>9.55292809086834</v>
+        <v>10.26282370644114</v>
       </c>
       <c r="L54" t="n">
         <v>2</v>
@@ -6470,7 +6472,7 @@
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>0.4080875946655071</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6497,7 +6499,7 @@
         <v>114.7400208810756</v>
       </c>
       <c r="Y54" t="n">
-        <v>36.89140510792615</v>
+        <v>36.48246565190647</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -6526,10 +6528,10 @@
         <v>15.82198552514697</v>
       </c>
       <c r="AJ54" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK54" t="n">
-        <v>61.40350877192982</v>
+        <v>60.3448275862069</v>
       </c>
     </row>
     <row r="55">
@@ -6539,10 +6541,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8674273452813068</v>
+        <v>0.882005497265862</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6567,25 +6569,25 @@
         <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>12.32149231737306</v>
+        <v>12.31616646597832</v>
       </c>
       <c r="K55" t="n">
-        <v>3.410232130166801</v>
+        <v>5.141777899817224</v>
       </c>
       <c r="L55" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="M55" t="n">
-        <v>66.66666666666667</v>
+        <v>66.0377358490566</v>
       </c>
       <c r="N55" t="n">
-        <v>12.0241634893214</v>
+        <v>13.00589306398004</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>2.504363268978405</v>
+        <v>0.8162522237359582</v>
       </c>
       <c r="Q55" t="n">
         <v>44</v>
@@ -6612,16 +6614,16 @@
         <v>25.41488056506582</v>
       </c>
       <c r="Y55" t="n">
-        <v>9.331451677129355</v>
+        <v>7.807658491613467</v>
       </c>
       <c r="Z55" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA55" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AB55" t="n">
-        <v>10.78082928863532</v>
+        <v>10.06535135336795</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6636,10 +6638,10 @@
         <v>54.16666666666666</v>
       </c>
       <c r="AG55" t="n">
-        <v>41.10326832506873</v>
+        <v>40.77810011195715</v>
       </c>
       <c r="AH55" t="n">
-        <v>13.06339834159793</v>
+        <v>13.38856655470951</v>
       </c>
       <c r="AI55" t="n">
         <v>40.2910745456498</v>
@@ -6658,14 +6660,14 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8552277956411526</v>
+        <v>0.8622465847672793</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6675,7 +6677,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -6686,10 +6688,10 @@
         <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>34.39082100018626</v>
+        <v>34.38683570496719</v>
       </c>
       <c r="K56" t="n">
-        <v>9.066526772026883</v>
+        <v>9.954948429596788</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6715,17 +6717,27 @@
       <c r="W56" t="n">
         <v>100</v>
       </c>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
+      <c r="X56" t="n">
+        <v>15.71888627084337</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>4.980982817062307</v>
+      </c>
       <c r="Z56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" t="inlineStr"/>
-      <c r="AB56" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>23.52941176470588</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>18.01250639514078</v>
+      </c>
       <c r="AC56" t="n">
         <v>10</v>
       </c>
-      <c r="AD56" t="inlineStr"/>
+      <c r="AD56" t="n">
+        <v>5.2821186029263</v>
+      </c>
       <c r="AE56" t="n">
         <v>0</v>
       </c>
@@ -6747,10 +6759,10 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C57" t="n">
-        <v>1.385065155982075</v>
+        <v>1.428319164994094</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6767,7 +6779,11 @@
           <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %83.33: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>5</v>
       </c>
@@ -6778,13 +6794,17 @@
         <v>32.76213282665623</v>
       </c>
       <c r="K57" t="n">
-        <v>18.59928460743274</v>
+        <v>22.30300533354659</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M57" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="N57" t="n">
+        <v>15.65787039974029</v>
+      </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
@@ -6807,22 +6827,26 @@
         <v>69.44100627964798</v>
       </c>
       <c r="V57" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="W57" t="n">
-        <v>80.53097345132744</v>
+        <v>80.70175438596492</v>
       </c>
       <c r="X57" t="n">
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>14.60996767541642</v>
+        <v>11.94333411543395</v>
       </c>
       <c r="Z57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA57" t="inlineStr"/>
-      <c r="AB57" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>83.33333333333333</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>12.36237164600526</v>
+      </c>
       <c r="AC57" t="n">
         <v>6</v>
       </c>
@@ -6858,10 +6882,10 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7559489895984578</v>
+        <v>0.756305006713627</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6893,7 +6917,7 @@
         <v>16.33691982084211</v>
       </c>
       <c r="K58" t="n">
-        <v>1.909688772139106</v>
+        <v>1.957683536208732</v>
       </c>
       <c r="L58" t="n">
         <v>37</v>
@@ -6908,7 +6932,7 @@
         <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>3.032401791325801</v>
+        <v>2.98390112277398</v>
       </c>
       <c r="Q58" t="n">
         <v>24</v>
@@ -6935,7 +6959,7 @@
         <v>41.32985472592288</v>
       </c>
       <c r="Y58" t="n">
-        <v>14.73921537223499</v>
+        <v>14.69906147428963</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -6977,10 +7001,10 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8270427147945381</v>
+        <v>0.8269327253459947</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7040,7 +7064,7 @@
         <v>10.2478061424703</v>
       </c>
       <c r="Y59" t="n">
-        <v>6.092668269098866</v>
+        <v>6.105157122995397</v>
       </c>
       <c r="Z59" t="n">
         <v>26</v>
@@ -7086,10 +7110,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C60" t="n">
-        <v>13.26170996411715</v>
+        <v>13.20065453831181</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7117,22 +7141,22 @@
         <v>17.06238107085701</v>
       </c>
       <c r="K60" t="n">
-        <v>4.368210881328327</v>
+        <v>3.887711339931132</v>
       </c>
       <c r="L60" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M60" t="n">
-        <v>48.38709677419355</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N60" t="n">
-        <v>12.20601152229256</v>
+        <v>11.5632679575326</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>3.479784781211981</v>
+        <v>3.958397588154616</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7195,10 +7219,10 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6377399555922313</v>
+        <v>0.6322861265228771</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7223,25 +7247,25 @@
         <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>36.10328933244122</v>
+        <v>33.98678515927238</v>
       </c>
       <c r="K61" t="n">
-        <v>2.969206790673184</v>
+        <v>2.088633998708445</v>
       </c>
       <c r="L61" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M61" t="n">
-        <v>57.14285714285715</v>
+        <v>50</v>
       </c>
       <c r="N61" t="n">
-        <v>43.93076393964234</v>
+        <v>22.27180963266649</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>6.828054161492925</v>
+        <v>7.749507160015146</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7296,10 +7320,10 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C62" t="n">
-        <v>8.613275543704953</v>
+        <v>8.607751645603003</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7324,25 +7348,25 @@
         <v>10</v>
       </c>
       <c r="J62" t="n">
-        <v>14.45999953470718</v>
+        <v>13.30115949155629</v>
       </c>
       <c r="K62" t="n">
-        <v>3.514524176921996</v>
+        <v>3.448137854932898</v>
       </c>
       <c r="L62" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="M62" t="n">
-        <v>61.53846153846154</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="N62" t="n">
-        <v>15.01384110579671</v>
+        <v>14.41202482502841</v>
       </c>
       <c r="O62" t="n">
         <v>6</v>
       </c>
       <c r="P62" t="n">
-        <v>2.401088970693577</v>
+        <v>2.466803364450731</v>
       </c>
       <c r="Q62" t="n">
         <v>29</v>
@@ -7405,19 +7429,19 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C63" t="n">
-        <v>0.106219885548797</v>
+        <v>0.1046803501031941</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7433,21 +7457,25 @@
         <v>10</v>
       </c>
       <c r="J63" t="n">
-        <v>33.28434552774222</v>
+        <v>31.19925725463639</v>
       </c>
       <c r="K63" t="n">
-        <v>6.447120573287002</v>
+        <v>4.904291616559742</v>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
-      </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M63" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="N63" t="n">
+        <v>8.912002084757088</v>
+      </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>0.09123400193205011</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7471,25 +7499,25 @@
         <v>66.66666666666667</v>
       </c>
       <c r="X63" t="n">
-        <v>10.24127163987956</v>
+        <v>10.24796802016521</v>
       </c>
       <c r="Y63" t="n">
-        <v>3.441679336743098</v>
+        <v>4.846961354088696</v>
       </c>
       <c r="Z63" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA63" t="n">
-        <v>57.14285714285715</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="AB63" t="n">
-        <v>11.68557514107501</v>
+        <v>12.20765442875811</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>6.792082358317697</v>
+        <v>5.415527154195332</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7520,10 +7548,10 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1606970061884738</v>
+        <v>0.1620653614942838</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7548,25 +7576,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>24.00559848640348</v>
+        <v>23.67654789977809</v>
       </c>
       <c r="K64" t="n">
-        <v>2.139035422088131</v>
+        <v>3.00250553392889</v>
       </c>
       <c r="L64" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M64" t="n">
-        <v>57.57575757575758</v>
+        <v>60</v>
       </c>
       <c r="N64" t="n">
-        <v>16.23377088890027</v>
+        <v>18.4981910044989</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>2.801049144520484</v>
+        <v>1.939267841803272</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7575,10 +7603,10 @@
         <v>70.37037037037037</v>
       </c>
       <c r="S64" t="n">
-        <v>73.98949442717146</v>
+        <v>74.20087527580721</v>
       </c>
       <c r="T64" t="n">
-        <v>-3.619124056801098</v>
+        <v>-3.83050490543684</v>
       </c>
       <c r="U64" t="n">
         <v>57.17242709884697</v>
@@ -7601,19 +7629,19 @@
       </c>
       <c r="AD64" t="inlineStr"/>
       <c r="AE64" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AF64" t="n">
-        <v>59.25925925925926</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="AG64" t="n">
-        <v>38.6780251892314</v>
+        <v>38.05195226551255</v>
       </c>
       <c r="AH64" t="n">
-        <v>20.58123407002786</v>
+        <v>23.48650927294899</v>
       </c>
       <c r="AI64" t="n">
-        <v>45.96684934349057</v>
+        <v>47.95987371581939</v>
       </c>
       <c r="AJ64" t="n">
         <v>100</v>
@@ -7629,10 +7657,10 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C65" t="n">
-        <v>6.27854151354317</v>
+        <v>6.264004860536494</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7651,7 +7679,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -7664,22 +7692,22 @@
         <v>28.12381406175567</v>
       </c>
       <c r="K65" t="n">
-        <v>3.447077130649912</v>
+        <v>3.207567005319145</v>
       </c>
       <c r="L65" t="n">
         <v>16</v>
       </c>
       <c r="M65" t="n">
-        <v>81.25</v>
+        <v>75</v>
       </c>
       <c r="N65" t="n">
-        <v>14.24622363239263</v>
+        <v>15.09819428359337</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>6.334565510317902</v>
+        <v>6.581332349720825</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7688,10 +7716,10 @@
         <v>68</v>
       </c>
       <c r="S65" t="n">
-        <v>45.53332171298345</v>
+        <v>45.64229607195782</v>
       </c>
       <c r="T65" t="n">
-        <v>22.46667828701655</v>
+        <v>22.35770392804218</v>
       </c>
       <c r="U65" t="n">
         <v>54.18970269185592</v>
@@ -7729,10 +7757,10 @@
         <v>40.06618319896197</v>
       </c>
       <c r="AJ65" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AK65" t="n">
-        <v>57.35294117647059</v>
+        <v>56.71641791044776</v>
       </c>
     </row>
     <row r="66">
@@ -7742,10 +7770,10 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4324516254298847</v>
+        <v>0.4321742839352609</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7841,14 +7869,14 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02944709545524157</v>
+        <v>0.02900780774342403</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7858,7 +7886,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -7869,13 +7897,13 @@
         <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>18.76478821017455</v>
+        <v>18.49825117353735</v>
       </c>
       <c r="K67" t="n">
-        <v>9.375001000976591</v>
+        <v>7.736815557078613</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
@@ -7896,17 +7924,27 @@
         <v>0</v>
       </c>
       <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="inlineStr"/>
+      <c r="X67" t="n">
+        <v>10.85961868230363</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>2.816898670898549</v>
+      </c>
       <c r="Z67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA67" t="inlineStr"/>
-      <c r="AB67" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>6.940091115500769</v>
+      </c>
       <c r="AC67" t="n">
         <v>3</v>
       </c>
-      <c r="AD67" t="inlineStr"/>
+      <c r="AD67" t="n">
+        <v>0.188408608695656</v>
+      </c>
       <c r="AE67" t="n">
         <v>0</v>
       </c>
@@ -7926,10 +7964,10 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C68" t="n">
-        <v>3.621992728584865</v>
+        <v>3.752096871160283</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7986,10 +8024,10 @@
         <v>80</v>
       </c>
       <c r="X68" t="n">
-        <v>108.2921914471068</v>
+        <v>109.448612884876</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.985917211267608</v>
+        <v>0.05599445497443956</v>
       </c>
       <c r="Z68" t="n">
         <v>1</v>
@@ -8000,7 +8038,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>5.168407147291754</v>
+        <v>7.948456239775902</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8031,10 +8069,10 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4112076442816664</v>
+        <v>0.4094725228248614</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8062,16 +8100,16 @@
         <v>29.4573350207784</v>
       </c>
       <c r="K69" t="n">
-        <v>5.185455659902982</v>
+        <v>4.741617750765537</v>
       </c>
       <c r="L69" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M69" t="n">
-        <v>60</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N69" t="n">
-        <v>14.20304940810647</v>
+        <v>12.83128146711089</v>
       </c>
       <c r="O69" t="n">
         <v>3</v>
@@ -8124,10 +8162,10 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4141523810026533</v>
+        <v>0.4183009877327328</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8155,22 +8193,22 @@
         <v>20.66985845799666</v>
       </c>
       <c r="K70" t="n">
-        <v>6.240473755072617</v>
+        <v>7.304695439275122</v>
       </c>
       <c r="L70" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M70" t="n">
-        <v>50</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N70" t="n">
-        <v>8.731453063316346</v>
+        <v>8.806559784819418</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>1.656173191568988</v>
+        <v>0.6479721673674277</v>
       </c>
       <c r="Q70" t="n">
         <v>30</v>
@@ -8179,19 +8217,19 @@
         <v>56.66666666666666</v>
       </c>
       <c r="S70" t="n">
-        <v>33.59415246670149</v>
+        <v>33.67748580003482</v>
       </c>
       <c r="T70" t="n">
-        <v>23.07251419996518</v>
+        <v>22.98918086663185</v>
       </c>
       <c r="U70" t="n">
         <v>39.19730700081361</v>
       </c>
       <c r="V70" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="W70" t="n">
-        <v>66.12903225806451</v>
+        <v>65.57377049180327</v>
       </c>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
@@ -8211,10 +8249,10 @@
         <v>48.83720930232558</v>
       </c>
       <c r="AG70" t="n">
-        <v>34.79867517086895</v>
+        <v>34.68090534379679</v>
       </c>
       <c r="AH70" t="n">
-        <v>14.03853413145664</v>
+        <v>14.15630395852879</v>
       </c>
       <c r="AI70" t="n">
         <v>34.61744754671859</v>
@@ -8233,19 +8271,19 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C71" t="n">
-        <v>3.350658902033429</v>
+        <v>3.293857525304879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8264,22 +8302,22 @@
         <v>20.51701021225919</v>
       </c>
       <c r="K71" t="n">
-        <v>6.954410025909552</v>
+        <v>5.141286722617</v>
       </c>
       <c r="L71" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M71" t="n">
-        <v>61.53846153846154</v>
+        <v>67.85714285714286</v>
       </c>
       <c r="N71" t="n">
-        <v>12.05814941002346</v>
+        <v>12.35555698952126</v>
       </c>
       <c r="O71" t="n">
         <v>6</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>0.8167231961393684</v>
       </c>
       <c r="Q71" t="n">
         <v>43</v>
@@ -8320,10 +8358,10 @@
         <v>54.83870967741935</v>
       </c>
       <c r="AG71" t="n">
-        <v>14.81145187022401</v>
+        <v>14.91604026428609</v>
       </c>
       <c r="AH71" t="n">
-        <v>40.02725780719535</v>
+        <v>39.92266941313326</v>
       </c>
       <c r="AI71" t="n">
         <v>37.77216763735451</v>
@@ -8342,10 +8380,10 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07971749442273686</v>
+        <v>0.07966636970091651</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8377,7 +8415,7 @@
         <v>20.36571476939619</v>
       </c>
       <c r="K72" t="n">
-        <v>11.44997666789682</v>
+        <v>11.37850115182233</v>
       </c>
       <c r="L72" t="n">
         <v>9</v>
@@ -8419,7 +8457,7 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>11.24760769084564</v>
+        <v>11.30452670718646</v>
       </c>
       <c r="Z72" t="n">
         <v>2</v>
@@ -8461,10 +8499,10 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07067302799883049</v>
+        <v>0.07062770370806086</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8489,10 +8527,10 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>21.17528272510304</v>
+        <v>21.17049467907518</v>
       </c>
       <c r="K73" t="n">
-        <v>1.510572837049651</v>
+        <v>1.439309973482961</v>
       </c>
       <c r="L73" t="n">
         <v>26</v>
@@ -8507,7 +8545,7 @@
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>8.363096498901701</v>
+        <v>8.439223441834208</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8570,10 +8608,10 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C74" t="n">
-        <v>4.825116867362479</v>
+        <v>4.916613082782068</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8598,25 +8636,25 @@
         <v>10</v>
       </c>
       <c r="J74" t="n">
-        <v>18.36466662125948</v>
+        <v>18.35970785011217</v>
       </c>
       <c r="K74" t="n">
-        <v>2.091676463638681</v>
+        <v>4.021269982818088</v>
       </c>
       <c r="L74" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="M74" t="n">
-        <v>67.5</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N74" t="n">
-        <v>20.79005760883963</v>
+        <v>17.52247925077782</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>5.787272519190778</v>
+        <v>3.824919670601123</v>
       </c>
       <c r="Q74" t="n">
         <v>35</v>
@@ -8643,7 +8681,7 @@
         <v>95.98093909010421</v>
       </c>
       <c r="Y74" t="n">
-        <v>16.6571195669634</v>
+        <v>15.07673128800374</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -8685,10 +8723,10 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1493388412673446</v>
+        <v>0.1469308474309697</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8716,10 +8754,10 @@
         <v>19.1703426786477</v>
       </c>
       <c r="K75" t="n">
-        <v>14.60103334931557</v>
+        <v>12.75316457247591</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
@@ -8751,25 +8789,25 @@
         <v>100</v>
       </c>
       <c r="X75" t="n">
-        <v>17.02218358940229</v>
+        <v>17.02929186229787</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.068966896551716</v>
+        <v>3.653894868349239</v>
       </c>
       <c r="Z75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA75" t="n">
-        <v>20</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="AB75" t="n">
-        <v>11.24142221425521</v>
+        <v>11.36055095633982</v>
       </c>
       <c r="AC75" t="n">
         <v>10</v>
       </c>
       <c r="AD75" t="n">
-        <v>8.098590254909732</v>
+        <v>6.586779115750674</v>
       </c>
       <c r="AE75" t="n">
         <v>4</v>
@@ -8787,10 +8825,10 @@
         <v>30.06418425824019</v>
       </c>
       <c r="AJ75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK75" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76">
@@ -8800,10 +8838,10 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C76" t="n">
-        <v>1.864632210324189</v>
+        <v>1.859232251037712</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8828,25 +8866,25 @@
         <v>10</v>
       </c>
       <c r="J76" t="n">
-        <v>20.88959101184773</v>
+        <v>20.51082830683794</v>
       </c>
       <c r="K76" t="n">
-        <v>7.585165881045453</v>
+        <v>7.273600140429193</v>
       </c>
       <c r="L76" t="n">
         <v>15</v>
       </c>
       <c r="M76" t="n">
-        <v>66.66666666666667</v>
+        <v>60</v>
       </c>
       <c r="N76" t="n">
-        <v>10.34072670763836</v>
+        <v>10.50856197334631</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>2.244579072940778</v>
+        <v>2.541538510874775</v>
       </c>
       <c r="Q76" t="n">
         <v>42</v>
@@ -8855,10 +8893,10 @@
         <v>64.28571428571429</v>
       </c>
       <c r="S76" t="n">
-        <v>29.74204478885298</v>
+        <v>29.97166714253549</v>
       </c>
       <c r="T76" t="n">
-        <v>34.54366949686131</v>
+        <v>34.3140471431788</v>
       </c>
       <c r="U76" t="n">
         <v>49.16636571945582</v>
@@ -8909,10 +8947,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5170068673387196</v>
+        <v>0.5402178848202404</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8926,7 +8964,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -8940,16 +8978,16 @@
         <v>21.60005234598619</v>
       </c>
       <c r="K77" t="n">
-        <v>6.480685049296242</v>
+        <v>11.26113420434449</v>
       </c>
       <c r="L77" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M77" t="n">
-        <v>52.17391304347826</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N77" t="n">
-        <v>10.83008970198139</v>
+        <v>19.39952210947289</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -8978,17 +9016,27 @@
       <c r="W77" t="n">
         <v>61.8421052631579</v>
       </c>
-      <c r="X77" t="inlineStr"/>
-      <c r="Y77" t="inlineStr"/>
+      <c r="X77" t="n">
+        <v>12.99282331276559</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>1.532565571556499</v>
+      </c>
       <c r="Z77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA77" t="inlineStr"/>
-      <c r="AB77" t="inlineStr"/>
+        <v>75</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>10.9975774868655</v>
+      </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
-      <c r="AD77" t="inlineStr"/>
+      <c r="AD77" t="n">
+        <v>8.599223162046332</v>
+      </c>
       <c r="AE77" t="n">
         <v>46</v>
       </c>
@@ -8996,10 +9044,10 @@
         <v>50</v>
       </c>
       <c r="AG77" t="n">
-        <v>25.56139577050298</v>
+        <v>25.57118817159973</v>
       </c>
       <c r="AH77" t="n">
-        <v>24.43860422949702</v>
+        <v>24.42881182840027</v>
       </c>
       <c r="AI77" t="n">
         <v>36.11893708270325</v>
@@ -9018,10 +9066,10 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05300477215597307</v>
+        <v>0.05360138282271081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9038,11 +9086,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>5</v>
       </c>
@@ -9050,19 +9094,19 @@
         <v>10</v>
       </c>
       <c r="J78" t="n">
-        <v>20.32485186011925</v>
+        <v>12.76206508896208</v>
       </c>
       <c r="K78" t="n">
-        <v>12.40872737765157</v>
+        <v>5.795475490745328</v>
       </c>
       <c r="L78" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="M78" t="n">
-        <v>75</v>
+        <v>64.91228070175438</v>
       </c>
       <c r="N78" t="n">
-        <v>15.49144004111212</v>
+        <v>16.50187791097123</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
@@ -9095,22 +9139,22 @@
         <v>23.16536029857119</v>
       </c>
       <c r="Y78" t="n">
-        <v>8.733488778698762</v>
+        <v>7.706211952560526</v>
       </c>
       <c r="Z78" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA78" t="n">
-        <v>43.75</v>
+        <v>50</v>
       </c>
       <c r="AB78" t="n">
-        <v>16.0191368974861</v>
+        <v>15.30682573548685</v>
       </c>
       <c r="AC78" t="n">
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.387706404411826</v>
+        <v>2.485311412573565</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9141,10 +9185,10 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C79" t="n">
-        <v>0.891826364423447</v>
+        <v>0.8920951600653764</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9169,25 +9213,25 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>12.92020537241256</v>
+        <v>12.46716859924595</v>
       </c>
       <c r="K79" t="n">
-        <v>3.274013610544135</v>
+        <v>3.305140302791032</v>
       </c>
       <c r="L79" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M79" t="n">
-        <v>49.12280701754386</v>
+        <v>51.78571428571428</v>
       </c>
       <c r="N79" t="n">
-        <v>10.39232662290731</v>
+        <v>10.07001107978507</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>1.671268820794292</v>
+        <v>1.640634427523424</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9228,10 +9272,10 @@
         <v>55.26315789473684</v>
       </c>
       <c r="AG79" t="n">
-        <v>26.54908548382558</v>
+        <v>26.62440966384084</v>
       </c>
       <c r="AH79" t="n">
-        <v>28.71407241091126</v>
+        <v>28.638748230896</v>
       </c>
       <c r="AI79" t="n">
         <v>39.70629712199248</v>
@@ -9250,10 +9294,10 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1356669734319282</v>
+        <v>0.1341085627492059</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9278,10 +9322,10 @@
         <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>69.28741377539056</v>
+        <v>69.28554820223583</v>
       </c>
       <c r="K80" t="n">
-        <v>4.032258188085325</v>
+        <v>2.830990191225946</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9292,7 +9336,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>5.736433982933731</v>
+        <v>6.971643271588146</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9333,10 +9377,10 @@
         <v>50</v>
       </c>
       <c r="AG80" t="n">
-        <v>39.74534888579511</v>
+        <v>39.88957965502588</v>
       </c>
       <c r="AH80" t="n">
-        <v>10.25465111420489</v>
+        <v>10.11042034497412</v>
       </c>
       <c r="AI80" t="n">
         <v>32.06059352575905</v>
@@ -9355,14 +9399,14 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C81" t="n">
-        <v>1.088490865413263</v>
+        <v>1.076231723557424</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9383,25 +9427,25 @@
         <v>10</v>
       </c>
       <c r="J81" t="n">
-        <v>11.85462855272487</v>
+        <v>11.84927434264682</v>
       </c>
       <c r="K81" t="n">
-        <v>3.70741164985291</v>
+        <v>2.533177473538051</v>
       </c>
       <c r="L81" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M81" t="n">
-        <v>43.18181818181818</v>
+        <v>48.97959183673469</v>
       </c>
       <c r="N81" t="n">
-        <v>14.02911596425254</v>
+        <v>13.20735979882997</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>6.067636102415475</v>
+        <v>7.282347734116601</v>
       </c>
       <c r="Q81" t="n">
         <v>31</v>
@@ -9428,22 +9472,22 @@
         <v>27.31228182970742</v>
       </c>
       <c r="Y81" t="n">
-        <v>8.586716782882464</v>
+        <v>9.616260017534417</v>
       </c>
       <c r="Z81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA81" t="n">
-        <v>25</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB81" t="n">
-        <v>15.30045963659641</v>
+        <v>9.276812191444455</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.546037039016324</v>
+        <v>0.4245674969192703</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9474,10 +9518,10 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C82" t="n">
-        <v>5.201619214233761</v>
+        <v>5.185671073789055</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9494,7 +9538,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H82" t="n">
         <v>5</v>
       </c>
@@ -9502,16 +9550,20 @@
         <v>10</v>
       </c>
       <c r="J82" t="n">
-        <v>15.23084223335499</v>
+        <v>12.20498494157071</v>
       </c>
       <c r="K82" t="n">
-        <v>14.41771964772396</v>
+        <v>12.93798782592066</v>
       </c>
       <c r="L82" t="n">
-        <v>2</v>
-      </c>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="M82" t="n">
+        <v>83.33333333333333</v>
+      </c>
+      <c r="N82" t="n">
+        <v>8.520914392672934</v>
+      </c>
       <c r="O82" t="n">
         <v>4</v>
       </c>
@@ -9543,22 +9595,22 @@
         <v>15.04024401260009</v>
       </c>
       <c r="Y82" t="n">
-        <v>0.5411361651909585</v>
+        <v>0.8460765815459181</v>
       </c>
       <c r="Z82" t="n">
         <v>12</v>
       </c>
       <c r="AA82" t="n">
-        <v>58.33333333333334</v>
+        <v>50</v>
       </c>
       <c r="AB82" t="n">
-        <v>11.30341333058647</v>
+        <v>11.23470967332035</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>3.477682834336282</v>
+        <v>3.180835724617526</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9589,19 +9641,19 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C83" t="n">
-        <v>5.99458737473971</v>
+        <v>5.927682451917086</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9620,22 +9672,22 @@
         <v>14.0949513048101</v>
       </c>
       <c r="K83" t="n">
-        <v>10.758771676542</v>
+        <v>9.522605347200685</v>
       </c>
       <c r="L83" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M83" t="n">
-        <v>65.38461538461539</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="N83" t="n">
-        <v>11.17763364443807</v>
+        <v>10.32070616999182</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>0.4358868667211802</v>
       </c>
       <c r="Q83" t="n">
         <v>44</v>
@@ -9644,10 +9696,10 @@
         <v>63.63636363636363</v>
       </c>
       <c r="S83" t="n">
-        <v>54.36087535210635</v>
+        <v>55.07418752743249</v>
       </c>
       <c r="T83" t="n">
-        <v>9.275488284257278</v>
+        <v>8.562176108931148</v>
       </c>
       <c r="U83" t="n">
         <v>48.86637687904344</v>
@@ -9659,25 +9711,25 @@
         <v>62.12121212121212</v>
       </c>
       <c r="X83" t="n">
-        <v>11.1473989455825</v>
+        <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>0.3496503496503545</v>
+        <v>1.467821951885984</v>
       </c>
       <c r="Z83" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AA83" t="n">
-        <v>56.14035087719298</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="AB83" t="n">
-        <v>11.88823380124909</v>
+        <v>11.66028660720694</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>5.670175438596492</v>
+        <v>4.599693356926426</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9708,10 +9760,10 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C84" t="n">
-        <v>2.2442893143903</v>
+        <v>2.244952141646015</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9739,16 +9791,16 @@
         <v>14.10735630446007</v>
       </c>
       <c r="K84" t="n">
-        <v>7.439855922092575</v>
+        <v>7.471587154068171</v>
       </c>
       <c r="L84" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M84" t="n">
-        <v>54.05405405405406</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N84" t="n">
-        <v>8.93109574327298</v>
+        <v>8.92656302190143</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
@@ -9817,10 +9869,10 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C85" t="n">
-        <v>6.814899331283039</v>
+        <v>6.61083734442526</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9848,22 +9900,22 @@
         <v>15.13449360257271</v>
       </c>
       <c r="K85" t="n">
-        <v>5.756271962906223</v>
+        <v>2.589558277150394</v>
       </c>
       <c r="L85" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="M85" t="n">
-        <v>66.66666666666667</v>
+        <v>54</v>
       </c>
       <c r="N85" t="n">
-        <v>13.02129877713198</v>
+        <v>13.0699515953862</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>2.121602809411405</v>
+        <v>5.273871740662983</v>
       </c>
       <c r="Q85" t="n">
         <v>34</v>
@@ -9872,10 +9924,10 @@
         <v>61.76470588235294</v>
       </c>
       <c r="S85" t="n">
-        <v>65.42887171084101</v>
+        <v>65.85496522516983</v>
       </c>
       <c r="T85" t="n">
-        <v>-3.664165828488066</v>
+        <v>-4.090259342816893</v>
       </c>
       <c r="U85" t="n">
         <v>45.0410173444307</v>
@@ -9904,10 +9956,10 @@
         <v>41.93548387096774</v>
       </c>
       <c r="AG85" t="n">
-        <v>22.56170152360549</v>
+        <v>22.62682387800984</v>
       </c>
       <c r="AH85" t="n">
-        <v>19.37378234736226</v>
+        <v>19.30865999295791</v>
       </c>
       <c r="AI85" t="n">
         <v>26.41554306731223</v>
@@ -9926,10 +9978,10 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C86" t="n">
-        <v>3.504204537539013</v>
+        <v>3.567119482308149</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9989,22 +10041,22 @@
         <v>39.94948119773951</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.960439425261629</v>
+        <v>0.2002243828252426</v>
       </c>
       <c r="Z86" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA86" t="n">
-        <v>37.5</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB86" t="n">
-        <v>14.11117846209332</v>
+        <v>12.3031665129609</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>4.12033729145379</v>
+        <v>5.811411479943917</v>
       </c>
       <c r="AE86" t="n">
         <v>51</v>
@@ -10035,19 +10087,19 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C87" t="n">
-        <v>5.752700515758985</v>
+        <v>5.691205758356563</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -10070,7 +10122,7 @@
         <v>29.54558799520699</v>
       </c>
       <c r="K87" t="n">
-        <v>5.915243496801104</v>
+        <v>4.783039206622641</v>
       </c>
       <c r="L87" t="n">
         <v>6</v>
@@ -10079,13 +10131,13 @@
         <v>83.33333333333333</v>
       </c>
       <c r="N87" t="n">
-        <v>8.337490203764601</v>
+        <v>9.637889717228306</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>0.2070571678585598</v>
       </c>
       <c r="Q87" t="n">
         <v>47</v>
@@ -10120,19 +10172,19 @@
       </c>
       <c r="AD87" t="inlineStr"/>
       <c r="AE87" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF87" t="n">
-        <v>53.19148936170212</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="AG87" t="n">
-        <v>46.42511283856881</v>
+        <v>47.63908977455571</v>
       </c>
       <c r="AH87" t="n">
-        <v>6.76637652313331</v>
+        <v>4.534823268922551</v>
       </c>
       <c r="AI87" t="n">
-        <v>39.23238322019481</v>
+        <v>38.13741307280403</v>
       </c>
       <c r="AJ87" t="n">
         <v>64</v>
@@ -10148,24 +10200,24 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9780642558785843</v>
+        <v>0.9913102962526857</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -10179,22 +10231,22 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>9.574103202656993</v>
+        <v>11.05807829555574</v>
       </c>
       <c r="L88" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M88" t="n">
-        <v>52.17391304347826</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N88" t="n">
-        <v>11.63023150978318</v>
+        <v>9.038376875760038</v>
       </c>
       <c r="O88" t="n">
         <v>10</v>
       </c>
       <c r="P88" t="n">
-        <v>0.3886838083952293</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
         <v>44</v>
@@ -10217,17 +10269,27 @@
       <c r="W88" t="n">
         <v>68.35443037974683</v>
       </c>
-      <c r="X88" t="inlineStr"/>
-      <c r="Y88" t="inlineStr"/>
+      <c r="X88" t="n">
+        <v>11.34066630670314</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>0.2538048500347334</v>
+      </c>
       <c r="Z88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA88" t="inlineStr"/>
-      <c r="AB88" t="inlineStr"/>
+        <v>69</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>10.96607414722795</v>
+      </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
-      <c r="AD88" t="inlineStr"/>
+      <c r="AD88" t="n">
+        <v>5.760816381342715</v>
+      </c>
       <c r="AE88" t="n">
         <v>30</v>
       </c>
@@ -10257,10 +10319,10 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C89" t="n">
-        <v>1.984523893456046</v>
+        <v>2.01688338007806</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10288,16 +10350,16 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>7.796073802799341</v>
+        <v>9.55378789212309</v>
       </c>
       <c r="L89" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="M89" t="n">
-        <v>68.57142857142857</v>
+        <v>65.51724137931035</v>
       </c>
       <c r="N89" t="n">
-        <v>16.05252990993683</v>
+        <v>15.0491963329399</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
@@ -10306,40 +10368,40 @@
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R89" t="n">
-        <v>69.76744186046511</v>
+        <v>70.45454545454545</v>
       </c>
       <c r="S89" t="n">
-        <v>35.41395324717753</v>
+        <v>35.20197604887212</v>
       </c>
       <c r="T89" t="n">
-        <v>34.35348861328758</v>
+        <v>35.25256940567333</v>
       </c>
       <c r="U89" t="n">
-        <v>54.89463582227039</v>
+        <v>55.77979987383978</v>
       </c>
       <c r="V89" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W89" t="n">
-        <v>75.82417582417582</v>
+        <v>76.08695652173913</v>
       </c>
       <c r="X89" t="n">
         <v>28.7873334490923</v>
       </c>
       <c r="Y89" t="n">
-        <v>13.45500599550143</v>
+        <v>12.04381030018848</v>
       </c>
       <c r="Z89" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AA89" t="n">
-        <v>33.33333333333334</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB89" t="n">
-        <v>24.68761358108778</v>
+        <v>11.78207688325951</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
@@ -10376,10 +10438,10 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C90" t="n">
-        <v>2.675478932573332</v>
+        <v>2.701089344224629</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10407,22 +10469,22 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>5.468045594177662</v>
+        <v>6.477614397295373</v>
       </c>
       <c r="L90" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M90" t="n">
-        <v>67.5</v>
+        <v>65.78947368421052</v>
       </c>
       <c r="N90" t="n">
-        <v>15.6798363091836</v>
+        <v>15.61991353247904</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>2.400683914789559</v>
+        <v>1.429770577902145</v>
       </c>
       <c r="Q90" t="n">
         <v>42</v>
@@ -10449,13 +10511,13 @@
         <v>33.24184775233741</v>
       </c>
       <c r="Y90" t="n">
-        <v>12.02563955815183</v>
+        <v>11.18352506483817</v>
       </c>
       <c r="Z90" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA90" t="n">
-        <v>28.57142857142857</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AB90" t="n">
         <v>8.158989511032161</v>
@@ -10495,10 +10557,10 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2372594525211416</v>
+        <v>0.2358460947198013</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10523,19 +10585,19 @@
         <v>10</v>
       </c>
       <c r="J91" t="n">
-        <v>14.9000517126033</v>
+        <v>14.82331888146111</v>
       </c>
       <c r="K91" t="n">
-        <v>4.643970977278489</v>
+        <v>4.020605411976996</v>
       </c>
       <c r="L91" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M91" t="n">
-        <v>59.09090909090909</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="N91" t="n">
-        <v>16.21885791524035</v>
+        <v>14.72533338612546</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
@@ -10550,10 +10612,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="S91" t="n">
-        <v>32.19411737547947</v>
+        <v>32.55801056789885</v>
       </c>
       <c r="T91" t="n">
-        <v>29.50801028409499</v>
+        <v>29.14411709167561</v>
       </c>
       <c r="U91" t="n">
         <v>47.42656695641357</v>
@@ -10604,10 +10666,10 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C92" t="n">
-        <v>1.129506479225996</v>
+        <v>1.129833091455827</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10632,25 +10694,25 @@
         <v>10</v>
       </c>
       <c r="J92" t="n">
-        <v>23.07989300517391</v>
+        <v>22.28274626067631</v>
       </c>
       <c r="K92" t="n">
-        <v>7.19908067077657</v>
+        <v>7.230078749510715</v>
       </c>
       <c r="L92" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M92" t="n">
-        <v>71.42857142857143</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N92" t="n">
-        <v>13.10328592465721</v>
+        <v>12.99255088315147</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>0.7471326472315409</v>
+        <v>0.7180086590142576</v>
       </c>
       <c r="Q92" t="n">
         <v>56</v>
@@ -10713,10 +10775,10 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04185694363395753</v>
+        <v>0.04204030107742614</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10741,25 +10803,25 @@
         <v>10</v>
       </c>
       <c r="J93" t="n">
-        <v>19.49655531533526</v>
+        <v>19.1493380128757</v>
       </c>
       <c r="K93" t="n">
-        <v>1.511841132971847</v>
+        <v>1.956521275762602</v>
       </c>
       <c r="L93" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M93" t="n">
-        <v>61.22448979591837</v>
+        <v>63.46153846153846</v>
       </c>
       <c r="N93" t="n">
-        <v>14.67814716503741</v>
+        <v>13.90414862604118</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>4.421315599181241</v>
+        <v>3.96588533390716</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10822,10 +10884,10 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C94" t="n">
-        <v>6.073463524407338</v>
+        <v>6.36910561323006</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10850,25 +10912,25 @@
         <v>10</v>
       </c>
       <c r="J94" t="n">
-        <v>12.24582326961634</v>
+        <v>12.24049282186025</v>
       </c>
       <c r="K94" t="n">
-        <v>2.031802120141357</v>
+        <v>6.991974103368959</v>
       </c>
       <c r="L94" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="M94" t="n">
-        <v>36.53846153846154</v>
+        <v>51.85185185185185</v>
       </c>
       <c r="N94" t="n">
-        <v>12.66321508749038</v>
+        <v>12.90032966927842</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>5.849350649350638</v>
+        <v>0.9421509464412336</v>
       </c>
       <c r="Q94" t="n">
         <v>40</v>
@@ -10895,13 +10957,17 @@
         <v>46.65531127586331</v>
       </c>
       <c r="Y94" t="n">
-        <v>10.46283204629581</v>
+        <v>6.104370806720483</v>
       </c>
       <c r="Z94" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA94" t="inlineStr"/>
-      <c r="AB94" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>9.657835500919472</v>
+      </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
@@ -10915,10 +10981,10 @@
         <v>54.05405405405406</v>
       </c>
       <c r="AG94" t="n">
-        <v>21.16476085623091</v>
+        <v>21.16703203497267</v>
       </c>
       <c r="AH94" t="n">
-        <v>32.88929319782315</v>
+        <v>32.88702201908139</v>
       </c>
       <c r="AI94" t="n">
         <v>38.38404689217949</v>
@@ -10937,10 +11003,10 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C95" t="n">
-        <v>0.14092538340977</v>
+        <v>0.1410452109555707</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10968,7 +11034,7 @@
         <v>23.400044414021</v>
       </c>
       <c r="K95" t="n">
-        <v>1.650395385039394</v>
+        <v>1.736827772973659</v>
       </c>
       <c r="L95" t="n">
         <v>26</v>
@@ -10977,13 +11043,13 @@
         <v>65.38461538461539</v>
       </c>
       <c r="N95" t="n">
-        <v>19.29680295145889</v>
+        <v>19.65396541550904</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>4.278984453021395</v>
+        <v>4.190392329255288</v>
       </c>
       <c r="Q95" t="n">
         <v>22</v>
@@ -11046,10 +11112,10 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1323015942011554</v>
+        <v>0.1311657345269349</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11077,22 +11143,22 @@
         <v>12.79622946674051</v>
       </c>
       <c r="K96" t="n">
-        <v>2.257513025901758</v>
+        <v>1.379593253781719</v>
       </c>
       <c r="L96" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M96" t="n">
-        <v>59.72222222222222</v>
+        <v>57.97101449275362</v>
       </c>
       <c r="N96" t="n">
-        <v>13.57796746080097</v>
+        <v>12.20935754886504</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>7.571558064527828</v>
+        <v>8.503098571957167</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11110,25 +11176,25 @@
         <v>48.36276351921527</v>
       </c>
       <c r="V96" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="W96" t="n">
-        <v>68.05555555555556</v>
+        <v>69.01408450704226</v>
       </c>
       <c r="X96" t="n">
         <v>16.74415231729489</v>
       </c>
       <c r="Y96" t="n">
-        <v>10.82759298787469</v>
+        <v>11.59317213142036</v>
       </c>
       <c r="Z96" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA96" t="n">
-        <v>36.8421052631579</v>
+        <v>40</v>
       </c>
       <c r="AB96" t="n">
-        <v>18.11843988336842</v>
+        <v>16.42948776937994</v>
       </c>
       <c r="AC96" t="n">
         <v>8</v>
@@ -11165,10 +11231,10 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C97" t="n">
-        <v>1.855166976030003</v>
+        <v>1.852926302148387</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11193,40 +11259,40 @@
         <v>10</v>
       </c>
       <c r="J97" t="n">
-        <v>23.59665213438843</v>
+        <v>22.80838616541501</v>
       </c>
       <c r="K97" t="n">
-        <v>3.796262648477167</v>
+        <v>3.670897342965151</v>
       </c>
       <c r="L97" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M97" t="n">
-        <v>56.52173913043478</v>
+        <v>56</v>
       </c>
       <c r="N97" t="n">
-        <v>12.9157255095876</v>
+        <v>12.77160703742497</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>0.1962858260251776</v>
+        <v>0.3174494148981077</v>
       </c>
       <c r="Q97" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R97" t="n">
-        <v>54.90196078431372</v>
+        <v>56</v>
       </c>
       <c r="S97" t="n">
-        <v>34.57993301552077</v>
+        <v>34.8420738243145</v>
       </c>
       <c r="T97" t="n">
-        <v>20.32202776879296</v>
+        <v>21.1579261756855</v>
       </c>
       <c r="U97" t="n">
-        <v>41.38470855036881</v>
+        <v>42.30602802165686</v>
       </c>
       <c r="V97" t="n">
         <v>63</v>
@@ -11252,10 +11318,10 @@
         <v>55</v>
       </c>
       <c r="AG97" t="n">
-        <v>58.11993765047036</v>
+        <v>58.39355666422097</v>
       </c>
       <c r="AH97" t="n">
-        <v>-3.119937650470362</v>
+        <v>-3.393556664220966</v>
       </c>
       <c r="AI97" t="n">
         <v>39.82909179893205</v>
@@ -11274,10 +11340,10 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6528842021997929</v>
+        <v>0.6507838413400181</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11296,7 +11362,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H98" t="n">
@@ -11306,25 +11372,25 @@
         <v>10</v>
       </c>
       <c r="J98" t="n">
-        <v>19.60032989595409</v>
+        <v>18.49937747698907</v>
       </c>
       <c r="K98" t="n">
-        <v>8.740929648093033</v>
+        <v>8.391104684157868</v>
       </c>
       <c r="L98" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M98" t="n">
-        <v>76.92307692307692</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="N98" t="n">
-        <v>16.5293966310366</v>
+        <v>15.64875646702917</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>1.157862412967758</v>
+        <v>1.484342576386055</v>
       </c>
       <c r="Q98" t="n">
         <v>48</v>
@@ -11333,10 +11399,10 @@
         <v>68.75</v>
       </c>
       <c r="S98" t="n">
-        <v>39.59359234758559</v>
+        <v>39.05234314689367</v>
       </c>
       <c r="T98" t="n">
-        <v>29.15640765241441</v>
+        <v>29.69765685310633</v>
       </c>
       <c r="U98" t="n">
         <v>54.66692858410841</v>
@@ -11387,10 +11453,10 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4829323530140469</v>
+        <v>0.4809410266688286</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11418,22 +11484,22 @@
         <v>28.77817890954801</v>
       </c>
       <c r="K99" t="n">
-        <v>3.894759745235188</v>
+        <v>3.466359430119437</v>
       </c>
       <c r="L99" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M99" t="n">
-        <v>66.66666666666667</v>
+        <v>60</v>
       </c>
       <c r="N99" t="n">
-        <v>12.77959199349419</v>
+        <v>13.15966388936777</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>0.1012950557110592</v>
+        <v>0.5157623915829301</v>
       </c>
       <c r="Q99" t="n">
         <v>35</v>
@@ -11468,19 +11534,19 @@
       </c>
       <c r="AD99" t="inlineStr"/>
       <c r="AE99" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF99" t="n">
-        <v>52.5</v>
+        <v>51.28205128205128</v>
       </c>
       <c r="AG99" t="n">
-        <v>38.08333281435104</v>
+        <v>37.92264871388912</v>
       </c>
       <c r="AH99" t="n">
-        <v>14.41666718564896</v>
+        <v>13.35940256816216</v>
       </c>
       <c r="AI99" t="n">
-        <v>37.49736210669248</v>
+        <v>36.19936288445796</v>
       </c>
       <c r="AJ99" t="n">
         <v>77</v>
@@ -11496,10 +11562,10 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C100" t="n">
-        <v>331.1723393095031</v>
+        <v>329.3454018946936</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11524,19 +11590,19 @@
         <v>10</v>
       </c>
       <c r="J100" t="n">
-        <v>25.87300653788257</v>
+        <v>25.19597156501795</v>
       </c>
       <c r="K100" t="n">
-        <v>8.054742969156891</v>
+        <v>7.458650755690122</v>
       </c>
       <c r="L100" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M100" t="n">
-        <v>54.54545454545455</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N100" t="n">
-        <v>13.39481695000269</v>
+        <v>11.81400718384301</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11605,10 +11671,10 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C101" t="n">
-        <v>325.7803739343845</v>
+        <v>326.9648698461843</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11633,19 +11699,19 @@
         <v>10</v>
       </c>
       <c r="J101" t="n">
-        <v>14.61847018515478</v>
+        <v>13.42090796247281</v>
       </c>
       <c r="K101" t="n">
-        <v>3.164559512477827</v>
+        <v>3.539652700288376</v>
       </c>
       <c r="L101" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="M101" t="n">
-        <v>53.33333333333334</v>
+        <v>34.28571428571428</v>
       </c>
       <c r="N101" t="n">
-        <v>9.217090275853739</v>
+        <v>8.303444048838744</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11714,10 +11780,10 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C102" t="n">
-        <v>388.837973408214</v>
+        <v>393.6120078130411</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11813,10 +11879,10 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7328120176670864</v>
+        <v>0.7285584145187723</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11841,10 +11907,10 @@
         <v>10</v>
       </c>
       <c r="J103" t="n">
-        <v>31.27238030517686</v>
+        <v>30.74202968074841</v>
       </c>
       <c r="K103" t="n">
-        <v>12.70527365479126</v>
+        <v>12.05107654108153</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
@@ -11883,25 +11949,25 @@
         <v>68.18181818181819</v>
       </c>
       <c r="X103" t="n">
-        <v>14.2580428648073</v>
+        <v>14.26498323563516</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.35900210705806</v>
+        <v>1.937519817412625</v>
       </c>
       <c r="Z103" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AA103" t="n">
-        <v>46.55172413793103</v>
+        <v>37.28813559322034</v>
       </c>
       <c r="AB103" t="n">
-        <v>10.43347479087641</v>
+        <v>10.95547504091795</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>6.732492609360675</v>
+        <v>6.182262748504153</v>
       </c>
       <c r="AE103" t="n">
         <v>34</v>
@@ -11932,10 +11998,10 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04942905168834941</v>
+        <v>0.04918715036877503</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11952,7 +12018,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.19: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H104" t="n">
         <v>5</v>
       </c>
@@ -11960,25 +12030,25 @@
         <v>10</v>
       </c>
       <c r="J104" t="n">
-        <v>27.71893445721953</v>
+        <v>27.71454389191555</v>
       </c>
       <c r="K104" t="n">
-        <v>2.173910916824151</v>
+        <v>1.667705418156329</v>
       </c>
       <c r="L104" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M104" t="n">
-        <v>70</v>
+        <v>76.19047619047619</v>
       </c>
       <c r="N104" t="n">
-        <v>13.71309755213932</v>
+        <v>15.96576789787374</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>1.787236161158989</v>
+        <v>2.294036805739852</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>
@@ -12019,10 +12089,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="AG104" t="n">
-        <v>34.6524603607966</v>
+        <v>34.83739231883841</v>
       </c>
       <c r="AH104" t="n">
-        <v>27.04966729877786</v>
+        <v>26.86473534073605</v>
       </c>
       <c r="AI104" t="n">
         <v>47.42656695641357</v>

--- a/TDA_Result.xlsx
+++ b/TDA_Result.xlsx
@@ -453,7 +453,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -679,7 +679,7 @@
         <v>46239</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4481496029691159</v>
+        <v>0.4439558494703479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -739,22 +739,22 @@
         <v>14.94856954517825</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.90911399934021</v>
+        <v>6.789610109909427</v>
       </c>
       <c r="Z2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA2" t="n">
-        <v>53.33333333333334</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.6279462467923</v>
+        <v>13.81015745570964</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.222198227196126</v>
+        <v>1.298556836333165</v>
       </c>
       <c r="AE2" t="n">
         <v>43</v>
@@ -788,7 +788,7 @@
         <v>46239</v>
       </c>
       <c r="C3" t="n">
-        <v>0.748317327017355</v>
+        <v>0.7399264023307063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,22 +848,22 @@
         <v>12.13279917920569</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.643431475112589</v>
+        <v>2.746309263896429</v>
       </c>
       <c r="Z3" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="AA3" t="n">
-        <v>42.1875</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.77839607848096</v>
+        <v>10.88232327535781</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>8.496197712278796</v>
+        <v>7.458524896280128</v>
       </c>
       <c r="AE3" t="n">
         <v>38</v>
@@ -897,7 +897,7 @@
         <v>46239</v>
       </c>
       <c r="C4" t="n">
-        <v>1.422013216104769</v>
+        <v>1.406280578955636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         <v>27.63389482946404</v>
       </c>
       <c r="K4" t="n">
-        <v>10.10207050337513</v>
+        <v>8.883941230749404</v>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M4" t="n">
-        <v>60</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N4" t="n">
-        <v>13.69615600604336</v>
+        <v>21.3980670392144</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -967,22 +967,22 @@
         <v>11.23805603488277</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.021220229838793</v>
+        <v>2.116285458454203</v>
       </c>
       <c r="Z4" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AA4" t="n">
-        <v>37.93103448275862</v>
+        <v>33.92857142857143</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.16310113391574</v>
+        <v>11.48867500196019</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>9.071418935463582</v>
+        <v>8.054163635361045</v>
       </c>
       <c r="AE4" t="n">
         <v>45</v>
@@ -1016,7 +1016,7 @@
         <v>46239</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2631722944139569</v>
+        <v>0.2625477385054309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,22 +1076,22 @@
         <v>16.70172291026088</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.800765785331031</v>
+        <v>6.024317768408915</v>
       </c>
       <c r="Z5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA5" t="n">
-        <v>37.93103448275862</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.33713608175451</v>
+        <v>16.24968379623781</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.457822029741143</v>
+        <v>4.230543622757132</v>
       </c>
       <c r="AE5" t="n">
         <v>44</v>
@@ -1125,7 +1125,7 @@
         <v>46239</v>
       </c>
       <c r="C6" t="n">
-        <v>2.003220410450814</v>
+        <v>1.96437836784379</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,7 +1142,11 @@
           <t>SATMA_BEKLE</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
@@ -1153,16 +1157,16 @@
         <v>23.73506360720576</v>
       </c>
       <c r="K6" t="n">
-        <v>5.508341796185579</v>
+        <v>3.462556177157428</v>
       </c>
       <c r="L6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M6" t="n">
-        <v>68.42105263157895</v>
+        <v>75</v>
       </c>
       <c r="N6" t="n">
-        <v>10.09994808370767</v>
+        <v>13.29868132789301</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
@@ -1195,7 +1199,7 @@
         <v>44.49622708587002</v>
       </c>
       <c r="Y6" t="n">
-        <v>19.53413024004713</v>
+        <v>21.09434734113188</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1240,16 +1244,16 @@
         <v>46239</v>
       </c>
       <c r="C7" t="n">
-        <v>2.173483597863762</v>
+        <v>2.139900806469227</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1268,22 +1272,22 @@
         <v>11.35312764557068</v>
       </c>
       <c r="K7" t="n">
-        <v>4.128605305762179</v>
+        <v>2.519700028710981</v>
       </c>
       <c r="L7" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="M7" t="n">
-        <v>53.57142857142857</v>
+        <v>57.97101449275362</v>
       </c>
       <c r="N7" t="n">
-        <v>13.18265863947417</v>
+        <v>12.62976515663752</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.468495295201321</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1310,22 +1314,22 @@
         <v>13.79329344082609</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.693248170153499</v>
+        <v>9.119492377404747</v>
       </c>
       <c r="Z7" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AA7" t="n">
-        <v>54.54545454545455</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.839646921407008</v>
+        <v>7.904398401892783</v>
       </c>
       <c r="AC7" t="n">
         <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.499006610154197</v>
+        <v>0.9688630110339935</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1359,7 +1363,7 @@
         <v>46239</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3327489813462158</v>
+        <v>0.3253994352389095</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,22 +1391,22 @@
         <v>22.10694516187944</v>
       </c>
       <c r="K8" t="n">
-        <v>5.796806583254588</v>
+        <v>3.460034567173276</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N8" t="n">
-        <v>17.20097034198387</v>
+        <v>17.67912674615781</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.082476293848878</v>
+        <v>4.388134463534388</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1468,7 +1472,7 @@
         <v>46239</v>
       </c>
       <c r="C9" t="n">
-        <v>0.585621406830838</v>
+        <v>0.5860553133534054</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,16 +1500,16 @@
         <v>10.57037035785485</v>
       </c>
       <c r="K9" t="n">
-        <v>5.370595034039449</v>
+        <v>5.44866763852212</v>
       </c>
       <c r="L9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M9" t="n">
-        <v>37.5</v>
+        <v>41.93548387096774</v>
       </c>
       <c r="N9" t="n">
-        <v>16.04479078410657</v>
+        <v>15.37109919094065</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1577,7 +1581,7 @@
         <v>46239</v>
       </c>
       <c r="C10" t="n">
-        <v>2.041056585148209</v>
+        <v>2.039001689671512</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1609,7 @@
         <v>10.23694539327734</v>
       </c>
       <c r="K10" t="n">
-        <v>1.062278090468438</v>
+        <v>0.9605305839936351</v>
       </c>
       <c r="L10" t="n">
         <v>43</v>
@@ -1614,13 +1618,13 @@
         <v>39.53488372093023</v>
       </c>
       <c r="N10" t="n">
-        <v>9.789932158108417</v>
+        <v>9.844583527866305</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>8.843776410354366</v>
+        <v>8.953468611663084</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1686,7 +1690,7 @@
         <v>46239</v>
       </c>
       <c r="C11" t="n">
-        <v>7.446388328339105</v>
+        <v>7.362477750592237</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1707,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>5</v>
       </c>
@@ -1714,16 +1722,16 @@
         <v>20.56423081971027</v>
       </c>
       <c r="K11" t="n">
-        <v>6.694005820835192</v>
+        <v>5.491710791917348</v>
       </c>
       <c r="L11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M11" t="n">
-        <v>66.66666666666667</v>
+        <v>81.25</v>
       </c>
       <c r="N11" t="n">
-        <v>14.54874782819977</v>
+        <v>14.41611962980027</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1795,7 +1803,7 @@
         <v>46239</v>
       </c>
       <c r="C12" t="n">
-        <v>6.479461403558304</v>
+        <v>6.458590403624454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1823,7 +1831,7 @@
         <v>20.08266526523165</v>
       </c>
       <c r="K12" t="n">
-        <v>12.80551881276546</v>
+        <v>12.44216083761243</v>
       </c>
       <c r="L12" t="n">
         <v>3</v>
@@ -1862,25 +1870,25 @@
         <v>70.58823529411765</v>
       </c>
       <c r="X12" t="n">
-        <v>13.26296211695348</v>
+        <v>14.27197631096657</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4038772213247221</v>
+        <v>1.601281024819856</v>
       </c>
       <c r="Z12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AA12" t="n">
-        <v>40</v>
+        <v>34.48275862068966</v>
       </c>
       <c r="AB12" t="n">
-        <v>14.22529094583299</v>
+        <v>13.8766589463101</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.602595296025955</v>
+        <v>0.4052074857607835</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -1914,7 +1922,7 @@
         <v>46239</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2993269388366395</v>
+        <v>0.3010155006598508</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,10 +1950,10 @@
         <v>38.11781916800814</v>
       </c>
       <c r="K13" t="n">
-        <v>5.18496881521906</v>
+        <v>5.778337803013289</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1978,7 +1986,7 @@
         <v>35.74308703619145</v>
       </c>
       <c r="Y13" t="n">
-        <v>22.51173071732565</v>
+        <v>22.07460423026113</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2013,7 +2021,7 @@
         <v>46239</v>
       </c>
       <c r="C14" t="n">
-        <v>8.045462618692428</v>
+        <v>8.050903578806073</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,16 +2081,16 @@
         <v>14.33662537827827</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.020270111068116</v>
+        <v>6.957390072258685</v>
       </c>
       <c r="Z14" t="n">
         <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>37.5</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.56978199300831</v>
+        <v>10.99649109428192</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2122,7 +2130,7 @@
         <v>46239</v>
       </c>
       <c r="C15" t="n">
-        <v>11.79230445221803</v>
+        <v>11.92921091637714</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,16 +2158,16 @@
         <v>16.27559902090345</v>
       </c>
       <c r="K15" t="n">
-        <v>11.03091587485958</v>
+        <v>12.31996418313284</v>
       </c>
       <c r="L15" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="M15" t="n">
-        <v>70.83333333333333</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N15" t="n">
-        <v>14.06653819062704</v>
+        <v>15.44994071782585</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
@@ -2189,25 +2197,25 @@
         <v>79.56989247311827</v>
       </c>
       <c r="X15" t="n">
-        <v>11.12987391039868</v>
+        <v>13.30956739179481</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.08904719501335867</v>
+        <v>0.8733624454148381</v>
       </c>
       <c r="Z15" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="AA15" t="n">
-        <v>26.08695652173913</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AB15" t="n">
-        <v>11.6548836476784</v>
+        <v>12.48497716224804</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>9.919786096256678</v>
+        <v>9.207048458149792</v>
       </c>
       <c r="AE15" t="n">
         <v>31</v>
@@ -2241,7 +2249,7 @@
         <v>46239</v>
       </c>
       <c r="C16" t="n">
-        <v>36.59608208789945</v>
+        <v>36.89121613787117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2269,22 +2277,22 @@
         <v>17.40096492560246</v>
       </c>
       <c r="K16" t="n">
-        <v>5.483321196855973</v>
+        <v>6.334005696757372</v>
       </c>
       <c r="L16" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="M16" t="n">
-        <v>61.90476190476191</v>
+        <v>59.375</v>
       </c>
       <c r="N16" t="n">
-        <v>15.42901561708397</v>
+        <v>16.65046628003577</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>4.281889072031464</v>
+        <v>3.447621745481211</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2350,7 +2358,7 @@
         <v>46239</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7365460942150444</v>
+        <v>0.7546408636997923</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2367,7 +2375,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>5</v>
       </c>
@@ -2378,22 +2390,22 @@
         <v>14.16674936134154</v>
       </c>
       <c r="K17" t="n">
-        <v>4.607622473965778</v>
+        <v>7.177523841824107</v>
       </c>
       <c r="L17" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="M17" t="n">
-        <v>74.50980392156863</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="N17" t="n">
-        <v>15.78087961695294</v>
+        <v>15.89076158887889</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>3.242954428945666</v>
+        <v>0.7673961187886214</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2420,22 +2432,22 @@
         <v>15.7396793517258</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.618185345002017</v>
+        <v>7.397770201074971</v>
       </c>
       <c r="Z17" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="AA17" t="n">
-        <v>41.66666666666666</v>
+        <v>51.61290322580645</v>
       </c>
       <c r="AB17" t="n">
-        <v>11.00132337973763</v>
+        <v>11.32757773766146</v>
       </c>
       <c r="AC17" t="n">
         <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.4224463255749322</v>
+        <v>2.810115700858895</v>
       </c>
       <c r="AE17" t="n">
         <v>35</v>
@@ -2469,7 +2481,7 @@
         <v>46239</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1044701437631723</v>
+        <v>0.1036317317881471</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,22 +2509,22 @@
         <v>25.10069993473878</v>
       </c>
       <c r="K18" t="n">
-        <v>4.545141405801068</v>
+        <v>3.706127546644944</v>
       </c>
       <c r="L18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M18" t="n">
-        <v>47.36842105263158</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="N18" t="n">
-        <v>22.19834958948873</v>
+        <v>21.58793351449615</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>5.217706457563076</v>
+        <v>6.068949446139715</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2578,7 +2590,7 @@
         <v>46239</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02522418169746321</v>
+        <v>0.02522476422222576</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2606,7 +2618,7 @@
         <v>22.96673379938283</v>
       </c>
       <c r="K19" t="n">
-        <v>2.125359877788258</v>
+        <v>2.127718350769725</v>
       </c>
       <c r="L19" t="n">
         <v>22</v>
@@ -2621,7 +2633,7 @@
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>7.710758749477309</v>
+        <v>7.708271345289441</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2687,7 +2699,7 @@
         <v>46239</v>
       </c>
       <c r="C20" t="n">
-        <v>1.839263172137394</v>
+        <v>1.842458775457532</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,16 +2759,16 @@
         <v>20.34011802710127</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.156157925967211</v>
+        <v>6.99484762819107</v>
       </c>
       <c r="Z20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA20" t="n">
-        <v>44.44444444444444</v>
+        <v>36.8421052631579</v>
       </c>
       <c r="AB20" t="n">
-        <v>12.96967327390692</v>
+        <v>13.07751158256018</v>
       </c>
       <c r="AC20" t="n">
         <v>4</v>
@@ -2796,7 +2808,7 @@
         <v>46239</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9694493203538858</v>
+        <v>0.9383611771458275</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,22 +2836,22 @@
         <v>13.7580634602656</v>
       </c>
       <c r="K21" t="n">
-        <v>3.623315382094949</v>
+        <v>0.3003397497881588</v>
       </c>
       <c r="L21" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M21" t="n">
-        <v>50</v>
+        <v>57.6271186440678</v>
       </c>
       <c r="N21" t="n">
-        <v>14.21383982371403</v>
+        <v>18.00456263135702</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>4.223648511695188</v>
+        <v>7.676604355897121</v>
       </c>
       <c r="Q21" t="n">
         <v>41</v>
@@ -2905,7 +2917,7 @@
         <v>46239</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3247613218292883</v>
+        <v>0.3111054164386464</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2931,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2933,22 +2945,22 @@
         <v>20.35908649698318</v>
       </c>
       <c r="K22" t="n">
-        <v>9.484721073664048</v>
+        <v>4.88099245142164</v>
       </c>
       <c r="L22" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M22" t="n">
-        <v>62.5</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N22" t="n">
-        <v>13.73609705603676</v>
+        <v>15.52421149080303</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>0.470640032036318</v>
+        <v>4.880777182719132</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -2972,25 +2984,25 @@
         <v>72.22222222222223</v>
       </c>
       <c r="X22" t="n">
-        <v>13.73655091481325</v>
+        <v>13.73917753549452</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.738314382624219</v>
+        <v>7.788156443551319</v>
       </c>
       <c r="Z22" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="AA22" t="n">
-        <v>38.70967741935484</v>
+        <v>65</v>
       </c>
       <c r="AB22" t="n">
-        <v>13.95240582378237</v>
+        <v>12.96035064914134</v>
       </c>
       <c r="AC22" t="n">
         <v>6</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.34951798617532</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3016,7 +3028,7 @@
         <v>46239</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8479528758847078</v>
+        <v>0.8492337255917697</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3044,10 +3056,10 @@
         <v>23.56853924970225</v>
       </c>
       <c r="K23" t="n">
-        <v>21.77244200776267</v>
+        <v>21.95638170666532</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3079,25 +3091,25 @@
         <v>87.5</v>
       </c>
       <c r="X23" t="n">
-        <v>23.76475220013776</v>
+        <v>27.6919469835746</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.609755731707319</v>
+        <v>4.49172043531224</v>
       </c>
       <c r="Z23" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AA23" t="n">
-        <v>41.66666666666666</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB23" t="n">
-        <v>10.3788617544537</v>
+        <v>9.8066042688297</v>
       </c>
       <c r="AC23" t="n">
         <v>6</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.462072739977419</v>
+        <v>1.57921341643078</v>
       </c>
       <c r="AE23" t="n">
         <v>10</v>
@@ -3131,7 +3143,7 @@
         <v>46239</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1828753056929751</v>
+        <v>0.182038704399021</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3171,7 @@
         <v>23.26504282616538</v>
       </c>
       <c r="K24" t="n">
-        <v>4.480929271919476</v>
+        <v>4.002959431807995</v>
       </c>
       <c r="L24" t="n">
         <v>11</v>
@@ -3174,7 +3186,7 @@
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>5.282371401690678</v>
+        <v>5.766221077703193</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3240,7 +3252,7 @@
         <v>46239</v>
       </c>
       <c r="C25" t="n">
-        <v>3.955992267274341</v>
+        <v>3.987614580533306</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3339,7 +3351,7 @@
         <v>46239</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4338558942967459</v>
+        <v>0.4342863361109606</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3438,7 +3450,7 @@
         <v>46239</v>
       </c>
       <c r="C27" t="n">
-        <v>34.01060357163774</v>
+        <v>33.21260484207205</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3463,10 +3475,10 @@
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>60.45453229009195</v>
+        <v>60.77982296475879</v>
       </c>
       <c r="K27" t="n">
-        <v>1.75356356736398</v>
+        <v>0.190234622701313</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3477,7 +3489,7 @@
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>6.138788867576794</v>
+        <v>7.794936708860778</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -3523,7 +3535,7 @@
         <v>46239</v>
       </c>
       <c r="C28" t="n">
-        <v>1.475614503706198</v>
+        <v>1.457781072773678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3551,16 +3563,16 @@
         <v>24.87361787048376</v>
       </c>
       <c r="K28" t="n">
-        <v>5.828449661485213</v>
+        <v>4.549467689572051</v>
       </c>
       <c r="L28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M28" t="n">
-        <v>37.5</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N28" t="n">
-        <v>16.04159935017336</v>
+        <v>12.16006990667934</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
@@ -3632,7 +3644,7 @@
         <v>46239</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3794137012484565</v>
+        <v>0.3678611295799119</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3649,11 +3661,7 @@
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>5</v>
       </c>
@@ -3661,25 +3669,25 @@
         <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>19.41382773128674</v>
+        <v>20.06506691394495</v>
       </c>
       <c r="K29" t="n">
-        <v>2.776800498666154</v>
+        <v>0.459241788935727</v>
       </c>
       <c r="L29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M29" t="n">
-        <v>85.71428571428571</v>
+        <v>50</v>
       </c>
       <c r="N29" t="n">
-        <v>22.76363899904027</v>
+        <v>16.83864030684587</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>1.190151372098525</v>
+        <v>3.524571904000018</v>
       </c>
       <c r="Q29" t="n">
         <v>6</v>
@@ -3706,7 +3714,7 @@
         <v>55.05052857749912</v>
       </c>
       <c r="Y29" t="n">
-        <v>17.17611049787314</v>
+        <v>19.69797229725598</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3751,7 +3759,7 @@
         <v>46239</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3874013809447285</v>
+        <v>0.3817347461709732</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3779,22 +3787,22 @@
         <v>21.6314445059014</v>
       </c>
       <c r="K30" t="n">
-        <v>4.795606539582176</v>
+        <v>3.262730155130922</v>
       </c>
       <c r="L30" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M30" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="N30" t="n">
-        <v>11.12294608260836</v>
+        <v>12.13088844184501</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>0.1950401044156669</v>
+        <v>1.682378378200133</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3860,7 +3868,7 @@
         <v>46239</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1858181339152461</v>
+        <v>0.182038704399021</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3885,25 +3893,25 @@
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>27.21774887994811</v>
+        <v>27.96470403013798</v>
       </c>
       <c r="K31" t="n">
-        <v>1.028573142857137</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
-        <v>57.14285714285715</v>
+        <v>25</v>
       </c>
       <c r="N31" t="n">
-        <v>13.69665025578728</v>
+        <v>12.88221960224227</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>8.88008865022476</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3969,7 +3977,7 @@
         <v>46239</v>
       </c>
       <c r="C32" t="n">
-        <v>2.293298391612765</v>
+        <v>2.329086530253182</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4029,22 +4037,22 @@
         <v>12.36180984775317</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.155532505121961</v>
+        <v>1.644223186657467</v>
       </c>
       <c r="Z32" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="AA32" t="n">
-        <v>39.1304347826087</v>
+        <v>40.38461538461539</v>
       </c>
       <c r="AB32" t="n">
-        <v>11.65371273481513</v>
+        <v>11.37486641220681</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>5.002317241441023</v>
+        <v>6.462026958929301</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4078,7 +4086,7 @@
         <v>46239</v>
       </c>
       <c r="C33" t="n">
-        <v>1.799324853953008</v>
+        <v>1.808825789847307</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4106,22 +4114,22 @@
         <v>12.57251846431013</v>
       </c>
       <c r="K33" t="n">
-        <v>0.8500880230916774</v>
+        <v>1.382604549574773</v>
       </c>
       <c r="L33" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M33" t="n">
-        <v>62.96296296296296</v>
+        <v>62.5</v>
       </c>
       <c r="N33" t="n">
-        <v>11.8035712977734</v>
+        <v>12.27595981318721</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>3.123360662002694</v>
+        <v>2.581700738557524</v>
       </c>
       <c r="Q33" t="n">
         <v>39</v>
@@ -4187,7 +4195,7 @@
         <v>46239</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8803239270528644</v>
+        <v>0.8782421454318938</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4215,22 +4223,22 @@
         <v>10.37797163438468</v>
       </c>
       <c r="K34" t="n">
-        <v>2.827025848908571</v>
+        <v>2.583861479551985</v>
       </c>
       <c r="L34" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M34" t="n">
-        <v>38.09523809523809</v>
+        <v>38.63636363636363</v>
       </c>
       <c r="N34" t="n">
-        <v>9.538689121041216</v>
+        <v>10.5823400077803</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>1.140725545067278</v>
+        <v>1.380469110855498</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4257,16 +4265,16 @@
         <v>14.68007915548277</v>
       </c>
       <c r="Y34" t="n">
-        <v>7.844333726172559</v>
+        <v>8.062262566252388</v>
       </c>
       <c r="Z34" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA34" t="n">
-        <v>53.84615384615385</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="AB34" t="n">
-        <v>11.84984593704369</v>
+        <v>11.68963248252191</v>
       </c>
       <c r="AC34" t="n">
         <v>2</v>
@@ -4306,7 +4314,7 @@
         <v>46239</v>
       </c>
       <c r="C35" t="n">
-        <v>1.930700794819965</v>
+        <v>1.928643350797538</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4325,7 +4333,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %88.89: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4338,16 +4346,16 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>8.843741397156691</v>
+        <v>8.727752474524554</v>
       </c>
       <c r="L35" t="n">
         <v>9</v>
       </c>
       <c r="M35" t="n">
-        <v>88.88888888888889</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N35" t="n">
-        <v>12.48259706892392</v>
+        <v>13.16691766425628</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4380,7 +4388,7 @@
         <v>42.52272358489104</v>
       </c>
       <c r="Y35" t="n">
-        <v>16.09149249279481</v>
+        <v>16.18090927744868</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -4425,7 +4433,7 @@
         <v>46239</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08302959567892415</v>
+        <v>0.08219068855799756</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4453,16 +4461,16 @@
         <v>19.86910865198848</v>
       </c>
       <c r="K36" t="n">
-        <v>3.775797236026768</v>
+        <v>2.727276469795514</v>
       </c>
       <c r="L36" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M36" t="n">
-        <v>52.94117647058823</v>
+        <v>45</v>
       </c>
       <c r="N36" t="n">
-        <v>13.72841217631283</v>
+        <v>16.06371808191339</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4534,7 +4542,7 @@
         <v>46239</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06369105550169608</v>
+        <v>0.06348232022709209</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4562,7 +4570,7 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>3.67828495363911</v>
+        <v>3.338499168809506</v>
       </c>
       <c r="L37" t="n">
         <v>68</v>
@@ -4571,13 +4579,13 @@
         <v>52.94117647058823</v>
       </c>
       <c r="N37" t="n">
-        <v>20.71797764396541</v>
+        <v>18.6341788687826</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>4.168389791838667</v>
+        <v>4.51090432770429</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4643,16 +4651,16 @@
         <v>46239</v>
       </c>
       <c r="C38" t="n">
-        <v>1.662693875451374</v>
+        <v>1.691110100155856</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4671,22 +4679,22 @@
         <v>16.52414407302303</v>
       </c>
       <c r="K38" t="n">
-        <v>4.945529610944654</v>
+        <v>6.739098346106975</v>
       </c>
       <c r="L38" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="M38" t="n">
-        <v>65.625</v>
+        <v>70.37037037037037</v>
       </c>
       <c r="N38" t="n">
-        <v>12.37025528795528</v>
+        <v>12.39457352361738</v>
       </c>
       <c r="O38" t="n">
         <v>6</v>
       </c>
       <c r="P38" t="n">
-        <v>1.004778758051428</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>34</v>
@@ -4752,7 +4760,7 @@
         <v>46239</v>
       </c>
       <c r="C39" t="n">
-        <v>2.743129645302055</v>
+        <v>2.703253914738832</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4780,16 +4788,16 @@
         <v>18.47027414490581</v>
       </c>
       <c r="K39" t="n">
-        <v>8.585415421599807</v>
+        <v>7.006954565452195</v>
       </c>
       <c r="L39" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M39" t="n">
-        <v>64.70588235294117</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N39" t="n">
-        <v>13.62657385415175</v>
+        <v>14.42261750646456</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4822,22 +4830,22 @@
         <v>10.2437411865161</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.504235748050908</v>
+        <v>2.93602755696375</v>
       </c>
       <c r="Z39" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AA39" t="n">
-        <v>40.38461538461539</v>
+        <v>38.63636363636363</v>
       </c>
       <c r="AB39" t="n">
-        <v>11.74839789809693</v>
+        <v>13.78517180818355</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.564423948677709</v>
+        <v>3.156652634255619</v>
       </c>
       <c r="AE39" t="n">
         <v>42</v>
@@ -4871,7 +4879,7 @@
         <v>46239</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1977996134162674</v>
+        <v>0.1952817073761678</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4888,7 +4896,11 @@
           <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H40" t="n">
         <v>5</v>
       </c>
@@ -4899,16 +4911,16 @@
         <v>14.73965458840789</v>
       </c>
       <c r="K40" t="n">
-        <v>8.026157107124021</v>
+        <v>6.651029477848258</v>
       </c>
       <c r="L40" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M40" t="n">
-        <v>71.42857142857143</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N40" t="n">
-        <v>11.37077883851085</v>
+        <v>11.36182252967595</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4941,16 +4953,16 @@
         <v>14.17330472629232</v>
       </c>
       <c r="Y40" t="n">
-        <v>5.384049830128723</v>
+        <v>6.588471154861653</v>
       </c>
       <c r="Z40" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA40" t="n">
-        <v>40</v>
+        <v>34.78260869565217</v>
       </c>
       <c r="AB40" t="n">
-        <v>11.69010824049992</v>
+        <v>12.33129410895796</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
@@ -4990,7 +5002,7 @@
         <v>46239</v>
       </c>
       <c r="C41" t="n">
-        <v>1.691071046728007</v>
+        <v>1.715283863479616</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5009,7 +5021,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -5022,16 +5034,16 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>11.7555079169205</v>
+        <v>13.35562734384286</v>
       </c>
       <c r="L41" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M41" t="n">
-        <v>77.77777777777777</v>
+        <v>80</v>
       </c>
       <c r="N41" t="n">
-        <v>13.38516228592029</v>
+        <v>12.17975430538131</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
@@ -5064,13 +5076,13 @@
         <v>40.81782021738603</v>
       </c>
       <c r="Y41" t="n">
-        <v>13.27636381379426</v>
+        <v>12.03465163672595</v>
       </c>
       <c r="Z41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA41" t="n">
-        <v>25</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="AB41" t="n">
         <v>22.19906898574699</v>
@@ -5113,7 +5125,7 @@
         <v>46239</v>
       </c>
       <c r="C42" t="n">
-        <v>3.218185175699889</v>
+        <v>3.193034476527756</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5145,7 +5157,7 @@
         <v>21.11518617286606</v>
       </c>
       <c r="K42" t="n">
-        <v>4.704315940280046</v>
+        <v>3.886032774935066</v>
       </c>
       <c r="L42" t="n">
         <v>6</v>
@@ -5154,7 +5166,7 @@
         <v>83.33333333333333</v>
       </c>
       <c r="N42" t="n">
-        <v>12.46777111330014</v>
+        <v>12.69257812864195</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
@@ -5222,7 +5234,7 @@
         <v>46239</v>
       </c>
       <c r="C43" t="n">
-        <v>7.104810882085017</v>
+        <v>7.104974959886299</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5282,7 +5294,7 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>8.295886117700313</v>
+        <v>8.293768311945316</v>
       </c>
       <c r="Z43" t="n">
         <v>8</v>
@@ -5331,7 +5343,7 @@
         <v>46239</v>
       </c>
       <c r="C44" t="n">
-        <v>5.017509869479351</v>
+        <v>5.078585780026263</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5348,7 +5360,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %77.27: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H44" t="n">
         <v>5</v>
       </c>
@@ -5359,22 +5375,22 @@
         <v>13.03201987649729</v>
       </c>
       <c r="K44" t="n">
-        <v>2.695109198212875</v>
+        <v>3.945170975101076</v>
       </c>
       <c r="L44" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M44" t="n">
-        <v>69.23076923076923</v>
+        <v>77.27272727272727</v>
       </c>
       <c r="N44" t="n">
-        <v>18.54409624254036</v>
+        <v>20.4740028993714</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>7.113182758964598</v>
+        <v>5.825021949648157</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5401,22 +5417,22 @@
         <v>12.1234692799834</v>
       </c>
       <c r="Y44" t="n">
-        <v>8.408908627530042</v>
+        <v>7.294011108825305</v>
       </c>
       <c r="Z44" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA44" t="n">
-        <v>14.28571428571429</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="AB44" t="n">
-        <v>9.691917834769438</v>
+        <v>8.772956734278921</v>
       </c>
       <c r="AC44" t="n">
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.737168264541722</v>
+        <v>2.918893292159563</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5442,7 +5458,7 @@
         <v>46239</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02080994924352745</v>
+        <v>0.02081042982644138</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5470,7 +5486,7 @@
         <v>10.6275101427813</v>
       </c>
       <c r="K45" t="n">
-        <v>3.052606957600967</v>
+        <v>3.054986844334984</v>
       </c>
       <c r="L45" t="n">
         <v>56</v>
@@ -5485,7 +5501,7 @@
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>6.741598536422688</v>
+        <v>6.739133513408224</v>
       </c>
       <c r="Q45" t="n">
         <v>37</v>
@@ -5551,7 +5567,7 @@
         <v>46239</v>
       </c>
       <c r="C46" t="n">
-        <v>8.923053903683698</v>
+        <v>8.671012340097924</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,11 +5584,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.19: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>5</v>
       </c>
@@ -5583,22 +5595,22 @@
         <v>20.98614247885408</v>
       </c>
       <c r="K46" t="n">
-        <v>8.063524284180556</v>
+        <v>5.011150072260806</v>
       </c>
       <c r="L46" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M46" t="n">
-        <v>76.19047619047619</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="N46" t="n">
-        <v>14.40054871052415</v>
+        <v>11.70185446250036</v>
       </c>
       <c r="O46" t="n">
         <v>10</v>
       </c>
       <c r="P46" t="n">
-        <v>1.791979049958603</v>
+        <v>4.750781154483352</v>
       </c>
       <c r="Q46" t="n">
         <v>54</v>
@@ -5664,7 +5676,7 @@
         <v>46239</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7911984534548681</v>
+        <v>0.7912167253138627</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5692,7 +5704,7 @@
         <v>25.31303456031801</v>
       </c>
       <c r="K47" t="n">
-        <v>6.142902312651333</v>
+        <v>6.145353566361278</v>
       </c>
       <c r="L47" t="n">
         <v>11</v>
@@ -5707,7 +5719,7 @@
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>3.633872452429587</v>
+        <v>3.631479197277199</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5773,7 +5785,7 @@
         <v>46239</v>
       </c>
       <c r="C48" t="n">
-        <v>0.06221964643539671</v>
+        <v>0.06095984643244901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5801,22 +5813,22 @@
         <v>30.07074365952763</v>
       </c>
       <c r="K48" t="n">
-        <v>6.01934295461275</v>
+        <v>3.872703167686065</v>
       </c>
       <c r="L48" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M48" t="n">
-        <v>69.23076923076923</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N48" t="n">
-        <v>10.60849138278571</v>
+        <v>14.12340481485396</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>3.754651683788857</v>
+        <v>5.898851811358363</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5882,7 +5894,7 @@
         <v>46239</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2625416753938916</v>
+        <v>0.2587640376931651</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5910,22 +5922,22 @@
         <v>23.59168796028241</v>
       </c>
       <c r="K49" t="n">
-        <v>3.897824223933144</v>
+        <v>2.402867900435424</v>
       </c>
       <c r="L49" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M49" t="n">
-        <v>52.63157894736842</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N49" t="n">
-        <v>9.357882125142343</v>
+        <v>9.60781177366678</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>1.060826619132382</v>
+        <v>2.536190785291015</v>
       </c>
       <c r="Q49" t="n">
         <v>53</v>
@@ -5991,7 +6003,7 @@
         <v>46239</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7319216352417425</v>
+        <v>0.7294160843427088</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6019,22 +6031,22 @@
         <v>11.86078125763058</v>
       </c>
       <c r="K50" t="n">
-        <v>2.437547909096338</v>
+        <v>2.086878550656524</v>
       </c>
       <c r="L50" t="n">
         <v>60</v>
       </c>
       <c r="M50" t="n">
-        <v>53.33333333333334</v>
+        <v>50</v>
       </c>
       <c r="N50" t="n">
-        <v>13.52691631999766</v>
+        <v>13.78965101893368</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>1.52527283481072</v>
+        <v>1.874013072497038</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6100,7 +6112,7 @@
         <v>46239</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1830855120329969</v>
+        <v>0.1864530387948054</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6119,7 +6131,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -6132,16 +6144,16 @@
         <v>27.30972539236674</v>
       </c>
       <c r="K51" t="n">
-        <v>6.116584957669891</v>
+        <v>8.068407555474799</v>
       </c>
       <c r="L51" t="n">
         <v>4</v>
       </c>
       <c r="M51" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N51" t="n">
-        <v>22.48074903415539</v>
+        <v>21.01343299532531</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
@@ -6174,7 +6186,7 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>16.88551466340381</v>
+        <v>15.35677407351765</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6219,7 +6231,7 @@
         <v>46239</v>
       </c>
       <c r="C52" t="n">
-        <v>4.24817255209683</v>
+        <v>4.267189103126978</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6279,22 +6291,22 @@
         <v>12.1710603868542</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.526019076741259</v>
+        <v>2.089685827654209</v>
       </c>
       <c r="Z52" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA52" t="n">
-        <v>37.73584905660378</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="AB52" t="n">
-        <v>12.13128424788364</v>
+        <v>12.49481897677179</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>5.615838064076195</v>
+        <v>6.036457162155773</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6328,7 +6340,7 @@
         <v>46239</v>
       </c>
       <c r="C53" t="n">
-        <v>1.610143499104591</v>
+        <v>1.620691001587639</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6347,7 +6359,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -6360,22 +6372,22 @@
         <v>28.17598592067425</v>
       </c>
       <c r="K53" t="n">
-        <v>6.153568722159308</v>
+        <v>6.84894465002166</v>
       </c>
       <c r="L53" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M53" t="n">
-        <v>85.71428571428571</v>
+        <v>100</v>
       </c>
       <c r="N53" t="n">
-        <v>11.95683582355183</v>
+        <v>11.18129841148397</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>1.739396329362641</v>
+        <v>1.077273485244579</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6433,7 +6445,7 @@
         <v>46239</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08912543344950878</v>
+        <v>0.08912749170347238</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6461,7 +6473,7 @@
         <v>42.39442432818535</v>
       </c>
       <c r="K54" t="n">
-        <v>10.26282370644114</v>
+        <v>10.26537010520914</v>
       </c>
       <c r="L54" t="n">
         <v>2</v>
@@ -6499,7 +6511,7 @@
         <v>114.7400208810756</v>
       </c>
       <c r="Y54" t="n">
-        <v>36.48246565190647</v>
+        <v>36.48099878423727</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -6544,21 +6556,21 @@
         <v>46239</v>
       </c>
       <c r="C55" t="n">
-        <v>0.882005497265862</v>
+        <v>0.8908545751547472</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -6572,22 +6584,22 @@
         <v>12.31616646597832</v>
       </c>
       <c r="K55" t="n">
-        <v>5.141777899817224</v>
+        <v>6.196655431641607</v>
       </c>
       <c r="L55" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M55" t="n">
-        <v>66.0377358490566</v>
+        <v>68</v>
       </c>
       <c r="N55" t="n">
-        <v>13.00589306398004</v>
+        <v>13.14746794751552</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>0.8162522237359582</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>44</v>
@@ -6614,16 +6626,16 @@
         <v>25.41488056506582</v>
       </c>
       <c r="Y55" t="n">
-        <v>7.807658491613467</v>
+        <v>6.882701432620775</v>
       </c>
       <c r="Z55" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA55" t="n">
-        <v>60</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="AB55" t="n">
-        <v>10.06535135336795</v>
+        <v>9.916378758105774</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6663,7 +6675,7 @@
         <v>46239</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8622465847672793</v>
+        <v>0.9013648931427447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6691,7 +6703,7 @@
         <v>34.38683570496719</v>
       </c>
       <c r="K56" t="n">
-        <v>9.954948429596788</v>
+        <v>14.9433724559306</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6718,25 +6730,25 @@
         <v>100</v>
       </c>
       <c r="X56" t="n">
-        <v>15.71888627084337</v>
+        <v>18.2672887877857</v>
       </c>
       <c r="Y56" t="n">
-        <v>4.980982817062307</v>
+        <v>2.810511990191478</v>
       </c>
       <c r="Z56" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA56" t="n">
-        <v>23.52941176470588</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="AB56" t="n">
-        <v>18.01250639514078</v>
+        <v>8.376267141289677</v>
       </c>
       <c r="AC56" t="n">
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>5.2821186029263</v>
+        <v>7.397392616249753</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6762,7 +6774,7 @@
         <v>46239</v>
       </c>
       <c r="C57" t="n">
-        <v>1.428319164994094</v>
+        <v>1.44727075478568</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6779,11 +6791,7 @@
           <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %83.33: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>5</v>
       </c>
@@ -6794,17 +6802,13 @@
         <v>32.76213282665623</v>
       </c>
       <c r="K57" t="n">
-        <v>22.30300533354659</v>
+        <v>23.92577736109212</v>
       </c>
       <c r="L57" t="n">
-        <v>3</v>
-      </c>
-      <c r="M57" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N57" t="n">
-        <v>15.65787039974029</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
         <v>10</v>
       </c>
@@ -6836,16 +6840,16 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>11.94333411543395</v>
+        <v>10.77495813115876</v>
       </c>
       <c r="Z57" t="n">
         <v>6</v>
       </c>
       <c r="AA57" t="n">
-        <v>83.33333333333333</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB57" t="n">
-        <v>12.36237164600526</v>
+        <v>14.70271092548353</v>
       </c>
       <c r="AC57" t="n">
         <v>6</v>
@@ -6885,7 +6889,7 @@
         <v>46239</v>
       </c>
       <c r="C58" t="n">
-        <v>0.756305006713627</v>
+        <v>0.7613674606957136</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6904,7 +6908,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %89.19: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %85.19: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -6917,22 +6921,22 @@
         <v>16.33691982084211</v>
       </c>
       <c r="K58" t="n">
-        <v>1.957683536208732</v>
+        <v>2.640154333625588</v>
       </c>
       <c r="L58" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="M58" t="n">
-        <v>89.18918918918919</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="N58" t="n">
-        <v>19.01585258090028</v>
+        <v>19.3576068357252</v>
       </c>
       <c r="O58" t="n">
         <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>2.98390112277398</v>
+        <v>2.299144697993993</v>
       </c>
       <c r="Q58" t="n">
         <v>24</v>
@@ -6959,7 +6963,7 @@
         <v>41.32985472592288</v>
       </c>
       <c r="Y58" t="n">
-        <v>14.69906147428963</v>
+        <v>14.12808538384743</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -7004,7 +7008,7 @@
         <v>46239</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8269327253459947</v>
+        <v>0.8206456478418286</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7064,16 +7068,16 @@
         <v>10.2478061424703</v>
       </c>
       <c r="Y59" t="n">
-        <v>6.105157122995397</v>
+        <v>6.819029166410095</v>
       </c>
       <c r="Z59" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AA59" t="n">
-        <v>50</v>
+        <v>47.61904761904762</v>
       </c>
       <c r="AB59" t="n">
-        <v>15.12318601205643</v>
+        <v>15.37190524642973</v>
       </c>
       <c r="AC59" t="n">
         <v>6</v>
@@ -7113,7 +7117,7 @@
         <v>46239</v>
       </c>
       <c r="C60" t="n">
-        <v>13.20065453831181</v>
+        <v>13.09585621304486</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7141,22 +7145,22 @@
         <v>17.06238107085701</v>
       </c>
       <c r="K60" t="n">
-        <v>3.887711339931132</v>
+        <v>3.062959951078192</v>
       </c>
       <c r="L60" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="M60" t="n">
-        <v>54.54545454545455</v>
+        <v>44.73684210526316</v>
       </c>
       <c r="N60" t="n">
-        <v>11.5632679575326</v>
+        <v>12.9081530423183</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>3.958397588154616</v>
+        <v>4.790314630266135</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7222,7 +7226,7 @@
         <v>46239</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6322861265228771</v>
+        <v>0.6264149361089667</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7239,7 +7243,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H61" t="n">
         <v>5</v>
       </c>
@@ -7250,22 +7258,22 @@
         <v>33.98678515927238</v>
       </c>
       <c r="K61" t="n">
-        <v>2.088633998708445</v>
+        <v>1.140674231508432</v>
       </c>
       <c r="L61" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M61" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N61" t="n">
-        <v>22.27180963266649</v>
+        <v>18.75763562026636</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>7.749507160015146</v>
+        <v>8.759409442152633</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7323,7 +7331,7 @@
         <v>46239</v>
       </c>
       <c r="C62" t="n">
-        <v>8.607751645603003</v>
+        <v>8.418764708385984</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7351,22 +7359,22 @@
         <v>13.30115949155629</v>
       </c>
       <c r="K62" t="n">
-        <v>3.448137854932898</v>
+        <v>1.176888922699315</v>
       </c>
       <c r="L62" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="M62" t="n">
-        <v>56.66666666666666</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="N62" t="n">
-        <v>14.41202482502841</v>
+        <v>13.7063349947116</v>
       </c>
       <c r="O62" t="n">
         <v>6</v>
       </c>
       <c r="P62" t="n">
-        <v>2.466803364450731</v>
+        <v>4.767008680199303</v>
       </c>
       <c r="Q62" t="n">
         <v>29</v>
@@ -7432,7 +7440,7 @@
         <v>46239</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1046803501031941</v>
+        <v>0.1044725563863614</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7449,7 +7457,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H63" t="n">
         <v>5</v>
       </c>
@@ -7460,22 +7472,22 @@
         <v>31.19925725463639</v>
       </c>
       <c r="K63" t="n">
-        <v>4.904291616559742</v>
+        <v>4.696053368930531</v>
       </c>
       <c r="L63" t="n">
         <v>3</v>
       </c>
       <c r="M63" t="n">
-        <v>66.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="N63" t="n">
-        <v>8.912002084757088</v>
+        <v>9.275776345707937</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>0.09123400193205011</v>
+        <v>0.2903133607132347</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7502,7 +7514,7 @@
         <v>10.24796802016521</v>
       </c>
       <c r="Y63" t="n">
-        <v>4.846961354088696</v>
+        <v>5.0358430644447</v>
       </c>
       <c r="Z63" t="n">
         <v>13</v>
@@ -7511,13 +7523,13 @@
         <v>46.15384615384615</v>
       </c>
       <c r="AB63" t="n">
-        <v>12.20765442875811</v>
+        <v>13.43404189779166</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>5.415527154195332</v>
+        <v>5.227400627506318</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7551,7 +7563,7 @@
         <v>46239</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1620653614942838</v>
+        <v>0.1597568313154982</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7579,22 +7591,22 @@
         <v>23.67654789977809</v>
       </c>
       <c r="K64" t="n">
-        <v>3.00250553392889</v>
+        <v>1.535292612406525</v>
       </c>
       <c r="L64" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="M64" t="n">
-        <v>60</v>
+        <v>70.27027027027027</v>
       </c>
       <c r="N64" t="n">
-        <v>18.4981910044989</v>
+        <v>16.01715466355967</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>1.939267841803272</v>
+        <v>3.412318316567431</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7660,7 +7672,7 @@
         <v>46239</v>
       </c>
       <c r="C65" t="n">
-        <v>6.264004860536494</v>
+        <v>6.232618566882508</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7679,7 +7691,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -7692,22 +7704,22 @@
         <v>28.12381406175567</v>
       </c>
       <c r="K65" t="n">
-        <v>3.207567005319145</v>
+        <v>2.690437297175041</v>
       </c>
       <c r="L65" t="n">
         <v>16</v>
       </c>
       <c r="M65" t="n">
-        <v>75</v>
+        <v>81.25</v>
       </c>
       <c r="N65" t="n">
-        <v>15.09819428359337</v>
+        <v>14.72106682780091</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>6.581332349720825</v>
+        <v>7.118055872789686</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7773,7 +7785,7 @@
         <v>46239</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4321742839352609</v>
+        <v>0.4258780897084043</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7872,11 +7884,11 @@
         <v>46239</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02900780774342403</v>
+        <v>0.02837785898800593</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7886,7 +7898,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -7900,7 +7912,7 @@
         <v>18.49825117353735</v>
       </c>
       <c r="K67" t="n">
-        <v>7.736815557078613</v>
+        <v>5.397146407544984</v>
       </c>
       <c r="L67" t="n">
         <v>2</v>
@@ -7925,25 +7937,25 @@
       </c>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="n">
-        <v>10.85961868230363</v>
+        <v>10.86217886339589</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.816898670898549</v>
+        <v>4.929573378297835</v>
       </c>
       <c r="Z67" t="n">
         <v>3</v>
       </c>
       <c r="AA67" t="n">
-        <v>66.66666666666667</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB67" t="n">
-        <v>6.940091115500769</v>
+        <v>5.358269135191785</v>
       </c>
       <c r="AC67" t="n">
         <v>3</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.188408608695656</v>
+        <v>0</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>
@@ -7967,7 +7979,7 @@
         <v>46239</v>
       </c>
       <c r="C68" t="n">
-        <v>3.752096871160283</v>
+        <v>3.865694827759595</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8024,10 +8036,10 @@
         <v>80</v>
       </c>
       <c r="X68" t="n">
-        <v>109.448612884876</v>
+        <v>116.020848317919</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.05599445497443956</v>
+        <v>0.1628681080171002</v>
       </c>
       <c r="Z68" t="n">
         <v>1</v>
@@ -8038,7 +8050,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>7.948456239775902</v>
+        <v>7.849916903123932</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8072,7 +8084,7 @@
         <v>46239</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4094725228248614</v>
+        <v>0.4048574537324093</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8100,7 +8112,7 @@
         <v>29.4573350207784</v>
       </c>
       <c r="K69" t="n">
-        <v>4.741617750765537</v>
+        <v>3.561099459965011</v>
       </c>
       <c r="L69" t="n">
         <v>7</v>
@@ -8109,7 +8121,7 @@
         <v>71.42857142857143</v>
       </c>
       <c r="N69" t="n">
-        <v>12.83128146711089</v>
+        <v>15.74456577461902</v>
       </c>
       <c r="O69" t="n">
         <v>3</v>
@@ -8165,7 +8177,7 @@
         <v>46239</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4183009877327328</v>
+        <v>0.4189412815179769</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8193,7 +8205,7 @@
         <v>20.66985845799666</v>
       </c>
       <c r="K70" t="n">
-        <v>7.304695439275122</v>
+        <v>7.468946855437641</v>
       </c>
       <c r="L70" t="n">
         <v>15</v>
@@ -8208,7 +8220,7 @@
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>0.6479721673674277</v>
+        <v>0.4941456672844513</v>
       </c>
       <c r="Q70" t="n">
         <v>30</v>
@@ -8274,7 +8286,7 @@
         <v>46239</v>
       </c>
       <c r="C71" t="n">
-        <v>3.293857525304879</v>
+        <v>3.264504831184958</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8291,7 +8303,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.67: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H71" t="n">
         <v>5</v>
       </c>
@@ -8302,22 +8318,22 @@
         <v>20.51701021225919</v>
       </c>
       <c r="K71" t="n">
-        <v>5.141286722617</v>
+        <v>4.204336655762386</v>
       </c>
       <c r="L71" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M71" t="n">
-        <v>67.85714285714286</v>
+        <v>76.66666666666667</v>
       </c>
       <c r="N71" t="n">
-        <v>12.35555698952126</v>
+        <v>11.82812245893715</v>
       </c>
       <c r="O71" t="n">
         <v>6</v>
       </c>
       <c r="P71" t="n">
-        <v>0.8167231961393684</v>
+        <v>1.723213641452914</v>
       </c>
       <c r="Q71" t="n">
         <v>43</v>
@@ -8383,7 +8399,7 @@
         <v>46239</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07966636970091651</v>
+        <v>0.07924779720908831</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8400,11 +8416,7 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>5</v>
       </c>
@@ -8415,16 +8427,16 @@
         <v>20.36571476939619</v>
       </c>
       <c r="K72" t="n">
-        <v>11.37850115182233</v>
+        <v>10.79331097762173</v>
       </c>
       <c r="L72" t="n">
         <v>9</v>
       </c>
       <c r="M72" t="n">
-        <v>77.77777777777777</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N72" t="n">
-        <v>15.59377252623562</v>
+        <v>15.39469661418315</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
@@ -8457,7 +8469,7 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>11.30452670718646</v>
+        <v>11.77053871965082</v>
       </c>
       <c r="Z72" t="n">
         <v>2</v>
@@ -8502,7 +8514,7 @@
         <v>46239</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07062770370806086</v>
+        <v>0.06957830381930519</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8527,25 +8539,25 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>21.17049467907518</v>
+        <v>21.46200936158552</v>
       </c>
       <c r="K73" t="n">
-        <v>1.439309973482961</v>
+        <v>0.3030300045913759</v>
       </c>
       <c r="L73" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M73" t="n">
-        <v>69.23076923076923</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N73" t="n">
-        <v>15.58923191844779</v>
+        <v>15.68138501637575</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>8.439223441834208</v>
+        <v>9.667674042314323</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8611,7 +8623,7 @@
         <v>46239</v>
       </c>
       <c r="C74" t="n">
-        <v>4.916613082782068</v>
+        <v>4.927236944547341</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8639,22 +8651,22 @@
         <v>18.35970785011217</v>
       </c>
       <c r="K74" t="n">
-        <v>4.021269982818088</v>
+        <v>4.246040078479196</v>
       </c>
       <c r="L74" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M74" t="n">
-        <v>58.8235294117647</v>
+        <v>60</v>
       </c>
       <c r="N74" t="n">
-        <v>17.52247925077782</v>
+        <v>20.43221953039583</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>3.824919670601123</v>
+        <v>3.601057573692712</v>
       </c>
       <c r="Q74" t="n">
         <v>35</v>
@@ -8681,7 +8693,7 @@
         <v>95.98093909010421</v>
       </c>
       <c r="Y74" t="n">
-        <v>15.07673128800374</v>
+        <v>14.89322832524044</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -8726,7 +8738,7 @@
         <v>46239</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1469308474309697</v>
+        <v>0.143781153228901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8754,13 +8766,17 @@
         <v>19.1703426786477</v>
       </c>
       <c r="K75" t="n">
-        <v>12.75316457247591</v>
+        <v>10.3361228489149</v>
       </c>
       <c r="L75" t="n">
-        <v>2</v>
-      </c>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M75" t="n">
+        <v>20</v>
+      </c>
+      <c r="N75" t="n">
+        <v>9.794958843326418</v>
+      </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
@@ -8792,22 +8808,22 @@
         <v>17.02929186229787</v>
       </c>
       <c r="Y75" t="n">
-        <v>3.653894868349239</v>
+        <v>5.71922542371569</v>
       </c>
       <c r="Z75" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA75" t="n">
-        <v>16.66666666666667</v>
+        <v>50</v>
       </c>
       <c r="AB75" t="n">
-        <v>11.36055095633982</v>
+        <v>14.30215207053015</v>
       </c>
       <c r="AC75" t="n">
         <v>10</v>
       </c>
       <c r="AD75" t="n">
-        <v>6.586779115750674</v>
+        <v>4.540453337939699</v>
       </c>
       <c r="AE75" t="n">
         <v>4</v>
@@ -8841,7 +8857,7 @@
         <v>46239</v>
       </c>
       <c r="C76" t="n">
-        <v>1.859232251037712</v>
+        <v>1.832999392993822</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8869,22 +8885,22 @@
         <v>20.51082830683794</v>
       </c>
       <c r="K76" t="n">
-        <v>7.273600140429193</v>
+        <v>5.760022090795935</v>
       </c>
       <c r="L76" t="n">
         <v>15</v>
       </c>
       <c r="M76" t="n">
-        <v>60</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N76" t="n">
-        <v>10.50856197334631</v>
+        <v>10.23768293434878</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>2.541538510874775</v>
+        <v>4.009055430760045</v>
       </c>
       <c r="Q76" t="n">
         <v>42</v>
@@ -8950,7 +8966,7 @@
         <v>46239</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5402178848202404</v>
+        <v>0.5158464261899016</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8978,16 +8994,16 @@
         <v>21.60005234598619</v>
       </c>
       <c r="K77" t="n">
-        <v>11.26113420434449</v>
+        <v>6.241685190123047</v>
       </c>
       <c r="L77" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M77" t="n">
-        <v>66.66666666666667</v>
+        <v>56.52173913043478</v>
       </c>
       <c r="N77" t="n">
-        <v>19.39952210947289</v>
+        <v>11.93943721732554</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -9017,25 +9033,25 @@
         <v>61.8421052631579</v>
       </c>
       <c r="X77" t="n">
-        <v>12.99282331276559</v>
+        <v>12.99543275787505</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.532565571556499</v>
+        <v>5.977009338265771</v>
       </c>
       <c r="Z77" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="AA77" t="n">
-        <v>48</v>
+        <v>45.09803921568628</v>
       </c>
       <c r="AB77" t="n">
-        <v>10.9975774868655</v>
+        <v>11.43048838845208</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>8.599223162046332</v>
+        <v>4.278730801286368</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9069,7 +9085,7 @@
         <v>46239</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05360138282271081</v>
+        <v>0.05339241453820177</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9097,16 +9113,16 @@
         <v>12.76206508896208</v>
       </c>
       <c r="K78" t="n">
-        <v>5.795475490745328</v>
+        <v>5.383025328867186</v>
       </c>
       <c r="L78" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M78" t="n">
-        <v>64.91228070175438</v>
+        <v>68.85245901639344</v>
       </c>
       <c r="N78" t="n">
-        <v>16.50187791097123</v>
+        <v>15.95590019296373</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
@@ -9139,7 +9155,7 @@
         <v>23.16536029857119</v>
       </c>
       <c r="Y78" t="n">
-        <v>7.706211952560526</v>
+        <v>8.06602495632024</v>
       </c>
       <c r="Z78" t="n">
         <v>18</v>
@@ -9148,13 +9164,13 @@
         <v>50</v>
       </c>
       <c r="AB78" t="n">
-        <v>15.30682573548685</v>
+        <v>14.64916186040179</v>
       </c>
       <c r="AC78" t="n">
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>2.485311412573565</v>
+        <v>2.103656502137419</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9188,7 +9204,7 @@
         <v>46239</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8920951600653764</v>
+        <v>0.8874912765516835</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9216,22 +9232,22 @@
         <v>12.46716859924595</v>
       </c>
       <c r="K79" t="n">
-        <v>3.305140302791032</v>
+        <v>2.772007904353968</v>
       </c>
       <c r="L79" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M79" t="n">
-        <v>51.78571428571428</v>
+        <v>46.55172413793103</v>
       </c>
       <c r="N79" t="n">
-        <v>10.07001107978507</v>
+        <v>10.33790854880191</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>1.640634427523424</v>
+        <v>2.16789779734532</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9297,7 +9313,7 @@
         <v>46239</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1341085627492059</v>
+        <v>0.1324300106426891</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9325,7 +9341,7 @@
         <v>69.28554820223583</v>
       </c>
       <c r="K80" t="n">
-        <v>2.830990191225946</v>
+        <v>1.543919689072548</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9336,7 +9352,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>6.971643271588146</v>
+        <v>8.32751024071159</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9402,11 +9418,11 @@
         <v>46239</v>
       </c>
       <c r="C81" t="n">
-        <v>1.076231723557424</v>
+        <v>1.061542116787746</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9416,7 +9432,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -9430,22 +9446,22 @@
         <v>11.84927434264682</v>
       </c>
       <c r="K81" t="n">
-        <v>2.533177473538051</v>
+        <v>1.133690704133694</v>
       </c>
       <c r="L81" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M81" t="n">
-        <v>48.97959183673469</v>
+        <v>51.92307692307692</v>
       </c>
       <c r="N81" t="n">
-        <v>13.20735979882997</v>
+        <v>12.31903901763035</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>7.282347734116601</v>
+        <v>8.766919543957584</v>
       </c>
       <c r="Q81" t="n">
         <v>31</v>
@@ -9472,7 +9488,7 @@
         <v>27.31228182970742</v>
       </c>
       <c r="Y81" t="n">
-        <v>9.616260017534417</v>
+        <v>10.849917760243</v>
       </c>
       <c r="Z81" t="n">
         <v>9</v>
@@ -9481,13 +9497,13 @@
         <v>55.55555555555556</v>
       </c>
       <c r="AB81" t="n">
-        <v>9.276812191444455</v>
+        <v>9.529724010146259</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.4245674969192703</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9521,7 +9537,7 @@
         <v>46239</v>
       </c>
       <c r="C82" t="n">
-        <v>5.185671073789055</v>
+        <v>5.189994894247278</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9553,7 +9569,7 @@
         <v>12.20498494157071</v>
       </c>
       <c r="K82" t="n">
-        <v>12.93798782592066</v>
+        <v>13.03215569259089</v>
       </c>
       <c r="L82" t="n">
         <v>6</v>
@@ -9595,7 +9611,7 @@
         <v>15.04024401260009</v>
       </c>
       <c r="Y82" t="n">
-        <v>0.8460765815459181</v>
+        <v>0.7634018888225902</v>
       </c>
       <c r="Z82" t="n">
         <v>12</v>
@@ -9610,7 +9626,7 @@
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>3.180835724617526</v>
+        <v>3.261496436578137</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9644,11 +9660,11 @@
         <v>46239</v>
       </c>
       <c r="C83" t="n">
-        <v>5.927682451917086</v>
+        <v>5.901543550260588</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -9672,22 +9688,22 @@
         <v>14.0949513048101</v>
       </c>
       <c r="K83" t="n">
-        <v>9.522605347200685</v>
+        <v>9.039650898551365</v>
       </c>
       <c r="L83" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M83" t="n">
-        <v>56.66666666666666</v>
+        <v>61.29032258064516</v>
       </c>
       <c r="N83" t="n">
-        <v>10.32070616999182</v>
+        <v>10.36209338144422</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>0.4358868667211802</v>
+        <v>0.8807338372186502</v>
       </c>
       <c r="Q83" t="n">
         <v>44</v>
@@ -9714,22 +9730,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.467821951885984</v>
+        <v>1.902312654262805</v>
       </c>
       <c r="Z83" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AA83" t="n">
-        <v>58.33333333333334</v>
+        <v>54.83870967741935</v>
       </c>
       <c r="AB83" t="n">
-        <v>11.66028660720694</v>
+        <v>11.77347530517702</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>4.599693356926426</v>
+        <v>4.17714979487257</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9763,7 +9779,7 @@
         <v>46239</v>
       </c>
       <c r="C84" t="n">
-        <v>2.244952141646015</v>
+        <v>2.215575064031443</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9791,16 +9807,16 @@
         <v>14.10735630446007</v>
       </c>
       <c r="K84" t="n">
-        <v>7.471587154068171</v>
+        <v>6.065231491238099</v>
       </c>
       <c r="L84" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M84" t="n">
-        <v>55.55555555555556</v>
+        <v>64.1025641025641</v>
       </c>
       <c r="N84" t="n">
-        <v>8.92656302190143</v>
+        <v>9.900639794897224</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
@@ -9872,7 +9888,7 @@
         <v>46239</v>
       </c>
       <c r="C85" t="n">
-        <v>6.61083734442526</v>
+        <v>6.568948742498427</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9900,22 +9916,22 @@
         <v>15.13449360257271</v>
       </c>
       <c r="K85" t="n">
-        <v>2.589558277150394</v>
+        <v>1.93951457699113</v>
       </c>
       <c r="L85" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="M85" t="n">
-        <v>54</v>
+        <v>62.06896551724138</v>
       </c>
       <c r="N85" t="n">
-        <v>13.0699515953862</v>
+        <v>14.88449958456434</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>5.273871740662983</v>
+        <v>5.945177832322934</v>
       </c>
       <c r="Q85" t="n">
         <v>34</v>
@@ -9981,7 +9997,7 @@
         <v>46239</v>
       </c>
       <c r="C86" t="n">
-        <v>3.567119482308149</v>
+        <v>3.67650910397564</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10038,25 +10054,25 @@
         <v>68.35443037974683</v>
       </c>
       <c r="X86" t="n">
-        <v>39.94948119773951</v>
+        <v>44.1992982541711</v>
       </c>
       <c r="Y86" t="n">
-        <v>0.2002243828252426</v>
+        <v>0.1712346205608895</v>
       </c>
       <c r="Z86" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA86" t="n">
-        <v>66.66666666666667</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB86" t="n">
-        <v>12.3031665129609</v>
+        <v>13.83837700712544</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>5.811411479943917</v>
+        <v>5.838763363730449</v>
       </c>
       <c r="AE86" t="n">
         <v>51</v>
@@ -10090,7 +10106,7 @@
         <v>46239</v>
       </c>
       <c r="C87" t="n">
-        <v>5.691205758356563</v>
+        <v>5.565213374644667</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10107,11 +10123,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>5</v>
       </c>
@@ -10122,22 +10134,22 @@
         <v>29.54558799520699</v>
       </c>
       <c r="K87" t="n">
-        <v>4.783039206622641</v>
+        <v>2.463343619648861</v>
       </c>
       <c r="L87" t="n">
         <v>6</v>
       </c>
       <c r="M87" t="n">
-        <v>83.33333333333333</v>
+        <v>50</v>
       </c>
       <c r="N87" t="n">
-        <v>9.637889717228306</v>
+        <v>11.43324102704426</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>0.2070571678585598</v>
+        <v>2.475672070362434</v>
       </c>
       <c r="Q87" t="n">
         <v>47</v>
@@ -10203,7 +10215,7 @@
         <v>46239</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9913102962526857</v>
+        <v>0.9829249029228563</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10231,16 +10243,16 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>11.05807829555574</v>
+        <v>10.11864926663959</v>
       </c>
       <c r="L88" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M88" t="n">
-        <v>55.55555555555556</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N88" t="n">
-        <v>9.038376875760038</v>
+        <v>11.37594108580531</v>
       </c>
       <c r="O88" t="n">
         <v>10</v>
@@ -10270,25 +10282,25 @@
         <v>68.35443037974683</v>
       </c>
       <c r="X88" t="n">
-        <v>11.34066630670314</v>
+        <v>11.34323759706175</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.2538048500347334</v>
+        <v>1.099831796569262</v>
       </c>
       <c r="Z88" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="AA88" t="n">
-        <v>33.33333333333334</v>
+        <v>37.33333333333334</v>
       </c>
       <c r="AB88" t="n">
-        <v>10.96607414722795</v>
+        <v>10.63614880233937</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>5.760816381342715</v>
+        <v>4.954661142083639</v>
       </c>
       <c r="AE88" t="n">
         <v>30</v>
@@ -10322,7 +10334,7 @@
         <v>46239</v>
       </c>
       <c r="C89" t="n">
-        <v>2.01688338007806</v>
+        <v>1.984348068295498</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10350,16 +10362,16 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>9.55378789212309</v>
+        <v>7.786523269270718</v>
       </c>
       <c r="L89" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="M89" t="n">
-        <v>65.51724137931035</v>
+        <v>68.57142857142857</v>
       </c>
       <c r="N89" t="n">
-        <v>15.0491963329399</v>
+        <v>16.05252990993683</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
@@ -10392,16 +10404,16 @@
         <v>28.7873334490923</v>
       </c>
       <c r="Y89" t="n">
-        <v>12.04381030018848</v>
+        <v>13.46267372251425</v>
       </c>
       <c r="Z89" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AA89" t="n">
-        <v>36.36363636363637</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB89" t="n">
-        <v>11.78207688325951</v>
+        <v>24.68761358108778</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
@@ -10441,7 +10453,7 @@
         <v>46239</v>
       </c>
       <c r="C90" t="n">
-        <v>2.701089344224629</v>
+        <v>2.682233118375385</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10469,22 +10481,22 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>6.477614397295373</v>
+        <v>5.734297279978562</v>
       </c>
       <c r="L90" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M90" t="n">
-        <v>65.78947368421052</v>
+        <v>64.1025641025641</v>
       </c>
       <c r="N90" t="n">
-        <v>15.61991353247904</v>
+        <v>15.0761275126997</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>1.429770577902145</v>
+        <v>2.14282666864658</v>
       </c>
       <c r="Q90" t="n">
         <v>42</v>
@@ -10511,13 +10523,13 @@
         <v>33.24184775233741</v>
       </c>
       <c r="Y90" t="n">
-        <v>11.18352506483817</v>
+        <v>11.80355028321611</v>
       </c>
       <c r="Z90" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA90" t="n">
-        <v>22.22222222222222</v>
+        <v>25</v>
       </c>
       <c r="AB90" t="n">
         <v>8.158989511032161</v>
@@ -10560,7 +10572,7 @@
         <v>46239</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2358460947198013</v>
+        <v>0.2360617323409309</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10588,7 +10600,7 @@
         <v>14.82331888146111</v>
       </c>
       <c r="K91" t="n">
-        <v>4.020605411976996</v>
+        <v>4.115713011389044</v>
       </c>
       <c r="L91" t="n">
         <v>46</v>
@@ -10597,7 +10609,7 @@
         <v>60.8695652173913</v>
       </c>
       <c r="N91" t="n">
-        <v>14.72533338612546</v>
+        <v>14.67506174697792</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
@@ -10669,7 +10681,7 @@
         <v>46239</v>
       </c>
       <c r="C92" t="n">
-        <v>1.129833091455827</v>
+        <v>1.094124086574855</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10697,22 +10709,22 @@
         <v>22.28274626067631</v>
       </c>
       <c r="K92" t="n">
-        <v>7.230078749510715</v>
+        <v>3.841012316238279</v>
       </c>
       <c r="L92" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M92" t="n">
-        <v>66.66666666666667</v>
+        <v>60</v>
       </c>
       <c r="N92" t="n">
-        <v>12.99255088315147</v>
+        <v>15.19496257703802</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>0.7180086590142576</v>
+        <v>4.005149401949115</v>
       </c>
       <c r="Q92" t="n">
         <v>56</v>
@@ -10778,7 +10790,7 @@
         <v>46239</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04204030107742614</v>
+        <v>0.04183106580243634</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10806,22 +10818,22 @@
         <v>19.1493380128757</v>
       </c>
       <c r="K93" t="n">
-        <v>1.956521275762602</v>
+        <v>1.449081980148414</v>
       </c>
       <c r="L93" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M93" t="n">
-        <v>63.46153846153846</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N93" t="n">
-        <v>13.90414862604118</v>
+        <v>13.82750385948612</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>3.96588533390716</v>
+        <v>4.48591345631113</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10887,11 +10899,11 @@
         <v>46239</v>
       </c>
       <c r="C94" t="n">
-        <v>6.36910561323006</v>
+        <v>6.39027333670247</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -10901,7 +10913,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -10915,22 +10927,22 @@
         <v>12.24049282186025</v>
       </c>
       <c r="K94" t="n">
-        <v>6.991974103368959</v>
+        <v>7.347561945543069</v>
       </c>
       <c r="L94" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="M94" t="n">
-        <v>51.85185185185185</v>
+        <v>54.16666666666666</v>
       </c>
       <c r="N94" t="n">
-        <v>12.90032966927842</v>
+        <v>13.88977423798863</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>0.9421509464412336</v>
+        <v>0.6077809711113158</v>
       </c>
       <c r="Q94" t="n">
         <v>40</v>
@@ -10957,7 +10969,7 @@
         <v>46.65531127586331</v>
       </c>
       <c r="Y94" t="n">
-        <v>6.104370806720483</v>
+        <v>5.792308668843116</v>
       </c>
       <c r="Z94" t="n">
         <v>4</v>
@@ -10972,7 +10984,7 @@
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>0</v>
+        <v>0.2204611197049955</v>
       </c>
       <c r="AE94" t="n">
         <v>37</v>
@@ -11006,7 +11018,7 @@
         <v>46239</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1410452109555707</v>
+        <v>0.1412586693443526</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11034,7 +11046,7 @@
         <v>23.400044414021</v>
       </c>
       <c r="K95" t="n">
-        <v>1.736827772973659</v>
+        <v>1.89079669676111</v>
       </c>
       <c r="L95" t="n">
         <v>26</v>
@@ -11049,7 +11061,7 @@
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>4.190392329255288</v>
+        <v>4.032948447216844</v>
       </c>
       <c r="Q95" t="n">
         <v>22</v>
@@ -11115,7 +11127,7 @@
         <v>46239</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1311657345269349</v>
+        <v>0.130117737952647</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11143,22 +11155,22 @@
         <v>12.79622946674051</v>
       </c>
       <c r="K96" t="n">
-        <v>1.379593253781719</v>
+        <v>0.5695839413965009</v>
       </c>
       <c r="L96" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="M96" t="n">
-        <v>57.97101449275362</v>
+        <v>51.51515151515152</v>
       </c>
       <c r="N96" t="n">
-        <v>12.20935754886504</v>
+        <v>13.79686370311483</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>8.503098571957167</v>
+        <v>9.377006137460775</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11185,16 +11197,16 @@
         <v>16.74415231729489</v>
       </c>
       <c r="Y96" t="n">
-        <v>11.59317213142036</v>
+        <v>12.29953079349081</v>
       </c>
       <c r="Z96" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA96" t="n">
-        <v>40</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB96" t="n">
-        <v>16.42948776937994</v>
+        <v>15.96559934023883</v>
       </c>
       <c r="AC96" t="n">
         <v>8</v>
@@ -11234,7 +11246,7 @@
         <v>46239</v>
       </c>
       <c r="C97" t="n">
-        <v>1.852926302148387</v>
+        <v>1.836152520341587</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11262,22 +11274,22 @@
         <v>22.80838616541501</v>
       </c>
       <c r="K97" t="n">
-        <v>3.670897342965151</v>
+        <v>2.732407231550682</v>
       </c>
       <c r="L97" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M97" t="n">
-        <v>56</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N97" t="n">
-        <v>12.77160703742497</v>
+        <v>11.66515273636023</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>0.3174494148981077</v>
+        <v>1.233878191515814</v>
       </c>
       <c r="Q97" t="n">
         <v>50</v>
@@ -11343,7 +11355,7 @@
         <v>46239</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6507838413400181</v>
+        <v>0.6524805600338689</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11362,7 +11374,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H98" t="n">
@@ -11375,22 +11387,22 @@
         <v>18.49937747698907</v>
       </c>
       <c r="K98" t="n">
-        <v>8.391104684157868</v>
+        <v>8.67370114996142</v>
       </c>
       <c r="L98" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M98" t="n">
-        <v>76.47058823529412</v>
+        <v>81.25</v>
       </c>
       <c r="N98" t="n">
-        <v>15.64875646702917</v>
+        <v>14.7580406367084</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>1.484342576386055</v>
+        <v>1.220441409470729</v>
       </c>
       <c r="Q98" t="n">
         <v>48</v>
@@ -11456,7 +11468,7 @@
         <v>46239</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4809410266688286</v>
+        <v>0.4742255364775094</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11484,22 +11496,22 @@
         <v>28.77817890954801</v>
       </c>
       <c r="K99" t="n">
-        <v>3.466359430119437</v>
+        <v>2.021634851937604</v>
       </c>
       <c r="L99" t="n">
         <v>20</v>
       </c>
       <c r="M99" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="N99" t="n">
-        <v>13.15966388936777</v>
+        <v>14.39545434204168</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>0.5157623915829301</v>
+        <v>1.939162365838931</v>
       </c>
       <c r="Q99" t="n">
         <v>35</v>
@@ -11565,7 +11577,7 @@
         <v>46239</v>
       </c>
       <c r="C100" t="n">
-        <v>329.3454018946936</v>
+        <v>325.7078159960379</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11593,16 +11605,16 @@
         <v>25.19597156501795</v>
       </c>
       <c r="K100" t="n">
-        <v>7.458650755690122</v>
+        <v>6.271781072892924</v>
       </c>
       <c r="L100" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M100" t="n">
-        <v>61.53846153846154</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N100" t="n">
-        <v>11.81400718384301</v>
+        <v>11.56873670362326</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11674,7 +11686,7 @@
         <v>46239</v>
       </c>
       <c r="C101" t="n">
-        <v>326.9648698461843</v>
+        <v>324.6519601254528</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11702,16 +11714,16 @@
         <v>13.42090796247281</v>
       </c>
       <c r="K101" t="n">
-        <v>3.539652700288376</v>
+        <v>2.807225790558499</v>
       </c>
       <c r="L101" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M101" t="n">
-        <v>34.28571428571428</v>
+        <v>43.24324324324324</v>
       </c>
       <c r="N101" t="n">
-        <v>8.303444048838744</v>
+        <v>9.868345659223998</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11783,7 +11795,7 @@
         <v>46239</v>
       </c>
       <c r="C102" t="n">
-        <v>393.6120078130411</v>
+        <v>392.719509634993</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11882,7 +11894,7 @@
         <v>46239</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7285584145187723</v>
+        <v>0.7172240770088678</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11910,7 +11922,7 @@
         <v>30.74202968074841</v>
       </c>
       <c r="K103" t="n">
-        <v>12.05107654108153</v>
+        <v>10.30787421913231</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
@@ -11952,22 +11964,22 @@
         <v>14.26498323563516</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.937519817412625</v>
+        <v>3.463098584054036</v>
       </c>
       <c r="Z103" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="AA103" t="n">
-        <v>37.28813559322034</v>
+        <v>43.75</v>
       </c>
       <c r="AB103" t="n">
-        <v>10.95547504091795</v>
+        <v>11.07527294839242</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>6.182262748504153</v>
+        <v>4.699655105354927</v>
       </c>
       <c r="AE103" t="n">
         <v>34</v>
@@ -12001,7 +12013,7 @@
         <v>46239</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04918715036877503</v>
+        <v>0.04855766784331022</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12020,7 +12032,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.19: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -12033,22 +12045,22 @@
         <v>27.71454389191555</v>
       </c>
       <c r="K104" t="n">
-        <v>1.667705418156329</v>
+        <v>0.36659235336165</v>
       </c>
       <c r="L104" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M104" t="n">
-        <v>76.19047619047619</v>
+        <v>75</v>
       </c>
       <c r="N104" t="n">
-        <v>15.96576789787374</v>
+        <v>14.95533509217345</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>2.294036805739852</v>
+        <v>3.620136503036964</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>

--- a/TDA_Result.xlsx
+++ b/TDA_Result.xlsx
@@ -679,7 +679,7 @@
         <v>46239</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4439558494703479</v>
+        <v>0.4490007972698404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -739,22 +739,22 @@
         <v>14.94856954517825</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.789610109909427</v>
+        <v>5.730402191088535</v>
       </c>
       <c r="Z2" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="AA2" t="n">
-        <v>44.44444444444444</v>
+        <v>54.83870967741935</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.81015745570964</v>
+        <v>11.90075437420743</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.298556836333165</v>
+        <v>2.407560721232771</v>
       </c>
       <c r="AE2" t="n">
         <v>43</v>
@@ -788,7 +788,7 @@
         <v>46239</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7399264023307063</v>
+        <v>0.7386651353738752</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,22 +848,22 @@
         <v>12.13279917920569</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.746309263896429</v>
+        <v>2.912086381957002</v>
       </c>
       <c r="Z3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA3" t="n">
-        <v>42.10526315789474</v>
+        <v>43.10344827586207</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.88232327535781</v>
+        <v>10.88608479467795</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>7.458524896280128</v>
+        <v>7.300510798828997</v>
       </c>
       <c r="AE3" t="n">
         <v>38</v>
@@ -897,7 +897,7 @@
         <v>46239</v>
       </c>
       <c r="C4" t="n">
-        <v>1.406280578955636</v>
+        <v>1.42309699146192</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         <v>27.63389482946404</v>
       </c>
       <c r="K4" t="n">
-        <v>8.883941230749404</v>
+        <v>10.18598386608609</v>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>53.84615384615385</v>
+        <v>50</v>
       </c>
       <c r="N4" t="n">
-        <v>21.3980670392144</v>
+        <v>15.39789546009553</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -967,22 +967,22 @@
         <v>11.23805603488277</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.116285458454203</v>
+        <v>0.9457843891723217</v>
       </c>
       <c r="Z4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AA4" t="n">
-        <v>33.92857142857143</v>
+        <v>35.08771929824562</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.48867500196019</v>
+        <v>12.49205119447462</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>8.054163635361045</v>
+        <v>9.140666608678849</v>
       </c>
       <c r="AE4" t="n">
         <v>45</v>
@@ -1125,7 +1125,7 @@
         <v>46239</v>
       </c>
       <c r="C6" t="n">
-        <v>1.96437836784379</v>
+        <v>1.984348068295498</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,11 +1142,7 @@
           <t>SATMA_BEKLE</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>5</v>
       </c>
@@ -1157,16 +1153,16 @@
         <v>23.73506360720576</v>
       </c>
       <c r="K6" t="n">
-        <v>3.462556177157428</v>
+        <v>4.51434756757767</v>
       </c>
       <c r="L6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M6" t="n">
-        <v>75</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N6" t="n">
-        <v>13.29868132789301</v>
+        <v>10.35125690414793</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
@@ -1199,7 +1195,7 @@
         <v>44.49622708587002</v>
       </c>
       <c r="Y6" t="n">
-        <v>21.09434734113188</v>
+        <v>20.29219930624301</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1244,7 +1240,7 @@
         <v>46239</v>
       </c>
       <c r="C7" t="n">
-        <v>2.139900806469227</v>
+        <v>2.133594551563489</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,22 +1268,22 @@
         <v>11.35312764557068</v>
       </c>
       <c r="K7" t="n">
-        <v>2.519700028710981</v>
+        <v>2.217576042736313</v>
       </c>
       <c r="L7" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M7" t="n">
-        <v>57.97101449275362</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N7" t="n">
-        <v>12.62976515663752</v>
+        <v>12.84328933954645</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0.468495295201321</v>
+        <v>0.7654495318266674</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1314,7 +1310,7 @@
         <v>13.79329344082609</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.119492377404747</v>
+        <v>9.387315841603815</v>
       </c>
       <c r="Z7" t="n">
         <v>18</v>
@@ -1323,13 +1319,13 @@
         <v>61.11111111111111</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.904398401892783</v>
+        <v>7.649714189658804</v>
       </c>
       <c r="AC7" t="n">
         <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.9688630110339935</v>
+        <v>0.6761571672738165</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1363,7 +1359,7 @@
         <v>46239</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3253994352389095</v>
+        <v>0.3279219292133632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,22 +1387,22 @@
         <v>22.10694516187944</v>
       </c>
       <c r="K8" t="n">
-        <v>3.460034567173276</v>
+        <v>4.262055976954926</v>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N8" t="n">
-        <v>17.67912674615781</v>
+        <v>15.15378575494074</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>4.388134463534388</v>
+        <v>3.585143212475383</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1472,7 +1468,7 @@
         <v>46239</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5860553133534054</v>
+        <v>0.5889982297168715</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,16 +1496,16 @@
         <v>10.57037035785485</v>
       </c>
       <c r="K9" t="n">
-        <v>5.44866763852212</v>
+        <v>5.978185249621681</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M9" t="n">
-        <v>41.93548387096774</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="N9" t="n">
-        <v>15.37109919094065</v>
+        <v>15.119494275747</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1581,7 +1577,7 @@
         <v>46239</v>
       </c>
       <c r="C10" t="n">
-        <v>2.039001689671512</v>
+        <v>2.054767166653508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,22 +1605,22 @@
         <v>10.23694539327734</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9605305839936351</v>
+        <v>1.74115324314823</v>
       </c>
       <c r="L10" t="n">
         <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>39.53488372093023</v>
+        <v>32.55813953488372</v>
       </c>
       <c r="N10" t="n">
-        <v>9.844583527866305</v>
+        <v>10.57138966011085</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>8.953468611663084</v>
+        <v>8.117508494438042</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1690,7 +1686,7 @@
         <v>46239</v>
       </c>
       <c r="C11" t="n">
-        <v>7.362477750592237</v>
+        <v>7.257374570712263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,11 +1703,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>5</v>
       </c>
@@ -1722,16 +1714,16 @@
         <v>20.56423081971027</v>
       </c>
       <c r="K11" t="n">
-        <v>5.491710791917348</v>
+        <v>3.985762029720119</v>
       </c>
       <c r="L11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M11" t="n">
-        <v>81.25</v>
+        <v>60</v>
       </c>
       <c r="N11" t="n">
-        <v>14.41611962980027</v>
+        <v>12.93461603959566</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1803,7 +1795,7 @@
         <v>46239</v>
       </c>
       <c r="C12" t="n">
-        <v>6.458590403624454</v>
+        <v>6.568948742498427</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,17 +1823,13 @@
         <v>20.08266526523165</v>
       </c>
       <c r="K12" t="n">
-        <v>12.44216083761243</v>
+        <v>14.36346708463427</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M12" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N12" t="n">
-        <v>22.33927009741701</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
         <v>6</v>
       </c>
@@ -1870,25 +1858,25 @@
         <v>70.58823529411765</v>
       </c>
       <c r="X12" t="n">
-        <v>14.27197631096657</v>
+        <v>14.91241172664053</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.601281024819856</v>
+        <v>0.4777070063694433</v>
       </c>
       <c r="Z12" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>34.48275862068966</v>
+        <v>37.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>13.8766589463101</v>
+        <v>12.17051868934601</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.4052074857607835</v>
+        <v>1.529599999999987</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -1922,16 +1910,16 @@
         <v>46239</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3010155006598508</v>
+        <v>0.2951297282621439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1950,10 +1938,10 @@
         <v>38.11781916800814</v>
       </c>
       <c r="K13" t="n">
-        <v>5.778337803013289</v>
+        <v>3.710048231374863</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1961,7 +1949,7 @@
         <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.243805967332401</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1986,7 +1974,7 @@
         <v>35.74308703619145</v>
       </c>
       <c r="Y13" t="n">
-        <v>22.07460423026113</v>
+        <v>23.59828371685405</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2021,7 +2009,7 @@
         <v>46239</v>
       </c>
       <c r="C14" t="n">
-        <v>8.050903578806073</v>
+        <v>8.008862306854082</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,16 +2069,16 @@
         <v>14.33662537827827</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.957390072258685</v>
+        <v>7.443252265092848</v>
       </c>
       <c r="Z14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA14" t="n">
-        <v>41.66666666666666</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.99649109428192</v>
+        <v>11.35075679918107</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2130,7 +2118,7 @@
         <v>46239</v>
       </c>
       <c r="C15" t="n">
-        <v>11.92921091637714</v>
+        <v>12.14992759412509</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2158,16 +2146,16 @@
         <v>16.27559902090345</v>
       </c>
       <c r="K15" t="n">
-        <v>12.31996418313284</v>
+        <v>14.39813092132296</v>
       </c>
       <c r="L15" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M15" t="n">
-        <v>73.33333333333333</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N15" t="n">
-        <v>15.44994071782585</v>
+        <v>29.7049020069249</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
@@ -2197,25 +2185,25 @@
         <v>79.56989247311827</v>
       </c>
       <c r="X15" t="n">
-        <v>13.30956739179481</v>
+        <v>14.79397220478775</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.8733624454148381</v>
+        <v>0.3448275862069083</v>
       </c>
       <c r="Z15" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="AA15" t="n">
-        <v>35.29411764705883</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="AB15" t="n">
-        <v>12.48497716224804</v>
+        <v>13.76180696936258</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>9.207048458149792</v>
+        <v>9.688581314878874</v>
       </c>
       <c r="AE15" t="n">
         <v>31</v>
@@ -2249,7 +2237,7 @@
         <v>46239</v>
       </c>
       <c r="C16" t="n">
-        <v>36.89121613787117</v>
+        <v>37.33264949336706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2277,22 +2265,22 @@
         <v>17.40096492560246</v>
       </c>
       <c r="K16" t="n">
-        <v>6.334005696757372</v>
+        <v>7.60637841449634</v>
       </c>
       <c r="L16" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M16" t="n">
-        <v>59.375</v>
+        <v>72.41379310344827</v>
       </c>
       <c r="N16" t="n">
-        <v>16.65046628003577</v>
+        <v>16.39294235019948</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>3.447621745481211</v>
+        <v>2.224423515382634</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2358,7 +2346,7 @@
         <v>46239</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7546408636997923</v>
+        <v>0.7474938441046524</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2375,11 +2363,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>5</v>
       </c>
@@ -2390,22 +2374,22 @@
         <v>14.16674936134154</v>
       </c>
       <c r="K17" t="n">
-        <v>7.177523841824107</v>
+        <v>6.162471649579149</v>
       </c>
       <c r="L17" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M17" t="n">
-        <v>78.57142857142857</v>
+        <v>72.34042553191489</v>
       </c>
       <c r="N17" t="n">
-        <v>15.89076158887889</v>
+        <v>16.34482177016434</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7673961187886214</v>
+        <v>1.730864326978154</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2432,22 +2416,22 @@
         <v>15.7396793517258</v>
       </c>
       <c r="Y17" t="n">
-        <v>7.397770201074971</v>
+        <v>8.274783337736825</v>
       </c>
       <c r="Z17" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="AA17" t="n">
-        <v>51.61290322580645</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="AB17" t="n">
-        <v>11.32757773766146</v>
+        <v>10.53365232663279</v>
       </c>
       <c r="AC17" t="n">
         <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.810115700858895</v>
+        <v>1.880853188513587</v>
       </c>
       <c r="AE17" t="n">
         <v>35</v>
@@ -2481,7 +2465,7 @@
         <v>46239</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1036317317881471</v>
+        <v>0.1027909071899327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,22 +2493,22 @@
         <v>25.10069993473878</v>
       </c>
       <c r="K18" t="n">
-        <v>3.706127546644944</v>
+        <v>2.864699332311571</v>
       </c>
       <c r="L18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M18" t="n">
-        <v>47.05882352941177</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="N18" t="n">
-        <v>21.58793351449615</v>
+        <v>18.59536970979411</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>6.068949446139715</v>
+        <v>6.936588269837207</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2590,7 +2574,7 @@
         <v>46239</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02522476422222576</v>
+        <v>0.02501455807267217</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2618,22 +2602,22 @@
         <v>22.96673379938283</v>
       </c>
       <c r="K19" t="n">
-        <v>2.127718350769725</v>
+        <v>1.276654917705256</v>
       </c>
       <c r="L19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M19" t="n">
-        <v>63.63636363636363</v>
+        <v>56.52173913043478</v>
       </c>
       <c r="N19" t="n">
-        <v>19.55780077327282</v>
+        <v>23.20016366411376</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>7.708271345289441</v>
+        <v>8.61338191845209</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2699,7 +2683,7 @@
         <v>46239</v>
       </c>
       <c r="C20" t="n">
-        <v>1.842458775457532</v>
+        <v>1.8351015848173</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,16 +2743,16 @@
         <v>20.34011802710127</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.99484762819107</v>
+        <v>7.366229960125881</v>
       </c>
       <c r="Z20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA20" t="n">
-        <v>36.8421052631579</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB20" t="n">
-        <v>13.07751158256018</v>
+        <v>12.96967327390692</v>
       </c>
       <c r="AC20" t="n">
         <v>4</v>
@@ -2808,7 +2792,7 @@
         <v>46239</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9383611771458275</v>
+        <v>0.9387815995348399</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,25 +2817,25 @@
         <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>13.7580634602656</v>
+        <v>13.9640994031937</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3003397497881588</v>
+        <v>0.5855817816229791</v>
       </c>
       <c r="L21" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M21" t="n">
-        <v>57.6271186440678</v>
+        <v>62.06896551724138</v>
       </c>
       <c r="N21" t="n">
-        <v>18.00456263135702</v>
+        <v>17.35617357110112</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>7.676604355897121</v>
+        <v>7.371253500799102</v>
       </c>
       <c r="Q21" t="n">
         <v>41</v>
@@ -2917,7 +2901,7 @@
         <v>46239</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3111054164386464</v>
+        <v>0.3209851210229357</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2931,7 +2915,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2945,22 +2929,22 @@
         <v>20.35908649698318</v>
       </c>
       <c r="K22" t="n">
-        <v>4.88099245142164</v>
+        <v>8.211674487719378</v>
       </c>
       <c r="L22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>66.66666666666667</v>
+        <v>60</v>
       </c>
       <c r="N22" t="n">
-        <v>15.52421149080303</v>
+        <v>13.06017923872908</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>4.880777182719132</v>
+        <v>1.652617909062659</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -2987,22 +2971,22 @@
         <v>13.73917753549452</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.788156443551319</v>
+        <v>4.859805712987675</v>
       </c>
       <c r="Z22" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AA22" t="n">
-        <v>65</v>
+        <v>37.93103448275862</v>
       </c>
       <c r="AB22" t="n">
-        <v>12.96035064914134</v>
+        <v>15.47656683121236</v>
       </c>
       <c r="AC22" t="n">
         <v>6</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.198435945561216</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3028,21 +3012,21 @@
         <v>46239</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8492337255917697</v>
+        <v>0.8820258662137638</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -3052,12 +3036,8 @@
       <c r="I23" t="n">
         <v>10</v>
       </c>
-      <c r="J23" t="n">
-        <v>23.56853924970225</v>
-      </c>
-      <c r="K23" t="n">
-        <v>21.95638170666532</v>
-      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
         <v>0</v>
       </c>
@@ -3066,9 +3046,7 @@
       <c r="O23" t="n">
         <v>5</v>
       </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="n">
         <v>6</v>
       </c>
@@ -3091,25 +3069,25 @@
         <v>87.5</v>
       </c>
       <c r="X23" t="n">
-        <v>27.6919469835746</v>
+        <v>35.78212339899063</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.49172043531224</v>
+        <v>6.714096244741762</v>
       </c>
       <c r="Z23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA23" t="n">
-        <v>42.85714285714285</v>
+        <v>20</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.8066042688297</v>
+        <v>18.16924423655518</v>
       </c>
       <c r="AC23" t="n">
         <v>6</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.57921341643078</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>10</v>
@@ -3143,7 +3121,7 @@
         <v>46239</v>
       </c>
       <c r="C24" t="n">
-        <v>0.182038704399021</v>
+        <v>0.1830897401917416</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,7 +3149,7 @@
         <v>23.26504282616538</v>
       </c>
       <c r="K24" t="n">
-        <v>4.002959431807995</v>
+        <v>4.603440704582229</v>
       </c>
       <c r="L24" t="n">
         <v>11</v>
@@ -3180,13 +3158,13 @@
         <v>54.54545454545455</v>
       </c>
       <c r="N24" t="n">
-        <v>12.73592039462029</v>
+        <v>12.45279767872284</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>5.766221077703193</v>
+        <v>5.159064806155444</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3252,7 +3230,7 @@
         <v>46239</v>
       </c>
       <c r="C25" t="n">
-        <v>3.987614580533306</v>
+        <v>4.017043663238518</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3351,7 +3329,7 @@
         <v>46239</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4342863361109606</v>
+        <v>0.4435354270813355</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3450,7 +3428,7 @@
         <v>46239</v>
       </c>
       <c r="C27" t="n">
-        <v>33.21260484207205</v>
+        <v>33.65403819756794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,10 +3453,10 @@
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>60.77982296475879</v>
+        <v>61.00365403217616</v>
       </c>
       <c r="K27" t="n">
-        <v>0.190234622701313</v>
+        <v>2.104591836734704</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3489,7 +3467,7 @@
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>7.794936708860778</v>
+        <v>5.773891317926294</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -3535,7 +3513,7 @@
         <v>46239</v>
       </c>
       <c r="C28" t="n">
-        <v>1.457781072773678</v>
+        <v>1.451474978255392</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3563,16 +3541,16 @@
         <v>24.87361787048376</v>
       </c>
       <c r="K28" t="n">
-        <v>4.549467689572051</v>
+        <v>4.097205798263182</v>
       </c>
       <c r="L28" t="n">
         <v>18</v>
       </c>
       <c r="M28" t="n">
-        <v>55.55555555555556</v>
+        <v>50</v>
       </c>
       <c r="N28" t="n">
-        <v>12.16006990667934</v>
+        <v>13.27856956737638</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
@@ -3644,7 +3622,7 @@
         <v>46239</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3678611295799119</v>
+        <v>0.3663896915779895</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3669,25 +3647,25 @@
         <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>20.06506691394495</v>
+        <v>20.6615924080966</v>
       </c>
       <c r="K29" t="n">
-        <v>0.459241788935727</v>
+        <v>0.809713028054615</v>
       </c>
       <c r="L29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M29" t="n">
         <v>50</v>
       </c>
       <c r="N29" t="n">
-        <v>16.83864030684587</v>
+        <v>19.30413149999403</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>3.524571904000018</v>
+        <v>3.164662289096642</v>
       </c>
       <c r="Q29" t="n">
         <v>6</v>
@@ -3714,7 +3692,7 @@
         <v>55.05052857749912</v>
       </c>
       <c r="Y29" t="n">
-        <v>19.69797229725598</v>
+        <v>20.01917898557388</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3759,7 +3737,7 @@
         <v>46239</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3817347461709732</v>
+        <v>0.3840470289509206</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3787,22 +3765,22 @@
         <v>21.6314445059014</v>
       </c>
       <c r="K30" t="n">
-        <v>3.262730155130922</v>
+        <v>3.888223734489604</v>
       </c>
       <c r="L30" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M30" t="n">
         <v>50</v>
       </c>
       <c r="N30" t="n">
-        <v>12.13088844184501</v>
+        <v>11.96636906909726</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>1.682378378200133</v>
+        <v>1.070165823945368</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3868,7 +3846,7 @@
         <v>46239</v>
       </c>
       <c r="C31" t="n">
-        <v>0.182038704399021</v>
+        <v>0.1786754057959572</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3885,7 +3863,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H31" t="n">
         <v>5</v>
       </c>
@@ -3893,25 +3875,25 @@
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>27.96470403013798</v>
+        <v>30.04424494288587</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1.070156380561649</v>
       </c>
       <c r="L31" t="n">
         <v>4</v>
       </c>
       <c r="M31" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="N31" t="n">
-        <v>12.88221960224227</v>
+        <v>7.316462366850085</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>10.00000000000001</v>
+        <v>8.835292176470588</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3977,7 +3959,7 @@
         <v>46239</v>
       </c>
       <c r="C32" t="n">
-        <v>2.329086530253182</v>
+        <v>2.326984338429703</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4037,7 +4019,7 @@
         <v>12.36180984775317</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.644223186657467</v>
+        <v>1.732997350744203</v>
       </c>
       <c r="Z32" t="n">
         <v>52</v>
@@ -4046,13 +4028,13 @@
         <v>40.38461538461539</v>
       </c>
       <c r="AB32" t="n">
-        <v>11.37486641220681</v>
+        <v>11.3712490544558</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>6.462026958929301</v>
+        <v>6.377524988346894</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4086,7 +4068,7 @@
         <v>46239</v>
       </c>
       <c r="C33" t="n">
-        <v>1.808825789847307</v>
+        <v>1.827744233999823</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4114,22 +4096,22 @@
         <v>12.57251846431013</v>
       </c>
       <c r="K33" t="n">
-        <v>1.382604549574773</v>
+        <v>2.442961579518288</v>
       </c>
       <c r="L33" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M33" t="n">
-        <v>62.5</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N33" t="n">
-        <v>12.27595981318721</v>
+        <v>11.15523360823073</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>2.581700738557524</v>
+        <v>1.519907660296527</v>
       </c>
       <c r="Q33" t="n">
         <v>39</v>
@@ -4195,7 +4177,7 @@
         <v>46239</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8782421454318938</v>
+        <v>0.8816054440349576</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4223,22 +4205,22 @@
         <v>10.37797163438468</v>
       </c>
       <c r="K34" t="n">
-        <v>2.583861479551985</v>
+        <v>2.976714589375562</v>
       </c>
       <c r="L34" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M34" t="n">
-        <v>38.63636363636363</v>
+        <v>39.53488372093023</v>
       </c>
       <c r="N34" t="n">
-        <v>10.5823400077803</v>
+        <v>9.237561190015192</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>1.380469110855498</v>
+        <v>0.9937056301561276</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4265,16 +4247,16 @@
         <v>14.68007915548277</v>
       </c>
       <c r="Y34" t="n">
-        <v>8.062262566252388</v>
+        <v>7.710179640731085</v>
       </c>
       <c r="Z34" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA34" t="n">
-        <v>45.83333333333334</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="AB34" t="n">
-        <v>11.68963248252191</v>
+        <v>11.78261791778148</v>
       </c>
       <c r="AC34" t="n">
         <v>2</v>
@@ -4314,7 +4296,7 @@
         <v>46239</v>
       </c>
       <c r="C35" t="n">
-        <v>1.928643350797538</v>
+        <v>1.927592254885799</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4346,7 +4328,7 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>8.727752474524554</v>
+        <v>8.668496678956483</v>
       </c>
       <c r="L35" t="n">
         <v>9</v>
@@ -4388,7 +4370,7 @@
         <v>42.52272358489104</v>
       </c>
       <c r="Y35" t="n">
-        <v>16.18090927744868</v>
+        <v>16.22659004240077</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -4542,7 +4524,7 @@
         <v>46239</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06348232022709209</v>
+        <v>0.0630619079279849</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4570,22 +4552,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>3.338499168809506</v>
+        <v>2.65413892699049</v>
       </c>
       <c r="L37" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M37" t="n">
-        <v>52.94117647058823</v>
+        <v>54.92957746478874</v>
       </c>
       <c r="N37" t="n">
-        <v>18.6341788687826</v>
+        <v>18.92950685343615</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>4.51090432770429</v>
+        <v>5.207642993149642</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4651,7 +4633,7 @@
         <v>46239</v>
       </c>
       <c r="C38" t="n">
-        <v>1.691110100155856</v>
+        <v>1.695314323625567</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4679,16 +4661,16 @@
         <v>16.52414407302303</v>
       </c>
       <c r="K38" t="n">
-        <v>6.739098346106975</v>
+        <v>7.004459556096343</v>
       </c>
       <c r="L38" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M38" t="n">
-        <v>70.37037037037037</v>
+        <v>68.96551724137932</v>
       </c>
       <c r="N38" t="n">
-        <v>12.39457352361738</v>
+        <v>12.47729186589563</v>
       </c>
       <c r="O38" t="n">
         <v>6</v>
@@ -4760,7 +4742,7 @@
         <v>46239</v>
       </c>
       <c r="C39" t="n">
-        <v>2.703253914738832</v>
+        <v>2.720070167067869</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4788,16 +4770,16 @@
         <v>18.47027414490581</v>
       </c>
       <c r="K39" t="n">
-        <v>7.006954565452195</v>
+        <v>7.672617505630819</v>
       </c>
       <c r="L39" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M39" t="n">
-        <v>63.1578947368421</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="N39" t="n">
-        <v>14.42261750646456</v>
+        <v>13.85968245525438</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4830,22 +4812,22 @@
         <v>10.2437411865161</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.93602755696375</v>
+        <v>2.332217369633105</v>
       </c>
       <c r="Z39" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AA39" t="n">
-        <v>38.63636363636363</v>
+        <v>38.29787234042553</v>
       </c>
       <c r="AB39" t="n">
-        <v>13.78517180818355</v>
+        <v>11.65613829774405</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.156652634255619</v>
+        <v>3.755365926805132</v>
       </c>
       <c r="AE39" t="n">
         <v>42</v>
@@ -4879,7 +4861,7 @@
         <v>46239</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1952817073761678</v>
+        <v>0.197593970186511</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4896,11 +4878,7 @@
           <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>5</v>
       </c>
@@ -4911,16 +4889,16 @@
         <v>14.73965458840789</v>
       </c>
       <c r="K40" t="n">
-        <v>6.651029477848258</v>
+        <v>7.91384724229669</v>
       </c>
       <c r="L40" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M40" t="n">
-        <v>77.77777777777777</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N40" t="n">
-        <v>11.36182252967595</v>
+        <v>11.52432638961163</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4953,16 +4931,16 @@
         <v>14.17330472629232</v>
       </c>
       <c r="Y40" t="n">
-        <v>6.588471154861653</v>
+        <v>5.482417714895282</v>
       </c>
       <c r="Z40" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA40" t="n">
-        <v>34.78260869565217</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB40" t="n">
-        <v>12.33129410895796</v>
+        <v>11.6504965019866</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
@@ -5002,7 +4980,7 @@
         <v>46239</v>
       </c>
       <c r="C41" t="n">
-        <v>1.715283863479616</v>
+        <v>1.72684527758956</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5021,7 +4999,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -5034,16 +5012,16 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>13.35562734384286</v>
+        <v>14.11967076389578</v>
       </c>
       <c r="L41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N41" t="n">
-        <v>12.17975430538131</v>
+        <v>8.290318992161135</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
@@ -5076,7 +5054,7 @@
         <v>40.81782021738603</v>
       </c>
       <c r="Y41" t="n">
-        <v>12.03465163672595</v>
+        <v>11.4417446308324</v>
       </c>
       <c r="Z41" t="n">
         <v>6</v>
@@ -5125,11 +5103,11 @@
         <v>46239</v>
       </c>
       <c r="C42" t="n">
-        <v>3.193034476527756</v>
+        <v>3.38011832905293</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5139,14 +5117,10 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BAND</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>5</v>
       </c>
@@ -5157,16 +5131,16 @@
         <v>21.11518617286606</v>
       </c>
       <c r="K42" t="n">
-        <v>3.886032774935066</v>
+        <v>9.97284435744772</v>
       </c>
       <c r="L42" t="n">
         <v>6</v>
       </c>
       <c r="M42" t="n">
-        <v>83.33333333333333</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="N42" t="n">
-        <v>12.69257812864195</v>
+        <v>22.80470238649248</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
@@ -5193,17 +5167,27 @@
         <v>0</v>
       </c>
       <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
+      <c r="X42" t="n">
+        <v>14.965394631075</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>4.342654839439664</v>
+      </c>
       <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>36.36363636363637</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>12.02158046138136</v>
+      </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
-      <c r="AD42" t="inlineStr"/>
+      <c r="AD42" t="n">
+        <v>5.91417747488655</v>
+      </c>
       <c r="AE42" t="n">
         <v>1</v>
       </c>
@@ -5234,7 +5218,7 @@
         <v>46239</v>
       </c>
       <c r="C43" t="n">
-        <v>7.104974959886299</v>
+        <v>7.120740436868295</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5294,16 +5278,16 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>8.293768311945316</v>
+        <v>8.090278152874186</v>
       </c>
       <c r="Z43" t="n">
         <v>8</v>
       </c>
       <c r="AA43" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="AB43" t="n">
-        <v>15.48463828947013</v>
+        <v>13.63280086769262</v>
       </c>
       <c r="AC43" t="n">
         <v>2</v>
@@ -5343,7 +5327,7 @@
         <v>46239</v>
       </c>
       <c r="C44" t="n">
-        <v>5.078585780026263</v>
+        <v>5.028136061345057</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5360,11 +5344,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.27: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>5</v>
       </c>
@@ -5375,22 +5355,22 @@
         <v>13.03201987649729</v>
       </c>
       <c r="K44" t="n">
-        <v>3.945170975101076</v>
+        <v>2.912599140912886</v>
       </c>
       <c r="L44" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M44" t="n">
-        <v>77.27272727272727</v>
+        <v>70.83333333333333</v>
       </c>
       <c r="N44" t="n">
-        <v>20.4740028993714</v>
+        <v>17.94687033846331</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>5.825021949648157</v>
+        <v>6.886815529148871</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5417,22 +5397,22 @@
         <v>12.1234692799834</v>
       </c>
       <c r="Y44" t="n">
-        <v>7.294011108825305</v>
+        <v>8.214935016031344</v>
       </c>
       <c r="Z44" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AA44" t="n">
-        <v>18.18181818181818</v>
+        <v>14.28571428571429</v>
       </c>
       <c r="AB44" t="n">
-        <v>8.772956734278921</v>
+        <v>9.691917834769438</v>
       </c>
       <c r="AC44" t="n">
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.918893292159563</v>
+        <v>1.944831639309119</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5458,7 +5438,7 @@
         <v>46239</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02081042982644138</v>
+        <v>0.02102063597599497</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5486,22 +5466,22 @@
         <v>10.6275101427813</v>
       </c>
       <c r="K45" t="n">
-        <v>3.054986844334984</v>
+        <v>4.095945255934885</v>
       </c>
       <c r="L45" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="M45" t="n">
-        <v>64.28571428571429</v>
+        <v>57.4468085106383</v>
       </c>
       <c r="N45" t="n">
-        <v>15.59634768604025</v>
+        <v>17.80916416571605</v>
       </c>
       <c r="O45" t="n">
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>6.739133513408224</v>
+        <v>5.671743245665484</v>
       </c>
       <c r="Q45" t="n">
         <v>37</v>
@@ -5567,7 +5547,7 @@
         <v>46239</v>
       </c>
       <c r="C46" t="n">
-        <v>8.671012340097924</v>
+        <v>9.02310799269584</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5595,22 +5575,22 @@
         <v>20.98614247885408</v>
       </c>
       <c r="K46" t="n">
-        <v>5.011150072260806</v>
+        <v>9.275239196407137</v>
       </c>
       <c r="L46" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="M46" t="n">
-        <v>57.69230769230769</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N46" t="n">
-        <v>11.70185446250036</v>
+        <v>16.01315420628742</v>
       </c>
       <c r="O46" t="n">
         <v>10</v>
       </c>
       <c r="P46" t="n">
-        <v>4.750781154483352</v>
+        <v>0.6632433924854686</v>
       </c>
       <c r="Q46" t="n">
         <v>54</v>
@@ -5676,7 +5656,7 @@
         <v>46239</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7912167253138627</v>
+        <v>0.7971024777419653</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5704,22 +5684,22 @@
         <v>25.31303456031801</v>
       </c>
       <c r="K47" t="n">
-        <v>6.145353566361278</v>
+        <v>6.934954256661641</v>
       </c>
       <c r="L47" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M47" t="n">
-        <v>63.63636363636363</v>
+        <v>60</v>
       </c>
       <c r="N47" t="n">
-        <v>14.52324590656573</v>
+        <v>13.69328890768449</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>3.631479197277199</v>
+        <v>2.866271150200106</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5785,7 +5765,7 @@
         <v>46239</v>
       </c>
       <c r="C48" t="n">
-        <v>0.06095984643244901</v>
+        <v>0.06159046488110978</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5813,22 +5793,22 @@
         <v>30.07074365952763</v>
       </c>
       <c r="K48" t="n">
-        <v>3.872703167686065</v>
+        <v>4.947247261270582</v>
       </c>
       <c r="L48" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M48" t="n">
-        <v>66.66666666666667</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N48" t="n">
-        <v>14.12340481485396</v>
+        <v>11.93146999034344</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>5.898851811358363</v>
+        <v>4.814564336452176</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5894,7 +5874,7 @@
         <v>46239</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2587640376931651</v>
+        <v>0.2602354756950876</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5922,22 +5902,22 @@
         <v>23.59168796028241</v>
       </c>
       <c r="K49" t="n">
-        <v>2.402867900435424</v>
+        <v>2.985172430376415</v>
       </c>
       <c r="L49" t="n">
         <v>21</v>
       </c>
       <c r="M49" t="n">
-        <v>61.90476190476191</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N49" t="n">
-        <v>9.60781177366678</v>
+        <v>9.669209748173083</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>2.536190785291015</v>
+        <v>1.956424912514199</v>
       </c>
       <c r="Q49" t="n">
         <v>53</v>
@@ -6003,7 +5983,7 @@
         <v>46239</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7294160843427088</v>
+        <v>0.7273139726078529</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6031,22 +6011,22 @@
         <v>11.86078125763058</v>
       </c>
       <c r="K50" t="n">
-        <v>2.086878550656524</v>
+        <v>1.792673322690486</v>
       </c>
       <c r="L50" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M50" t="n">
-        <v>50</v>
+        <v>47.61904761904762</v>
       </c>
       <c r="N50" t="n">
-        <v>13.78965101893368</v>
+        <v>13.63160196619841</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>1.874013072497038</v>
+        <v>2.168453391839043</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6112,7 +6092,7 @@
         <v>46239</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1864530387948054</v>
+        <v>0.1845611781936641</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6144,7 +6124,7 @@
         <v>27.30972539236674</v>
       </c>
       <c r="K51" t="n">
-        <v>8.068407555474799</v>
+        <v>6.971882855186662</v>
       </c>
       <c r="L51" t="n">
         <v>4</v>
@@ -6153,7 +6133,7 @@
         <v>100</v>
       </c>
       <c r="N51" t="n">
-        <v>21.01343299532531</v>
+        <v>19.54837245931199</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
@@ -6186,7 +6166,7 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>15.35677407351765</v>
+        <v>16.21561330359341</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6231,7 +6211,7 @@
         <v>46239</v>
       </c>
       <c r="C52" t="n">
-        <v>4.267189103126978</v>
+        <v>4.334455074137223</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6291,22 +6271,22 @@
         <v>12.1710603868542</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.089685827654209</v>
+        <v>0.546273479254944</v>
       </c>
       <c r="Z52" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AA52" t="n">
-        <v>38.88888888888889</v>
+        <v>33.9622641509434</v>
       </c>
       <c r="AB52" t="n">
-        <v>12.49481897677179</v>
+        <v>10.55744009261507</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>6.036457162155773</v>
+        <v>7.494667903862084</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6340,16 +6320,16 @@
         <v>46239</v>
       </c>
       <c r="C53" t="n">
-        <v>1.620691001587639</v>
+        <v>1.650119924115605</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6359,7 +6339,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -6372,22 +6352,22 @@
         <v>28.17598592067425</v>
       </c>
       <c r="K53" t="n">
-        <v>6.84894465002166</v>
+        <v>8.789135168275974</v>
       </c>
       <c r="L53" t="n">
         <v>5</v>
       </c>
       <c r="M53" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N53" t="n">
-        <v>11.18129841148397</v>
+        <v>13.45498152972782</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>1.077273485244579</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6445,16 +6425,16 @@
         <v>46239</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08912749170347238</v>
+        <v>0.08450295620308704</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6473,18 +6453,22 @@
         <v>42.39442432818535</v>
       </c>
       <c r="K54" t="n">
-        <v>10.26537010520914</v>
+        <v>4.544058882728019</v>
       </c>
       <c r="L54" t="n">
-        <v>2</v>
-      </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M54" t="n">
+        <v>60</v>
+      </c>
+      <c r="N54" t="n">
+        <v>28.91863102314376</v>
+      </c>
       <c r="O54" t="n">
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>5.21879595605923</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6511,7 +6495,7 @@
         <v>114.7400208810756</v>
       </c>
       <c r="Y54" t="n">
-        <v>36.48099878423727</v>
+        <v>39.77679304992365</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -6556,7 +6540,7 @@
         <v>46239</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8908545751547472</v>
+        <v>0.8921157620229551</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6584,16 +6568,16 @@
         <v>12.31616646597832</v>
       </c>
       <c r="K55" t="n">
-        <v>6.196655431641607</v>
+        <v>6.346998519069458</v>
       </c>
       <c r="L55" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M55" t="n">
-        <v>68</v>
+        <v>67.34693877551021</v>
       </c>
       <c r="N55" t="n">
-        <v>13.14746794751552</v>
+        <v>13.01700412313512</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
@@ -6626,7 +6610,7 @@
         <v>25.41488056506582</v>
       </c>
       <c r="Y55" t="n">
-        <v>6.882701432620775</v>
+        <v>6.750874850110633</v>
       </c>
       <c r="Z55" t="n">
         <v>21</v>
@@ -6675,7 +6659,7 @@
         <v>46239</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9013648931427447</v>
+        <v>0.887070854162671</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6703,7 +6687,7 @@
         <v>34.38683570496719</v>
       </c>
       <c r="K56" t="n">
-        <v>14.9433724559306</v>
+        <v>13.12057565201068</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6733,22 +6717,22 @@
         <v>18.2672887877857</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.810511990191478</v>
+        <v>4.351763863472069</v>
       </c>
       <c r="Z56" t="n">
         <v>15</v>
       </c>
       <c r="AA56" t="n">
-        <v>13.33333333333333</v>
+        <v>20</v>
       </c>
       <c r="AB56" t="n">
-        <v>8.376267141289677</v>
+        <v>13.60730707672086</v>
       </c>
       <c r="AC56" t="n">
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>7.397392616249753</v>
+        <v>5.905217246730676</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6774,7 +6758,7 @@
         <v>46239</v>
       </c>
       <c r="C57" t="n">
-        <v>1.44727075478568</v>
+        <v>1.420994959815687</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6791,7 +6775,11 @@
           <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %80.00: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>5</v>
       </c>
@@ -6802,13 +6790,17 @@
         <v>32.76213282665623</v>
       </c>
       <c r="K57" t="n">
-        <v>23.92577736109212</v>
+        <v>21.6758539748358</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M57" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="N57" t="n">
+        <v>15.65787039974029</v>
+      </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
@@ -6840,16 +6832,16 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>10.77495813115876</v>
+        <v>12.39487541241547</v>
       </c>
       <c r="Z57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA57" t="n">
-        <v>66.66666666666667</v>
+        <v>80</v>
       </c>
       <c r="AB57" t="n">
-        <v>14.70271092548353</v>
+        <v>12.75692533836235</v>
       </c>
       <c r="AC57" t="n">
         <v>6</v>
@@ -6889,7 +6881,7 @@
         <v>46239</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7613674606957136</v>
+        <v>0.7697756669488552</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6908,7 +6900,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.19: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -6921,22 +6913,22 @@
         <v>16.33691982084211</v>
       </c>
       <c r="K58" t="n">
-        <v>2.640154333625588</v>
+        <v>3.773666904155992</v>
       </c>
       <c r="L58" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M58" t="n">
-        <v>85.18518518518519</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N58" t="n">
-        <v>19.3576068357252</v>
+        <v>19.44892960831233</v>
       </c>
       <c r="O58" t="n">
         <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>2.299144697993993</v>
+        <v>1.18173823131511</v>
       </c>
       <c r="Q58" t="n">
         <v>24</v>
@@ -6963,7 +6955,7 @@
         <v>41.32985472592288</v>
       </c>
       <c r="Y58" t="n">
-        <v>14.12808538384743</v>
+        <v>13.17975385312373</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -7008,7 +7000,7 @@
         <v>46239</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8206456478418286</v>
+        <v>0.8113965165118328</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7025,7 +7017,11 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %76.47: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H59" t="n">
         <v>5</v>
       </c>
@@ -7068,16 +7064,16 @@
         <v>10.2478061424703</v>
       </c>
       <c r="Y59" t="n">
-        <v>6.819029166410095</v>
+        <v>7.869230357341772</v>
       </c>
       <c r="Z59" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AA59" t="n">
-        <v>47.61904761904762</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="AB59" t="n">
-        <v>15.37190524642973</v>
+        <v>13.17365761123391</v>
       </c>
       <c r="AC59" t="n">
         <v>6</v>
@@ -7117,7 +7113,7 @@
         <v>46239</v>
       </c>
       <c r="C60" t="n">
-        <v>13.09585621304486</v>
+        <v>13.20095939292484</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7145,22 +7141,22 @@
         <v>17.06238107085701</v>
       </c>
       <c r="K60" t="n">
-        <v>3.062959951078192</v>
+        <v>3.890110512483336</v>
       </c>
       <c r="L60" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M60" t="n">
-        <v>44.73684210526316</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N60" t="n">
-        <v>12.9081530423183</v>
+        <v>11.5632679575326</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>4.790314630266135</v>
+        <v>3.955996838623865</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7226,7 +7222,7 @@
         <v>46239</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6264149361089667</v>
+        <v>0.620529183680864</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7255,10 +7251,10 @@
         <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>33.98678515927238</v>
+        <v>34.04035822988622</v>
       </c>
       <c r="K61" t="n">
-        <v>1.140674231508432</v>
+        <v>0.2717388877710114</v>
       </c>
       <c r="L61" t="n">
         <v>8</v>
@@ -7267,13 +7263,13 @@
         <v>75</v>
       </c>
       <c r="N61" t="n">
-        <v>18.75763562026636</v>
+        <v>20.85686400970598</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>8.759409442152633</v>
+        <v>9.701897284455541</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7331,7 +7327,7 @@
         <v>46239</v>
       </c>
       <c r="C62" t="n">
-        <v>8.418764708385984</v>
+        <v>8.518612729271961</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7359,22 +7355,22 @@
         <v>13.30115949155629</v>
       </c>
       <c r="K62" t="n">
-        <v>1.176888922699315</v>
+        <v>2.376864509173293</v>
       </c>
       <c r="L62" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M62" t="n">
-        <v>59.09090909090909</v>
+        <v>53.73134328358209</v>
       </c>
       <c r="N62" t="n">
-        <v>13.7063349947116</v>
+        <v>14.63649661857709</v>
       </c>
       <c r="O62" t="n">
         <v>6</v>
       </c>
       <c r="P62" t="n">
-        <v>4.767008680199303</v>
+        <v>3.539017832004476</v>
       </c>
       <c r="Q62" t="n">
         <v>29</v>
@@ -7440,7 +7436,7 @@
         <v>46239</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1044725563863614</v>
+        <v>0.1040521440872542</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7472,7 +7468,7 @@
         <v>31.19925725463639</v>
       </c>
       <c r="K63" t="n">
-        <v>4.696053368930531</v>
+        <v>4.274741686449013</v>
       </c>
       <c r="L63" t="n">
         <v>3</v>
@@ -7481,13 +7477,13 @@
         <v>100</v>
       </c>
       <c r="N63" t="n">
-        <v>9.275776345707937</v>
+        <v>9.443683317782943</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>0.2903133607132347</v>
+        <v>0.6955263583695359</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7514,22 +7510,22 @@
         <v>10.24796802016521</v>
       </c>
       <c r="Y63" t="n">
-        <v>5.0358430644447</v>
+        <v>5.417992223333901</v>
       </c>
       <c r="Z63" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA63" t="n">
-        <v>46.15384615384615</v>
+        <v>50</v>
       </c>
       <c r="AB63" t="n">
-        <v>13.43404189779166</v>
+        <v>13.37630344651862</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>5.227400627506318</v>
+        <v>4.844481402303769</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7563,7 +7559,7 @@
         <v>46239</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1597568313154982</v>
+        <v>0.1561833217281345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7588,25 +7584,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>23.67654789977809</v>
+        <v>24.54410599778878</v>
       </c>
       <c r="K64" t="n">
-        <v>1.535292612406525</v>
+        <v>0.4054017512783448</v>
       </c>
       <c r="L64" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="M64" t="n">
-        <v>70.27027027027027</v>
+        <v>70</v>
       </c>
       <c r="N64" t="n">
-        <v>16.01715466355967</v>
+        <v>16.17568740291264</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>3.412318316567431</v>
+        <v>4.576046874552908</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7672,7 +7668,7 @@
         <v>46239</v>
       </c>
       <c r="C65" t="n">
-        <v>6.232618566882508</v>
+        <v>6.138025704990531</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7691,7 +7687,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %88.24: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -7704,22 +7700,22 @@
         <v>28.12381406175567</v>
       </c>
       <c r="K65" t="n">
-        <v>2.690437297175041</v>
+        <v>1.131897776644575</v>
       </c>
       <c r="L65" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M65" t="n">
-        <v>81.25</v>
+        <v>88.23529411764706</v>
       </c>
       <c r="N65" t="n">
-        <v>14.72106682780091</v>
+        <v>13.77843664472946</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>7.118055872789686</v>
+        <v>8.768847829733328</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7785,7 +7781,7 @@
         <v>46239</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4258780897084043</v>
+        <v>0.4254576673193919</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7979,7 +7975,7 @@
         <v>46239</v>
       </c>
       <c r="C68" t="n">
-        <v>3.865694827759595</v>
+        <v>3.914042354617323</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8036,10 +8032,10 @@
         <v>80</v>
       </c>
       <c r="X68" t="n">
-        <v>116.020848317919</v>
+        <v>119.0700097329771</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.1628681080171002</v>
+        <v>0.3212024037490879</v>
       </c>
       <c r="Z68" t="n">
         <v>1</v>
@@ -8050,7 +8046,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>7.849916903123932</v>
+        <v>7.703541556905503</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8084,7 +8080,7 @@
         <v>46239</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4048574537324093</v>
+        <v>0.4067493141233443</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8112,7 +8108,7 @@
         <v>29.4573350207784</v>
       </c>
       <c r="K69" t="n">
-        <v>3.561099459965011</v>
+        <v>4.045030632044866</v>
       </c>
       <c r="L69" t="n">
         <v>7</v>
@@ -8121,7 +8117,7 @@
         <v>71.42857142857143</v>
       </c>
       <c r="N69" t="n">
-        <v>15.74456577461902</v>
+        <v>15.30141509712112</v>
       </c>
       <c r="O69" t="n">
         <v>3</v>
@@ -8177,16 +8173,16 @@
         <v>46239</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4189412815179769</v>
+        <v>0.4237760181229631</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -8205,22 +8201,22 @@
         <v>20.66985845799666</v>
       </c>
       <c r="K70" t="n">
-        <v>7.468946855437641</v>
+        <v>8.709178062490475</v>
       </c>
       <c r="L70" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M70" t="n">
-        <v>66.66666666666667</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N70" t="n">
-        <v>8.806559784819418</v>
+        <v>7.201184133223345</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>0.4941456672844513</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>30</v>
@@ -8286,7 +8282,7 @@
         <v>46239</v>
       </c>
       <c r="C71" t="n">
-        <v>3.264504831184958</v>
+        <v>3.277117020431736</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8318,7 +8314,7 @@
         <v>20.51701021225919</v>
       </c>
       <c r="K71" t="n">
-        <v>4.204336655762386</v>
+        <v>4.606922922960655</v>
       </c>
       <c r="L71" t="n">
         <v>30</v>
@@ -8327,13 +8323,13 @@
         <v>76.66666666666667</v>
       </c>
       <c r="N71" t="n">
-        <v>11.82812245893715</v>
+        <v>11.96068581999267</v>
       </c>
       <c r="O71" t="n">
         <v>6</v>
       </c>
       <c r="P71" t="n">
-        <v>1.723213641452914</v>
+        <v>1.331725509281356</v>
       </c>
       <c r="Q71" t="n">
         <v>43</v>
@@ -8399,7 +8395,7 @@
         <v>46239</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07924779720908831</v>
+        <v>0.07840697261087394</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8427,16 +8423,16 @@
         <v>20.36571476939619</v>
       </c>
       <c r="K72" t="n">
-        <v>10.79331097762173</v>
+        <v>9.617786300994947</v>
       </c>
       <c r="L72" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M72" t="n">
-        <v>66.66666666666667</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N72" t="n">
-        <v>15.39469661418315</v>
+        <v>14.39782702990865</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
@@ -8469,10 +8465,10 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>11.77053871965082</v>
+        <v>12.70665939359192</v>
       </c>
       <c r="Z72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr"/>
@@ -8514,7 +8510,7 @@
         <v>46239</v>
       </c>
       <c r="C73" t="n">
-        <v>0.06957830381930519</v>
+        <v>0.06936809766975159</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8539,25 +8535,25 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>21.46200936158552</v>
+        <v>21.93799671486063</v>
       </c>
       <c r="K73" t="n">
-        <v>0.3030300045913759</v>
+        <v>0.6097554933819138</v>
       </c>
       <c r="L73" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M73" t="n">
-        <v>66.66666666666667</v>
+        <v>68.18181818181819</v>
       </c>
       <c r="N73" t="n">
-        <v>15.68138501637575</v>
+        <v>16.34029941072919</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>9.667674042314323</v>
+        <v>9.333333989898996</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8623,7 +8619,7 @@
         <v>46239</v>
       </c>
       <c r="C74" t="n">
-        <v>4.927236944547341</v>
+        <v>5.007115425369062</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8651,22 +8647,22 @@
         <v>18.35970785011217</v>
       </c>
       <c r="K74" t="n">
-        <v>4.246040078479196</v>
+        <v>5.936037009185791</v>
       </c>
       <c r="L74" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M74" t="n">
-        <v>60</v>
+        <v>62.96296296296296</v>
       </c>
       <c r="N74" t="n">
-        <v>20.43221953039583</v>
+        <v>19.58729280616051</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>3.601057573692712</v>
+        <v>1.948310555203459</v>
       </c>
       <c r="Q74" t="n">
         <v>35</v>
@@ -8693,10 +8689,10 @@
         <v>95.98093909010421</v>
       </c>
       <c r="Y74" t="n">
-        <v>14.89322832524044</v>
+        <v>13.51350989368744</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA74" t="inlineStr"/>
       <c r="AB74" t="inlineStr"/>
@@ -8738,21 +8734,21 @@
         <v>46239</v>
       </c>
       <c r="C75" t="n">
-        <v>0.143781153228901</v>
+        <v>0.1343218611539252</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>AL_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>VERİ_YETERSİZ</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -8766,22 +8762,22 @@
         <v>19.1703426786477</v>
       </c>
       <c r="K75" t="n">
-        <v>10.3361228489149</v>
+        <v>3.077163040832698</v>
       </c>
       <c r="L75" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M75" t="n">
-        <v>20</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N75" t="n">
-        <v>9.794958843326418</v>
+        <v>12.26647622156585</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.835581493457928</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8808,22 +8804,22 @@
         <v>17.02929186229787</v>
       </c>
       <c r="Y75" t="n">
-        <v>5.71922542371569</v>
+        <v>11.92191168505222</v>
       </c>
       <c r="Z75" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA75" t="n">
-        <v>50</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB75" t="n">
-        <v>14.30215207053015</v>
+        <v>12.35746193532061</v>
       </c>
       <c r="AC75" t="n">
         <v>10</v>
       </c>
       <c r="AD75" t="n">
-        <v>4.540453337939699</v>
+        <v>0</v>
       </c>
       <c r="AE75" t="n">
         <v>4</v>
@@ -8857,7 +8853,7 @@
         <v>46239</v>
       </c>
       <c r="C76" t="n">
-        <v>1.832999392993822</v>
+        <v>1.88134691985155</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8885,22 +8881,22 @@
         <v>20.51082830683794</v>
       </c>
       <c r="K76" t="n">
-        <v>5.760022090795935</v>
+        <v>8.549567754614863</v>
       </c>
       <c r="L76" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M76" t="n">
-        <v>73.33333333333333</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N76" t="n">
-        <v>10.23768293434878</v>
+        <v>10.0083946713961</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>4.009055430760045</v>
+        <v>1.336193478599546</v>
       </c>
       <c r="Q76" t="n">
         <v>42</v>
@@ -8966,7 +8962,7 @@
         <v>46239</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5158464261899016</v>
+        <v>0.5238342502034455</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8994,16 +8990,16 @@
         <v>21.60005234598619</v>
       </c>
       <c r="K77" t="n">
-        <v>6.241685190123047</v>
+        <v>7.886825761260052</v>
       </c>
       <c r="L77" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M77" t="n">
-        <v>56.52173913043478</v>
+        <v>45</v>
       </c>
       <c r="N77" t="n">
-        <v>11.93943721732554</v>
+        <v>10.68617526204291</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -9036,22 +9032,22 @@
         <v>12.99543275787505</v>
       </c>
       <c r="Y77" t="n">
-        <v>5.977009338265771</v>
+        <v>4.521073880536086</v>
       </c>
       <c r="Z77" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="AA77" t="n">
-        <v>45.09803921568628</v>
+        <v>49.15254237288136</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.43048838845208</v>
+        <v>11.57400389360102</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>4.278730801286368</v>
+        <v>5.738361691048599</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9085,7 +9081,7 @@
         <v>46239</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05339241453820177</v>
+        <v>0.05423323913641614</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9113,16 +9109,16 @@
         <v>12.76206508896208</v>
       </c>
       <c r="K78" t="n">
-        <v>5.383025328867186</v>
+        <v>7.04259889745642</v>
       </c>
       <c r="L78" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="M78" t="n">
-        <v>68.85245901639344</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="N78" t="n">
-        <v>15.95590019296373</v>
+        <v>17.20774729385692</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
@@ -9155,22 +9151,22 @@
         <v>23.16536029857119</v>
       </c>
       <c r="Y78" t="n">
-        <v>8.06602495632024</v>
+        <v>6.618247246753583</v>
       </c>
       <c r="Z78" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA78" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AB78" t="n">
-        <v>14.64916186040179</v>
+        <v>13.25512377513977</v>
       </c>
       <c r="AC78" t="n">
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>2.103656502137419</v>
+        <v>3.621427798836052</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9204,7 +9200,7 @@
         <v>46239</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8874912765516835</v>
+        <v>0.8942178737578109</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9232,22 +9228,22 @@
         <v>12.46716859924595</v>
       </c>
       <c r="K79" t="n">
-        <v>2.772007904353968</v>
+        <v>3.550951787524936</v>
       </c>
       <c r="L79" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="M79" t="n">
-        <v>46.55172413793103</v>
+        <v>50.9433962264151</v>
       </c>
       <c r="N79" t="n">
-        <v>10.33790854880191</v>
+        <v>10.33290339162583</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>2.16789779734532</v>
+        <v>1.399357695377201</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9313,7 +9309,7 @@
         <v>46239</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1324300106426891</v>
+        <v>0.1257034035568626</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9338,10 +9334,10 @@
         <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>69.28554820223583</v>
+        <v>71.23712742986181</v>
       </c>
       <c r="K80" t="n">
-        <v>1.543919689072548</v>
+        <v>2.925991080130719</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9352,7 +9348,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>8.32751024071159</v>
+        <v>6.872908237883246</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9418,11 +9414,11 @@
         <v>46239</v>
       </c>
       <c r="C81" t="n">
-        <v>1.061542116787746</v>
+        <v>1.07310345059886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9432,7 +9428,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -9443,25 +9439,25 @@
         <v>10</v>
       </c>
       <c r="J81" t="n">
-        <v>11.84927434264682</v>
+        <v>12.05035505845211</v>
       </c>
       <c r="K81" t="n">
-        <v>1.133690704133694</v>
+        <v>2.46888710889912</v>
       </c>
       <c r="L81" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M81" t="n">
-        <v>51.92307692307692</v>
+        <v>51.02040816326531</v>
       </c>
       <c r="N81" t="n">
-        <v>12.31903901763035</v>
+        <v>12.98769363041235</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>8.766919543957584</v>
+        <v>7.349658129005721</v>
       </c>
       <c r="Q81" t="n">
         <v>31</v>
@@ -9488,7 +9484,7 @@
         <v>27.31228182970742</v>
       </c>
       <c r="Y81" t="n">
-        <v>10.849917760243</v>
+        <v>9.878977612167695</v>
       </c>
       <c r="Z81" t="n">
         <v>9</v>
@@ -9503,7 +9499,7 @@
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>0.1342887426548312</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9537,7 +9533,7 @@
         <v>46239</v>
       </c>
       <c r="C82" t="n">
-        <v>5.189994894247278</v>
+        <v>5.248852739093004</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9546,7 +9542,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9554,38 +9550,24 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>5</v>
       </c>
       <c r="I82" t="n">
         <v>10</v>
       </c>
-      <c r="J82" t="n">
-        <v>12.20498494157071</v>
-      </c>
-      <c r="K82" t="n">
-        <v>13.03215569259089</v>
-      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="n">
-        <v>6</v>
-      </c>
-      <c r="M82" t="n">
-        <v>83.33333333333333</v>
-      </c>
-      <c r="N82" t="n">
-        <v>8.520914392672934</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="O82" t="n">
         <v>4</v>
       </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
+      <c r="P82" t="inlineStr"/>
       <c r="Q82" t="n">
         <v>8</v>
       </c>
@@ -9608,25 +9590,25 @@
         <v>57.14285714285715</v>
       </c>
       <c r="X82" t="n">
-        <v>15.04024401260009</v>
+        <v>16.28898299114456</v>
       </c>
       <c r="Y82" t="n">
-        <v>0.7634018888225902</v>
+        <v>0.7157069781312031</v>
       </c>
       <c r="Z82" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AA82" t="n">
         <v>50</v>
       </c>
       <c r="AB82" t="n">
-        <v>11.23470967332035</v>
+        <v>11.22183907241817</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>3.261496436578137</v>
+        <v>3.307968382416127</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9660,7 +9642,7 @@
         <v>46239</v>
       </c>
       <c r="C83" t="n">
-        <v>5.901543550260588</v>
+        <v>5.948839981206576</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9688,22 +9670,22 @@
         <v>14.0949513048101</v>
       </c>
       <c r="K83" t="n">
-        <v>9.039650898551365</v>
+        <v>9.913521653749013</v>
       </c>
       <c r="L83" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M83" t="n">
-        <v>61.29032258064516</v>
+        <v>60.71428571428572</v>
       </c>
       <c r="N83" t="n">
-        <v>10.36209338144422</v>
+        <v>10.70932204243479</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>0.8807338372186502</v>
+        <v>0.07867853285914439</v>
       </c>
       <c r="Q83" t="n">
         <v>44</v>
@@ -9730,22 +9712,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.902312654262805</v>
+        <v>1.116133503673644</v>
       </c>
       <c r="Z83" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AA83" t="n">
-        <v>54.83870967741935</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="AB83" t="n">
-        <v>11.77347530517702</v>
+        <v>12.00425528872013</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>4.17714979487257</v>
+        <v>4.938992243499907</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9779,7 +9761,7 @@
         <v>46239</v>
       </c>
       <c r="C84" t="n">
-        <v>2.215575064031443</v>
+        <v>2.219779126903496</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9807,7 +9789,7 @@
         <v>14.10735630446007</v>
       </c>
       <c r="K84" t="n">
-        <v>6.065231491238099</v>
+        <v>6.266490707848282</v>
       </c>
       <c r="L84" t="n">
         <v>39</v>
@@ -9816,7 +9798,7 @@
         <v>64.1025641025641</v>
       </c>
       <c r="N84" t="n">
-        <v>9.900639794897224</v>
+        <v>10.5206215097878</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
@@ -9888,7 +9870,7 @@
         <v>46239</v>
       </c>
       <c r="C85" t="n">
-        <v>6.568948742498427</v>
+        <v>6.579459060486425</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9916,22 +9898,22 @@
         <v>15.13449360257271</v>
       </c>
       <c r="K85" t="n">
-        <v>1.93951457699113</v>
+        <v>2.102617800314333</v>
       </c>
       <c r="L85" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="M85" t="n">
-        <v>62.06896551724138</v>
+        <v>58.18181818181818</v>
       </c>
       <c r="N85" t="n">
-        <v>14.88449958456434</v>
+        <v>13.88678250642891</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>5.945177832322934</v>
+        <v>5.775936334188203</v>
       </c>
       <c r="Q85" t="n">
         <v>34</v>
@@ -9997,7 +9979,7 @@
         <v>46239</v>
       </c>
       <c r="C86" t="n">
-        <v>3.67650910397564</v>
+        <v>3.890919847382548</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10054,25 +10036,25 @@
         <v>68.35443037974683</v>
       </c>
       <c r="X86" t="n">
-        <v>44.1992982541711</v>
+        <v>52.347553944765</v>
       </c>
       <c r="Y86" t="n">
-        <v>0.1712346205608895</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AA86" t="n">
-        <v>41.66666666666666</v>
+        <v>40</v>
       </c>
       <c r="AB86" t="n">
-        <v>13.83837700712544</v>
+        <v>9.831530790531973</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>5.838763363730449</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="AE86" t="n">
         <v>51</v>
@@ -10106,7 +10088,7 @@
         <v>46239</v>
       </c>
       <c r="C87" t="n">
-        <v>5.565213374644667</v>
+        <v>5.517916943698679</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10134,22 +10116,22 @@
         <v>29.54558799520699</v>
       </c>
       <c r="K87" t="n">
-        <v>2.463343619648861</v>
+        <v>1.592550331096598</v>
       </c>
       <c r="L87" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M87" t="n">
-        <v>50</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N87" t="n">
-        <v>11.43324102704426</v>
+        <v>11.76555496029376</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>2.475672070362434</v>
+        <v>3.354034973822695</v>
       </c>
       <c r="Q87" t="n">
         <v>47</v>
@@ -10215,7 +10197,7 @@
         <v>46239</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9829249029228563</v>
+        <v>1.01193340306181</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10243,16 +10225,16 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>10.11864926663959</v>
+        <v>13.36851794231744</v>
       </c>
       <c r="L88" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="M88" t="n">
-        <v>61.90476190476191</v>
+        <v>50</v>
       </c>
       <c r="N88" t="n">
-        <v>11.37594108580531</v>
+        <v>5.666376892907188</v>
       </c>
       <c r="O88" t="n">
         <v>10</v>
@@ -10282,25 +10264,25 @@
         <v>68.35443037974683</v>
       </c>
       <c r="X88" t="n">
-        <v>11.34323759706175</v>
+        <v>13.50981969714924</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.099831796569262</v>
+        <v>0.1244841681616649</v>
       </c>
       <c r="Z88" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="AA88" t="n">
-        <v>37.33333333333334</v>
+        <v>38.0281690140845</v>
       </c>
       <c r="AB88" t="n">
-        <v>10.63614880233937</v>
+        <v>12.18459957953473</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>4.954661142083639</v>
+        <v>5.882839035075449</v>
       </c>
       <c r="AE88" t="n">
         <v>30</v>
@@ -10334,7 +10316,7 @@
         <v>46239</v>
       </c>
       <c r="C89" t="n">
-        <v>1.984348068295498</v>
+        <v>2.067379516077532</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10348,7 +10330,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -10362,16 +10344,16 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>7.786523269270718</v>
+        <v>12.29665494497365</v>
       </c>
       <c r="L89" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="M89" t="n">
-        <v>68.57142857142857</v>
+        <v>68.18181818181819</v>
       </c>
       <c r="N89" t="n">
-        <v>16.05252990993683</v>
+        <v>11.98702487689557</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
@@ -10404,22 +10386,22 @@
         <v>28.7873334490923</v>
       </c>
       <c r="Y89" t="n">
-        <v>13.46267372251425</v>
+        <v>9.841676175356151</v>
       </c>
       <c r="Z89" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AA89" t="n">
-        <v>33.33333333333334</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="AB89" t="n">
-        <v>24.68761358108778</v>
+        <v>17.01341296973431</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>0.1756064420094794</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10453,24 +10435,28 @@
         <v>46239</v>
       </c>
       <c r="C90" t="n">
-        <v>2.682233118375385</v>
+        <v>2.79994864788959</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr"/>
+          <t>ÇELİŞKİLİ_BEKLE</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.76: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H90" t="n">
         <v>5</v>
       </c>
@@ -10481,22 +10467,22 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>5.734297279978562</v>
+        <v>10.37467275922248</v>
       </c>
       <c r="L90" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="M90" t="n">
-        <v>64.1025641025641</v>
+        <v>75.75757575757575</v>
       </c>
       <c r="N90" t="n">
-        <v>15.0761275126997</v>
+        <v>14.98538149859456</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>2.14282666864658</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>42</v>
@@ -10523,16 +10509,16 @@
         <v>33.24184775233741</v>
       </c>
       <c r="Y90" t="n">
-        <v>11.80355028321611</v>
+        <v>7.932860704238509</v>
       </c>
       <c r="Z90" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AA90" t="n">
-        <v>25</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="AB90" t="n">
-        <v>8.158989511032161</v>
+        <v>8.412413089294214</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
@@ -10572,7 +10558,7 @@
         <v>46239</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2360617323409309</v>
+        <v>0.2379535927318659</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10600,16 +10586,16 @@
         <v>14.82331888146111</v>
       </c>
       <c r="K91" t="n">
-        <v>4.115713011389044</v>
+        <v>4.950123534292938</v>
       </c>
       <c r="L91" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M91" t="n">
-        <v>60.8695652173913</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="N91" t="n">
-        <v>14.67506174697792</v>
+        <v>15.63258073362421</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
@@ -10681,7 +10667,7 @@
         <v>46239</v>
       </c>
       <c r="C92" t="n">
-        <v>1.094124086574855</v>
+        <v>1.120399881544848</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10698,7 +10684,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H92" t="n">
         <v>5</v>
       </c>
@@ -10709,22 +10699,22 @@
         <v>22.28274626067631</v>
       </c>
       <c r="K92" t="n">
-        <v>3.841012316238279</v>
+        <v>6.334792667642142</v>
       </c>
       <c r="L92" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M92" t="n">
-        <v>60</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="N92" t="n">
-        <v>15.19496257703802</v>
+        <v>11.86346955680526</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>4.005149401949115</v>
+        <v>1.566004212339611</v>
       </c>
       <c r="Q92" t="n">
         <v>56</v>
@@ -10899,21 +10889,21 @@
         <v>46239</v>
       </c>
       <c r="C94" t="n">
-        <v>6.39027333670247</v>
+        <v>6.363997541732476</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AL_BEKLE_EŞİK</t>
-        </is>
-      </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -10927,22 +10917,22 @@
         <v>12.24049282186025</v>
       </c>
       <c r="K94" t="n">
-        <v>7.347561945543069</v>
+        <v>6.906165720438029</v>
       </c>
       <c r="L94" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="M94" t="n">
-        <v>54.16666666666666</v>
+        <v>51.72413793103448</v>
       </c>
       <c r="N94" t="n">
-        <v>13.88977423798863</v>
+        <v>13.30431828192241</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>0.6077809711113158</v>
+        <v>1.023172304600628</v>
       </c>
       <c r="Q94" t="n">
         <v>40</v>
@@ -10969,7 +10959,7 @@
         <v>46.65531127586331</v>
       </c>
       <c r="Y94" t="n">
-        <v>5.792308668843116</v>
+        <v>6.179675820698205</v>
       </c>
       <c r="Z94" t="n">
         <v>4</v>
@@ -10984,7 +10974,7 @@
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>0.2204611197049955</v>
+        <v>0</v>
       </c>
       <c r="AE94" t="n">
         <v>37</v>
@@ -11018,7 +11008,7 @@
         <v>46239</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1412586693443526</v>
+        <v>0.1408382570452454</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11046,7 +11036,7 @@
         <v>23.400044414021</v>
       </c>
       <c r="K95" t="n">
-        <v>1.89079669676111</v>
+        <v>1.587550571790719</v>
       </c>
       <c r="L95" t="n">
         <v>26</v>
@@ -11055,13 +11045,13 @@
         <v>65.38461538461539</v>
       </c>
       <c r="N95" t="n">
-        <v>19.65396541550904</v>
+        <v>19.42490216729606</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>4.032948447216844</v>
+        <v>4.343494260245073</v>
       </c>
       <c r="Q95" t="n">
         <v>22</v>
@@ -11127,7 +11117,7 @@
         <v>46239</v>
       </c>
       <c r="C96" t="n">
-        <v>0.130117737952647</v>
+        <v>0.1313789748499685</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11152,25 +11142,25 @@
         <v>10</v>
       </c>
       <c r="J96" t="n">
-        <v>12.79622946674051</v>
+        <v>12.86625377026597</v>
       </c>
       <c r="K96" t="n">
-        <v>0.5695839413965009</v>
+        <v>1.626014607707083</v>
       </c>
       <c r="L96" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="M96" t="n">
-        <v>51.51515151515152</v>
+        <v>60.27397260273973</v>
       </c>
       <c r="N96" t="n">
-        <v>13.79686370311483</v>
+        <v>12.88642560075273</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>9.377006137460775</v>
+        <v>8.240001760000016</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11197,16 +11187,16 @@
         <v>16.74415231729489</v>
       </c>
       <c r="Y96" t="n">
-        <v>12.29953079349081</v>
+        <v>11.44944632832807</v>
       </c>
       <c r="Z96" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA96" t="n">
-        <v>42.85714285714285</v>
+        <v>40</v>
       </c>
       <c r="AB96" t="n">
-        <v>15.96559934023883</v>
+        <v>16.42948776937994</v>
       </c>
       <c r="AC96" t="n">
         <v>8</v>
@@ -11246,7 +11236,7 @@
         <v>46239</v>
       </c>
       <c r="C97" t="n">
-        <v>1.836152520341587</v>
+        <v>1.837203616463533</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11274,22 +11264,22 @@
         <v>22.80838616541501</v>
       </c>
       <c r="K97" t="n">
-        <v>2.732407231550682</v>
+        <v>2.791215872795338</v>
       </c>
       <c r="L97" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M97" t="n">
-        <v>53.84615384615385</v>
+        <v>48</v>
       </c>
       <c r="N97" t="n">
-        <v>11.66515273636023</v>
+        <v>12.93095395568185</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>1.233878191515814</v>
+        <v>1.175960530227149</v>
       </c>
       <c r="Q97" t="n">
         <v>50</v>
@@ -11355,26 +11345,26 @@
         <v>46239</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6524805600338689</v>
+        <v>0.6613091884658165</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H98" t="n">
@@ -11387,22 +11377,22 @@
         <v>18.49937747698907</v>
       </c>
       <c r="K98" t="n">
-        <v>8.67370114996142</v>
+        <v>10.14415067220884</v>
       </c>
       <c r="L98" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M98" t="n">
-        <v>81.25</v>
+        <v>80</v>
       </c>
       <c r="N98" t="n">
-        <v>14.7580406367084</v>
+        <v>11.79346297877967</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>1.220441409470729</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
         <v>48</v>
@@ -11425,17 +11415,27 @@
       <c r="W98" t="n">
         <v>73.52941176470588</v>
       </c>
-      <c r="X98" t="inlineStr"/>
-      <c r="Y98" t="inlineStr"/>
+      <c r="X98" t="n">
+        <v>10.7043305347843</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>0.5060144078098627</v>
+      </c>
       <c r="Z98" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA98" t="inlineStr"/>
-      <c r="AB98" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>11.82280735143941</v>
+      </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
-      <c r="AD98" t="inlineStr"/>
+      <c r="AD98" t="n">
+        <v>7.532099098840783</v>
+      </c>
       <c r="AE98" t="n">
         <v>50</v>
       </c>
@@ -11468,7 +11468,7 @@
         <v>46239</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4742255364775094</v>
+        <v>0.481372555862443</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11496,22 +11496,22 @@
         <v>28.77817890954801</v>
       </c>
       <c r="K99" t="n">
-        <v>2.021634851937604</v>
+        <v>3.559195666113601</v>
       </c>
       <c r="L99" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M99" t="n">
-        <v>70</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N99" t="n">
-        <v>14.39545434204168</v>
+        <v>13.14362189634568</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>1.939162365838931</v>
+        <v>0.4256544588349342</v>
       </c>
       <c r="Q99" t="n">
         <v>35</v>
@@ -11577,7 +11577,7 @@
         <v>46239</v>
       </c>
       <c r="C100" t="n">
-        <v>325.7078159960379</v>
+        <v>328.536364268523</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11605,16 +11605,16 @@
         <v>25.19597156501795</v>
       </c>
       <c r="K100" t="n">
-        <v>6.271781072892924</v>
+        <v>7.194678369196383</v>
       </c>
       <c r="L100" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M100" t="n">
-        <v>73.33333333333333</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N100" t="n">
-        <v>11.56873670362326</v>
+        <v>11.81400718384301</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11686,7 +11686,7 @@
         <v>46239</v>
       </c>
       <c r="C101" t="n">
-        <v>324.6519601254528</v>
+        <v>325.8478167159021</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11714,16 +11714,16 @@
         <v>13.42090796247281</v>
       </c>
       <c r="K101" t="n">
-        <v>2.807225790558499</v>
+        <v>3.185916553614265</v>
       </c>
       <c r="L101" t="n">
         <v>37</v>
       </c>
       <c r="M101" t="n">
-        <v>43.24324324324324</v>
+        <v>37.83783783783784</v>
       </c>
       <c r="N101" t="n">
-        <v>9.868345659223998</v>
+        <v>9.528582219891799</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11795,7 +11795,7 @@
         <v>46239</v>
       </c>
       <c r="C102" t="n">
-        <v>392.719509634993</v>
+        <v>394.4911140550203</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>46239</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7172240770088678</v>
+        <v>0.7231099097357999</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>30.74202968074841</v>
       </c>
       <c r="K103" t="n">
-        <v>10.30787421913231</v>
+        <v>11.21310553655399</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
@@ -11964,22 +11964,22 @@
         <v>14.26498323563516</v>
       </c>
       <c r="Y103" t="n">
-        <v>3.463098584054036</v>
+        <v>2.67087747502458</v>
       </c>
       <c r="Z103" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="AA103" t="n">
-        <v>43.75</v>
+        <v>39.62264150943396</v>
       </c>
       <c r="AB103" t="n">
-        <v>11.07527294839242</v>
+        <v>10.76966505008277</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>4.699655105354927</v>
+        <v>5.475362755487623</v>
       </c>
       <c r="AE103" t="n">
         <v>34</v>
@@ -12013,7 +12013,7 @@
         <v>46239</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04855766784331022</v>
+        <v>0.0489780801424174</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %76.19: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -12042,25 +12042,25 @@
         <v>10</v>
       </c>
       <c r="J104" t="n">
-        <v>27.71454389191555</v>
+        <v>27.76362183938114</v>
       </c>
       <c r="K104" t="n">
-        <v>0.36659235336165</v>
+        <v>1.304346550094482</v>
       </c>
       <c r="L104" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M104" t="n">
-        <v>75</v>
+        <v>76.19047619047619</v>
       </c>
       <c r="N104" t="n">
-        <v>14.95533509217345</v>
+        <v>15.41015006677772</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>3.620136503036964</v>
+        <v>2.660945499088263</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>

--- a/TDA_Result.xlsx
+++ b/TDA_Result.xlsx
@@ -453,7 +453,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4490007972698404</v>
+        <v>0.4559599599779542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -739,22 +739,22 @@
         <v>14.94856954517825</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.730402191088535</v>
+        <v>4.269296835441705</v>
       </c>
       <c r="Z2" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="AA2" t="n">
-        <v>54.83870967741935</v>
+        <v>45.94594594594594</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.90075437420743</v>
+        <v>11.57649322829002</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.407560721232771</v>
+        <v>3.897081125733837</v>
       </c>
       <c r="AE2" t="n">
         <v>43</v>
@@ -763,10 +763,10 @@
         <v>53.48837209302326</v>
       </c>
       <c r="AG2" t="n">
-        <v>35.37001391759068</v>
+        <v>35.49954416339999</v>
       </c>
       <c r="AH2" t="n">
-        <v>18.11835817543258</v>
+        <v>17.98882792962327</v>
       </c>
       <c r="AI2" t="n">
         <v>38.91564047231397</v>
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7386651353738752</v>
+        <v>0.7446645064980887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,22 +848,22 @@
         <v>12.13279917920569</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.912086381957002</v>
+        <v>2.123547167668238</v>
       </c>
       <c r="Z3" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="AA3" t="n">
-        <v>43.10344827586207</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.88608479467795</v>
+        <v>10.30082810885584</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>7.300510798828997</v>
+        <v>8.047341934044749</v>
       </c>
       <c r="AE3" t="n">
         <v>38</v>
@@ -872,10 +872,10 @@
         <v>60.52631578947368</v>
       </c>
       <c r="AG3" t="n">
-        <v>31.9061389697014</v>
+        <v>32.24210038018699</v>
       </c>
       <c r="AH3" t="n">
-        <v>28.62017681977228</v>
+        <v>28.28421540928669</v>
       </c>
       <c r="AI3" t="n">
         <v>44.71786799604255</v>
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C4" t="n">
-        <v>1.42309699146192</v>
+        <v>1.421460410590665</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         <v>27.63389482946404</v>
       </c>
       <c r="K4" t="n">
-        <v>10.18598386608609</v>
+        <v>10.05926848789502</v>
       </c>
       <c r="L4" t="n">
         <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N4" t="n">
-        <v>15.39789546009553</v>
+        <v>13.69615600604336</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -949,10 +949,10 @@
         <v>58.49056603773585</v>
       </c>
       <c r="S4" t="n">
-        <v>37.63323703111325</v>
+        <v>37.96921228915578</v>
       </c>
       <c r="T4" t="n">
-        <v>20.85732900662259</v>
+        <v>20.52135374858006</v>
       </c>
       <c r="U4" t="n">
         <v>45.09442218134437</v>
@@ -967,22 +967,22 @@
         <v>11.23805603488277</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.9457843891723217</v>
+        <v>1.059698082658056</v>
       </c>
       <c r="Z4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA4" t="n">
-        <v>35.08771929824562</v>
+        <v>37.93103448275862</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.49205119447462</v>
+        <v>11.63814518191822</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>9.140666608678849</v>
+        <v>9.036056838406425</v>
       </c>
       <c r="AE4" t="n">
         <v>45</v>
@@ -991,10 +991,10 @@
         <v>60</v>
       </c>
       <c r="AG4" t="n">
-        <v>38.92068184220413</v>
+        <v>38.03914789647139</v>
       </c>
       <c r="AH4" t="n">
-        <v>21.07931815779587</v>
+        <v>21.96085210352861</v>
       </c>
       <c r="AI4" t="n">
         <v>45.45185459035139</v>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2625477385054309</v>
+        <v>0.2660116508183434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
         <v>62</v>
       </c>
       <c r="S5" t="n">
-        <v>44.94124694222501</v>
+        <v>44.99047771145579</v>
       </c>
       <c r="T5" t="n">
-        <v>17.05875305777499</v>
+        <v>17.00952228854421</v>
       </c>
       <c r="U5" t="n">
         <v>48.15044693099298</v>
@@ -1076,22 +1076,22 @@
         <v>16.70172291026088</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.024317768408915</v>
+        <v>4.784453640652863</v>
       </c>
       <c r="Z5" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="AA5" t="n">
-        <v>46.42857142857143</v>
+        <v>31.42857142857143</v>
       </c>
       <c r="AB5" t="n">
-        <v>16.24968379623781</v>
+        <v>17.33118271183639</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.230543622757132</v>
+        <v>5.477620576437658</v>
       </c>
       <c r="AE5" t="n">
         <v>44</v>
@@ -1100,19 +1100,19 @@
         <v>50</v>
       </c>
       <c r="AG5" t="n">
-        <v>26.09501963826463</v>
+        <v>26.14098445825691</v>
       </c>
       <c r="AH5" t="n">
-        <v>23.90498036173537</v>
+        <v>23.85901554174309</v>
       </c>
       <c r="AI5" t="n">
         <v>35.8317605399894</v>
       </c>
       <c r="AJ5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AK5" t="n">
-        <v>51.51515151515152</v>
+        <v>50.76923076923077</v>
       </c>
     </row>
     <row r="6">
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C6" t="n">
-        <v>1.984348068295498</v>
+        <v>2.032908966951901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,16 +1153,16 @@
         <v>23.73506360720576</v>
       </c>
       <c r="K6" t="n">
-        <v>4.51434756757767</v>
+        <v>7.072019138134711</v>
       </c>
       <c r="L6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M6" t="n">
-        <v>63.1578947368421</v>
+        <v>50</v>
       </c>
       <c r="N6" t="n">
-        <v>10.35125690414793</v>
+        <v>9.264475517829858</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
@@ -1177,10 +1177,10 @@
         <v>67.5</v>
       </c>
       <c r="S6" t="n">
-        <v>47.77901735896405</v>
+        <v>48.17580730943047</v>
       </c>
       <c r="T6" t="n">
-        <v>19.72098264103595</v>
+        <v>19.32419269056953</v>
       </c>
       <c r="U6" t="n">
         <v>52.01774618987768</v>
@@ -1195,7 +1195,7 @@
         <v>44.49622708587002</v>
       </c>
       <c r="Y6" t="n">
-        <v>20.29219930624301</v>
+        <v>18.3415927098211</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1237,10 +1237,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C7" t="n">
-        <v>2.133594551563489</v>
+        <v>2.1348170328885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,22 +1268,22 @@
         <v>11.35312764557068</v>
       </c>
       <c r="K7" t="n">
-        <v>2.217576042736313</v>
+        <v>2.276143439109068</v>
       </c>
       <c r="L7" t="n">
         <v>70</v>
       </c>
       <c r="M7" t="n">
-        <v>57.14285714285715</v>
+        <v>58.57142857142857</v>
       </c>
       <c r="N7" t="n">
-        <v>12.84328933954645</v>
+        <v>12.72321302237388</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7654495318266674</v>
+        <v>0.7077472190001766</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1292,10 +1292,10 @@
         <v>58.8235294117647</v>
       </c>
       <c r="S7" t="n">
-        <v>51.42401469059773</v>
+        <v>51.16039193471492</v>
       </c>
       <c r="T7" t="n">
-        <v>7.399514721166973</v>
+        <v>7.663137477049787</v>
       </c>
       <c r="U7" t="n">
         <v>45.16533720637157</v>
@@ -1310,7 +1310,7 @@
         <v>13.79329344082609</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.387315841603815</v>
+        <v>9.335397676499946</v>
       </c>
       <c r="Z7" t="n">
         <v>18</v>
@@ -1325,7 +1325,7 @@
         <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.6761571672738165</v>
+        <v>0.7330339586431811</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1343,10 +1343,10 @@
         <v>35.8317605399894</v>
       </c>
       <c r="AJ7" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK7" t="n">
-        <v>43.75</v>
+        <v>42.85714285714285</v>
       </c>
     </row>
     <row r="8">
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3279219292133632</v>
+        <v>0.3290475877780922</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>22.10694516187944</v>
       </c>
       <c r="K8" t="n">
-        <v>4.262055976954926</v>
+        <v>4.619956641202227</v>
       </c>
       <c r="L8" t="n">
         <v>6</v>
@@ -1396,13 +1396,13 @@
         <v>50</v>
       </c>
       <c r="N8" t="n">
-        <v>15.15378575494074</v>
+        <v>15.17112081618959</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>3.585143212475383</v>
+        <v>3.230782603351434</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5889982297168715</v>
+        <v>0.5963199459891619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,19 +1493,19 @@
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>10.57037035785485</v>
+        <v>10.25501703215621</v>
       </c>
       <c r="K9" t="n">
-        <v>5.978185249621681</v>
+        <v>7.295578349127174</v>
       </c>
       <c r="L9" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="M9" t="n">
-        <v>46.42857142857143</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="N9" t="n">
-        <v>15.119494275747</v>
+        <v>10.75145883361706</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C10" t="n">
-        <v>2.054767166653508</v>
+        <v>2.103299064408626</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,22 +1605,22 @@
         <v>10.23694539327734</v>
       </c>
       <c r="K10" t="n">
-        <v>1.74115324314823</v>
+        <v>4.144194973042148</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="M10" t="n">
-        <v>32.55813953488372</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="N10" t="n">
-        <v>10.57138966011085</v>
+        <v>8.579114898075336</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>8.117508494438042</v>
+        <v>5.622785819674014</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1629,10 +1629,10 @@
         <v>51.16279069767442</v>
       </c>
       <c r="S10" t="n">
-        <v>37.07477737648844</v>
+        <v>37.22786100783294</v>
       </c>
       <c r="T10" t="n">
-        <v>14.08801332118598</v>
+        <v>13.93492968984147</v>
       </c>
       <c r="U10" t="n">
         <v>36.75230846944931</v>
@@ -1661,10 +1661,10 @@
         <v>53.33333333333334</v>
       </c>
       <c r="AG10" t="n">
-        <v>39.64895902395903</v>
+        <v>39.93002956818746</v>
       </c>
       <c r="AH10" t="n">
-        <v>13.68437430937431</v>
+        <v>13.40330376514587</v>
       </c>
       <c r="AI10" t="n">
         <v>36.1422996198733</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C11" t="n">
-        <v>7.257374570712263</v>
+        <v>7.291156708344285</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,16 +1714,16 @@
         <v>20.56423081971027</v>
       </c>
       <c r="K11" t="n">
-        <v>3.985762029720119</v>
+        <v>4.469802269125034</v>
       </c>
       <c r="L11" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M11" t="n">
-        <v>60</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N11" t="n">
-        <v>12.93461603959566</v>
+        <v>14.94987009323926</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1738,10 +1738,10 @@
         <v>61.22448979591837</v>
       </c>
       <c r="S11" t="n">
-        <v>51.19092252237243</v>
+        <v>51.34398374686223</v>
       </c>
       <c r="T11" t="n">
-        <v>10.03356727354593</v>
+        <v>9.880506049056137</v>
       </c>
       <c r="U11" t="n">
         <v>47.24599944352045</v>
@@ -1770,10 +1770,10 @@
         <v>55.55555555555556</v>
       </c>
       <c r="AG11" t="n">
-        <v>22.68103887282604</v>
+        <v>22.7365944283816</v>
       </c>
       <c r="AH11" t="n">
-        <v>32.87451668272951</v>
+        <v>32.81896112717396</v>
       </c>
       <c r="AI11" t="n">
         <v>41.17613449352105</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C12" t="n">
-        <v>6.568948742498427</v>
+        <v>6.566243433307173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>20.08266526523165</v>
       </c>
       <c r="K12" t="n">
-        <v>14.36346708463427</v>
+        <v>14.31636844666713</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -1858,25 +1858,25 @@
         <v>70.58823529411765</v>
       </c>
       <c r="X12" t="n">
-        <v>14.91241172664053</v>
+        <v>15.50525867851247</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4777070063694433</v>
+        <v>1.029295328582736</v>
       </c>
       <c r="Z12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AA12" t="n">
-        <v>37.5</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="AB12" t="n">
-        <v>12.17051868934601</v>
+        <v>13.04623712745359</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.529599999999987</v>
+        <v>0.9808000000000039</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -1907,19 +1907,19 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2951297282621439</v>
+        <v>0.3000510542551703</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1938,10 +1938,10 @@
         <v>38.11781916800814</v>
       </c>
       <c r="K13" t="n">
-        <v>3.710048231374863</v>
+        <v>5.439426559693383</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1949,7 +1949,7 @@
         <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.243805967332401</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1974,7 +1974,7 @@
         <v>35.74308703619145</v>
       </c>
       <c r="Y13" t="n">
-        <v>23.59828371685405</v>
+        <v>22.32427531902129</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C14" t="n">
-        <v>8.008862306854082</v>
+        <v>8.079105920341146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,10 +2051,10 @@
         <v>60.97560975609756</v>
       </c>
       <c r="S14" t="n">
-        <v>34.77464671535319</v>
+        <v>35.04345016472312</v>
       </c>
       <c r="T14" t="n">
-        <v>26.20096304074437</v>
+        <v>25.93215959137444</v>
       </c>
       <c r="U14" t="n">
         <v>45.72685693412379</v>
@@ -2069,16 +2069,16 @@
         <v>14.33662537827827</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.443252265092848</v>
+        <v>6.631461505755365</v>
       </c>
       <c r="Z14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA14" t="n">
-        <v>39.1304347826087</v>
+        <v>36</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.35075679918107</v>
+        <v>11.60453219869498</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2093,10 +2093,10 @@
         <v>52.63157894736842</v>
       </c>
       <c r="AG14" t="n">
-        <v>26.75224893688489</v>
+        <v>26.90236404365634</v>
       </c>
       <c r="AH14" t="n">
-        <v>25.87933001048353</v>
+        <v>25.72921490371208</v>
       </c>
       <c r="AI14" t="n">
         <v>37.25897138449667</v>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C15" t="n">
-        <v>12.14992759412509</v>
+        <v>12.21846578069799</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2143,19 +2143,19 @@
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>16.27559902090345</v>
+        <v>15.99936296068698</v>
       </c>
       <c r="K15" t="n">
-        <v>14.39813092132296</v>
+        <v>15.04345496790145</v>
       </c>
       <c r="L15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>57.14285714285715</v>
+        <v>60</v>
       </c>
       <c r="N15" t="n">
-        <v>29.7049020069249</v>
+        <v>35.52870565309881</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
@@ -2185,25 +2185,25 @@
         <v>79.56989247311827</v>
       </c>
       <c r="X15" t="n">
-        <v>14.79397220478775</v>
+        <v>15.04345496790145</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.3448275862069083</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="AA15" t="n">
-        <v>35.71428571428572</v>
+        <v>32.55813953488372</v>
       </c>
       <c r="AB15" t="n">
-        <v>13.76180696936258</v>
+        <v>14.74834399230339</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>9.688581314878874</v>
+        <v>9.999999999999998</v>
       </c>
       <c r="AE15" t="n">
         <v>31</v>
@@ -2212,10 +2212,10 @@
         <v>58.06451612903226</v>
       </c>
       <c r="AG15" t="n">
-        <v>25.2719114250453</v>
+        <v>24.45565362405026</v>
       </c>
       <c r="AH15" t="n">
-        <v>32.79260470398695</v>
+        <v>33.60886250498199</v>
       </c>
       <c r="AI15" t="n">
         <v>40.76626249536972</v>
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C16" t="n">
-        <v>37.33264949336706</v>
+        <v>37.44334655409082</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2265,22 +2265,22 @@
         <v>17.40096492560246</v>
       </c>
       <c r="K16" t="n">
-        <v>7.60637841449634</v>
+        <v>7.925447914445161</v>
       </c>
       <c r="L16" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M16" t="n">
-        <v>72.41379310344827</v>
+        <v>70.37037037037037</v>
       </c>
       <c r="N16" t="n">
-        <v>16.39294235019948</v>
+        <v>16.89668310275174</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>2.224423515382634</v>
+        <v>1.922208455599272</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2289,10 +2289,10 @@
         <v>67.85714285714286</v>
       </c>
       <c r="S16" t="n">
-        <v>54.06943234635268</v>
+        <v>54.20959311151343</v>
       </c>
       <c r="T16" t="n">
-        <v>13.78771051079018</v>
+        <v>13.64754974562943</v>
       </c>
       <c r="U16" t="n">
         <v>49.33884318085762</v>
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7474938441046524</v>
+        <v>0.7501276657901155</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2363,7 +2363,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>5</v>
       </c>
@@ -2374,22 +2378,22 @@
         <v>14.16674936134154</v>
       </c>
       <c r="K17" t="n">
-        <v>6.162471649579149</v>
+        <v>6.53653897096016</v>
       </c>
       <c r="L17" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M17" t="n">
-        <v>72.34042553191489</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N17" t="n">
-        <v>16.34482177016434</v>
+        <v>15.99393037286352</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>1.730864326978154</v>
+        <v>1.373670520157177</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2398,10 +2402,10 @@
         <v>65.21739130434783</v>
       </c>
       <c r="S17" t="n">
-        <v>46.09896089064624</v>
+        <v>46.12044224483081</v>
       </c>
       <c r="T17" t="n">
-        <v>19.11843041370159</v>
+        <v>19.09694905951702</v>
       </c>
       <c r="U17" t="n">
         <v>50.77005884206276</v>
@@ -2416,7 +2420,7 @@
         <v>15.7396793517258</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.274783337736825</v>
+        <v>7.951586208216321</v>
       </c>
       <c r="Z17" t="n">
         <v>26</v>
@@ -2425,13 +2429,13 @@
         <v>57.69230769230769</v>
       </c>
       <c r="AB17" t="n">
-        <v>10.53365232663279</v>
+        <v>10.81356870547704</v>
       </c>
       <c r="AC17" t="n">
         <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.880853188513587</v>
+        <v>2.225365660745937</v>
       </c>
       <c r="AE17" t="n">
         <v>35</v>
@@ -2440,10 +2444,10 @@
         <v>60</v>
       </c>
       <c r="AG17" t="n">
-        <v>42.74330625133689</v>
+        <v>42.74770185573249</v>
       </c>
       <c r="AH17" t="n">
-        <v>17.25669374866311</v>
+        <v>17.25229814426751</v>
       </c>
       <c r="AI17" t="n">
         <v>43.5727090128925</v>
@@ -2462,10 +2466,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1027909071899327</v>
+        <v>0.1040092919913096</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,25 +2494,25 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>25.10069993473878</v>
+        <v>24.80221998015493</v>
       </c>
       <c r="K18" t="n">
-        <v>2.864699332311571</v>
+        <v>4.083958794951736</v>
       </c>
       <c r="L18" t="n">
         <v>19</v>
       </c>
       <c r="M18" t="n">
-        <v>47.36842105263158</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="N18" t="n">
-        <v>18.59536970979411</v>
+        <v>16.99147144679783</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>6.936588269837207</v>
+        <v>5.683912558229109</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2549,10 +2553,10 @@
         <v>59.52380952380953</v>
       </c>
       <c r="AG18" t="n">
-        <v>39.49419406858492</v>
+        <v>39.52539606551272</v>
       </c>
       <c r="AH18" t="n">
-        <v>20.02961545522461</v>
+        <v>19.9984134582968</v>
       </c>
       <c r="AI18" t="n">
         <v>44.49431275003934</v>
@@ -2571,10 +2575,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02501455807267217</v>
+        <v>0.02500425625475245</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,25 +2603,25 @@
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>22.96673379938283</v>
+        <v>19.67465331637003</v>
       </c>
       <c r="K19" t="n">
-        <v>1.276654917705256</v>
+        <v>1.234945859506076</v>
       </c>
       <c r="L19" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="M19" t="n">
-        <v>56.52173913043478</v>
+        <v>65.625</v>
       </c>
       <c r="N19" t="n">
-        <v>23.20016366411376</v>
+        <v>20.64312188935456</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>8.61338191845209</v>
+        <v>8.658130911294283</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2680,10 +2684,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C20" t="n">
-        <v>1.8351015848173</v>
+        <v>1.85115531656963</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,19 +2744,19 @@
         <v>70.49180327868852</v>
       </c>
       <c r="X20" t="n">
-        <v>20.34011802710127</v>
+        <v>19.7256789664253</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.366229960125881</v>
+        <v>6.555856459426623</v>
       </c>
       <c r="Z20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="n">
-        <v>44.44444444444444</v>
+        <v>55</v>
       </c>
       <c r="AB20" t="n">
-        <v>12.96967327390692</v>
+        <v>11.03630868831303</v>
       </c>
       <c r="AC20" t="n">
         <v>4</v>
@@ -2789,10 +2793,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9387815995348399</v>
+        <v>0.9417568916649346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,40 +2821,40 @@
         <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>13.9640994031937</v>
+        <v>13.9566823466854</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5855817816229791</v>
+        <v>0.8956708092711541</v>
       </c>
       <c r="L21" t="n">
         <v>58</v>
       </c>
       <c r="M21" t="n">
-        <v>62.06896551724138</v>
+        <v>58.62068965517241</v>
       </c>
       <c r="N21" t="n">
-        <v>17.35617357110112</v>
+        <v>17.32124353265598</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>7.371253500799102</v>
+        <v>7.041262656510372</v>
       </c>
       <c r="Q21" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R21" t="n">
-        <v>70.73170731707317</v>
+        <v>72.5</v>
       </c>
       <c r="S21" t="n">
-        <v>45.01718077437626</v>
+        <v>46.14261029373566</v>
       </c>
       <c r="T21" t="n">
-        <v>25.71452654269692</v>
+        <v>26.35738970626434</v>
       </c>
       <c r="U21" t="n">
-        <v>55.52053227700284</v>
+        <v>57.16504419378943</v>
       </c>
       <c r="V21" t="n">
         <v>69</v>
@@ -2876,10 +2880,10 @@
         <v>61.53846153846154</v>
       </c>
       <c r="AG21" t="n">
-        <v>34.72910501900224</v>
+        <v>34.78776096001112</v>
       </c>
       <c r="AH21" t="n">
-        <v>26.8093565194593</v>
+        <v>26.75070057845042</v>
       </c>
       <c r="AI21" t="n">
         <v>45.89906145692508</v>
@@ -2898,19 +2902,19 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3209851210229357</v>
+        <v>0.3181213690009388</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2929,7 +2933,7 @@
         <v>20.35908649698318</v>
       </c>
       <c r="K22" t="n">
-        <v>8.211674487719378</v>
+        <v>7.246235963247294</v>
       </c>
       <c r="L22" t="n">
         <v>10</v>
@@ -2938,55 +2942,55 @@
         <v>60</v>
       </c>
       <c r="N22" t="n">
-        <v>13.06017923872908</v>
+        <v>13.1486425633712</v>
       </c>
       <c r="O22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P22" t="n">
-        <v>1.652617909062659</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>92.26190476190476</v>
+        <v>92.85714285714286</v>
       </c>
       <c r="T22" t="n">
-        <v>-42.26190476190476</v>
+        <v>-92.85714285714286</v>
       </c>
       <c r="U22" t="n">
-        <v>9.453120573423075</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>18</v>
       </c>
       <c r="W22" t="n">
-        <v>72.22222222222223</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="X22" t="n">
-        <v>13.73917753549452</v>
+        <v>13.74898285979678</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.859805712987675</v>
+        <v>5.716751686970745</v>
       </c>
       <c r="Z22" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA22" t="n">
-        <v>37.93103448275862</v>
+        <v>36</v>
       </c>
       <c r="AB22" t="n">
-        <v>15.47656683121236</v>
+        <v>15.59589356828433</v>
       </c>
       <c r="AC22" t="n">
         <v>6</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.198435945561216</v>
+        <v>0.3004227347883193</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3009,24 +3013,24 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8820258662137638</v>
+        <v>0.9207449126783517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -3036,17 +3040,27 @@
       <c r="I23" t="n">
         <v>10</v>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>11.24944735826469</v>
+      </c>
+      <c r="K23" t="n">
+        <v>9.714878230518309</v>
+      </c>
       <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="M23" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="N23" t="n">
+        <v>17.09663517999777</v>
+      </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
       <c r="Q23" t="n">
         <v>6</v>
       </c>
@@ -3069,10 +3083,10 @@
         <v>87.5</v>
       </c>
       <c r="X23" t="n">
-        <v>35.78212339899063</v>
+        <v>35.79382902042403</v>
       </c>
       <c r="Y23" t="n">
-        <v>6.714096244741762</v>
+        <v>2.627439240208052</v>
       </c>
       <c r="Z23" t="n">
         <v>5</v>
@@ -3081,13 +3095,13 @@
         <v>20</v>
       </c>
       <c r="AB23" t="n">
-        <v>18.16924423655518</v>
+        <v>8.545625828904191</v>
       </c>
       <c r="AC23" t="n">
         <v>6</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>3.463563794025826</v>
       </c>
       <c r="AE23" t="n">
         <v>10</v>
@@ -3118,10 +3132,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1830897401917416</v>
+        <v>0.1832244624362377</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3146,25 +3160,25 @@
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>23.26504282616538</v>
+        <v>22.86774633531589</v>
       </c>
       <c r="K24" t="n">
-        <v>4.603440704582229</v>
+        <v>4.68041066641065</v>
       </c>
       <c r="L24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M24" t="n">
-        <v>54.54545454545455</v>
+        <v>60</v>
       </c>
       <c r="N24" t="n">
-        <v>12.45279767872284</v>
+        <v>11.14400172635923</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>5.159064806155444</v>
+        <v>5.081742896998676</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3227,10 +3241,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C25" t="n">
-        <v>4.017043663238518</v>
+        <v>4.032198639352197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,10 +3286,10 @@
         <v>68.18181818181819</v>
       </c>
       <c r="S25" t="n">
-        <v>37.02646258844482</v>
+        <v>37.04152801544206</v>
       </c>
       <c r="T25" t="n">
-        <v>31.15535559337336</v>
+        <v>31.14029016637613</v>
       </c>
       <c r="U25" t="n">
         <v>53.44310393781777</v>
@@ -3304,10 +3318,10 @@
         <v>53.48837209302326</v>
       </c>
       <c r="AG25" t="n">
-        <v>50.76681922686738</v>
+        <v>50.9547405806394</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.721552866155882</v>
+        <v>2.533631512383863</v>
       </c>
       <c r="AI25" t="n">
         <v>38.91564047231397</v>
@@ -3326,10 +3340,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4435354270813355</v>
+        <v>0.4454539704846627</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,19 +3439,19 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C27" t="n">
-        <v>33.65403819756794</v>
+        <v>35.63631636124469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3453,10 +3467,10 @@
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>61.00365403217616</v>
+        <v>61.00029220182797</v>
       </c>
       <c r="K27" t="n">
-        <v>2.104591836734704</v>
+        <v>8.109400127579969</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3467,7 +3481,7 @@
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>5.773891317926294</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -3510,10 +3524,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C28" t="n">
-        <v>1.451474978255392</v>
+        <v>1.450877213110089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3538,19 +3552,19 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>24.87361787048376</v>
+        <v>20.14178232803948</v>
       </c>
       <c r="K28" t="n">
-        <v>4.097205798263182</v>
+        <v>4.054335144423549</v>
       </c>
       <c r="L28" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="M28" t="n">
-        <v>50</v>
+        <v>35.48387096774194</v>
       </c>
       <c r="N28" t="n">
-        <v>13.27856956737638</v>
+        <v>13.62202580110631</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
@@ -3559,19 +3573,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R28" t="n">
-        <v>57.5</v>
+        <v>56.41025641025641</v>
       </c>
       <c r="S28" t="n">
-        <v>59.09887512108735</v>
+        <v>60.17058821183797</v>
       </c>
       <c r="T28" t="n">
-        <v>-1.598875121087346</v>
+        <v>-3.760331801581557</v>
       </c>
       <c r="U28" t="n">
-        <v>42.19506854199106</v>
+        <v>40.97569164866947</v>
       </c>
       <c r="V28" t="n">
         <v>63</v>
@@ -3619,19 +3633,19 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3663896915779895</v>
+        <v>0.4030097634763746</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3647,25 +3661,25 @@
         <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>20.6615924080966</v>
+        <v>20.65475273479386</v>
       </c>
       <c r="K29" t="n">
-        <v>0.809713028054615</v>
+        <v>10.87592638756596</v>
       </c>
       <c r="L29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M29" t="n">
-        <v>50</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N29" t="n">
-        <v>19.30413149999403</v>
+        <v>22.43735037689824</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>3.164662289096642</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>6</v>
@@ -3692,7 +3706,7 @@
         <v>55.05052857749912</v>
       </c>
       <c r="Y29" t="n">
-        <v>20.01917898557388</v>
+        <v>12.02522205019785</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3734,10 +3748,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3840470289509206</v>
+        <v>0.3851495731431072</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3765,22 +3779,22 @@
         <v>21.6314445059014</v>
       </c>
       <c r="K30" t="n">
-        <v>3.888223734489604</v>
+        <v>4.186471993375851</v>
       </c>
       <c r="L30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M30" t="n">
-        <v>50</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="N30" t="n">
-        <v>11.96636906909726</v>
+        <v>11.52134526409605</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>1.070165823945368</v>
+        <v>0.7808384246621447</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3843,10 +3857,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1786754057959572</v>
+        <v>0.1781815721407131</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,10 +3889,10 @@
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>30.04424494288587</v>
+        <v>30.03821413731819</v>
       </c>
       <c r="K31" t="n">
-        <v>1.070156380561649</v>
+        <v>0.7821243924439392</v>
       </c>
       <c r="L31" t="n">
         <v>4</v>
@@ -3893,7 +3907,7 @@
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>8.835292176470588</v>
+        <v>9.146339852553421</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3956,10 +3970,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C32" t="n">
-        <v>2.326984338429703</v>
+        <v>2.386960780727496</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4016,25 +4030,25 @@
         <v>55.76923076923077</v>
       </c>
       <c r="X32" t="n">
-        <v>12.36180984775317</v>
+        <v>14.15775499371903</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.732997350744203</v>
+        <v>0.786027537117906</v>
       </c>
       <c r="Z32" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="AA32" t="n">
-        <v>40.38461538461539</v>
+        <v>27.65957446808511</v>
       </c>
       <c r="AB32" t="n">
-        <v>11.3712490544558</v>
+        <v>12.90964469105402</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>6.377524988346894</v>
+        <v>7.271125511662158</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4065,10 +4079,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C33" t="n">
-        <v>1.827744233999823</v>
+        <v>1.846952985068969</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4096,22 +4110,22 @@
         <v>12.57251846431013</v>
       </c>
       <c r="K33" t="n">
-        <v>2.442961579518288</v>
+        <v>3.519589978154136</v>
       </c>
       <c r="L33" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M33" t="n">
-        <v>61.11111111111111</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N33" t="n">
-        <v>11.15523360823073</v>
+        <v>11.1783669017964</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>1.519907660296527</v>
+        <v>0.4640764341775849</v>
       </c>
       <c r="Q33" t="n">
         <v>39</v>
@@ -4174,10 +4188,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8816054440349576</v>
+        <v>0.8846042831868146</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4205,22 +4219,22 @@
         <v>10.37797163438468</v>
       </c>
       <c r="K34" t="n">
-        <v>2.976714589375562</v>
+        <v>3.326996686122685</v>
       </c>
       <c r="L34" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M34" t="n">
-        <v>39.53488372093023</v>
+        <v>40.90909090909091</v>
       </c>
       <c r="N34" t="n">
-        <v>9.237561190015192</v>
+        <v>8.994868973026261</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>0.9937056301561276</v>
+        <v>0.6513334708853513</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4247,37 +4261,37 @@
         <v>14.68007915548277</v>
       </c>
       <c r="Y34" t="n">
-        <v>7.710179640731085</v>
+        <v>7.396249720624725</v>
       </c>
       <c r="Z34" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA34" t="n">
-        <v>53.84615384615385</v>
+        <v>48.14814814814815</v>
       </c>
       <c r="AB34" t="n">
-        <v>11.78261791778148</v>
+        <v>11.46261217295156</v>
       </c>
       <c r="AC34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AF34" t="n">
-        <v>53.84615384615385</v>
+        <v>52.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>27.93582805228828</v>
+        <v>26.7568759332134</v>
       </c>
       <c r="AH34" t="n">
-        <v>25.91032579386557</v>
+        <v>25.7431240667866</v>
       </c>
       <c r="AI34" t="n">
-        <v>38.56944827051576</v>
+        <v>37.49736210669248</v>
       </c>
       <c r="AJ34" t="n">
         <v>51</v>
@@ -4293,10 +4307,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C35" t="n">
-        <v>1.927592254885799</v>
+        <v>1.911039424743184</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4315,7 +4329,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %81.82: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4328,16 +4342,16 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>8.668496678956483</v>
+        <v>7.735326729336256</v>
       </c>
       <c r="L35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M35" t="n">
-        <v>77.77777777777777</v>
+        <v>81.81818181818181</v>
       </c>
       <c r="N35" t="n">
-        <v>13.16691766425628</v>
+        <v>13.27568040215743</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4370,7 +4384,7 @@
         <v>42.52272358489104</v>
       </c>
       <c r="Y35" t="n">
-        <v>16.22659004240077</v>
+        <v>16.94597819203719</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -4412,10 +4426,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08219068855799756</v>
+        <v>0.08194672014887143</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4440,19 +4454,19 @@
         <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>19.86910865198848</v>
+        <v>18.45194908889744</v>
       </c>
       <c r="K36" t="n">
-        <v>2.727276469795514</v>
+        <v>2.422348859942103</v>
       </c>
       <c r="L36" t="n">
         <v>20</v>
       </c>
       <c r="M36" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="N36" t="n">
-        <v>16.06371808191339</v>
+        <v>12.00877207999885</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4521,10 +4535,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0630619079279849</v>
+        <v>0.06408653485847907</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4552,22 +4566,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>2.65413892699049</v>
+        <v>4.322058574956089</v>
       </c>
       <c r="L37" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="M37" t="n">
-        <v>54.92957746478874</v>
+        <v>56.92307692307692</v>
       </c>
       <c r="N37" t="n">
-        <v>18.92950685343615</v>
+        <v>19.56677529205659</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>5.207642993149642</v>
+        <v>3.525564463819797</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4576,10 +4590,10 @@
         <v>55.55555555555556</v>
       </c>
       <c r="S37" t="n">
-        <v>35.29200562532744</v>
+        <v>35.22063979309204</v>
       </c>
       <c r="T37" t="n">
-        <v>20.26354993022812</v>
+        <v>20.33491576246352</v>
       </c>
       <c r="U37" t="n">
         <v>39.5810617556973</v>
@@ -4630,10 +4644,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C38" t="n">
-        <v>1.695314323625567</v>
+        <v>1.680958318926636</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4658,19 +4672,19 @@
         <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>16.52414407302303</v>
+        <v>16.08125753671009</v>
       </c>
       <c r="K38" t="n">
-        <v>7.004459556096343</v>
+        <v>6.098340553392068</v>
       </c>
       <c r="L38" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="M38" t="n">
-        <v>68.96551724137932</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="N38" t="n">
-        <v>12.47729186589563</v>
+        <v>12.00601244214094</v>
       </c>
       <c r="O38" t="n">
         <v>6</v>
@@ -4685,10 +4699,10 @@
         <v>52.94117647058823</v>
       </c>
       <c r="S38" t="n">
-        <v>48.79049758232556</v>
+        <v>49.08858960574084</v>
       </c>
       <c r="T38" t="n">
-        <v>4.150678888262675</v>
+        <v>3.852586864847396</v>
       </c>
       <c r="U38" t="n">
         <v>36.73671298006892</v>
@@ -4717,10 +4731,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="AG38" t="n">
-        <v>19.47451786828455</v>
+        <v>19.61707415469311</v>
       </c>
       <c r="AH38" t="n">
-        <v>37.6683392745726</v>
+        <v>37.52578298816404</v>
       </c>
       <c r="AI38" t="n">
         <v>40.85741114397492</v>
@@ -4739,10 +4753,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C39" t="n">
-        <v>2.720070167067869</v>
+        <v>2.723152604834223</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4770,16 +4784,16 @@
         <v>18.47027414490581</v>
       </c>
       <c r="K39" t="n">
-        <v>7.672617505630819</v>
+        <v>7.79463426336735</v>
       </c>
       <c r="L39" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M39" t="n">
-        <v>70.58823529411765</v>
+        <v>68.75</v>
       </c>
       <c r="N39" t="n">
-        <v>13.85968245525438</v>
+        <v>10.24116858981309</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4794,10 +4808,10 @@
         <v>65.11627906976744</v>
       </c>
       <c r="S39" t="n">
-        <v>49.81801559321186</v>
+        <v>50.36106194402293</v>
       </c>
       <c r="T39" t="n">
-        <v>15.29826347655558</v>
+        <v>14.75521712574452</v>
       </c>
       <c r="U39" t="n">
         <v>50.17178199285205</v>
@@ -4812,22 +4826,22 @@
         <v>10.2437411865161</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.332217369633105</v>
+        <v>2.221538290328184</v>
       </c>
       <c r="Z39" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="AA39" t="n">
-        <v>38.29787234042553</v>
+        <v>38</v>
       </c>
       <c r="AB39" t="n">
-        <v>11.65613829774405</v>
+        <v>11.50825751455693</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.755365926805132</v>
+        <v>3.864308809532102</v>
       </c>
       <c r="AE39" t="n">
         <v>42</v>
@@ -4858,24 +4872,24 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C40" t="n">
-        <v>0.197593970186511</v>
+        <v>0.2038161921775786</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4886,19 +4900,19 @@
         <v>10</v>
       </c>
       <c r="J40" t="n">
-        <v>14.73965458840789</v>
+        <v>13.0200875267008</v>
       </c>
       <c r="K40" t="n">
-        <v>7.91384724229669</v>
+        <v>11.31204766722833</v>
       </c>
       <c r="L40" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M40" t="n">
-        <v>66.66666666666667</v>
+        <v>55</v>
       </c>
       <c r="N40" t="n">
-        <v>11.52432638961163</v>
+        <v>12.78131349536254</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4931,37 +4945,37 @@
         <v>14.17330472629232</v>
       </c>
       <c r="Y40" t="n">
-        <v>5.482417714895282</v>
+        <v>2.50606485108168</v>
       </c>
       <c r="Z40" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AA40" t="n">
-        <v>41.66666666666666</v>
+        <v>56.25</v>
       </c>
       <c r="AB40" t="n">
-        <v>11.6504965019866</v>
+        <v>10.88111544832883</v>
       </c>
       <c r="AC40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>3.58374615157494</v>
       </c>
       <c r="AE40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF40" t="n">
-        <v>61.53846153846154</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="AG40" t="n">
-        <v>14.37537416937274</v>
+        <v>15.24897860424176</v>
       </c>
       <c r="AH40" t="n">
-        <v>47.1630873690888</v>
+        <v>43.08435472909157</v>
       </c>
       <c r="AI40" t="n">
-        <v>35.5228915126657</v>
+        <v>31.95113125495497</v>
       </c>
       <c r="AJ40" t="n">
         <v>36</v>
@@ -4977,10 +4991,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C41" t="n">
-        <v>1.72684527758956</v>
+        <v>1.715628116402826</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4999,7 +5013,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -5012,16 +5026,16 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>14.11967076389578</v>
+        <v>13.37837751768067</v>
       </c>
       <c r="L41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M41" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N41" t="n">
-        <v>8.290318992161135</v>
+        <v>12.17975430538131</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
@@ -5054,16 +5068,16 @@
         <v>40.81782021738603</v>
       </c>
       <c r="Y41" t="n">
-        <v>11.4417446308324</v>
+        <v>12.01699722455548</v>
       </c>
       <c r="Z41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA41" t="n">
-        <v>16.66666666666667</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AB41" t="n">
-        <v>22.19906898574699</v>
+        <v>17.85423125778112</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
@@ -5100,10 +5114,10 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C42" t="n">
-        <v>3.38011832905293</v>
+        <v>3.353511974431711</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5131,16 +5145,16 @@
         <v>21.11518617286606</v>
       </c>
       <c r="K42" t="n">
-        <v>9.97284435744772</v>
+        <v>9.107201142969434</v>
       </c>
       <c r="L42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M42" t="n">
-        <v>33.33333333333334</v>
+        <v>60</v>
       </c>
       <c r="N42" t="n">
-        <v>22.80470238649248</v>
+        <v>12.88139896333518</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
@@ -5168,25 +5182,25 @@
       </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="n">
-        <v>14.965394631075</v>
+        <v>14.97530566614946</v>
       </c>
       <c r="Y42" t="n">
-        <v>4.342654839439664</v>
+        <v>5.103795540425937</v>
       </c>
       <c r="Z42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA42" t="n">
-        <v>36.36363636363637</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB42" t="n">
-        <v>12.02158046138136</v>
+        <v>9.790507698665648</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>5.91417747488655</v>
+        <v>5.15953666161627</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5215,10 +5229,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C43" t="n">
-        <v>7.120740436868295</v>
+        <v>7.212361787144599</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5278,16 +5292,16 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>8.090278152874186</v>
+        <v>6.907691469113997</v>
       </c>
       <c r="Z43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA43" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AB43" t="n">
-        <v>13.63280086769262</v>
+        <v>13.09070057304151</v>
       </c>
       <c r="AC43" t="n">
         <v>2</v>
@@ -5324,10 +5338,10 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C44" t="n">
-        <v>5.028136061345057</v>
+        <v>5.023964303865056</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,13 +5369,13 @@
         <v>13.03201987649729</v>
       </c>
       <c r="K44" t="n">
-        <v>2.912599140912886</v>
+        <v>2.8272143382714</v>
       </c>
       <c r="L44" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M44" t="n">
-        <v>70.83333333333333</v>
+        <v>68</v>
       </c>
       <c r="N44" t="n">
         <v>17.94687033846331</v>
@@ -5370,7 +5384,7 @@
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>6.886815529148871</v>
+        <v>6.975571309490358</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5397,7 +5411,7 @@
         <v>12.1234692799834</v>
       </c>
       <c r="Y44" t="n">
-        <v>8.214935016031344</v>
+        <v>8.291087496140804</v>
       </c>
       <c r="Z44" t="n">
         <v>7</v>
@@ -5412,7 +5426,7 @@
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.944831639309119</v>
+        <v>1.86340940831381</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5435,10 +5449,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02102063597599497</v>
+        <v>0.02101197898658295</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5463,25 +5477,25 @@
         <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>10.6275101427813</v>
+        <v>10.56080028712586</v>
       </c>
       <c r="K45" t="n">
-        <v>4.095945255934885</v>
+        <v>4.053075121228056</v>
       </c>
       <c r="L45" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M45" t="n">
-        <v>57.4468085106383</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="N45" t="n">
-        <v>17.80916416571605</v>
+        <v>17.35967966641912</v>
       </c>
       <c r="O45" t="n">
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>5.671743245665484</v>
+        <v>5.715280275804857</v>
       </c>
       <c r="Q45" t="n">
         <v>37</v>
@@ -5544,10 +5558,10 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C46" t="n">
-        <v>9.02310799269584</v>
+        <v>9.014138985244088</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5561,7 +5575,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -5575,22 +5589,22 @@
         <v>20.98614247885408</v>
       </c>
       <c r="K46" t="n">
-        <v>9.275239196407137</v>
+        <v>9.166619147147181</v>
       </c>
       <c r="L46" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M46" t="n">
-        <v>58.8235294117647</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N46" t="n">
-        <v>16.01315420628742</v>
+        <v>15.19441695119586</v>
       </c>
       <c r="O46" t="n">
         <v>10</v>
       </c>
       <c r="P46" t="n">
-        <v>0.6632433924854686</v>
+        <v>0.7634026402608463</v>
       </c>
       <c r="Q46" t="n">
         <v>54</v>
@@ -5613,17 +5627,27 @@
       <c r="W46" t="n">
         <v>66.26506024096386</v>
       </c>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
+      <c r="X46" t="n">
+        <v>10.37534045472048</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.0951008645533</v>
+      </c>
       <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="inlineStr"/>
-      <c r="AB46" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>42.5925925925926</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>13.21801222200241</v>
+      </c>
       <c r="AC46" t="n">
         <v>3</v>
       </c>
-      <c r="AD46" t="inlineStr"/>
+      <c r="AD46" t="n">
+        <v>1.925990675990696</v>
+      </c>
       <c r="AE46" t="n">
         <v>38</v>
       </c>
@@ -5631,10 +5655,10 @@
         <v>57.89473684210526</v>
       </c>
       <c r="AG46" t="n">
-        <v>17.68276374282521</v>
+        <v>17.01873734472678</v>
       </c>
       <c r="AH46" t="n">
-        <v>40.21197309928006</v>
+        <v>40.87599949737848</v>
       </c>
       <c r="AI46" t="n">
         <v>42.19234534367055</v>
@@ -5653,10 +5677,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7971024777419653</v>
+        <v>0.7942527897237316</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5681,25 +5705,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>25.31303456031801</v>
+        <v>24.7868707712232</v>
       </c>
       <c r="K47" t="n">
-        <v>6.934954256661641</v>
+        <v>6.552655535499929</v>
       </c>
       <c r="L47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M47" t="n">
-        <v>60</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N47" t="n">
-        <v>13.69328890768449</v>
+        <v>12.37065508502562</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>2.866271150200106</v>
+        <v>3.23534354650743</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5762,10 +5786,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C48" t="n">
-        <v>0.06159046488110978</v>
+        <v>0.06135498032178054</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5790,10 +5814,10 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>30.07074365952763</v>
+        <v>28.7395090084999</v>
       </c>
       <c r="K48" t="n">
-        <v>4.947247261270582</v>
+        <v>4.545992678733457</v>
       </c>
       <c r="L48" t="n">
         <v>14</v>
@@ -5802,13 +5826,13 @@
         <v>71.42857142857143</v>
       </c>
       <c r="N48" t="n">
-        <v>11.93146999034344</v>
+        <v>12.06150998109382</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>4.814564336452176</v>
+        <v>5.216849715155081</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5871,10 +5895,10 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2602354756950876</v>
+        <v>0.2605485314490766</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5902,22 +5926,22 @@
         <v>23.59168796028241</v>
       </c>
       <c r="K49" t="n">
-        <v>2.985172430376415</v>
+        <v>3.109060615562398</v>
       </c>
       <c r="L49" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M49" t="n">
-        <v>57.14285714285715</v>
+        <v>50</v>
       </c>
       <c r="N49" t="n">
-        <v>9.669209748173083</v>
+        <v>10.06022013884285</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>1.956424912514199</v>
+        <v>1.833921648736458</v>
       </c>
       <c r="Q49" t="n">
         <v>53</v>
@@ -5926,10 +5950,10 @@
         <v>73.58490566037736</v>
       </c>
       <c r="S49" t="n">
-        <v>38.5102534828344</v>
+        <v>38.77300867067283</v>
       </c>
       <c r="T49" t="n">
-        <v>35.07465217754296</v>
+        <v>34.81189698970453</v>
       </c>
       <c r="U49" t="n">
         <v>60.41933558938148</v>
@@ -5958,10 +5982,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="AG49" t="n">
-        <v>34.9341277788763</v>
+        <v>34.52525732504036</v>
       </c>
       <c r="AH49" t="n">
-        <v>26.76799988069816</v>
+        <v>27.1768703345341</v>
       </c>
       <c r="AI49" t="n">
         <v>47.42656695641357</v>
@@ -5980,10 +6004,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7273139726078529</v>
+        <v>0.7282751885231683</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6011,7 +6035,7 @@
         <v>11.86078125763058</v>
       </c>
       <c r="K50" t="n">
-        <v>1.792673322690486</v>
+        <v>1.927202207526069</v>
       </c>
       <c r="L50" t="n">
         <v>63</v>
@@ -6020,13 +6044,13 @@
         <v>47.61904761904762</v>
       </c>
       <c r="N50" t="n">
-        <v>13.63160196619841</v>
+        <v>13.98988835133535</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>2.168453391839043</v>
+        <v>2.033606090995876</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6089,10 +6113,10 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1845611781936641</v>
+        <v>0.1838548161326009</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6111,7 +6135,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -6121,19 +6145,19 @@
         <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>27.30972539236674</v>
+        <v>27.11346359280836</v>
       </c>
       <c r="K51" t="n">
-        <v>6.971882855186662</v>
+        <v>6.562474547389008</v>
       </c>
       <c r="L51" t="n">
         <v>4</v>
       </c>
       <c r="M51" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N51" t="n">
-        <v>19.54837245931199</v>
+        <v>22.48074903415539</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
@@ -6166,7 +6190,7 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>16.21561330359341</v>
+        <v>16.53627723005412</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6208,10 +6232,10 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C52" t="n">
-        <v>4.334455074137223</v>
+        <v>4.26753306034807</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6271,22 +6295,22 @@
         <v>12.1710603868542</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.546273479254944</v>
+        <v>2.081793756605776</v>
       </c>
       <c r="Z52" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA52" t="n">
-        <v>33.9622641509434</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="AB52" t="n">
-        <v>10.55744009261507</v>
+        <v>12.49481897677179</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>7.494667903862084</v>
+        <v>6.044030492841546</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6295,10 +6319,10 @@
         <v>68.42105263157895</v>
       </c>
       <c r="AG52" t="n">
-        <v>36.16335835852274</v>
+        <v>35.57125309536485</v>
       </c>
       <c r="AH52" t="n">
-        <v>32.25769427305621</v>
+        <v>32.8497995362141</v>
       </c>
       <c r="AI52" t="n">
         <v>52.54424010939046</v>
@@ -6317,19 +6341,19 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C53" t="n">
-        <v>1.650119924115605</v>
+        <v>1.63683319520314</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6352,7 +6376,7 @@
         <v>28.17598592067425</v>
       </c>
       <c r="K53" t="n">
-        <v>8.789135168275974</v>
+        <v>7.913167472547977</v>
       </c>
       <c r="L53" t="n">
         <v>5</v>
@@ -6361,13 +6385,13 @@
         <v>80</v>
       </c>
       <c r="N53" t="n">
-        <v>13.45498152972782</v>
+        <v>13.60621978110839</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>0.08046518278144177</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6409,10 +6433,10 @@
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="inlineStr"/>
       <c r="AJ53" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK53" t="n">
-        <v>71.42857142857143</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54">
@@ -6422,10 +6446,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08450295620308704</v>
+        <v>0.08719971489551716</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6453,22 +6477,22 @@
         <v>42.39442432818535</v>
       </c>
       <c r="K54" t="n">
-        <v>4.544058882728019</v>
+        <v>7.880393044296952</v>
       </c>
       <c r="L54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M54" t="n">
-        <v>60</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N54" t="n">
-        <v>28.91863102314376</v>
+        <v>25.74621644893126</v>
       </c>
       <c r="O54" t="n">
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>5.21879595605923</v>
+        <v>1.964774965950222</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6486,16 +6510,16 @@
         <v>35.42021355803963</v>
       </c>
       <c r="V54" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="W54" t="n">
-        <v>69.81132075471699</v>
+        <v>68.51851851851852</v>
       </c>
       <c r="X54" t="n">
         <v>114.7400208810756</v>
       </c>
       <c r="Y54" t="n">
-        <v>39.77679304992365</v>
+        <v>37.85487854981646</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -6537,10 +6561,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8921157620229551</v>
+        <v>0.8917483594041693</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6568,7 +6592,7 @@
         <v>12.31616646597832</v>
       </c>
       <c r="K55" t="n">
-        <v>6.346998519069458</v>
+        <v>6.303201326575825</v>
       </c>
       <c r="L55" t="n">
         <v>49</v>
@@ -6610,7 +6634,7 @@
         <v>25.41488056506582</v>
       </c>
       <c r="Y55" t="n">
-        <v>6.750874850110633</v>
+        <v>6.789277907469316</v>
       </c>
       <c r="Z55" t="n">
         <v>21</v>
@@ -6619,7 +6643,7 @@
         <v>61.90476190476191</v>
       </c>
       <c r="AB55" t="n">
-        <v>9.916378758105774</v>
+        <v>9.948561667779504</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6634,10 +6658,10 @@
         <v>54.16666666666666</v>
       </c>
       <c r="AG55" t="n">
-        <v>40.77810011195715</v>
+        <v>40.55679911762984</v>
       </c>
       <c r="AH55" t="n">
-        <v>13.38856655470951</v>
+        <v>13.60986754903682</v>
       </c>
       <c r="AI55" t="n">
         <v>40.2910745456498</v>
@@ -6656,10 +6680,10 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C56" t="n">
-        <v>0.887070854162671</v>
+        <v>0.8854447816772985</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6687,7 +6711,7 @@
         <v>34.38683570496719</v>
       </c>
       <c r="K56" t="n">
-        <v>13.12057565201068</v>
+        <v>12.9132165050676</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6714,25 +6738,25 @@
         <v>100</v>
       </c>
       <c r="X56" t="n">
-        <v>18.2672887877857</v>
+        <v>18.27748447537585</v>
       </c>
       <c r="Y56" t="n">
-        <v>4.351763863472069</v>
+        <v>4.535324701993481</v>
       </c>
       <c r="Z56" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA56" t="n">
-        <v>20</v>
+        <v>14.28571428571429</v>
       </c>
       <c r="AB56" t="n">
-        <v>13.60730707672086</v>
+        <v>14.3406155753398</v>
       </c>
       <c r="AC56" t="n">
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>5.905217246730676</v>
+        <v>5.724290457122239</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6755,10 +6779,10 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C57" t="n">
-        <v>1.420994959815687</v>
+        <v>1.42251091330513</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6790,7 +6814,7 @@
         <v>32.76213282665623</v>
       </c>
       <c r="K57" t="n">
-        <v>21.6758539748358</v>
+        <v>21.80566086411435</v>
       </c>
       <c r="L57" t="n">
         <v>3</v>
@@ -6832,7 +6856,7 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>12.39487541241547</v>
+        <v>12.30141604199737</v>
       </c>
       <c r="Z57" t="n">
         <v>5</v>
@@ -6878,10 +6902,10 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7697756669488552</v>
+        <v>0.7631550702789794</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6913,7 +6937,7 @@
         <v>16.33691982084211</v>
       </c>
       <c r="K58" t="n">
-        <v>3.773666904155992</v>
+        <v>2.881142467459163</v>
       </c>
       <c r="L58" t="n">
         <v>28</v>
@@ -6922,13 +6946,13 @@
         <v>85.71428571428571</v>
       </c>
       <c r="N58" t="n">
-        <v>19.44892960831233</v>
+        <v>19.66632034833653</v>
       </c>
       <c r="O58" t="n">
         <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>1.18173823131511</v>
+        <v>2.059519832034362</v>
       </c>
       <c r="Q58" t="n">
         <v>24</v>
@@ -6955,7 +6979,7 @@
         <v>41.32985472592288</v>
       </c>
       <c r="Y58" t="n">
-        <v>13.17975385312373</v>
+        <v>13.92646728821598</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -6997,10 +7021,10 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8113965165118328</v>
+        <v>0.810642187754292</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7017,11 +7041,7 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %76.47: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>5</v>
       </c>
@@ -7064,16 +7084,16 @@
         <v>10.2478061424703</v>
       </c>
       <c r="Y59" t="n">
-        <v>7.869230357341772</v>
+        <v>7.954881315389494</v>
       </c>
       <c r="Z59" t="n">
         <v>17</v>
       </c>
       <c r="AA59" t="n">
-        <v>76.47058823529412</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="AB59" t="n">
-        <v>13.17365761123391</v>
+        <v>13.8254719095032</v>
       </c>
       <c r="AC59" t="n">
         <v>6</v>
@@ -7110,10 +7130,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C60" t="n">
-        <v>13.20095939292484</v>
+        <v>13.29007670901372</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7141,22 +7161,22 @@
         <v>17.06238107085701</v>
       </c>
       <c r="K60" t="n">
-        <v>3.890110512483336</v>
+        <v>4.591454069529011</v>
       </c>
       <c r="L60" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M60" t="n">
-        <v>54.54545454545455</v>
+        <v>48.38709677419355</v>
       </c>
       <c r="N60" t="n">
-        <v>11.5632679575326</v>
+        <v>12.05258119927817</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>3.955996838623865</v>
+        <v>3.258914373831256</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7219,10 +7239,10 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C61" t="n">
-        <v>0.620529183680864</v>
+        <v>0.6219545859874075</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7251,10 +7271,10 @@
         <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>34.04035822988622</v>
+        <v>32.27682383221734</v>
       </c>
       <c r="K61" t="n">
-        <v>0.2717388877710114</v>
+        <v>0.4934072082516616</v>
       </c>
       <c r="L61" t="n">
         <v>8</v>
@@ -7263,13 +7283,13 @@
         <v>75</v>
       </c>
       <c r="N61" t="n">
-        <v>20.85686400970598</v>
+        <v>16.22363039036922</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>9.701897284455541</v>
+        <v>9.459916879967967</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7324,19 +7344,19 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C62" t="n">
-        <v>8.518612729271961</v>
+        <v>8.840790158604777</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7352,25 +7372,25 @@
         <v>10</v>
       </c>
       <c r="J62" t="n">
-        <v>13.30115949155629</v>
+        <v>12.64888173871529</v>
       </c>
       <c r="K62" t="n">
-        <v>2.376864509173293</v>
+        <v>6.24879953885018</v>
       </c>
       <c r="L62" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="M62" t="n">
-        <v>53.73134328358209</v>
+        <v>71.11111111111111</v>
       </c>
       <c r="N62" t="n">
-        <v>14.63649661857709</v>
+        <v>12.3763888608676</v>
       </c>
       <c r="O62" t="n">
         <v>6</v>
       </c>
       <c r="P62" t="n">
-        <v>3.539017832004476</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>29</v>
@@ -7433,10 +7453,10 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1040521440872542</v>
+        <v>0.1033789382949465</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7465,10 +7485,10 @@
         <v>10</v>
       </c>
       <c r="J63" t="n">
-        <v>31.19925725463639</v>
+        <v>31.14790266414816</v>
       </c>
       <c r="K63" t="n">
-        <v>4.274741686449013</v>
+        <v>3.600095712447282</v>
       </c>
       <c r="L63" t="n">
         <v>3</v>
@@ -7477,13 +7497,13 @@
         <v>100</v>
       </c>
       <c r="N63" t="n">
-        <v>9.443683317782943</v>
+        <v>8.331563656967848</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>0.6955263583695359</v>
+        <v>1.351257716439092</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7510,22 +7530,22 @@
         <v>10.24796802016521</v>
       </c>
       <c r="Y63" t="n">
-        <v>5.417992223333901</v>
+        <v>6.029927287641257</v>
       </c>
       <c r="Z63" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA63" t="n">
-        <v>50</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="AB63" t="n">
-        <v>13.37630344651862</v>
+        <v>12.46566142394676</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>4.844481402303769</v>
+        <v>4.224826689781425</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7556,10 +7576,10 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1561833217281345</v>
+        <v>0.1563291249208959</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7584,25 +7604,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>24.54410599778878</v>
+        <v>20.54832742781827</v>
       </c>
       <c r="K64" t="n">
-        <v>0.4054017512783448</v>
+        <v>0.5405399926954102</v>
       </c>
       <c r="L64" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="M64" t="n">
-        <v>70</v>
+        <v>63.41463414634146</v>
       </c>
       <c r="N64" t="n">
-        <v>16.17568740291264</v>
+        <v>14.00923472969788</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.576046874552908</v>
+        <v>4.435484440036408</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7611,10 +7631,10 @@
         <v>70.37037037037037</v>
       </c>
       <c r="S64" t="n">
-        <v>74.20087527580721</v>
+        <v>74.33196236101367</v>
       </c>
       <c r="T64" t="n">
-        <v>-3.83050490543684</v>
+        <v>-3.961591990643299</v>
       </c>
       <c r="U64" t="n">
         <v>57.17242709884697</v>
@@ -7643,10 +7663,10 @@
         <v>61.53846153846154</v>
       </c>
       <c r="AG64" t="n">
-        <v>38.05195226551255</v>
+        <v>38.55549511678084</v>
       </c>
       <c r="AH64" t="n">
-        <v>23.48650927294899</v>
+        <v>22.9829664216807</v>
       </c>
       <c r="AI64" t="n">
         <v>47.95987371581939</v>
@@ -7665,10 +7685,10 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C65" t="n">
-        <v>6.138025704990531</v>
+        <v>6.146003853575514</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7687,7 +7707,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %88.24: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %82.35: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -7700,22 +7720,22 @@
         <v>28.12381406175567</v>
       </c>
       <c r="K65" t="n">
-        <v>1.131897776644575</v>
+        <v>1.26334807449644</v>
       </c>
       <c r="L65" t="n">
         <v>17</v>
       </c>
       <c r="M65" t="n">
-        <v>88.23529411764706</v>
+        <v>82.35294117647059</v>
       </c>
       <c r="N65" t="n">
-        <v>13.77843664472946</v>
+        <v>15.22565301073229</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>8.768847829733328</v>
+        <v>8.627654617025172</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7724,10 +7744,10 @@
         <v>68</v>
       </c>
       <c r="S65" t="n">
-        <v>45.64229607195782</v>
+        <v>45.74951102699886</v>
       </c>
       <c r="T65" t="n">
-        <v>22.35770392804218</v>
+        <v>22.25048897300114</v>
       </c>
       <c r="U65" t="n">
         <v>54.18970269185592</v>
@@ -7756,10 +7776,10 @@
         <v>54.54545454545455</v>
       </c>
       <c r="AG65" t="n">
-        <v>20.98624104431364</v>
+        <v>20.99388046371777</v>
       </c>
       <c r="AH65" t="n">
-        <v>33.5592135011409</v>
+        <v>33.55157408173678</v>
       </c>
       <c r="AI65" t="n">
         <v>40.06618319896197</v>
@@ -7778,10 +7798,10 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4254576673193919</v>
+        <v>0.4265431574585299</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7877,10 +7897,10 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02837785898800593</v>
+        <v>0.02815605247238052</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7908,7 +7928,7 @@
         <v>18.49825117353735</v>
       </c>
       <c r="K67" t="n">
-        <v>5.397146407544984</v>
+        <v>4.573343110354777</v>
       </c>
       <c r="L67" t="n">
         <v>2</v>
@@ -7933,20 +7953,18 @@
       </c>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="n">
-        <v>10.86217886339589</v>
+        <v>10.87173616493582</v>
       </c>
       <c r="Y67" t="n">
-        <v>4.929573378297835</v>
+        <v>5.680792303289417</v>
       </c>
       <c r="Z67" t="n">
         <v>3</v>
       </c>
       <c r="AA67" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>5.358269135191785</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
         <v>3</v>
       </c>
@@ -7972,44 +7990,58 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C68" t="n">
-        <v>3.914042354617323</v>
+        <v>3.454369217221166</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+          <t>VERİ_YETERSİZ</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H68" t="n">
         <v>5</v>
       </c>
       <c r="I68" t="n">
         <v>10</v>
       </c>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+      <c r="J68" t="n">
+        <v>12.03526755137827</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
       <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="M68" t="n">
+        <v>80</v>
+      </c>
+      <c r="N68" t="n">
+        <v>15.55496830427127</v>
+      </c>
       <c r="O68" t="n">
         <v>2</v>
       </c>
-      <c r="P68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>2.000000000000002</v>
+      </c>
       <c r="Q68" t="n">
         <v>5</v>
       </c>
@@ -8032,13 +8064,13 @@
         <v>80</v>
       </c>
       <c r="X68" t="n">
-        <v>119.0700097329771</v>
+        <v>119.0888955077547</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.3212024037490879</v>
+        <v>12.03526755137827</v>
       </c>
       <c r="Z68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="inlineStr"/>
       <c r="AB68" t="inlineStr"/>
@@ -8046,7 +8078,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>7.703541556905503</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8077,19 +8109,19 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4067493141233443</v>
+        <v>0.4002781837253012</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -8097,7 +8129,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H69" t="n">
         <v>5</v>
       </c>
@@ -8108,22 +8144,22 @@
         <v>29.4573350207784</v>
       </c>
       <c r="K69" t="n">
-        <v>4.045030632044866</v>
+        <v>2.389738448112189</v>
       </c>
       <c r="L69" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M69" t="n">
-        <v>71.42857142857143</v>
+        <v>80</v>
       </c>
       <c r="N69" t="n">
-        <v>15.30141509712112</v>
+        <v>16.19449547156433</v>
       </c>
       <c r="O69" t="n">
         <v>3</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>0.5960182740354147</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8170,19 +8206,19 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4237760181229631</v>
+        <v>0.4139360020047883</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -8201,22 +8237,22 @@
         <v>20.66985845799666</v>
       </c>
       <c r="K70" t="n">
-        <v>8.709178062490475</v>
+        <v>6.184967114767459</v>
       </c>
       <c r="L70" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M70" t="n">
-        <v>63.63636363636363</v>
+        <v>50</v>
       </c>
       <c r="N70" t="n">
-        <v>7.201184133223345</v>
+        <v>8.934628394870565</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.709312471011848</v>
       </c>
       <c r="Q70" t="n">
         <v>30</v>
@@ -8225,10 +8261,10 @@
         <v>56.66666666666666</v>
       </c>
       <c r="S70" t="n">
-        <v>33.67748580003482</v>
+        <v>33.76081913336815</v>
       </c>
       <c r="T70" t="n">
-        <v>22.98918086663185</v>
+        <v>22.90584753329851</v>
       </c>
       <c r="U70" t="n">
         <v>39.19730700081361</v>
@@ -8257,10 +8293,10 @@
         <v>48.83720930232558</v>
       </c>
       <c r="AG70" t="n">
-        <v>34.68090534379679</v>
+        <v>34.62276580891307</v>
       </c>
       <c r="AH70" t="n">
-        <v>14.15630395852879</v>
+        <v>14.21444349341251</v>
       </c>
       <c r="AI70" t="n">
         <v>34.61744754671859</v>
@@ -8279,10 +8315,10 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C71" t="n">
-        <v>3.277117020431736</v>
+        <v>3.284172379689451</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8299,11 +8335,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.67: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>5</v>
       </c>
@@ -8314,22 +8346,22 @@
         <v>20.51701021225919</v>
       </c>
       <c r="K71" t="n">
-        <v>4.606922922960655</v>
+        <v>4.832132891803465</v>
       </c>
       <c r="L71" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M71" t="n">
-        <v>76.66666666666667</v>
+        <v>68.96551724137932</v>
       </c>
       <c r="N71" t="n">
-        <v>11.96068581999267</v>
+        <v>11.98090556200918</v>
       </c>
       <c r="O71" t="n">
         <v>6</v>
       </c>
       <c r="P71" t="n">
-        <v>1.331725509281356</v>
+        <v>1.1140354354918</v>
       </c>
       <c r="Q71" t="n">
         <v>43</v>
@@ -8370,10 +8402,10 @@
         <v>54.83870967741935</v>
       </c>
       <c r="AG71" t="n">
-        <v>14.91604026428609</v>
+        <v>14.94127772585631</v>
       </c>
       <c r="AH71" t="n">
-        <v>39.92266941313326</v>
+        <v>39.89743195156304</v>
       </c>
       <c r="AI71" t="n">
         <v>37.77216763735451</v>
@@ -8392,10 +8424,10 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07840697261087394</v>
+        <v>0.07753420372120984</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8423,16 +8455,16 @@
         <v>20.36571476939619</v>
       </c>
       <c r="K72" t="n">
-        <v>9.617786300994947</v>
+        <v>8.397601533599808</v>
       </c>
       <c r="L72" t="n">
         <v>13</v>
       </c>
       <c r="M72" t="n">
-        <v>69.23076923076923</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N72" t="n">
-        <v>14.39782702990865</v>
+        <v>14.52327366036347</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
@@ -8465,10 +8497,10 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>12.70665939359192</v>
+        <v>13.67834481159975</v>
       </c>
       <c r="Z72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr"/>
@@ -8507,10 +8539,10 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C73" t="n">
-        <v>0.06936809766975159</v>
+        <v>0.06891929044563272</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8535,25 +8567,25 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>21.93799671486063</v>
+        <v>22.20804087883598</v>
       </c>
       <c r="K73" t="n">
-        <v>0.6097554933819138</v>
+        <v>0.3058100936135233</v>
       </c>
       <c r="L73" t="n">
         <v>22</v>
       </c>
       <c r="M73" t="n">
-        <v>68.18181818181819</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N73" t="n">
-        <v>16.34029941072919</v>
+        <v>17.02474442198509</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>9.333333989898996</v>
+        <v>9.664634478639943</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8616,10 +8648,10 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C74" t="n">
-        <v>5.007115425369062</v>
+        <v>4.98194034589189</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8647,22 +8679,22 @@
         <v>18.35970785011217</v>
       </c>
       <c r="K74" t="n">
-        <v>5.936037009185791</v>
+        <v>5.403405359096292</v>
       </c>
       <c r="L74" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M74" t="n">
-        <v>62.96296296296296</v>
+        <v>63.33333333333334</v>
       </c>
       <c r="N74" t="n">
-        <v>19.58729280616051</v>
+        <v>19.98684471942212</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>1.948310555203459</v>
+        <v>2.463482685457308</v>
       </c>
       <c r="Q74" t="n">
         <v>35</v>
@@ -8689,7 +8721,7 @@
         <v>95.98093909010421</v>
       </c>
       <c r="Y74" t="n">
-        <v>13.51350989368744</v>
+        <v>13.94835192890326</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
@@ -8731,10 +8763,10 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1343218611539252</v>
+        <v>0.1334260644636039</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8748,7 +8780,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -8759,25 +8791,25 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>19.1703426786477</v>
+        <v>19.32404686587293</v>
       </c>
       <c r="K75" t="n">
-        <v>3.077163040832698</v>
+        <v>2.584811606609261</v>
       </c>
       <c r="L75" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M75" t="n">
-        <v>55.55555555555556</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N75" t="n">
-        <v>12.26647622156585</v>
+        <v>10.83572863913616</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>2.835581493457928</v>
+        <v>3.329136487073026</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8800,27 +8832,17 @@
       <c r="W75" t="n">
         <v>100</v>
       </c>
-      <c r="X75" t="n">
-        <v>17.02929186229787</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>11.92191168505222</v>
-      </c>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA75" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>12.35746193532061</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
         <v>10</v>
       </c>
-      <c r="AD75" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD75" t="inlineStr"/>
       <c r="AE75" t="n">
         <v>4</v>
       </c>
@@ -8850,10 +8872,10 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C76" t="n">
-        <v>1.88134691985155</v>
+        <v>1.867964964055552</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8881,37 +8903,37 @@
         <v>20.51082830683794</v>
       </c>
       <c r="K76" t="n">
-        <v>8.549567754614863</v>
+        <v>7.777458420584393</v>
       </c>
       <c r="L76" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M76" t="n">
-        <v>63.63636363636363</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N76" t="n">
-        <v>10.0083946713961</v>
+        <v>9.784914623553925</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>1.336193478599546</v>
+        <v>2.062158091298172</v>
       </c>
       <c r="Q76" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="R76" t="n">
-        <v>64.28571428571429</v>
+        <v>62.5</v>
       </c>
       <c r="S76" t="n">
-        <v>29.97166714253549</v>
+        <v>31.61089190017208</v>
       </c>
       <c r="T76" t="n">
-        <v>34.3140471431788</v>
+        <v>30.88910809982792</v>
       </c>
       <c r="U76" t="n">
-        <v>49.16636571945582</v>
+        <v>47.0324391373011</v>
       </c>
       <c r="V76" t="n">
         <v>56</v>
@@ -8959,10 +8981,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5238342502034455</v>
+        <v>0.5215173119332754</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8987,19 +9009,19 @@
         <v>10</v>
       </c>
       <c r="J77" t="n">
-        <v>21.60005234598619</v>
+        <v>20.65935288471739</v>
       </c>
       <c r="K77" t="n">
-        <v>7.886825761260052</v>
+        <v>7.409638339176916</v>
       </c>
       <c r="L77" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M77" t="n">
-        <v>45</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="N77" t="n">
-        <v>10.68617526204291</v>
+        <v>10.30623200640147</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -9029,25 +9051,25 @@
         <v>61.8421052631579</v>
       </c>
       <c r="X77" t="n">
-        <v>12.99543275787505</v>
+        <v>13.00517396479135</v>
       </c>
       <c r="Y77" t="n">
-        <v>4.521073880536086</v>
+        <v>4.951574719364471</v>
       </c>
       <c r="Z77" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AA77" t="n">
-        <v>49.15254237288136</v>
+        <v>54.3859649122807</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.57400389360102</v>
+        <v>11.12731655578788</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>5.738361691048599</v>
+        <v>5.311424429946932</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9056,10 +9078,10 @@
         <v>50</v>
       </c>
       <c r="AG77" t="n">
-        <v>25.57118817159973</v>
+        <v>25.58154013847343</v>
       </c>
       <c r="AH77" t="n">
-        <v>24.42881182840027</v>
+        <v>24.41845986152657</v>
       </c>
       <c r="AI77" t="n">
         <v>36.11893708270325</v>
@@ -9078,10 +9100,10 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05423323913641614</v>
+        <v>0.05421090410442571</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9109,7 +9131,7 @@
         <v>12.76206508896208</v>
       </c>
       <c r="K78" t="n">
-        <v>7.04259889745642</v>
+        <v>6.998515233843783</v>
       </c>
       <c r="L78" t="n">
         <v>46</v>
@@ -9118,7 +9140,7 @@
         <v>60.8695652173913</v>
       </c>
       <c r="N78" t="n">
-        <v>17.20774729385692</v>
+        <v>17.21197307077892</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
@@ -9151,13 +9173,13 @@
         <v>23.16536029857119</v>
       </c>
       <c r="Y78" t="n">
-        <v>6.618247246753583</v>
+        <v>6.656704924522372</v>
       </c>
       <c r="Z78" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA78" t="n">
-        <v>45</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="AB78" t="n">
         <v>13.25512377513977</v>
@@ -9166,7 +9188,7 @@
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>3.621427798836052</v>
+        <v>3.581719579080889</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9197,10 +9219,10 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8942178737578109</v>
+        <v>0.8988924354114044</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9228,22 +9250,22 @@
         <v>12.46716859924595</v>
       </c>
       <c r="K79" t="n">
-        <v>3.550951787524936</v>
+        <v>4.092268755821382</v>
       </c>
       <c r="L79" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M79" t="n">
-        <v>50.9433962264151</v>
+        <v>53.06122448979592</v>
       </c>
       <c r="N79" t="n">
-        <v>10.33290339162583</v>
+        <v>10.48581150109307</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>1.399357695377201</v>
+        <v>0.872044826218521</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9284,10 +9306,10 @@
         <v>55.26315789473684</v>
       </c>
       <c r="AG79" t="n">
-        <v>26.62440966384084</v>
+        <v>26.70060063534073</v>
       </c>
       <c r="AH79" t="n">
-        <v>28.638748230896</v>
+        <v>28.56255725939611</v>
       </c>
       <c r="AI79" t="n">
         <v>39.70629712199248</v>
@@ -9306,24 +9328,24 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1257034035568626</v>
+        <v>0.1296439120281752</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AL_BEKLE_EŞİK</t>
-        </is>
-      </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -9334,13 +9356,13 @@
         <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>71.23712742986181</v>
+        <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>2.925991080130719</v>
+        <v>6.14333030849834</v>
       </c>
       <c r="L80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
@@ -9348,7 +9370,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>6.872908237883246</v>
+        <v>3.633454575329909</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9371,17 +9393,27 @@
       <c r="W80" t="n">
         <v>75.9493670886076</v>
       </c>
-      <c r="X80" t="inlineStr"/>
-      <c r="Y80" t="inlineStr"/>
+      <c r="X80" t="n">
+        <v>11.5318431483495</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>4.831367157345234</v>
+      </c>
       <c r="Z80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA80" t="inlineStr"/>
-      <c r="AB80" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>35</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>12.77169324801085</v>
+      </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
-      <c r="AD80" t="inlineStr"/>
+      <c r="AD80" t="n">
+        <v>3.329492867564421</v>
+      </c>
       <c r="AE80" t="n">
         <v>26</v>
       </c>
@@ -9389,10 +9421,10 @@
         <v>50</v>
       </c>
       <c r="AG80" t="n">
-        <v>39.88957965502588</v>
+        <v>40.05441481986104</v>
       </c>
       <c r="AH80" t="n">
-        <v>10.11042034497412</v>
+        <v>9.945585180138956</v>
       </c>
       <c r="AI80" t="n">
         <v>32.06059352575905</v>
@@ -9411,14 +9443,14 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C81" t="n">
-        <v>1.07310345059886</v>
+        <v>1.088420495535893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9439,25 +9471,25 @@
         <v>10</v>
       </c>
       <c r="J81" t="n">
-        <v>12.05035505845211</v>
+        <v>12.04277302023445</v>
       </c>
       <c r="K81" t="n">
-        <v>2.46888710889912</v>
+        <v>3.922527546441357</v>
       </c>
       <c r="L81" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="M81" t="n">
-        <v>51.02040816326531</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="N81" t="n">
-        <v>12.98769363041235</v>
+        <v>14.60263830628129</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>7.349658129005721</v>
+        <v>5.848079908220782</v>
       </c>
       <c r="Q81" t="n">
         <v>31</v>
@@ -9484,22 +9516,22 @@
         <v>27.31228182970742</v>
       </c>
       <c r="Y81" t="n">
-        <v>9.878977612167695</v>
+        <v>8.592626562867212</v>
       </c>
       <c r="Z81" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA81" t="n">
-        <v>55.55555555555556</v>
+        <v>25</v>
       </c>
       <c r="AB81" t="n">
-        <v>9.529724010146259</v>
+        <v>15.30045963659641</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.1342887426548312</v>
+        <v>1.539671674408993</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9530,10 +9562,10 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C82" t="n">
-        <v>5.248852739093004</v>
+        <v>5.26350073613903</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9590,25 +9622,25 @@
         <v>57.14285714285715</v>
       </c>
       <c r="X82" t="n">
-        <v>16.28898299114456</v>
+        <v>18.78314306215709</v>
       </c>
       <c r="Y82" t="n">
-        <v>0.7157069781312031</v>
+        <v>2.529182879377434</v>
       </c>
       <c r="Z82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA82" t="n">
-        <v>50</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB82" t="n">
-        <v>11.22183907241817</v>
+        <v>14.94796830916254</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>3.307968382416127</v>
+        <v>1.508982035928141</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9639,10 +9671,10 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C83" t="n">
-        <v>5.948839981206576</v>
+        <v>5.888607110989873</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9670,22 +9702,22 @@
         <v>14.0949513048101</v>
       </c>
       <c r="K83" t="n">
-        <v>9.913521653749013</v>
+        <v>8.800631257344648</v>
       </c>
       <c r="L83" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M83" t="n">
-        <v>60.71428571428572</v>
+        <v>61.29032258064516</v>
       </c>
       <c r="N83" t="n">
-        <v>10.70932204243479</v>
+        <v>10.39405110257578</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>0.07867853285914439</v>
+        <v>1.102354580846598</v>
       </c>
       <c r="Q83" t="n">
         <v>44</v>
@@ -9694,10 +9726,10 @@
         <v>63.63636363636363</v>
       </c>
       <c r="S83" t="n">
-        <v>55.07418752743249</v>
+        <v>54.37059527766615</v>
       </c>
       <c r="T83" t="n">
-        <v>8.562176108931148</v>
+        <v>9.265768358697485</v>
       </c>
       <c r="U83" t="n">
         <v>48.86637687904344</v>
@@ -9712,22 +9744,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.116133503673644</v>
+        <v>2.11734703707096</v>
       </c>
       <c r="Z83" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AA83" t="n">
-        <v>58.33333333333334</v>
+        <v>56.89655172413793</v>
       </c>
       <c r="AB83" t="n">
-        <v>12.00425528872013</v>
+        <v>11.2408989891791</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>4.938992243499907</v>
+        <v>3.966640508200692</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9758,10 +9790,10 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C84" t="n">
-        <v>2.219779126903496</v>
+        <v>2.20835895934154</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9789,16 +9821,16 @@
         <v>14.10735630446007</v>
       </c>
       <c r="K84" t="n">
-        <v>6.266490707848282</v>
+        <v>5.719778147397525</v>
       </c>
       <c r="L84" t="n">
         <v>39</v>
       </c>
       <c r="M84" t="n">
-        <v>64.1025641025641</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N84" t="n">
-        <v>10.5206215097878</v>
+        <v>10.95030722644272</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
@@ -9867,10 +9899,10 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C85" t="n">
-        <v>6.579459060486425</v>
+        <v>6.597761401787047</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9898,22 +9930,22 @@
         <v>15.13449360257271</v>
       </c>
       <c r="K85" t="n">
-        <v>2.102617800314333</v>
+        <v>2.38664068752874</v>
       </c>
       <c r="L85" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="M85" t="n">
-        <v>58.18181818181818</v>
+        <v>54.90196078431372</v>
       </c>
       <c r="N85" t="n">
-        <v>13.88678250642891</v>
+        <v>13.1715021887886</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>5.775936334188203</v>
+        <v>5.482511463192297</v>
       </c>
       <c r="Q85" t="n">
         <v>34</v>
@@ -9922,10 +9954,10 @@
         <v>61.76470588235294</v>
       </c>
       <c r="S85" t="n">
-        <v>65.85496522516983</v>
+        <v>66.25603474388642</v>
       </c>
       <c r="T85" t="n">
-        <v>-4.090259342816893</v>
+        <v>-4.491328861533475</v>
       </c>
       <c r="U85" t="n">
         <v>45.0410173444307</v>
@@ -9954,10 +9986,10 @@
         <v>41.93548387096774</v>
       </c>
       <c r="AG85" t="n">
-        <v>22.62682387800984</v>
+        <v>22.66019428957825</v>
       </c>
       <c r="AH85" t="n">
-        <v>19.30865999295791</v>
+        <v>19.2752895813895</v>
       </c>
       <c r="AI85" t="n">
         <v>26.41554306731223</v>
@@ -9976,10 +10008,10 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C86" t="n">
-        <v>3.890919847382548</v>
+        <v>3.971264028464178</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10030,31 +10062,31 @@
         <v>51.48483072023632</v>
       </c>
       <c r="V86" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="W86" t="n">
-        <v>68.35443037974683</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="X86" t="n">
-        <v>52.347553944765</v>
+        <v>56.06930016097078</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>0.3690020881679357</v>
       </c>
       <c r="Z86" t="n">
         <v>5</v>
       </c>
       <c r="AA86" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AB86" t="n">
-        <v>9.831530790531973</v>
+        <v>8.457591085917171</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>6.000000000000005</v>
+        <v>5.651853368783066</v>
       </c>
       <c r="AE86" t="n">
         <v>51</v>
@@ -10085,10 +10117,10 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C87" t="n">
-        <v>5.517916943698679</v>
+        <v>5.531403468217962</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10113,25 +10145,25 @@
         <v>10</v>
       </c>
       <c r="J87" t="n">
-        <v>29.54558799520699</v>
+        <v>26.73202875980171</v>
       </c>
       <c r="K87" t="n">
-        <v>1.592550331096598</v>
+        <v>1.840856065850649</v>
       </c>
       <c r="L87" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="M87" t="n">
-        <v>42.85714285714285</v>
+        <v>62.5</v>
       </c>
       <c r="N87" t="n">
-        <v>11.76555496029376</v>
+        <v>13.89511345784383</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>3.354034973822695</v>
+        <v>3.10203984548858</v>
       </c>
       <c r="Q87" t="n">
         <v>47</v>
@@ -10172,10 +10204,10 @@
         <v>52.17391304347826</v>
       </c>
       <c r="AG87" t="n">
-        <v>47.63908977455571</v>
+        <v>48.0219981925345</v>
       </c>
       <c r="AH87" t="n">
-        <v>4.534823268922551</v>
+        <v>4.151914850943754</v>
       </c>
       <c r="AI87" t="n">
         <v>38.13741307280403</v>
@@ -10194,10 +10226,10 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C88" t="n">
-        <v>1.01193340306181</v>
+        <v>1.030847717868171</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10225,7 +10257,7 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>13.36851794231744</v>
+        <v>15.48751888744251</v>
       </c>
       <c r="L88" t="n">
         <v>6</v>
@@ -10234,7 +10266,7 @@
         <v>50</v>
       </c>
       <c r="N88" t="n">
-        <v>5.666376892907188</v>
+        <v>14.0838396102281</v>
       </c>
       <c r="O88" t="n">
         <v>10</v>
@@ -10264,46 +10296,46 @@
         <v>68.35443037974683</v>
       </c>
       <c r="X88" t="n">
-        <v>13.50981969714924</v>
+        <v>15.62875348080186</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.1244841681616649</v>
+        <v>0.1221448723675689</v>
       </c>
       <c r="Z88" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="AA88" t="n">
-        <v>38.0281690140845</v>
+        <v>30.50847457627119</v>
       </c>
       <c r="AB88" t="n">
-        <v>12.18459957953473</v>
+        <v>12.26169163870217</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>5.882839035075449</v>
+        <v>5.885043406389945</v>
       </c>
       <c r="AE88" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AF88" t="n">
-        <v>53.33333333333334</v>
+        <v>54.83870967741935</v>
       </c>
       <c r="AG88" t="n">
-        <v>50.14066042316816</v>
+        <v>49.73289718371112</v>
       </c>
       <c r="AH88" t="n">
-        <v>3.192672910165179</v>
+        <v>5.105812493708228</v>
       </c>
       <c r="AI88" t="n">
-        <v>36.1422996198733</v>
+        <v>37.77216763735451</v>
       </c>
       <c r="AJ88" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AK88" t="n">
-        <v>42.10526315789474</v>
+        <v>42.85714285714285</v>
       </c>
     </row>
     <row r="89">
@@ -10313,10 +10345,10 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C89" t="n">
-        <v>2.067379516077532</v>
+        <v>2.107501556440806</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10344,16 +10376,16 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>12.29665494497365</v>
+        <v>14.47601818589006</v>
       </c>
       <c r="L89" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="M89" t="n">
-        <v>68.18181818181819</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N89" t="n">
-        <v>11.98702487689557</v>
+        <v>14.19332941038719</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
@@ -10386,22 +10418,22 @@
         <v>28.7873334490923</v>
       </c>
       <c r="Y89" t="n">
-        <v>9.841676175356151</v>
+        <v>8.091955875117939</v>
       </c>
       <c r="Z89" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AA89" t="n">
-        <v>30.76923076923077</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="AB89" t="n">
-        <v>17.01341296973431</v>
+        <v>17.51130243662222</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.1756064420094794</v>
+        <v>2.076036045647389</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10432,10 +10464,10 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C90" t="n">
-        <v>2.79994864788959</v>
+        <v>2.868135131668573</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10452,11 +10484,7 @@
           <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.76: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>5</v>
       </c>
@@ -10467,16 +10495,16 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>10.37467275922248</v>
+        <v>13.0626009251122</v>
       </c>
       <c r="L90" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="M90" t="n">
-        <v>75.75757575757575</v>
+        <v>72.22222222222223</v>
       </c>
       <c r="N90" t="n">
-        <v>14.98538149859456</v>
+        <v>14.83784955153763</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
@@ -10500,25 +10528,25 @@
         <v>64.06015468367708</v>
       </c>
       <c r="V90" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="W90" t="n">
-        <v>70.45454545454545</v>
+        <v>70.78651685393258</v>
       </c>
       <c r="X90" t="n">
         <v>33.24184775233741</v>
       </c>
       <c r="Y90" t="n">
-        <v>7.932860704238509</v>
+        <v>5.69077154846076</v>
       </c>
       <c r="Z90" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA90" t="n">
-        <v>26.66666666666667</v>
+        <v>50</v>
       </c>
       <c r="AB90" t="n">
-        <v>8.412413089294214</v>
+        <v>10.56986052093374</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
@@ -10555,10 +10583,10 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2379535927318659</v>
+        <v>0.2378555956144056</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10583,19 +10611,19 @@
         <v>10</v>
       </c>
       <c r="J91" t="n">
-        <v>14.82331888146111</v>
+        <v>14.34427620336855</v>
       </c>
       <c r="K91" t="n">
-        <v>4.950123534292938</v>
+        <v>4.906901620871129</v>
       </c>
       <c r="L91" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="M91" t="n">
-        <v>59.09090909090909</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N91" t="n">
-        <v>15.63258073362421</v>
+        <v>14.76152527384818</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
@@ -10610,10 +10638,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="S91" t="n">
-        <v>32.55801056789885</v>
+        <v>32.9469787376493</v>
       </c>
       <c r="T91" t="n">
-        <v>29.14411709167561</v>
+        <v>28.75514892192517</v>
       </c>
       <c r="U91" t="n">
         <v>47.42656695641357</v>
@@ -10664,10 +10692,10 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C92" t="n">
-        <v>1.120399881544848</v>
+        <v>1.111533720538566</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10684,11 +10712,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>5</v>
       </c>
@@ -10699,22 +10723,22 @@
         <v>22.28274626067631</v>
       </c>
       <c r="K92" t="n">
-        <v>6.334792667642142</v>
+        <v>5.493324002846278</v>
       </c>
       <c r="L92" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M92" t="n">
-        <v>76.47058823529412</v>
+        <v>65</v>
       </c>
       <c r="N92" t="n">
-        <v>11.86346955680526</v>
+        <v>13.65852513941646</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>1.566004212339611</v>
+        <v>2.376146567422688</v>
       </c>
       <c r="Q92" t="n">
         <v>56</v>
@@ -10755,10 +10779,10 @@
         <v>52.94117647058823</v>
       </c>
       <c r="AG92" t="n">
-        <v>40.31765720771973</v>
+        <v>40.2686375998766</v>
       </c>
       <c r="AH92" t="n">
-        <v>12.6235192628685</v>
+        <v>12.67253887071163</v>
       </c>
       <c r="AI92" t="n">
         <v>39.52330421009647</v>
@@ -10777,10 +10801,10 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04183106580243634</v>
+        <v>0.04223407755291195</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10805,25 +10829,25 @@
         <v>10</v>
       </c>
       <c r="J93" t="n">
-        <v>19.1493380128757</v>
+        <v>18.40038502869544</v>
       </c>
       <c r="K93" t="n">
-        <v>1.449081980148414</v>
+        <v>2.426469749947513</v>
       </c>
       <c r="L93" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M93" t="n">
-        <v>64.70588235294117</v>
+        <v>59.18367346938776</v>
       </c>
       <c r="N93" t="n">
-        <v>13.82750385948612</v>
+        <v>14.81503794226588</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>4.48591345631113</v>
+        <v>3.488873783091928</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10886,24 +10910,24 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C94" t="n">
-        <v>6.363997541732476</v>
+        <v>6.487448512107487</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -10917,22 +10941,22 @@
         <v>12.24049282186025</v>
       </c>
       <c r="K94" t="n">
-        <v>6.906165720438029</v>
+        <v>8.97996757386661</v>
       </c>
       <c r="L94" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="M94" t="n">
-        <v>51.72413793103448</v>
+        <v>54.16666666666666</v>
       </c>
       <c r="N94" t="n">
-        <v>13.30431828192241</v>
+        <v>12.71643650941258</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>1.023172304600628</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
         <v>40</v>
@@ -10959,22 +10983,22 @@
         <v>46.65531127586331</v>
       </c>
       <c r="Y94" t="n">
-        <v>6.179675820698205</v>
+        <v>4.359717534278151</v>
       </c>
       <c r="Z94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA94" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AB94" t="n">
-        <v>9.657835500919472</v>
+        <v>10.2252458307341</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>0</v>
+        <v>1.715053974573677</v>
       </c>
       <c r="AE94" t="n">
         <v>37</v>
@@ -10983,10 +11007,10 @@
         <v>54.05405405405406</v>
       </c>
       <c r="AG94" t="n">
-        <v>21.16703203497267</v>
+        <v>21.23700842847849</v>
       </c>
       <c r="AH94" t="n">
-        <v>32.88702201908139</v>
+        <v>32.81704562557557</v>
       </c>
       <c r="AI94" t="n">
         <v>38.38404689217949</v>
@@ -11005,10 +11029,10 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1408382570452454</v>
+        <v>0.1405701406809587</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11036,43 +11060,43 @@
         <v>23.400044414021</v>
       </c>
       <c r="K95" t="n">
-        <v>1.587550571790719</v>
+        <v>1.394156494872023</v>
       </c>
       <c r="L95" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M95" t="n">
-        <v>65.38461538461539</v>
+        <v>64</v>
       </c>
       <c r="N95" t="n">
-        <v>19.42490216729606</v>
+        <v>19.79473256227971</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>4.343494260245073</v>
+        <v>4.54251375458794</v>
       </c>
       <c r="Q95" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R95" t="n">
-        <v>81.81818181818181</v>
+        <v>82.60869565217391</v>
       </c>
       <c r="S95" t="n">
-        <v>41.20844390387734</v>
+        <v>42.52236249190751</v>
       </c>
       <c r="T95" t="n">
-        <v>40.60973791430447</v>
+        <v>40.08633316026639</v>
       </c>
       <c r="U95" t="n">
-        <v>61.48339256287345</v>
+        <v>62.86235235977385</v>
       </c>
       <c r="V95" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W95" t="n">
-        <v>84.44444444444444</v>
+        <v>84.78260869565217</v>
       </c>
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr"/>
@@ -11114,10 +11138,10 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1313789748499685</v>
+        <v>0.1317451078256355</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11142,10 +11166,10 @@
         <v>10</v>
       </c>
       <c r="J96" t="n">
-        <v>12.86625377026597</v>
+        <v>12.85874206974231</v>
       </c>
       <c r="K96" t="n">
-        <v>1.626014607707083</v>
+        <v>1.900445943171691</v>
       </c>
       <c r="L96" t="n">
         <v>73</v>
@@ -11154,13 +11178,13 @@
         <v>60.27397260273973</v>
       </c>
       <c r="N96" t="n">
-        <v>12.88642560075273</v>
+        <v>12.8932908073108</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>8.240001760000016</v>
+        <v>7.948497164914592</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11187,7 +11211,7 @@
         <v>16.74415231729489</v>
       </c>
       <c r="Y96" t="n">
-        <v>11.44944632832807</v>
+        <v>11.20266956857795</v>
       </c>
       <c r="Z96" t="n">
         <v>15</v>
@@ -11233,10 +11257,10 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C97" t="n">
-        <v>1.837203616463533</v>
+        <v>1.846952985068969</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11261,25 +11285,25 @@
         <v>10</v>
       </c>
       <c r="J97" t="n">
-        <v>22.80838616541501</v>
+        <v>20.83793142975532</v>
       </c>
       <c r="K97" t="n">
-        <v>2.791215872795338</v>
+        <v>3.336691313821261</v>
       </c>
       <c r="L97" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M97" t="n">
-        <v>48</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N97" t="n">
-        <v>12.93095395568185</v>
+        <v>13.50638102302412</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>1.175960530227149</v>
+        <v>0.6418907725275869</v>
       </c>
       <c r="Q97" t="n">
         <v>50</v>
@@ -11288,10 +11312,10 @@
         <v>56</v>
       </c>
       <c r="S97" t="n">
-        <v>34.8420738243145</v>
+        <v>35.02295617725568</v>
       </c>
       <c r="T97" t="n">
-        <v>21.1579261756855</v>
+        <v>20.97704382274432</v>
       </c>
       <c r="U97" t="n">
         <v>42.30602802165686</v>
@@ -11320,10 +11344,10 @@
         <v>55</v>
       </c>
       <c r="AG97" t="n">
-        <v>58.39355666422097</v>
+        <v>58.59541082931041</v>
       </c>
       <c r="AH97" t="n">
-        <v>-3.393556664220966</v>
+        <v>-3.59541082931041</v>
       </c>
       <c r="AI97" t="n">
         <v>39.82909179893205</v>
@@ -11342,19 +11366,19 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6613091884658165</v>
+        <v>0.6601963814393947</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -11377,7 +11401,7 @@
         <v>18.49937747698907</v>
       </c>
       <c r="K98" t="n">
-        <v>10.14415067220884</v>
+        <v>9.958807436510497</v>
       </c>
       <c r="L98" t="n">
         <v>15</v>
@@ -11386,13 +11410,13 @@
         <v>80</v>
       </c>
       <c r="N98" t="n">
-        <v>11.79346297877967</v>
+        <v>11.9239160746963</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>0.03746181360988476</v>
       </c>
       <c r="Q98" t="n">
         <v>48</v>
@@ -11401,10 +11425,10 @@
         <v>68.75</v>
       </c>
       <c r="S98" t="n">
-        <v>39.05234314689367</v>
+        <v>39.30577672753313</v>
       </c>
       <c r="T98" t="n">
-        <v>29.69765685310633</v>
+        <v>29.44422327246687</v>
       </c>
       <c r="U98" t="n">
         <v>54.66692858410841</v>
@@ -11416,25 +11440,25 @@
         <v>73.52941176470588</v>
       </c>
       <c r="X98" t="n">
-        <v>10.7043305347843</v>
+        <v>10.71387422840049</v>
       </c>
       <c r="Y98" t="n">
-        <v>0.5060144078098627</v>
+        <v>0.6819983467765911</v>
       </c>
       <c r="Z98" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AA98" t="n">
-        <v>38</v>
+        <v>39.21568627450981</v>
       </c>
       <c r="AB98" t="n">
-        <v>11.82280735143941</v>
+        <v>11.44074982040592</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>7.532099098840783</v>
+        <v>7.36825301698556</v>
       </c>
       <c r="AE98" t="n">
         <v>50</v>
@@ -11465,19 +11489,19 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C99" t="n">
-        <v>0.481372555862443</v>
+        <v>0.4836957659366499</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -11496,22 +11520,22 @@
         <v>28.77817890954801</v>
       </c>
       <c r="K99" t="n">
-        <v>3.559195666113601</v>
+        <v>4.058995174245572</v>
       </c>
       <c r="L99" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M99" t="n">
-        <v>63.1578947368421</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N99" t="n">
-        <v>13.14362189634568</v>
+        <v>12.71234207232084</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>0.4256544588349342</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>35</v>
@@ -11552,10 +11576,10 @@
         <v>51.28205128205128</v>
       </c>
       <c r="AG99" t="n">
-        <v>37.92264871388912</v>
+        <v>37.49037809779497</v>
       </c>
       <c r="AH99" t="n">
-        <v>13.35940256816216</v>
+        <v>13.79167318425631</v>
       </c>
       <c r="AI99" t="n">
         <v>36.19936288445796</v>
@@ -11574,10 +11598,10 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C100" t="n">
-        <v>328.536364268523</v>
+        <v>328.1165591696308</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11602,10 +11626,10 @@
         <v>10</v>
       </c>
       <c r="J100" t="n">
-        <v>25.19597156501795</v>
+        <v>25.15478290083538</v>
       </c>
       <c r="K100" t="n">
-        <v>7.194678369196383</v>
+        <v>7.05770457436643</v>
       </c>
       <c r="L100" t="n">
         <v>13</v>
@@ -11614,7 +11638,7 @@
         <v>61.53846153846154</v>
       </c>
       <c r="N100" t="n">
-        <v>11.81400718384301</v>
+        <v>11.90267572555307</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11683,10 +11707,10 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C101" t="n">
-        <v>325.8478167159021</v>
+        <v>327.6389470379006</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11714,16 +11738,16 @@
         <v>13.42090796247281</v>
       </c>
       <c r="K101" t="n">
-        <v>3.185916553614265</v>
+        <v>3.753112080056975</v>
       </c>
       <c r="L101" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M101" t="n">
-        <v>37.83783783783784</v>
+        <v>32.35294117647059</v>
       </c>
       <c r="N101" t="n">
-        <v>9.528582219891799</v>
+        <v>8.34505652045217</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11792,10 +11816,10 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C102" t="n">
-        <v>394.4911140550203</v>
+        <v>397.972955781057</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11891,10 +11915,10 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7231099097357999</v>
+        <v>0.7202906140254492</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11922,7 +11946,7 @@
         <v>30.74202968074841</v>
       </c>
       <c r="K103" t="n">
-        <v>11.21310553655399</v>
+        <v>10.7795025293866</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
@@ -11964,43 +11988,43 @@
         <v>14.26498323563516</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.67087747502458</v>
+        <v>3.050348941163261</v>
       </c>
       <c r="Z103" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AA103" t="n">
-        <v>39.62264150943396</v>
+        <v>40</v>
       </c>
       <c r="AB103" t="n">
-        <v>10.76966505008277</v>
+        <v>11.60528731344739</v>
       </c>
       <c r="AC103" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD103" t="n">
-        <v>5.475362755487623</v>
+        <v>7.168309512139592</v>
       </c>
       <c r="AE103" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="AF103" t="n">
-        <v>61.76470588235294</v>
+        <v>60.97560975609756</v>
       </c>
       <c r="AG103" t="n">
-        <v>38.98129988960439</v>
+        <v>37.05048140167025</v>
       </c>
       <c r="AH103" t="n">
-        <v>22.78340599274856</v>
+        <v>23.92512835442732</v>
       </c>
       <c r="AI103" t="n">
-        <v>45.0410173444307</v>
+        <v>45.72685693412379</v>
       </c>
       <c r="AJ103" t="n">
         <v>61</v>
       </c>
       <c r="AK103" t="n">
-        <v>50.81967213114754</v>
+        <v>52.45901639344262</v>
       </c>
     </row>
     <row r="104">
@@ -12010,10 +12034,10 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0489780801424174</v>
+        <v>0.04895790935777997</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12042,10 +12066,10 @@
         <v>10</v>
       </c>
       <c r="J104" t="n">
-        <v>27.76362183938114</v>
+        <v>27.75739442390626</v>
       </c>
       <c r="K104" t="n">
-        <v>1.304346550094482</v>
+        <v>1.253897105002322</v>
       </c>
       <c r="L104" t="n">
         <v>21</v>
@@ -12054,13 +12078,13 @@
         <v>76.19047619047619</v>
       </c>
       <c r="N104" t="n">
-        <v>15.41015006677772</v>
+        <v>15.59629030718294</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>2.660945499088263</v>
+        <v>2.712096001746889</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>
@@ -12101,19 +12125,19 @@
         <v>61.70212765957447</v>
       </c>
       <c r="AG104" t="n">
-        <v>34.83739231883841</v>
+        <v>34.98188601905284</v>
       </c>
       <c r="AH104" t="n">
-        <v>26.86473534073605</v>
+        <v>26.72024164052162</v>
       </c>
       <c r="AI104" t="n">
         <v>47.42656695641357</v>
       </c>
       <c r="AJ104" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AK104" t="n">
-        <v>51.89873417721519</v>
+        <v>51.28205128205128</v>
       </c>
     </row>
   </sheetData>

--- a/TDA_Result.xlsx
+++ b/TDA_Result.xlsx
@@ -453,7 +453,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -679,7 +679,7 @@
         <v>46240</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4559599599779542</v>
+        <v>0.4526123042288233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -739,22 +739,22 @@
         <v>14.94856954517825</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.269296835441705</v>
+        <v>4.972151180004492</v>
       </c>
       <c r="Z2" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="AA2" t="n">
-        <v>45.94594594594594</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.57649322829002</v>
+        <v>10.73616807324932</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.897081125733837</v>
+        <v>3.186275242040826</v>
       </c>
       <c r="AE2" t="n">
         <v>43</v>
@@ -788,7 +788,7 @@
         <v>46240</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7446645064980887</v>
+        <v>0.742166469928462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,22 +848,22 @@
         <v>12.13279917920569</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.123547167668238</v>
+        <v>2.451881546904733</v>
       </c>
       <c r="Z3" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="AA3" t="n">
-        <v>44.44444444444444</v>
+        <v>45</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.30082810885584</v>
+        <v>10.50156852205022</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>8.047341934044749</v>
+        <v>7.737841152440761</v>
       </c>
       <c r="AE3" t="n">
         <v>38</v>
@@ -897,7 +897,7 @@
         <v>46240</v>
       </c>
       <c r="C4" t="n">
-        <v>1.421460410590665</v>
+        <v>1.420454492411954</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>27.63389482946404</v>
       </c>
       <c r="K4" t="n">
-        <v>10.05926848789502</v>
+        <v>9.981383364902729</v>
       </c>
       <c r="L4" t="n">
         <v>10</v>
@@ -967,7 +967,7 @@
         <v>11.23805603488277</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.059698082658056</v>
+        <v>1.129714699064821</v>
       </c>
       <c r="Z4" t="n">
         <v>58</v>
@@ -976,13 +976,13 @@
         <v>37.93103448275862</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.63814518191822</v>
+        <v>11.52873663594415</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>9.036056838406425</v>
+        <v>8.971639228041429</v>
       </c>
       <c r="AE4" t="n">
         <v>45</v>
@@ -1016,7 +1016,7 @@
         <v>46240</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2660116508183434</v>
+        <v>0.2660200305899085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>16.70172291026088</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.784453640652863</v>
+        <v>4.781454206133806</v>
       </c>
       <c r="Z5" t="n">
         <v>35</v>
@@ -1091,7 +1091,7 @@
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.477620576437658</v>
+        <v>5.480598081348099</v>
       </c>
       <c r="AE5" t="n">
         <v>44</v>
@@ -1125,7 +1125,7 @@
         <v>46240</v>
       </c>
       <c r="C6" t="n">
-        <v>2.032908966951901</v>
+        <v>2.030871774735866</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,16 +1153,16 @@
         <v>23.73506360720576</v>
       </c>
       <c r="K6" t="n">
-        <v>7.072019138134711</v>
+        <v>6.964721522998318</v>
       </c>
       <c r="L6" t="n">
         <v>20</v>
       </c>
       <c r="M6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="N6" t="n">
-        <v>9.264475517829858</v>
+        <v>9.409115462639447</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
@@ -1195,7 +1195,7 @@
         <v>44.49622708587002</v>
       </c>
       <c r="Y6" t="n">
-        <v>18.3415927098211</v>
+        <v>18.42342316775585</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
         <v>46240</v>
       </c>
       <c r="C7" t="n">
-        <v>2.1348170328885</v>
+        <v>2.149593227736786</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,22 +1268,22 @@
         <v>11.35312764557068</v>
       </c>
       <c r="K7" t="n">
-        <v>2.276143439109068</v>
+        <v>2.98405058080109</v>
       </c>
       <c r="L7" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M7" t="n">
-        <v>58.57142857142857</v>
+        <v>58.20895522388059</v>
       </c>
       <c r="N7" t="n">
-        <v>12.72321302237388</v>
+        <v>12.61338027889698</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7077472190001766</v>
+        <v>0.01548727119293769</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1310,22 +1310,22 @@
         <v>13.79329344082609</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.335397676499946</v>
+        <v>8.70786013621635</v>
       </c>
       <c r="Z7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
-        <v>61.11111111111111</v>
+        <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.649714189658804</v>
+        <v>8.615798389642457</v>
       </c>
       <c r="AC7" t="n">
         <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.7330339586431811</v>
+        <v>1.415390049692822</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1359,7 +1359,7 @@
         <v>46240</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3290475877780922</v>
+        <v>0.3288478220356737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>22.10694516187944</v>
       </c>
       <c r="K8" t="n">
-        <v>4.619956641202227</v>
+        <v>4.556441562877711</v>
       </c>
       <c r="L8" t="n">
         <v>6</v>
@@ -1396,13 +1396,13 @@
         <v>50</v>
       </c>
       <c r="N8" t="n">
-        <v>15.17112081618959</v>
+        <v>15.13025449178977</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>3.230782603351434</v>
+        <v>3.293492381386587</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1468,7 +1468,7 @@
         <v>46240</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5963199459891619</v>
+        <v>0.5963387309743748</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>10.25501703215621</v>
       </c>
       <c r="K9" t="n">
-        <v>7.295578349127174</v>
+        <v>7.29895832302585</v>
       </c>
       <c r="L9" t="n">
         <v>18</v>
@@ -1577,7 +1577,7 @@
         <v>46240</v>
       </c>
       <c r="C10" t="n">
-        <v>2.103299064408626</v>
+        <v>2.099162857647467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,22 +1605,22 @@
         <v>10.23694539327734</v>
       </c>
       <c r="K10" t="n">
-        <v>4.144194973042148</v>
+        <v>3.939391989637575</v>
       </c>
       <c r="L10" t="n">
         <v>30</v>
       </c>
       <c r="M10" t="n">
-        <v>33.33333333333334</v>
+        <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>8.579114898075336</v>
+        <v>8.866752637384604</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>5.622785819674014</v>
+        <v>5.830905775325923</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1686,7 +1686,7 @@
         <v>46240</v>
       </c>
       <c r="C11" t="n">
-        <v>7.291156708344285</v>
+        <v>7.296639551093337</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,16 +1714,16 @@
         <v>20.56423081971027</v>
       </c>
       <c r="K11" t="n">
-        <v>4.469802269125034</v>
+        <v>4.548362025934338</v>
       </c>
       <c r="L11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M11" t="n">
-        <v>63.1578947368421</v>
+        <v>72.22222222222223</v>
       </c>
       <c r="N11" t="n">
-        <v>14.94987009323926</v>
+        <v>14.54040142703891</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1795,7 +1795,7 @@
         <v>46240</v>
       </c>
       <c r="C12" t="n">
-        <v>6.566243433307173</v>
+        <v>6.676766644664961</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1812,7 +1812,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>5</v>
       </c>
@@ -1823,13 +1827,17 @@
         <v>20.08266526523165</v>
       </c>
       <c r="K12" t="n">
-        <v>14.31636844666713</v>
+        <v>16.24054507517847</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>75</v>
+      </c>
+      <c r="N12" t="n">
+        <v>27.22793810052844</v>
+      </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
@@ -1858,25 +1866,25 @@
         <v>70.58823529411765</v>
       </c>
       <c r="X12" t="n">
-        <v>15.50525867851247</v>
+        <v>16.33200105084738</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.029295328582736</v>
+        <v>0.07861635220125507</v>
       </c>
       <c r="Z12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA12" t="n">
-        <v>46.42857142857143</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="AB12" t="n">
-        <v>13.04623712745359</v>
+        <v>12.14070721441706</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.9808000000000039</v>
+        <v>1.922895357985843</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -1910,7 +1918,7 @@
         <v>46240</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3000510542551703</v>
+        <v>0.3000605063197125</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,7 +1946,7 @@
         <v>38.11781916800814</v>
       </c>
       <c r="K13" t="n">
-        <v>5.439426559693383</v>
+        <v>5.442748061987768</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1974,7 +1982,7 @@
         <v>35.74308703619145</v>
       </c>
       <c r="Y13" t="n">
-        <v>22.32427531902129</v>
+        <v>22.32182841556056</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2009,7 +2017,7 @@
         <v>46240</v>
       </c>
       <c r="C14" t="n">
-        <v>8.079105920341146</v>
+        <v>8.032081982449037</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,16 +2077,16 @@
         <v>14.33662537827827</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.631461505755365</v>
+        <v>7.174907327424318</v>
       </c>
       <c r="Z14" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA14" t="n">
-        <v>36</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.60453219869498</v>
+        <v>11.74339053151457</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2118,7 +2126,7 @@
         <v>46240</v>
       </c>
       <c r="C15" t="n">
-        <v>12.21846578069799</v>
+        <v>12.34492652632782</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,7 +2154,7 @@
         <v>15.99936296068698</v>
       </c>
       <c r="K15" t="n">
-        <v>15.04345496790145</v>
+        <v>16.23415119410488</v>
       </c>
       <c r="L15" t="n">
         <v>5</v>
@@ -2155,7 +2163,7 @@
         <v>60</v>
       </c>
       <c r="N15" t="n">
-        <v>35.52870565309881</v>
+        <v>28.57987049720584</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
@@ -2185,25 +2193,25 @@
         <v>79.56989247311827</v>
       </c>
       <c r="X15" t="n">
-        <v>15.04345496790145</v>
+        <v>17.02553264904345</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>0.6762468300929858</v>
       </c>
       <c r="Z15" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="AA15" t="n">
-        <v>32.55813953488372</v>
+        <v>34.04255319148936</v>
       </c>
       <c r="AB15" t="n">
-        <v>14.74834399230339</v>
+        <v>11.36592399615845</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>9.999999999999998</v>
+        <v>9.387234042553183</v>
       </c>
       <c r="AE15" t="n">
         <v>31</v>
@@ -2237,7 +2245,7 @@
         <v>46240</v>
       </c>
       <c r="C16" t="n">
-        <v>37.44334655409082</v>
+        <v>37.57060192182833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2265,7 +2273,7 @@
         <v>17.40096492560246</v>
       </c>
       <c r="K16" t="n">
-        <v>7.925447914445161</v>
+        <v>8.292244523897452</v>
       </c>
       <c r="L16" t="n">
         <v>27</v>
@@ -2274,13 +2282,13 @@
         <v>70.37037037037037</v>
       </c>
       <c r="N16" t="n">
-        <v>16.89668310275174</v>
+        <v>16.41520330597012</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>1.922208455599272</v>
+        <v>1.576987792256634</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2346,7 +2354,7 @@
         <v>46240</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7501276657901155</v>
+        <v>0.749731033678815</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2373,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %76.09: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2378,22 +2386,22 @@
         <v>14.16674936134154</v>
       </c>
       <c r="K17" t="n">
-        <v>6.53653897096016</v>
+        <v>6.48020747658955</v>
       </c>
       <c r="L17" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M17" t="n">
-        <v>77.77777777777777</v>
+        <v>76.08695652173913</v>
       </c>
       <c r="N17" t="n">
-        <v>15.99393037286352</v>
+        <v>16.03425148948132</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>1.373670520157177</v>
+        <v>1.427300490323136</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2420,7 +2428,7 @@
         <v>15.7396793517258</v>
       </c>
       <c r="Y17" t="n">
-        <v>7.951586208216321</v>
+        <v>8.000257065683824</v>
       </c>
       <c r="Z17" t="n">
         <v>26</v>
@@ -2429,13 +2437,13 @@
         <v>57.69230769230769</v>
       </c>
       <c r="AB17" t="n">
-        <v>10.81356870547704</v>
+        <v>10.7297595688137</v>
       </c>
       <c r="AC17" t="n">
         <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.225365660745937</v>
+        <v>2.173639697823837</v>
       </c>
       <c r="AE17" t="n">
         <v>35</v>
@@ -2469,7 +2477,7 @@
         <v>46240</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1040092919913096</v>
+        <v>0.1035923160445253</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,22 +2505,22 @@
         <v>24.80221998015493</v>
       </c>
       <c r="K18" t="n">
-        <v>4.083958794951736</v>
+        <v>3.666683507016844</v>
       </c>
       <c r="L18" t="n">
         <v>19</v>
       </c>
       <c r="M18" t="n">
-        <v>57.89473684210526</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N18" t="n">
-        <v>16.99147144679783</v>
+        <v>17.67867101612232</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>5.683912558229109</v>
+        <v>6.109307521692342</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2578,7 +2586,7 @@
         <v>46240</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02500425625475245</v>
+        <v>0.02500504392685225</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2606,7 +2614,7 @@
         <v>19.67465331637003</v>
       </c>
       <c r="K19" t="n">
-        <v>1.234945859506076</v>
+        <v>1.238134914264011</v>
       </c>
       <c r="L19" t="n">
         <v>32</v>
@@ -2621,7 +2629,7 @@
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>8.658130911294283</v>
+        <v>8.654708122740695</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2687,7 +2695,7 @@
         <v>46240</v>
       </c>
       <c r="C20" t="n">
-        <v>1.85115531656963</v>
+        <v>1.851213630777436</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2755,7 @@
         <v>19.7256789664253</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.555856459426623</v>
+        <v>6.55291282679038</v>
       </c>
       <c r="Z20" t="n">
         <v>20</v>
@@ -2796,7 +2804,7 @@
         <v>46240</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9417568916649346</v>
+        <v>0.9384245392579769</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,22 +2832,22 @@
         <v>13.9566823466854</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8956708092711541</v>
+        <v>0.5386573013811402</v>
       </c>
       <c r="L21" t="n">
         <v>58</v>
       </c>
       <c r="M21" t="n">
-        <v>58.62068965517241</v>
+        <v>62.06896551724138</v>
       </c>
       <c r="N21" t="n">
-        <v>17.32124353265598</v>
+        <v>17.35617357110112</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>7.041262656510372</v>
+        <v>7.421366963607112</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2905,11 +2913,11 @@
         <v>46240</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3181213690009388</v>
+        <v>0.316870623028816</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2919,7 +2927,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2933,16 +2941,16 @@
         <v>20.35908649698318</v>
       </c>
       <c r="K22" t="n">
-        <v>7.246235963247294</v>
+        <v>6.824579920216856</v>
       </c>
       <c r="L22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M22" t="n">
-        <v>60</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N22" t="n">
-        <v>13.1486425633712</v>
+        <v>12.75000060540042</v>
       </c>
       <c r="O22" t="n">
         <v>2</v>
@@ -2975,13 +2983,13 @@
         <v>13.74898285979678</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.716751686970745</v>
+        <v>6.087441632875712</v>
       </c>
       <c r="Z22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA22" t="n">
-        <v>36</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="AB22" t="n">
         <v>15.59589356828433</v>
@@ -2990,7 +2998,7 @@
         <v>6</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.3004227347883193</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3016,7 +3024,7 @@
         <v>46240</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9207449126783517</v>
+        <v>0.967422006177813</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,7 +3033,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3040,27 +3048,17 @@
       <c r="I23" t="n">
         <v>10</v>
       </c>
-      <c r="J23" t="n">
-        <v>11.24944735826469</v>
-      </c>
-      <c r="K23" t="n">
-        <v>9.714878230518309</v>
-      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>12</v>
-      </c>
-      <c r="M23" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N23" t="n">
-        <v>17.09663517999777</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
         <v>5</v>
       </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="n">
         <v>6</v>
       </c>
@@ -3083,25 +3081,25 @@
         <v>87.5</v>
       </c>
       <c r="X23" t="n">
-        <v>35.79382902042403</v>
+        <v>43.33476743273008</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.627439240208052</v>
+        <v>3.073682273684231</v>
       </c>
       <c r="Z23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA23" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.545625828904191</v>
+        <v>14.99838693058465</v>
       </c>
       <c r="AC23" t="n">
         <v>6</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.463563794025826</v>
+        <v>3.019115752007229</v>
       </c>
       <c r="AE23" t="n">
         <v>10</v>
@@ -3135,7 +3133,7 @@
         <v>46240</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1832244624362377</v>
+        <v>0.1834403453551926</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3163,7 +3161,7 @@
         <v>22.86774633531589</v>
       </c>
       <c r="K24" t="n">
-        <v>4.68041066641065</v>
+        <v>4.803749615323794</v>
       </c>
       <c r="L24" t="n">
         <v>10</v>
@@ -3178,7 +3176,7 @@
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>5.081742896998676</v>
+        <v>4.95807678995146</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3244,7 +3242,7 @@
         <v>46240</v>
       </c>
       <c r="C25" t="n">
-        <v>4.032198639352197</v>
+        <v>4.032325659741714</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3343,7 +3341,7 @@
         <v>46240</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4454539704846627</v>
+        <v>0.4442072157211318</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3442,16 +3440,16 @@
         <v>46240</v>
       </c>
       <c r="C27" t="n">
-        <v>35.63631636124469</v>
+        <v>35.59541367761587</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3470,7 +3468,7 @@
         <v>61.00029220182797</v>
       </c>
       <c r="K27" t="n">
-        <v>8.109400127579969</v>
+        <v>7.985314221901785</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3481,7 +3479,7 @@
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>0.01359979197546046</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -3527,7 +3525,7 @@
         <v>46240</v>
       </c>
       <c r="C28" t="n">
-        <v>1.450877213110089</v>
+        <v>1.453024150099245</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,16 +3553,16 @@
         <v>20.14178232803948</v>
       </c>
       <c r="K28" t="n">
-        <v>4.054335144423549</v>
+        <v>4.208309649629749</v>
       </c>
       <c r="L28" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M28" t="n">
-        <v>35.48387096774194</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="N28" t="n">
-        <v>13.62202580110631</v>
+        <v>13.66043265150333</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
@@ -3636,7 +3634,7 @@
         <v>46240</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4030097634763746</v>
+        <v>0.4040730747619026</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3664,7 +3662,7 @@
         <v>20.65475273479386</v>
       </c>
       <c r="K29" t="n">
-        <v>10.87592638756596</v>
+        <v>11.16846427251521</v>
       </c>
       <c r="L29" t="n">
         <v>7</v>
@@ -3706,7 +3704,7 @@
         <v>55.05052857749912</v>
       </c>
       <c r="Y29" t="n">
-        <v>12.02522205019785</v>
+        <v>11.79310714204046</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3751,7 +3749,7 @@
         <v>46240</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3851495731431072</v>
+        <v>0.3855819684241491</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3779,22 +3777,22 @@
         <v>21.6314445059014</v>
       </c>
       <c r="K30" t="n">
-        <v>4.186471993375851</v>
+        <v>4.303438860223707</v>
       </c>
       <c r="L30" t="n">
         <v>22</v>
       </c>
       <c r="M30" t="n">
-        <v>59.09090909090909</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N30" t="n">
-        <v>11.52134526409605</v>
+        <v>12.49555200477302</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>0.7808384246621447</v>
+        <v>0.6678218353948662</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3860,7 +3858,7 @@
         <v>46240</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1781815721407131</v>
+        <v>0.1773466803358939</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3889,10 +3887,10 @@
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>30.03821413731819</v>
+        <v>30.15400413033618</v>
       </c>
       <c r="K31" t="n">
-        <v>0.7821243924439392</v>
+        <v>0.4761900215419557</v>
       </c>
       <c r="L31" t="n">
         <v>4</v>
@@ -3907,7 +3905,7 @@
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>9.146339852553421</v>
+        <v>9.478673481166201</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3973,7 +3971,7 @@
         <v>46240</v>
       </c>
       <c r="C32" t="n">
-        <v>2.386960780727496</v>
+        <v>2.366023332726425</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4030,25 +4028,25 @@
         <v>55.76923076923077</v>
       </c>
       <c r="X32" t="n">
-        <v>14.15775499371903</v>
+        <v>14.16135113661838</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.786027537117906</v>
+        <v>1.659389982532766</v>
       </c>
       <c r="Z32" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AA32" t="n">
-        <v>27.65957446808511</v>
+        <v>25</v>
       </c>
       <c r="AB32" t="n">
-        <v>12.90964469105402</v>
+        <v>13.30984986546575</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>7.271125511662158</v>
+        <v>6.44760086025602</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4082,7 +4080,7 @@
         <v>46240</v>
       </c>
       <c r="C33" t="n">
-        <v>1.846952985068969</v>
+        <v>1.830200989881558</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4110,22 +4108,22 @@
         <v>12.57251846431013</v>
       </c>
       <c r="K33" t="n">
-        <v>3.519589978154136</v>
+        <v>2.580659920304251</v>
       </c>
       <c r="L33" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M33" t="n">
-        <v>61.53846153846154</v>
+        <v>57.4074074074074</v>
       </c>
       <c r="N33" t="n">
-        <v>11.1783669017964</v>
+        <v>11.38704204195266</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>0.4640764341775849</v>
+        <v>1.383633211950919</v>
       </c>
       <c r="Q33" t="n">
         <v>39</v>
@@ -4191,7 +4189,7 @@
         <v>46240</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8846042831868146</v>
+        <v>0.8829511801105722</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4219,22 +4217,22 @@
         <v>10.37797163438468</v>
       </c>
       <c r="K34" t="n">
-        <v>3.326996686122685</v>
+        <v>3.133904498658513</v>
       </c>
       <c r="L34" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M34" t="n">
-        <v>40.90909090909091</v>
+        <v>39.53488372093023</v>
       </c>
       <c r="N34" t="n">
-        <v>8.994868973026261</v>
+        <v>9.105486921275626</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>0.6513334708853513</v>
+        <v>0.8397776711273064</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4261,16 +4259,16 @@
         <v>14.68007915548277</v>
       </c>
       <c r="Y34" t="n">
-        <v>7.396249720624725</v>
+        <v>7.569302855645654</v>
       </c>
       <c r="Z34" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA34" t="n">
-        <v>48.14814814814815</v>
+        <v>50</v>
       </c>
       <c r="AB34" t="n">
-        <v>11.46261217295156</v>
+        <v>11.50882648141719</v>
       </c>
       <c r="AC34" t="n">
         <v>3</v>
@@ -4310,7 +4308,7 @@
         <v>46240</v>
       </c>
       <c r="C35" t="n">
-        <v>1.911039424743184</v>
+        <v>1.949973139225953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4329,7 +4327,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.82: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4342,16 +4340,16 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>7.735326729336256</v>
+        <v>9.930224645244801</v>
       </c>
       <c r="L35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M35" t="n">
-        <v>81.81818181818181</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N35" t="n">
-        <v>13.27568040215743</v>
+        <v>11.33742913819006</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4384,7 +4382,7 @@
         <v>42.52272358489104</v>
       </c>
       <c r="Y35" t="n">
-        <v>16.94597819203719</v>
+        <v>15.25391389977305</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -4429,7 +4427,7 @@
         <v>46240</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08194672014887143</v>
+        <v>0.08194930159518495</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4457,7 +4455,7 @@
         <v>18.45194908889744</v>
       </c>
       <c r="K36" t="n">
-        <v>2.422348859942103</v>
+        <v>2.425575319700424</v>
       </c>
       <c r="L36" t="n">
         <v>20</v>
@@ -4538,7 +4536,7 @@
         <v>46240</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06408653485847907</v>
+        <v>0.06366830128412851</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,22 +4564,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>4.322058574956089</v>
+        <v>3.641244929191645</v>
       </c>
       <c r="L37" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M37" t="n">
-        <v>56.92307692307692</v>
+        <v>52.23880597014925</v>
       </c>
       <c r="N37" t="n">
-        <v>19.56677529205659</v>
+        <v>20.59198358626421</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>3.525564463819797</v>
+        <v>4.205618210960593</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4647,16 +4645,16 @@
         <v>46240</v>
       </c>
       <c r="C38" t="n">
-        <v>1.680958318926636</v>
+        <v>1.671555647355581</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4675,22 +4673,22 @@
         <v>16.08125753671009</v>
       </c>
       <c r="K38" t="n">
-        <v>6.098340553392068</v>
+        <v>5.50486489178581</v>
       </c>
       <c r="L38" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M38" t="n">
-        <v>70.58823529411765</v>
+        <v>74.28571428571429</v>
       </c>
       <c r="N38" t="n">
-        <v>12.00601244214094</v>
+        <v>11.24175812914092</v>
       </c>
       <c r="O38" t="n">
         <v>6</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>0.4693007367215118</v>
       </c>
       <c r="Q38" t="n">
         <v>34</v>
@@ -4756,7 +4754,7 @@
         <v>46240</v>
       </c>
       <c r="C39" t="n">
-        <v>2.723152604834223</v>
+        <v>2.723238388282787</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4784,7 +4782,7 @@
         <v>18.47027414490581</v>
       </c>
       <c r="K39" t="n">
-        <v>7.79463426336735</v>
+        <v>7.798029958286312</v>
       </c>
       <c r="L39" t="n">
         <v>16</v>
@@ -4826,7 +4824,7 @@
         <v>10.2437411865161</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.221538290328184</v>
+        <v>2.218458120077771</v>
       </c>
       <c r="Z39" t="n">
         <v>50</v>
@@ -4841,7 +4839,7 @@
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.864308809532102</v>
+        <v>3.8673371346159</v>
       </c>
       <c r="AE39" t="n">
         <v>42</v>
@@ -4875,7 +4873,7 @@
         <v>46240</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2038161921775786</v>
+        <v>0.2027719766604108</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4903,13 +4901,13 @@
         <v>13.0200875267008</v>
       </c>
       <c r="K40" t="n">
-        <v>11.31204766722833</v>
+        <v>10.74176045805229</v>
       </c>
       <c r="L40" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M40" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="N40" t="n">
         <v>12.78131349536254</v>
@@ -4945,22 +4943,22 @@
         <v>14.17330472629232</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.50606485108168</v>
+        <v>3.005557451863627</v>
       </c>
       <c r="Z40" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA40" t="n">
-        <v>56.25</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="AB40" t="n">
-        <v>10.88111544832883</v>
+        <v>10.23579542945735</v>
       </c>
       <c r="AC40" t="n">
         <v>6</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.58374615157494</v>
+        <v>3.087231051047379</v>
       </c>
       <c r="AE40" t="n">
         <v>12</v>
@@ -4994,7 +4992,7 @@
         <v>46240</v>
       </c>
       <c r="C41" t="n">
-        <v>1.715628116402826</v>
+        <v>1.729340409819243</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5013,7 +5011,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -5026,16 +5024,16 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>13.37837751768067</v>
+        <v>14.28456316755187</v>
       </c>
       <c r="L41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N41" t="n">
-        <v>12.17975430538131</v>
+        <v>8.290318992161135</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
@@ -5068,7 +5066,7 @@
         <v>40.81782021738603</v>
       </c>
       <c r="Y41" t="n">
-        <v>12.01699722455548</v>
+        <v>11.31378611593602</v>
       </c>
       <c r="Z41" t="n">
         <v>7</v>
@@ -5117,7 +5115,7 @@
         <v>46240</v>
       </c>
       <c r="C42" t="n">
-        <v>3.353511974431711</v>
+        <v>3.370427471521584</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5145,16 +5143,16 @@
         <v>21.11518617286606</v>
       </c>
       <c r="K42" t="n">
-        <v>9.107201142969434</v>
+        <v>9.657550316459652</v>
       </c>
       <c r="L42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M42" t="n">
-        <v>60</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="N42" t="n">
-        <v>12.88139896333518</v>
+        <v>22.80470238649248</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
@@ -5185,22 +5183,22 @@
         <v>14.97530566614946</v>
       </c>
       <c r="Y42" t="n">
-        <v>5.103795540425937</v>
+        <v>4.625128255915079</v>
       </c>
       <c r="Z42" t="n">
         <v>12</v>
       </c>
       <c r="AA42" t="n">
-        <v>33.33333333333334</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB42" t="n">
-        <v>9.790507698665648</v>
+        <v>11.25581968481021</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>5.15953666161627</v>
+        <v>5.63552185790307</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5232,7 +5230,7 @@
         <v>46240</v>
       </c>
       <c r="C43" t="n">
-        <v>7.212361787144599</v>
+        <v>7.27562691019746</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5292,16 +5290,16 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>6.907691469113997</v>
+        <v>6.091107868859924</v>
       </c>
       <c r="Z43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA43" t="n">
-        <v>60</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="AB43" t="n">
-        <v>13.09070057304151</v>
+        <v>12.72045075786758</v>
       </c>
       <c r="AC43" t="n">
         <v>2</v>
@@ -5341,7 +5339,7 @@
         <v>46240</v>
       </c>
       <c r="C44" t="n">
-        <v>5.023964303865056</v>
+        <v>4.990502212770821</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5369,22 +5367,22 @@
         <v>13.03201987649729</v>
       </c>
       <c r="K44" t="n">
-        <v>2.8272143382714</v>
+        <v>2.142334151024339</v>
       </c>
       <c r="L44" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M44" t="n">
-        <v>68</v>
+        <v>65.38461538461539</v>
       </c>
       <c r="N44" t="n">
-        <v>17.94687033846331</v>
+        <v>18.2306631515482</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>6.975571309490358</v>
+        <v>7.692859101259208</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5411,7 +5409,7 @@
         <v>12.1234692799834</v>
       </c>
       <c r="Y44" t="n">
-        <v>8.291087496140804</v>
+        <v>8.90191428525563</v>
       </c>
       <c r="Z44" t="n">
         <v>7</v>
@@ -5420,13 +5418,13 @@
         <v>14.28571428571429</v>
       </c>
       <c r="AB44" t="n">
-        <v>9.691917834769438</v>
+        <v>9.672387522044957</v>
       </c>
       <c r="AC44" t="n">
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.86340940831381</v>
+        <v>1.205388352706782</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5452,7 +5450,7 @@
         <v>46240</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02101197898658295</v>
+        <v>0.0212227670947095</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5480,22 +5478,22 @@
         <v>10.56080028712586</v>
       </c>
       <c r="K45" t="n">
-        <v>4.053075121228056</v>
+        <v>5.096915440293603</v>
       </c>
       <c r="L45" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>59.09090909090909</v>
+        <v>58.69565217391305</v>
       </c>
       <c r="N45" t="n">
-        <v>17.35967966641912</v>
+        <v>16.76312935190209</v>
       </c>
       <c r="O45" t="n">
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>5.715280275804857</v>
+        <v>4.66529825272739</v>
       </c>
       <c r="Q45" t="n">
         <v>37</v>
@@ -5561,7 +5559,7 @@
         <v>46240</v>
       </c>
       <c r="C46" t="n">
-        <v>9.014138985244088</v>
+        <v>9.045941905675109</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5589,22 +5587,22 @@
         <v>20.98614247885408</v>
       </c>
       <c r="K46" t="n">
-        <v>9.166619147147181</v>
+        <v>9.551771551402721</v>
       </c>
       <c r="L46" t="n">
         <v>18</v>
       </c>
       <c r="M46" t="n">
-        <v>61.11111111111111</v>
+        <v>50</v>
       </c>
       <c r="N46" t="n">
-        <v>15.19441695119586</v>
+        <v>17.6288119769074</v>
       </c>
       <c r="O46" t="n">
         <v>10</v>
       </c>
       <c r="P46" t="n">
-        <v>0.7634026402608463</v>
+        <v>0.4091476041416353</v>
       </c>
       <c r="Q46" t="n">
         <v>54</v>
@@ -5628,25 +5626,25 @@
         <v>66.26506024096386</v>
       </c>
       <c r="X46" t="n">
-        <v>10.37534045472048</v>
+        <v>10.37881744580935</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.0951008645533</v>
+        <v>0.7492795389048901</v>
       </c>
       <c r="Z46" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AA46" t="n">
-        <v>42.5925925925926</v>
+        <v>47.16981132075472</v>
       </c>
       <c r="AB46" t="n">
-        <v>13.21801222200241</v>
+        <v>12.6835380196473</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.925990675990696</v>
+        <v>2.267711962833929</v>
       </c>
       <c r="AE46" t="n">
         <v>38</v>
@@ -5680,7 +5678,7 @@
         <v>46240</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7942527897237316</v>
+        <v>0.7896550833201957</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5708,22 +5706,22 @@
         <v>24.7868707712232</v>
       </c>
       <c r="K47" t="n">
-        <v>6.552655535499929</v>
+        <v>5.935852128564822</v>
       </c>
       <c r="L47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M47" t="n">
-        <v>66.66666666666667</v>
+        <v>70</v>
       </c>
       <c r="N47" t="n">
-        <v>12.37065508502562</v>
+        <v>13.23971601910641</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>3.23534354650743</v>
+        <v>3.836423448506276</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5789,7 +5787,7 @@
         <v>46240</v>
       </c>
       <c r="C48" t="n">
-        <v>0.06135498032178054</v>
+        <v>0.06156703929580488</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5817,7 +5815,7 @@
         <v>28.7395090084999</v>
       </c>
       <c r="K48" t="n">
-        <v>4.545992678733457</v>
+        <v>4.907331168771867</v>
       </c>
       <c r="L48" t="n">
         <v>14</v>
@@ -5832,7 +5830,7 @@
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>5.216849715155081</v>
+        <v>4.85444513218547</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5898,7 +5896,7 @@
         <v>46240</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2605485314490766</v>
+        <v>0.2607668703659392</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5926,7 +5924,7 @@
         <v>23.59168796028241</v>
       </c>
       <c r="K49" t="n">
-        <v>3.109060615562398</v>
+        <v>3.195465710568346</v>
       </c>
       <c r="L49" t="n">
         <v>20</v>
@@ -5941,7 +5939,7 @@
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>1.833921648736458</v>
+        <v>1.748656568393048</v>
       </c>
       <c r="Q49" t="n">
         <v>53</v>
@@ -6007,7 +6005,7 @@
         <v>46240</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7282751885231683</v>
+        <v>0.7282981302992055</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6035,7 +6033,7 @@
         <v>11.86078125763058</v>
       </c>
       <c r="K50" t="n">
-        <v>1.927202207526069</v>
+        <v>1.930413069411796</v>
       </c>
       <c r="L50" t="n">
         <v>63</v>
@@ -6050,7 +6048,7 @@
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>2.033606090995876</v>
+        <v>2.030391978475432</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6116,7 +6114,7 @@
         <v>46240</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1838548161326009</v>
+        <v>0.1842808703226573</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6135,7 +6133,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -6148,16 +6146,16 @@
         <v>27.11346359280836</v>
       </c>
       <c r="K51" t="n">
-        <v>6.562474547389008</v>
+        <v>6.809416072983621</v>
       </c>
       <c r="L51" t="n">
         <v>4</v>
       </c>
       <c r="M51" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N51" t="n">
-        <v>22.48074903415539</v>
+        <v>19.74713983084996</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
@@ -6190,7 +6188,7 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>16.53627723005412</v>
+        <v>16.3428633747532</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6235,7 +6233,7 @@
         <v>46240</v>
       </c>
       <c r="C52" t="n">
-        <v>4.26753306034807</v>
+        <v>4.244553460967182</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6295,22 +6293,22 @@
         <v>12.1710603868542</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.081793756605776</v>
+        <v>2.609058834520561</v>
       </c>
       <c r="Z52" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AA52" t="n">
-        <v>38.88888888888889</v>
+        <v>33.9622641509434</v>
       </c>
       <c r="AB52" t="n">
-        <v>12.49481897677179</v>
+        <v>12.69470510007346</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>6.044030492841546</v>
+        <v>5.535362017212209</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6344,7 +6342,7 @@
         <v>46240</v>
       </c>
       <c r="C53" t="n">
-        <v>1.63683319520314</v>
+        <v>1.633732829654448</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6376,7 +6374,7 @@
         <v>28.17598592067425</v>
       </c>
       <c r="K53" t="n">
-        <v>7.913167472547977</v>
+        <v>7.708766518521237</v>
       </c>
       <c r="L53" t="n">
         <v>5</v>
@@ -6391,7 +6389,7 @@
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>0.08046518278144177</v>
+        <v>0.2703897657473364</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6449,7 +6447,7 @@
         <v>46240</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08719971489551716</v>
+        <v>0.08720246181915421</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6477,7 +6475,7 @@
         <v>42.39442432818535</v>
       </c>
       <c r="K54" t="n">
-        <v>7.880393044296952</v>
+        <v>7.883791440747934</v>
       </c>
       <c r="L54" t="n">
         <v>3</v>
@@ -6492,7 +6490,7 @@
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>1.964774965950222</v>
+        <v>1.961563021646628</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6519,7 +6517,7 @@
         <v>114.7400208810756</v>
       </c>
       <c r="Y54" t="n">
-        <v>37.85487854981646</v>
+        <v>37.85292088397726</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -6564,7 +6562,7 @@
         <v>46240</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8917483594041693</v>
+        <v>0.8938777630422431</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6592,16 +6590,16 @@
         <v>12.31616646597832</v>
       </c>
       <c r="K55" t="n">
-        <v>6.303201326575825</v>
+        <v>6.557042470500041</v>
       </c>
       <c r="L55" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M55" t="n">
-        <v>67.34693877551021</v>
+        <v>70.83333333333333</v>
       </c>
       <c r="N55" t="n">
-        <v>13.01700412313512</v>
+        <v>12.8962223488033</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
@@ -6634,16 +6632,16 @@
         <v>25.41488056506582</v>
       </c>
       <c r="Y55" t="n">
-        <v>6.789277907469316</v>
+        <v>6.566700261389946</v>
       </c>
       <c r="Z55" t="n">
         <v>21</v>
       </c>
       <c r="AA55" t="n">
-        <v>61.90476190476191</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB55" t="n">
-        <v>9.948561667779504</v>
+        <v>10.16668915712046</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6683,7 +6681,7 @@
         <v>46240</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8854447816772985</v>
+        <v>0.9043840834901816</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6711,7 +6709,7 @@
         <v>34.38683570496719</v>
       </c>
       <c r="K56" t="n">
-        <v>12.9132165050676</v>
+        <v>15.32838403477166</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6741,22 +6739,22 @@
         <v>18.27748447537585</v>
       </c>
       <c r="Y56" t="n">
-        <v>4.535324701993481</v>
+        <v>2.493374333826115</v>
       </c>
       <c r="Z56" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA56" t="n">
-        <v>14.28571428571429</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="AB56" t="n">
-        <v>14.3406155753398</v>
+        <v>10.94735490085388</v>
       </c>
       <c r="AC56" t="n">
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>5.724290457122239</v>
+        <v>7.698580086109996</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6782,7 +6780,7 @@
         <v>46240</v>
       </c>
       <c r="C57" t="n">
-        <v>1.42251091330513</v>
+        <v>1.412049404114389</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6814,17 +6812,13 @@
         <v>32.76213282665623</v>
       </c>
       <c r="K57" t="n">
-        <v>21.80566086411435</v>
+        <v>20.90987087143619</v>
       </c>
       <c r="L57" t="n">
-        <v>3</v>
-      </c>
-      <c r="M57" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N57" t="n">
-        <v>15.65787039974029</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
         <v>10</v>
       </c>
@@ -6856,7 +6850,7 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>12.30141604199737</v>
+        <v>12.94637386517494</v>
       </c>
       <c r="Z57" t="n">
         <v>5</v>
@@ -6905,7 +6899,7 @@
         <v>46240</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7631550702789794</v>
+        <v>0.7623385860670008</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6937,7 +6931,7 @@
         <v>16.33691982084211</v>
       </c>
       <c r="K58" t="n">
-        <v>2.881142467459163</v>
+        <v>2.771072008903075</v>
       </c>
       <c r="L58" t="n">
         <v>28</v>
@@ -6946,13 +6940,13 @@
         <v>85.71428571428571</v>
       </c>
       <c r="N58" t="n">
-        <v>19.66632034833653</v>
+        <v>20.15533012800163</v>
       </c>
       <c r="O58" t="n">
         <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>2.059519832034362</v>
+        <v>2.168828199927542</v>
       </c>
       <c r="Q58" t="n">
         <v>24</v>
@@ -6979,7 +6973,7 @@
         <v>41.32985472592288</v>
       </c>
       <c r="Y58" t="n">
-        <v>13.92646728821598</v>
+        <v>14.01855562421133</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -7024,7 +7018,7 @@
         <v>46240</v>
       </c>
       <c r="C59" t="n">
-        <v>0.810642187754292</v>
+        <v>0.8085664120075375</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7041,7 +7035,11 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H59" t="n">
         <v>5</v>
       </c>
@@ -7084,16 +7082,16 @@
         <v>10.2478061424703</v>
       </c>
       <c r="Y59" t="n">
-        <v>7.954881315389494</v>
+        <v>8.190577196826343</v>
       </c>
       <c r="Z59" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA59" t="n">
-        <v>70.58823529411765</v>
+        <v>75</v>
       </c>
       <c r="AB59" t="n">
-        <v>13.8254719095032</v>
+        <v>13.74479814113217</v>
       </c>
       <c r="AC59" t="n">
         <v>6</v>
@@ -7133,7 +7131,7 @@
         <v>46240</v>
       </c>
       <c r="C60" t="n">
-        <v>13.29007670901372</v>
+        <v>13.22745744395466</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7161,22 +7159,22 @@
         <v>17.06238107085701</v>
       </c>
       <c r="K60" t="n">
-        <v>4.591454069529011</v>
+        <v>4.098647283782597</v>
       </c>
       <c r="L60" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M60" t="n">
-        <v>48.38709677419355</v>
+        <v>50</v>
       </c>
       <c r="N60" t="n">
-        <v>12.05258119927817</v>
+        <v>12.16113743442288</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>3.258914373831256</v>
+        <v>3.747745833413152</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7242,7 +7240,7 @@
         <v>46240</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6219545859874075</v>
+        <v>0.6232349258198198</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7274,7 +7272,7 @@
         <v>32.27682383221734</v>
       </c>
       <c r="K61" t="n">
-        <v>0.4934072082516616</v>
+        <v>0.7002803707660599</v>
       </c>
       <c r="L61" t="n">
         <v>8</v>
@@ -7289,7 +7287,7 @@
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>9.459916879967967</v>
+        <v>9.235048398071498</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7347,7 +7345,7 @@
         <v>46240</v>
       </c>
       <c r="C62" t="n">
-        <v>8.840790158604777</v>
+        <v>8.825309176268398</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7375,16 +7373,16 @@
         <v>12.64888173871529</v>
       </c>
       <c r="K62" t="n">
-        <v>6.24879953885018</v>
+        <v>6.062748771960114</v>
       </c>
       <c r="L62" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M62" t="n">
-        <v>71.11111111111111</v>
+        <v>71.73913043478261</v>
       </c>
       <c r="N62" t="n">
-        <v>12.3763888608676</v>
+        <v>12.85416131712193</v>
       </c>
       <c r="O62" t="n">
         <v>6</v>
@@ -7456,7 +7454,7 @@
         <v>46240</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1033789382949465</v>
+        <v>0.1029619424910621</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7473,11 +7471,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>5</v>
       </c>
@@ -7488,22 +7482,22 @@
         <v>31.14790266414816</v>
       </c>
       <c r="K63" t="n">
-        <v>3.600095712447282</v>
+        <v>3.182207834058959</v>
       </c>
       <c r="L63" t="n">
         <v>3</v>
       </c>
       <c r="M63" t="n">
-        <v>100</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N63" t="n">
-        <v>8.331563656967848</v>
+        <v>9.813599242264171</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>1.351257716439092</v>
+        <v>1.761730247974991</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7530,7 +7524,7 @@
         <v>10.24796802016521</v>
       </c>
       <c r="Y63" t="n">
-        <v>6.029927287641257</v>
+        <v>6.40897089805218</v>
       </c>
       <c r="Z63" t="n">
         <v>11</v>
@@ -7539,13 +7533,13 @@
         <v>63.63636363636363</v>
       </c>
       <c r="AB63" t="n">
-        <v>12.46566142394676</v>
+        <v>12.49876729611108</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>4.224826689781425</v>
+        <v>3.836937296667764</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7579,7 +7573,7 @@
         <v>46240</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1563291249208959</v>
+        <v>0.1561239182842182</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7604,10 +7598,10 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>20.54832742781827</v>
+        <v>20.54582457929801</v>
       </c>
       <c r="K64" t="n">
-        <v>0.5405399926954102</v>
+        <v>0.405401751278367</v>
       </c>
       <c r="L64" t="n">
         <v>41</v>
@@ -7616,13 +7610,13 @@
         <v>63.41463414634146</v>
       </c>
       <c r="N64" t="n">
-        <v>14.00923472969788</v>
+        <v>14.12842797055185</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.435484440036408</v>
+        <v>4.576046874552886</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7688,7 +7682,7 @@
         <v>46240</v>
       </c>
       <c r="C65" t="n">
-        <v>6.146003853575514</v>
+        <v>6.17246326316391</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7720,7 +7714,7 @@
         <v>28.12381406175567</v>
       </c>
       <c r="K65" t="n">
-        <v>1.26334807449644</v>
+        <v>1.699301006975751</v>
       </c>
       <c r="L65" t="n">
         <v>17</v>
@@ -7729,13 +7723,13 @@
         <v>82.35294117647059</v>
       </c>
       <c r="N65" t="n">
-        <v>15.22565301073229</v>
+        <v>15.45749138105129</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>8.627654617025172</v>
+        <v>8.162002010667614</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7801,7 +7795,7 @@
         <v>46240</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4265431574585299</v>
+        <v>0.4278173814577695</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7900,7 +7894,7 @@
         <v>46240</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02815605247238052</v>
+        <v>0.02815693943085459</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7928,7 +7922,7 @@
         <v>18.49825117353735</v>
       </c>
       <c r="K67" t="n">
-        <v>4.573343110354777</v>
+        <v>4.576637329703348</v>
       </c>
       <c r="L67" t="n">
         <v>2</v>
@@ -7956,7 +7950,7 @@
         <v>10.87173616493582</v>
       </c>
       <c r="Y67" t="n">
-        <v>5.680792303289417</v>
+        <v>5.677821104801417</v>
       </c>
       <c r="Z67" t="n">
         <v>3</v>
@@ -7993,7 +7987,7 @@
         <v>46240</v>
       </c>
       <c r="C68" t="n">
-        <v>3.454369217221166</v>
+        <v>3.422959073761277</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8022,7 +8016,7 @@
         <v>10</v>
       </c>
       <c r="J68" t="n">
-        <v>12.03526755137827</v>
+        <v>12.83511976516236</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -8034,7 +8028,7 @@
         <v>80</v>
       </c>
       <c r="N68" t="n">
-        <v>15.55496830427127</v>
+        <v>15.9555472372298</v>
       </c>
       <c r="O68" t="n">
         <v>2</v>
@@ -8067,7 +8061,7 @@
         <v>119.0888955077547</v>
       </c>
       <c r="Y68" t="n">
-        <v>12.03526755137827</v>
+        <v>12.83511976516236</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -8112,7 +8106,7 @@
         <v>46240</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4002781837253012</v>
+        <v>0.4000807019891304</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8144,7 +8138,7 @@
         <v>29.4573350207784</v>
       </c>
       <c r="K69" t="n">
-        <v>2.389738448112189</v>
+        <v>2.339223321040729</v>
       </c>
       <c r="L69" t="n">
         <v>10</v>
@@ -8159,7 +8153,7 @@
         <v>3</v>
       </c>
       <c r="P69" t="n">
-        <v>0.5960182740354147</v>
+        <v>0.6456729468098388</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8209,7 +8203,7 @@
         <v>46240</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4139360020047883</v>
+        <v>0.4091161037440056</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8237,22 +8231,22 @@
         <v>20.66985845799666</v>
       </c>
       <c r="K70" t="n">
-        <v>6.184967114767459</v>
+        <v>4.948542315187443</v>
       </c>
       <c r="L70" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M70" t="n">
-        <v>50</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N70" t="n">
-        <v>8.934628394870565</v>
+        <v>9.17358300998244</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>1.709312471011848</v>
+        <v>2.90757510061288</v>
       </c>
       <c r="Q70" t="n">
         <v>30</v>
@@ -8318,7 +8312,7 @@
         <v>46240</v>
       </c>
       <c r="C71" t="n">
-        <v>3.284172379689451</v>
+        <v>3.296883228386014</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8346,22 +8340,22 @@
         <v>20.51701021225919</v>
       </c>
       <c r="K71" t="n">
-        <v>4.832132891803465</v>
+        <v>5.237868409210011</v>
       </c>
       <c r="L71" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M71" t="n">
-        <v>68.96551724137932</v>
+        <v>67.85714285714286</v>
       </c>
       <c r="N71" t="n">
-        <v>11.98090556200918</v>
+        <v>12.35555698952126</v>
       </c>
       <c r="O71" t="n">
         <v>6</v>
       </c>
       <c r="P71" t="n">
-        <v>1.1140354354918</v>
+        <v>0.7241990001417564</v>
       </c>
       <c r="Q71" t="n">
         <v>43</v>
@@ -8427,7 +8421,7 @@
         <v>46240</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07753420372120984</v>
+        <v>0.07774677236537746</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8455,16 +8449,16 @@
         <v>20.36571476939619</v>
       </c>
       <c r="K72" t="n">
-        <v>8.397601533599808</v>
+        <v>8.694785616019374</v>
       </c>
       <c r="L72" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M72" t="n">
-        <v>61.53846153846154</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N72" t="n">
-        <v>14.52327366036347</v>
+        <v>14.76921865557234</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
@@ -8497,7 +8491,7 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>13.67834481159975</v>
+        <v>13.4416843917458</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -8542,7 +8536,7 @@
         <v>46240</v>
       </c>
       <c r="C73" t="n">
-        <v>0.06891929044563272</v>
+        <v>0.06913158770693015</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8567,25 +8561,25 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>22.20804087883598</v>
+        <v>22.20559031381362</v>
       </c>
       <c r="K73" t="n">
-        <v>0.3058100936135233</v>
+        <v>0.6116201872270244</v>
       </c>
       <c r="L73" t="n">
         <v>22</v>
       </c>
       <c r="M73" t="n">
-        <v>63.63636363636363</v>
+        <v>68.18181818181819</v>
       </c>
       <c r="N73" t="n">
-        <v>17.02474442198509</v>
+        <v>16.55352964721532</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>9.664634478639943</v>
+        <v>9.331307651444497</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8651,7 +8645,7 @@
         <v>46240</v>
       </c>
       <c r="C74" t="n">
-        <v>4.98194034589189</v>
+        <v>5.038831350919892</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8679,22 +8673,22 @@
         <v>18.35970785011217</v>
       </c>
       <c r="K74" t="n">
-        <v>5.403405359096292</v>
+        <v>6.607053987526301</v>
       </c>
       <c r="L74" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M74" t="n">
-        <v>63.33333333333334</v>
+        <v>56</v>
       </c>
       <c r="N74" t="n">
-        <v>19.98684471942212</v>
+        <v>18.9315259078591</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>2.463482685457308</v>
+        <v>1.306617114320296</v>
       </c>
       <c r="Q74" t="n">
         <v>35</v>
@@ -8721,7 +8715,7 @@
         <v>95.98093909010421</v>
       </c>
       <c r="Y74" t="n">
-        <v>13.94835192890326</v>
+        <v>12.96568967219488</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
@@ -8766,7 +8760,7 @@
         <v>46240</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1334260644636039</v>
+        <v>0.1323796416364278</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8791,25 +8785,25 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>19.32404686587293</v>
+        <v>19.32150545065303</v>
       </c>
       <c r="K75" t="n">
-        <v>2.584811606609261</v>
+        <v>1.777061856765161</v>
       </c>
       <c r="L75" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M75" t="n">
-        <v>72.72727272727273</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N75" t="n">
-        <v>10.83572863913616</v>
+        <v>11.85404116615281</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>3.329136487073026</v>
+        <v>4.149204217722402</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8875,7 +8869,7 @@
         <v>46240</v>
       </c>
       <c r="C76" t="n">
-        <v>1.867964964055552</v>
+        <v>1.872226271673313</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8903,22 +8897,22 @@
         <v>20.51082830683794</v>
       </c>
       <c r="K76" t="n">
-        <v>7.777458420584393</v>
+        <v>8.023326471339143</v>
       </c>
       <c r="L76" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M76" t="n">
-        <v>53.84615384615385</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N76" t="n">
-        <v>9.784914623553925</v>
+        <v>9.761903539512996</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>2.062158091298172</v>
+        <v>1.829858043841415</v>
       </c>
       <c r="Q76" t="n">
         <v>40</v>
@@ -8984,7 +8978,7 @@
         <v>46240</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5215173119332754</v>
+        <v>0.5194324684473607</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9012,16 +9006,16 @@
         <v>20.65935288471739</v>
       </c>
       <c r="K77" t="n">
-        <v>7.409638339176916</v>
+        <v>6.980252238865536</v>
       </c>
       <c r="L77" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M77" t="n">
-        <v>46.15384615384615</v>
+        <v>51.85185185185185</v>
       </c>
       <c r="N77" t="n">
-        <v>10.30623200640147</v>
+        <v>11.33815338459839</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -9054,22 +9048,22 @@
         <v>13.00517396479135</v>
       </c>
       <c r="Y77" t="n">
-        <v>4.951574719364471</v>
+        <v>5.331545020941231</v>
       </c>
       <c r="Z77" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="AA77" t="n">
-        <v>54.3859649122807</v>
+        <v>52.83018867924528</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.12731655578788</v>
+        <v>10.77858371723429</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>5.311424429946932</v>
+        <v>4.931373370455294</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9103,7 +9097,7 @@
         <v>46240</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05421090410442571</v>
+        <v>0.05442273802918411</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9131,16 +9125,16 @@
         <v>12.76206508896208</v>
       </c>
       <c r="K78" t="n">
-        <v>6.998515233843783</v>
+        <v>7.416621439592475</v>
       </c>
       <c r="L78" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M78" t="n">
-        <v>60.8695652173913</v>
+        <v>68.18181818181819</v>
       </c>
       <c r="N78" t="n">
-        <v>17.21197307077892</v>
+        <v>16.13062039734869</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
@@ -9173,22 +9167,22 @@
         <v>23.16536029857119</v>
       </c>
       <c r="Y78" t="n">
-        <v>6.656704924522372</v>
+        <v>6.291957704892326</v>
       </c>
       <c r="Z78" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA78" t="n">
-        <v>47.36842105263158</v>
+        <v>50</v>
       </c>
       <c r="AB78" t="n">
-        <v>13.25512377513977</v>
+        <v>12.59914204489547</v>
       </c>
       <c r="AC78" t="n">
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>3.581719579080889</v>
+        <v>3.957016072782971</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9222,7 +9216,7 @@
         <v>46240</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8988924354114044</v>
+        <v>0.8951384700150257</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9250,22 +9244,22 @@
         <v>12.46716859924595</v>
       </c>
       <c r="K79" t="n">
-        <v>4.092268755821382</v>
+        <v>3.657557371515363</v>
       </c>
       <c r="L79" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M79" t="n">
-        <v>53.06122448979592</v>
+        <v>50</v>
       </c>
       <c r="N79" t="n">
-        <v>10.48581150109307</v>
+        <v>10.28630761445481</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>0.872044826218521</v>
+        <v>1.295074534385598</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9331,7 +9325,7 @@
         <v>46240</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1296439120281752</v>
+        <v>0.1281771073635865</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9359,7 +9353,7 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>6.14333030849834</v>
+        <v>4.942413662465261</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -9370,7 +9364,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>3.633454575329909</v>
+        <v>4.819392046576954</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9397,22 +9391,22 @@
         <v>11.5318431483495</v>
       </c>
       <c r="Y80" t="n">
-        <v>4.831367157345234</v>
+        <v>5.908114938188158</v>
       </c>
       <c r="Z80" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AA80" t="n">
-        <v>35</v>
+        <v>37.5</v>
       </c>
       <c r="AB80" t="n">
-        <v>12.77169324801085</v>
+        <v>11.5451345579825</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>3.329492867564421</v>
+        <v>2.223236425157826</v>
       </c>
       <c r="AE80" t="n">
         <v>26</v>
@@ -9446,11 +9440,11 @@
         <v>46240</v>
       </c>
       <c r="C81" t="n">
-        <v>1.088420495535893</v>
+        <v>1.076897845913704</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9474,22 +9468,22 @@
         <v>12.04277302023445</v>
       </c>
       <c r="K81" t="n">
-        <v>3.922527546441357</v>
+        <v>2.822343492868939</v>
       </c>
       <c r="L81" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M81" t="n">
-        <v>43.47826086956522</v>
+        <v>44.68085106382978</v>
       </c>
       <c r="N81" t="n">
-        <v>14.60263830628129</v>
+        <v>13.24544604600182</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>5.848079908220782</v>
+        <v>6.980638899393354</v>
       </c>
       <c r="Q81" t="n">
         <v>31</v>
@@ -9516,22 +9510,22 @@
         <v>27.31228182970742</v>
       </c>
       <c r="Y81" t="n">
-        <v>8.592626562867212</v>
+        <v>9.56031794806308</v>
       </c>
       <c r="Z81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA81" t="n">
-        <v>25</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB81" t="n">
-        <v>15.30045963659641</v>
+        <v>9.438232199299446</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.539671674408993</v>
+        <v>0.4861605458590823</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9565,7 +9559,7 @@
         <v>46240</v>
       </c>
       <c r="C82" t="n">
-        <v>5.26350073613903</v>
+        <v>5.284679185313101</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9622,25 +9616,25 @@
         <v>57.14285714285715</v>
       </c>
       <c r="X82" t="n">
-        <v>18.78314306215709</v>
+        <v>18.78688491181513</v>
       </c>
       <c r="Y82" t="n">
-        <v>2.529182879377434</v>
+        <v>2.140077821011677</v>
       </c>
       <c r="Z82" t="n">
         <v>9</v>
       </c>
       <c r="AA82" t="n">
-        <v>44.44444444444444</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB82" t="n">
-        <v>14.94796830916254</v>
+        <v>13.13899195875419</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>1.508982035928141</v>
+        <v>1.900596421471168</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9674,7 +9668,7 @@
         <v>46240</v>
       </c>
       <c r="C83" t="n">
-        <v>5.888607110989873</v>
+        <v>5.883539450845599</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9702,7 +9696,7 @@
         <v>14.0949513048101</v>
       </c>
       <c r="K83" t="n">
-        <v>8.800631257344648</v>
+        <v>8.706998822321822</v>
       </c>
       <c r="L83" t="n">
         <v>31</v>
@@ -9717,7 +9711,7 @@
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>1.102354580846598</v>
+        <v>1.189436919136688</v>
       </c>
       <c r="Q83" t="n">
         <v>44</v>
@@ -9744,22 +9738,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>2.11734703707096</v>
+        <v>2.201583599281109</v>
       </c>
       <c r="Z83" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AA83" t="n">
-        <v>56.89655172413793</v>
+        <v>54.3859649122807</v>
       </c>
       <c r="AB83" t="n">
-        <v>11.2408989891791</v>
+        <v>11.43680207503701</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>3.966640508200692</v>
+        <v>3.883924239790626</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9793,7 +9787,7 @@
         <v>46240</v>
       </c>
       <c r="C84" t="n">
-        <v>2.20835895934154</v>
+        <v>2.208428526007347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9821,7 +9815,7 @@
         <v>14.10735630446007</v>
       </c>
       <c r="K84" t="n">
-        <v>5.719778147397525</v>
+        <v>5.723108481193306</v>
       </c>
       <c r="L84" t="n">
         <v>39</v>
@@ -9902,7 +9896,7 @@
         <v>46240</v>
       </c>
       <c r="C85" t="n">
-        <v>6.597761401787047</v>
+        <v>6.661007163993053</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9930,22 +9924,22 @@
         <v>15.13449360257271</v>
       </c>
       <c r="K85" t="n">
-        <v>2.38664068752874</v>
+        <v>3.368113150028118</v>
       </c>
       <c r="L85" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M85" t="n">
-        <v>54.90196078431372</v>
+        <v>51.02040816326531</v>
       </c>
       <c r="N85" t="n">
-        <v>13.1715021887886</v>
+        <v>13.46665735539501</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>5.482511463192297</v>
+        <v>4.480962947683098</v>
       </c>
       <c r="Q85" t="n">
         <v>34</v>
@@ -10011,7 +10005,7 @@
         <v>46240</v>
       </c>
       <c r="C86" t="n">
-        <v>3.971264028464178</v>
+        <v>3.960882808872841</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10068,25 +10062,25 @@
         <v>69.23076923076923</v>
       </c>
       <c r="X86" t="n">
-        <v>56.06930016097078</v>
+        <v>56.6501336995608</v>
       </c>
       <c r="Y86" t="n">
-        <v>0.3690020881679357</v>
+        <v>0.9978959878527482</v>
       </c>
       <c r="Z86" t="n">
         <v>5</v>
       </c>
       <c r="AA86" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AB86" t="n">
-        <v>8.457591085917171</v>
+        <v>8.88736983675275</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>5.651853368783066</v>
+        <v>5.052522935809034</v>
       </c>
       <c r="AE86" t="n">
         <v>51</v>
@@ -10120,7 +10114,7 @@
         <v>46240</v>
       </c>
       <c r="C87" t="n">
-        <v>5.531403468217962</v>
+        <v>5.489552434047903</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10148,7 +10142,7 @@
         <v>26.73202875980171</v>
       </c>
       <c r="K87" t="n">
-        <v>1.840856065850649</v>
+        <v>1.070320130150204</v>
       </c>
       <c r="L87" t="n">
         <v>16</v>
@@ -10157,13 +10151,13 @@
         <v>62.5</v>
       </c>
       <c r="N87" t="n">
-        <v>13.89511345784383</v>
+        <v>14.27632919573386</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>3.10203984548858</v>
+        <v>3.888065126131468</v>
       </c>
       <c r="Q87" t="n">
         <v>47</v>
@@ -10229,7 +10223,7 @@
         <v>46240</v>
       </c>
       <c r="C88" t="n">
-        <v>1.030847717868171</v>
+        <v>1.036763704954474</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10257,7 +10251,7 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>15.48751888744251</v>
+        <v>16.15029638456911</v>
       </c>
       <c r="L88" t="n">
         <v>6</v>
@@ -10296,25 +10290,25 @@
         <v>68.35443037974683</v>
       </c>
       <c r="X88" t="n">
-        <v>15.62875348080186</v>
+        <v>16.29154441961764</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.1221448723675689</v>
+        <v>0.1214602796389741</v>
       </c>
       <c r="Z88" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AA88" t="n">
-        <v>30.50847457627119</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB88" t="n">
-        <v>12.26169163870217</v>
+        <v>12.08910023020015</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>5.885043406389945</v>
+        <v>5.885688494064601</v>
       </c>
       <c r="AE88" t="n">
         <v>31</v>
@@ -10348,7 +10342,7 @@
         <v>46240</v>
       </c>
       <c r="C89" t="n">
-        <v>2.107501556440806</v>
+        <v>2.126479194574212</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10365,7 +10359,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H89" t="n">
         <v>5</v>
       </c>
@@ -10376,16 +10374,16 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>14.47601818589006</v>
+        <v>15.50685227540498</v>
       </c>
       <c r="L89" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M89" t="n">
-        <v>66.66666666666667</v>
+        <v>75</v>
       </c>
       <c r="N89" t="n">
-        <v>14.19332941038719</v>
+        <v>16.70454998265742</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
@@ -10418,22 +10416,22 @@
         <v>28.7873334490923</v>
       </c>
       <c r="Y89" t="n">
-        <v>8.091955875117939</v>
+        <v>7.264341965358034</v>
       </c>
       <c r="Z89" t="n">
         <v>17</v>
       </c>
       <c r="AA89" t="n">
-        <v>23.52941176470588</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AB89" t="n">
-        <v>17.51130243662222</v>
+        <v>13.77949730923438</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>2.076036045647389</v>
+        <v>2.949952685535528</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10467,7 +10465,7 @@
         <v>46240</v>
       </c>
       <c r="C90" t="n">
-        <v>2.868135131668573</v>
+        <v>2.901845835897742</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10495,16 +10493,16 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>13.0626009251122</v>
+        <v>14.39148527825276</v>
       </c>
       <c r="L90" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="M90" t="n">
-        <v>72.22222222222223</v>
+        <v>70</v>
       </c>
       <c r="N90" t="n">
-        <v>14.83784955153763</v>
+        <v>15.52634973642465</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
@@ -10537,16 +10535,16 @@
         <v>33.24184775233741</v>
       </c>
       <c r="Y90" t="n">
-        <v>5.69077154846076</v>
+        <v>4.582305468425874</v>
       </c>
       <c r="Z90" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA90" t="n">
         <v>50</v>
       </c>
       <c r="AB90" t="n">
-        <v>10.56986052093374</v>
+        <v>10.51857883774578</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
@@ -10586,7 +10584,7 @@
         <v>46240</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2378555956144056</v>
+        <v>0.2374428461158135</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10614,16 +10612,16 @@
         <v>14.34427620336855</v>
       </c>
       <c r="K91" t="n">
-        <v>4.906901620871129</v>
+        <v>4.724857255124704</v>
       </c>
       <c r="L91" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M91" t="n">
-        <v>58.8235294117647</v>
+        <v>59.61538461538461</v>
       </c>
       <c r="N91" t="n">
-        <v>14.76152527384818</v>
+        <v>15.26367243033973</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
@@ -10695,7 +10693,7 @@
         <v>46240</v>
       </c>
       <c r="C92" t="n">
-        <v>1.111533720538566</v>
+        <v>1.10316364703355</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10723,7 +10721,7 @@
         <v>22.28274626067631</v>
       </c>
       <c r="K92" t="n">
-        <v>5.493324002846278</v>
+        <v>4.698937957801697</v>
       </c>
       <c r="L92" t="n">
         <v>20</v>
@@ -10732,13 +10730,13 @@
         <v>65</v>
       </c>
       <c r="N92" t="n">
-        <v>13.65852513941646</v>
+        <v>13.94637883112967</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>2.376146567422688</v>
+        <v>3.152908813199984</v>
       </c>
       <c r="Q92" t="n">
         <v>56</v>
@@ -10804,7 +10802,7 @@
         <v>46240</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04223407755291195</v>
+        <v>0.04244553418941901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10832,22 +10830,22 @@
         <v>18.40038502869544</v>
       </c>
       <c r="K93" t="n">
-        <v>2.426469749947513</v>
+        <v>2.93929631175609</v>
       </c>
       <c r="L93" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M93" t="n">
-        <v>59.18367346938776</v>
+        <v>55.31914893617022</v>
       </c>
       <c r="N93" t="n">
-        <v>14.81503794226588</v>
+        <v>17.14938892187325</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>3.488873783091928</v>
+        <v>2.973309317147876</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10913,7 +10911,7 @@
         <v>46240</v>
       </c>
       <c r="C94" t="n">
-        <v>6.487448512107487</v>
+        <v>6.582209760633514</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10941,16 +10939,16 @@
         <v>12.24049282186025</v>
       </c>
       <c r="K94" t="n">
-        <v>8.97996757386661</v>
+        <v>10.57182264174918</v>
       </c>
       <c r="L94" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M94" t="n">
-        <v>54.16666666666666</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N94" t="n">
-        <v>12.71643650941258</v>
+        <v>13.06957274637224</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
@@ -10983,22 +10981,22 @@
         <v>46.65531127586331</v>
       </c>
       <c r="Y94" t="n">
-        <v>4.359717534278151</v>
+        <v>2.962713371714165</v>
       </c>
       <c r="Z94" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA94" t="n">
-        <v>40</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB94" t="n">
-        <v>10.2252458307341</v>
+        <v>11.014852533138</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>1.715053974573677</v>
+        <v>3.130020153923474</v>
       </c>
       <c r="AE94" t="n">
         <v>37</v>
@@ -11032,7 +11030,7 @@
         <v>46240</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1405701406809587</v>
+        <v>0.1407846900099751</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11060,22 +11058,22 @@
         <v>23.400044414021</v>
       </c>
       <c r="K95" t="n">
-        <v>1.394156494872023</v>
+        <v>1.54891232094414</v>
       </c>
       <c r="L95" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M95" t="n">
-        <v>64</v>
+        <v>65.38461538461539</v>
       </c>
       <c r="N95" t="n">
-        <v>19.79473256227971</v>
+        <v>19.60590204166581</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>4.54251375458794</v>
+        <v>4.383195818964802</v>
       </c>
       <c r="Q95" t="n">
         <v>23</v>
@@ -11141,7 +11139,7 @@
         <v>46240</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1317451078256355</v>
+        <v>0.1315391368410983</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11169,7 +11167,7 @@
         <v>12.85874206974231</v>
       </c>
       <c r="K96" t="n">
-        <v>1.900445943171691</v>
+        <v>1.741134257735344</v>
       </c>
       <c r="L96" t="n">
         <v>73</v>
@@ -11178,13 +11176,13 @@
         <v>60.27397260273973</v>
       </c>
       <c r="N96" t="n">
-        <v>12.8932908073108</v>
+        <v>12.82733746537946</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>7.948497164914592</v>
+        <v>8.11752866971478</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11211,7 +11209,7 @@
         <v>16.74415231729489</v>
       </c>
       <c r="Y96" t="n">
-        <v>11.20266956857795</v>
+        <v>11.34149577529709</v>
       </c>
       <c r="Z96" t="n">
         <v>15</v>
@@ -11260,7 +11258,7 @@
         <v>46240</v>
       </c>
       <c r="C97" t="n">
-        <v>1.846952985068969</v>
+        <v>1.845960470553466</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11288,22 +11286,22 @@
         <v>20.83793142975532</v>
       </c>
       <c r="K97" t="n">
-        <v>3.336691313821261</v>
+        <v>3.281160303047193</v>
       </c>
       <c r="L97" t="n">
         <v>30</v>
       </c>
       <c r="M97" t="n">
-        <v>53.33333333333334</v>
+        <v>50</v>
       </c>
       <c r="N97" t="n">
-        <v>13.50638102302412</v>
+        <v>14.06887767617043</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>0.6418907725275869</v>
+        <v>0.696002731614942</v>
       </c>
       <c r="Q97" t="n">
         <v>50</v>
@@ -11369,7 +11367,7 @@
         <v>46240</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6601963814393947</v>
+        <v>0.6589564313124181</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11388,7 +11386,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H98" t="n">
@@ -11401,22 +11399,22 @@
         <v>18.49937747698907</v>
       </c>
       <c r="K98" t="n">
-        <v>9.958807436510497</v>
+        <v>9.75228792038434</v>
       </c>
       <c r="L98" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M98" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="N98" t="n">
-        <v>11.9239160746963</v>
+        <v>13.04478611817466</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>0.03746181360988476</v>
+        <v>0.2257010621913969</v>
       </c>
       <c r="Q98" t="n">
         <v>48</v>
@@ -11443,22 +11441,22 @@
         <v>10.71387422840049</v>
       </c>
       <c r="Y98" t="n">
-        <v>0.6819983467765911</v>
+        <v>0.8685327965602729</v>
       </c>
       <c r="Z98" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA98" t="n">
-        <v>39.21568627450981</v>
+        <v>40.38461538461539</v>
       </c>
       <c r="AB98" t="n">
-        <v>11.44074982040592</v>
+        <v>12.23255013477923</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>7.36825301698556</v>
+        <v>7.193949009959044</v>
       </c>
       <c r="AE98" t="n">
         <v>50</v>
@@ -11492,16 +11490,16 @@
         <v>46240</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4836957659366499</v>
+        <v>0.4824502156377095</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -11520,7 +11518,7 @@
         <v>28.77817890954801</v>
       </c>
       <c r="K99" t="n">
-        <v>4.058995174245572</v>
+        <v>3.791036011328908</v>
       </c>
       <c r="L99" t="n">
         <v>18</v>
@@ -11529,13 +11527,13 @@
         <v>66.66666666666667</v>
       </c>
       <c r="N99" t="n">
-        <v>12.71234207232084</v>
+        <v>12.82986200275538</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>0.2013314412318667</v>
       </c>
       <c r="Q99" t="n">
         <v>35</v>
@@ -11601,7 +11599,7 @@
         <v>46240</v>
       </c>
       <c r="C100" t="n">
-        <v>328.1165591696308</v>
+        <v>327.9818999099119</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11629,7 +11627,7 @@
         <v>25.15478290083538</v>
       </c>
       <c r="K100" t="n">
-        <v>7.05770457436643</v>
+        <v>7.013768019376121</v>
       </c>
       <c r="L100" t="n">
         <v>13</v>
@@ -11710,7 +11708,7 @@
         <v>46240</v>
       </c>
       <c r="C101" t="n">
-        <v>327.6389470379006</v>
+        <v>328.1651243928274</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11738,7 +11736,7 @@
         <v>13.42090796247281</v>
       </c>
       <c r="K101" t="n">
-        <v>3.753112080056975</v>
+        <v>3.919736159926801</v>
       </c>
       <c r="L101" t="n">
         <v>34</v>
@@ -11747,7 +11745,7 @@
         <v>32.35294117647059</v>
       </c>
       <c r="N101" t="n">
-        <v>8.34505652045217</v>
+        <v>7.906266739941217</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11819,7 +11817,7 @@
         <v>46240</v>
       </c>
       <c r="C102" t="n">
-        <v>397.972955781057</v>
+        <v>399.7450960079855</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11918,7 +11916,7 @@
         <v>46240</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7202906140254492</v>
+        <v>0.7207335667589788</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11946,7 +11944,7 @@
         <v>30.74202968074841</v>
       </c>
       <c r="K103" t="n">
-        <v>10.7795025293866</v>
+        <v>10.84762792559328</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
@@ -11988,7 +11986,7 @@
         <v>14.26498323563516</v>
       </c>
       <c r="Y103" t="n">
-        <v>3.050348941163261</v>
+        <v>2.99072840451452</v>
       </c>
       <c r="Z103" t="n">
         <v>50</v>
@@ -11997,13 +11995,13 @@
         <v>40</v>
       </c>
       <c r="AB103" t="n">
-        <v>11.60528731344739</v>
+        <v>11.58097532289587</v>
       </c>
       <c r="AC103" t="n">
         <v>10</v>
       </c>
       <c r="AD103" t="n">
-        <v>7.168309512139592</v>
+        <v>7.225362566078342</v>
       </c>
       <c r="AE103" t="n">
         <v>41</v>
@@ -12037,7 +12035,7 @@
         <v>46240</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04895790935777997</v>
+        <v>0.04895945160638247</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12069,7 +12067,7 @@
         <v>27.75739442390626</v>
       </c>
       <c r="K104" t="n">
-        <v>1.253897105002322</v>
+        <v>1.257086756753312</v>
       </c>
       <c r="L104" t="n">
         <v>21</v>
@@ -12078,13 +12076,13 @@
         <v>76.19047619047619</v>
       </c>
       <c r="N104" t="n">
-        <v>15.59629030718294</v>
+        <v>15.58903477762779</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>2.712096001746889</v>
+        <v>2.708860516435663</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>

--- a/TDA_Result.xlsx
+++ b/TDA_Result.xlsx
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4526123042288233</v>
+        <v>0.4536573510560203</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -739,22 +739,22 @@
         <v>14.94856954517825</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.972151180004492</v>
+        <v>4.752739221962599</v>
       </c>
       <c r="Z2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AA2" t="n">
-        <v>44.11764705882353</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.73616807324932</v>
+        <v>10.76204541000136</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.186275242040826</v>
+        <v>3.409295712560967</v>
       </c>
       <c r="AE2" t="n">
         <v>43</v>
@@ -763,10 +763,10 @@
         <v>53.48837209302326</v>
       </c>
       <c r="AG2" t="n">
-        <v>35.49954416339999</v>
+        <v>35.54963360883827</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.98882792962327</v>
+        <v>17.93873848418499</v>
       </c>
       <c r="AI2" t="n">
         <v>38.91564047231397</v>
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" t="n">
-        <v>0.742166469928462</v>
+        <v>0.7274450494530948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,22 +848,22 @@
         <v>12.13279917920569</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.451881546904733</v>
+        <v>4.386820575432071</v>
       </c>
       <c r="Z3" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AA3" t="n">
-        <v>45</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.50156852205022</v>
+        <v>10.51048519875236</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>7.737841152440761</v>
+        <v>5.87071725712911</v>
       </c>
       <c r="AE3" t="n">
         <v>38</v>
@@ -872,10 +872,10 @@
         <v>60.52631578947368</v>
       </c>
       <c r="AG3" t="n">
-        <v>32.24210038018699</v>
+        <v>32.72355667318509</v>
       </c>
       <c r="AH3" t="n">
-        <v>28.28421540928669</v>
+        <v>27.80275911628859</v>
       </c>
       <c r="AI3" t="n">
         <v>44.71786799604255</v>
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C4" t="n">
-        <v>1.420454492411954</v>
+        <v>1.416107038415637</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,19 +922,19 @@
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>27.63389482946404</v>
+        <v>23.54405567752772</v>
       </c>
       <c r="K4" t="n">
-        <v>9.981383364902729</v>
+        <v>9.644773493073355</v>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M4" t="n">
-        <v>60</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N4" t="n">
-        <v>13.69615600604336</v>
+        <v>13.32021955243562</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -949,40 +949,40 @@
         <v>58.49056603773585</v>
       </c>
       <c r="S4" t="n">
-        <v>37.96921228915578</v>
+        <v>38.32922985242704</v>
       </c>
       <c r="T4" t="n">
-        <v>20.52135374858006</v>
+        <v>20.16133618530881</v>
       </c>
       <c r="U4" t="n">
         <v>45.09442218134437</v>
       </c>
       <c r="V4" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W4" t="n">
-        <v>61.64383561643836</v>
+        <v>62.5</v>
       </c>
       <c r="X4" t="n">
-        <v>11.23805603488277</v>
+        <v>12.1087988317258</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.129714699064821</v>
+        <v>2.19788755595437</v>
       </c>
       <c r="Z4" t="n">
         <v>58</v>
       </c>
       <c r="AA4" t="n">
-        <v>37.93103448275862</v>
+        <v>32.75862068965517</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.52873663594415</v>
+        <v>11.61845741265214</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>8.971639228041429</v>
+        <v>7.977447775997026</v>
       </c>
       <c r="AE4" t="n">
         <v>45</v>
@@ -991,10 +991,10 @@
         <v>60</v>
       </c>
       <c r="AG4" t="n">
-        <v>38.03914789647139</v>
+        <v>36.82394641834451</v>
       </c>
       <c r="AH4" t="n">
-        <v>21.96085210352861</v>
+        <v>23.17605358165549</v>
       </c>
       <c r="AI4" t="n">
         <v>45.45185459035139</v>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2660200305899085</v>
+        <v>0.264144314086122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
         <v>62</v>
       </c>
       <c r="S5" t="n">
-        <v>44.99047771145579</v>
+        <v>44.86047771145579</v>
       </c>
       <c r="T5" t="n">
-        <v>17.00952228854421</v>
+        <v>17.13952228854421</v>
       </c>
       <c r="U5" t="n">
         <v>48.15044693099298</v>
@@ -1076,22 +1076,22 @@
         <v>16.70172291026088</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.781454206133806</v>
+        <v>5.452843489925852</v>
       </c>
       <c r="Z5" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="AA5" t="n">
-        <v>31.42857142857143</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.33118271183639</v>
+        <v>17.06253747739354</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.480598081348099</v>
+        <v>4.809405885823381</v>
       </c>
       <c r="AE5" t="n">
         <v>44</v>
@@ -1100,10 +1100,10 @@
         <v>50</v>
       </c>
       <c r="AG5" t="n">
-        <v>26.14098445825691</v>
+        <v>26.2626935873381</v>
       </c>
       <c r="AH5" t="n">
-        <v>23.85901554174309</v>
+        <v>23.7373064126619</v>
       </c>
       <c r="AI5" t="n">
         <v>35.8317605399894</v>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C6" t="n">
-        <v>2.030871774735866</v>
+        <v>1.971648634620116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,16 +1153,16 @@
         <v>23.73506360720576</v>
       </c>
       <c r="K6" t="n">
-        <v>6.964721522998318</v>
+        <v>3.845476492857181</v>
       </c>
       <c r="L6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M6" t="n">
-        <v>55</v>
+        <v>73.68421052631579</v>
       </c>
       <c r="N6" t="n">
-        <v>9.409115462639447</v>
+        <v>13.53822118044896</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
@@ -1171,31 +1171,31 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R6" t="n">
-        <v>67.5</v>
+        <v>65.85365853658537</v>
       </c>
       <c r="S6" t="n">
-        <v>48.17580730943047</v>
+        <v>49.69053325824036</v>
       </c>
       <c r="T6" t="n">
-        <v>19.32419269056953</v>
+        <v>16.16312527834501</v>
       </c>
       <c r="U6" t="n">
-        <v>52.01774618987768</v>
+        <v>50.5498365198297</v>
       </c>
       <c r="V6" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W6" t="n">
-        <v>75.64102564102564</v>
+        <v>74.68354430379746</v>
       </c>
       <c r="X6" t="n">
         <v>44.49622708587002</v>
       </c>
       <c r="Y6" t="n">
-        <v>18.42342316775585</v>
+        <v>20.80231340592837</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1237,14 +1237,14 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C7" t="n">
-        <v>2.149593227736786</v>
+        <v>2.092190679079578</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1265,25 +1265,25 @@
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>11.35312764557068</v>
+        <v>11.72442900972028</v>
       </c>
       <c r="K7" t="n">
-        <v>2.98405058080109</v>
+        <v>0.6555738880178685</v>
       </c>
       <c r="L7" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M7" t="n">
-        <v>58.20895522388059</v>
+        <v>61.76470588235294</v>
       </c>
       <c r="N7" t="n">
-        <v>12.61338027889698</v>
+        <v>13.3664732084733</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01548727119293769</v>
+        <v>2.329156768397511</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1292,10 +1292,10 @@
         <v>58.8235294117647</v>
       </c>
       <c r="S7" t="n">
-        <v>51.16039193471492</v>
+        <v>51.33940159127875</v>
       </c>
       <c r="T7" t="n">
-        <v>7.663137477049787</v>
+        <v>7.484127820485952</v>
       </c>
       <c r="U7" t="n">
         <v>45.16533720637157</v>
@@ -1310,22 +1310,22 @@
         <v>13.79329344082609</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.70786013621635</v>
+        <v>11.14571741680933</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AA7" t="n">
-        <v>60</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.615798389642457</v>
+        <v>8.16676137028197</v>
       </c>
       <c r="AC7" t="n">
         <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.415390049692822</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3288478220356737</v>
+        <v>0.3303900258097036</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,22 +1387,22 @@
         <v>22.10694516187944</v>
       </c>
       <c r="K8" t="n">
-        <v>4.556441562877711</v>
+        <v>5.046781860037752</v>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
         <v>50</v>
       </c>
       <c r="N8" t="n">
-        <v>15.13025449178977</v>
+        <v>17.20097034198387</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>3.293492381386587</v>
+        <v>2.811336137738207</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1465,19 +1465,19 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5963387309743748</v>
+        <v>0.5869873469330338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1492,27 +1492,17 @@
       <c r="I9" t="n">
         <v>10</v>
       </c>
-      <c r="J9" t="n">
-        <v>10.25501703215621</v>
-      </c>
-      <c r="K9" t="n">
-        <v>7.29895832302585</v>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>18</v>
-      </c>
-      <c r="M9" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="N9" t="n">
-        <v>10.75145883361706</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
         <v>2</v>
       </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
         <v>35</v>
       </c>
@@ -1574,10 +1564,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C10" t="n">
-        <v>2.099162857647467</v>
+        <v>2.037684583270695</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,22 +1595,22 @@
         <v>10.23694539327734</v>
       </c>
       <c r="K10" t="n">
-        <v>3.939391989637575</v>
+        <v>0.8953144727292139</v>
       </c>
       <c r="L10" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="M10" t="n">
-        <v>30</v>
+        <v>40.47619047619047</v>
       </c>
       <c r="N10" t="n">
-        <v>8.866752637384604</v>
+        <v>9.764403333337537</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>5.830905775325923</v>
+        <v>9.023893304511855</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1629,10 +1619,10 @@
         <v>51.16279069767442</v>
       </c>
       <c r="S10" t="n">
-        <v>37.22786100783294</v>
+        <v>37.50055988518298</v>
       </c>
       <c r="T10" t="n">
-        <v>13.93492968984147</v>
+        <v>13.66223081249144</v>
       </c>
       <c r="U10" t="n">
         <v>36.75230846944931</v>
@@ -1661,10 +1651,10 @@
         <v>53.33333333333334</v>
       </c>
       <c r="AG10" t="n">
-        <v>39.93002956818746</v>
+        <v>40.12944416748765</v>
       </c>
       <c r="AH10" t="n">
-        <v>13.40330376514587</v>
+        <v>13.20388916584569</v>
       </c>
       <c r="AI10" t="n">
         <v>36.1422996198733</v>
@@ -1683,24 +1673,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C11" t="n">
-        <v>7.296639551093337</v>
+        <v>7.468365798031903</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1714,16 +1704,16 @@
         <v>20.56423081971027</v>
       </c>
       <c r="K11" t="n">
-        <v>4.548362025934338</v>
+        <v>7.008905363531182</v>
       </c>
       <c r="L11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M11" t="n">
-        <v>72.22222222222223</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N11" t="n">
-        <v>14.54040142703891</v>
+        <v>14.25086188382207</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1738,10 +1728,10 @@
         <v>61.22448979591837</v>
       </c>
       <c r="S11" t="n">
-        <v>51.34398374686223</v>
+        <v>51.44602456318876</v>
       </c>
       <c r="T11" t="n">
-        <v>9.880506049056137</v>
+        <v>9.778465232729602</v>
       </c>
       <c r="U11" t="n">
         <v>47.24599944352045</v>
@@ -1752,17 +1742,27 @@
       <c r="W11" t="n">
         <v>61.76470588235294</v>
       </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
+      <c r="X11" t="n">
+        <v>10.68850982866312</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.324287652645852</v>
+      </c>
       <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>11.14381797994836</v>
+      </c>
       <c r="AC11" t="n">
         <v>3</v>
       </c>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
       <c r="AE11" t="n">
         <v>45</v>
       </c>
@@ -1792,14 +1792,14 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C12" t="n">
-        <v>6.676766644664961</v>
+        <v>6.682222029818019</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1827,7 +1827,7 @@
         <v>20.08266526523165</v>
       </c>
       <c r="K12" t="n">
-        <v>16.24054507517847</v>
+        <v>16.33552172743171</v>
       </c>
       <c r="L12" t="n">
         <v>4</v>
@@ -1866,25 +1866,25 @@
         <v>70.58823529411765</v>
       </c>
       <c r="X12" t="n">
-        <v>16.33200105084738</v>
+        <v>18.79909748165969</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.07861635220125507</v>
+        <v>2.073732718894006</v>
       </c>
       <c r="Z12" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AA12" t="n">
-        <v>38.46153846153846</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="AB12" t="n">
-        <v>12.14070721441706</v>
+        <v>11.47145741891312</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.922895357985843</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -1915,24 +1915,24 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3000605063197125</v>
+        <v>0.2848985047452868</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1943,13 +1943,13 @@
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>38.11781916800814</v>
+        <v>38.41151038872205</v>
       </c>
       <c r="K13" t="n">
-        <v>5.442748061987768</v>
+        <v>0.5921533577945892</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1957,7 +1957,7 @@
         <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4.381899079669971</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1978,12 +1978,8 @@
         <v>0</v>
       </c>
       <c r="W13" t="inlineStr"/>
-      <c r="X13" t="n">
-        <v>35.74308703619145</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>22.32182841556056</v>
-      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
@@ -1992,9 +1988,7 @@
       <c r="AC13" t="n">
         <v>10</v>
       </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="n">
         <v>0</v>
       </c>
@@ -2014,10 +2008,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C14" t="n">
-        <v>8.032081982449037</v>
+        <v>8.060594103419696</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,10 +2053,10 @@
         <v>60.97560975609756</v>
       </c>
       <c r="S14" t="n">
-        <v>35.04345016472312</v>
+        <v>35.29072284515984</v>
       </c>
       <c r="T14" t="n">
-        <v>25.93215959137444</v>
+        <v>25.68488691093772</v>
       </c>
       <c r="U14" t="n">
         <v>45.72685693412379</v>
@@ -2077,16 +2071,16 @@
         <v>14.33662537827827</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.174907327424318</v>
+        <v>6.845398704731442</v>
       </c>
       <c r="Z14" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AA14" t="n">
-        <v>39.1304347826087</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.74339053151457</v>
+        <v>11.58494518108551</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2101,10 +2095,10 @@
         <v>52.63157894736842</v>
       </c>
       <c r="AG14" t="n">
-        <v>26.90236404365634</v>
+        <v>26.96855224142348</v>
       </c>
       <c r="AH14" t="n">
-        <v>25.72921490371208</v>
+        <v>25.66302670594494</v>
       </c>
       <c r="AI14" t="n">
         <v>37.25897138449667</v>
@@ -2123,10 +2117,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C15" t="n">
-        <v>12.34492652632782</v>
+        <v>12.23239703340804</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,19 +2145,19 @@
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>15.99936296068698</v>
+        <v>14.74031958141837</v>
       </c>
       <c r="K15" t="n">
-        <v>16.23415119410488</v>
+        <v>15.17462523694844</v>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N15" t="n">
-        <v>28.57987049720584</v>
+        <v>21.98911348984758</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
@@ -2193,25 +2187,25 @@
         <v>79.56989247311827</v>
       </c>
       <c r="X15" t="n">
-        <v>17.02553264904345</v>
+        <v>17.12346148492163</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.6762468300929858</v>
+        <v>1.663916198569737</v>
       </c>
       <c r="Z15" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="AA15" t="n">
-        <v>34.04255319148936</v>
+        <v>31.48148148148148</v>
       </c>
       <c r="AB15" t="n">
-        <v>11.36592399615845</v>
+        <v>11.506728548456</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>9.387234042553183</v>
+        <v>8.477136244578631</v>
       </c>
       <c r="AE15" t="n">
         <v>31</v>
@@ -2220,10 +2214,10 @@
         <v>58.06451612903226</v>
       </c>
       <c r="AG15" t="n">
-        <v>24.45565362405026</v>
+        <v>23.43818908765165</v>
       </c>
       <c r="AH15" t="n">
-        <v>33.60886250498199</v>
+        <v>34.62632704138061</v>
       </c>
       <c r="AI15" t="n">
         <v>40.76626249536972</v>
@@ -2242,10 +2236,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C16" t="n">
-        <v>37.57060192182833</v>
+        <v>37.21080502879053</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,22 +2267,22 @@
         <v>17.40096492560246</v>
       </c>
       <c r="K16" t="n">
-        <v>8.292244523897452</v>
+        <v>7.25517801107296</v>
       </c>
       <c r="L16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M16" t="n">
-        <v>70.37037037037037</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N16" t="n">
-        <v>16.41520330597012</v>
+        <v>15.06614223841034</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>1.576987792256634</v>
+        <v>2.559151026390238</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2297,10 +2291,10 @@
         <v>67.85714285714286</v>
       </c>
       <c r="S16" t="n">
-        <v>54.20959311151343</v>
+        <v>54.03239530931563</v>
       </c>
       <c r="T16" t="n">
-        <v>13.64754974562943</v>
+        <v>13.82474754782723</v>
       </c>
       <c r="U16" t="n">
         <v>49.33884318085762</v>
@@ -2351,10 +2345,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C17" t="n">
-        <v>0.749731033678815</v>
+        <v>0.7534401587357346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2373,7 +2367,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.09: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %77.27: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2386,22 +2380,22 @@
         <v>14.16674936134154</v>
       </c>
       <c r="K17" t="n">
-        <v>6.48020747658955</v>
+        <v>7.006994267953193</v>
       </c>
       <c r="L17" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M17" t="n">
-        <v>76.08695652173913</v>
+        <v>77.27272727272727</v>
       </c>
       <c r="N17" t="n">
-        <v>16.03425148948132</v>
+        <v>16.09615650604118</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>1.427300490323136</v>
+        <v>0.9279820808350658</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2410,10 +2404,10 @@
         <v>65.21739130434783</v>
       </c>
       <c r="S17" t="n">
-        <v>46.12044224483081</v>
+        <v>46.198317268358</v>
       </c>
       <c r="T17" t="n">
-        <v>19.09694905951702</v>
+        <v>19.01907403598982</v>
       </c>
       <c r="U17" t="n">
         <v>50.77005884206276</v>
@@ -2428,22 +2422,22 @@
         <v>15.7396793517258</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.000257065683824</v>
+        <v>7.545109104056269</v>
       </c>
       <c r="Z17" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="AA17" t="n">
-        <v>57.69230769230769</v>
+        <v>51.61290322580645</v>
       </c>
       <c r="AB17" t="n">
-        <v>10.7297595688137</v>
+        <v>11.26949414919576</v>
       </c>
       <c r="AC17" t="n">
         <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.173639697823837</v>
+        <v>2.655230969561861</v>
       </c>
       <c r="AE17" t="n">
         <v>35</v>
@@ -2452,10 +2446,10 @@
         <v>60</v>
       </c>
       <c r="AG17" t="n">
-        <v>42.74770185573249</v>
+        <v>42.75246376049439</v>
       </c>
       <c r="AH17" t="n">
-        <v>17.25229814426751</v>
+        <v>17.24753623950561</v>
       </c>
       <c r="AI17" t="n">
         <v>43.5727090128925</v>
@@ -2474,10 +2468,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1035923160445253</v>
+        <v>0.1056577216093927</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,25 +2496,25 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>24.80221998015493</v>
+        <v>24.37863714425642</v>
       </c>
       <c r="K18" t="n">
-        <v>3.666683507016844</v>
+        <v>5.733571797406145</v>
       </c>
       <c r="L18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M18" t="n">
-        <v>52.63157894736842</v>
+        <v>60</v>
       </c>
       <c r="N18" t="n">
-        <v>17.67867101612232</v>
+        <v>16.45192868322132</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>6.109307521692342</v>
+        <v>4.035074319411702</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2529,10 +2523,10 @@
         <v>77.19298245614036</v>
       </c>
       <c r="S18" t="n">
-        <v>41.9297113507373</v>
+        <v>41.88485489140715</v>
       </c>
       <c r="T18" t="n">
-        <v>35.26327110540306</v>
+        <v>35.3081275647332</v>
       </c>
       <c r="U18" t="n">
         <v>64.79398895432649</v>
@@ -2561,10 +2555,10 @@
         <v>59.52380952380953</v>
       </c>
       <c r="AG18" t="n">
-        <v>39.52539606551272</v>
+        <v>39.55867819556905</v>
       </c>
       <c r="AH18" t="n">
-        <v>19.9984134582968</v>
+        <v>19.96513132824047</v>
       </c>
       <c r="AI18" t="n">
         <v>44.49431275003934</v>
@@ -2583,10 +2577,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02500504392685225</v>
+        <v>0.02494696350248397</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2611,25 +2605,25 @@
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>19.67465331637003</v>
+        <v>18.34152851742537</v>
       </c>
       <c r="K19" t="n">
-        <v>1.238134914264011</v>
+        <v>1.002984204060309</v>
       </c>
       <c r="L19" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M19" t="n">
-        <v>65.625</v>
+        <v>57.57575757575758</v>
       </c>
       <c r="N19" t="n">
-        <v>20.64312188935456</v>
+        <v>18.29602034729423</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>8.654708122740695</v>
+        <v>8.907673240389279</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2692,10 +2686,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C20" t="n">
-        <v>1.851213630777436</v>
+        <v>1.867877561201524</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,19 +2746,19 @@
         <v>70.49180327868852</v>
       </c>
       <c r="X20" t="n">
-        <v>19.7256789664253</v>
+        <v>16.65604614151002</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.55291282679038</v>
+        <v>5.711737214695233</v>
       </c>
       <c r="Z20" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AA20" t="n">
-        <v>55</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB20" t="n">
-        <v>11.03630868831303</v>
+        <v>13.1471808178665</v>
       </c>
       <c r="AC20" t="n">
         <v>4</v>
@@ -2801,10 +2795,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9384245392579769</v>
+        <v>0.9471460184428765</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2832,22 +2826,22 @@
         <v>13.9566823466854</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5386573013811402</v>
+        <v>1.473038032329521</v>
       </c>
       <c r="L21" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M21" t="n">
-        <v>62.06896551724138</v>
+        <v>54.23728813559322</v>
       </c>
       <c r="N21" t="n">
-        <v>17.35617357110112</v>
+        <v>17.64651861840198</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>7.421366963607112</v>
+        <v>6.432213023513667</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2888,10 +2882,10 @@
         <v>61.53846153846154</v>
       </c>
       <c r="AG21" t="n">
-        <v>34.78776096001112</v>
+        <v>34.85374889364611</v>
       </c>
       <c r="AH21" t="n">
-        <v>26.75070057845042</v>
+        <v>26.68471264481543</v>
       </c>
       <c r="AI21" t="n">
         <v>45.89906145692508</v>
@@ -2910,14 +2904,14 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C22" t="n">
-        <v>0.316870623028816</v>
+        <v>0.3331153265122002</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2927,10 +2921,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>5</v>
       </c>
@@ -2941,64 +2939,64 @@
         <v>20.35908649698318</v>
       </c>
       <c r="K22" t="n">
-        <v>6.824579920216856</v>
+        <v>12.30105359566762</v>
       </c>
       <c r="L22" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M22" t="n">
-        <v>63.63636363636363</v>
+        <v>80</v>
       </c>
       <c r="N22" t="n">
-        <v>12.75000060540042</v>
+        <v>17.21117446734009</v>
       </c>
       <c r="O22" t="n">
+        <v>10</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2</v>
       </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S22" t="n">
-        <v>92.85714285714286</v>
+        <v>92.26190476190476</v>
       </c>
       <c r="T22" t="n">
-        <v>-92.85714285714286</v>
+        <v>-42.26190476190476</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>9.453120573423075</v>
       </c>
       <c r="V22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W22" t="n">
-        <v>83.33333333333333</v>
+        <v>73.68421052631579</v>
       </c>
       <c r="X22" t="n">
-        <v>13.74898285979678</v>
+        <v>19.29777531785657</v>
       </c>
       <c r="Y22" t="n">
-        <v>6.087441632875712</v>
+        <v>5.864922211287604</v>
       </c>
       <c r="Z22" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AA22" t="n">
-        <v>39.1304347826087</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB22" t="n">
-        <v>15.59589356828433</v>
+        <v>12.75464260894753</v>
       </c>
       <c r="AC22" t="n">
         <v>6</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>0.1434935752808175</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3021,44 +3019,58 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C23" t="n">
-        <v>0.967422006177813</v>
+        <v>0.8993485029113496</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>SATMA_BEKLE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>5</v>
       </c>
       <c r="I23" t="n">
         <v>10</v>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>13.07033123031079</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.851858071735224</v>
+      </c>
       <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="M23" t="n">
+        <v>62.16216216216216</v>
+      </c>
+      <c r="N23" t="n">
+        <v>17.46543687934854</v>
+      </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>3.090902795359418</v>
+      </c>
       <c r="Q23" t="n">
         <v>6</v>
       </c>
@@ -3081,46 +3093,46 @@
         <v>87.5</v>
       </c>
       <c r="X23" t="n">
-        <v>43.33476743273008</v>
+        <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.073682273684231</v>
+        <v>11.4605171424666</v>
       </c>
       <c r="Z23" t="n">
         <v>4</v>
       </c>
       <c r="AA23" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AB23" t="n">
-        <v>14.99838693058465</v>
+        <v>12.55681756557071</v>
       </c>
       <c r="AC23" t="n">
         <v>6</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.019115752007229</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF23" t="n">
-        <v>70</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="AG23" t="n">
-        <v>72.72772657450075</v>
+        <v>74.81176724164101</v>
       </c>
       <c r="AH23" t="n">
-        <v>-2.72772657450075</v>
+        <v>-2.084494514368274</v>
       </c>
       <c r="AI23" t="n">
-        <v>39.67781474611454</v>
+        <v>43.43546988238708</v>
       </c>
       <c r="AJ23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK23" t="n">
-        <v>46.15384615384615</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
@@ -3130,10 +3142,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1834403453551926</v>
+        <v>0.1807082452140766</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3161,22 +3173,22 @@
         <v>22.86774633531589</v>
       </c>
       <c r="K24" t="n">
-        <v>4.803749615323794</v>
+        <v>3.242837055117409</v>
       </c>
       <c r="L24" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M24" t="n">
-        <v>60</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N24" t="n">
-        <v>11.14400172635923</v>
+        <v>11.15287235946911</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>4.95807678995146</v>
+        <v>6.544921795664349</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3239,10 +3251,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C25" t="n">
-        <v>4.032325659741714</v>
+        <v>4.025056093255089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3284,10 +3296,10 @@
         <v>68.18181818181819</v>
       </c>
       <c r="S25" t="n">
-        <v>37.04152801544206</v>
+        <v>37.11438358728957</v>
       </c>
       <c r="T25" t="n">
-        <v>31.14029016637613</v>
+        <v>31.06743459452861</v>
       </c>
       <c r="U25" t="n">
         <v>53.44310393781777</v>
@@ -3316,10 +3328,10 @@
         <v>53.48837209302326</v>
       </c>
       <c r="AG25" t="n">
-        <v>50.9547405806394</v>
+        <v>51.10067347911028</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.533631512383863</v>
+        <v>2.387698613912974</v>
       </c>
       <c r="AI25" t="n">
         <v>38.91564047231397</v>
@@ -3338,10 +3350,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4442072157211318</v>
+        <v>0.4293393069705126</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3437,24 +3449,24 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C27" t="n">
-        <v>35.59541367761587</v>
+        <v>36.47707084512424</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3468,7 +3480,7 @@
         <v>61.00029220182797</v>
       </c>
       <c r="K27" t="n">
-        <v>7.985314221901785</v>
+        <v>10.65998537846296</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3479,7 +3491,7 @@
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>0.01359979197546046</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -3492,17 +3504,27 @@
         <v>0</v>
       </c>
       <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
+      <c r="X27" t="n">
+        <v>14.98462848520752</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>3.761061946902666</v>
+      </c>
       <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>19.9709957394613</v>
+      </c>
       <c r="AC27" t="n">
         <v>5</v>
       </c>
-      <c r="AD27" t="inlineStr"/>
+      <c r="AD27" t="n">
+        <v>1.287356321839073</v>
+      </c>
       <c r="AE27" t="n">
         <v>0</v>
       </c>
@@ -3522,10 +3544,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C28" t="n">
-        <v>1.453024150099245</v>
+        <v>1.452793747598952</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3550,19 +3572,19 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>20.14178232803948</v>
+        <v>18.25342733104113</v>
       </c>
       <c r="K28" t="n">
-        <v>4.208309649629749</v>
+        <v>4.191785591792918</v>
       </c>
       <c r="L28" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="M28" t="n">
-        <v>46.66666666666666</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="N28" t="n">
-        <v>13.66043265150333</v>
+        <v>16.72635294557637</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
@@ -3577,10 +3599,10 @@
         <v>56.41025641025641</v>
       </c>
       <c r="S28" t="n">
-        <v>60.17058821183797</v>
+        <v>61.28894421480936</v>
       </c>
       <c r="T28" t="n">
-        <v>-3.760331801581557</v>
+        <v>-4.878687804552953</v>
       </c>
       <c r="U28" t="n">
         <v>40.97569164866947</v>
@@ -3631,14 +3653,14 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4040730747619026</v>
+        <v>0.4138260747661071</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3648,7 +3670,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3662,16 +3684,16 @@
         <v>20.65475273479386</v>
       </c>
       <c r="K29" t="n">
-        <v>11.16846427251521</v>
+        <v>13.85170673591398</v>
       </c>
       <c r="L29" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>71.42857142857143</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N29" t="n">
-        <v>22.43735037689824</v>
+        <v>18.00706743337966</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
@@ -3695,7 +3717,7 @@
         <v>43.64971778135299</v>
       </c>
       <c r="V29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W29" t="n">
         <v>100</v>
@@ -3704,10 +3726,10 @@
         <v>55.05052857749912</v>
       </c>
       <c r="Y29" t="n">
-        <v>11.79310714204046</v>
+        <v>9.664081774731702</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
@@ -3715,7 +3737,7 @@
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>0.3718545533910711</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3746,10 +3768,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3855819684241491</v>
+        <v>0.3758815468741205</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3777,22 +3799,22 @@
         <v>21.6314445059014</v>
       </c>
       <c r="K30" t="n">
-        <v>4.303438860223707</v>
+        <v>1.679386365764679</v>
       </c>
       <c r="L30" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="M30" t="n">
-        <v>54.54545454545455</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N30" t="n">
-        <v>12.49555200477302</v>
+        <v>13.61680851217371</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>0.6678218353948662</v>
+        <v>3.265768758959942</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3855,10 +3877,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1773466803358939</v>
+        <v>0.1758865728694233</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,11 +3897,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>5</v>
       </c>
@@ -3887,25 +3905,25 @@
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>30.15400413033618</v>
+        <v>31.09418993049242</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4761900215419557</v>
+        <v>1.008623567153566</v>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>75</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N31" t="n">
-        <v>7.316462366850085</v>
+        <v>7.249414780450302</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>9.478673481166201</v>
+        <v>8.901592869314467</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3968,10 +3986,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C32" t="n">
-        <v>2.366023332726425</v>
+        <v>2.354238601817539</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4028,25 +4046,25 @@
         <v>55.76923076923077</v>
       </c>
       <c r="X32" t="n">
-        <v>14.16135113661838</v>
+        <v>15.25475988862757</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.659389982532766</v>
+        <v>3.077505942222258</v>
       </c>
       <c r="Z32" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AA32" t="n">
-        <v>25</v>
+        <v>30.95238095238095</v>
       </c>
       <c r="AB32" t="n">
-        <v>13.30984986546575</v>
+        <v>12.43016672738332</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>6.44760086025602</v>
+        <v>5.078794252697749</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4077,10 +4095,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C33" t="n">
-        <v>1.830200989881558</v>
+        <v>1.826998149403733</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,22 +4126,22 @@
         <v>12.57251846431013</v>
       </c>
       <c r="K33" t="n">
-        <v>2.580659920304251</v>
+        <v>2.401144396243682</v>
       </c>
       <c r="L33" t="n">
         <v>54</v>
       </c>
       <c r="M33" t="n">
-        <v>57.4074074074074</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N33" t="n">
-        <v>11.38704204195266</v>
+        <v>11.46424234246147</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>1.383633211950919</v>
+        <v>1.561364976127133</v>
       </c>
       <c r="Q33" t="n">
         <v>39</v>
@@ -4186,14 +4204,14 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8829511801105722</v>
+        <v>0.8175895189424399</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4203,7 +4221,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -4214,25 +4232,25 @@
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>10.37797163438468</v>
+        <v>14.80663485356992</v>
       </c>
       <c r="K34" t="n">
-        <v>3.133904498658513</v>
+        <v>0.463679318488941</v>
       </c>
       <c r="L34" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="M34" t="n">
-        <v>39.53488372093023</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="N34" t="n">
-        <v>9.105486921275626</v>
+        <v>15.19973050008377</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>0.8397776711273064</v>
+        <v>3.519999173333344</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4255,27 +4273,17 @@
       <c r="W34" t="n">
         <v>48.33333333333334</v>
       </c>
-      <c r="X34" t="n">
-        <v>14.68007915548277</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>7.569302855645654</v>
-      </c>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>11.50882648141719</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
         <v>3</v>
       </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="n">
         <v>40</v>
       </c>
@@ -4283,10 +4291,10 @@
         <v>52.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>26.7568759332134</v>
+        <v>27.05588988514636</v>
       </c>
       <c r="AH34" t="n">
-        <v>25.7431240667866</v>
+        <v>25.44411011485364</v>
       </c>
       <c r="AI34" t="n">
         <v>37.49736210669248</v>
@@ -4305,10 +4313,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C35" t="n">
-        <v>1.949973139225953</v>
+        <v>1.902467919077601</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4327,7 +4335,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %81.82: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4340,16 +4348,16 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>9.930224645244801</v>
+        <v>7.252105948285092</v>
       </c>
       <c r="L35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M35" t="n">
-        <v>77.77777777777777</v>
+        <v>81.81818181818181</v>
       </c>
       <c r="N35" t="n">
-        <v>11.33742913819006</v>
+        <v>13.27568040215743</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4382,7 +4390,7 @@
         <v>42.52272358489104</v>
       </c>
       <c r="Y35" t="n">
-        <v>15.25391389977305</v>
+        <v>17.31849694244031</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -4424,10 +4432,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08194930159518495</v>
+        <v>0.08175895399062738</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4455,16 +4463,16 @@
         <v>18.45194908889744</v>
       </c>
       <c r="K36" t="n">
-        <v>2.425575319700424</v>
+        <v>2.187666484261586</v>
       </c>
       <c r="L36" t="n">
         <v>20</v>
       </c>
       <c r="M36" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="N36" t="n">
-        <v>12.00877207999885</v>
+        <v>11.59571865267865</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4533,10 +4541,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06366830128412851</v>
+        <v>0.06393969209987092</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4564,22 +4572,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>3.641244929191645</v>
+        <v>4.083023356424542</v>
       </c>
       <c r="L37" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M37" t="n">
-        <v>52.23880597014925</v>
+        <v>55.88235294117647</v>
       </c>
       <c r="N37" t="n">
-        <v>20.59198358626421</v>
+        <v>19.25285603332703</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>4.205618210960593</v>
+        <v>3.763319432182577</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4588,10 +4596,10 @@
         <v>55.55555555555556</v>
       </c>
       <c r="S37" t="n">
-        <v>35.22063979309204</v>
+        <v>35.14247721492947</v>
       </c>
       <c r="T37" t="n">
-        <v>20.33491576246352</v>
+        <v>20.41307834062609</v>
       </c>
       <c r="U37" t="n">
         <v>39.5810617556973</v>
@@ -4642,10 +4650,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C38" t="n">
-        <v>1.671555647355581</v>
+        <v>1.629938079430121</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4670,25 +4678,25 @@
         <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>16.08125753671009</v>
+        <v>15.02885014069408</v>
       </c>
       <c r="K38" t="n">
-        <v>5.50486489178581</v>
+        <v>2.87805681151232</v>
       </c>
       <c r="L38" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="M38" t="n">
-        <v>74.28571428571429</v>
+        <v>57.4074074074074</v>
       </c>
       <c r="N38" t="n">
-        <v>11.24175812914092</v>
+        <v>13.87484178911396</v>
       </c>
       <c r="O38" t="n">
         <v>6</v>
       </c>
       <c r="P38" t="n">
-        <v>0.4693007367215118</v>
+        <v>3.034605517683464</v>
       </c>
       <c r="Q38" t="n">
         <v>34</v>
@@ -4697,10 +4705,10 @@
         <v>52.94117647058823</v>
       </c>
       <c r="S38" t="n">
-        <v>49.08858960574084</v>
+        <v>49.48773690843407</v>
       </c>
       <c r="T38" t="n">
-        <v>3.852586864847396</v>
+        <v>3.453439562154159</v>
       </c>
       <c r="U38" t="n">
         <v>36.73671298006892</v>
@@ -4729,10 +4737,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="AG38" t="n">
-        <v>19.61707415469311</v>
+        <v>19.84050728315898</v>
       </c>
       <c r="AH38" t="n">
-        <v>37.52578298816404</v>
+        <v>37.30234985969817</v>
       </c>
       <c r="AI38" t="n">
         <v>40.85741114397492</v>
@@ -4751,10 +4759,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C39" t="n">
-        <v>2.723238388282787</v>
+        <v>2.698045348570359</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4779,19 +4787,19 @@
         <v>10</v>
       </c>
       <c r="J39" t="n">
-        <v>18.47027414490581</v>
+        <v>16.13238434452433</v>
       </c>
       <c r="K39" t="n">
-        <v>7.798029958286312</v>
+        <v>6.800776077999671</v>
       </c>
       <c r="L39" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="M39" t="n">
-        <v>68.75</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N39" t="n">
-        <v>10.24116858981309</v>
+        <v>12.00195659539717</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4800,19 +4808,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R39" t="n">
-        <v>65.11627906976744</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="S39" t="n">
-        <v>50.36106194402293</v>
+        <v>50.88486212738523</v>
       </c>
       <c r="T39" t="n">
-        <v>14.75521712574452</v>
+        <v>13.40085215832907</v>
       </c>
       <c r="U39" t="n">
-        <v>50.17178199285205</v>
+        <v>49.16636571945582</v>
       </c>
       <c r="V39" t="n">
         <v>65</v>
@@ -4824,22 +4832,22 @@
         <v>10.2437411865161</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.218458120077771</v>
+        <v>3.12304813993155</v>
       </c>
       <c r="Z39" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AA39" t="n">
-        <v>38</v>
+        <v>40.47619047619047</v>
       </c>
       <c r="AB39" t="n">
-        <v>11.50825751455693</v>
+        <v>13.62390751815907</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.8673371346159</v>
+        <v>2.969696924634868</v>
       </c>
       <c r="AE39" t="n">
         <v>42</v>
@@ -4870,19 +4878,19 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2027719766604108</v>
+        <v>0.2010431694691391</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4897,27 +4905,17 @@
       <c r="I40" t="n">
         <v>10</v>
       </c>
-      <c r="J40" t="n">
-        <v>13.0200875267008</v>
-      </c>
-      <c r="K40" t="n">
-        <v>10.74176045805229</v>
-      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>22</v>
-      </c>
-      <c r="M40" t="n">
-        <v>50</v>
-      </c>
-      <c r="N40" t="n">
-        <v>12.78131349536254</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="n">
         <v>3</v>
       </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="n">
         <v>27</v>
       </c>
@@ -4940,46 +4938,46 @@
         <v>76.47058823529412</v>
       </c>
       <c r="X40" t="n">
-        <v>14.17330472629232</v>
+        <v>14.39492020679223</v>
       </c>
       <c r="Y40" t="n">
-        <v>3.005557451863627</v>
+        <v>4.018823054510323</v>
       </c>
       <c r="Z40" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AA40" t="n">
-        <v>55.17241379310344</v>
+        <v>50</v>
       </c>
       <c r="AB40" t="n">
-        <v>10.23579542945735</v>
+        <v>12.03512905673069</v>
       </c>
       <c r="AC40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.087231051047379</v>
+        <v>1.022259756250876</v>
       </c>
       <c r="AE40" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF40" t="n">
-        <v>58.33333333333334</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AG40" t="n">
-        <v>15.24897860424176</v>
+        <v>14.77713315727469</v>
       </c>
       <c r="AH40" t="n">
-        <v>43.08435472909157</v>
+        <v>42.36572398558246</v>
       </c>
       <c r="AI40" t="n">
-        <v>31.95113125495497</v>
+        <v>32.59064457965074</v>
       </c>
       <c r="AJ40" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AK40" t="n">
-        <v>47.22222222222222</v>
+        <v>45.94594594594594</v>
       </c>
     </row>
     <row r="41">
@@ -4989,10 +4987,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C41" t="n">
-        <v>1.729340409819243</v>
+        <v>1.719034373161028</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5024,16 +5022,16 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>14.28456316755187</v>
+        <v>13.60348216650358</v>
       </c>
       <c r="L41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M41" t="n">
         <v>100</v>
       </c>
       <c r="N41" t="n">
-        <v>8.290318992161135</v>
+        <v>12.17975430538131</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
@@ -5066,7 +5064,7 @@
         <v>40.81782021738603</v>
       </c>
       <c r="Y41" t="n">
-        <v>11.31378611593602</v>
+        <v>11.84231327356086</v>
       </c>
       <c r="Z41" t="n">
         <v>7</v>
@@ -5112,10 +5110,10 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C42" t="n">
-        <v>3.370427471521584</v>
+        <v>3.465321794226496</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5140,20 +5138,16 @@
         <v>10</v>
       </c>
       <c r="J42" t="n">
-        <v>21.11518617286606</v>
+        <v>19.79504810217467</v>
       </c>
       <c r="K42" t="n">
-        <v>9.657550316459652</v>
+        <v>12.74495660384745</v>
       </c>
       <c r="L42" t="n">
-        <v>6</v>
-      </c>
-      <c r="M42" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="N42" t="n">
-        <v>22.80470238649248</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
         <v>2</v>
       </c>
@@ -5183,22 +5177,22 @@
         <v>14.97530566614946</v>
       </c>
       <c r="Y42" t="n">
-        <v>4.625128255915079</v>
+        <v>1.939850517795727</v>
       </c>
       <c r="Z42" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA42" t="n">
-        <v>41.66666666666666</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB42" t="n">
-        <v>11.25581968481021</v>
+        <v>11.18614412044539</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>5.63552185790307</v>
+        <v>8.219597384630751</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5227,10 +5221,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C43" t="n">
-        <v>7.27562691019746</v>
+        <v>7.127703498472553</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5290,16 +5284,16 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>6.091107868859924</v>
+        <v>8.000403643204058</v>
       </c>
       <c r="Z43" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AA43" t="n">
-        <v>63.63636363636363</v>
+        <v>50</v>
       </c>
       <c r="AB43" t="n">
-        <v>12.72045075786758</v>
+        <v>13.63280086769262</v>
       </c>
       <c r="AC43" t="n">
         <v>2</v>
@@ -5336,10 +5330,10 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C44" t="n">
-        <v>4.990502212770821</v>
+        <v>5.048091247563783</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5356,7 +5350,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %78.26: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H44" t="n">
         <v>5</v>
       </c>
@@ -5367,22 +5365,22 @@
         <v>13.03201987649729</v>
       </c>
       <c r="K44" t="n">
-        <v>2.142334151024339</v>
+        <v>3.321028836341755</v>
       </c>
       <c r="L44" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M44" t="n">
-        <v>65.38461538461539</v>
+        <v>78.26086956521739</v>
       </c>
       <c r="N44" t="n">
-        <v>18.2306631515482</v>
+        <v>19.74854765260397</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>7.692859101259208</v>
+        <v>6.46429022134265</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5409,22 +5407,22 @@
         <v>12.1234692799834</v>
       </c>
       <c r="Y44" t="n">
-        <v>8.90191428525563</v>
+        <v>7.85066721549712</v>
       </c>
       <c r="Z44" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA44" t="n">
-        <v>14.28571428571429</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="AB44" t="n">
-        <v>9.672387522044957</v>
+        <v>9.691917834769438</v>
       </c>
       <c r="AC44" t="n">
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.205388352706782</v>
+        <v>2.332445303244057</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5447,19 +5445,19 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0212227670947095</v>
+        <v>0.02117347194758895</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5474,27 +5472,17 @@
       <c r="I45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" t="n">
-        <v>10.56080028712586</v>
-      </c>
-      <c r="K45" t="n">
-        <v>5.096915440293603</v>
-      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
-        <v>46</v>
-      </c>
-      <c r="M45" t="n">
-        <v>58.69565217391305</v>
-      </c>
-      <c r="N45" t="n">
-        <v>16.76312935190209</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
         <v>10</v>
       </c>
-      <c r="P45" t="n">
-        <v>4.66529825272739</v>
-      </c>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="n">
         <v>37</v>
       </c>
@@ -5556,19 +5544,19 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C46" t="n">
-        <v>9.045941905675109</v>
+        <v>9.480893844659448</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5584,25 +5572,25 @@
         <v>10</v>
       </c>
       <c r="J46" t="n">
-        <v>20.98614247885408</v>
+        <v>20.92024905883424</v>
       </c>
       <c r="K46" t="n">
-        <v>9.551771551402721</v>
+        <v>14.81929990304494</v>
       </c>
       <c r="L46" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="M46" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="N46" t="n">
-        <v>17.6288119769074</v>
+        <v>10.48461562337478</v>
       </c>
       <c r="O46" t="n">
         <v>10</v>
       </c>
       <c r="P46" t="n">
-        <v>0.4091476041416353</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>54</v>
@@ -5626,40 +5614,40 @@
         <v>66.26506024096386</v>
       </c>
       <c r="X46" t="n">
-        <v>10.37881744580935</v>
+        <v>15.26359791262</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.7492795389048901</v>
+        <v>0.385462555066074</v>
       </c>
       <c r="Z46" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA46" t="n">
-        <v>47.16981132075472</v>
+        <v>35.18518518518518</v>
       </c>
       <c r="AB46" t="n">
-        <v>12.6835380196473</v>
+        <v>10.45668142974212</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.267711962833929</v>
+        <v>2.624654505251534</v>
       </c>
       <c r="AE46" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AF46" t="n">
-        <v>57.89473684210526</v>
+        <v>56.75675675675676</v>
       </c>
       <c r="AG46" t="n">
-        <v>17.01873734472678</v>
+        <v>17.51782422577153</v>
       </c>
       <c r="AH46" t="n">
-        <v>40.87599949737848</v>
+        <v>39.23893253098522</v>
       </c>
       <c r="AI46" t="n">
-        <v>42.19234534367055</v>
+        <v>40.91418109016808</v>
       </c>
       <c r="AJ46" t="n">
         <v>81</v>
@@ -5675,10 +5663,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7896550833201957</v>
+        <v>0.7765004239438545</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5706,22 +5694,22 @@
         <v>24.7868707712232</v>
       </c>
       <c r="K47" t="n">
-        <v>5.935852128564822</v>
+        <v>4.171094223588923</v>
       </c>
       <c r="L47" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M47" t="n">
-        <v>70</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="N47" t="n">
-        <v>13.23971601910641</v>
+        <v>15.79730259714992</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>3.836423448506276</v>
+        <v>5.595511710667211</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5784,10 +5772,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C48" t="n">
-        <v>0.06156703929580488</v>
+        <v>0.06058548183340008</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5812,25 +5800,25 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>28.7395090084999</v>
+        <v>21.44820004664813</v>
       </c>
       <c r="K48" t="n">
-        <v>4.907331168771867</v>
+        <v>3.23480354770278</v>
       </c>
       <c r="L48" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="M48" t="n">
-        <v>71.42857142857143</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N48" t="n">
-        <v>12.06150998109382</v>
+        <v>17.70506821122857</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>4.85444513218547</v>
+        <v>6.553212889266713</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5871,10 +5859,10 @@
         <v>60.37735849056604</v>
       </c>
       <c r="AG48" t="n">
-        <v>23.4089869862009</v>
+        <v>23.45615679752166</v>
       </c>
       <c r="AH48" t="n">
-        <v>36.96837150436514</v>
+        <v>36.92120169304438</v>
       </c>
       <c r="AI48" t="n">
         <v>46.94147867320552</v>
@@ -5893,10 +5881,10 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2607668703659392</v>
+        <v>0.2601611745496731</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5921,25 +5909,25 @@
         <v>10</v>
       </c>
       <c r="J49" t="n">
-        <v>23.59168796028241</v>
+        <v>21.9393534200744</v>
       </c>
       <c r="K49" t="n">
-        <v>3.195465710568346</v>
+        <v>2.955768613499221</v>
       </c>
       <c r="L49" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M49" t="n">
-        <v>50</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="N49" t="n">
-        <v>10.06022013884285</v>
+        <v>9.897294507717938</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>1.748656568393048</v>
+        <v>1.985543320233885</v>
       </c>
       <c r="Q49" t="n">
         <v>53</v>
@@ -5948,10 +5936,10 @@
         <v>73.58490566037736</v>
       </c>
       <c r="S49" t="n">
-        <v>38.77300867067283</v>
+        <v>39.05541494364515</v>
       </c>
       <c r="T49" t="n">
-        <v>34.81189698970453</v>
+        <v>34.52949071673221</v>
       </c>
       <c r="U49" t="n">
         <v>60.41933558938148</v>
@@ -5980,10 +5968,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="AG49" t="n">
-        <v>34.52525732504036</v>
+        <v>34.13669582835028</v>
       </c>
       <c r="AH49" t="n">
-        <v>27.1768703345341</v>
+        <v>27.56543183122418</v>
       </c>
       <c r="AI49" t="n">
         <v>47.42656695641357</v>
@@ -6002,10 +5990,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7282981302992055</v>
+        <v>0.7173824188633207</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6030,25 +6018,25 @@
         <v>10</v>
       </c>
       <c r="J50" t="n">
-        <v>11.86078125763058</v>
+        <v>10.06953698454314</v>
       </c>
       <c r="K50" t="n">
-        <v>1.930413069411796</v>
+        <v>0.4107963101010137</v>
       </c>
       <c r="L50" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="M50" t="n">
-        <v>47.61904761904762</v>
+        <v>42.5531914893617</v>
       </c>
       <c r="N50" t="n">
-        <v>13.98988835133535</v>
+        <v>13.52451100484172</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>2.030391978475432</v>
+        <v>3.574519694888556</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6111,10 +6099,10 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1842808703226573</v>
+        <v>0.1861588466190696</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6146,7 +6134,7 @@
         <v>27.11346359280836</v>
       </c>
       <c r="K51" t="n">
-        <v>6.809416072983621</v>
+        <v>7.897893413401502</v>
       </c>
       <c r="L51" t="n">
         <v>4</v>
@@ -6155,7 +6143,7 @@
         <v>100</v>
       </c>
       <c r="N51" t="n">
-        <v>19.74713983084996</v>
+        <v>21.01343299532531</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
@@ -6188,7 +6176,7 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>16.3428633747532</v>
+        <v>15.49032713844796</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6230,10 +6218,10 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C52" t="n">
-        <v>4.244553460967182</v>
+        <v>4.171802929988347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6293,22 +6281,22 @@
         <v>12.1710603868542</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.609058834520561</v>
+        <v>4.278313974660231</v>
       </c>
       <c r="Z52" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="AA52" t="n">
-        <v>33.9622641509434</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB52" t="n">
-        <v>12.69470510007346</v>
+        <v>13.27167146973482</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>5.535362017212209</v>
+        <v>3.888028073758065</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6317,10 +6305,10 @@
         <v>68.42105263157895</v>
       </c>
       <c r="AG52" t="n">
-        <v>35.57125309536485</v>
+        <v>35.71221378586114</v>
       </c>
       <c r="AH52" t="n">
-        <v>32.8497995362141</v>
+        <v>32.70883884571781</v>
       </c>
       <c r="AI52" t="n">
         <v>52.54424010939046</v>
@@ -6339,10 +6327,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C53" t="n">
-        <v>1.633732829654448</v>
+        <v>1.614215204065843</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6361,7 +6349,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -6374,22 +6362,22 @@
         <v>28.17598592067425</v>
       </c>
       <c r="K53" t="n">
-        <v>7.708766518521237</v>
+        <v>6.42200815793692</v>
       </c>
       <c r="L53" t="n">
         <v>5</v>
       </c>
       <c r="M53" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N53" t="n">
-        <v>13.60621978110839</v>
+        <v>11.73282595803085</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>0.2703897657473364</v>
+        <v>1.482768338407259</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6444,10 +6432,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08720246181915421</v>
+        <v>0.08762882179972258</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6475,7 +6463,7 @@
         <v>42.39442432818535</v>
       </c>
       <c r="K54" t="n">
-        <v>7.883791440747934</v>
+        <v>8.411268879604105</v>
       </c>
       <c r="L54" t="n">
         <v>3</v>
@@ -6490,7 +6478,7 @@
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>1.961563021646628</v>
+        <v>1.465466770027635</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6517,7 +6505,7 @@
         <v>114.7400208810756</v>
       </c>
       <c r="Y54" t="n">
-        <v>37.85292088397726</v>
+        <v>37.54906446878523</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -6559,24 +6547,24 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8938777630422431</v>
+        <v>0.8272328632124698</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -6587,25 +6575,25 @@
         <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>12.31616646597832</v>
+        <v>14.36548603251675</v>
       </c>
       <c r="K55" t="n">
-        <v>6.557042470500041</v>
+        <v>0.9723572983773465</v>
       </c>
       <c r="L55" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="M55" t="n">
-        <v>70.83333333333333</v>
+        <v>64.17910447761194</v>
       </c>
       <c r="N55" t="n">
-        <v>12.8962223488033</v>
+        <v>14.3964833592985</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>4.979226826175576</v>
       </c>
       <c r="Q55" t="n">
         <v>44</v>
@@ -6632,16 +6620,16 @@
         <v>25.41488056506582</v>
       </c>
       <c r="Y55" t="n">
-        <v>6.566700261389946</v>
+        <v>13.53281258602396</v>
       </c>
       <c r="Z55" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AA55" t="n">
-        <v>66.66666666666667</v>
+        <v>37.5</v>
       </c>
       <c r="AB55" t="n">
-        <v>10.16668915712046</v>
+        <v>12.23057392064236</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6650,19 +6638,19 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF55" t="n">
-        <v>54.16666666666666</v>
+        <v>55.31914893617022</v>
       </c>
       <c r="AG55" t="n">
-        <v>40.55679911762984</v>
+        <v>40.15796807227672</v>
       </c>
       <c r="AH55" t="n">
-        <v>13.60986754903682</v>
+        <v>15.1611808638935</v>
       </c>
       <c r="AI55" t="n">
-        <v>40.2910745456498</v>
+        <v>41.24545983821874</v>
       </c>
       <c r="AJ55" t="n">
         <v>71</v>
@@ -6678,10 +6666,10 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9043840834901816</v>
+        <v>0.9186351914514095</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6709,7 +6697,7 @@
         <v>34.38683570496719</v>
       </c>
       <c r="K56" t="n">
-        <v>15.32838403477166</v>
+        <v>17.14570621223712</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6736,25 +6724,25 @@
         <v>100</v>
       </c>
       <c r="X56" t="n">
-        <v>18.27748447537585</v>
+        <v>19.34032560415109</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.493374333826115</v>
+        <v>1.838958776762079</v>
       </c>
       <c r="Z56" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AA56" t="n">
-        <v>6.666666666666667</v>
+        <v>22.72727272727273</v>
       </c>
       <c r="AB56" t="n">
-        <v>10.94735490085388</v>
+        <v>9.075451416718147</v>
       </c>
       <c r="AC56" t="n">
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>7.698580086109996</v>
+        <v>8.313930986813878</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6764,10 +6752,10 @@
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="inlineStr"/>
       <c r="AJ56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK56" t="n">
-        <v>33.33333333333334</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57">
@@ -6777,10 +6765,10 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C57" t="n">
-        <v>1.412049404114389</v>
+        <v>1.459082801730304</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6799,7 +6787,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %80.00: SAT yönü değerlendirmeye alınabilir.</t>
+          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -6812,10 +6800,10 @@
         <v>32.76213282665623</v>
       </c>
       <c r="K57" t="n">
-        <v>20.90987087143619</v>
+        <v>24.93721015277799</v>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -6850,16 +6838,16 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>12.94637386517494</v>
+        <v>10.04673890907767</v>
       </c>
       <c r="Z57" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA57" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB57" t="n">
-        <v>12.75692533836235</v>
+        <v>13.75807019707077</v>
       </c>
       <c r="AC57" t="n">
         <v>6</v>
@@ -6883,10 +6871,10 @@
         <v>36.48450865154381</v>
       </c>
       <c r="AJ57" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AK57" t="n">
-        <v>48.62385321100918</v>
+        <v>49.09090909090909</v>
       </c>
     </row>
     <row r="58">
@@ -6896,19 +6884,19 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7623385860670008</v>
+        <v>0.7878209132832233</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6918,7 +6906,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %85.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -6931,22 +6919,22 @@
         <v>16.33691982084211</v>
       </c>
       <c r="K58" t="n">
-        <v>2.771072008903075</v>
+        <v>6.20635146760633</v>
       </c>
       <c r="L58" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M58" t="n">
-        <v>85.71428571428571</v>
+        <v>85</v>
       </c>
       <c r="N58" t="n">
-        <v>20.15533012800163</v>
+        <v>16.32811750653458</v>
       </c>
       <c r="O58" t="n">
         <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>2.168828199927542</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>24</v>
@@ -6973,10 +6961,10 @@
         <v>41.32985472592288</v>
       </c>
       <c r="Y58" t="n">
-        <v>14.01855562421133</v>
+        <v>11.1444950162983</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA58" t="inlineStr"/>
       <c r="AB58" t="inlineStr"/>
@@ -7015,14 +7003,14 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8085664120075375</v>
+        <v>0.8184280915819284</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -7032,14 +7020,10 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>5</v>
       </c>
@@ -7082,43 +7066,43 @@
         <v>10.2478061424703</v>
       </c>
       <c r="Y59" t="n">
-        <v>8.190577196826343</v>
+        <v>7.070823647644497</v>
       </c>
       <c r="Z59" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AA59" t="n">
-        <v>75</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB59" t="n">
-        <v>13.74479814113217</v>
+        <v>14.32858544529427</v>
       </c>
       <c r="AC59" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>3.152052420274409</v>
       </c>
       <c r="AE59" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AF59" t="n">
-        <v>51.21951219512195</v>
+        <v>51.16279069767442</v>
       </c>
       <c r="AG59" t="n">
-        <v>41.10515706114365</v>
+        <v>41.74059437030751</v>
       </c>
       <c r="AH59" t="n">
-        <v>10.1143551339783</v>
+        <v>9.422196327366912</v>
       </c>
       <c r="AI59" t="n">
-        <v>36.48450865154381</v>
+        <v>36.75230846944931</v>
       </c>
       <c r="AJ59" t="n">
         <v>55</v>
       </c>
       <c r="AK59" t="n">
-        <v>47.27272727272727</v>
+        <v>54.54545454545455</v>
       </c>
     </row>
     <row r="60">
@@ -7128,10 +7112,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C60" t="n">
-        <v>13.22745744395466</v>
+        <v>13.39588981036459</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7156,25 +7140,25 @@
         <v>10</v>
       </c>
       <c r="J60" t="n">
-        <v>17.06238107085701</v>
+        <v>15.44754852801727</v>
       </c>
       <c r="K60" t="n">
-        <v>4.098647283782597</v>
+        <v>5.424191635474607</v>
       </c>
       <c r="L60" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M60" t="n">
-        <v>50</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="N60" t="n">
-        <v>12.16113743442288</v>
+        <v>12.9634600651239</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>3.747745833413152</v>
+        <v>2.443280166123318</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7237,10 +7221,10 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6232349258198198</v>
+        <v>0.6226258803579103</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7257,11 +7241,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>5</v>
       </c>
@@ -7269,25 +7249,25 @@
         <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>32.27682383221734</v>
+        <v>30.3360843704085</v>
       </c>
       <c r="K61" t="n">
-        <v>0.7002803707660599</v>
+        <v>1.32183729175126</v>
       </c>
       <c r="L61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M61" t="n">
-        <v>75</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N61" t="n">
-        <v>16.22363039036922</v>
+        <v>12.22538449547143</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>9.235048398071498</v>
+        <v>8.56494803115384</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7329,10 +7309,10 @@
         <v>20.76596008020477</v>
       </c>
       <c r="AJ61" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AK61" t="n">
-        <v>60.52631578947368</v>
+        <v>58.97435897435897</v>
       </c>
     </row>
     <row r="62">
@@ -7342,10 +7322,10 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C62" t="n">
-        <v>8.825309176268398</v>
+        <v>8.84673787163358</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7362,7 +7342,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H62" t="n">
         <v>5</v>
       </c>
@@ -7370,19 +7354,19 @@
         <v>10</v>
       </c>
       <c r="J62" t="n">
-        <v>12.64888173871529</v>
+        <v>10.67683828611802</v>
       </c>
       <c r="K62" t="n">
-        <v>6.062748771960114</v>
+        <v>6.320279277422736</v>
       </c>
       <c r="L62" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M62" t="n">
-        <v>71.73913043478261</v>
+        <v>75</v>
       </c>
       <c r="N62" t="n">
-        <v>12.85416131712193</v>
+        <v>12.07162369147996</v>
       </c>
       <c r="O62" t="n">
         <v>6</v>
@@ -7451,10 +7435,10 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1029619424910621</v>
+        <v>0.1023035113429219</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7479,25 +7463,25 @@
         <v>10</v>
       </c>
       <c r="J63" t="n">
-        <v>31.14790266414816</v>
+        <v>29.14654498090023</v>
       </c>
       <c r="K63" t="n">
-        <v>3.182207834058959</v>
+        <v>2.522368111457429</v>
       </c>
       <c r="L63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M63" t="n">
-        <v>66.66666666666667</v>
+        <v>60</v>
       </c>
       <c r="N63" t="n">
-        <v>9.813599242264171</v>
+        <v>13.09147462811611</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>1.761730247974991</v>
+        <v>2.416674462541679</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7524,22 +7508,22 @@
         <v>10.24796802016521</v>
       </c>
       <c r="Y63" t="n">
-        <v>6.40897089805218</v>
+        <v>7.00747600835121</v>
       </c>
       <c r="Z63" t="n">
         <v>11</v>
       </c>
       <c r="AA63" t="n">
-        <v>63.63636363636363</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB63" t="n">
-        <v>12.49876729611108</v>
+        <v>12.44107905981065</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>3.836937296667764</v>
+        <v>3.218026421045983</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7570,10 +7554,10 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1561239182842182</v>
+        <v>0.157648029899881</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7598,25 +7582,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>20.54582457929801</v>
+        <v>20.58679888238519</v>
       </c>
       <c r="K64" t="n">
-        <v>0.405401751278367</v>
+        <v>1.437889773628465</v>
       </c>
       <c r="L64" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M64" t="n">
-        <v>63.41463414634146</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N64" t="n">
-        <v>14.12842797055185</v>
+        <v>13.84013301975477</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.576046874552886</v>
+        <v>3.511617044006776</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7625,10 +7609,10 @@
         <v>70.37037037037037</v>
       </c>
       <c r="S64" t="n">
-        <v>74.33196236101367</v>
+        <v>74.52373898919379</v>
       </c>
       <c r="T64" t="n">
-        <v>-3.961591990643299</v>
+        <v>-4.153368618823421</v>
       </c>
       <c r="U64" t="n">
         <v>57.17242709884697</v>
@@ -7654,22 +7638,22 @@
         <v>52</v>
       </c>
       <c r="AF64" t="n">
-        <v>61.53846153846154</v>
+        <v>59.61538461538461</v>
       </c>
       <c r="AG64" t="n">
-        <v>38.55549511678084</v>
+        <v>38.79330402819375</v>
       </c>
       <c r="AH64" t="n">
-        <v>22.9829664216807</v>
+        <v>20.82208058719086</v>
       </c>
       <c r="AI64" t="n">
-        <v>47.95987371581939</v>
+        <v>46.06757548486152</v>
       </c>
       <c r="AJ64" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="n">
-        <v>54</v>
+        <v>53.46534653465346</v>
       </c>
     </row>
     <row r="65">
@@ -7679,10 +7663,10 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C65" t="n">
-        <v>6.17246326316391</v>
+        <v>5.744090466416116</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7699,11 +7683,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %82.35: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>5</v>
       </c>
@@ -7711,25 +7691,25 @@
         <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>28.12381406175567</v>
+        <v>32.96849810841169</v>
       </c>
       <c r="K65" t="n">
-        <v>1.699301006975751</v>
+        <v>1.481481481481484</v>
       </c>
       <c r="L65" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="M65" t="n">
-        <v>82.35294117647059</v>
+        <v>50</v>
       </c>
       <c r="N65" t="n">
-        <v>15.45749138105129</v>
+        <v>16.7570516336534</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>8.162002010667614</v>
+        <v>8.394160583941623</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7738,10 +7718,10 @@
         <v>68</v>
       </c>
       <c r="S65" t="n">
-        <v>45.74951102699886</v>
+        <v>45.86884729850905</v>
       </c>
       <c r="T65" t="n">
-        <v>22.25048897300114</v>
+        <v>22.13115270149095</v>
       </c>
       <c r="U65" t="n">
         <v>54.18970269185592</v>
@@ -7770,10 +7750,10 @@
         <v>54.54545454545455</v>
       </c>
       <c r="AG65" t="n">
-        <v>20.99388046371777</v>
+        <v>21.00198287823729</v>
       </c>
       <c r="AH65" t="n">
-        <v>33.55157408173678</v>
+        <v>33.54347166721725</v>
       </c>
       <c r="AI65" t="n">
         <v>40.06618319896197</v>
@@ -7792,10 +7772,10 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4278173814577695</v>
+        <v>0.4280814882618407</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7891,10 +7871,10 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02815693943085459</v>
+        <v>0.02830117607497652</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7922,7 +7902,7 @@
         <v>18.49825117353735</v>
       </c>
       <c r="K67" t="n">
-        <v>4.576637329703348</v>
+        <v>5.112341263685005</v>
       </c>
       <c r="L67" t="n">
         <v>2</v>
@@ -7950,15 +7930,17 @@
         <v>10.87173616493582</v>
       </c>
       <c r="Y67" t="n">
-        <v>5.677821104801417</v>
+        <v>5.194646625432997</v>
       </c>
       <c r="Z67" t="n">
         <v>3</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB67" t="inlineStr"/>
+        <v>33.33333333333334</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>5.358269135191785</v>
+      </c>
       <c r="AC67" t="n">
         <v>3</v>
       </c>
@@ -7984,19 +7966,19 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C68" t="n">
-        <v>3.422959073761277</v>
+        <v>3.666574407070171</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -8004,38 +7986,24 @@
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>5</v>
       </c>
       <c r="I68" t="n">
         <v>10</v>
       </c>
-      <c r="J68" t="n">
-        <v>12.83511976516236</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="n">
-        <v>30</v>
-      </c>
-      <c r="M68" t="n">
-        <v>80</v>
-      </c>
-      <c r="N68" t="n">
-        <v>15.9555472372298</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
         <v>2</v>
       </c>
-      <c r="P68" t="n">
-        <v>2.000000000000002</v>
-      </c>
+      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="n">
         <v>5</v>
       </c>
@@ -8058,10 +8026,10 @@
         <v>80</v>
       </c>
       <c r="X68" t="n">
-        <v>119.0888955077547</v>
+        <v>127.8346976754615</v>
       </c>
       <c r="Y68" t="n">
-        <v>12.83511976516236</v>
+        <v>10.21561028666523</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -8103,19 +8071,19 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4000807019891304</v>
+        <v>0.4066983681230594</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -8123,11 +8091,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>5</v>
       </c>
@@ -8138,22 +8102,22 @@
         <v>29.4573350207784</v>
       </c>
       <c r="K69" t="n">
-        <v>2.339223321040729</v>
+        <v>4.03199882602534</v>
       </c>
       <c r="L69" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M69" t="n">
-        <v>80</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N69" t="n">
-        <v>16.19449547156433</v>
+        <v>15.30141509712112</v>
       </c>
       <c r="O69" t="n">
         <v>3</v>
       </c>
       <c r="P69" t="n">
-        <v>0.6456729468098388</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8200,10 +8164,10 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4091161037440056</v>
+        <v>0.3897176738404715</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8228,25 +8192,25 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>20.66985845799666</v>
+        <v>22.01429878684488</v>
       </c>
       <c r="K70" t="n">
-        <v>4.948542315187443</v>
+        <v>1.695839432706281</v>
       </c>
       <c r="L70" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="M70" t="n">
-        <v>52.63157894736842</v>
+        <v>70</v>
       </c>
       <c r="N70" t="n">
-        <v>9.17358300998244</v>
+        <v>13.32346002337922</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>2.90757510061288</v>
+        <v>6.199034889195532</v>
       </c>
       <c r="Q70" t="n">
         <v>30</v>
@@ -8309,10 +8273,10 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C71" t="n">
-        <v>3.296883228386014</v>
+        <v>3.209563085573939</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8337,25 +8301,25 @@
         <v>10</v>
       </c>
       <c r="J71" t="n">
-        <v>20.51701021225919</v>
+        <v>19.51282806733038</v>
       </c>
       <c r="K71" t="n">
-        <v>5.237868409210011</v>
+        <v>2.450573542467271</v>
       </c>
       <c r="L71" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="M71" t="n">
-        <v>67.85714285714286</v>
+        <v>70</v>
       </c>
       <c r="N71" t="n">
-        <v>12.35555698952126</v>
+        <v>13.99961672524713</v>
       </c>
       <c r="O71" t="n">
         <v>6</v>
       </c>
       <c r="P71" t="n">
-        <v>0.7241990001417564</v>
+        <v>3.464525707180588</v>
       </c>
       <c r="Q71" t="n">
         <v>43</v>
@@ -8396,19 +8360,19 @@
         <v>54.83870967741935</v>
       </c>
       <c r="AG71" t="n">
-        <v>14.94127772585631</v>
+        <v>15.0226990154828</v>
       </c>
       <c r="AH71" t="n">
-        <v>39.89743195156304</v>
+        <v>39.81601066193655</v>
       </c>
       <c r="AI71" t="n">
         <v>37.77216763735451</v>
       </c>
       <c r="AJ71" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AK71" t="n">
-        <v>50.64935064935065</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72">
@@ -8418,10 +8382,10 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07774677236537746</v>
+        <v>0.07840473869283643</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8449,16 +8413,16 @@
         <v>20.36571476939619</v>
       </c>
       <c r="K72" t="n">
-        <v>8.694785616019374</v>
+        <v>9.61466314572068</v>
       </c>
       <c r="L72" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M72" t="n">
-        <v>64.28571428571429</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N72" t="n">
-        <v>14.76921865557234</v>
+        <v>14.39782702990865</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
@@ -8491,10 +8455,10 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>13.4416843917458</v>
+        <v>12.70914649597125</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr"/>
@@ -8520,10 +8484,10 @@
         <v>25.04583645276572</v>
       </c>
       <c r="AJ72" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK72" t="n">
-        <v>48.27586206896552</v>
+        <v>46.66666666666666</v>
       </c>
     </row>
     <row r="73">
@@ -8533,10 +8497,10 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C73" t="n">
-        <v>0.06913158770693015</v>
+        <v>0.06939028868318217</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8561,10 +8525,10 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>22.20559031381362</v>
+        <v>22.14049070857409</v>
       </c>
       <c r="K73" t="n">
-        <v>0.6116201872270244</v>
+        <v>0.9036864431843483</v>
       </c>
       <c r="L73" t="n">
         <v>22</v>
@@ -8573,13 +8537,13 @@
         <v>68.18181818181819</v>
       </c>
       <c r="N73" t="n">
-        <v>16.55352964721532</v>
+        <v>16.33753430337937</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>9.331307651444497</v>
+        <v>9.01484760117015</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8642,27 +8606,31 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C74" t="n">
-        <v>5.038831350919892</v>
+        <v>5.10679004619678</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
+          <t>ÇELİŞKİLİ_BEKLE</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %82.35: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H74" t="n">
         <v>5</v>
       </c>
@@ -8673,22 +8641,22 @@
         <v>18.35970785011217</v>
       </c>
       <c r="K74" t="n">
-        <v>6.607053987526301</v>
+        <v>8.044862834806409</v>
       </c>
       <c r="L74" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M74" t="n">
-        <v>56</v>
+        <v>82.35294117647059</v>
       </c>
       <c r="N74" t="n">
-        <v>18.9315259078591</v>
+        <v>18.93961936180272</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>1.306617114320296</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
         <v>35</v>
@@ -8715,7 +8683,7 @@
         <v>95.98093909010421</v>
       </c>
       <c r="Y74" t="n">
-        <v>12.96568967219488</v>
+        <v>11.79185832871846</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
@@ -8757,10 +8725,10 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1323796416364278</v>
+        <v>0.1287179369235883</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8785,10 +8753,10 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>19.32150545065303</v>
+        <v>21.58944468202061</v>
       </c>
       <c r="K75" t="n">
-        <v>1.777061856765161</v>
+        <v>1.8242065699696</v>
       </c>
       <c r="L75" t="n">
         <v>15</v>
@@ -8797,13 +8765,13 @@
         <v>66.66666666666667</v>
       </c>
       <c r="N75" t="n">
-        <v>11.85404116615281</v>
+        <v>14.09467689902224</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>4.149204217722402</v>
+        <v>4.100983028196703</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8866,10 +8834,10 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C76" t="n">
-        <v>1.872226271673313</v>
+        <v>1.851106590160653</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8894,25 +8862,25 @@
         <v>10</v>
       </c>
       <c r="J76" t="n">
-        <v>20.51082830683794</v>
+        <v>18.36583782901725</v>
       </c>
       <c r="K76" t="n">
-        <v>8.023326471339143</v>
+        <v>6.804767429875791</v>
       </c>
       <c r="L76" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="M76" t="n">
-        <v>63.63636363636363</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N76" t="n">
-        <v>9.761903539512996</v>
+        <v>13.49039130179921</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>1.829858043841415</v>
+        <v>2.991657251837654</v>
       </c>
       <c r="Q76" t="n">
         <v>40</v>
@@ -8921,10 +8889,10 @@
         <v>62.5</v>
       </c>
       <c r="S76" t="n">
-        <v>31.61089190017208</v>
+        <v>31.96848527289704</v>
       </c>
       <c r="T76" t="n">
-        <v>30.88910809982792</v>
+        <v>30.53151472710296</v>
       </c>
       <c r="U76" t="n">
         <v>47.0324391373011</v>
@@ -8975,10 +8943,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5194324684473607</v>
+        <v>0.5358355813037518</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9003,19 +8971,19 @@
         <v>10</v>
       </c>
       <c r="J77" t="n">
-        <v>20.65935288471739</v>
+        <v>20.36657537342047</v>
       </c>
       <c r="K77" t="n">
-        <v>6.980252238865536</v>
+        <v>10.35857234296802</v>
       </c>
       <c r="L77" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M77" t="n">
-        <v>51.85185185185185</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N77" t="n">
-        <v>11.33815338459839</v>
+        <v>20.42536750761273</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -9045,25 +9013,25 @@
         <v>61.8421052631579</v>
       </c>
       <c r="X77" t="n">
-        <v>13.00517396479135</v>
+        <v>14.762554963676</v>
       </c>
       <c r="Y77" t="n">
-        <v>5.331545020941231</v>
+        <v>3.837473487847931</v>
       </c>
       <c r="Z77" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AA77" t="n">
-        <v>52.83018867924528</v>
+        <v>41.81818181818182</v>
       </c>
       <c r="AB77" t="n">
-        <v>10.77858371723429</v>
+        <v>12.4012367260855</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>4.931373370455294</v>
+        <v>6.408449045245613</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9094,10 +9062,10 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05442273802918411</v>
+        <v>0.05387705144745651</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9125,16 +9093,16 @@
         <v>12.76206508896208</v>
       </c>
       <c r="K78" t="n">
-        <v>7.416621439592475</v>
+        <v>6.339575133273478</v>
       </c>
       <c r="L78" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="M78" t="n">
-        <v>68.18181818181819</v>
+        <v>60.78431372549019</v>
       </c>
       <c r="N78" t="n">
-        <v>16.13062039734869</v>
+        <v>17.62088487466303</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
@@ -9167,22 +9135,22 @@
         <v>23.16536029857119</v>
       </c>
       <c r="Y78" t="n">
-        <v>6.291957704892326</v>
+        <v>7.231550660560626</v>
       </c>
       <c r="Z78" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA78" t="n">
         <v>50</v>
       </c>
       <c r="AB78" t="n">
-        <v>12.59914204489547</v>
+        <v>13.44443485632872</v>
       </c>
       <c r="AC78" t="n">
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>3.957016072782971</v>
+        <v>2.984257427123338</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9213,10 +9181,10 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8951384700150257</v>
+        <v>0.8725147411170144</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9241,25 +9209,25 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>12.46716859924595</v>
+        <v>11.83621857703275</v>
       </c>
       <c r="K79" t="n">
-        <v>3.657557371515363</v>
+        <v>1.037716358354746</v>
       </c>
       <c r="L79" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="M79" t="n">
-        <v>50</v>
+        <v>57.6271186440678</v>
       </c>
       <c r="N79" t="n">
-        <v>10.28630761445481</v>
+        <v>10.8917057232686</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>1.295074534385598</v>
+        <v>3.921588674462972</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9277,10 +9245,10 @@
         <v>41.04052722210609</v>
       </c>
       <c r="V79" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="W79" t="n">
-        <v>58.33333333333334</v>
+        <v>59.32203389830509</v>
       </c>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
@@ -9300,10 +9268,10 @@
         <v>55.26315789473684</v>
       </c>
       <c r="AG79" t="n">
-        <v>26.70060063534073</v>
+        <v>26.25773210036694</v>
       </c>
       <c r="AH79" t="n">
-        <v>28.56255725939611</v>
+        <v>29.00542579436991</v>
       </c>
       <c r="AI79" t="n">
         <v>39.70629712199248</v>
@@ -9322,10 +9290,10 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1281771073635865</v>
+        <v>0.1282986606664842</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9353,7 +9321,7 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>4.942413662465261</v>
+        <v>5.041932970219265</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -9364,7 +9332,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>4.819392046576954</v>
+        <v>4.720083579560952</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9388,25 +9356,25 @@
         <v>75.9493670886076</v>
       </c>
       <c r="X80" t="n">
-        <v>11.5318431483495</v>
+        <v>11.74527658842108</v>
       </c>
       <c r="Y80" t="n">
-        <v>5.908114938188158</v>
+        <v>5.99877133320944</v>
       </c>
       <c r="Z80" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AA80" t="n">
-        <v>37.5</v>
+        <v>31.42857142857143</v>
       </c>
       <c r="AB80" t="n">
-        <v>11.5451345579825</v>
+        <v>11.86932253340606</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>2.223236425157826</v>
+        <v>2.128938839602168</v>
       </c>
       <c r="AE80" t="n">
         <v>26</v>
@@ -9415,10 +9383,10 @@
         <v>50</v>
       </c>
       <c r="AG80" t="n">
-        <v>40.05441481986104</v>
+        <v>39.94875125265902</v>
       </c>
       <c r="AH80" t="n">
-        <v>9.945585180138956</v>
+        <v>10.05124874734098</v>
       </c>
       <c r="AI80" t="n">
         <v>32.06059352575905</v>
@@ -9437,10 +9405,10 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C81" t="n">
-        <v>1.076897845913704</v>
+        <v>1.07544465898408</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9468,22 +9436,22 @@
         <v>12.04277302023445</v>
       </c>
       <c r="K81" t="n">
-        <v>2.822343492868939</v>
+        <v>2.683593019735353</v>
       </c>
       <c r="L81" t="n">
         <v>47</v>
       </c>
       <c r="M81" t="n">
-        <v>44.68085106382978</v>
+        <v>46.80851063829788</v>
       </c>
       <c r="N81" t="n">
-        <v>13.24544604600182</v>
+        <v>13.53882956749119</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>6.980638899393354</v>
+        <v>7.125195725142253</v>
       </c>
       <c r="Q81" t="n">
         <v>31</v>
@@ -9510,7 +9478,7 @@
         <v>27.31228182970742</v>
       </c>
       <c r="Y81" t="n">
-        <v>9.56031794806308</v>
+        <v>9.682359016652697</v>
       </c>
       <c r="Z81" t="n">
         <v>9</v>
@@ -9519,13 +9487,13 @@
         <v>55.55555555555556</v>
       </c>
       <c r="AB81" t="n">
-        <v>9.438232199299446</v>
+        <v>9.276812191444455</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.4861605458590823</v>
+        <v>0.3516931796368139</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9556,10 +9524,10 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C82" t="n">
-        <v>5.284679185313101</v>
+        <v>5.445355834494841</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9616,10 +9584,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="X82" t="n">
-        <v>18.78688491181513</v>
+        <v>20.35550163226623</v>
       </c>
       <c r="Y82" t="n">
-        <v>2.140077821011677</v>
+        <v>0.478927203065127</v>
       </c>
       <c r="Z82" t="n">
         <v>9</v>
@@ -9628,13 +9596,13 @@
         <v>55.55555555555556</v>
       </c>
       <c r="AB82" t="n">
-        <v>13.13899195875419</v>
+        <v>13.66017785399789</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>1.900596421471168</v>
+        <v>3.538017324350351</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9665,10 +9633,10 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C83" t="n">
-        <v>5.883539450845599</v>
+        <v>5.780777175599431</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9693,40 +9661,40 @@
         <v>10</v>
       </c>
       <c r="J83" t="n">
-        <v>14.0949513048101</v>
+        <v>12.767909949277</v>
       </c>
       <c r="K83" t="n">
-        <v>8.706998822321822</v>
+        <v>6.80831544856475</v>
       </c>
       <c r="L83" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="M83" t="n">
-        <v>61.29032258064516</v>
+        <v>51.06382978723404</v>
       </c>
       <c r="N83" t="n">
-        <v>10.39405110257578</v>
+        <v>12.75679562492979</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>1.189436919136688</v>
+        <v>2.988236017047075</v>
       </c>
       <c r="Q83" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R83" t="n">
-        <v>63.63636363636363</v>
+        <v>65.11627906976744</v>
       </c>
       <c r="S83" t="n">
-        <v>54.37059527766615</v>
+        <v>56.26460231053829</v>
       </c>
       <c r="T83" t="n">
-        <v>9.265768358697485</v>
+        <v>8.851676759229157</v>
       </c>
       <c r="U83" t="n">
-        <v>48.86637687904344</v>
+        <v>50.17178199285205</v>
       </c>
       <c r="V83" t="n">
         <v>66</v>
@@ -9738,22 +9706,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>2.201583599281109</v>
+        <v>3.909736976814027</v>
       </c>
       <c r="Z83" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="AA83" t="n">
-        <v>54.3859649122807</v>
+        <v>46.93877551020408</v>
       </c>
       <c r="AB83" t="n">
-        <v>11.43680207503701</v>
+        <v>12.49448922988003</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>3.883924239790626</v>
+        <v>2.175312000844054</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9784,10 +9752,10 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C84" t="n">
-        <v>2.208428526007347</v>
+        <v>2.215877170732509</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9812,19 +9780,19 @@
         <v>10</v>
       </c>
       <c r="J84" t="n">
-        <v>14.10735630446007</v>
+        <v>13.05747170375323</v>
       </c>
       <c r="K84" t="n">
-        <v>5.723108481193306</v>
+        <v>6.079694109861999</v>
       </c>
       <c r="L84" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M84" t="n">
-        <v>61.53846153846154</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N84" t="n">
-        <v>10.95030722644272</v>
+        <v>9.985260231565674</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
@@ -9893,10 +9861,10 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C85" t="n">
-        <v>6.661007163993053</v>
+        <v>6.441137940899094</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9921,25 +9889,25 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>15.13449360257271</v>
+        <v>16.27610717942479</v>
       </c>
       <c r="K85" t="n">
-        <v>3.368113150028118</v>
+        <v>1.319043693322342</v>
       </c>
       <c r="L85" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M85" t="n">
-        <v>51.02040816326531</v>
+        <v>62</v>
       </c>
       <c r="N85" t="n">
-        <v>13.46665735539501</v>
+        <v>15.28721336308754</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>4.480962947683098</v>
+        <v>6.593978844589099</v>
       </c>
       <c r="Q85" t="n">
         <v>34</v>
@@ -9948,10 +9916,10 @@
         <v>61.76470588235294</v>
       </c>
       <c r="S85" t="n">
-        <v>66.25603474388642</v>
+        <v>66.70612387044612</v>
       </c>
       <c r="T85" t="n">
-        <v>-4.491328861533475</v>
+        <v>-4.941417988093178</v>
       </c>
       <c r="U85" t="n">
         <v>45.0410173444307</v>
@@ -9980,10 +9948,10 @@
         <v>41.93548387096774</v>
       </c>
       <c r="AG85" t="n">
-        <v>22.66019428957825</v>
+        <v>22.89308091846042</v>
       </c>
       <c r="AH85" t="n">
-        <v>19.2752895813895</v>
+        <v>19.04240295250732</v>
       </c>
       <c r="AI85" t="n">
         <v>26.41554306731223</v>
@@ -10002,10 +9970,10 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C86" t="n">
-        <v>3.960882808872841</v>
+        <v>4.347899006188871</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10062,25 +10030,21 @@
         <v>69.23076923076923</v>
       </c>
       <c r="X86" t="n">
-        <v>56.6501336995608</v>
+        <v>72.04624587018722</v>
       </c>
       <c r="Y86" t="n">
-        <v>0.9978959878527482</v>
+        <v>1.049624110674119</v>
       </c>
       <c r="Z86" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA86" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB86" t="n">
-        <v>8.88736983675275</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>5.052522935809034</v>
+        <v>5.002887401724266</v>
       </c>
       <c r="AE86" t="n">
         <v>51</v>
@@ -10111,10 +10075,10 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C87" t="n">
-        <v>5.489552434047903</v>
+        <v>5.440114876040081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10139,25 +10103,25 @@
         <v>10</v>
       </c>
       <c r="J87" t="n">
-        <v>26.73202875980171</v>
+        <v>25.69784138952578</v>
       </c>
       <c r="K87" t="n">
-        <v>1.070320130150204</v>
+        <v>0.9727626459143934</v>
       </c>
       <c r="L87" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M87" t="n">
-        <v>62.5</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N87" t="n">
-        <v>14.27632919573386</v>
+        <v>13.37583562188185</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>3.888065126131468</v>
+        <v>3.988439306358393</v>
       </c>
       <c r="Q87" t="n">
         <v>47</v>
@@ -10188,23 +10152,23 @@
       <c r="AA87" t="inlineStr"/>
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AD87" t="inlineStr"/>
       <c r="AE87" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="AF87" t="n">
-        <v>52.17391304347826</v>
+        <v>44.18604651162791</v>
       </c>
       <c r="AG87" t="n">
-        <v>48.0219981925345</v>
+        <v>41.42703049349428</v>
       </c>
       <c r="AH87" t="n">
-        <v>4.151914850943754</v>
+        <v>2.759016018133629</v>
       </c>
       <c r="AI87" t="n">
-        <v>38.13741307280403</v>
+        <v>30.43330983917051</v>
       </c>
       <c r="AJ87" t="n">
         <v>64</v>
@@ -10220,10 +10184,10 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C88" t="n">
-        <v>1.036763704954474</v>
+        <v>1.077541090373163</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10251,17 +10215,13 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>16.15029638456911</v>
+        <v>20.71865210490804</v>
       </c>
       <c r="L88" t="n">
-        <v>6</v>
-      </c>
-      <c r="M88" t="n">
-        <v>50</v>
-      </c>
-      <c r="N88" t="n">
-        <v>14.0838396102281</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="O88" t="n">
         <v>10</v>
       </c>
@@ -10290,25 +10250,25 @@
         <v>68.35443037974683</v>
       </c>
       <c r="X88" t="n">
-        <v>16.29154441961764</v>
+        <v>21.54066265509293</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.1214602796389741</v>
+        <v>0.6763255458937079</v>
       </c>
       <c r="Z88" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="AA88" t="n">
-        <v>33.33333333333334</v>
+        <v>48.83720930232558</v>
       </c>
       <c r="AB88" t="n">
-        <v>12.08910023020015</v>
+        <v>12.1566647073723</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>5.885688494064601</v>
+        <v>5.359924996095633</v>
       </c>
       <c r="AE88" t="n">
         <v>31</v>
@@ -10339,10 +10299,10 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C89" t="n">
-        <v>2.126479194574212</v>
+        <v>2.152985669275398</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10374,7 +10334,7 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>15.50685227540498</v>
+        <v>16.94664038406071</v>
       </c>
       <c r="L89" t="n">
         <v>4</v>
@@ -10383,7 +10343,7 @@
         <v>75</v>
       </c>
       <c r="N89" t="n">
-        <v>16.70454998265742</v>
+        <v>13.89075511307736</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
@@ -10416,22 +10376,22 @@
         <v>28.7873334490923</v>
       </c>
       <c r="Y89" t="n">
-        <v>7.264341965358034</v>
+        <v>6.108395845656956</v>
       </c>
       <c r="Z89" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA89" t="n">
-        <v>52.94117647058823</v>
+        <v>36.8421052631579</v>
       </c>
       <c r="AB89" t="n">
-        <v>13.77949730923438</v>
+        <v>13.70601402841478</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>2.949952685535528</v>
+        <v>4.144783965929322</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10462,24 +10422,24 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C90" t="n">
-        <v>2.901845835897742</v>
+        <v>2.890912555765805</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -10493,16 +10453,16 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>14.39148527825276</v>
+        <v>13.96049265356407</v>
       </c>
       <c r="L90" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M90" t="n">
-        <v>70</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N90" t="n">
-        <v>15.52634973642465</v>
+        <v>15.79134081414257</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
@@ -10535,16 +10495,16 @@
         <v>33.24184775233741</v>
       </c>
       <c r="Y90" t="n">
-        <v>4.582305468425874</v>
+        <v>4.941810570644578</v>
       </c>
       <c r="Z90" t="n">
         <v>18</v>
       </c>
       <c r="AA90" t="n">
-        <v>50</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="AB90" t="n">
-        <v>10.51857883774578</v>
+        <v>11.43145410878323</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
@@ -10553,25 +10513,25 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF90" t="n">
-        <v>59.09090909090909</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="AG90" t="n">
-        <v>41.29320159469655</v>
+        <v>42.47267337890883</v>
       </c>
       <c r="AH90" t="n">
-        <v>17.79770749621255</v>
+        <v>18.39689183848247</v>
       </c>
       <c r="AI90" t="n">
-        <v>38.73481847631513</v>
+        <v>40.78552239138171</v>
       </c>
       <c r="AJ90" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK90" t="n">
-        <v>41.46341463414634</v>
+        <v>42.16867469879518</v>
       </c>
     </row>
     <row r="91">
@@ -10581,10 +10541,10 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2374428461158135</v>
+        <v>0.2352142211098294</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10609,19 +10569,19 @@
         <v>10</v>
       </c>
       <c r="J91" t="n">
-        <v>14.34427620336855</v>
+        <v>14.07074278425192</v>
       </c>
       <c r="K91" t="n">
-        <v>4.724857255124704</v>
+        <v>3.741915720162448</v>
       </c>
       <c r="L91" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M91" t="n">
-        <v>59.61538461538461</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N91" t="n">
-        <v>15.26367243033973</v>
+        <v>14.96833074810355</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
@@ -10636,10 +10596,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="S91" t="n">
-        <v>32.9469787376493</v>
+        <v>33.28085897378712</v>
       </c>
       <c r="T91" t="n">
-        <v>28.75514892192517</v>
+        <v>28.42126868578735</v>
       </c>
       <c r="U91" t="n">
         <v>47.42656695641357</v>
@@ -10690,10 +10650,10 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C92" t="n">
-        <v>1.10316364703355</v>
+        <v>1.121565109318475</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10721,22 +10681,22 @@
         <v>22.28274626067631</v>
       </c>
       <c r="K92" t="n">
-        <v>4.698937957801697</v>
+        <v>6.445381981118636</v>
       </c>
       <c r="L92" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M92" t="n">
-        <v>65</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="N92" t="n">
-        <v>13.94637883112967</v>
+        <v>12.52921606166961</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>3.152908813199984</v>
+        <v>1.460484231394021</v>
       </c>
       <c r="Q92" t="n">
         <v>56</v>
@@ -10799,10 +10759,10 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04244553418941901</v>
+        <v>0.04234694389517791</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10827,10 +10787,10 @@
         <v>10</v>
       </c>
       <c r="J93" t="n">
-        <v>18.40038502869544</v>
+        <v>17.21421071359344</v>
       </c>
       <c r="K93" t="n">
-        <v>2.93929631175609</v>
+        <v>2.700194231733777</v>
       </c>
       <c r="L93" t="n">
         <v>47</v>
@@ -10839,13 +10799,13 @@
         <v>55.31914893617022</v>
       </c>
       <c r="N93" t="n">
-        <v>17.14938892187325</v>
+        <v>18.15875267269455</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>2.973309317147876</v>
+        <v>3.213047251712609</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10908,19 +10868,19 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C94" t="n">
-        <v>6.582209760633514</v>
+        <v>6.729390655910851</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -10935,27 +10895,17 @@
       <c r="I94" t="n">
         <v>10</v>
       </c>
-      <c r="J94" t="n">
-        <v>12.24049282186025</v>
-      </c>
-      <c r="K94" t="n">
-        <v>10.57182264174918</v>
-      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="n">
-        <v>18</v>
-      </c>
-      <c r="M94" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N94" t="n">
-        <v>13.06957274637224</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="O94" t="n">
         <v>8</v>
       </c>
-      <c r="P94" t="n">
-        <v>0</v>
-      </c>
+      <c r="P94" t="inlineStr"/>
       <c r="Q94" t="n">
         <v>40</v>
       </c>
@@ -10978,25 +10928,25 @@
         <v>70.90909090909091</v>
       </c>
       <c r="X94" t="n">
-        <v>46.65531127586331</v>
+        <v>49.30897816906403</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.962713371714165</v>
+        <v>3.31325301204819</v>
       </c>
       <c r="Z94" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA94" t="n">
-        <v>42.85714285714285</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB94" t="n">
-        <v>11.014852533138</v>
+        <v>10.23034872298341</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>3.130020153923474</v>
+        <v>2.778816199376954</v>
       </c>
       <c r="AE94" t="n">
         <v>37</v>
@@ -11005,10 +10955,10 @@
         <v>54.05405405405406</v>
       </c>
       <c r="AG94" t="n">
-        <v>21.23700842847849</v>
+        <v>21.23956780603786</v>
       </c>
       <c r="AH94" t="n">
-        <v>32.81704562557557</v>
+        <v>32.81448624801619</v>
       </c>
       <c r="AI94" t="n">
         <v>38.38404689217949</v>
@@ -11027,10 +10977,10 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1407846900099751</v>
+        <v>0.1383613011092603</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11055,25 +11005,25 @@
         <v>10</v>
       </c>
       <c r="J95" t="n">
-        <v>23.400044414021</v>
+        <v>23.90003550114733</v>
       </c>
       <c r="K95" t="n">
-        <v>1.54891232094414</v>
+        <v>0.4566168831620976</v>
       </c>
       <c r="L95" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M95" t="n">
-        <v>65.38461538461539</v>
+        <v>60</v>
       </c>
       <c r="N95" t="n">
-        <v>19.60590204166581</v>
+        <v>18.64216108458992</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>4.383195818964802</v>
+        <v>5.518186147245263</v>
       </c>
       <c r="Q95" t="n">
         <v>23</v>
@@ -11136,10 +11086,10 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1315391368410983</v>
+        <v>0.1301854088547726</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11167,22 +11117,22 @@
         <v>12.85874206974231</v>
       </c>
       <c r="K96" t="n">
-        <v>1.741134257735344</v>
+        <v>0.6940708200939838</v>
       </c>
       <c r="L96" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="M96" t="n">
-        <v>60.27397260273973</v>
+        <v>56.71641791044776</v>
       </c>
       <c r="N96" t="n">
-        <v>12.82733746537946</v>
+        <v>13.21518502957764</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>8.11752866971478</v>
+        <v>9.241784649398621</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11200,25 +11150,25 @@
         <v>48.36276351921527</v>
       </c>
       <c r="V96" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="W96" t="n">
-        <v>69.01408450704226</v>
+        <v>68.57142857142857</v>
       </c>
       <c r="X96" t="n">
         <v>16.74415231729489</v>
       </c>
       <c r="Y96" t="n">
-        <v>11.34149577529709</v>
+        <v>12.25392002618556</v>
       </c>
       <c r="Z96" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA96" t="n">
-        <v>40</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB96" t="n">
-        <v>16.42948776937994</v>
+        <v>15.96559934023883</v>
       </c>
       <c r="AC96" t="n">
         <v>8</v>
@@ -11255,10 +11205,10 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C97" t="n">
-        <v>1.845960470553466</v>
+        <v>1.829094500710971</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11283,25 +11233,25 @@
         <v>10</v>
       </c>
       <c r="J97" t="n">
-        <v>20.83793142975532</v>
+        <v>19.26562870655475</v>
       </c>
       <c r="K97" t="n">
-        <v>3.281160303047193</v>
+        <v>2.337512287417276</v>
       </c>
       <c r="L97" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M97" t="n">
-        <v>50</v>
+        <v>54.83870967741935</v>
       </c>
       <c r="N97" t="n">
-        <v>14.06887767617043</v>
+        <v>13.11922177865826</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>0.696002731614942</v>
+        <v>1.624514486841933</v>
       </c>
       <c r="Q97" t="n">
         <v>50</v>
@@ -11310,10 +11260,10 @@
         <v>56</v>
       </c>
       <c r="S97" t="n">
-        <v>35.02295617725568</v>
+        <v>35.11462284392235</v>
       </c>
       <c r="T97" t="n">
-        <v>20.97704382274432</v>
+        <v>20.88537715607765</v>
       </c>
       <c r="U97" t="n">
         <v>42.30602802165686</v>
@@ -11342,10 +11292,10 @@
         <v>55</v>
       </c>
       <c r="AG97" t="n">
-        <v>58.59541082931041</v>
+        <v>58.32067290383721</v>
       </c>
       <c r="AH97" t="n">
-        <v>-3.59541082931041</v>
+        <v>-3.320672903837206</v>
       </c>
       <c r="AI97" t="n">
         <v>39.82909179893205</v>
@@ -11364,10 +11314,10 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6589564313124181</v>
+        <v>0.6473631707222397</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11384,11 +11334,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>5</v>
       </c>
@@ -11396,25 +11342,25 @@
         <v>10</v>
       </c>
       <c r="J98" t="n">
-        <v>18.49937747698907</v>
+        <v>17.47600423199651</v>
       </c>
       <c r="K98" t="n">
-        <v>9.75228792038434</v>
+        <v>7.821375930201402</v>
       </c>
       <c r="L98" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M98" t="n">
-        <v>81.25</v>
+        <v>65</v>
       </c>
       <c r="N98" t="n">
-        <v>13.04478611817466</v>
+        <v>15.90711376272659</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>0.2257010621913969</v>
+        <v>2.020586410628766</v>
       </c>
       <c r="Q98" t="n">
         <v>48</v>
@@ -11423,10 +11369,10 @@
         <v>68.75</v>
       </c>
       <c r="S98" t="n">
-        <v>39.30577672753313</v>
+        <v>39.82837795433201</v>
       </c>
       <c r="T98" t="n">
-        <v>29.44422327246687</v>
+        <v>28.92162204566799</v>
       </c>
       <c r="U98" t="n">
         <v>54.66692858410841</v>
@@ -11438,25 +11384,25 @@
         <v>73.52941176470588</v>
       </c>
       <c r="X98" t="n">
-        <v>10.71387422840049</v>
+        <v>11.17514685780745</v>
       </c>
       <c r="Y98" t="n">
-        <v>0.8685327965602729</v>
+        <v>3.016655270890256</v>
       </c>
       <c r="Z98" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="AA98" t="n">
-        <v>40.38461538461539</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="AB98" t="n">
-        <v>12.23255013477923</v>
+        <v>11.72835158567628</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>7.193949009959044</v>
+        <v>5.138351067421976</v>
       </c>
       <c r="AE98" t="n">
         <v>50</v>
@@ -11487,10 +11433,10 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4824502156377095</v>
+        <v>0.472105547248075</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11518,22 +11464,22 @@
         <v>28.77817890954801</v>
       </c>
       <c r="K99" t="n">
-        <v>3.791036011328908</v>
+        <v>1.565554884878173</v>
       </c>
       <c r="L99" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M99" t="n">
-        <v>66.66666666666667</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N99" t="n">
-        <v>12.82986200275538</v>
+        <v>14.51941654239078</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>0.2013314412318667</v>
+        <v>2.396920016713544</v>
       </c>
       <c r="Q99" t="n">
         <v>35</v>
@@ -11574,10 +11520,10 @@
         <v>51.28205128205128</v>
       </c>
       <c r="AG99" t="n">
-        <v>37.49037809779497</v>
+        <v>36.8637115774028</v>
       </c>
       <c r="AH99" t="n">
-        <v>13.79167318425631</v>
+        <v>14.41833970464849</v>
       </c>
       <c r="AI99" t="n">
         <v>36.19936288445796</v>
@@ -11596,10 +11542,10 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C100" t="n">
-        <v>327.9818999099119</v>
+        <v>326.5064707730453</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11627,16 +11573,16 @@
         <v>25.15478290083538</v>
       </c>
       <c r="K100" t="n">
-        <v>7.013768019376121</v>
+        <v>6.532365748625679</v>
       </c>
       <c r="L100" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M100" t="n">
-        <v>61.53846153846154</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N100" t="n">
-        <v>11.90267572555307</v>
+        <v>11.56873670362326</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11705,10 +11651,10 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C101" t="n">
-        <v>328.1651243928274</v>
+        <v>327.4418794948024</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11736,16 +11682,16 @@
         <v>13.42090796247281</v>
       </c>
       <c r="K101" t="n">
-        <v>3.919736159926801</v>
+        <v>3.690706889614059</v>
       </c>
       <c r="L101" t="n">
         <v>34</v>
       </c>
       <c r="M101" t="n">
-        <v>32.35294117647059</v>
+        <v>38.23529411764706</v>
       </c>
       <c r="N101" t="n">
-        <v>7.906266739941217</v>
+        <v>8.144715481479819</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11814,10 +11760,10 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C102" t="n">
-        <v>399.7450960079855</v>
+        <v>398.8581069658313</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11913,10 +11859,10 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7207335667589788</v>
+        <v>0.7190594840604526</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11941,19 +11887,19 @@
         <v>10</v>
       </c>
       <c r="J103" t="n">
-        <v>30.74202968074841</v>
+        <v>26.3831854858525</v>
       </c>
       <c r="K103" t="n">
-        <v>10.84762792559328</v>
+        <v>10.59015678141253</v>
       </c>
       <c r="L103" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="M103" t="n">
-        <v>33.33333333333334</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N103" t="n">
-        <v>15.31498501728872</v>
+        <v>11.83420089682727</v>
       </c>
       <c r="O103" t="n">
         <v>10</v>
@@ -11986,22 +11932,22 @@
         <v>14.26498323563516</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.99072840451452</v>
+        <v>3.216056529448297</v>
       </c>
       <c r="Z103" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA103" t="n">
-        <v>40</v>
+        <v>40.81632653061224</v>
       </c>
       <c r="AB103" t="n">
-        <v>11.58097532289587</v>
+        <v>11.25377200429218</v>
       </c>
       <c r="AC103" t="n">
         <v>10</v>
       </c>
       <c r="AD103" t="n">
-        <v>7.225362566078342</v>
+        <v>7.009368731308041</v>
       </c>
       <c r="AE103" t="n">
         <v>41</v>
@@ -12010,10 +11956,10 @@
         <v>60.97560975609756</v>
       </c>
       <c r="AG103" t="n">
-        <v>37.05048140167025</v>
+        <v>36.58483847917071</v>
       </c>
       <c r="AH103" t="n">
-        <v>23.92512835442732</v>
+        <v>24.39077127692686</v>
       </c>
       <c r="AI103" t="n">
         <v>45.72685693412379</v>
@@ -12032,10 +11978,10 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04895945160638247</v>
+        <v>0.04821681673559323</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12054,7 +12000,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.19: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %78.95: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -12064,25 +12010,25 @@
         <v>10</v>
       </c>
       <c r="J104" t="n">
-        <v>27.75739442390626</v>
+        <v>28.27204186542799</v>
       </c>
       <c r="K104" t="n">
-        <v>1.257086756753312</v>
+        <v>0.4366807936538208</v>
       </c>
       <c r="L104" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M104" t="n">
-        <v>76.19047619047619</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="N104" t="n">
-        <v>15.58903477762779</v>
+        <v>14.07646711978468</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>2.708860516435663</v>
+        <v>3.547826529300568</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>
@@ -12123,10 +12069,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="AG104" t="n">
-        <v>34.98188601905284</v>
+        <v>35.28413789334237</v>
       </c>
       <c r="AH104" t="n">
-        <v>26.72024164052162</v>
+        <v>26.4179897662321</v>
       </c>
       <c r="AI104" t="n">
         <v>47.42656695641357</v>

--- a/TDA_Result.xlsx
+++ b/TDA_Result.xlsx
@@ -679,7 +679,7 @@
         <v>46241</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4536573510560203</v>
+        <v>0.4499118467722017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -739,22 +739,22 @@
         <v>14.94856954517825</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.752739221962599</v>
+        <v>5.539123532578738</v>
       </c>
       <c r="Z2" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AA2" t="n">
-        <v>42.85714285714285</v>
+        <v>51.61290322580645</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.76204541000136</v>
+        <v>11.90435794292219</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.409295712560967</v>
+        <v>2.605180641394955</v>
       </c>
       <c r="AE2" t="n">
         <v>43</v>
@@ -788,7 +788,7 @@
         <v>46241</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7274450494530948</v>
+        <v>0.7304254185005438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,22 +848,22 @@
         <v>12.13279917920569</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.386820575432071</v>
+        <v>3.995089872612112</v>
       </c>
       <c r="Z3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AA3" t="n">
-        <v>43.47826086956522</v>
+        <v>42</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.51048519875236</v>
+        <v>11.44884507590466</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.87071725712911</v>
+        <v>6.254794801036779</v>
       </c>
       <c r="AE3" t="n">
         <v>38</v>
@@ -897,7 +897,7 @@
         <v>46241</v>
       </c>
       <c r="C4" t="n">
-        <v>1.416107038415637</v>
+        <v>1.40047129660055</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         <v>23.54405567752772</v>
       </c>
       <c r="K4" t="n">
-        <v>9.644773493073355</v>
+        <v>8.434146525475272</v>
       </c>
       <c r="L4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M4" t="n">
-        <v>53.33333333333334</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N4" t="n">
-        <v>13.32021955243562</v>
+        <v>10.11394003839786</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -967,22 +967,22 @@
         <v>12.1087988317258</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.19788755595437</v>
+        <v>3.277755488011369</v>
       </c>
       <c r="Z4" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="AA4" t="n">
-        <v>32.75862068965517</v>
+        <v>25.92592592592593</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.61845741265214</v>
+        <v>12.66076555103657</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>7.977447775997026</v>
+        <v>6.95005016261323</v>
       </c>
       <c r="AE4" t="n">
         <v>45</v>
@@ -1016,7 +1016,7 @@
         <v>46241</v>
       </c>
       <c r="C5" t="n">
-        <v>0.264144314086122</v>
+        <v>0.2608063105696654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,22 +1076,22 @@
         <v>16.70172291026088</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.452843489925852</v>
+        <v>6.647640137332411</v>
       </c>
       <c r="Z5" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="AA5" t="n">
-        <v>33.33333333333334</v>
+        <v>48</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.06253747739354</v>
+        <v>16.59827446987049</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.809405885823381</v>
+        <v>3.591082076124597</v>
       </c>
       <c r="AE5" t="n">
         <v>44</v>
@@ -1125,16 +1125,16 @@
         <v>46241</v>
       </c>
       <c r="C6" t="n">
-        <v>1.971648634620116</v>
+        <v>1.925647912826546</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1142,7 +1142,11 @@
           <t>SATMA_BEKLE</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
@@ -1153,22 +1157,22 @@
         <v>23.73506360720576</v>
       </c>
       <c r="K6" t="n">
-        <v>3.845476492857181</v>
+        <v>1.422647805336519</v>
       </c>
       <c r="L6" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="M6" t="n">
-        <v>73.68421052631579</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N6" t="n">
-        <v>13.53822118044896</v>
+        <v>14.69846461632307</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.5692537191215985</v>
       </c>
       <c r="Q6" t="n">
         <v>41</v>
@@ -1195,7 +1199,7 @@
         <v>44.49622708587002</v>
       </c>
       <c r="Y6" t="n">
-        <v>20.80231340592837</v>
+        <v>22.65008216337239</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1240,7 +1244,7 @@
         <v>46241</v>
       </c>
       <c r="C7" t="n">
-        <v>2.092190679079578</v>
+        <v>2.113285995857045</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,25 +1269,25 @@
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>11.72442900972028</v>
+        <v>11.71893639989927</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6555738880178685</v>
+        <v>1.664146741844252</v>
       </c>
       <c r="L7" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="M7" t="n">
-        <v>61.76470588235294</v>
+        <v>58.9041095890411</v>
       </c>
       <c r="N7" t="n">
-        <v>13.3664732084733</v>
+        <v>13.56877259738972</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.329156768397511</v>
+        <v>1.313986593078753</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1310,16 +1314,16 @@
         <v>13.79329344082609</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.14571741680933</v>
+        <v>10.24980995633276</v>
       </c>
       <c r="Z7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="n">
-        <v>52.94117647058823</v>
+        <v>62.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.16676137028197</v>
+        <v>7.504924063550045</v>
       </c>
       <c r="AC7" t="n">
         <v>10</v>
@@ -1359,7 +1363,7 @@
         <v>46241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3303900258097036</v>
+        <v>0.3322974486495597</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1391,7 @@
         <v>22.10694516187944</v>
       </c>
       <c r="K8" t="n">
-        <v>5.046781860037752</v>
+        <v>5.653242755708465</v>
       </c>
       <c r="L8" t="n">
         <v>4</v>
@@ -1402,7 +1406,7 @@
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.811336137738207</v>
+        <v>2.221188089529558</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1468,7 +1472,7 @@
         <v>46241</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5869873469330338</v>
+        <v>0.5912169135521274</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,7 +1571,7 @@
         <v>46241</v>
       </c>
       <c r="C10" t="n">
-        <v>2.037684583270695</v>
+        <v>2.033618406702353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,22 +1599,22 @@
         <v>10.23694539327734</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8953144727292139</v>
+        <v>0.6939790124068868</v>
       </c>
       <c r="L10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M10" t="n">
-        <v>40.47619047619047</v>
+        <v>43.90243902439025</v>
       </c>
       <c r="N10" t="n">
-        <v>9.764403333337537</v>
+        <v>9.525580081718513</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>9.023893304511855</v>
+        <v>9.24188425054342</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1676,7 +1680,7 @@
         <v>46241</v>
       </c>
       <c r="C11" t="n">
-        <v>7.468365798031903</v>
+        <v>7.348280943805926</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1697,11 @@
           <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>5</v>
       </c>
@@ -1704,16 +1712,16 @@
         <v>20.56423081971027</v>
       </c>
       <c r="K11" t="n">
-        <v>7.008905363531182</v>
+        <v>5.288294837886132</v>
       </c>
       <c r="L11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M11" t="n">
-        <v>66.66666666666667</v>
+        <v>81.25</v>
       </c>
       <c r="N11" t="n">
-        <v>14.25086188382207</v>
+        <v>14.41611962980027</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1743,19 +1751,19 @@
         <v>61.76470588235294</v>
       </c>
       <c r="X11" t="n">
-        <v>10.68850982866312</v>
+        <v>10.6953969978917</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.324287652645852</v>
+        <v>4.884667571234724</v>
       </c>
       <c r="Z11" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="AA11" t="n">
-        <v>50</v>
+        <v>54.28571428571428</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.14381797994836</v>
+        <v>10.66948699666083</v>
       </c>
       <c r="AC11" t="n">
         <v>3</v>
@@ -1795,7 +1803,7 @@
         <v>46241</v>
       </c>
       <c r="C12" t="n">
-        <v>6.682222029818019</v>
+        <v>6.48346899250209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1812,11 +1820,7 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>5</v>
       </c>
@@ -1827,16 +1831,16 @@
         <v>20.08266526523165</v>
       </c>
       <c r="K12" t="n">
-        <v>16.33552172743171</v>
+        <v>12.87528975850236</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>75</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N12" t="n">
-        <v>27.22793810052844</v>
+        <v>22.33927009741701</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -1866,19 +1870,19 @@
         <v>70.58823529411765</v>
       </c>
       <c r="X12" t="n">
-        <v>18.79909748165969</v>
+        <v>18.80648930118842</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.073732718894006</v>
+        <v>4.992319508448539</v>
       </c>
       <c r="Z12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AA12" t="n">
-        <v>52.63157894736842</v>
+        <v>50</v>
       </c>
       <c r="AB12" t="n">
-        <v>11.47145741891312</v>
+        <v>12.0508960571445</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
@@ -1918,7 +1922,7 @@
         <v>46241</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2848985047452868</v>
+        <v>0.2779977375320148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,10 +1947,10 @@
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>38.41151038872205</v>
+        <v>39.9577447695258</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5921533577945892</v>
+        <v>0.6833724332065527</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
@@ -1957,7 +1961,7 @@
         <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>4.381899079669971</v>
+        <v>4.287329141320839</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -2011,7 +2015,7 @@
         <v>46241</v>
       </c>
       <c r="C14" t="n">
-        <v>8.060594103419696</v>
+        <v>8.061095643062421</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2071,7 +2075,7 @@
         <v>14.33662537827827</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.845398704731442</v>
+        <v>6.839602515908084</v>
       </c>
       <c r="Z14" t="n">
         <v>26</v>
@@ -2120,7 +2124,7 @@
         <v>46241</v>
       </c>
       <c r="C15" t="n">
-        <v>12.23239703340804</v>
+        <v>11.90819850522615</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2137,7 +2141,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %82.61: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>5</v>
       </c>
@@ -2148,16 +2156,16 @@
         <v>14.74031958141837</v>
       </c>
       <c r="K15" t="n">
-        <v>15.17462523694844</v>
+        <v>12.12212098257035</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="M15" t="n">
-        <v>50</v>
+        <v>82.60869565217391</v>
       </c>
       <c r="N15" t="n">
-        <v>21.98911348984758</v>
+        <v>17.42902534732851</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
@@ -2190,22 +2198,22 @@
         <v>17.12346148492163</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.663916198569737</v>
+        <v>4.270144033435297</v>
       </c>
       <c r="Z15" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="AA15" t="n">
-        <v>31.48148148148148</v>
+        <v>35.55555555555556</v>
       </c>
       <c r="AB15" t="n">
-        <v>11.506728548456</v>
+        <v>15.29745172712114</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>8.477136244578631</v>
+        <v>5.985443003869085</v>
       </c>
       <c r="AE15" t="n">
         <v>31</v>
@@ -2239,7 +2247,7 @@
         <v>46241</v>
       </c>
       <c r="C16" t="n">
-        <v>37.21080502879053</v>
+        <v>36.77285242634976</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,22 +2275,22 @@
         <v>17.40096492560246</v>
       </c>
       <c r="K16" t="n">
-        <v>7.25517801107296</v>
+        <v>5.992838099349651</v>
       </c>
       <c r="L16" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="M16" t="n">
-        <v>71.42857142857143</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="N16" t="n">
-        <v>15.06614223841034</v>
+        <v>16.72563066637132</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>2.559151026390238</v>
+        <v>3.780596852114049</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2348,7 +2356,7 @@
         <v>46241</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7534401587357346</v>
+        <v>0.7560029126983925</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2367,7 +2375,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.27: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %79.07: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2380,22 +2388,22 @@
         <v>14.16674936134154</v>
       </c>
       <c r="K17" t="n">
-        <v>7.006994267953193</v>
+        <v>7.370968228476449</v>
       </c>
       <c r="L17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M17" t="n">
-        <v>77.27272727272727</v>
+        <v>79.06976744186046</v>
       </c>
       <c r="N17" t="n">
-        <v>16.09615650604118</v>
+        <v>15.65469996868638</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9279820808350658</v>
+        <v>0.5858490259536664</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2422,7 +2430,7 @@
         <v>15.7396793517258</v>
       </c>
       <c r="Y17" t="n">
-        <v>7.545109104056269</v>
+        <v>7.230632718289587</v>
       </c>
       <c r="Z17" t="n">
         <v>31</v>
@@ -2431,13 +2439,13 @@
         <v>51.61290322580645</v>
       </c>
       <c r="AB17" t="n">
-        <v>11.26949414919576</v>
+        <v>11.4183129698492</v>
       </c>
       <c r="AC17" t="n">
         <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.655230969561861</v>
+        <v>2.98521738679185</v>
       </c>
       <c r="AE17" t="n">
         <v>35</v>
@@ -2471,7 +2479,7 @@
         <v>46241</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1056577216093927</v>
+        <v>0.1035677840322343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2499,22 +2507,22 @@
         <v>24.37863714425642</v>
       </c>
       <c r="K18" t="n">
-        <v>5.733571797406145</v>
+        <v>3.642133883540222</v>
       </c>
       <c r="L18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M18" t="n">
-        <v>60</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N18" t="n">
-        <v>16.45192868322132</v>
+        <v>16.9566017494627</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>4.035074319411702</v>
+        <v>6.134441542475333</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2580,7 +2588,7 @@
         <v>46241</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02494696350248397</v>
+        <v>0.0251581669043685</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2608,22 +2616,22 @@
         <v>18.34152851742537</v>
       </c>
       <c r="K19" t="n">
-        <v>1.002984204060309</v>
+        <v>1.85808522115456</v>
       </c>
       <c r="L19" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M19" t="n">
-        <v>57.57575757575758</v>
+        <v>60</v>
       </c>
       <c r="N19" t="n">
-        <v>18.29602034729423</v>
+        <v>23.05253883909682</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>8.907673240389279</v>
+        <v>7.99339076634682</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2689,7 +2697,7 @@
         <v>46241</v>
       </c>
       <c r="C20" t="n">
-        <v>1.867877561201524</v>
+        <v>1.855414731888229</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2749,16 +2757,16 @@
         <v>16.65604614151002</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.711737214695233</v>
+        <v>6.340846182942816</v>
       </c>
       <c r="Z20" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA20" t="n">
-        <v>54.54545454545455</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="AB20" t="n">
-        <v>13.1471808178665</v>
+        <v>11.37893977148107</v>
       </c>
       <c r="AC20" t="n">
         <v>4</v>
@@ -2798,7 +2806,7 @@
         <v>46241</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9471460184428765</v>
+        <v>0.9363030694668487</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,22 +2834,22 @@
         <v>13.9566823466854</v>
       </c>
       <c r="K21" t="n">
-        <v>1.473038032329521</v>
+        <v>0.3113724048522171</v>
       </c>
       <c r="L21" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M21" t="n">
-        <v>54.23728813559322</v>
+        <v>59.64912280701754</v>
       </c>
       <c r="N21" t="n">
-        <v>17.64651861840198</v>
+        <v>17.7688681608701</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>6.432213023513667</v>
+        <v>7.664761642495366</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2907,7 +2915,7 @@
         <v>46241</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3331153265122002</v>
+        <v>0.3339746582390741</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,7 +2934,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2939,16 +2947,16 @@
         <v>20.35908649698318</v>
       </c>
       <c r="K22" t="n">
-        <v>12.30105359566762</v>
+        <v>12.59075464102795</v>
       </c>
       <c r="L22" t="n">
         <v>5</v>
       </c>
       <c r="M22" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>17.21117446734009</v>
+        <v>23.34097628590485</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
@@ -2978,16 +2986,16 @@
         <v>73.68421052631579</v>
       </c>
       <c r="X22" t="n">
-        <v>19.29777531785657</v>
+        <v>19.30519816570662</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.864922211287604</v>
+        <v>5.627955552575992</v>
       </c>
       <c r="Z22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA22" t="n">
-        <v>57.14285714285715</v>
+        <v>50</v>
       </c>
       <c r="AB22" t="n">
         <v>12.75464260894753</v>
@@ -2996,7 +3004,7 @@
         <v>6</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.1434935752808175</v>
+        <v>0.3942316282352976</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3022,7 +3030,7 @@
         <v>46241</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8993485029113496</v>
+        <v>0.895211417646809</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,11 +3047,7 @@
           <t>SATMA_BEKLE</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>5</v>
       </c>
@@ -3051,10 +3055,10 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>13.07033123031079</v>
+        <v>13.06492236410843</v>
       </c>
       <c r="K23" t="n">
-        <v>1.851858071735224</v>
+        <v>1.377022423395391</v>
       </c>
       <c r="L23" t="n">
         <v>37</v>
@@ -3063,13 +3067,13 @@
         <v>62.16216216216216</v>
       </c>
       <c r="N23" t="n">
-        <v>17.46543687934854</v>
+        <v>17.13245148878242</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>3.090902795359418</v>
+        <v>3.57376601718824</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3096,16 +3100,16 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>11.4605171424666</v>
+        <v>11.86780685126601</v>
       </c>
       <c r="Z23" t="n">
         <v>4</v>
       </c>
       <c r="AA23" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AB23" t="n">
-        <v>12.55681756557071</v>
+        <v>12.69643539804235</v>
       </c>
       <c r="AC23" t="n">
         <v>6</v>
@@ -3145,7 +3149,7 @@
         <v>46241</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1807082452140766</v>
+        <v>0.1903634533007</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3163,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -3173,22 +3177,22 @@
         <v>22.86774633531589</v>
       </c>
       <c r="K24" t="n">
-        <v>3.242837055117409</v>
+        <v>8.759082725256118</v>
       </c>
       <c r="L24" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M24" t="n">
-        <v>53.84615384615385</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N24" t="n">
-        <v>11.15287235946911</v>
+        <v>12.34101096402614</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>6.544921795664349</v>
+        <v>1.140978062382758</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3211,17 +3215,27 @@
       <c r="W24" t="n">
         <v>75</v>
       </c>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
+      <c r="X24" t="n">
+        <v>12.5919983806515</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>3.404252265278274</v>
+      </c>
       <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>51.61290322580645</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>14.81671937360062</v>
+      </c>
       <c r="AC24" t="n">
         <v>2</v>
       </c>
-      <c r="AD24" t="inlineStr"/>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
       <c r="AE24" t="n">
         <v>3</v>
       </c>
@@ -3254,7 +3268,7 @@
         <v>46241</v>
       </c>
       <c r="C25" t="n">
-        <v>4.025056093255089</v>
+        <v>4.044175033482595</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3353,7 +3367,7 @@
         <v>46241</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4293393069705126</v>
+        <v>0.4293660209670075</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3452,7 +3466,7 @@
         <v>46241</v>
       </c>
       <c r="C27" t="n">
-        <v>36.47707084512424</v>
+        <v>36.77285242634976</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,7 +3494,7 @@
         <v>61.00029220182797</v>
       </c>
       <c r="K27" t="n">
-        <v>10.65998537846296</v>
+        <v>11.55729387103921</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3505,25 +3519,25 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>14.98462848520752</v>
+        <v>14.99178296399024</v>
       </c>
       <c r="Y27" t="n">
-        <v>3.761061946902666</v>
+        <v>2.986725663716816</v>
       </c>
       <c r="Z27" t="n">
         <v>8</v>
       </c>
       <c r="AA27" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>19.9709957394613</v>
+        <v>24.39428197679019</v>
       </c>
       <c r="AC27" t="n">
         <v>5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.287356321839073</v>
+        <v>2.075256556442417</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3547,7 +3561,7 @@
         <v>46241</v>
       </c>
       <c r="C28" t="n">
-        <v>1.452793747598952</v>
+        <v>1.439256770428378</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3575,16 +3589,16 @@
         <v>18.25342733104113</v>
       </c>
       <c r="K28" t="n">
-        <v>4.191785591792918</v>
+        <v>3.220937647789546</v>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M28" t="n">
-        <v>41.66666666666666</v>
+        <v>47.5</v>
       </c>
       <c r="N28" t="n">
-        <v>16.72635294557637</v>
+        <v>17.42087226656076</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
@@ -3656,7 +3670,7 @@
         <v>46241</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4138260747661071</v>
+        <v>0.4140614797151698</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3684,7 +3698,7 @@
         <v>20.65475273479386</v>
       </c>
       <c r="K29" t="n">
-        <v>13.85170673591398</v>
+        <v>13.91647127555789</v>
       </c>
       <c r="L29" t="n">
         <v>3</v>
@@ -3726,7 +3740,7 @@
         <v>55.05052857749912</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.664081774731702</v>
+        <v>9.612694190611059</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
@@ -3737,7 +3751,7 @@
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.3718545533910711</v>
+        <v>0.4284958002904737</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3771,7 +3785,7 @@
         <v>46241</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3758815468741205</v>
+        <v>0.371502234675969</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3799,22 +3813,22 @@
         <v>21.6314445059014</v>
       </c>
       <c r="K30" t="n">
-        <v>1.679386365764679</v>
+        <v>0.4947424780420651</v>
       </c>
       <c r="L30" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M30" t="n">
-        <v>52.94117647058823</v>
+        <v>50</v>
       </c>
       <c r="N30" t="n">
-        <v>13.61680851217371</v>
+        <v>14.79227902534712</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>3.265768758959942</v>
+        <v>4.483077831601312</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3880,7 +3894,7 @@
         <v>46241</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1758865728694233</v>
+        <v>0.1756878605346777</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3908,7 +3922,7 @@
         <v>31.09418993049242</v>
       </c>
       <c r="K31" t="n">
-        <v>1.008623567153566</v>
+        <v>0.8945065024395848</v>
       </c>
       <c r="L31" t="n">
         <v>3</v>
@@ -3923,7 +3937,7 @@
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>8.901592869314467</v>
+        <v>9.024766375501581</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3989,7 +4003,7 @@
         <v>46241</v>
       </c>
       <c r="C32" t="n">
-        <v>2.354238601817539</v>
+        <v>2.362771012709475</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4049,22 +4063,22 @@
         <v>15.25475988862757</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.077505942222258</v>
+        <v>2.726232055482969</v>
       </c>
       <c r="Z32" t="n">
         <v>42</v>
       </c>
       <c r="AA32" t="n">
-        <v>30.95238095238095</v>
+        <v>38.09523809523809</v>
       </c>
       <c r="AB32" t="n">
-        <v>12.43016672738332</v>
+        <v>12.34316210709314</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>5.078794252697749</v>
+        <v>5.421572594499557</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4098,7 +4112,7 @@
         <v>46241</v>
       </c>
       <c r="C33" t="n">
-        <v>1.826998149403733</v>
+        <v>1.806146689163339</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4126,22 +4140,22 @@
         <v>12.57251846431013</v>
       </c>
       <c r="K33" t="n">
-        <v>2.401144396243682</v>
+        <v>1.232444038421199</v>
       </c>
       <c r="L33" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M33" t="n">
-        <v>61.11111111111111</v>
+        <v>61.81818181818182</v>
       </c>
       <c r="N33" t="n">
-        <v>11.46424234246147</v>
+        <v>12.12906634908658</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>1.561364976127133</v>
+        <v>2.733862634521023</v>
       </c>
       <c r="Q33" t="n">
         <v>39</v>
@@ -4207,7 +4221,7 @@
         <v>46241</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8175895189424399</v>
+        <v>0.804642027064</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4232,25 +4246,25 @@
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>14.80663485356992</v>
+        <v>15.89868933724038</v>
       </c>
       <c r="K34" t="n">
-        <v>0.463679318488941</v>
+        <v>0.1565798029368182</v>
       </c>
       <c r="L34" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M34" t="n">
-        <v>57.69230769230769</v>
+        <v>64.44444444444444</v>
       </c>
       <c r="N34" t="n">
-        <v>15.19973050008377</v>
+        <v>12.99617883422956</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>3.519999173333344</v>
+        <v>3.837411585564632</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4316,7 +4330,7 @@
         <v>46241</v>
       </c>
       <c r="C35" t="n">
-        <v>1.902467919077601</v>
+        <v>1.88895892095305</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4335,7 +4349,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.82: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4348,16 +4362,16 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>7.252105948285092</v>
+        <v>6.490532791870485</v>
       </c>
       <c r="L35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M35" t="n">
-        <v>81.81818181818181</v>
+        <v>100</v>
       </c>
       <c r="N35" t="n">
-        <v>13.27568040215743</v>
+        <v>16.98741539906919</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4390,7 +4404,7 @@
         <v>42.52272358489104</v>
       </c>
       <c r="Y35" t="n">
-        <v>17.31849694244031</v>
+        <v>17.90559975691569</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -4435,7 +4449,7 @@
         <v>46241</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08175895399062738</v>
+        <v>0.08176404112887647</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4463,7 +4477,7 @@
         <v>18.45194908889744</v>
       </c>
       <c r="K36" t="n">
-        <v>2.187666484261586</v>
+        <v>2.194024721022014</v>
       </c>
       <c r="L36" t="n">
         <v>20</v>
@@ -4544,7 +4558,7 @@
         <v>46241</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06393969209987092</v>
+        <v>0.06415332167517625</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4572,22 +4586,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>4.083023356424542</v>
+        <v>4.430776236457135</v>
       </c>
       <c r="L37" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M37" t="n">
-        <v>55.88235294117647</v>
+        <v>56.92307692307692</v>
       </c>
       <c r="N37" t="n">
-        <v>19.25285603332703</v>
+        <v>19.42924632473793</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>3.763319432182577</v>
+        <v>3.417789173051111</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4653,7 +4667,7 @@
         <v>46241</v>
       </c>
       <c r="C38" t="n">
-        <v>1.629938079430121</v>
+        <v>1.617460445242502</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4681,22 +4695,22 @@
         <v>15.02885014069408</v>
       </c>
       <c r="K38" t="n">
-        <v>2.87805681151232</v>
+        <v>2.090496366715611</v>
       </c>
       <c r="L38" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M38" t="n">
-        <v>57.4074074074074</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N38" t="n">
-        <v>13.87484178911396</v>
+        <v>13.2195873040694</v>
       </c>
       <c r="O38" t="n">
         <v>6</v>
       </c>
       <c r="P38" t="n">
-        <v>3.034605517683464</v>
+        <v>3.829449138185415</v>
       </c>
       <c r="Q38" t="n">
         <v>34</v>
@@ -4762,7 +4776,7 @@
         <v>46241</v>
       </c>
       <c r="C39" t="n">
-        <v>2.698045348570359</v>
+        <v>2.654186465743111</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4790,16 +4804,16 @@
         <v>16.13238434452433</v>
       </c>
       <c r="K39" t="n">
-        <v>6.800776077999671</v>
+        <v>5.064644131089957</v>
       </c>
       <c r="L39" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="M39" t="n">
-        <v>64.28571428571429</v>
+        <v>61.76470588235294</v>
       </c>
       <c r="N39" t="n">
-        <v>12.00195659539717</v>
+        <v>14.35146834624859</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4832,22 +4846,22 @@
         <v>10.2437411865161</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.12304813993155</v>
+        <v>4.697860395234487</v>
       </c>
       <c r="Z39" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AA39" t="n">
-        <v>40.47619047619047</v>
+        <v>46.875</v>
       </c>
       <c r="AB39" t="n">
-        <v>13.62390751815907</v>
+        <v>10.46535753231656</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.969696924634868</v>
+        <v>1.366327776234322</v>
       </c>
       <c r="AE39" t="n">
         <v>42</v>
@@ -4881,11 +4895,11 @@
         <v>46241</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2010431694691391</v>
+        <v>0.2039907851726745</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4895,7 +4909,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4938,25 +4952,25 @@
         <v>76.47058823529412</v>
       </c>
       <c r="X40" t="n">
-        <v>14.39492020679223</v>
+        <v>18.04834458245343</v>
       </c>
       <c r="Y40" t="n">
-        <v>4.018823054510323</v>
+        <v>5.625614513796496</v>
       </c>
       <c r="Z40" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AA40" t="n">
-        <v>50</v>
+        <v>31.25</v>
       </c>
       <c r="AB40" t="n">
-        <v>12.03512905673069</v>
+        <v>11.76313020993737</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.022259756250876</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>14</v>
@@ -4990,7 +5004,7 @@
         <v>46241</v>
       </c>
       <c r="C41" t="n">
-        <v>1.719034373161028</v>
+        <v>1.695031392478857</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5009,7 +5023,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -5022,16 +5036,16 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>13.60348216650358</v>
+        <v>12.01722988996778</v>
       </c>
       <c r="L41" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M41" t="n">
-        <v>100</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N41" t="n">
-        <v>12.17975430538131</v>
+        <v>13.38516228592029</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
@@ -5064,16 +5078,16 @@
         <v>40.81782021738603</v>
       </c>
       <c r="Y41" t="n">
-        <v>11.84231327356086</v>
+        <v>13.0732643729205</v>
       </c>
       <c r="Z41" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AA41" t="n">
-        <v>28.57142857142857</v>
+        <v>25</v>
       </c>
       <c r="AB41" t="n">
-        <v>17.85423125778112</v>
+        <v>22.19906898574699</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
@@ -5113,7 +5127,7 @@
         <v>46241</v>
       </c>
       <c r="C42" t="n">
-        <v>3.465321794226496</v>
+        <v>3.480212943428769</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5141,10 +5155,10 @@
         <v>19.79504810217467</v>
       </c>
       <c r="K42" t="n">
-        <v>12.74495660384745</v>
+        <v>13.22944320286659</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -5177,7 +5191,7 @@
         <v>14.97530566614946</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.939850517795727</v>
+        <v>1.518467337979768</v>
       </c>
       <c r="Z42" t="n">
         <v>11</v>
@@ -5186,13 +5200,13 @@
         <v>36.36363636363637</v>
       </c>
       <c r="AB42" t="n">
-        <v>11.18614412044539</v>
+        <v>11.34304697646094</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>8.219597384630751</v>
+        <v>8.612307742130787</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5224,7 +5238,7 @@
         <v>46241</v>
       </c>
       <c r="C43" t="n">
-        <v>7.127703498472553</v>
+        <v>7.117664423458236</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5284,7 +5298,7 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>8.000403643204058</v>
+        <v>8.129981262322294</v>
       </c>
       <c r="Z43" t="n">
         <v>8</v>
@@ -5333,7 +5347,7 @@
         <v>46241</v>
       </c>
       <c r="C44" t="n">
-        <v>5.048091247563783</v>
+        <v>5.063080878542457</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5365,7 +5379,7 @@
         <v>13.03201987649729</v>
       </c>
       <c r="K44" t="n">
-        <v>3.321028836341755</v>
+        <v>3.627826795935096</v>
       </c>
       <c r="L44" t="n">
         <v>23</v>
@@ -5374,13 +5388,13 @@
         <v>78.26086956521739</v>
       </c>
       <c r="N44" t="n">
-        <v>19.74854765260397</v>
+        <v>19.71680359537179</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>6.46429022134265</v>
+        <v>6.149094698871815</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5407,13 +5421,13 @@
         <v>12.1234692799834</v>
       </c>
       <c r="Y44" t="n">
-        <v>7.85066721549712</v>
+        <v>7.577042111347643</v>
       </c>
       <c r="Z44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA44" t="n">
-        <v>11.11111111111111</v>
+        <v>10</v>
       </c>
       <c r="AB44" t="n">
         <v>9.691917834769438</v>
@@ -5422,7 +5436,7 @@
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.332445303244057</v>
+        <v>2.621597429906364</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5448,7 +5462,7 @@
         <v>46241</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02117347194758895</v>
+        <v>0.02138444055839208</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5547,7 +5561,7 @@
         <v>46241</v>
       </c>
       <c r="C46" t="n">
-        <v>9.480893844659448</v>
+        <v>9.339969074081425</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5575,16 +5589,16 @@
         <v>20.92024905883424</v>
       </c>
       <c r="K46" t="n">
-        <v>14.81929990304494</v>
+        <v>13.11261657108458</v>
       </c>
       <c r="L46" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M46" t="n">
-        <v>62.5</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N46" t="n">
-        <v>10.48461562337478</v>
+        <v>12.63146762234659</v>
       </c>
       <c r="O46" t="n">
         <v>10</v>
@@ -5614,25 +5628,25 @@
         <v>66.26506024096386</v>
       </c>
       <c r="X46" t="n">
-        <v>15.26359791262</v>
+        <v>15.9689957774251</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.385462555066074</v>
+        <v>2.463054187192126</v>
       </c>
       <c r="Z46" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="AA46" t="n">
-        <v>35.18518518518518</v>
+        <v>34.69387755102041</v>
       </c>
       <c r="AB46" t="n">
-        <v>10.45668142974212</v>
+        <v>12.5177170812975</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.624654505251534</v>
+        <v>0.5505050505050457</v>
       </c>
       <c r="AE46" t="n">
         <v>37</v>
@@ -5666,7 +5680,7 @@
         <v>46241</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7765004239438545</v>
+        <v>0.7723556949273964</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5694,22 +5708,22 @@
         <v>24.7868707712232</v>
       </c>
       <c r="K47" t="n">
-        <v>4.171094223588923</v>
+        <v>3.615059811254939</v>
       </c>
       <c r="L47" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M47" t="n">
-        <v>33.33333333333334</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="N47" t="n">
-        <v>15.79730259714992</v>
+        <v>14.91896878085846</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>5.595511710667211</v>
+        <v>6.16217391600784</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5775,7 +5789,7 @@
         <v>46241</v>
       </c>
       <c r="C48" t="n">
-        <v>0.06058548183340008</v>
+        <v>0.06121820526041591</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5803,22 +5817,22 @@
         <v>21.44820004664813</v>
       </c>
       <c r="K48" t="n">
-        <v>3.23480354770278</v>
+        <v>4.312934425123616</v>
       </c>
       <c r="L48" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="M48" t="n">
-        <v>52.63157894736842</v>
+        <v>50</v>
       </c>
       <c r="N48" t="n">
-        <v>17.70506821122857</v>
+        <v>16.08201378722749</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>6.553212889266713</v>
+        <v>5.451927516197519</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5884,7 +5898,7 @@
         <v>46241</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2601611745496731</v>
+        <v>0.2574518916002879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5912,22 +5926,22 @@
         <v>21.9393534200744</v>
       </c>
       <c r="K49" t="n">
-        <v>2.955768613499221</v>
+        <v>1.883601296726356</v>
       </c>
       <c r="L49" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="M49" t="n">
-        <v>59.09090909090909</v>
+        <v>52</v>
       </c>
       <c r="N49" t="n">
-        <v>9.897294507717938</v>
+        <v>10.74970651135409</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>1.985543320233885</v>
+        <v>3.058783419126931</v>
       </c>
       <c r="Q49" t="n">
         <v>53</v>
@@ -5993,7 +6007,7 @@
         <v>46241</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7173824188633207</v>
+        <v>0.7119760744400307</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6018,10 +6032,10 @@
         <v>10</v>
       </c>
       <c r="J50" t="n">
-        <v>10.06953698454314</v>
+        <v>10.48618605822325</v>
       </c>
       <c r="K50" t="n">
-        <v>0.4107963101010137</v>
+        <v>0.1179272174471446</v>
       </c>
       <c r="L50" t="n">
         <v>47</v>
@@ -6030,13 +6044,13 @@
         <v>42.5531914893617</v>
       </c>
       <c r="N50" t="n">
-        <v>13.52451100484172</v>
+        <v>13.684937882731</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>3.574519694888556</v>
+        <v>3.877500154514135</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6102,7 +6116,7 @@
         <v>46241</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1861588466190696</v>
+        <v>0.1893151924066524</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6121,7 +6135,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -6134,16 +6148,16 @@
         <v>27.11346359280836</v>
       </c>
       <c r="K51" t="n">
-        <v>7.897893413401502</v>
+        <v>9.727315262266579</v>
       </c>
       <c r="L51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M51" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N51" t="n">
-        <v>21.01343299532531</v>
+        <v>22.72871476502574</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
@@ -6176,10 +6190,10 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>15.49032713844796</v>
+        <v>14.05745540126758</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="inlineStr"/>
@@ -6221,7 +6235,7 @@
         <v>46241</v>
       </c>
       <c r="C52" t="n">
-        <v>4.171802929988347</v>
+        <v>4.142711438860384</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6281,22 +6295,22 @@
         <v>12.1710603868542</v>
       </c>
       <c r="Y52" t="n">
-        <v>4.278313974660231</v>
+        <v>4.94581592201796</v>
       </c>
       <c r="Z52" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="AA52" t="n">
-        <v>45.45454545454545</v>
+        <v>50</v>
       </c>
       <c r="AB52" t="n">
-        <v>13.27167146973482</v>
+        <v>13.44360014086126</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.888028073758065</v>
+        <v>3.21309798995949</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6330,7 +6344,7 @@
         <v>46241</v>
       </c>
       <c r="C53" t="n">
-        <v>1.614215204065843</v>
+        <v>1.621653408731865</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6362,7 +6376,7 @@
         <v>28.17598592067425</v>
       </c>
       <c r="K53" t="n">
-        <v>6.42200815793692</v>
+        <v>6.912394245029851</v>
       </c>
       <c r="L53" t="n">
         <v>5</v>
@@ -6371,13 +6385,13 @@
         <v>100</v>
       </c>
       <c r="N53" t="n">
-        <v>11.73282595803085</v>
+        <v>11.18129841148397</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>1.482768338407259</v>
+        <v>1.017286875530532</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6435,7 +6449,7 @@
         <v>46241</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08762882179972258</v>
+        <v>0.08511845988860257</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6463,22 +6477,22 @@
         <v>42.39442432818535</v>
       </c>
       <c r="K54" t="n">
-        <v>8.411268879604105</v>
+        <v>5.305538201705051</v>
       </c>
       <c r="L54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M54" t="n">
-        <v>66.66666666666667</v>
+        <v>50</v>
       </c>
       <c r="N54" t="n">
-        <v>25.74621644893126</v>
+        <v>26.43294614127311</v>
       </c>
       <c r="O54" t="n">
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>1.465466770027635</v>
+        <v>4.457943882593396</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6505,7 +6519,7 @@
         <v>114.7400208810756</v>
       </c>
       <c r="Y54" t="n">
-        <v>37.54906446878523</v>
+        <v>39.33813850460513</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -6550,7 +6564,7 @@
         <v>46241</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8272328632124698</v>
+        <v>0.8130280343392041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6575,25 +6589,25 @@
         <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>14.36548603251675</v>
+        <v>15.19289137992348</v>
       </c>
       <c r="K55" t="n">
-        <v>0.9723572983773465</v>
+        <v>0.2067132259146787</v>
       </c>
       <c r="L55" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="M55" t="n">
-        <v>64.17910447761194</v>
+        <v>68.96551724137932</v>
       </c>
       <c r="N55" t="n">
-        <v>14.3964833592985</v>
+        <v>14.55767284840611</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>4.979226826175576</v>
+        <v>5.781335987963643</v>
       </c>
       <c r="Q55" t="n">
         <v>44</v>
@@ -6620,16 +6634,16 @@
         <v>25.41488056506582</v>
       </c>
       <c r="Y55" t="n">
-        <v>13.53281258602396</v>
+        <v>15.01758386988995</v>
       </c>
       <c r="Z55" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AA55" t="n">
-        <v>37.5</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB55" t="n">
-        <v>12.23057392064236</v>
+        <v>13.02435706412203</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6669,7 +6683,7 @@
         <v>46241</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9186351914514095</v>
+        <v>0.9472049509817939</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6697,7 +6711,7 @@
         <v>34.38683570496719</v>
       </c>
       <c r="K56" t="n">
-        <v>17.14570621223712</v>
+        <v>20.78896382706115</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6724,25 +6738,25 @@
         <v>100</v>
       </c>
       <c r="X56" t="n">
-        <v>19.34032560415109</v>
+        <v>21.43059934346674</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.838958776762079</v>
+        <v>0.5283968949133966</v>
       </c>
       <c r="Z56" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AA56" t="n">
-        <v>22.72727272727273</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AB56" t="n">
-        <v>9.075451416718147</v>
+        <v>14.48058828459551</v>
       </c>
       <c r="AC56" t="n">
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>8.313930986813878</v>
+        <v>9.521916616826154</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6768,7 +6782,7 @@
         <v>46241</v>
       </c>
       <c r="C57" t="n">
-        <v>1.459082801730304</v>
+        <v>1.434015485875022</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6785,11 +6799,7 @@
           <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>5</v>
       </c>
@@ -6800,7 +6810,7 @@
         <v>32.76213282665623</v>
       </c>
       <c r="K57" t="n">
-        <v>24.93721015277799</v>
+        <v>22.79076547858716</v>
       </c>
       <c r="L57" t="n">
         <v>1</v>
@@ -6838,16 +6848,16 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>10.04673890907767</v>
+        <v>11.59215278504465</v>
       </c>
       <c r="Z57" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA57" t="n">
-        <v>75</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="AB57" t="n">
-        <v>13.75807019707077</v>
+        <v>12.36237164600526</v>
       </c>
       <c r="AC57" t="n">
         <v>6</v>
@@ -6887,16 +6897,16 @@
         <v>46241</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7878209132832233</v>
+        <v>0.7715170703205835</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6906,7 +6916,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %84.62: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -6919,22 +6929,22 @@
         <v>16.33691982084211</v>
       </c>
       <c r="K58" t="n">
-        <v>6.20635146760633</v>
+        <v>4.008425966052287</v>
       </c>
       <c r="L58" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M58" t="n">
-        <v>85</v>
+        <v>84.61538461538461</v>
       </c>
       <c r="N58" t="n">
-        <v>16.32811750653458</v>
+        <v>20.44222564624019</v>
       </c>
       <c r="O58" t="n">
         <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>0.9533593309751343</v>
       </c>
       <c r="Q58" t="n">
         <v>24</v>
@@ -6961,10 +6971,10 @@
         <v>41.32985472592288</v>
       </c>
       <c r="Y58" t="n">
-        <v>11.1444950162983</v>
+        <v>12.98334719094161</v>
       </c>
       <c r="Z58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="inlineStr"/>
       <c r="AB58" t="inlineStr"/>
@@ -7006,7 +7016,7 @@
         <v>46241</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8184280915819284</v>
+        <v>0.8180597027318586</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7066,7 +7076,7 @@
         <v>10.2478061424703</v>
       </c>
       <c r="Y59" t="n">
-        <v>7.070823647644497</v>
+        <v>7.11265270112702</v>
       </c>
       <c r="Z59" t="n">
         <v>22</v>
@@ -7075,13 +7085,13 @@
         <v>54.54545454545455</v>
       </c>
       <c r="AB59" t="n">
-        <v>14.32858544529427</v>
+        <v>14.40253231574566</v>
       </c>
       <c r="AC59" t="n">
         <v>10</v>
       </c>
       <c r="AD59" t="n">
-        <v>3.152052420274409</v>
+        <v>3.108439828282195</v>
       </c>
       <c r="AE59" t="n">
         <v>43</v>
@@ -7115,7 +7125,7 @@
         <v>46241</v>
       </c>
       <c r="C60" t="n">
-        <v>13.39588981036459</v>
+        <v>13.56444442408683</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7143,22 +7153,22 @@
         <v>15.44754852801727</v>
       </c>
       <c r="K60" t="n">
-        <v>5.424191635474607</v>
+        <v>6.750698060180182</v>
       </c>
       <c r="L60" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M60" t="n">
-        <v>47.05882352941177</v>
+        <v>48.48484848484848</v>
       </c>
       <c r="N60" t="n">
-        <v>12.9634600651239</v>
+        <v>13.2557668906823</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>2.443280166123318</v>
+        <v>1.170298613987075</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7224,7 +7234,7 @@
         <v>46241</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6226258803579103</v>
+        <v>0.6184715772960765</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7252,22 +7262,22 @@
         <v>30.3360843704085</v>
       </c>
       <c r="K61" t="n">
-        <v>1.32183729175126</v>
+        <v>0.6457946919001589</v>
       </c>
       <c r="L61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M61" t="n">
-        <v>66.66666666666667</v>
+        <v>62.5</v>
       </c>
       <c r="N61" t="n">
-        <v>12.22538449547143</v>
+        <v>12.83082373170765</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>8.56494803115384</v>
+        <v>9.294183961421542</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7325,7 +7335,7 @@
         <v>46241</v>
       </c>
       <c r="C62" t="n">
-        <v>8.84673787163358</v>
+        <v>8.873494748832691</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7342,11 +7352,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>5</v>
       </c>
@@ -7357,16 +7363,16 @@
         <v>10.67683828611802</v>
       </c>
       <c r="K62" t="n">
-        <v>6.320279277422736</v>
+        <v>6.641843982704976</v>
       </c>
       <c r="L62" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M62" t="n">
-        <v>75</v>
+        <v>71.875</v>
       </c>
       <c r="N62" t="n">
-        <v>12.07162369147996</v>
+        <v>12.47974734393846</v>
       </c>
       <c r="O62" t="n">
         <v>6</v>
@@ -7438,11 +7444,11 @@
         <v>46241</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1023035113429219</v>
+        <v>0.1016809182386038</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7466,22 +7472,22 @@
         <v>29.14654498090023</v>
       </c>
       <c r="K63" t="n">
-        <v>2.522368111457429</v>
+        <v>1.89844310060816</v>
       </c>
       <c r="L63" t="n">
         <v>5</v>
       </c>
       <c r="M63" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="N63" t="n">
-        <v>13.09147462811611</v>
+        <v>15.31610697611221</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>2.416674462541679</v>
+        <v>3.043772608311168</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7508,22 +7514,22 @@
         <v>10.24796802016521</v>
       </c>
       <c r="Y63" t="n">
-        <v>7.00747600835121</v>
+        <v>7.57340481597798</v>
       </c>
       <c r="Z63" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA63" t="n">
-        <v>54.54545454545455</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB63" t="n">
-        <v>12.44107905981065</v>
+        <v>11.99689407402366</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>3.218026421045983</v>
+        <v>2.62542959544344</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7557,7 +7563,7 @@
         <v>46241</v>
       </c>
       <c r="C64" t="n">
-        <v>0.157648029899881</v>
+        <v>0.1563999319107659</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7585,22 +7591,22 @@
         <v>20.58679888238519</v>
       </c>
       <c r="K64" t="n">
-        <v>1.437889773628465</v>
+        <v>0.6348069420387015</v>
       </c>
       <c r="L64" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M64" t="n">
-        <v>57.14285714285715</v>
+        <v>60.97560975609756</v>
       </c>
       <c r="N64" t="n">
-        <v>13.84013301975477</v>
+        <v>14.36390006558601</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>3.511617044006776</v>
+        <v>4.337657308246712</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7666,7 +7672,7 @@
         <v>46241</v>
       </c>
       <c r="C65" t="n">
-        <v>5.744090466416116</v>
+        <v>5.718241447712029</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7691,10 +7697,10 @@
         <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>32.96849810841169</v>
+        <v>32.96432732954867</v>
       </c>
       <c r="K65" t="n">
-        <v>1.481481481481484</v>
+        <v>1.01851851851853</v>
       </c>
       <c r="L65" t="n">
         <v>6</v>
@@ -7709,7 +7715,7 @@
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>8.394160583941623</v>
+        <v>8.890925756186974</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7775,7 +7781,7 @@
         <v>46241</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4280814882618407</v>
+        <v>0.4310432305565219</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7874,16 +7880,16 @@
         <v>46241</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02830117607497652</v>
+        <v>0.02788363466246254</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7902,7 +7908,7 @@
         <v>18.49825117353735</v>
       </c>
       <c r="K67" t="n">
-        <v>5.112341263685005</v>
+        <v>3.56156629491271</v>
       </c>
       <c r="L67" t="n">
         <v>2</v>
@@ -7913,7 +7919,7 @@
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>0.4233556142234862</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7930,17 +7936,13 @@
         <v>10.87173616493582</v>
       </c>
       <c r="Y67" t="n">
-        <v>5.194646625432997</v>
+        <v>6.59335744427082</v>
       </c>
       <c r="Z67" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>5.358269135191785</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
         <v>3</v>
       </c>
@@ -7969,7 +7971,7 @@
         <v>46241</v>
       </c>
       <c r="C68" t="n">
-        <v>3.666574407070171</v>
+        <v>3.746470134795612</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8026,10 +8028,10 @@
         <v>80</v>
       </c>
       <c r="X68" t="n">
-        <v>127.8346976754615</v>
+        <v>127.8488738182379</v>
       </c>
       <c r="Y68" t="n">
-        <v>10.21561028666523</v>
+        <v>8.264890065667775</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -8074,7 +8076,7 @@
         <v>46241</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4066983681230594</v>
+        <v>0.407771954184647</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8102,7 +8104,7 @@
         <v>29.4573350207784</v>
       </c>
       <c r="K69" t="n">
-        <v>4.03199882602534</v>
+        <v>4.306618329452827</v>
       </c>
       <c r="L69" t="n">
         <v>7</v>
@@ -8167,7 +8169,7 @@
         <v>46241</v>
       </c>
       <c r="C70" t="n">
-        <v>0.3897176738404715</v>
+        <v>0.3857585351602917</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8192,25 +8194,25 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>22.01429878684488</v>
+        <v>22.00944642482017</v>
       </c>
       <c r="K70" t="n">
-        <v>1.695839432706281</v>
+        <v>0.6564492640617869</v>
       </c>
       <c r="L70" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M70" t="n">
-        <v>70</v>
+        <v>67.85714285714286</v>
       </c>
       <c r="N70" t="n">
-        <v>13.32346002337922</v>
+        <v>13.19062072266356</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>6.199034889195532</v>
+        <v>7.295658439801689</v>
       </c>
       <c r="Q70" t="n">
         <v>30</v>
@@ -8276,7 +8278,7 @@
         <v>46241</v>
       </c>
       <c r="C71" t="n">
-        <v>3.209563085573939</v>
+        <v>3.207666146654227</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8304,7 +8306,7 @@
         <v>19.51282806733038</v>
       </c>
       <c r="K71" t="n">
-        <v>2.450573542467271</v>
+        <v>2.390022472082332</v>
       </c>
       <c r="L71" t="n">
         <v>40</v>
@@ -8319,7 +8321,7 @@
         <v>6</v>
       </c>
       <c r="P71" t="n">
-        <v>3.464525707180588</v>
+        <v>3.525712213709076</v>
       </c>
       <c r="Q71" t="n">
         <v>43</v>
@@ -8385,7 +8387,7 @@
         <v>46241</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07840473869283643</v>
+        <v>0.07799031478290006</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8413,13 +8415,13 @@
         <v>20.36571476939619</v>
       </c>
       <c r="K72" t="n">
-        <v>9.61466314572068</v>
+        <v>9.035272945018956</v>
       </c>
       <c r="L72" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M72" t="n">
-        <v>69.23076923076923</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N72" t="n">
         <v>14.39782702990865</v>
@@ -8455,10 +8457,10 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>12.70914649597125</v>
+        <v>13.17053974099621</v>
       </c>
       <c r="Z72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr"/>
@@ -8500,7 +8502,7 @@
         <v>46241</v>
       </c>
       <c r="C73" t="n">
-        <v>0.06939028868318217</v>
+        <v>0.07023321091846435</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8517,7 +8519,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H73" t="n">
         <v>5</v>
       </c>
@@ -8528,22 +8534,22 @@
         <v>22.14049070857409</v>
       </c>
       <c r="K73" t="n">
-        <v>0.9036864431843483</v>
+        <v>2.129419359691354</v>
       </c>
       <c r="L73" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="M73" t="n">
-        <v>68.18181818181819</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="N73" t="n">
-        <v>16.33753430337937</v>
+        <v>13.89858393598737</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>9.01484760117015</v>
+        <v>7.706477418214952</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8609,28 +8615,24 @@
         <v>46241</v>
       </c>
       <c r="C74" t="n">
-        <v>5.10679004619678</v>
+        <v>4.975027361989737</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %82.35: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>5</v>
       </c>
@@ -8641,22 +8643,22 @@
         <v>18.35970785011217</v>
       </c>
       <c r="K74" t="n">
-        <v>8.044862834806409</v>
+        <v>5.257146673947566</v>
       </c>
       <c r="L74" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="M74" t="n">
-        <v>82.35294117647059</v>
+        <v>62.06896551724138</v>
       </c>
       <c r="N74" t="n">
-        <v>18.93961936180272</v>
+        <v>20.2220764956805</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.605859471517791</v>
       </c>
       <c r="Q74" t="n">
         <v>35</v>
@@ -8683,7 +8685,7 @@
         <v>95.98093909010421</v>
       </c>
       <c r="Y74" t="n">
-        <v>11.79185832871846</v>
+        <v>14.06775794675327</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
@@ -8728,7 +8730,7 @@
         <v>46241</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1287179369235883</v>
+        <v>0.1280969972095028</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8753,25 +8755,25 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>21.58944468202061</v>
+        <v>21.58456588507395</v>
       </c>
       <c r="K75" t="n">
-        <v>1.8242065699696</v>
+        <v>1.326698461259279</v>
       </c>
       <c r="L75" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M75" t="n">
-        <v>66.66666666666667</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N75" t="n">
-        <v>14.09467689902224</v>
+        <v>16.73664961466951</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>4.100983028196703</v>
+        <v>4.612112710380556</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8837,7 +8839,7 @@
         <v>46241</v>
       </c>
       <c r="C76" t="n">
-        <v>1.851106590160653</v>
+        <v>1.837594396483478</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8865,22 +8867,22 @@
         <v>18.36583782901725</v>
       </c>
       <c r="K76" t="n">
-        <v>6.804767429875791</v>
+        <v>6.025143657355581</v>
       </c>
       <c r="L76" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M76" t="n">
-        <v>42.85714285714285</v>
+        <v>44</v>
       </c>
       <c r="N76" t="n">
-        <v>13.49039130179921</v>
+        <v>12.61717600445746</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>2.991657251837654</v>
+        <v>3.748975201099536</v>
       </c>
       <c r="Q76" t="n">
         <v>40</v>
@@ -8946,7 +8948,7 @@
         <v>46241</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5358355813037518</v>
+        <v>0.5312566054729937</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8974,16 +8976,16 @@
         <v>20.36657537342047</v>
       </c>
       <c r="K77" t="n">
-        <v>10.35857234296802</v>
+        <v>9.41550463132803</v>
       </c>
       <c r="L77" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M77" t="n">
-        <v>58.8235294117647</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="N77" t="n">
-        <v>20.42536750761273</v>
+        <v>14.59152648540055</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -9013,25 +9015,25 @@
         <v>61.8421052631579</v>
       </c>
       <c r="X77" t="n">
-        <v>14.762554963676</v>
+        <v>14.76969562478312</v>
       </c>
       <c r="Y77" t="n">
-        <v>3.837473487847931</v>
+        <v>4.6651609245001</v>
       </c>
       <c r="Z77" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AA77" t="n">
-        <v>41.81818181818182</v>
+        <v>51.85185185185185</v>
       </c>
       <c r="AB77" t="n">
-        <v>12.4012367260855</v>
+        <v>11.57223803247395</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>6.408449045245613</v>
+        <v>5.595896659850652</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9065,7 +9067,7 @@
         <v>46241</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05387705144745651</v>
+        <v>0.05388040374094596</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9093,7 +9095,7 @@
         <v>12.76206508896208</v>
       </c>
       <c r="K78" t="n">
-        <v>6.339575133273478</v>
+        <v>6.346191706671855</v>
       </c>
       <c r="L78" t="n">
         <v>51</v>
@@ -9135,7 +9137,7 @@
         <v>23.16536029857119</v>
       </c>
       <c r="Y78" t="n">
-        <v>7.231550660560626</v>
+        <v>7.225778498566005</v>
       </c>
       <c r="Z78" t="n">
         <v>18</v>
@@ -9150,7 +9152,7 @@
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>2.984257427123338</v>
+        <v>2.990293485126272</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9184,7 +9186,7 @@
         <v>46241</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8725147411170144</v>
+        <v>0.8629250857198566</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9209,25 +9211,25 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>11.83621857703275</v>
+        <v>11.94318589124698</v>
       </c>
       <c r="K79" t="n">
-        <v>1.037716358354746</v>
+        <v>0.04861560597120285</v>
       </c>
       <c r="L79" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="M79" t="n">
-        <v>57.6271186440678</v>
+        <v>58.49056603773585</v>
       </c>
       <c r="N79" t="n">
-        <v>10.8917057232686</v>
+        <v>10.926012998354</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>3.921588674462972</v>
+        <v>4.948978418181427</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9293,7 +9295,7 @@
         <v>46241</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1282986606664842</v>
+        <v>0.127468038660421</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9321,10 +9323,10 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>5.041932970219265</v>
+        <v>4.361878006034603</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
@@ -9332,7 +9334,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>4.720083579560952</v>
+        <v>5.402472724417051</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9359,22 +9361,22 @@
         <v>11.74527658842108</v>
       </c>
       <c r="Y80" t="n">
-        <v>5.99877133320944</v>
+        <v>6.607347359818105</v>
       </c>
       <c r="Z80" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AA80" t="n">
-        <v>31.42857142857143</v>
+        <v>38.70967741935484</v>
       </c>
       <c r="AB80" t="n">
-        <v>11.86932253340606</v>
+        <v>11.51059405130598</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>2.128938839602168</v>
+        <v>1.491180088381716</v>
       </c>
       <c r="AE80" t="n">
         <v>26</v>
@@ -9408,7 +9410,7 @@
         <v>46241</v>
       </c>
       <c r="C81" t="n">
-        <v>1.07544465898408</v>
+        <v>1.073415092460933</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9436,22 +9438,22 @@
         <v>12.04277302023445</v>
       </c>
       <c r="K81" t="n">
-        <v>2.683593019735353</v>
+        <v>2.489809749598293</v>
       </c>
       <c r="L81" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M81" t="n">
-        <v>46.80851063829788</v>
+        <v>51.02040816326531</v>
       </c>
       <c r="N81" t="n">
-        <v>13.53882956749119</v>
+        <v>12.98769363041235</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>7.125195725142253</v>
+        <v>7.327743381269336</v>
       </c>
       <c r="Q81" t="n">
         <v>31</v>
@@ -9478,7 +9480,7 @@
         <v>27.31228182970742</v>
       </c>
       <c r="Y81" t="n">
-        <v>9.682359016652697</v>
+        <v>9.852805407415953</v>
       </c>
       <c r="Z81" t="n">
         <v>9</v>
@@ -9487,13 +9489,13 @@
         <v>55.55555555555556</v>
       </c>
       <c r="AB81" t="n">
-        <v>9.276812191444455</v>
+        <v>9.529724010146259</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.3516931796368139</v>
+        <v>0.1632824995267845</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9527,7 +9529,7 @@
         <v>46241</v>
       </c>
       <c r="C82" t="n">
-        <v>5.445355834494841</v>
+        <v>5.4561772200442</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9584,10 +9586,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="X82" t="n">
-        <v>20.35550163226623</v>
+        <v>20.59357073426573</v>
       </c>
       <c r="Y82" t="n">
-        <v>0.478927203065127</v>
+        <v>0.4780114722753304</v>
       </c>
       <c r="Z82" t="n">
         <v>9</v>
@@ -9596,13 +9598,13 @@
         <v>55.55555555555556</v>
       </c>
       <c r="AB82" t="n">
-        <v>13.66017785399789</v>
+        <v>11.42912722426582</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>3.538017324350351</v>
+        <v>3.538904899135453</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9636,7 +9638,7 @@
         <v>46241</v>
       </c>
       <c r="C83" t="n">
-        <v>5.780777175599431</v>
+        <v>5.770654293245594</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9664,7 +9666,7 @@
         <v>12.767909949277</v>
       </c>
       <c r="K83" t="n">
-        <v>6.80831544856475</v>
+        <v>6.621280387559292</v>
       </c>
       <c r="L83" t="n">
         <v>47</v>
@@ -9673,13 +9675,13 @@
         <v>51.06382978723404</v>
       </c>
       <c r="N83" t="n">
-        <v>12.75679562492979</v>
+        <v>12.9489451409831</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>2.988236017047075</v>
+        <v>3.168897991244668</v>
       </c>
       <c r="Q83" t="n">
         <v>43</v>
@@ -9706,22 +9708,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>3.909736976814027</v>
+        <v>4.078003353182702</v>
       </c>
       <c r="Z83" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AA83" t="n">
-        <v>46.93877551020408</v>
+        <v>48</v>
       </c>
       <c r="AB83" t="n">
-        <v>12.49448922988003</v>
+        <v>12.32759992881112</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>2.175312000844054</v>
+        <v>2.00370792310971</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9755,16 +9757,16 @@
         <v>46241</v>
       </c>
       <c r="C84" t="n">
-        <v>2.215877170732509</v>
+        <v>2.188760461558369</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -9783,22 +9785,22 @@
         <v>13.05747170375323</v>
       </c>
       <c r="K84" t="n">
-        <v>6.079694109861999</v>
+        <v>4.781548051744533</v>
       </c>
       <c r="L84" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M84" t="n">
-        <v>63.63636363636363</v>
+        <v>54</v>
       </c>
       <c r="N84" t="n">
-        <v>9.985260231565674</v>
+        <v>10.93702068392672</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>0.2084832227784883</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9864,7 +9866,7 @@
         <v>46241</v>
       </c>
       <c r="C85" t="n">
-        <v>6.441137940899094</v>
+        <v>6.410091008755098</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9889,25 +9891,25 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>16.27610717942479</v>
+        <v>16.27089778037133</v>
       </c>
       <c r="K85" t="n">
-        <v>1.319043693322342</v>
+        <v>0.8244023083264773</v>
       </c>
       <c r="L85" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M85" t="n">
-        <v>62</v>
+        <v>61.22448979591837</v>
       </c>
       <c r="N85" t="n">
-        <v>15.28721336308754</v>
+        <v>15.26658355411092</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>6.593978844589099</v>
+        <v>7.116925592804568</v>
       </c>
       <c r="Q85" t="n">
         <v>34</v>
@@ -9973,7 +9975,7 @@
         <v>46241</v>
       </c>
       <c r="C86" t="n">
-        <v>4.347899006188871</v>
+        <v>4.360748748392675</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10030,10 +10032,10 @@
         <v>69.23076923076923</v>
       </c>
       <c r="X86" t="n">
-        <v>72.04624587018722</v>
+        <v>72.05695078989642</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.049624110674119</v>
+        <v>0.7633616667151233</v>
       </c>
       <c r="Z86" t="n">
         <v>2</v>
@@ -10044,7 +10046,7 @@
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>5.002887401724266</v>
+        <v>5.276920320192335</v>
       </c>
       <c r="AE86" t="n">
         <v>51</v>
@@ -10078,7 +10080,7 @@
         <v>46241</v>
       </c>
       <c r="C87" t="n">
-        <v>5.440114876040081</v>
+        <v>5.450935935490843</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10103,25 +10105,25 @@
         <v>10</v>
       </c>
       <c r="J87" t="n">
-        <v>25.69784138952578</v>
+        <v>25.69321822185289</v>
       </c>
       <c r="K87" t="n">
-        <v>0.9727626459143934</v>
+        <v>1.167315175097272</v>
       </c>
       <c r="L87" t="n">
         <v>18</v>
       </c>
       <c r="M87" t="n">
-        <v>61.11111111111111</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N87" t="n">
-        <v>13.37583562188185</v>
+        <v>13.89809848647828</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>3.988439306358393</v>
+        <v>3.788461538461552</v>
       </c>
       <c r="Q87" t="n">
         <v>47</v>
@@ -10187,7 +10189,7 @@
         <v>46241</v>
       </c>
       <c r="C88" t="n">
-        <v>1.077541090373163</v>
+        <v>1.082849420800131</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10215,7 +10217,7 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>20.71865210490804</v>
+        <v>21.3133528544164</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -10250,25 +10252,25 @@
         <v>68.35443037974683</v>
       </c>
       <c r="X88" t="n">
-        <v>21.54066265509293</v>
+        <v>23.42722965068291</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.6763255458937079</v>
+        <v>1.712650281667261</v>
       </c>
       <c r="Z88" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AA88" t="n">
-        <v>48.83720930232558</v>
+        <v>52.38095238095238</v>
       </c>
       <c r="AB88" t="n">
-        <v>12.1566647073723</v>
+        <v>14.00463844929242</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>5.359924996095633</v>
+        <v>4.362056491114297</v>
       </c>
       <c r="AE88" t="n">
         <v>31</v>
@@ -10302,7 +10304,7 @@
         <v>46241</v>
       </c>
       <c r="C89" t="n">
-        <v>2.152985669275398</v>
+        <v>2.169891805089624</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10321,7 +10323,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -10334,16 +10336,16 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>16.94664038406071</v>
+        <v>17.86495387474723</v>
       </c>
       <c r="L89" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M89" t="n">
-        <v>75</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N89" t="n">
-        <v>13.89075511307736</v>
+        <v>12.23354717638958</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
@@ -10376,22 +10378,22 @@
         <v>28.7873334490923</v>
       </c>
       <c r="Y89" t="n">
-        <v>6.108395845656956</v>
+        <v>5.37112005497179</v>
       </c>
       <c r="Z89" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA89" t="n">
-        <v>36.8421052631579</v>
+        <v>50</v>
       </c>
       <c r="AB89" t="n">
-        <v>13.70601402841478</v>
+        <v>13.5371704471235</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>4.144783965929322</v>
+        <v>4.891614428615465</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10425,7 +10427,7 @@
         <v>46241</v>
       </c>
       <c r="C90" t="n">
-        <v>2.890912555765805</v>
+        <v>2.924636780772972</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10453,16 +10455,16 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>13.96049265356407</v>
+        <v>15.28990999913931</v>
       </c>
       <c r="L90" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M90" t="n">
-        <v>72.72727272727273</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N90" t="n">
-        <v>15.79134081414257</v>
+        <v>12.26477270856481</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
@@ -10495,16 +10497,16 @@
         <v>33.24184775233741</v>
       </c>
       <c r="Y90" t="n">
-        <v>4.941810570644578</v>
+        <v>3.832899904116227</v>
       </c>
       <c r="Z90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA90" t="n">
-        <v>38.88888888888889</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB90" t="n">
-        <v>11.43145410878323</v>
+        <v>11.48286031783636</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
@@ -10544,16 +10546,16 @@
         <v>46241</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2352142211098294</v>
+        <v>0.2333419906216001</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -10572,22 +10574,22 @@
         <v>14.07074278425192</v>
       </c>
       <c r="K91" t="n">
-        <v>3.741915720162448</v>
+        <v>2.91616302288864</v>
       </c>
       <c r="L91" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M91" t="n">
-        <v>61.11111111111111</v>
+        <v>62.5</v>
       </c>
       <c r="N91" t="n">
-        <v>14.96833074810355</v>
+        <v>13.96131255902363</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>0.08146142903979747</v>
       </c>
       <c r="Q91" t="n">
         <v>47</v>
@@ -10653,7 +10655,7 @@
         <v>46241</v>
       </c>
       <c r="C92" t="n">
-        <v>1.121565109318475</v>
+        <v>1.13002098178034</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10681,22 +10683,22 @@
         <v>22.28274626067631</v>
       </c>
       <c r="K92" t="n">
-        <v>6.445381981118636</v>
+        <v>7.247911024424702</v>
       </c>
       <c r="L92" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M92" t="n">
-        <v>70.58823529411765</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N92" t="n">
-        <v>12.52921606166961</v>
+        <v>13.41652570645844</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>1.460484231394021</v>
+        <v>0.7012621209974146</v>
       </c>
       <c r="Q92" t="n">
         <v>56</v>
@@ -10762,7 +10764,7 @@
         <v>46241</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04234694389517791</v>
+        <v>0.04234957877181841</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10790,7 +10792,7 @@
         <v>17.21421071359344</v>
       </c>
       <c r="K93" t="n">
-        <v>2.700194231733777</v>
+        <v>2.706584358573294</v>
       </c>
       <c r="L93" t="n">
         <v>47</v>
@@ -10805,7 +10807,7 @@
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>3.213047251712609</v>
+        <v>3.20662561411702</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10871,7 +10873,7 @@
         <v>46241</v>
       </c>
       <c r="C94" t="n">
-        <v>6.729390655910851</v>
+        <v>6.708844228296423</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10928,25 +10930,25 @@
         <v>70.90909090909091</v>
       </c>
       <c r="X94" t="n">
-        <v>49.30897816906403</v>
+        <v>49.31826834924253</v>
       </c>
       <c r="Y94" t="n">
-        <v>3.31325301204819</v>
+        <v>3.614457831325302</v>
       </c>
       <c r="Z94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA94" t="n">
-        <v>33.33333333333334</v>
+        <v>40</v>
       </c>
       <c r="AB94" t="n">
-        <v>10.23034872298341</v>
+        <v>8.62290485169116</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>2.778816199376954</v>
+        <v>2.475000000000005</v>
       </c>
       <c r="AE94" t="n">
         <v>37</v>
@@ -10980,7 +10982,7 @@
         <v>46241</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1383613011092603</v>
+        <v>0.1379506077671341</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11005,10 +11007,10 @@
         <v>10</v>
       </c>
       <c r="J95" t="n">
-        <v>23.90003550114733</v>
+        <v>23.89530047187822</v>
       </c>
       <c r="K95" t="n">
-        <v>0.4566168831620976</v>
+        <v>0.1522031924087397</v>
       </c>
       <c r="L95" t="n">
         <v>20</v>
@@ -11023,7 +11025,7 @@
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>5.518186147245263</v>
+        <v>5.83890980047308</v>
       </c>
       <c r="Q95" t="n">
         <v>23</v>
@@ -11089,7 +11091,7 @@
         <v>46241</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1301854088547726</v>
+        <v>0.1310321138339145</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11117,22 +11119,22 @@
         <v>12.85874206974231</v>
       </c>
       <c r="K96" t="n">
-        <v>0.6940708200939838</v>
+        <v>1.348968875747425</v>
       </c>
       <c r="L96" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M96" t="n">
-        <v>56.71641791044776</v>
+        <v>57.97101449275362</v>
       </c>
       <c r="N96" t="n">
-        <v>13.21518502957764</v>
+        <v>12.20935754886504</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>9.241784649398621</v>
+        <v>8.535884696428075</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11159,16 +11161,16 @@
         <v>16.74415231729489</v>
       </c>
       <c r="Y96" t="n">
-        <v>12.25392002618556</v>
+        <v>11.68323362232835</v>
       </c>
       <c r="Z96" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA96" t="n">
-        <v>42.85714285714285</v>
+        <v>40</v>
       </c>
       <c r="AB96" t="n">
-        <v>15.96559934023883</v>
+        <v>16.42948776937994</v>
       </c>
       <c r="AC96" t="n">
         <v>8</v>
@@ -11208,7 +11210,7 @@
         <v>46241</v>
       </c>
       <c r="C97" t="n">
-        <v>1.829094500710971</v>
+        <v>1.820822221759415</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11236,22 +11238,22 @@
         <v>19.26562870655475</v>
       </c>
       <c r="K97" t="n">
-        <v>2.337512287417276</v>
+        <v>1.874679750049291</v>
       </c>
       <c r="L97" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M97" t="n">
-        <v>54.83870967741935</v>
+        <v>54.28571428571428</v>
       </c>
       <c r="N97" t="n">
-        <v>13.11922177865826</v>
+        <v>13.16763130338414</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>1.624514486841933</v>
+        <v>2.086210484455231</v>
       </c>
       <c r="Q97" t="n">
         <v>50</v>
@@ -11317,7 +11319,7 @@
         <v>46241</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6473631707222397</v>
+        <v>0.6406946126907851</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11345,22 +11347,22 @@
         <v>17.47600423199651</v>
       </c>
       <c r="K98" t="n">
-        <v>7.821375930201402</v>
+        <v>6.710696276276007</v>
       </c>
       <c r="L98" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M98" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="N98" t="n">
-        <v>15.90711376272659</v>
+        <v>15.9466109479899</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>2.020586410628766</v>
+        <v>3.082449874760385</v>
       </c>
       <c r="Q98" t="n">
         <v>48</v>
@@ -11387,22 +11389,22 @@
         <v>11.17514685780745</v>
       </c>
       <c r="Y98" t="n">
-        <v>3.016655270890256</v>
+        <v>4.015691193321702</v>
       </c>
       <c r="Z98" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="AA98" t="n">
-        <v>43.47826086956522</v>
+        <v>41.86046511627907</v>
       </c>
       <c r="AB98" t="n">
-        <v>11.72835158567628</v>
+        <v>11.96674257710748</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>5.138351067421976</v>
+        <v>4.151000154309681</v>
       </c>
       <c r="AE98" t="n">
         <v>50</v>
@@ -11436,7 +11438,7 @@
         <v>46241</v>
       </c>
       <c r="C99" t="n">
-        <v>0.472105547248075</v>
+        <v>0.4821981789088054</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11464,22 +11466,22 @@
         <v>28.77817890954801</v>
       </c>
       <c r="K99" t="n">
-        <v>1.565554884878173</v>
+        <v>3.736814555191126</v>
       </c>
       <c r="L99" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="M99" t="n">
-        <v>72.72727272727273</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N99" t="n">
-        <v>14.51941654239078</v>
+        <v>12.82986200275538</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>2.396920016713544</v>
+        <v>0.2537049609026232</v>
       </c>
       <c r="Q99" t="n">
         <v>35</v>
@@ -11545,7 +11547,7 @@
         <v>46241</v>
       </c>
       <c r="C100" t="n">
-        <v>326.5064707730453</v>
+        <v>322.6811576386785</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11573,16 +11575,16 @@
         <v>25.15478290083538</v>
       </c>
       <c r="K100" t="n">
-        <v>6.532365748625679</v>
+        <v>5.28424451853633</v>
       </c>
       <c r="L100" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M100" t="n">
-        <v>73.33333333333333</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N100" t="n">
-        <v>11.56873670362326</v>
+        <v>9.914713839392286</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11654,7 +11656,7 @@
         <v>46241</v>
       </c>
       <c r="C101" t="n">
-        <v>327.4418794948024</v>
+        <v>324.8397274502345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11682,16 +11684,16 @@
         <v>13.42090796247281</v>
       </c>
       <c r="K101" t="n">
-        <v>3.690706889614059</v>
+        <v>2.866685889759713</v>
       </c>
       <c r="L101" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M101" t="n">
-        <v>38.23529411764706</v>
+        <v>37.83783783783784</v>
       </c>
       <c r="N101" t="n">
-        <v>8.144715481479819</v>
+        <v>10.22874357253002</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11763,7 +11765,7 @@
         <v>46241</v>
       </c>
       <c r="C102" t="n">
-        <v>398.8581069658313</v>
+        <v>396.5549750938205</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11862,16 +11864,16 @@
         <v>46241</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7190594840604526</v>
+        <v>0.7098795926953495</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -11890,22 +11892,22 @@
         <v>26.3831854858525</v>
       </c>
       <c r="K103" t="n">
-        <v>10.59015678141253</v>
+        <v>9.178304705461414</v>
       </c>
       <c r="L103" t="n">
         <v>14</v>
       </c>
       <c r="M103" t="n">
-        <v>57.14285714285715</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N103" t="n">
-        <v>11.83420089682727</v>
+        <v>14.7065956041638</v>
       </c>
       <c r="O103" t="n">
         <v>10</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>0.7526177446657956</v>
       </c>
       <c r="Q103" t="n">
         <v>43</v>
@@ -11932,22 +11934,22 @@
         <v>14.26498323563516</v>
       </c>
       <c r="Y103" t="n">
-        <v>3.216056529448297</v>
+        <v>4.451651228691911</v>
       </c>
       <c r="Z103" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="AA103" t="n">
-        <v>40.81632653061224</v>
+        <v>45</v>
       </c>
       <c r="AB103" t="n">
-        <v>11.25377200429218</v>
+        <v>10.96541638459621</v>
       </c>
       <c r="AC103" t="n">
         <v>10</v>
       </c>
       <c r="AD103" t="n">
-        <v>7.009368731308041</v>
+        <v>5.806849456486041</v>
       </c>
       <c r="AE103" t="n">
         <v>41</v>
@@ -11981,7 +11983,7 @@
         <v>46241</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04821681673559323</v>
+        <v>0.04842946801510651</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12000,7 +12002,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.95: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -12010,25 +12012,25 @@
         <v>10</v>
       </c>
       <c r="J104" t="n">
-        <v>28.27204186542799</v>
+        <v>28.26757886753546</v>
       </c>
       <c r="K104" t="n">
-        <v>0.4366807936538208</v>
+        <v>0.8733615873076417</v>
       </c>
       <c r="L104" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M104" t="n">
-        <v>78.94736842105263</v>
+        <v>80</v>
       </c>
       <c r="N104" t="n">
-        <v>14.07646711978468</v>
+        <v>15.48542247307857</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>3.547826529300568</v>
+        <v>3.09956797661215</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>

--- a/TDA_Result.xlsx
+++ b/TDA_Result.xlsx
@@ -679,7 +679,7 @@
         <v>46241</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4499118467722017</v>
+        <v>0.4524706706916669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -739,22 +739,22 @@
         <v>14.94856954517825</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.539123532578738</v>
+        <v>5.001887734293875</v>
       </c>
       <c r="Z2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="AA2" t="n">
-        <v>51.61290322580645</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.90435794292219</v>
+        <v>10.73616807324932</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.605180641394955</v>
+        <v>3.15597036004307</v>
       </c>
       <c r="AE2" t="n">
         <v>43</v>
@@ -788,7 +788,7 @@
         <v>46241</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7304254185005438</v>
+        <v>0.7393009799620726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,22 +848,22 @@
         <v>12.13279917920569</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.995089872612112</v>
+        <v>2.828512890401647</v>
       </c>
       <c r="Z3" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="AA3" t="n">
-        <v>42</v>
+        <v>43.10344827586207</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.44884507590466</v>
+        <v>10.88608479467795</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>6.254794801036779</v>
+        <v>7.380238095471081</v>
       </c>
       <c r="AE3" t="n">
         <v>38</v>
@@ -897,7 +897,7 @@
         <v>46241</v>
       </c>
       <c r="C4" t="n">
-        <v>1.40047129660055</v>
+        <v>1.413184615845841</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         <v>23.54405567752772</v>
       </c>
       <c r="K4" t="n">
-        <v>8.434146525475272</v>
+        <v>9.418499382413703</v>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M4" t="n">
-        <v>69.23076923076923</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="N4" t="n">
-        <v>10.11394003839786</v>
+        <v>11.66216497550878</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -967,22 +967,22 @@
         <v>12.1087988317258</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.277755488011369</v>
+        <v>2.39972194631235</v>
       </c>
       <c r="Z4" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AA4" t="n">
-        <v>25.92592592592593</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.66076555103657</v>
+        <v>11.8808641691881</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>6.95005016261323</v>
+        <v>7.78714795208566</v>
       </c>
       <c r="AE4" t="n">
         <v>45</v>
@@ -1016,7 +1016,7 @@
         <v>46241</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2608063105696654</v>
+        <v>0.2629278134109778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,22 +1076,22 @@
         <v>16.70172291026088</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.647640137332411</v>
+        <v>5.888274705340835</v>
       </c>
       <c r="Z5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AA5" t="n">
-        <v>48</v>
+        <v>37.93103448275862</v>
       </c>
       <c r="AB5" t="n">
-        <v>16.59827446987049</v>
+        <v>17.33713608175451</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.591082076124597</v>
+        <v>4.368983016500394</v>
       </c>
       <c r="AE5" t="n">
         <v>44</v>
@@ -1125,7 +1125,7 @@
         <v>46241</v>
       </c>
       <c r="C6" t="n">
-        <v>1.925647912826546</v>
+        <v>1.916395743596392</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1157,22 +1157,22 @@
         <v>23.73506360720576</v>
       </c>
       <c r="K6" t="n">
-        <v>1.422647805336519</v>
+        <v>0.9353419510238714</v>
       </c>
       <c r="L6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M6" t="n">
-        <v>77.77777777777777</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="N6" t="n">
-        <v>14.69846461632307</v>
+        <v>14.62179439154069</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5692537191215985</v>
+        <v>1.054792135635441</v>
       </c>
       <c r="Q6" t="n">
         <v>41</v>
@@ -1199,7 +1199,7 @@
         <v>44.49622708587002</v>
       </c>
       <c r="Y6" t="n">
-        <v>22.65008216337239</v>
+        <v>23.0217256632023</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1244,11 +1244,11 @@
         <v>46241</v>
       </c>
       <c r="C7" t="n">
-        <v>2.113285995857045</v>
+        <v>2.134453930825002</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1269,25 +1269,25 @@
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>11.71893639989927</v>
+        <v>11.71054792447627</v>
       </c>
       <c r="K7" t="n">
-        <v>1.664146741844252</v>
+        <v>2.672719595670592</v>
       </c>
       <c r="L7" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="M7" t="n">
-        <v>58.9041095890411</v>
+        <v>53.73134328358209</v>
       </c>
       <c r="N7" t="n">
-        <v>13.56877259738972</v>
+        <v>12.90798239203889</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.313986593078753</v>
+        <v>0.3187608213927273</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1314,22 +1314,22 @@
         <v>13.79329344082609</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.24980995633276</v>
+        <v>9.350818437943541</v>
       </c>
       <c r="Z7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA7" t="n">
-        <v>62.5</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.504924063550045</v>
+        <v>7.649714189658804</v>
       </c>
       <c r="AC7" t="n">
         <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>0.7161471850819057</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1363,7 +1363,7 @@
         <v>46241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3322974486495597</v>
+        <v>0.3335870402929</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>22.10694516187944</v>
       </c>
       <c r="K8" t="n">
-        <v>5.653242755708465</v>
+        <v>6.063265581653332</v>
       </c>
       <c r="L8" t="n">
         <v>4</v>
@@ -1406,7 +1406,7 @@
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.221188089529558</v>
+        <v>1.826018091867687</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1472,7 +1472,7 @@
         <v>46241</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5912169135521274</v>
+        <v>0.5996599352035831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>46241</v>
       </c>
       <c r="C10" t="n">
-        <v>2.033618406702353</v>
+        <v>2.052682090695499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,22 +1599,22 @@
         <v>10.23694539327734</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6939790124068868</v>
+        <v>1.637911359585908</v>
       </c>
       <c r="L10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>43.90243902439025</v>
+        <v>34.88372093023256</v>
       </c>
       <c r="N10" t="n">
-        <v>9.525580081718513</v>
+        <v>10.2042419622148</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>9.24188425054342</v>
+        <v>8.227332231208262</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1680,7 +1680,7 @@
         <v>46241</v>
       </c>
       <c r="C11" t="n">
-        <v>7.348280943805926</v>
+        <v>7.417122351739895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1712,16 +1712,16 @@
         <v>20.56423081971027</v>
       </c>
       <c r="K11" t="n">
-        <v>5.288294837886132</v>
+        <v>6.274674442998629</v>
       </c>
       <c r="L11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M11" t="n">
-        <v>81.25</v>
+        <v>80</v>
       </c>
       <c r="N11" t="n">
-        <v>14.41611962980027</v>
+        <v>13.5681865072563</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1751,19 +1751,19 @@
         <v>61.76470588235294</v>
       </c>
       <c r="X11" t="n">
-        <v>10.6953969978917</v>
+        <v>10.70591528549823</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.884667571234724</v>
+        <v>4.002713704206251</v>
       </c>
       <c r="Z11" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="AA11" t="n">
-        <v>54.28571428571428</v>
+        <v>45</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.66948699666083</v>
+        <v>11.50303049746318</v>
       </c>
       <c r="AC11" t="n">
         <v>3</v>
@@ -1803,7 +1803,7 @@
         <v>46241</v>
       </c>
       <c r="C12" t="n">
-        <v>6.48346899250209</v>
+        <v>6.468359704626876</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>20.08266526523165</v>
       </c>
       <c r="K12" t="n">
-        <v>12.87528975850236</v>
+        <v>12.61224149700353</v>
       </c>
       <c r="L12" t="n">
         <v>3</v>
@@ -1870,19 +1870,19 @@
         <v>70.58823529411765</v>
       </c>
       <c r="X12" t="n">
-        <v>18.80648930118842</v>
+        <v>18.81777830559044</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.992319508448539</v>
+        <v>5.222734254992334</v>
       </c>
       <c r="Z12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA12" t="n">
-        <v>50</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB12" t="n">
-        <v>12.0508960571445</v>
+        <v>11.651820968583</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
@@ -1922,7 +1922,7 @@
         <v>46241</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2779977375320148</v>
+        <v>0.2771854685303871</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,10 +1947,10 @@
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>39.9577447695258</v>
+        <v>39.9520395484761</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6833724332065527</v>
+        <v>0.379652161702948</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
@@ -1961,7 +1961,7 @@
         <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>4.287329141320839</v>
+        <v>4.602872931711377</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -2015,7 +2015,7 @@
         <v>46241</v>
       </c>
       <c r="C14" t="n">
-        <v>8.061095643062421</v>
+        <v>8.088070522073963</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,16 +2075,16 @@
         <v>14.33662537827827</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.839602515908084</v>
+        <v>6.527859477235265</v>
       </c>
       <c r="Z14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA14" t="n">
-        <v>34.61538461538461</v>
+        <v>37.03703703703704</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.58494518108551</v>
+        <v>11.18997592652526</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2124,7 +2124,7 @@
         <v>46241</v>
       </c>
       <c r="C15" t="n">
-        <v>11.90819850522615</v>
+        <v>11.99319854472147</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %82.61: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2156,16 +2156,16 @@
         <v>14.74031958141837</v>
       </c>
       <c r="K15" t="n">
-        <v>12.12212098257035</v>
+        <v>12.92244226606549</v>
       </c>
       <c r="L15" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M15" t="n">
-        <v>82.60869565217391</v>
+        <v>75</v>
       </c>
       <c r="N15" t="n">
-        <v>17.42902534732851</v>
+        <v>20.15946868531259</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
@@ -2198,22 +2198,22 @@
         <v>17.12346148492163</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.270144033435297</v>
+        <v>3.586829799593116</v>
       </c>
       <c r="Z15" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AA15" t="n">
-        <v>35.55555555555556</v>
+        <v>32.6530612244898</v>
       </c>
       <c r="AB15" t="n">
-        <v>15.29745172712114</v>
+        <v>14.82982024306668</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>5.985443003869085</v>
+        <v>6.651757417660164</v>
       </c>
       <c r="AE15" t="n">
         <v>31</v>
@@ -2247,7 +2247,7 @@
         <v>46241</v>
       </c>
       <c r="C16" t="n">
-        <v>36.77285242634976</v>
+        <v>37.04891928063433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2275,22 +2275,22 @@
         <v>17.40096492560246</v>
       </c>
       <c r="K16" t="n">
-        <v>5.992838099349651</v>
+        <v>6.78856395307248</v>
       </c>
       <c r="L16" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="M16" t="n">
-        <v>57.89473684210526</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N16" t="n">
-        <v>16.72563066637132</v>
+        <v>15.92006307930395</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>3.780596852114049</v>
+        <v>3.007284608058569</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2356,7 +2356,7 @@
         <v>46241</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7560029126983925</v>
+        <v>0.7523006584219034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %79.07: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.56: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2388,22 +2388,22 @@
         <v>14.16674936134154</v>
       </c>
       <c r="K17" t="n">
-        <v>7.370968228476449</v>
+        <v>6.845157256563916</v>
       </c>
       <c r="L17" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M17" t="n">
-        <v>79.06976744186046</v>
+        <v>75.55555555555556</v>
       </c>
       <c r="N17" t="n">
-        <v>15.65469996868638</v>
+        <v>16.1993530881949</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5858490259536664</v>
+        <v>1.080856421656073</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2430,22 +2430,22 @@
         <v>15.7396793517258</v>
       </c>
       <c r="Y17" t="n">
-        <v>7.230632718289587</v>
+        <v>7.684937564179672</v>
       </c>
       <c r="Z17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AA17" t="n">
-        <v>51.61290322580645</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="AB17" t="n">
-        <v>11.4183129698492</v>
+        <v>11.01046228963967</v>
       </c>
       <c r="AC17" t="n">
         <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.98521738679185</v>
+        <v>2.507784076330788</v>
       </c>
       <c r="AE17" t="n">
         <v>35</v>
@@ -2479,7 +2479,7 @@
         <v>46241</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1035677840322343</v>
+        <v>0.104416309427582</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2507,22 +2507,22 @@
         <v>24.37863714425642</v>
       </c>
       <c r="K18" t="n">
-        <v>3.642133883540222</v>
+        <v>4.491268423300521</v>
       </c>
       <c r="L18" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M18" t="n">
-        <v>52.63157894736842</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N18" t="n">
-        <v>16.9566017494627</v>
+        <v>18.22091744975853</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>6.134441542475333</v>
+        <v>5.271953972635579</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2588,7 +2588,7 @@
         <v>46241</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0251581669043685</v>
+        <v>0.02537022852944217</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,22 +2616,22 @@
         <v>18.34152851742537</v>
       </c>
       <c r="K19" t="n">
-        <v>1.85808522115456</v>
+        <v>2.716660933804738</v>
       </c>
       <c r="L19" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="M19" t="n">
-        <v>60</v>
+        <v>58.62068965517241</v>
       </c>
       <c r="N19" t="n">
-        <v>23.05253883909682</v>
+        <v>23.82410481760151</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>7.99339076634682</v>
+        <v>7.090708556900016</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2697,7 +2697,7 @@
         <v>46241</v>
       </c>
       <c r="C20" t="n">
-        <v>1.855414731888229</v>
+        <v>1.866074598741627</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2757,16 +2757,16 @@
         <v>16.65604614151002</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.340846182942816</v>
+        <v>5.802748639502653</v>
       </c>
       <c r="Z20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="n">
-        <v>57.89473684210526</v>
+        <v>55</v>
       </c>
       <c r="AB20" t="n">
-        <v>11.37893977148107</v>
+        <v>11.83530055065416</v>
       </c>
       <c r="AC20" t="n">
         <v>4</v>
@@ -2806,7 +2806,7 @@
         <v>46241</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9363030694668487</v>
+        <v>0.939746774574344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2834,22 +2834,22 @@
         <v>13.9566823466854</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3113724048522171</v>
+        <v>0.6803157488990852</v>
       </c>
       <c r="L21" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M21" t="n">
-        <v>59.64912280701754</v>
+        <v>60.3448275862069</v>
       </c>
       <c r="N21" t="n">
-        <v>17.7688681608701</v>
+        <v>17.56054848099487</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>7.664761642495366</v>
+        <v>7.270223773787632</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2915,7 +2915,7 @@
         <v>46241</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3339746582390741</v>
+        <v>0.3335870402929</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2947,16 +2947,16 @@
         <v>20.35908649698318</v>
       </c>
       <c r="K22" t="n">
-        <v>12.59075464102795</v>
+        <v>12.4600794655453</v>
       </c>
       <c r="L22" t="n">
         <v>5</v>
       </c>
       <c r="M22" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N22" t="n">
-        <v>23.34097628590485</v>
+        <v>17.21117446734009</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
@@ -2986,16 +2986,16 @@
         <v>73.68421052631579</v>
       </c>
       <c r="X22" t="n">
-        <v>19.30519816570662</v>
+        <v>19.31653455747442</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.627955552575992</v>
+        <v>5.746441695912974</v>
       </c>
       <c r="Z22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA22" t="n">
-        <v>50</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="AB22" t="n">
         <v>12.75464260894753</v>
@@ -3004,7 +3004,7 @@
         <v>6</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.3942316282352976</v>
+        <v>0.2690172218952069</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3030,7 +3030,7 @@
         <v>46241</v>
       </c>
       <c r="C23" t="n">
-        <v>0.895211417646809</v>
+        <v>0.8848129155630716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3055,25 +3055,25 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>13.06492236410843</v>
+        <v>13.05666178440531</v>
       </c>
       <c r="K23" t="n">
-        <v>1.377022423395391</v>
+        <v>0.1899378728213108</v>
       </c>
       <c r="L23" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M23" t="n">
-        <v>62.16216216216216</v>
+        <v>64.51612903225806</v>
       </c>
       <c r="N23" t="n">
-        <v>17.13245148878242</v>
+        <v>15.08455575055588</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>3.57376601718824</v>
+        <v>4.800943317565953</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3100,17 +3100,13 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>11.86780685126601</v>
+        <v>12.89152345723877</v>
       </c>
       <c r="Z23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>12.69643539804235</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
         <v>6</v>
       </c>
@@ -3149,7 +3145,7 @@
         <v>46241</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1903634533007</v>
+        <v>0.1897525334063584</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3177,22 +3173,22 @@
         <v>22.86774633531589</v>
       </c>
       <c r="K24" t="n">
-        <v>8.759082725256118</v>
+        <v>8.41004993469079</v>
       </c>
       <c r="L24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M24" t="n">
-        <v>57.14285714285715</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N24" t="n">
-        <v>12.34101096402614</v>
+        <v>10.20060895618112</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>1.140978062382758</v>
+        <v>1.466607631180916</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3216,19 +3212,19 @@
         <v>75</v>
       </c>
       <c r="X24" t="n">
-        <v>12.5919983806515</v>
+        <v>12.60269688350961</v>
       </c>
       <c r="Y24" t="n">
-        <v>3.404252265278274</v>
+        <v>3.723398342009709</v>
       </c>
       <c r="Z24" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AA24" t="n">
-        <v>51.61290322580645</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="AB24" t="n">
-        <v>14.81671937360062</v>
+        <v>14.95270948470093</v>
       </c>
       <c r="AC24" t="n">
         <v>2</v>
@@ -3268,7 +3264,7 @@
         <v>46241</v>
       </c>
       <c r="C25" t="n">
-        <v>4.044175033482595</v>
+        <v>4.073913485696917</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3367,7 +3363,7 @@
         <v>46241</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4293660209670075</v>
+        <v>0.4298261716202625</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3466,7 +3462,7 @@
         <v>46241</v>
       </c>
       <c r="C27" t="n">
-        <v>36.77285242634976</v>
+        <v>37.17472206257197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3494,7 +3490,7 @@
         <v>61.00029220182797</v>
       </c>
       <c r="K27" t="n">
-        <v>11.55729387103921</v>
+        <v>12.7764402289585</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3519,25 +3515,25 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>14.99178296399024</v>
+        <v>15.00270949461759</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.986725663716816</v>
+        <v>1.935840707964609</v>
       </c>
       <c r="Z27" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AA27" t="n">
-        <v>37.5</v>
+        <v>20</v>
       </c>
       <c r="AB27" t="n">
-        <v>24.39428197679019</v>
+        <v>26.05926118730342</v>
       </c>
       <c r="AC27" t="n">
         <v>5</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.075256556442417</v>
+        <v>3.124647490129717</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3561,7 +3557,7 @@
         <v>46241</v>
       </c>
       <c r="C28" t="n">
-        <v>1.439256770428378</v>
+        <v>1.457215557444304</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3589,16 +3585,16 @@
         <v>18.25342733104113</v>
       </c>
       <c r="K28" t="n">
-        <v>3.220937647789546</v>
+        <v>4.508909935214755</v>
       </c>
       <c r="L28" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M28" t="n">
-        <v>47.5</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="N28" t="n">
-        <v>17.42087226656076</v>
+        <v>15.88163857029287</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
@@ -3670,7 +3666,7 @@
         <v>46241</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4140614797151698</v>
+        <v>0.4145201761293965</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3694,7 @@
         <v>20.65475273479386</v>
       </c>
       <c r="K29" t="n">
-        <v>13.91647127555789</v>
+        <v>14.04266769675455</v>
       </c>
       <c r="L29" t="n">
         <v>3</v>
@@ -3740,7 +3736,7 @@
         <v>55.05052857749912</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.612694190611059</v>
+        <v>9.51256332817273</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
@@ -3751,7 +3747,7 @@
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.4284958002904737</v>
+        <v>0.5386788373673013</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3785,7 +3781,7 @@
         <v>46241</v>
       </c>
       <c r="C30" t="n">
-        <v>0.371502234675969</v>
+        <v>0.3761503291061161</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3813,22 +3809,22 @@
         <v>21.6314445059014</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4947424780420651</v>
+        <v>1.752094410739513</v>
       </c>
       <c r="L30" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M30" t="n">
-        <v>50</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N30" t="n">
-        <v>14.79227902534712</v>
+        <v>13.60925753485135</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>4.483077831601312</v>
+        <v>3.191979101825426</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3894,7 +3890,7 @@
         <v>46241</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1756878605346777</v>
+        <v>0.1750755461640555</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3922,7 +3918,7 @@
         <v>31.09418993049242</v>
       </c>
       <c r="K31" t="n">
-        <v>0.8945065024395848</v>
+        <v>0.5428649259512142</v>
       </c>
       <c r="L31" t="n">
         <v>3</v>
@@ -3931,13 +3927,13 @@
         <v>66.66666666666667</v>
       </c>
       <c r="N31" t="n">
-        <v>7.249414780450302</v>
+        <v>8.284865476453684</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>9.024766375501581</v>
+        <v>9.406072803887056</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -4003,7 +3999,7 @@
         <v>46241</v>
       </c>
       <c r="C32" t="n">
-        <v>2.362771012709475</v>
+        <v>2.373479088607019</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4063,22 +4059,22 @@
         <v>15.25475988862757</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.726232055482969</v>
+        <v>2.285387435167618</v>
       </c>
       <c r="Z32" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA32" t="n">
-        <v>38.09523809523809</v>
+        <v>31.81818181818182</v>
       </c>
       <c r="AB32" t="n">
-        <v>12.34316210709314</v>
+        <v>12.64953902913536</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>5.421572594499557</v>
+        <v>5.848268150314572</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4112,7 +4108,7 @@
         <v>46241</v>
       </c>
       <c r="C33" t="n">
-        <v>1.806146689163339</v>
+        <v>1.810511671306128</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4140,22 +4136,22 @@
         <v>12.57251846431013</v>
       </c>
       <c r="K33" t="n">
-        <v>1.232444038421199</v>
+        <v>1.477096265812161</v>
       </c>
       <c r="L33" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M33" t="n">
-        <v>61.81818181818182</v>
+        <v>60.71428571428572</v>
       </c>
       <c r="N33" t="n">
-        <v>12.12906634908658</v>
+        <v>12.30850360623689</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>2.733862634521023</v>
+        <v>2.486180455518028</v>
       </c>
       <c r="Q33" t="n">
         <v>39</v>
@@ -4221,7 +4217,7 @@
         <v>46241</v>
       </c>
       <c r="C34" t="n">
-        <v>0.804642027064</v>
+        <v>0.8110086073911154</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4246,25 +4242,25 @@
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>15.89868933724038</v>
+        <v>15.89069802235623</v>
       </c>
       <c r="K34" t="n">
-        <v>0.1565798029368182</v>
+        <v>0.9394588280592808</v>
       </c>
       <c r="L34" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>64.44444444444444</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="N34" t="n">
-        <v>12.99617883422956</v>
+        <v>13.83623491196254</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>3.837411585564632</v>
+        <v>3.032056251811355</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4330,7 +4326,7 @@
         <v>46241</v>
       </c>
       <c r="C35" t="n">
-        <v>1.88895892095305</v>
+        <v>1.922685786663817</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4347,11 +4343,7 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>5</v>
       </c>
@@ -4362,16 +4354,16 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>6.490532791870485</v>
+        <v>8.391893302731845</v>
       </c>
       <c r="L35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M35" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="N35" t="n">
-        <v>16.98741539906919</v>
+        <v>13.94206337498728</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4404,7 +4396,7 @@
         <v>42.52272358489104</v>
       </c>
       <c r="Y35" t="n">
-        <v>17.90559975691569</v>
+        <v>16.43982578910094</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -4449,7 +4441,7 @@
         <v>46241</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08176404112887647</v>
+        <v>0.08323950801108425</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4477,16 +4469,16 @@
         <v>18.45194908889744</v>
       </c>
       <c r="K36" t="n">
-        <v>2.194024721022014</v>
+        <v>4.038159342471626</v>
       </c>
       <c r="L36" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="M36" t="n">
-        <v>55</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N36" t="n">
-        <v>11.59571865267865</v>
+        <v>13.16774825086663</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4558,7 +4550,7 @@
         <v>46241</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06415332167517625</v>
+        <v>0.06415941753016746</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4586,22 +4578,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>4.430776236457135</v>
+        <v>4.440699259177294</v>
       </c>
       <c r="L37" t="n">
         <v>65</v>
       </c>
       <c r="M37" t="n">
-        <v>56.92307692307692</v>
+        <v>58.46153846153846</v>
       </c>
       <c r="N37" t="n">
-        <v>19.42924632473793</v>
+        <v>19.09008605054506</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>3.417789173051111</v>
+        <v>3.40796333811404</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4667,7 +4659,7 @@
         <v>46241</v>
       </c>
       <c r="C38" t="n">
-        <v>1.617460445242502</v>
+        <v>1.637532846141876</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4695,22 +4687,22 @@
         <v>15.02885014069408</v>
       </c>
       <c r="K38" t="n">
-        <v>2.090496366715611</v>
+        <v>3.357421550027628</v>
       </c>
       <c r="L38" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M38" t="n">
-        <v>63.1578947368421</v>
+        <v>60</v>
       </c>
       <c r="N38" t="n">
-        <v>13.2195873040694</v>
+        <v>12.68953661268957</v>
       </c>
       <c r="O38" t="n">
         <v>6</v>
       </c>
       <c r="P38" t="n">
-        <v>3.829449138185415</v>
+        <v>2.556737978117329</v>
       </c>
       <c r="Q38" t="n">
         <v>34</v>
@@ -4776,7 +4768,7 @@
         <v>46241</v>
       </c>
       <c r="C39" t="n">
-        <v>2.654186465743111</v>
+        <v>2.662825551013333</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4804,16 +4796,16 @@
         <v>16.13238434452433</v>
       </c>
       <c r="K39" t="n">
-        <v>5.064644131089957</v>
+        <v>5.406618001897079</v>
       </c>
       <c r="L39" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M39" t="n">
-        <v>61.76470588235294</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N39" t="n">
-        <v>14.35146834624859</v>
+        <v>13.03319696046832</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4846,22 +4838,22 @@
         <v>10.2437411865161</v>
       </c>
       <c r="Y39" t="n">
-        <v>4.697860395234487</v>
+        <v>4.38766240383236</v>
       </c>
       <c r="Z39" t="n">
         <v>32</v>
       </c>
       <c r="AA39" t="n">
-        <v>46.875</v>
+        <v>43.75</v>
       </c>
       <c r="AB39" t="n">
-        <v>10.46535753231656</v>
+        <v>11.71889448169242</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.366327776234322</v>
+        <v>1.686327974719726</v>
       </c>
       <c r="AE39" t="n">
         <v>42</v>
@@ -4895,7 +4887,7 @@
         <v>46241</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2039907851726745</v>
+        <v>0.2044295206486614</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4952,16 +4944,16 @@
         <v>76.47058823529412</v>
       </c>
       <c r="X40" t="n">
-        <v>18.04834458245343</v>
+        <v>18.05956154786905</v>
       </c>
       <c r="Y40" t="n">
-        <v>5.625614513796496</v>
+        <v>5.431623639060912</v>
       </c>
       <c r="Z40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA40" t="n">
-        <v>31.25</v>
+        <v>29.41176470588235</v>
       </c>
       <c r="AB40" t="n">
         <v>11.76313020993737</v>
@@ -5004,7 +4996,7 @@
         <v>46241</v>
       </c>
       <c r="C41" t="n">
-        <v>1.695031392478857</v>
+        <v>1.71930468648105</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5015,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -5036,16 +5028,16 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>12.01722988996778</v>
+        <v>13.62134599453981</v>
       </c>
       <c r="L41" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M41" t="n">
-        <v>77.77777777777777</v>
+        <v>100</v>
       </c>
       <c r="N41" t="n">
-        <v>13.38516228592029</v>
+        <v>12.17975430538131</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
@@ -5078,16 +5070,16 @@
         <v>40.81782021738603</v>
       </c>
       <c r="Y41" t="n">
-        <v>13.0732643729205</v>
+        <v>11.82845072528574</v>
       </c>
       <c r="Z41" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA41" t="n">
-        <v>25</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AB41" t="n">
-        <v>22.19906898574699</v>
+        <v>17.85423125778112</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
@@ -5127,7 +5119,7 @@
         <v>46241</v>
       </c>
       <c r="C42" t="n">
-        <v>3.480212943428769</v>
+        <v>3.556025430670057</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5155,7 +5147,7 @@
         <v>19.79504810217467</v>
       </c>
       <c r="K42" t="n">
-        <v>13.22944320286659</v>
+        <v>15.69601805265095</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5188,25 +5180,25 @@
       </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="n">
-        <v>14.97530566614946</v>
+        <v>17.40144278572016</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.518467337979768</v>
+        <v>1.452643760249117</v>
       </c>
       <c r="Z42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA42" t="n">
-        <v>36.36363636363637</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB42" t="n">
-        <v>11.34304697646094</v>
+        <v>11.58190407518745</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>8.612307742130787</v>
+        <v>8.673349104319394</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5238,7 +5230,7 @@
         <v>46241</v>
       </c>
       <c r="C43" t="n">
-        <v>7.117664423458236</v>
+        <v>7.118340744638005</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5298,7 +5290,7 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>8.129981262322294</v>
+        <v>8.121251764026006</v>
       </c>
       <c r="Z43" t="n">
         <v>8</v>
@@ -5347,7 +5339,7 @@
         <v>46241</v>
       </c>
       <c r="C44" t="n">
-        <v>5.063080878542457</v>
+        <v>5.074045538151391</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5366,7 +5358,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.26: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %77.27: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -5379,22 +5371,22 @@
         <v>13.03201987649729</v>
       </c>
       <c r="K44" t="n">
-        <v>3.627826795935096</v>
+        <v>3.852244274953942</v>
       </c>
       <c r="L44" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M44" t="n">
-        <v>78.26086956521739</v>
+        <v>77.27272727272727</v>
       </c>
       <c r="N44" t="n">
-        <v>19.71680359537179</v>
+        <v>20.4740028993714</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>6.149094698871815</v>
+        <v>5.919713885787181</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5421,22 +5413,22 @@
         <v>12.1234692799834</v>
       </c>
       <c r="Y44" t="n">
-        <v>7.577042111347643</v>
+        <v>7.376890010757132</v>
       </c>
       <c r="Z44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA44" t="n">
-        <v>10</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="AB44" t="n">
-        <v>9.691917834769438</v>
+        <v>8.772956734278921</v>
       </c>
       <c r="AC44" t="n">
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.621597429906364</v>
+        <v>2.832025387128023</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5462,7 +5454,7 @@
         <v>46241</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02138444055839208</v>
+        <v>0.02138647251005582</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5561,7 +5553,7 @@
         <v>46241</v>
       </c>
       <c r="C46" t="n">
-        <v>9.339969074081425</v>
+        <v>9.356581906611812</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5589,7 +5581,7 @@
         <v>20.92024905883424</v>
       </c>
       <c r="K46" t="n">
-        <v>13.11261657108458</v>
+        <v>13.31380791778654</v>
       </c>
       <c r="L46" t="n">
         <v>13</v>
@@ -5628,25 +5620,25 @@
         <v>66.26506024096386</v>
       </c>
       <c r="X46" t="n">
-        <v>15.9689957774251</v>
+        <v>15.98001516291092</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.463054187192126</v>
+        <v>2.298850574712641</v>
       </c>
       <c r="Z46" t="n">
         <v>49</v>
       </c>
       <c r="AA46" t="n">
-        <v>34.69387755102041</v>
+        <v>36.73469387755102</v>
       </c>
       <c r="AB46" t="n">
-        <v>12.5177170812975</v>
+        <v>12.07559113826556</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.5505050505050457</v>
+        <v>0.717647058823534</v>
       </c>
       <c r="AE46" t="n">
         <v>37</v>
@@ -5680,7 +5672,7 @@
         <v>46241</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7723556949273964</v>
+        <v>0.7762031742001051</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5708,22 +5700,22 @@
         <v>24.7868707712232</v>
       </c>
       <c r="K47" t="n">
-        <v>3.615059811254939</v>
+        <v>4.131216806772087</v>
       </c>
       <c r="L47" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="M47" t="n">
-        <v>47.05882352941177</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="N47" t="n">
-        <v>14.91896878085846</v>
+        <v>15.79730259714992</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>6.16217391600784</v>
+        <v>5.635949884383029</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5789,7 +5781,7 @@
         <v>46241</v>
       </c>
       <c r="C48" t="n">
-        <v>0.06121820526041591</v>
+        <v>0.06143369331391225</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5817,22 +5809,22 @@
         <v>21.44820004664813</v>
       </c>
       <c r="K48" t="n">
-        <v>4.312934425123616</v>
+        <v>4.680115904850779</v>
       </c>
       <c r="L48" t="n">
         <v>32</v>
       </c>
       <c r="M48" t="n">
-        <v>50</v>
+        <v>53.125</v>
       </c>
       <c r="N48" t="n">
-        <v>16.08201378722749</v>
+        <v>15.39363674846669</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>5.451927516197519</v>
+        <v>5.082038789472443</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5898,7 +5890,7 @@
         <v>46241</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2574518916002879</v>
+        <v>0.2591537236627096</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5926,22 +5918,22 @@
         <v>21.9393534200744</v>
       </c>
       <c r="K49" t="n">
-        <v>1.883601296726356</v>
+        <v>2.557081605004474</v>
       </c>
       <c r="L49" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M49" t="n">
-        <v>52</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="N49" t="n">
-        <v>10.74970651135409</v>
+        <v>9.984806883436532</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>3.058783419126931</v>
+        <v>2.382008493966659</v>
       </c>
       <c r="Q49" t="n">
         <v>53</v>
@@ -6007,7 +5999,7 @@
         <v>46241</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7119760744400307</v>
+        <v>0.7133017832312862</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6032,25 +6024,25 @@
         <v>10</v>
       </c>
       <c r="J50" t="n">
-        <v>10.48618605822325</v>
+        <v>10.47768044674046</v>
       </c>
       <c r="K50" t="n">
-        <v>0.1179272174471446</v>
+        <v>0.2948180878395323</v>
       </c>
       <c r="L50" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M50" t="n">
-        <v>42.5531914893617</v>
+        <v>43.75</v>
       </c>
       <c r="N50" t="n">
-        <v>13.684937882731</v>
+        <v>13.34788312333409</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>3.877500154514135</v>
+        <v>3.694290475620998</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6116,7 +6108,7 @@
         <v>46241</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1893151924066524</v>
+        <v>0.1905912177805908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6135,7 +6127,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -6148,16 +6140,16 @@
         <v>27.11346359280836</v>
       </c>
       <c r="K51" t="n">
-        <v>9.727315262266579</v>
+        <v>10.46690111752133</v>
       </c>
       <c r="L51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M51" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="N51" t="n">
-        <v>22.72871476502574</v>
+        <v>21.23919812340072</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
@@ -6190,13 +6182,17 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>14.05745540126758</v>
+        <v>13.47818404847907</v>
       </c>
       <c r="Z51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA51" t="inlineStr"/>
-      <c r="AB51" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>11.13314894388493</v>
+      </c>
       <c r="AC51" t="n">
         <v>10</v>
       </c>
@@ -6235,7 +6231,7 @@
         <v>46241</v>
       </c>
       <c r="C52" t="n">
-        <v>4.142711438860384</v>
+        <v>4.161975369103518</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6295,22 +6291,22 @@
         <v>12.1710603868542</v>
       </c>
       <c r="Y52" t="n">
-        <v>4.94581592201796</v>
+        <v>4.50380657658791</v>
       </c>
       <c r="Z52" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="AA52" t="n">
-        <v>50</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB52" t="n">
-        <v>13.44360014086126</v>
+        <v>13.28027921400272</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.21309798995949</v>
+        <v>3.661081450556491</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6344,7 +6340,7 @@
         <v>46241</v>
       </c>
       <c r="C53" t="n">
-        <v>1.621653408731865</v>
+        <v>1.635436165189291</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6363,7 +6359,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -6376,22 +6372,22 @@
         <v>28.17598592067425</v>
       </c>
       <c r="K53" t="n">
-        <v>6.912394245029851</v>
+        <v>7.821064053402771</v>
       </c>
       <c r="L53" t="n">
         <v>5</v>
       </c>
       <c r="M53" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N53" t="n">
-        <v>11.18129841148397</v>
+        <v>13.60621978110839</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>1.017286875530532</v>
+        <v>0.1659563909595763</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6449,7 +6445,7 @@
         <v>46241</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08511845988860257</v>
+        <v>0.0851265478531071</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6477,7 +6473,7 @@
         <v>42.39442432818535</v>
       </c>
       <c r="K54" t="n">
-        <v>5.305538201705051</v>
+        <v>5.315544344393941</v>
       </c>
       <c r="L54" t="n">
         <v>4</v>
@@ -6492,7 +6488,7 @@
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>4.457943882593396</v>
+        <v>4.448019221443089</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6519,7 +6515,7 @@
         <v>114.7400208810756</v>
       </c>
       <c r="Y54" t="n">
-        <v>39.33813850460513</v>
+        <v>39.33237440850665</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -6564,7 +6560,7 @@
         <v>46241</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8130280343392041</v>
+        <v>0.8298790565517992</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6589,25 +6585,25 @@
         <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>15.19289137992348</v>
+        <v>15.18483300004738</v>
       </c>
       <c r="K55" t="n">
-        <v>0.2067132259146787</v>
+        <v>2.273904528987925</v>
       </c>
       <c r="L55" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="M55" t="n">
-        <v>68.96551724137932</v>
+        <v>67.74193548387096</v>
       </c>
       <c r="N55" t="n">
-        <v>14.55767284840611</v>
+        <v>14.34384572044462</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>5.781335987963643</v>
+        <v>3.643251412148807</v>
       </c>
       <c r="Q55" t="n">
         <v>44</v>
@@ -6634,16 +6630,16 @@
         <v>25.41488056506582</v>
       </c>
       <c r="Y55" t="n">
-        <v>15.01758386988995</v>
+        <v>13.2562170763668</v>
       </c>
       <c r="Z55" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AA55" t="n">
-        <v>33.33333333333334</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB55" t="n">
-        <v>13.02435706412203</v>
+        <v>11.11232349515831</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6683,7 +6679,7 @@
         <v>46241</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9472049509817939</v>
+        <v>0.9137475778435578</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6711,7 +6707,7 @@
         <v>34.38683570496719</v>
       </c>
       <c r="K56" t="n">
-        <v>20.78896382706115</v>
+        <v>16.52243056036522</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6738,25 +6734,25 @@
         <v>100</v>
       </c>
       <c r="X56" t="n">
-        <v>21.43059934346674</v>
+        <v>21.86994894803782</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.5283968949133966</v>
+        <v>4.387889249016286</v>
       </c>
       <c r="Z56" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AA56" t="n">
-        <v>35.29411764705883</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="AB56" t="n">
-        <v>14.48058828459551</v>
+        <v>14.89161191615037</v>
       </c>
       <c r="AC56" t="n">
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>9.521916616826154</v>
+        <v>5.869665157377534</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6782,7 +6778,7 @@
         <v>46241</v>
       </c>
       <c r="C57" t="n">
-        <v>1.434015485875022</v>
+        <v>1.467699122605774</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6810,10 +6806,10 @@
         <v>32.76213282665623</v>
       </c>
       <c r="K57" t="n">
-        <v>22.79076547858716</v>
+        <v>25.67500179194049</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -6848,16 +6844,16 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>11.59215278504465</v>
+        <v>9.515537965282551</v>
       </c>
       <c r="Z57" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA57" t="n">
-        <v>71.42857142857143</v>
+        <v>70</v>
       </c>
       <c r="AB57" t="n">
-        <v>12.36237164600526</v>
+        <v>13.83153316962987</v>
       </c>
       <c r="AC57" t="n">
         <v>6</v>
@@ -6897,16 +6893,16 @@
         <v>46241</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7715170703205835</v>
+        <v>0.7862673871102362</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6916,7 +6912,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %84.62: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.95: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -6929,22 +6925,22 @@
         <v>16.33691982084211</v>
       </c>
       <c r="K58" t="n">
-        <v>4.008425966052287</v>
+        <v>5.99692018194169</v>
       </c>
       <c r="L58" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M58" t="n">
-        <v>84.61538461538461</v>
+        <v>80.95238095238095</v>
       </c>
       <c r="N58" t="n">
-        <v>20.44222564624019</v>
+        <v>16.16334641984738</v>
       </c>
       <c r="O58" t="n">
         <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>0.9533593309751343</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>24</v>
@@ -6971,10 +6967,10 @@
         <v>41.32985472592288</v>
       </c>
       <c r="Y58" t="n">
-        <v>12.98334719094161</v>
+        <v>11.31971168074414</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA58" t="inlineStr"/>
       <c r="AB58" t="inlineStr"/>
@@ -7016,7 +7012,7 @@
         <v>46241</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8180597027318586</v>
+        <v>0.8206534680499077</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7076,22 +7072,22 @@
         <v>10.2478061424703</v>
       </c>
       <c r="Y59" t="n">
-        <v>7.11265270112702</v>
+        <v>6.818141213634322</v>
       </c>
       <c r="Z59" t="n">
         <v>22</v>
       </c>
       <c r="AA59" t="n">
-        <v>54.54545454545455</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB59" t="n">
-        <v>14.40253231574566</v>
+        <v>15.37190524642973</v>
       </c>
       <c r="AC59" t="n">
         <v>10</v>
       </c>
       <c r="AD59" t="n">
-        <v>3.108439828282195</v>
+        <v>3.414676233987346</v>
       </c>
       <c r="AE59" t="n">
         <v>43</v>
@@ -7125,7 +7121,7 @@
         <v>46241</v>
       </c>
       <c r="C60" t="n">
-        <v>13.56444442408683</v>
+        <v>13.72298679636399</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7153,22 +7149,22 @@
         <v>15.44754852801727</v>
       </c>
       <c r="K60" t="n">
-        <v>6.750698060180182</v>
+        <v>7.998409236809745</v>
       </c>
       <c r="L60" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="M60" t="n">
-        <v>48.48484848484848</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N60" t="n">
-        <v>13.2557668906823</v>
+        <v>12.24867975336606</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>1.170298613987075</v>
+        <v>0.001472950575376331</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7234,7 +7230,7 @@
         <v>46241</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6184715772960765</v>
+        <v>0.6231430987304459</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7262,22 +7258,22 @@
         <v>30.3360843704085</v>
       </c>
       <c r="K61" t="n">
-        <v>0.6457946919001589</v>
+        <v>1.406005838931201</v>
       </c>
       <c r="L61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M61" t="n">
-        <v>62.5</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N61" t="n">
-        <v>12.83082373170765</v>
+        <v>12.22538449547143</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>9.294183961421542</v>
+        <v>8.474837451658557</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7335,7 +7331,7 @@
         <v>46241</v>
       </c>
       <c r="C62" t="n">
-        <v>8.873494748832691</v>
+        <v>8.947722865314489</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7352,7 +7348,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H62" t="n">
         <v>5</v>
       </c>
@@ -7363,16 +7363,16 @@
         <v>10.67683828611802</v>
       </c>
       <c r="K62" t="n">
-        <v>6.641843982704976</v>
+        <v>7.533919026534042</v>
       </c>
       <c r="L62" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M62" t="n">
-        <v>71.875</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="N62" t="n">
-        <v>12.47974734393846</v>
+        <v>12.72275526639178</v>
       </c>
       <c r="O62" t="n">
         <v>6</v>
@@ -7444,7 +7444,7 @@
         <v>46241</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1016809182386038</v>
+        <v>0.1016905799695442</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>29.14654498090023</v>
       </c>
       <c r="K63" t="n">
-        <v>1.89844310060816</v>
+        <v>1.908125500782498</v>
       </c>
       <c r="L63" t="n">
         <v>5</v>
@@ -7487,7 +7487,7 @@
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>3.043772608311168</v>
+        <v>3.033982309088556</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7514,7 +7514,7 @@
         <v>10.24796802016521</v>
       </c>
       <c r="Y63" t="n">
-        <v>7.57340481597798</v>
+        <v>7.564622431732538</v>
       </c>
       <c r="Z63" t="n">
         <v>9</v>
@@ -7529,7 +7529,7 @@
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>2.62542959544344</v>
+        <v>2.63468125769144</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7563,7 +7563,7 @@
         <v>46241</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1563999319107659</v>
+        <v>0.1580921617962796</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7591,22 +7591,22 @@
         <v>20.58679888238519</v>
       </c>
       <c r="K64" t="n">
-        <v>0.6348069420387015</v>
+        <v>1.723664371512457</v>
       </c>
       <c r="L64" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M64" t="n">
-        <v>60.97560975609756</v>
+        <v>54.76190476190476</v>
       </c>
       <c r="N64" t="n">
-        <v>14.36390006558601</v>
+        <v>14.58900884433736</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.337657308246712</v>
+        <v>3.220819510120876</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7672,7 +7672,7 @@
         <v>46241</v>
       </c>
       <c r="C65" t="n">
-        <v>5.718241447712029</v>
+        <v>5.72402657816252</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7697,10 +7697,10 @@
         <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>32.96432732954867</v>
+        <v>32.95795759327989</v>
       </c>
       <c r="K65" t="n">
-        <v>1.01851851851853</v>
+        <v>1.111111111111107</v>
       </c>
       <c r="L65" t="n">
         <v>6</v>
@@ -7715,7 +7715,7 @@
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>8.890925756186974</v>
+        <v>8.791208791208804</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7781,7 +7781,7 @@
         <v>46241</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4310432305565219</v>
+        <v>0.4331809093268633</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>46241</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02788363466246254</v>
+        <v>0.02788628416819493</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>18.49825117353735</v>
       </c>
       <c r="K67" t="n">
-        <v>3.56156629491271</v>
+        <v>3.571406725217985</v>
       </c>
       <c r="L67" t="n">
         <v>2</v>
@@ -7919,7 +7919,7 @@
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>0.4233556142234862</v>
+        <v>0.4138142836266567</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7936,7 +7936,7 @@
         <v>10.87173616493582</v>
       </c>
       <c r="Y67" t="n">
-        <v>6.59335744427082</v>
+        <v>6.584481935826869</v>
       </c>
       <c r="Z67" t="n">
         <v>2</v>
@@ -7971,7 +7971,7 @@
         <v>46241</v>
       </c>
       <c r="C68" t="n">
-        <v>3.746470134795612</v>
+        <v>3.652474038306337</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8028,10 +8028,10 @@
         <v>80</v>
       </c>
       <c r="X68" t="n">
-        <v>127.8488738182379</v>
+        <v>127.8705240408364</v>
       </c>
       <c r="Y68" t="n">
-        <v>8.264890065667775</v>
+        <v>10.57495163114166</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -8076,7 +8076,7 @@
         <v>46241</v>
       </c>
       <c r="C69" t="n">
-        <v>0.407771954184647</v>
+        <v>0.4117944267525849</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8104,16 +8104,16 @@
         <v>29.4573350207784</v>
       </c>
       <c r="K69" t="n">
-        <v>4.306618329452827</v>
+        <v>5.335552532942933</v>
       </c>
       <c r="L69" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M69" t="n">
-        <v>71.42857142857143</v>
+        <v>60</v>
       </c>
       <c r="N69" t="n">
-        <v>15.30141509712112</v>
+        <v>14.20304940810647</v>
       </c>
       <c r="O69" t="n">
         <v>3</v>
@@ -8169,7 +8169,7 @@
         <v>46241</v>
       </c>
       <c r="C70" t="n">
-        <v>0.3857585351602917</v>
+        <v>0.3883112632257219</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8194,25 +8194,25 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>22.00944642482017</v>
+        <v>22.00203575468081</v>
       </c>
       <c r="K70" t="n">
-        <v>0.6564492640617869</v>
+        <v>1.312908976700911</v>
       </c>
       <c r="L70" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M70" t="n">
-        <v>67.85714285714286</v>
+        <v>72.41379310344827</v>
       </c>
       <c r="N70" t="n">
-        <v>13.19062072266356</v>
+        <v>13.42081270102377</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>7.295658439801689</v>
+        <v>6.600433341457945</v>
       </c>
       <c r="Q70" t="n">
         <v>30</v>
@@ -8278,7 +8278,7 @@
         <v>46241</v>
       </c>
       <c r="C71" t="n">
-        <v>3.207666146654227</v>
+        <v>3.218454504571234</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8306,22 +8306,22 @@
         <v>19.51282806733038</v>
       </c>
       <c r="K71" t="n">
-        <v>2.390022472082332</v>
+        <v>2.734391293230187</v>
       </c>
       <c r="L71" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M71" t="n">
-        <v>70</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N71" t="n">
-        <v>13.99961672524713</v>
+        <v>13.8278543896199</v>
       </c>
       <c r="O71" t="n">
         <v>6</v>
       </c>
       <c r="P71" t="n">
-        <v>3.525712213709076</v>
+        <v>3.178690860637823</v>
       </c>
       <c r="Q71" t="n">
         <v>43</v>
@@ -8387,7 +8387,7 @@
         <v>46241</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07799031478290006</v>
+        <v>0.07757838324323316</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8415,16 +8415,16 @@
         <v>20.36571476939619</v>
       </c>
       <c r="K72" t="n">
-        <v>9.035272945018956</v>
+        <v>8.459367231761217</v>
       </c>
       <c r="L72" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M72" t="n">
-        <v>64.28571428571429</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N72" t="n">
-        <v>14.39782702990865</v>
+        <v>14.52327366036347</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
@@ -8457,7 +8457,7 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>13.17053974099621</v>
+        <v>13.62915813935123</v>
       </c>
       <c r="Z72" t="n">
         <v>1</v>
@@ -8502,7 +8502,7 @@
         <v>46241</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07023321091846435</v>
+        <v>0.07023988448513474</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>22.14049070857409</v>
       </c>
       <c r="K73" t="n">
-        <v>2.129419359691354</v>
+        <v>2.139123707252755</v>
       </c>
       <c r="L73" t="n">
         <v>17</v>
@@ -8549,7 +8549,7 @@
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>7.706477418214952</v>
+        <v>7.696244110413364</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8615,7 +8615,7 @@
         <v>46241</v>
       </c>
       <c r="C74" t="n">
-        <v>4.975027361989737</v>
+        <v>4.979693451698163</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8643,22 +8643,22 @@
         <v>18.35970785011217</v>
       </c>
       <c r="K74" t="n">
-        <v>5.257146673947566</v>
+        <v>5.355867596084796</v>
       </c>
       <c r="L74" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M74" t="n">
-        <v>62.06896551724138</v>
+        <v>63.33333333333334</v>
       </c>
       <c r="N74" t="n">
-        <v>20.2220764956805</v>
+        <v>19.98684471942212</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>2.605859471517791</v>
+        <v>2.509715371575072</v>
       </c>
       <c r="Q74" t="n">
         <v>35</v>
@@ -8685,7 +8685,7 @@
         <v>95.98093909010421</v>
       </c>
       <c r="Y74" t="n">
-        <v>14.06775794675327</v>
+        <v>13.98716189750737</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
@@ -8730,7 +8730,7 @@
         <v>46241</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1280969972095028</v>
+        <v>0.1278994928732187</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8755,25 +8755,25 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>21.58456588507395</v>
+        <v>21.57711484274354</v>
       </c>
       <c r="K75" t="n">
-        <v>1.326698461259279</v>
+        <v>1.160857173502472</v>
       </c>
       <c r="L75" t="n">
         <v>14</v>
       </c>
       <c r="M75" t="n">
-        <v>71.42857142857143</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N75" t="n">
-        <v>16.73664961466951</v>
+        <v>17.51856000057698</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>4.612112710380556</v>
+        <v>4.783611924321529</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8839,7 +8839,7 @@
         <v>46241</v>
       </c>
       <c r="C76" t="n">
-        <v>1.837594396483478</v>
+        <v>1.846155888884582</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8867,22 +8867,22 @@
         <v>18.36583782901725</v>
       </c>
       <c r="K76" t="n">
-        <v>6.025143657355581</v>
+        <v>6.51912288557126</v>
       </c>
       <c r="L76" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M76" t="n">
-        <v>44</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="N76" t="n">
-        <v>12.61717600445746</v>
+        <v>12.88955665858701</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>3.748975201099536</v>
+        <v>3.267842449442715</v>
       </c>
       <c r="Q76" t="n">
         <v>40</v>
@@ -8948,7 +8948,7 @@
         <v>46241</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5312566054729937</v>
+        <v>0.5338231187322832</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8976,16 +8976,16 @@
         <v>20.36657537342047</v>
       </c>
       <c r="K77" t="n">
-        <v>9.41550463132803</v>
+        <v>9.9440935288875</v>
       </c>
       <c r="L77" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M77" t="n">
-        <v>45.45454545454545</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="N77" t="n">
-        <v>14.59152648540055</v>
+        <v>15.91559869114716</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -9015,25 +9015,25 @@
         <v>61.8421052631579</v>
       </c>
       <c r="X77" t="n">
-        <v>14.76969562478312</v>
+        <v>14.78060105264944</v>
       </c>
       <c r="Y77" t="n">
-        <v>4.6651609245001</v>
+        <v>4.213697680101425</v>
       </c>
       <c r="Z77" t="n">
         <v>54</v>
       </c>
       <c r="AA77" t="n">
-        <v>51.85185185185185</v>
+        <v>48.14814814814815</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.57223803247395</v>
+        <v>11.9142865272163</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>5.595896659850652</v>
+        <v>6.040845277202578</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9067,7 +9067,7 @@
         <v>46241</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05388040374094596</v>
+        <v>0.05409519455581383</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9095,16 +9095,16 @@
         <v>12.76206508896208</v>
       </c>
       <c r="K78" t="n">
-        <v>6.346191706671855</v>
+        <v>6.770134060270294</v>
       </c>
       <c r="L78" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M78" t="n">
-        <v>60.78431372549019</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N78" t="n">
-        <v>17.62088487466303</v>
+        <v>17.42970274188952</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
@@ -9137,22 +9137,22 @@
         <v>23.16536029857119</v>
       </c>
       <c r="Y78" t="n">
-        <v>7.225778498566005</v>
+        <v>6.855939944073485</v>
       </c>
       <c r="Z78" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA78" t="n">
-        <v>50</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="AB78" t="n">
-        <v>13.44443485632872</v>
+        <v>13.62107476173054</v>
       </c>
       <c r="AC78" t="n">
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>2.990293485126272</v>
+        <v>3.375481006559866</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9186,7 +9186,7 @@
         <v>46241</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8629250857198566</v>
+        <v>0.866781170695394</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9211,25 +9211,25 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>11.94318589124698</v>
+        <v>11.93481872403289</v>
       </c>
       <c r="K79" t="n">
-        <v>0.04861560597120285</v>
+        <v>0.4861467257304186</v>
       </c>
       <c r="L79" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="M79" t="n">
-        <v>58.49056603773585</v>
+        <v>59.32203389830509</v>
       </c>
       <c r="N79" t="n">
-        <v>10.926012998354</v>
+        <v>11.10797001425765</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>4.948978418181427</v>
+        <v>4.492015488055112</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9295,7 +9295,7 @@
         <v>46241</v>
       </c>
       <c r="C80" t="n">
-        <v>0.127468038660421</v>
+        <v>0.1276898268117719</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>4.361878006034603</v>
+        <v>4.543462568233236</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9334,7 +9334,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>5.402472724417051</v>
+        <v>5.219396122646502</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9361,22 +9361,22 @@
         <v>11.74527658842108</v>
       </c>
       <c r="Y80" t="n">
-        <v>6.607347359818105</v>
+        <v>6.444848713125917</v>
       </c>
       <c r="Z80" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AA80" t="n">
-        <v>38.70967741935484</v>
+        <v>37.5</v>
       </c>
       <c r="AB80" t="n">
-        <v>11.51059405130598</v>
+        <v>11.34301121239574</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.491180088381716</v>
+        <v>1.662282905305146</v>
       </c>
       <c r="AE80" t="n">
         <v>26</v>
@@ -9410,11 +9410,11 @@
         <v>46241</v>
       </c>
       <c r="C81" t="n">
-        <v>1.073415092460933</v>
+        <v>1.084000653630998</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9438,22 +9438,22 @@
         <v>12.04277302023445</v>
       </c>
       <c r="K81" t="n">
-        <v>2.489809749598293</v>
+        <v>3.500520478404456</v>
       </c>
       <c r="L81" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="M81" t="n">
-        <v>51.02040816326531</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="N81" t="n">
-        <v>12.98769363041235</v>
+        <v>13.80916877265594</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>7.327743381269336</v>
+        <v>6.279658780026787</v>
       </c>
       <c r="Q81" t="n">
         <v>31</v>
@@ -9480,22 +9480,22 @@
         <v>27.31228182970742</v>
       </c>
       <c r="Y81" t="n">
-        <v>9.852805407415953</v>
+        <v>8.963812277571071</v>
       </c>
       <c r="Z81" t="n">
         <v>9</v>
       </c>
       <c r="AA81" t="n">
-        <v>55.55555555555556</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB81" t="n">
-        <v>9.529724010146259</v>
+        <v>11.50734464839207</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.1632824995267845</v>
+        <v>1.138215195904602</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9529,7 +9529,7 @@
         <v>46241</v>
       </c>
       <c r="C82" t="n">
-        <v>5.4561772200442</v>
+        <v>5.524838840094593</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9586,10 +9586,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="X82" t="n">
-        <v>20.59357073426573</v>
+        <v>21.6427401266019</v>
       </c>
       <c r="Y82" t="n">
-        <v>0.4780114722753304</v>
+        <v>0.09478672985782088</v>
       </c>
       <c r="Z82" t="n">
         <v>9</v>
@@ -9598,13 +9598,13 @@
         <v>55.55555555555556</v>
       </c>
       <c r="AB82" t="n">
-        <v>11.42912722426582</v>
+        <v>11.37010739086874</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>3.538904899135453</v>
+        <v>3.908918406072104</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9638,7 +9638,7 @@
         <v>46241</v>
       </c>
       <c r="C83" t="n">
-        <v>5.770654293245594</v>
+        <v>5.776444403969869</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>12.767909949277</v>
       </c>
       <c r="K83" t="n">
-        <v>6.621280387559292</v>
+        <v>6.72826115397438</v>
       </c>
       <c r="L83" t="n">
         <v>47</v>
@@ -9675,13 +9675,13 @@
         <v>51.06382978723404</v>
       </c>
       <c r="N83" t="n">
-        <v>12.9489451409831</v>
+        <v>12.86430364214105</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>3.168897991244668</v>
+        <v>3.06548500898518</v>
       </c>
       <c r="Q83" t="n">
         <v>43</v>
@@ -9708,22 +9708,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>4.078003353182702</v>
+        <v>3.981757944385877</v>
       </c>
       <c r="Z83" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA83" t="n">
-        <v>48</v>
+        <v>46.93877551020408</v>
       </c>
       <c r="AB83" t="n">
-        <v>12.32759992881112</v>
+        <v>12.51277349367968</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>2.00370792310971</v>
+        <v>2.101936061738308</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9757,16 +9757,16 @@
         <v>46241</v>
       </c>
       <c r="C84" t="n">
-        <v>2.188760461558369</v>
+        <v>2.203645364861246</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -9785,22 +9785,22 @@
         <v>13.05747170375323</v>
       </c>
       <c r="K84" t="n">
-        <v>4.781548051744533</v>
+        <v>5.494126352599582</v>
       </c>
       <c r="L84" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M84" t="n">
-        <v>54</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N84" t="n">
-        <v>10.93702068392672</v>
+        <v>10.49837034120071</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>0.2084832227784883</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9866,7 +9866,7 @@
         <v>46241</v>
       </c>
       <c r="C85" t="n">
-        <v>6.410091008755098</v>
+        <v>6.421183661400263</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9891,10 +9891,10 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>16.27089778037133</v>
+        <v>16.26294183277037</v>
       </c>
       <c r="K85" t="n">
-        <v>0.8244023083264773</v>
+        <v>0.9892827699917506</v>
       </c>
       <c r="L85" t="n">
         <v>49</v>
@@ -9903,13 +9903,13 @@
         <v>61.22448979591837</v>
       </c>
       <c r="N85" t="n">
-        <v>15.26658355411092</v>
+        <v>15.21855013264566</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>7.116925592804568</v>
+        <v>6.942040816326545</v>
       </c>
       <c r="Q85" t="n">
         <v>34</v>
@@ -9975,7 +9975,7 @@
         <v>46241</v>
       </c>
       <c r="C86" t="n">
-        <v>4.360748748392675</v>
+        <v>4.382130237494383</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
         <v>69.23076923076923</v>
       </c>
       <c r="X86" t="n">
-        <v>72.05695078989642</v>
+        <v>72.0732996584329</v>
       </c>
       <c r="Y86" t="n">
-        <v>0.7633616667151233</v>
+        <v>0.2862624439589623</v>
       </c>
       <c r="Z86" t="n">
         <v>2</v>
@@ -10046,7 +10046,7 @@
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>5.276920320192335</v>
+        <v>5.730140797129191</v>
       </c>
       <c r="AE86" t="n">
         <v>51</v>
@@ -10080,7 +10080,7 @@
         <v>46241</v>
       </c>
       <c r="C87" t="n">
-        <v>5.450935935490843</v>
+        <v>5.514355274933123</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10105,25 +10105,25 @@
         <v>10</v>
       </c>
       <c r="J87" t="n">
-        <v>25.69321822185289</v>
+        <v>25.68615758407521</v>
       </c>
       <c r="K87" t="n">
-        <v>1.167315175097272</v>
+        <v>2.334630350194544</v>
       </c>
       <c r="L87" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M87" t="n">
-        <v>55.55555555555556</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N87" t="n">
-        <v>13.89809848647828</v>
+        <v>12.2966575427839</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>3.788461538461552</v>
+        <v>2.604562737642602</v>
       </c>
       <c r="Q87" t="n">
         <v>47</v>
@@ -10189,7 +10189,7 @@
         <v>46241</v>
       </c>
       <c r="C88" t="n">
-        <v>1.082849420800131</v>
+        <v>1.093435878421011</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>21.3133528544164</v>
+        <v>22.49937063691769</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -10252,25 +10252,25 @@
         <v>68.35443037974683</v>
       </c>
       <c r="X88" t="n">
-        <v>23.42722965068291</v>
+        <v>23.43895771829143</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.712650281667261</v>
+        <v>0.7611754819884631</v>
       </c>
       <c r="Z88" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA88" t="n">
-        <v>52.38095238095238</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="AB88" t="n">
-        <v>14.00463844929242</v>
+        <v>13.93247104962249</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>4.362056491114297</v>
+        <v>5.279007025179661</v>
       </c>
       <c r="AE88" t="n">
         <v>31</v>
@@ -10304,7 +10304,7 @@
         <v>46241</v>
       </c>
       <c r="C89" t="n">
-        <v>2.169891805089624</v>
+        <v>2.178484872633137</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>17.86495387474723</v>
+        <v>18.33171517007224</v>
       </c>
       <c r="L89" t="n">
         <v>6</v>
@@ -10378,22 +10378,22 @@
         <v>28.7873334490923</v>
       </c>
       <c r="Y89" t="n">
-        <v>5.37112005497179</v>
+        <v>4.996376782045764</v>
       </c>
       <c r="Z89" t="n">
         <v>20</v>
       </c>
       <c r="AA89" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AB89" t="n">
-        <v>13.5371704471235</v>
+        <v>12.07316893631934</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>4.891614428615465</v>
+        <v>5.266770938277887</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10427,7 +10427,7 @@
         <v>46241</v>
       </c>
       <c r="C90" t="n">
-        <v>2.924636780772972</v>
+        <v>2.924914680050079</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>15.28990999913931</v>
+        <v>15.30086485782711</v>
       </c>
       <c r="L90" t="n">
         <v>9</v>
@@ -10497,7 +10497,7 @@
         <v>33.24184775233741</v>
       </c>
       <c r="Y90" t="n">
-        <v>3.832899904116227</v>
+        <v>3.823762096722905</v>
       </c>
       <c r="Z90" t="n">
         <v>21</v>
@@ -10546,7 +10546,7 @@
         <v>46241</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2333419906216001</v>
+        <v>0.2331544868847044</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10574,22 +10574,22 @@
         <v>14.07074278425192</v>
       </c>
       <c r="K91" t="n">
-        <v>2.91616302288864</v>
+        <v>2.833463954871096</v>
       </c>
       <c r="L91" t="n">
         <v>56</v>
       </c>
       <c r="M91" t="n">
-        <v>62.5</v>
+        <v>58.92857142857143</v>
       </c>
       <c r="N91" t="n">
-        <v>13.96131255902363</v>
+        <v>14.44970221801777</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>0.08146142903979747</v>
+        <v>0.1619473260202398</v>
       </c>
       <c r="Q91" t="n">
         <v>47</v>
@@ -10655,16 +10655,16 @@
         <v>46241</v>
       </c>
       <c r="C92" t="n">
-        <v>1.13002098178034</v>
+        <v>1.14270860260021</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -10683,22 +10683,22 @@
         <v>22.28274626067631</v>
       </c>
       <c r="K92" t="n">
-        <v>7.247911024424702</v>
+        <v>8.452066390334135</v>
       </c>
       <c r="L92" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M92" t="n">
-        <v>66.66666666666667</v>
+        <v>50</v>
       </c>
       <c r="N92" t="n">
-        <v>13.41652570645844</v>
+        <v>14.60018434921859</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>0.7012621209974146</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
         <v>56</v>
@@ -10764,7 +10764,7 @@
         <v>46241</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04234957877181841</v>
+        <v>0.04214393173943735</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10792,22 +10792,22 @@
         <v>17.21421071359344</v>
       </c>
       <c r="K93" t="n">
-        <v>2.706584358573294</v>
+        <v>2.207847301632593</v>
       </c>
       <c r="L93" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M93" t="n">
-        <v>55.31914893617022</v>
+        <v>56.86274509803921</v>
       </c>
       <c r="N93" t="n">
-        <v>18.15875267269455</v>
+        <v>17.01166850852463</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>3.20662561411702</v>
+        <v>3.710236345332785</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10873,7 +10873,7 @@
         <v>46241</v>
       </c>
       <c r="C94" t="n">
-        <v>6.708844228296423</v>
+        <v>6.782866659470971</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10930,25 +10930,25 @@
         <v>70.90909090909091</v>
       </c>
       <c r="X94" t="n">
-        <v>49.31826834924253</v>
+        <v>49.33245658591723</v>
       </c>
       <c r="Y94" t="n">
-        <v>3.614457831325302</v>
+        <v>2.560240963855409</v>
       </c>
       <c r="Z94" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA94" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="AB94" t="n">
-        <v>8.62290485169116</v>
+        <v>11.50265433776413</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>2.475000000000005</v>
+        <v>3.530139103554886</v>
       </c>
       <c r="AE94" t="n">
         <v>37</v>
@@ -10982,7 +10982,7 @@
         <v>46241</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1379506077671341</v>
+        <v>0.1383830580346886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11007,10 +11007,10 @@
         <v>10</v>
       </c>
       <c r="J95" t="n">
-        <v>23.89530047187822</v>
+        <v>23.88806899577756</v>
       </c>
       <c r="K95" t="n">
-        <v>0.1522031924087397</v>
+        <v>0.456616883162142</v>
       </c>
       <c r="L95" t="n">
         <v>20</v>
@@ -11025,7 +11025,7 @@
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>5.83890980047308</v>
+        <v>5.518186147245219</v>
       </c>
       <c r="Q95" t="n">
         <v>23</v>
@@ -11091,7 +11091,7 @@
         <v>46241</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1310321138339145</v>
+        <v>0.1318832488926051</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11119,22 +11119,22 @@
         <v>12.85874206974231</v>
       </c>
       <c r="K96" t="n">
-        <v>1.348968875747425</v>
+        <v>2.007293450146252</v>
       </c>
       <c r="L96" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M96" t="n">
-        <v>57.97101449275362</v>
+        <v>61.42857142857143</v>
       </c>
       <c r="N96" t="n">
-        <v>12.20935754886504</v>
+        <v>12.92956115569449</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>8.535884696428075</v>
+        <v>7.835426546004776</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11161,7 +11161,7 @@
         <v>16.74415231729489</v>
       </c>
       <c r="Y96" t="n">
-        <v>11.68323362232835</v>
+        <v>11.1095613069332</v>
       </c>
       <c r="Z96" t="n">
         <v>15</v>
@@ -11210,16 +11210,16 @@
         <v>46241</v>
       </c>
       <c r="C97" t="n">
-        <v>1.820822221759415</v>
+        <v>1.870267960856468</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -11238,22 +11238,22 @@
         <v>19.26562870655475</v>
       </c>
       <c r="K97" t="n">
-        <v>1.874679750049291</v>
+        <v>4.641160066095407</v>
       </c>
       <c r="L97" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="M97" t="n">
-        <v>54.28571428571428</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="N97" t="n">
-        <v>13.16763130338414</v>
+        <v>12.42621476522564</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>2.086210484455231</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>50</v>
@@ -11319,7 +11319,7 @@
         <v>46241</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6406946126907851</v>
+        <v>0.6445295813047244</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11347,22 +11347,22 @@
         <v>17.47600423199651</v>
       </c>
       <c r="K98" t="n">
-        <v>6.710696276276007</v>
+        <v>7.349428306926975</v>
       </c>
       <c r="L98" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M98" t="n">
-        <v>50</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N98" t="n">
-        <v>15.9466109479899</v>
+        <v>16.71038564991307</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>3.082449874760385</v>
+        <v>2.469106482332339</v>
       </c>
       <c r="Q98" t="n">
         <v>48</v>
@@ -11389,22 +11389,22 @@
         <v>11.17514685780745</v>
       </c>
       <c r="Y98" t="n">
-        <v>4.015691193321702</v>
+        <v>3.441163478536746</v>
       </c>
       <c r="Z98" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AA98" t="n">
-        <v>41.86046511627907</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB98" t="n">
-        <v>11.96674257710748</v>
+        <v>11.75714725586849</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>4.151000154309681</v>
+        <v>4.721304321484765</v>
       </c>
       <c r="AE98" t="n">
         <v>50</v>
@@ -11438,7 +11438,7 @@
         <v>46241</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4821981789088054</v>
+        <v>0.477211890972546</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11466,22 +11466,22 @@
         <v>28.77817890954801</v>
       </c>
       <c r="K99" t="n">
-        <v>3.736814555191126</v>
+        <v>2.664098710156071</v>
       </c>
       <c r="L99" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M99" t="n">
-        <v>66.66666666666667</v>
+        <v>70</v>
       </c>
       <c r="N99" t="n">
-        <v>12.82986200275538</v>
+        <v>13.34926119412081</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>0.2537049609026232</v>
+        <v>1.301235102268294</v>
       </c>
       <c r="Q99" t="n">
         <v>35</v>
@@ -11547,7 +11547,7 @@
         <v>46241</v>
       </c>
       <c r="C100" t="n">
-        <v>322.6811576386785</v>
+        <v>324.7766511811801</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11575,16 +11575,16 @@
         <v>25.15478290083538</v>
       </c>
       <c r="K100" t="n">
-        <v>5.28424451853633</v>
+        <v>5.967961089191509</v>
       </c>
       <c r="L100" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M100" t="n">
-        <v>64.28571428571429</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N100" t="n">
-        <v>9.914713839392286</v>
+        <v>11.35281488036559</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11656,7 +11656,7 @@
         <v>46241</v>
       </c>
       <c r="C101" t="n">
-        <v>324.8397274502345</v>
+        <v>326.9991669954117</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11684,16 +11684,16 @@
         <v>13.42090796247281</v>
       </c>
       <c r="K101" t="n">
-        <v>2.866685889759713</v>
+        <v>3.550513545740297</v>
       </c>
       <c r="L101" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M101" t="n">
-        <v>37.83783783783784</v>
+        <v>34.28571428571428</v>
       </c>
       <c r="N101" t="n">
-        <v>10.22874357253002</v>
+        <v>8.303444048838744</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11765,7 +11765,7 @@
         <v>46241</v>
       </c>
       <c r="C102" t="n">
-        <v>396.5549750938205</v>
+        <v>398.731917351343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>46241</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7098795926953495</v>
+        <v>0.7133017832312862</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11892,22 +11892,22 @@
         <v>26.3831854858525</v>
       </c>
       <c r="K103" t="n">
-        <v>9.178304705461414</v>
+        <v>9.704631937483965</v>
       </c>
       <c r="L103" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M103" t="n">
-        <v>64.28571428571429</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N103" t="n">
-        <v>14.7065956041638</v>
+        <v>13.56527573110525</v>
       </c>
       <c r="O103" t="n">
         <v>10</v>
       </c>
       <c r="P103" t="n">
-        <v>0.7526177446657956</v>
+        <v>0.2692393723943809</v>
       </c>
       <c r="Q103" t="n">
         <v>43</v>
@@ -11934,22 +11934,22 @@
         <v>14.26498323563516</v>
       </c>
       <c r="Y103" t="n">
-        <v>4.451651228691911</v>
+        <v>3.991031345750884</v>
       </c>
       <c r="Z103" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AA103" t="n">
-        <v>45</v>
+        <v>44.18604651162791</v>
       </c>
       <c r="AB103" t="n">
-        <v>10.96541638459621</v>
+        <v>11.36992378833388</v>
       </c>
       <c r="AC103" t="n">
         <v>10</v>
       </c>
       <c r="AD103" t="n">
-        <v>5.806849456486041</v>
+        <v>6.258757633246558</v>
       </c>
       <c r="AE103" t="n">
         <v>41</v>
@@ -11983,7 +11983,7 @@
         <v>46241</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04842946801510651</v>
+        <v>0.04843406978796273</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12012,10 +12012,10 @@
         <v>10</v>
       </c>
       <c r="J104" t="n">
-        <v>28.26757886753546</v>
+        <v>28.26076284576177</v>
       </c>
       <c r="K104" t="n">
-        <v>0.8733615873076417</v>
+        <v>0.8733615873076195</v>
       </c>
       <c r="L104" t="n">
         <v>20</v>
@@ -12030,7 +12030,7 @@
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>3.09956797661215</v>
+        <v>3.099567976612172</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>

--- a/TDA_Result.xlsx
+++ b/TDA_Result.xlsx
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4524706706916669</v>
+        <v>0.4526626889599994</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>14.94856954517825</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.001887734293875</v>
+        <v>4.961572694682037</v>
       </c>
       <c r="Z2" t="n">
         <v>34</v>
@@ -754,22 +754,22 @@
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.15597036004307</v>
+        <v>3.197051331201839</v>
       </c>
       <c r="AE2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AF2" t="n">
-        <v>53.48837209302326</v>
+        <v>54.76190476190476</v>
       </c>
       <c r="AG2" t="n">
-        <v>35.54963360883827</v>
+        <v>36.45160901222331</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.93873848418499</v>
+        <v>18.31029574968145</v>
       </c>
       <c r="AI2" t="n">
-        <v>38.91564047231397</v>
+        <v>39.94911903473349</v>
       </c>
       <c r="AJ2" t="n">
         <v>54</v>
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7393009799620726</v>
+        <v>0.738929878308468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>12.13279917920569</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.828512890401647</v>
+        <v>2.877289370518632</v>
       </c>
       <c r="Z3" t="n">
         <v>58</v>
@@ -863,7 +863,7 @@
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>7.380238095471081</v>
+        <v>7.333723063655196</v>
       </c>
       <c r="AE3" t="n">
         <v>38</v>
@@ -872,10 +872,10 @@
         <v>60.52631578947368</v>
       </c>
       <c r="AG3" t="n">
-        <v>32.72355667318509</v>
+        <v>33.09632405046492</v>
       </c>
       <c r="AH3" t="n">
-        <v>27.80275911628859</v>
+        <v>27.42999173900876</v>
       </c>
       <c r="AI3" t="n">
         <v>44.71786799604255</v>
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C4" t="n">
-        <v>1.413184615845841</v>
+        <v>1.413522983916297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>23.54405567752772</v>
       </c>
       <c r="K4" t="n">
-        <v>9.418499382413703</v>
+        <v>9.44469817207867</v>
       </c>
       <c r="L4" t="n">
         <v>15</v>
@@ -967,7 +967,7 @@
         <v>12.1087988317258</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.39972194631235</v>
+        <v>2.376352870969478</v>
       </c>
       <c r="Z4" t="n">
         <v>57</v>
@@ -982,7 +982,7 @@
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>7.78714795208566</v>
+        <v>7.809221795365051</v>
       </c>
       <c r="AE4" t="n">
         <v>45</v>
@@ -991,10 +991,10 @@
         <v>60</v>
       </c>
       <c r="AG4" t="n">
-        <v>36.82394641834451</v>
+        <v>37.04914784511599</v>
       </c>
       <c r="AH4" t="n">
-        <v>23.17605358165549</v>
+        <v>22.95085215488401</v>
       </c>
       <c r="AI4" t="n">
         <v>45.45185459035139</v>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2629278134109778</v>
+        <v>0.2646819310545627</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
         <v>62</v>
       </c>
       <c r="S5" t="n">
-        <v>44.86047771145579</v>
+        <v>44.82786901580361</v>
       </c>
       <c r="T5" t="n">
-        <v>17.13952228854421</v>
+        <v>17.17213098419639</v>
       </c>
       <c r="U5" t="n">
         <v>48.15044693099298</v>
@@ -1076,22 +1076,22 @@
         <v>16.70172291026088</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.888274705340835</v>
+        <v>5.260410214072486</v>
       </c>
       <c r="Z5" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="AA5" t="n">
-        <v>37.93103448275862</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.33713608175451</v>
+        <v>17.12502756887595</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.368983016500394</v>
+        <v>5.002755233199796</v>
       </c>
       <c r="AE5" t="n">
         <v>44</v>
@@ -1100,10 +1100,10 @@
         <v>50</v>
       </c>
       <c r="AG5" t="n">
-        <v>26.2626935873381</v>
+        <v>26.30848113312565</v>
       </c>
       <c r="AH5" t="n">
-        <v>23.7373064126619</v>
+        <v>23.69151886687435</v>
       </c>
       <c r="AI5" t="n">
         <v>35.8317605399894</v>
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C6" t="n">
-        <v>1.916395743596392</v>
+        <v>1.956299100854092</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %89.47: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1157,22 +1157,22 @@
         <v>23.73506360720576</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9353419510238714</v>
+        <v>3.037026336025317</v>
       </c>
       <c r="L6" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="M6" t="n">
-        <v>76.92307692307692</v>
+        <v>89.47368421052632</v>
       </c>
       <c r="N6" t="n">
-        <v>14.62179439154069</v>
+        <v>12.18640485162359</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.054792135635441</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>41</v>
@@ -1199,7 +1199,7 @@
         <v>44.49622708587002</v>
       </c>
       <c r="Y6" t="n">
-        <v>23.0217256632023</v>
+        <v>21.41887740380365</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1207,31 +1207,31 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="AF6" t="n">
-        <v>45.83333333333334</v>
+        <v>49.01960784313726</v>
       </c>
       <c r="AG6" t="n">
-        <v>41.65634683346627</v>
+        <v>44.28004025287129</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.176986499867063</v>
+        <v>4.73956759026597</v>
       </c>
       <c r="AI6" t="n">
-        <v>32.57524229286744</v>
+        <v>35.85748589437075</v>
       </c>
       <c r="AJ6" t="n">
         <v>79</v>
       </c>
       <c r="AK6" t="n">
-        <v>37.9746835443038</v>
+        <v>43.03797468354431</v>
       </c>
     </row>
     <row r="7">
@@ -1241,14 +1241,14 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C7" t="n">
-        <v>2.134453930825002</v>
+        <v>2.129191097068028</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1269,25 +1269,25 @@
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>11.71054792447627</v>
+        <v>11.64775322580256</v>
       </c>
       <c r="K7" t="n">
-        <v>2.672719595670592</v>
+        <v>2.34677098672722</v>
       </c>
       <c r="L7" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M7" t="n">
-        <v>53.73134328358209</v>
+        <v>58.57142857142857</v>
       </c>
       <c r="N7" t="n">
-        <v>12.90798239203889</v>
+        <v>12.60717207997788</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3187608213927273</v>
+        <v>0.6382507303112739</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1296,10 +1296,10 @@
         <v>58.8235294117647</v>
       </c>
       <c r="S7" t="n">
-        <v>51.33940159127875</v>
+        <v>51.72013062713113</v>
       </c>
       <c r="T7" t="n">
-        <v>7.484127820485952</v>
+        <v>7.103398784633576</v>
       </c>
       <c r="U7" t="n">
         <v>45.16533720637157</v>
@@ -1314,7 +1314,7 @@
         <v>13.79329344082609</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.350818437943541</v>
+        <v>9.574328332384063</v>
       </c>
       <c r="Z7" t="n">
         <v>18</v>
@@ -1323,34 +1323,34 @@
         <v>61.11111111111111</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.649714189658804</v>
+        <v>7.482902640383853</v>
       </c>
       <c r="AC7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.7161471850819057</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
       </c>
       <c r="AF7" t="n">
-        <v>50</v>
+        <v>47.72727272727273</v>
       </c>
       <c r="AG7" t="n">
-        <v>30.70145275754492</v>
+        <v>31.93404692648117</v>
       </c>
       <c r="AH7" t="n">
-        <v>19.29854724245508</v>
+        <v>15.79322580079156</v>
       </c>
       <c r="AI7" t="n">
-        <v>35.8317605399894</v>
+        <v>33.75499103225111</v>
       </c>
       <c r="AJ7" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AK7" t="n">
-        <v>42.85714285714285</v>
+        <v>48.4375</v>
       </c>
     </row>
     <row r="8">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3335870402929</v>
+        <v>0.3315334941221773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>22.10694516187944</v>
       </c>
       <c r="K8" t="n">
-        <v>6.063265581653332</v>
+        <v>5.41034509439966</v>
       </c>
       <c r="L8" t="n">
         <v>4</v>
@@ -1406,7 +1406,7 @@
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>1.826018091867687</v>
+        <v>2.456736958105199</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1456,10 +1456,10 @@
         <v>11.76207742326478</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK8" t="n">
-        <v>50</v>
+        <v>66.66666666666667</v>
       </c>
     </row>
     <row r="9">
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5996599352035831</v>
+        <v>0.6102563727247416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,19 +1540,19 @@
       </c>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AF9" t="n">
-        <v>45.71428571428572</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="AG9" t="n">
-        <v>27.67425460905149</v>
+        <v>28.48820327402359</v>
       </c>
       <c r="AH9" t="n">
-        <v>18.04003110523422</v>
+        <v>18.57062025538817</v>
       </c>
       <c r="AI9" t="n">
-        <v>30.46601928840721</v>
+        <v>31.45150447508847</v>
       </c>
       <c r="AJ9" t="n">
         <v>56</v>
@@ -1568,19 +1568,19 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C10" t="n">
-        <v>2.052682090695499</v>
+        <v>2.057938606168244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1595,47 +1595,37 @@
       <c r="I10" t="n">
         <v>10</v>
       </c>
-      <c r="J10" t="n">
-        <v>10.23694539327734</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.637911359585908</v>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>43</v>
-      </c>
-      <c r="M10" t="n">
-        <v>34.88372093023256</v>
-      </c>
-      <c r="N10" t="n">
-        <v>10.2042419622148</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>10</v>
-      </c>
-      <c r="P10" t="n">
-        <v>8.227332231208262</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="R10" t="n">
-        <v>51.16279069767442</v>
+        <v>48.78048780487805</v>
       </c>
       <c r="S10" t="n">
-        <v>37.50055988518298</v>
+        <v>37.07543417321452</v>
       </c>
       <c r="T10" t="n">
-        <v>13.66223081249144</v>
+        <v>11.70505363166352</v>
       </c>
       <c r="U10" t="n">
-        <v>36.75230846944931</v>
+        <v>34.25442955443266</v>
       </c>
       <c r="V10" t="n">
         <v>54</v>
       </c>
       <c r="W10" t="n">
-        <v>62.96296296296296</v>
+        <v>57.4074074074074</v>
       </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
@@ -1655,10 +1645,10 @@
         <v>53.33333333333334</v>
       </c>
       <c r="AG10" t="n">
-        <v>40.12944416748765</v>
+        <v>40.61533766137347</v>
       </c>
       <c r="AH10" t="n">
-        <v>13.20388916584569</v>
+        <v>12.71799567195987</v>
       </c>
       <c r="AI10" t="n">
         <v>36.1422996198733</v>
@@ -1677,10 +1667,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C11" t="n">
-        <v>7.417122351739895</v>
+        <v>7.334811960591262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,7 +1689,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1712,16 +1702,16 @@
         <v>20.56423081971027</v>
       </c>
       <c r="K11" t="n">
-        <v>6.274674442998629</v>
+        <v>5.095307350510958</v>
       </c>
       <c r="L11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M11" t="n">
-        <v>80</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="N11" t="n">
-        <v>13.5681865072563</v>
+        <v>14.83018974219779</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1736,10 +1726,10 @@
         <v>61.22448979591837</v>
       </c>
       <c r="S11" t="n">
-        <v>51.44602456318876</v>
+        <v>51.49704497135203</v>
       </c>
       <c r="T11" t="n">
-        <v>9.778465232729602</v>
+        <v>9.727444824566341</v>
       </c>
       <c r="U11" t="n">
         <v>47.24599944352045</v>
@@ -1751,19 +1741,19 @@
         <v>61.76470588235294</v>
       </c>
       <c r="X11" t="n">
-        <v>10.70591528549823</v>
+        <v>10.78465339552526</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.002713704206251</v>
+        <v>5.135500153348948</v>
       </c>
       <c r="Z11" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="AA11" t="n">
-        <v>45</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.50303049746318</v>
+        <v>10.83553485163747</v>
       </c>
       <c r="AC11" t="n">
         <v>3</v>
@@ -1772,25 +1762,25 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF11" t="n">
-        <v>55.55555555555556</v>
+        <v>56.52173913043478</v>
       </c>
       <c r="AG11" t="n">
-        <v>22.7365944283816</v>
+        <v>23.25681339008345</v>
       </c>
       <c r="AH11" t="n">
-        <v>32.81896112717396</v>
+        <v>33.26492574035133</v>
       </c>
       <c r="AI11" t="n">
-        <v>41.17613449352105</v>
+        <v>42.24743369429499</v>
       </c>
       <c r="AJ11" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AK11" t="n">
-        <v>51.47058823529412</v>
+        <v>52.17391304347826</v>
       </c>
     </row>
     <row r="12">
@@ -1800,10 +1790,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C12" t="n">
-        <v>6.468359704626876</v>
+        <v>6.507026039324534</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,17 +1821,13 @@
         <v>20.08266526523165</v>
       </c>
       <c r="K12" t="n">
-        <v>12.61224149700353</v>
+        <v>13.28541102059415</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M12" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N12" t="n">
-        <v>22.33927009741701</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
         <v>6</v>
       </c>
@@ -1870,19 +1856,19 @@
         <v>70.58823529411765</v>
       </c>
       <c r="X12" t="n">
-        <v>18.81777830559044</v>
+        <v>18.9022858703151</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.222734254992334</v>
+        <v>4.723941855791725</v>
       </c>
       <c r="Z12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA12" t="n">
-        <v>54.54545454545455</v>
+        <v>50</v>
       </c>
       <c r="AB12" t="n">
-        <v>11.651820968583</v>
+        <v>12.53915470955308</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
@@ -1919,10 +1905,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2771854685303871</v>
+        <v>0.279141980117954</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,13 +1933,13 @@
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>39.9520395484761</v>
+        <v>35.3274613290198</v>
       </c>
       <c r="K13" t="n">
-        <v>0.379652161702948</v>
+        <v>1.016334672306196</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1961,7 +1947,7 @@
         <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>4.602872931711377</v>
+        <v>3.943585302928176</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -2012,10 +1998,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C14" t="n">
-        <v>8.088070522073963</v>
+        <v>8.104967216453344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,16 +2061,16 @@
         <v>14.33662537827827</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.527859477235265</v>
+        <v>6.332587911898468</v>
       </c>
       <c r="Z14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA14" t="n">
-        <v>37.03703703703704</v>
+        <v>39.28571428571428</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.18997592652526</v>
+        <v>10.75804611379783</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2099,10 +2085,10 @@
         <v>52.63157894736842</v>
       </c>
       <c r="AG14" t="n">
-        <v>26.96855224142348</v>
+        <v>27.03952079422842</v>
       </c>
       <c r="AH14" t="n">
-        <v>25.66302670594494</v>
+        <v>25.59205815313999</v>
       </c>
       <c r="AI14" t="n">
         <v>37.25897138449667</v>
@@ -2121,19 +2107,19 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C15" t="n">
-        <v>11.99319854472147</v>
+        <v>12.80448602263217</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2141,38 +2127,24 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>5</v>
       </c>
       <c r="I15" t="n">
         <v>10</v>
       </c>
-      <c r="J15" t="n">
-        <v>14.74031958141837</v>
-      </c>
-      <c r="K15" t="n">
-        <v>12.92244226606549</v>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>20</v>
-      </c>
-      <c r="M15" t="n">
-        <v>75</v>
-      </c>
-      <c r="N15" t="n">
-        <v>20.15946868531259</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
         <v>8</v>
       </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="n">
         <v>39</v>
       </c>
@@ -2180,10 +2152,10 @@
         <v>76.92307692307692</v>
       </c>
       <c r="S15" t="n">
-        <v>53.33993478862341</v>
+        <v>53.34964729833591</v>
       </c>
       <c r="T15" t="n">
-        <v>23.58314213445351</v>
+        <v>23.57342962474101</v>
       </c>
       <c r="U15" t="n">
         <v>61.66374277165825</v>
@@ -2195,25 +2167,25 @@
         <v>79.56989247311827</v>
       </c>
       <c r="X15" t="n">
-        <v>17.12346148492163</v>
+        <v>21.6463997632442</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.586829799593116</v>
+        <v>0.8921330089213253</v>
       </c>
       <c r="Z15" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="AA15" t="n">
-        <v>32.6530612244898</v>
+        <v>34.21052631578947</v>
       </c>
       <c r="AB15" t="n">
-        <v>14.82982024306668</v>
+        <v>12.71812976763059</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.651757417660164</v>
+        <v>9.189852700490997</v>
       </c>
       <c r="AE15" t="n">
         <v>31</v>
@@ -2222,10 +2194,10 @@
         <v>58.06451612903226</v>
       </c>
       <c r="AG15" t="n">
-        <v>23.43818908765165</v>
+        <v>23.58838146168542</v>
       </c>
       <c r="AH15" t="n">
-        <v>34.62632704138061</v>
+        <v>34.47613466734684</v>
       </c>
       <c r="AI15" t="n">
         <v>40.76626249536972</v>
@@ -2244,27 +2216,31 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C16" t="n">
-        <v>37.04891928063433</v>
+        <v>38.56015430710835</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>BAND</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>5</v>
       </c>
@@ -2275,22 +2251,22 @@
         <v>17.40096492560246</v>
       </c>
       <c r="K16" t="n">
-        <v>6.78856395307248</v>
+        <v>11.14449717342687</v>
       </c>
       <c r="L16" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M16" t="n">
-        <v>66.66666666666667</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N16" t="n">
-        <v>15.92006307930395</v>
+        <v>21.57061637385742</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>3.007284608058569</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2299,10 +2275,10 @@
         <v>67.85714285714286</v>
       </c>
       <c r="S16" t="n">
-        <v>54.03239530931563</v>
+        <v>53.94310959502992</v>
       </c>
       <c r="T16" t="n">
-        <v>13.82474754782723</v>
+        <v>13.91403326211294</v>
       </c>
       <c r="U16" t="n">
         <v>49.33884318085762</v>
@@ -2313,17 +2289,27 @@
       <c r="W16" t="n">
         <v>77.35849056603773</v>
       </c>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
+      <c r="X16" t="n">
+        <v>12.29218491597857</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.02205486820871</v>
+      </c>
       <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
+        <v>73</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>36.98630136986301</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>14.289170281546</v>
+      </c>
       <c r="AC16" t="n">
         <v>5</v>
       </c>
-      <c r="AD16" t="inlineStr"/>
+      <c r="AD16" t="n">
+        <v>4.019021739130446</v>
+      </c>
       <c r="AE16" t="n">
         <v>30</v>
       </c>
@@ -2353,19 +2339,19 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7523006584219034</v>
+        <v>0.7657543879658049</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2373,11 +2359,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.56: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>5</v>
       </c>
@@ -2388,22 +2370,22 @@
         <v>14.16674936134154</v>
       </c>
       <c r="K17" t="n">
-        <v>6.845157256563916</v>
+        <v>8.755917047497498</v>
       </c>
       <c r="L17" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M17" t="n">
-        <v>75.55555555555556</v>
+        <v>65.78947368421052</v>
       </c>
       <c r="N17" t="n">
-        <v>16.1993530881949</v>
+        <v>14.81983602063213</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>1.080856421656073</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2412,10 +2394,10 @@
         <v>65.21739130434783</v>
       </c>
       <c r="S17" t="n">
-        <v>46.198317268358</v>
+        <v>46.25266509444496</v>
       </c>
       <c r="T17" t="n">
-        <v>19.01907403598982</v>
+        <v>18.96472620990286</v>
       </c>
       <c r="U17" t="n">
         <v>50.77005884206276</v>
@@ -2430,43 +2412,43 @@
         <v>15.7396793517258</v>
       </c>
       <c r="Y17" t="n">
-        <v>7.684937564179672</v>
+        <v>6.034025965291534</v>
       </c>
       <c r="Z17" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AA17" t="n">
-        <v>56.66666666666666</v>
+        <v>47.22222222222222</v>
       </c>
       <c r="AB17" t="n">
-        <v>11.01046228963967</v>
+        <v>12.18320241180209</v>
       </c>
       <c r="AC17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.507784076330788</v>
+        <v>2.092219077069624</v>
       </c>
       <c r="AE17" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="AF17" t="n">
-        <v>60</v>
+        <v>56.09756097560975</v>
       </c>
       <c r="AG17" t="n">
-        <v>42.75246376049439</v>
+        <v>39.27802642270026</v>
       </c>
       <c r="AH17" t="n">
-        <v>17.24753623950561</v>
+        <v>16.81953455290949</v>
       </c>
       <c r="AI17" t="n">
-        <v>43.5727090128925</v>
+        <v>41.04052722210609</v>
       </c>
       <c r="AJ17" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AK17" t="n">
-        <v>55.29411764705883</v>
+        <v>52.32558139534883</v>
       </c>
     </row>
     <row r="18">
@@ -2476,10 +2458,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C18" t="n">
-        <v>0.104416309427582</v>
+        <v>0.1045734571324104</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2507,22 +2489,22 @@
         <v>24.37863714425642</v>
       </c>
       <c r="K18" t="n">
-        <v>4.491268423300521</v>
+        <v>4.648528942249652</v>
       </c>
       <c r="L18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M18" t="n">
-        <v>57.14285714285715</v>
+        <v>60</v>
       </c>
       <c r="N18" t="n">
-        <v>18.22091744975853</v>
+        <v>16.1263886239993</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>5.271953972635579</v>
+        <v>5.113756602067077</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2531,19 +2513,19 @@
         <v>77.19298245614036</v>
       </c>
       <c r="S18" t="n">
-        <v>41.88485489140715</v>
+        <v>41.83710446695893</v>
       </c>
       <c r="T18" t="n">
-        <v>35.3081275647332</v>
+        <v>35.35587798918143</v>
       </c>
       <c r="U18" t="n">
         <v>64.79398895432649</v>
       </c>
       <c r="V18" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W18" t="n">
-        <v>75</v>
+        <v>75.82417582417582</v>
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
@@ -2563,10 +2545,10 @@
         <v>59.52380952380953</v>
       </c>
       <c r="AG18" t="n">
-        <v>39.55867819556905</v>
+        <v>39.60203653507343</v>
       </c>
       <c r="AH18" t="n">
-        <v>19.96513132824047</v>
+        <v>19.92177298873609</v>
       </c>
       <c r="AI18" t="n">
         <v>44.49431275003934</v>
@@ -2585,10 +2567,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02537022852944217</v>
+        <v>0.02556705946275914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,22 +2598,22 @@
         <v>18.34152851742537</v>
       </c>
       <c r="K19" t="n">
-        <v>2.716660933804738</v>
+        <v>3.51357201465452</v>
       </c>
       <c r="L19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M19" t="n">
-        <v>58.62068965517241</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N19" t="n">
-        <v>23.82410481760151</v>
+        <v>25.37572101645628</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>7.090708556900016</v>
+        <v>6.266258480991449</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2694,10 +2676,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C20" t="n">
-        <v>1.866074598741627</v>
+        <v>1.876664095548926</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2754,19 +2736,19 @@
         <v>70.49180327868852</v>
       </c>
       <c r="X20" t="n">
-        <v>16.65604614151002</v>
+        <v>16.29942815131207</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.802748639502653</v>
+        <v>5.268203293238949</v>
       </c>
       <c r="Z20" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AA20" t="n">
-        <v>55</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="AB20" t="n">
-        <v>11.83530055065416</v>
+        <v>13.92148976383984</v>
       </c>
       <c r="AC20" t="n">
         <v>4</v>
@@ -2803,10 +2785,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C21" t="n">
-        <v>0.939746774574344</v>
+        <v>0.9518489880781407</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2834,22 +2816,22 @@
         <v>13.9566823466854</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6803157488990852</v>
+        <v>1.976893411934677</v>
       </c>
       <c r="L21" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M21" t="n">
-        <v>60.3448275862069</v>
+        <v>55.73770491803279</v>
       </c>
       <c r="N21" t="n">
-        <v>17.56054848099487</v>
+        <v>17.73370807604084</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>7.270223773787632</v>
+        <v>5.906344453674461</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2858,10 +2840,10 @@
         <v>72.5</v>
       </c>
       <c r="S21" t="n">
-        <v>46.14261029373566</v>
+        <v>46.20511029373566</v>
       </c>
       <c r="T21" t="n">
-        <v>26.35738970626434</v>
+        <v>26.29488970626434</v>
       </c>
       <c r="U21" t="n">
         <v>57.16504419378943</v>
@@ -2884,25 +2866,25 @@
       </c>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AF21" t="n">
-        <v>61.53846153846154</v>
+        <v>62.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>34.85374889364611</v>
+        <v>35.79490517130495</v>
       </c>
       <c r="AH21" t="n">
-        <v>26.68471264481543</v>
+        <v>26.70509482869505</v>
       </c>
       <c r="AI21" t="n">
-        <v>45.89906145692508</v>
+        <v>47.0324391373011</v>
       </c>
       <c r="AJ21" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK21" t="n">
-        <v>59.72222222222222</v>
+        <v>60.27397260273973</v>
       </c>
     </row>
     <row r="22">
@@ -2912,10 +2894,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3335870402929</v>
+        <v>0.3390778851318809</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2932,11 +2914,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>5</v>
       </c>
@@ -2947,17 +2925,13 @@
         <v>20.35908649698318</v>
       </c>
       <c r="K22" t="n">
-        <v>12.4600794655453</v>
+        <v>14.31117310030576</v>
       </c>
       <c r="L22" t="n">
-        <v>5</v>
-      </c>
-      <c r="M22" t="n">
-        <v>80</v>
-      </c>
-      <c r="N22" t="n">
-        <v>17.21117446734009</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
         <v>10</v>
       </c>
@@ -2986,25 +2960,25 @@
         <v>73.68421052631579</v>
       </c>
       <c r="X22" t="n">
-        <v>19.31653455747442</v>
+        <v>19.40139685595055</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.746441695912974</v>
+        <v>4.263119100512524</v>
       </c>
       <c r="Z22" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA22" t="n">
-        <v>53.33333333333334</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="AB22" t="n">
-        <v>12.75464260894753</v>
+        <v>11.56018940523159</v>
       </c>
       <c r="AC22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.2690172218952069</v>
+        <v>0.7696938656912344</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3014,10 +2988,10 @@
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK22" t="n">
-        <v>55.55555555555556</v>
+        <v>57.89473684210526</v>
       </c>
     </row>
     <row r="23">
@@ -3027,10 +3001,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8848129155630716</v>
+        <v>0.8311389750195075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3055,25 +3029,25 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>13.05666178440531</v>
+        <v>18.91837442883233</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1899378728213108</v>
+        <v>0.9160321042286146</v>
       </c>
       <c r="L23" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="M23" t="n">
-        <v>64.51612903225806</v>
+        <v>68.18181818181819</v>
       </c>
       <c r="N23" t="n">
-        <v>15.08455575055588</v>
+        <v>19.28490917746859</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.800943317565953</v>
+        <v>4.046897019844553</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3100,10 +3074,10 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>12.89152345723877</v>
+        <v>18.17564070797</v>
       </c>
       <c r="Z23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
@@ -3142,10 +3116,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1897525334063584</v>
+        <v>0.18881902129124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,16 +3144,16 @@
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>22.86774633531589</v>
+        <v>22.66030863734194</v>
       </c>
       <c r="K24" t="n">
-        <v>8.41004993469079</v>
+        <v>7.876712681174936</v>
       </c>
       <c r="L24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M24" t="n">
-        <v>66.66666666666667</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N24" t="n">
         <v>10.20060895618112</v>
@@ -3188,7 +3162,7 @@
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>1.466607631180916</v>
+        <v>1.968253635147699</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3212,19 +3186,19 @@
         <v>75</v>
       </c>
       <c r="X24" t="n">
-        <v>12.60269688350961</v>
+        <v>12.68278405422394</v>
       </c>
       <c r="Y24" t="n">
-        <v>3.723398342009709</v>
+        <v>4.265133678926746</v>
       </c>
       <c r="Z24" t="n">
         <v>29</v>
       </c>
       <c r="AA24" t="n">
-        <v>55.17241379310344</v>
+        <v>51.72413793103448</v>
       </c>
       <c r="AB24" t="n">
-        <v>14.95270948470093</v>
+        <v>15.01891149573349</v>
       </c>
       <c r="AC24" t="n">
         <v>2</v>
@@ -3261,10 +3235,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C25" t="n">
-        <v>4.073913485696917</v>
+        <v>4.149407909134485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3306,10 +3280,10 @@
         <v>68.18181818181819</v>
       </c>
       <c r="S25" t="n">
-        <v>37.11438358728957</v>
+        <v>37.1425961155021</v>
       </c>
       <c r="T25" t="n">
-        <v>31.06743459452861</v>
+        <v>31.03922206631609</v>
       </c>
       <c r="U25" t="n">
         <v>53.44310393781777</v>
@@ -3338,10 +3312,10 @@
         <v>53.48837209302326</v>
       </c>
       <c r="AG25" t="n">
-        <v>51.10067347911028</v>
+        <v>51.16280823548845</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.387698613912974</v>
+        <v>2.32556385753481</v>
       </c>
       <c r="AI25" t="n">
         <v>38.91564047231397</v>
@@ -3360,10 +3334,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4298261716202625</v>
+        <v>0.4379930491117967</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3459,10 +3433,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C27" t="n">
-        <v>37.17472206257197</v>
+        <v>38.37154485669314</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3490,7 +3464,7 @@
         <v>61.00029220182797</v>
       </c>
       <c r="K27" t="n">
-        <v>12.7764402289585</v>
+        <v>16.40722498852378</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3515,25 +3489,25 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>15.00270949461759</v>
+        <v>17.80589180979497</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.935840707964609</v>
+        <v>1.187263896384239</v>
       </c>
       <c r="Z27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AA27" t="n">
         <v>20</v>
       </c>
       <c r="AB27" t="n">
-        <v>26.05926118730342</v>
+        <v>10.10968013007894</v>
       </c>
       <c r="AC27" t="n">
         <v>5</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.124647490129717</v>
+        <v>3.858547241944299</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3554,10 +3528,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C28" t="n">
-        <v>1.457215557444304</v>
+        <v>1.477440694919097</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3582,19 +3556,19 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>18.25342733104113</v>
+        <v>16.53966926125512</v>
       </c>
       <c r="K28" t="n">
-        <v>4.508909935214755</v>
+        <v>5.95942084966552</v>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M28" t="n">
-        <v>41.66666666666666</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="N28" t="n">
-        <v>15.88163857029287</v>
+        <v>17.29337785004663</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
@@ -3663,10 +3637,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4145201761293965</v>
+        <v>0.4216469223095378</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3694,17 +3668,13 @@
         <v>20.65475273479386</v>
       </c>
       <c r="K29" t="n">
-        <v>14.04266769675455</v>
+        <v>16.00337598837525</v>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
-      </c>
-      <c r="M29" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N29" t="n">
-        <v>18.00706743337966</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
         <v>4</v>
       </c>
@@ -3736,7 +3706,7 @@
         <v>55.05052857749912</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.51256332817273</v>
+        <v>7.95683448603689</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
@@ -3747,7 +3717,7 @@
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.5386788373673013</v>
+        <v>2.219790576034841</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3778,10 +3748,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3761503291061161</v>
+        <v>0.3761710864773436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3809,7 +3779,7 @@
         <v>21.6314445059014</v>
       </c>
       <c r="K30" t="n">
-        <v>1.752094410739513</v>
+        <v>1.75770946895808</v>
       </c>
       <c r="L30" t="n">
         <v>34</v>
@@ -3824,7 +3794,7 @@
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>3.191979101825426</v>
+        <v>3.186284899652736</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3887,10 +3857,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1750755461640555</v>
+        <v>0.1783407184903954</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3907,7 +3877,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H31" t="n">
         <v>5</v>
       </c>
@@ -3918,22 +3892,22 @@
         <v>31.09418993049242</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5428649259512142</v>
+        <v>2.417997046684506</v>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
-        <v>66.66666666666667</v>
+        <v>75</v>
       </c>
       <c r="N31" t="n">
-        <v>8.284865476453684</v>
+        <v>16.18915332817012</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>9.406072803887056</v>
+        <v>7.402998664247895</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3996,10 +3970,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C32" t="n">
-        <v>2.373479088607019</v>
+        <v>2.376479107295175</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4059,13 +4033,13 @@
         <v>15.25475988862757</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.285387435167618</v>
+        <v>2.161878588931077</v>
       </c>
       <c r="Z32" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA32" t="n">
-        <v>31.81818181818182</v>
+        <v>31.11111111111111</v>
       </c>
       <c r="AB32" t="n">
         <v>12.64953902913536</v>
@@ -4074,7 +4048,7 @@
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>5.848268150314572</v>
+        <v>5.967123373659156</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4105,10 +4079,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C33" t="n">
-        <v>1.810511671306128</v>
+        <v>1.806459338947972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4136,22 +4110,22 @@
         <v>12.57251846431013</v>
       </c>
       <c r="K33" t="n">
-        <v>1.477096265812161</v>
+        <v>1.249967699160615</v>
       </c>
       <c r="L33" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M33" t="n">
-        <v>60.71428571428572</v>
+        <v>61.81818181818182</v>
       </c>
       <c r="N33" t="n">
-        <v>12.30850360623689</v>
+        <v>12.0757370060047</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>2.486180455518028</v>
+        <v>2.716082151265908</v>
       </c>
       <c r="Q33" t="n">
         <v>39</v>
@@ -4214,10 +4188,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8110086073911154</v>
+        <v>0.7825196563105701</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4242,25 +4216,25 @@
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>15.89069802235623</v>
+        <v>18.21448986654661</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9394588280592808</v>
+        <v>0.1609478861683611</v>
       </c>
       <c r="L34" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="M34" t="n">
-        <v>60.8695652173913</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N34" t="n">
-        <v>13.83623491196254</v>
+        <v>11.06621659967589</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>3.032056251811355</v>
+        <v>3.83288316939121</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4278,10 +4252,10 @@
         <v>38.18972506848375</v>
       </c>
       <c r="V34" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="W34" t="n">
-        <v>48.33333333333334</v>
+        <v>49.15254237288136</v>
       </c>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
@@ -4301,10 +4275,10 @@
         <v>52.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>27.05588988514636</v>
+        <v>27.36770347413387</v>
       </c>
       <c r="AH34" t="n">
-        <v>25.44411011485364</v>
+        <v>25.13229652586613</v>
       </c>
       <c r="AI34" t="n">
         <v>37.49736210669248</v>
@@ -4323,10 +4297,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C35" t="n">
-        <v>1.922685786663817</v>
+        <v>1.925912086858855</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4343,7 +4317,11 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H35" t="n">
         <v>5</v>
       </c>
@@ -4354,16 +4332,16 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>8.391893302731845</v>
+        <v>8.573776785164998</v>
       </c>
       <c r="L35" t="n">
         <v>10</v>
       </c>
       <c r="M35" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="N35" t="n">
-        <v>13.94206337498728</v>
+        <v>14.18470627803493</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4393,10 +4371,10 @@
         <v>87.5</v>
       </c>
       <c r="X35" t="n">
-        <v>42.52272358489104</v>
+        <v>38.58137734187126</v>
       </c>
       <c r="Y35" t="n">
-        <v>16.43982578910094</v>
+        <v>16.29961036325028</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -4438,10 +4416,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08323950801108425</v>
+        <v>0.08382642240675728</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4466,19 +4444,19 @@
         <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>18.45194908889744</v>
+        <v>17.66670693852417</v>
       </c>
       <c r="K36" t="n">
-        <v>4.038159342471626</v>
+        <v>4.77172318584862</v>
       </c>
       <c r="L36" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M36" t="n">
-        <v>66.66666666666667</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N36" t="n">
-        <v>13.16774825086663</v>
+        <v>13.7664191568117</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4547,10 +4525,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06415941753016746</v>
+        <v>0.06601330974098192</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4578,22 +4556,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>4.440699259177294</v>
+        <v>7.458522772889276</v>
       </c>
       <c r="L37" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="M37" t="n">
-        <v>58.46153846153846</v>
+        <v>62.85714285714285</v>
       </c>
       <c r="N37" t="n">
-        <v>19.09008605054506</v>
+        <v>18.87520782182908</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>3.40796333811404</v>
+        <v>0.5038941659891716</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4656,10 +4634,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C38" t="n">
-        <v>1.637532846141876</v>
+        <v>1.630423979729076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4684,25 +4662,25 @@
         <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>15.02885014069408</v>
+        <v>14.71604491689452</v>
       </c>
       <c r="K38" t="n">
-        <v>3.357421550027628</v>
+        <v>2.908725754824659</v>
       </c>
       <c r="L38" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M38" t="n">
-        <v>60</v>
+        <v>56.36363636363637</v>
       </c>
       <c r="N38" t="n">
-        <v>12.68953661268957</v>
+        <v>13.56277763441883</v>
       </c>
       <c r="O38" t="n">
         <v>6</v>
       </c>
       <c r="P38" t="n">
-        <v>2.556737978117329</v>
+        <v>3.003899059580406</v>
       </c>
       <c r="Q38" t="n">
         <v>34</v>
@@ -4711,10 +4689,10 @@
         <v>52.94117647058823</v>
       </c>
       <c r="S38" t="n">
-        <v>49.48773690843407</v>
+        <v>49.93944655262882</v>
       </c>
       <c r="T38" t="n">
-        <v>3.453439562154159</v>
+        <v>3.001729917959409</v>
       </c>
       <c r="U38" t="n">
         <v>36.73671298006892</v>
@@ -4733,29 +4711,29 @@
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="n">
         <v>35</v>
       </c>
       <c r="AF38" t="n">
-        <v>57.14285714285715</v>
+        <v>54.28571428571428</v>
       </c>
       <c r="AG38" t="n">
-        <v>19.84050728315898</v>
+        <v>17.21883667956938</v>
       </c>
       <c r="AH38" t="n">
-        <v>37.30234985969817</v>
+        <v>37.0668776061449</v>
       </c>
       <c r="AI38" t="n">
-        <v>40.85741114397492</v>
+        <v>38.18972506848375</v>
       </c>
       <c r="AJ38" t="n">
         <v>67</v>
       </c>
       <c r="AK38" t="n">
-        <v>55.22388059701493</v>
+        <v>49.25373134328358</v>
       </c>
     </row>
     <row r="39">
@@ -4765,10 +4743,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C39" t="n">
-        <v>2.662825551013333</v>
+        <v>2.671967214215388</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4796,16 +4774,16 @@
         <v>16.13238434452433</v>
       </c>
       <c r="K39" t="n">
-        <v>5.406618001897079</v>
+        <v>5.768486168842646</v>
       </c>
       <c r="L39" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="M39" t="n">
-        <v>63.63636363636363</v>
+        <v>70</v>
       </c>
       <c r="N39" t="n">
-        <v>13.03319696046832</v>
+        <v>12.24070780756101</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4838,37 +4816,37 @@
         <v>10.2437411865161</v>
       </c>
       <c r="Y39" t="n">
-        <v>4.38766240383236</v>
+        <v>4.059418674935921</v>
       </c>
       <c r="Z39" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AA39" t="n">
-        <v>43.75</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB39" t="n">
-        <v>11.71889448169242</v>
+        <v>14.00849739507054</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.686327974719726</v>
+        <v>2.022690813691286</v>
       </c>
       <c r="AE39" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AF39" t="n">
-        <v>59.52380952380953</v>
+        <v>58.69565217391305</v>
       </c>
       <c r="AG39" t="n">
-        <v>41.25123138669232</v>
+        <v>37.57931640024876</v>
       </c>
       <c r="AH39" t="n">
-        <v>18.27257813711721</v>
+        <v>21.11633577366428</v>
       </c>
       <c r="AI39" t="n">
-        <v>44.49431275003934</v>
+        <v>44.33949777984616</v>
       </c>
       <c r="AJ39" t="n">
         <v>67</v>
@@ -4884,14 +4862,14 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2044295206486614</v>
+        <v>0.208937363507126</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4901,7 +4879,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4944,25 +4922,25 @@
         <v>76.47058823529412</v>
       </c>
       <c r="X40" t="n">
-        <v>18.05956154786905</v>
+        <v>18.14352984100791</v>
       </c>
       <c r="Y40" t="n">
-        <v>5.431623639060912</v>
+        <v>3.415006199347725</v>
       </c>
       <c r="Z40" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AA40" t="n">
-        <v>29.41176470588235</v>
+        <v>38.09523809523809</v>
       </c>
       <c r="AB40" t="n">
-        <v>11.76313020993737</v>
+        <v>12.40472491959226</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.641035256391532</v>
       </c>
       <c r="AE40" t="n">
         <v>14</v>
@@ -4993,10 +4971,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C41" t="n">
-        <v>1.71930468648105</v>
+        <v>1.710058985034242</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5015,7 +4993,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -5028,13 +5006,13 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>13.62134599453981</v>
+        <v>13.01033792173563</v>
       </c>
       <c r="L41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M41" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N41" t="n">
         <v>12.17975430538131</v>
@@ -5067,19 +5045,19 @@
         <v>81.25</v>
       </c>
       <c r="X41" t="n">
-        <v>40.81782021738603</v>
+        <v>36.58819281794096</v>
       </c>
       <c r="Y41" t="n">
-        <v>11.82845072528574</v>
+        <v>12.30260043656527</v>
       </c>
       <c r="Z41" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AA41" t="n">
-        <v>28.57142857142857</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB41" t="n">
-        <v>17.85423125778112</v>
+        <v>22.49011102054075</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
@@ -5116,10 +5094,10 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C42" t="n">
-        <v>3.556025430670057</v>
+        <v>3.589866603487027</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5144,10 +5122,10 @@
         <v>10</v>
       </c>
       <c r="J42" t="n">
-        <v>19.79504810217467</v>
+        <v>18.35939977786119</v>
       </c>
       <c r="K42" t="n">
-        <v>15.69601805265095</v>
+        <v>16.79704756368494</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5180,25 +5158,25 @@
       </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="n">
-        <v>17.40144278572016</v>
+        <v>18.29706591648155</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.452643760249117</v>
+        <v>1.268009769452461</v>
       </c>
       <c r="Z42" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AA42" t="n">
         <v>66.66666666666667</v>
       </c>
       <c r="AB42" t="n">
-        <v>11.58190407518745</v>
+        <v>12.42836034283877</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>8.673349104319394</v>
+        <v>8.8441347228569</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5227,10 +5205,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C43" t="n">
-        <v>7.118340744638005</v>
+        <v>7.209072326981126</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5290,16 +5268,16 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>8.121251764026006</v>
+        <v>6.950149605501988</v>
       </c>
       <c r="Z43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA43" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AB43" t="n">
-        <v>13.63280086769262</v>
+        <v>13.09070057304151</v>
       </c>
       <c r="AC43" t="n">
         <v>2</v>
@@ -5336,10 +5314,10 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C44" t="n">
-        <v>5.074045538151391</v>
+        <v>5.086168115612351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5358,7 +5336,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.27: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.95: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -5371,22 +5349,22 @@
         <v>13.03201987649729</v>
       </c>
       <c r="K44" t="n">
-        <v>3.852244274953942</v>
+        <v>4.100361258976193</v>
       </c>
       <c r="L44" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M44" t="n">
-        <v>77.27272727272727</v>
+        <v>80.95238095238095</v>
       </c>
       <c r="N44" t="n">
-        <v>20.4740028993714</v>
+        <v>20.49521452087832</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>5.919713885787181</v>
+        <v>5.667260583608313</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5413,7 +5391,7 @@
         <v>12.1234692799834</v>
       </c>
       <c r="Y44" t="n">
-        <v>7.376890010757132</v>
+        <v>7.155600939329398</v>
       </c>
       <c r="Z44" t="n">
         <v>11</v>
@@ -5428,7 +5406,7 @@
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.832025387128023</v>
+        <v>3.063619442258314</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5451,10 +5429,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02138647251005582</v>
+        <v>0.02158530314104183</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5550,10 +5528,10 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C46" t="n">
-        <v>9.356581906611812</v>
+        <v>9.357124401154282</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5581,7 +5559,7 @@
         <v>20.92024905883424</v>
       </c>
       <c r="K46" t="n">
-        <v>13.31380791778654</v>
+        <v>13.32037785144347</v>
       </c>
       <c r="L46" t="n">
         <v>13</v>
@@ -5620,25 +5598,25 @@
         <v>66.26506024096386</v>
       </c>
       <c r="X46" t="n">
-        <v>15.98001516291092</v>
+        <v>16.0625044063383</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.298850574712641</v>
+        <v>2.362629144460437</v>
       </c>
       <c r="Z46" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA46" t="n">
-        <v>36.73469387755102</v>
+        <v>37.5</v>
       </c>
       <c r="AB46" t="n">
-        <v>12.07559113826556</v>
+        <v>12.1758723098851</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.717647058823534</v>
+        <v>0.6527939557923967</v>
       </c>
       <c r="AE46" t="n">
         <v>37</v>
@@ -5669,10 +5647,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7762031742001051</v>
+        <v>0.7494081811093126</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5697,25 +5675,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>24.7868707712232</v>
+        <v>25.22913744871184</v>
       </c>
       <c r="K47" t="n">
-        <v>4.131216806772087</v>
+        <v>1.131215223697923</v>
       </c>
       <c r="L47" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="M47" t="n">
-        <v>33.33333333333334</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="N47" t="n">
-        <v>15.79730259714992</v>
+        <v>13.24296250924603</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>5.635949884383029</v>
+        <v>8.769581930450165</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5756,10 +5734,10 @@
         <v>56.81818181818182</v>
       </c>
       <c r="AG47" t="n">
-        <v>30.73108141313401</v>
+        <v>32.77439796655892</v>
       </c>
       <c r="AH47" t="n">
-        <v>26.08710040504781</v>
+        <v>24.0437838516229</v>
       </c>
       <c r="AI47" t="n">
         <v>42.22414699362943</v>
@@ -5778,10 +5756,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C48" t="n">
-        <v>0.06143369331391225</v>
+        <v>0.06182198757281377</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5806,25 +5784,25 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>21.44820004664813</v>
+        <v>20.70237270975156</v>
       </c>
       <c r="K48" t="n">
-        <v>4.680115904850779</v>
+        <v>5.341751008234596</v>
       </c>
       <c r="L48" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M48" t="n">
-        <v>53.125</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N48" t="n">
-        <v>15.39363674846669</v>
+        <v>14.23814929331134</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>5.082038789472443</v>
+        <v>4.422034898016158</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5865,10 +5843,10 @@
         <v>60.37735849056604</v>
       </c>
       <c r="AG48" t="n">
-        <v>23.45615679752166</v>
+        <v>23.53015765389077</v>
       </c>
       <c r="AH48" t="n">
-        <v>36.92120169304438</v>
+        <v>36.84720083667527</v>
       </c>
       <c r="AI48" t="n">
         <v>46.94147867320552</v>
@@ -5887,10 +5865,10 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2591537236627096</v>
+        <v>0.2590236381116341</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5918,7 +5896,7 @@
         <v>21.9393534200744</v>
       </c>
       <c r="K49" t="n">
-        <v>2.557081605004474</v>
+        <v>2.505601756331188</v>
       </c>
       <c r="L49" t="n">
         <v>23</v>
@@ -5927,13 +5905,13 @@
         <v>60.8695652173913</v>
       </c>
       <c r="N49" t="n">
-        <v>9.984806883436532</v>
+        <v>10.2084549776116</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>2.382008493966659</v>
+        <v>2.433426272252248</v>
       </c>
       <c r="Q49" t="n">
         <v>53</v>
@@ -5942,10 +5920,10 @@
         <v>73.58490566037736</v>
       </c>
       <c r="S49" t="n">
-        <v>39.05541494364515</v>
+        <v>39.14430853516574</v>
       </c>
       <c r="T49" t="n">
-        <v>34.52949071673221</v>
+        <v>34.44059712521162</v>
       </c>
       <c r="U49" t="n">
         <v>60.41933558938148</v>
@@ -5974,10 +5952,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="AG49" t="n">
-        <v>34.13669582835028</v>
+        <v>34.30771144707561</v>
       </c>
       <c r="AH49" t="n">
-        <v>27.56543183122418</v>
+        <v>27.39441621249885</v>
       </c>
       <c r="AI49" t="n">
         <v>47.42656695641357</v>
@@ -5996,10 +5974,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7133017832312862</v>
+        <v>0.7129437322095092</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6024,25 +6002,25 @@
         <v>10</v>
       </c>
       <c r="J50" t="n">
-        <v>10.47768044674046</v>
+        <v>10.41400888746848</v>
       </c>
       <c r="K50" t="n">
-        <v>0.2948180878395323</v>
+        <v>0.1732269359833394</v>
       </c>
       <c r="L50" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M50" t="n">
-        <v>43.75</v>
+        <v>42.5531914893617</v>
       </c>
       <c r="N50" t="n">
-        <v>13.34788312333409</v>
+        <v>13.684937882731</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>3.694290475620998</v>
+        <v>3.820155525649782</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6105,10 +6083,10 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1905912177805908</v>
+        <v>0.1904955480628467</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6127,7 +6105,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -6140,16 +6118,16 @@
         <v>27.11346359280836</v>
       </c>
       <c r="K51" t="n">
-        <v>10.46690111752133</v>
+        <v>10.41145083301693</v>
       </c>
       <c r="L51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M51" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N51" t="n">
-        <v>21.23919812340072</v>
+        <v>22.187736672458</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
@@ -6182,7 +6160,7 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>13.47818404847907</v>
+        <v>13.52161478892544</v>
       </c>
       <c r="Z51" t="n">
         <v>3</v>
@@ -6228,10 +6206,10 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C52" t="n">
-        <v>4.161975369103518</v>
+        <v>4.21018193754409</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6291,22 +6269,22 @@
         <v>12.1710603868542</v>
       </c>
       <c r="Y52" t="n">
-        <v>4.50380657658791</v>
+        <v>3.397710702437784</v>
       </c>
       <c r="Z52" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="AA52" t="n">
-        <v>45.45454545454545</v>
+        <v>35</v>
       </c>
       <c r="AB52" t="n">
-        <v>13.28027921400272</v>
+        <v>13.31268153984237</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.661081450556491</v>
+        <v>4.764161730562999</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6315,10 +6293,10 @@
         <v>68.42105263157895</v>
       </c>
       <c r="AG52" t="n">
-        <v>35.71221378586114</v>
+        <v>36.01597576226742</v>
       </c>
       <c r="AH52" t="n">
-        <v>32.70883884571781</v>
+        <v>32.40507686931152</v>
       </c>
       <c r="AI52" t="n">
         <v>52.54424010939046</v>
@@ -6337,10 +6315,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C53" t="n">
-        <v>1.635436165189291</v>
+        <v>1.628328191333613</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6359,7 +6337,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -6372,22 +6350,22 @@
         <v>28.17598592067425</v>
       </c>
       <c r="K53" t="n">
-        <v>7.821064053402771</v>
+        <v>7.352449428939978</v>
       </c>
       <c r="L53" t="n">
         <v>5</v>
       </c>
       <c r="M53" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N53" t="n">
-        <v>13.60621978110839</v>
+        <v>12.63443633390716</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>0.1659563909595763</v>
+        <v>0.6032005552781161</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6442,10 +6420,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0851265478531071</v>
+        <v>0.08382642240675728</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6473,22 +6451,22 @@
         <v>42.39442432818535</v>
       </c>
       <c r="K54" t="n">
-        <v>5.315544344393941</v>
+        <v>3.707075276264904</v>
       </c>
       <c r="L54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M54" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N54" t="n">
-        <v>26.43294614127311</v>
+        <v>28.91863102314376</v>
       </c>
       <c r="O54" t="n">
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>4.448019221443089</v>
+        <v>6.067980132475448</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6515,7 +6493,7 @@
         <v>114.7400208810756</v>
       </c>
       <c r="Y54" t="n">
-        <v>39.33237440850665</v>
+        <v>40.25894227470545</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -6557,10 +6535,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8298790565517992</v>
+        <v>0.8181459019700281</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6585,25 +6563,25 @@
         <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>15.18483300004738</v>
+        <v>15.124509340431</v>
       </c>
       <c r="K55" t="n">
-        <v>2.273904528987925</v>
+        <v>0.7562545318334557</v>
       </c>
       <c r="L55" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M55" t="n">
-        <v>67.74193548387096</v>
+        <v>70</v>
       </c>
       <c r="N55" t="n">
-        <v>14.34384572044462</v>
+        <v>14.00276981247055</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>3.643251412148807</v>
+        <v>5.204387055207382</v>
       </c>
       <c r="Q55" t="n">
         <v>44</v>
@@ -6630,16 +6608,16 @@
         <v>25.41488056506582</v>
       </c>
       <c r="Y55" t="n">
-        <v>13.2562170763668</v>
+        <v>14.48263459590213</v>
       </c>
       <c r="Z55" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AA55" t="n">
-        <v>44.44444444444444</v>
+        <v>40</v>
       </c>
       <c r="AB55" t="n">
-        <v>11.11232349515831</v>
+        <v>12.49559209226058</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6654,10 +6632,10 @@
         <v>55.31914893617022</v>
       </c>
       <c r="AG55" t="n">
-        <v>40.15796807227672</v>
+        <v>39.9694240369405</v>
       </c>
       <c r="AH55" t="n">
-        <v>15.1611808638935</v>
+        <v>15.34972489922972</v>
       </c>
       <c r="AI55" t="n">
         <v>41.24545983821874</v>
@@ -6676,10 +6654,10 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9137475778435578</v>
+        <v>0.9049062363774925</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6707,7 +6685,7 @@
         <v>34.38683570496719</v>
       </c>
       <c r="K56" t="n">
-        <v>16.52243056036522</v>
+        <v>15.39496973636898</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6734,25 +6712,25 @@
         <v>100</v>
       </c>
       <c r="X56" t="n">
-        <v>21.86994894803782</v>
+        <v>21.95662732854271</v>
       </c>
       <c r="Y56" t="n">
-        <v>4.387889249016286</v>
+        <v>5.38032064013797</v>
       </c>
       <c r="Z56" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA56" t="n">
-        <v>27.27272727272727</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB56" t="n">
-        <v>14.89161191615037</v>
+        <v>14.70795307963829</v>
       </c>
       <c r="AC56" t="n">
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>5.869665157377534</v>
+        <v>4.882366322857901</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6775,10 +6753,10 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C57" t="n">
-        <v>1.467699122605774</v>
+        <v>1.476392800721365</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6806,7 +6784,7 @@
         <v>32.76213282665623</v>
       </c>
       <c r="K57" t="n">
-        <v>25.67500179194049</v>
+        <v>26.4194173168443</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -6844,13 +6822,13 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>9.515537965282551</v>
+        <v>8.979567904882412</v>
       </c>
       <c r="Z57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA57" t="n">
-        <v>70</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="AB57" t="n">
         <v>13.83153316962987</v>
@@ -6890,10 +6868,10 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7862673871102362</v>
+        <v>0.7850344265592049</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6912,7 +6890,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.95: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %78.26: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -6925,16 +6903,16 @@
         <v>16.33691982084211</v>
       </c>
       <c r="K58" t="n">
-        <v>5.99692018194169</v>
+        <v>5.830704434910028</v>
       </c>
       <c r="L58" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M58" t="n">
-        <v>80.95238095238095</v>
+        <v>78.26086956521739</v>
       </c>
       <c r="N58" t="n">
-        <v>16.16334641984738</v>
+        <v>16.33740473192407</v>
       </c>
       <c r="O58" t="n">
         <v>5</v>
@@ -6967,7 +6945,7 @@
         <v>41.32985472592288</v>
       </c>
       <c r="Y58" t="n">
-        <v>11.31971168074414</v>
+        <v>11.45877289445363</v>
       </c>
       <c r="Z58" t="n">
         <v>1</v>
@@ -7009,10 +6987,10 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8206534680499077</v>
+        <v>0.8194032469624459</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7072,22 +7050,22 @@
         <v>10.2478061424703</v>
       </c>
       <c r="Y59" t="n">
-        <v>6.818141213634322</v>
+        <v>6.960098725981679</v>
       </c>
       <c r="Z59" t="n">
         <v>22</v>
       </c>
       <c r="AA59" t="n">
-        <v>45.45454545454545</v>
+        <v>50</v>
       </c>
       <c r="AB59" t="n">
-        <v>15.37190524642973</v>
+        <v>15.44866820059028</v>
       </c>
       <c r="AC59" t="n">
         <v>10</v>
       </c>
       <c r="AD59" t="n">
-        <v>3.414676233987346</v>
+        <v>3.267309221519155</v>
       </c>
       <c r="AE59" t="n">
         <v>43</v>
@@ -7118,10 +7096,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C60" t="n">
-        <v>13.72298679636399</v>
+        <v>13.57988042989468</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7146,25 +7124,25 @@
         <v>10</v>
       </c>
       <c r="J60" t="n">
-        <v>15.44754852801727</v>
+        <v>14.21636055978318</v>
       </c>
       <c r="K60" t="n">
-        <v>7.998409236809745</v>
+        <v>6.872177742187846</v>
       </c>
       <c r="L60" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="M60" t="n">
-        <v>55.17241379310344</v>
+        <v>51.35135135135135</v>
       </c>
       <c r="N60" t="n">
-        <v>12.24867975336606</v>
+        <v>12.90110247085263</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>0.001472950575376331</v>
+        <v>1.055300155418237</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7227,10 +7205,10 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6231430987304459</v>
+        <v>0.6236685875262934</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7258,7 +7236,7 @@
         <v>30.3360843704085</v>
       </c>
       <c r="K61" t="n">
-        <v>1.406005838931201</v>
+        <v>1.491520257703671</v>
       </c>
       <c r="L61" t="n">
         <v>9</v>
@@ -7273,7 +7251,7 @@
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>8.474837451658557</v>
+        <v>8.383439050564911</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7328,10 +7306,10 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C62" t="n">
-        <v>8.947722865314489</v>
+        <v>9.142319193736965</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7348,11 +7326,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>5</v>
       </c>
@@ -7363,16 +7337,16 @@
         <v>10.67683828611802</v>
       </c>
       <c r="K62" t="n">
-        <v>7.533919026534042</v>
+        <v>9.872581738648334</v>
       </c>
       <c r="L62" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M62" t="n">
-        <v>76.92307692307692</v>
+        <v>70.37037037037037</v>
       </c>
       <c r="N62" t="n">
-        <v>12.72275526639178</v>
+        <v>11.75173400008662</v>
       </c>
       <c r="O62" t="n">
         <v>6</v>
@@ -7441,14 +7415,14 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1016905799695442</v>
+        <v>0.102477798667902</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7469,25 +7443,25 @@
         <v>10</v>
       </c>
       <c r="J63" t="n">
-        <v>29.14654498090023</v>
+        <v>28.76464722640304</v>
       </c>
       <c r="K63" t="n">
-        <v>1.908125500782498</v>
+        <v>2.697028287381209</v>
       </c>
       <c r="L63" t="n">
         <v>5</v>
       </c>
       <c r="M63" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="N63" t="n">
-        <v>15.31610697611221</v>
+        <v>13.09147462811611</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>3.033982309088556</v>
+        <v>2.242491093485488</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7514,22 +7488,22 @@
         <v>10.24796802016521</v>
       </c>
       <c r="Y63" t="n">
-        <v>7.564622431732538</v>
+        <v>6.84905116020178</v>
       </c>
       <c r="Z63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA63" t="n">
-        <v>66.66666666666667</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB63" t="n">
-        <v>11.99689407402366</v>
+        <v>12.44107905981065</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>2.63468125769144</v>
+        <v>3.382626671057587</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7560,10 +7534,10 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1580921617962796</v>
+        <v>0.1594797713532145</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7591,22 +7565,22 @@
         <v>20.58679888238519</v>
       </c>
       <c r="K64" t="n">
-        <v>1.723664371512457</v>
+        <v>2.616515270915243</v>
       </c>
       <c r="L64" t="n">
         <v>42</v>
       </c>
       <c r="M64" t="n">
-        <v>54.76190476190476</v>
+        <v>59.52380952380953</v>
       </c>
       <c r="N64" t="n">
-        <v>14.58900884433736</v>
+        <v>12.54705725435966</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>3.220819510120876</v>
+        <v>2.322710650222515</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7647,10 +7621,10 @@
         <v>59.61538461538461</v>
       </c>
       <c r="AG64" t="n">
-        <v>38.79330402819375</v>
+        <v>38.5877021554118</v>
       </c>
       <c r="AH64" t="n">
-        <v>20.82208058719086</v>
+        <v>21.02768245997281</v>
       </c>
       <c r="AI64" t="n">
         <v>46.06757548486152</v>
@@ -7669,10 +7643,10 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C65" t="n">
-        <v>5.72402657816252</v>
+        <v>5.825936357269631</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7689,7 +7663,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H65" t="n">
         <v>5</v>
       </c>
@@ -7697,25 +7675,25 @@
         <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>32.95795759327989</v>
+        <v>32.91027483217498</v>
       </c>
       <c r="K65" t="n">
-        <v>1.111111111111107</v>
+        <v>2.838137119475914</v>
       </c>
       <c r="L65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M65" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N65" t="n">
-        <v>16.7570516336534</v>
+        <v>20.04918278117306</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>8.791208791208804</v>
+        <v>6.964209077614414</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7724,10 +7702,10 @@
         <v>68</v>
       </c>
       <c r="S65" t="n">
-        <v>45.86884729850905</v>
+        <v>46.10290213256388</v>
       </c>
       <c r="T65" t="n">
-        <v>22.13115270149095</v>
+        <v>21.89709786743612</v>
       </c>
       <c r="U65" t="n">
         <v>54.18970269185592</v>
@@ -7778,10 +7756,10 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4331809093268633</v>
+        <v>0.4367356638826963</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7877,19 +7855,19 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02788628416819493</v>
+        <v>0.02808185213496186</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7908,10 +7886,10 @@
         <v>18.49825117353735</v>
       </c>
       <c r="K67" t="n">
-        <v>3.571406725217985</v>
+        <v>4.29775840786859</v>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
@@ -7919,7 +7897,7 @@
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>0.4138142836266567</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7936,12 +7914,14 @@
         <v>10.87173616493582</v>
       </c>
       <c r="Y67" t="n">
-        <v>6.584481935826869</v>
+        <v>5.929354030577805</v>
       </c>
       <c r="Z67" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA67" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
         <v>3</v>
@@ -7968,19 +7948,19 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C68" t="n">
-        <v>3.652474038306337</v>
+        <v>3.453648667076047</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7988,24 +7968,38 @@
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %94.12: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H68" t="n">
         <v>5</v>
       </c>
       <c r="I68" t="n">
         <v>10</v>
       </c>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+      <c r="J68" t="n">
+        <v>16.5796986006275</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1.290722888363272</v>
+      </c>
       <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="M68" t="n">
+        <v>94.11764705882354</v>
+      </c>
+      <c r="N68" t="n">
+        <v>15.24835904859901</v>
+      </c>
       <c r="O68" t="n">
         <v>2</v>
       </c>
-      <c r="P68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>0.700238967016209</v>
+      </c>
       <c r="Q68" t="n">
         <v>5</v>
       </c>
@@ -8028,10 +8022,10 @@
         <v>80</v>
       </c>
       <c r="X68" t="n">
-        <v>127.8705240408364</v>
+        <v>128.0325939207301</v>
       </c>
       <c r="Y68" t="n">
-        <v>10.57495163114166</v>
+        <v>15.50297367692418</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -8073,10 +8067,10 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4117944267525849</v>
+        <v>0.4241616925581725</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8093,7 +8087,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H69" t="n">
         <v>5</v>
       </c>
@@ -8104,16 +8102,16 @@
         <v>29.4573350207784</v>
       </c>
       <c r="K69" t="n">
-        <v>5.335552532942933</v>
+        <v>8.499055223415365</v>
       </c>
       <c r="L69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M69" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="N69" t="n">
-        <v>14.20304940810647</v>
+        <v>21.5371107368305</v>
       </c>
       <c r="O69" t="n">
         <v>3</v>
@@ -8166,10 +8164,10 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C70" t="n">
-        <v>0.3883112632257219</v>
+        <v>0.3900024430309676</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8194,25 +8192,25 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>22.00203575468081</v>
+        <v>21.94656073986526</v>
       </c>
       <c r="K70" t="n">
-        <v>1.312908976700911</v>
+        <v>1.681828829137344</v>
       </c>
       <c r="L70" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M70" t="n">
-        <v>72.41379310344827</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N70" t="n">
-        <v>13.42081270102377</v>
+        <v>13.69136707203828</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>6.600433341457945</v>
+        <v>6.213667912562326</v>
       </c>
       <c r="Q70" t="n">
         <v>30</v>
@@ -8247,25 +8245,25 @@
       </c>
       <c r="AD70" t="inlineStr"/>
       <c r="AE70" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AF70" t="n">
-        <v>48.83720930232558</v>
+        <v>50</v>
       </c>
       <c r="AG70" t="n">
-        <v>34.62276580891307</v>
+        <v>35.09405254046762</v>
       </c>
       <c r="AH70" t="n">
-        <v>14.21444349341251</v>
+        <v>14.90594745953238</v>
       </c>
       <c r="AI70" t="n">
-        <v>34.61744754671859</v>
+        <v>35.8317605399894</v>
       </c>
       <c r="AJ70" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK70" t="n">
-        <v>49.12280701754386</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71">
@@ -8275,10 +8273,10 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C71" t="n">
-        <v>3.218454504571234</v>
+        <v>3.223126005457464</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8303,25 +8301,25 @@
         <v>10</v>
       </c>
       <c r="J71" t="n">
-        <v>19.51282806733038</v>
+        <v>18.95735500740921</v>
       </c>
       <c r="K71" t="n">
-        <v>2.734391293230187</v>
+        <v>2.883507522554241</v>
       </c>
       <c r="L71" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M71" t="n">
-        <v>69.23076923076923</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N71" t="n">
-        <v>13.8278543896199</v>
+        <v>14.5090794565403</v>
       </c>
       <c r="O71" t="n">
         <v>6</v>
       </c>
       <c r="P71" t="n">
-        <v>3.178690860637823</v>
+        <v>3.02914680155375</v>
       </c>
       <c r="Q71" t="n">
         <v>43</v>
@@ -8339,10 +8337,10 @@
         <v>36.75230846944931</v>
       </c>
       <c r="V71" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="W71" t="n">
-        <v>59.49367088607595</v>
+        <v>60.25641025641026</v>
       </c>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
@@ -8362,10 +8360,10 @@
         <v>54.83870967741935</v>
       </c>
       <c r="AG71" t="n">
-        <v>15.0226990154828</v>
+        <v>15.08127246115302</v>
       </c>
       <c r="AH71" t="n">
-        <v>39.81601066193655</v>
+        <v>39.75743721626634</v>
       </c>
       <c r="AI71" t="n">
         <v>37.77216763735451</v>
@@ -8384,10 +8382,10 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07757838324323316</v>
+        <v>0.07753944177408076</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8415,7 +8413,7 @@
         <v>20.36571476939619</v>
       </c>
       <c r="K72" t="n">
-        <v>8.459367231761217</v>
+        <v>8.404924654760059</v>
       </c>
       <c r="L72" t="n">
         <v>13</v>
@@ -8457,7 +8455,7 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>13.62915813935123</v>
+        <v>13.67251309640721</v>
       </c>
       <c r="Z72" t="n">
         <v>1</v>
@@ -8499,10 +8497,10 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07023988448513474</v>
+        <v>0.06999506082354782</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8519,11 +8517,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>5</v>
       </c>
@@ -8534,22 +8528,22 @@
         <v>22.14049070857409</v>
       </c>
       <c r="K73" t="n">
-        <v>2.139123707252755</v>
+        <v>1.783114091909765</v>
       </c>
       <c r="L73" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M73" t="n">
-        <v>76.47058823529412</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N73" t="n">
-        <v>13.89858393598737</v>
+        <v>15.63995587073383</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>7.696244110413364</v>
+        <v>8.072936244287465</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8599,10 +8593,10 @@
         <v>68.5312955758489</v>
       </c>
       <c r="AJ73" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AK73" t="n">
-        <v>68.75</v>
+        <v>69.6969696969697</v>
       </c>
     </row>
     <row r="74">
@@ -8612,10 +8606,10 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C74" t="n">
-        <v>4.979693451698163</v>
+        <v>5.037967858810818</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8643,22 +8637,22 @@
         <v>18.35970785011217</v>
       </c>
       <c r="K74" t="n">
-        <v>5.355867596084796</v>
+        <v>6.588784999445751</v>
       </c>
       <c r="L74" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M74" t="n">
-        <v>63.33333333333334</v>
+        <v>56</v>
       </c>
       <c r="N74" t="n">
-        <v>19.98684471942212</v>
+        <v>18.9315259078591</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>2.509715371575072</v>
+        <v>1.323980755162557</v>
       </c>
       <c r="Q74" t="n">
         <v>35</v>
@@ -8682,13 +8676,13 @@
         <v>77.58620689655173</v>
       </c>
       <c r="X74" t="n">
-        <v>95.98093909010421</v>
+        <v>59.69432739383429</v>
       </c>
       <c r="Y74" t="n">
-        <v>13.98716189750737</v>
+        <v>12.98060452743668</v>
       </c>
       <c r="Z74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="inlineStr"/>
       <c r="AB74" t="inlineStr"/>
@@ -8727,10 +8721,10 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1278994928732187</v>
+        <v>0.1297213899318532</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8747,7 +8741,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H75" t="n">
         <v>5</v>
       </c>
@@ -8755,25 +8753,25 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>21.57711484274354</v>
+        <v>21.52133760858017</v>
       </c>
       <c r="K75" t="n">
-        <v>1.160857173502472</v>
+        <v>2.528946543134447</v>
       </c>
       <c r="L75" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M75" t="n">
-        <v>64.28571428571429</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N75" t="n">
-        <v>17.51856000057698</v>
+        <v>17.14542780110784</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>4.783611924321529</v>
+        <v>3.385437550950821</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8836,10 +8834,10 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C76" t="n">
-        <v>1.846155888884582</v>
+        <v>1.852563967252942</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8867,22 +8865,22 @@
         <v>18.36583782901725</v>
       </c>
       <c r="K76" t="n">
-        <v>6.51912288557126</v>
+        <v>6.888854873692885</v>
       </c>
       <c r="L76" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M76" t="n">
-        <v>45.45454545454545</v>
+        <v>38.09523809523809</v>
       </c>
       <c r="N76" t="n">
-        <v>12.88955665858701</v>
+        <v>14.44637822264828</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>3.267842449442715</v>
+        <v>2.910635659801453</v>
       </c>
       <c r="Q76" t="n">
         <v>40</v>
@@ -8891,10 +8889,10 @@
         <v>62.5</v>
       </c>
       <c r="S76" t="n">
-        <v>31.96848527289704</v>
+        <v>32.30446664612266</v>
       </c>
       <c r="T76" t="n">
-        <v>30.53151472710296</v>
+        <v>30.19553335387734</v>
       </c>
       <c r="U76" t="n">
         <v>47.0324391373011</v>
@@ -8917,19 +8915,19 @@
       </c>
       <c r="AD76" t="inlineStr"/>
       <c r="AE76" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AF76" t="n">
-        <v>56.25</v>
+        <v>51.42857142857143</v>
       </c>
       <c r="AG76" t="n">
-        <v>27.96884590221791</v>
+        <v>28.1921981661551</v>
       </c>
       <c r="AH76" t="n">
-        <v>28.28115409778209</v>
+        <v>23.23637326241633</v>
       </c>
       <c r="AI76" t="n">
-        <v>39.32559113685198</v>
+        <v>35.56880459586856</v>
       </c>
       <c r="AJ76" t="n">
         <v>54</v>
@@ -8945,10 +8943,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5338231187322832</v>
+        <v>0.5318786325673263</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8976,13 +8974,13 @@
         <v>20.36657537342047</v>
       </c>
       <c r="K77" t="n">
-        <v>9.9440935288875</v>
+        <v>9.543614866042493</v>
       </c>
       <c r="L77" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M77" t="n">
-        <v>47.36842105263158</v>
+        <v>45</v>
       </c>
       <c r="N77" t="n">
         <v>15.91559869114716</v>
@@ -9015,25 +9013,25 @@
         <v>61.8421052631579</v>
       </c>
       <c r="X77" t="n">
-        <v>14.78060105264944</v>
+        <v>14.86223722874125</v>
       </c>
       <c r="Y77" t="n">
-        <v>4.213697680101425</v>
+        <v>4.630435982286352</v>
       </c>
       <c r="Z77" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AA77" t="n">
-        <v>48.14814814814815</v>
+        <v>48.07692307692308</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.9142865272163</v>
+        <v>11.71375424262182</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>6.040845277202578</v>
+        <v>5.630270068883103</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9064,10 +9062,10 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05409519455581383</v>
+        <v>0.05469673852474857</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9095,16 +9093,16 @@
         <v>12.76206508896208</v>
       </c>
       <c r="K78" t="n">
-        <v>6.770134060270294</v>
+        <v>7.957428620049378</v>
       </c>
       <c r="L78" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M78" t="n">
-        <v>58.33333333333334</v>
+        <v>60.97560975609756</v>
       </c>
       <c r="N78" t="n">
-        <v>17.42970274188952</v>
+        <v>16.82932389301555</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
@@ -9128,31 +9126,31 @@
         <v>56.63145942523844</v>
       </c>
       <c r="V78" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W78" t="n">
-        <v>65</v>
+        <v>65.82278481012658</v>
       </c>
       <c r="X78" t="n">
         <v>23.16536029857119</v>
       </c>
       <c r="Y78" t="n">
-        <v>6.855939944073485</v>
+        <v>5.820168688811112</v>
       </c>
       <c r="Z78" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AA78" t="n">
-        <v>47.36842105263158</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="AB78" t="n">
-        <v>13.62107476173054</v>
+        <v>13.72480224961067</v>
       </c>
       <c r="AC78" t="n">
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>3.375481006559866</v>
+        <v>4.438138455969298</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9183,10 +9181,10 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C79" t="n">
-        <v>0.866781170695394</v>
+        <v>0.8701182742221791</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9211,25 +9209,25 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>11.93481872403289</v>
+        <v>11.87218353498292</v>
       </c>
       <c r="K79" t="n">
-        <v>0.4861467257304186</v>
+        <v>0.8013243277523951</v>
       </c>
       <c r="L79" t="n">
         <v>59</v>
       </c>
       <c r="M79" t="n">
-        <v>59.32203389830509</v>
+        <v>55.93220338983051</v>
       </c>
       <c r="N79" t="n">
-        <v>11.10797001425765</v>
+        <v>11.30416543619934</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>4.492015488055112</v>
+        <v>4.165298125048178</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9270,10 +9268,10 @@
         <v>55.26315789473684</v>
       </c>
       <c r="AG79" t="n">
-        <v>26.25773210036694</v>
+        <v>26.60029402187623</v>
       </c>
       <c r="AH79" t="n">
-        <v>29.00542579436991</v>
+        <v>28.66286387286062</v>
       </c>
       <c r="AI79" t="n">
         <v>39.70629712199248</v>
@@ -9292,10 +9290,10 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1276898268117719</v>
+        <v>0.1278352920746443</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9323,7 +9321,7 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>4.543462568233236</v>
+        <v>4.662559309483361</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9334,7 +9332,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>5.219396122646502</v>
+        <v>5.099665750322457</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9361,22 +9359,22 @@
         <v>11.74527658842108</v>
       </c>
       <c r="Y80" t="n">
-        <v>6.444848713125917</v>
+        <v>6.338269943189367</v>
       </c>
       <c r="Z80" t="n">
         <v>32</v>
       </c>
       <c r="AA80" t="n">
-        <v>37.5</v>
+        <v>34.375</v>
       </c>
       <c r="AB80" t="n">
-        <v>11.34301121239574</v>
+        <v>12.14812307065434</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.662282905305146</v>
+        <v>1.77418253517494</v>
       </c>
       <c r="AE80" t="n">
         <v>26</v>
@@ -9385,10 +9383,10 @@
         <v>50</v>
       </c>
       <c r="AG80" t="n">
-        <v>39.94875125265902</v>
+        <v>40.14598991143613</v>
       </c>
       <c r="AH80" t="n">
-        <v>10.05124874734098</v>
+        <v>9.854010088563868</v>
       </c>
       <c r="AI80" t="n">
         <v>32.06059352575905</v>
@@ -9407,10 +9405,10 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C81" t="n">
-        <v>1.084000653630998</v>
+        <v>1.087647862791282</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9438,7 +9436,7 @@
         <v>12.04277302023445</v>
       </c>
       <c r="K81" t="n">
-        <v>3.500520478404456</v>
+        <v>3.848756473575299</v>
       </c>
       <c r="L81" t="n">
         <v>46</v>
@@ -9447,13 +9445,13 @@
         <v>43.47826086956522</v>
       </c>
       <c r="N81" t="n">
-        <v>13.80916877265594</v>
+        <v>14.77634724828385</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>6.279658780026787</v>
+        <v>5.923271241085981</v>
       </c>
       <c r="Q81" t="n">
         <v>31</v>
@@ -9480,22 +9478,22 @@
         <v>27.31228182970742</v>
       </c>
       <c r="Y81" t="n">
-        <v>8.963812277571071</v>
+        <v>8.65751355287342</v>
       </c>
       <c r="Z81" t="n">
         <v>9</v>
       </c>
       <c r="AA81" t="n">
-        <v>33.33333333333334</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AB81" t="n">
-        <v>11.50734464839207</v>
+        <v>14.43690406407305</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.138215195904602</v>
+        <v>1.469728380892799</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9526,10 +9524,10 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C82" t="n">
-        <v>5.524838840094593</v>
+        <v>5.459195759240068</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9586,25 +9584,25 @@
         <v>57.14285714285715</v>
       </c>
       <c r="X82" t="n">
-        <v>21.6427401266019</v>
+        <v>21.7292569078541</v>
       </c>
       <c r="Y82" t="n">
-        <v>0.09478672985782088</v>
+        <v>1.351967345653282</v>
       </c>
       <c r="Z82" t="n">
         <v>9</v>
       </c>
       <c r="AA82" t="n">
-        <v>55.55555555555556</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB82" t="n">
-        <v>11.37010739086874</v>
+        <v>11.75788225422557</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>3.908918406072104</v>
+        <v>2.684323836061864</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9635,14 +9633,14 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C83" t="n">
-        <v>5.776444403969869</v>
+        <v>5.736870783462451</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -9663,25 +9661,25 @@
         <v>10</v>
       </c>
       <c r="J83" t="n">
-        <v>12.767909949277</v>
+        <v>12.20482860933025</v>
       </c>
       <c r="K83" t="n">
-        <v>6.72826115397438</v>
+        <v>5.997080619903739</v>
       </c>
       <c r="L83" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M83" t="n">
-        <v>51.06382978723404</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="N83" t="n">
-        <v>12.86430364214105</v>
+        <v>13.64942371105745</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>3.06548500898518</v>
+        <v>3.776443046059352</v>
       </c>
       <c r="Q83" t="n">
         <v>43</v>
@@ -9690,10 +9688,10 @@
         <v>65.11627906976744</v>
       </c>
       <c r="S83" t="n">
-        <v>56.26460231053829</v>
+        <v>57.01585123752359</v>
       </c>
       <c r="T83" t="n">
-        <v>8.851676759229157</v>
+        <v>8.100427832243852</v>
       </c>
       <c r="U83" t="n">
         <v>50.17178199285205</v>
@@ -9708,22 +9706,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>3.981757944385877</v>
+        <v>4.639565621074826</v>
       </c>
       <c r="Z83" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AA83" t="n">
-        <v>46.93877551020408</v>
+        <v>48.93617021276596</v>
       </c>
       <c r="AB83" t="n">
-        <v>12.51277349367968</v>
+        <v>12.77433850361352</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>2.101936061738308</v>
+        <v>1.426623512975356</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9754,10 +9752,10 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C84" t="n">
-        <v>2.203645364861246</v>
+        <v>2.208826262481661</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9785,16 +9783,16 @@
         <v>13.05747170375323</v>
       </c>
       <c r="K84" t="n">
-        <v>5.494126352599582</v>
+        <v>5.742149141067787</v>
       </c>
       <c r="L84" t="n">
         <v>44</v>
       </c>
       <c r="M84" t="n">
-        <v>63.63636363636363</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="N84" t="n">
-        <v>10.49837034120071</v>
+        <v>11.02609612234209</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
@@ -9841,10 +9839,10 @@
         <v>41.02564102564103</v>
       </c>
       <c r="AG84" t="n">
-        <v>26.40911098078695</v>
+        <v>26.47321354488951</v>
       </c>
       <c r="AH84" t="n">
-        <v>14.61653004485408</v>
+        <v>14.55242748075152</v>
       </c>
       <c r="AI84" t="n">
         <v>27.07931000072518</v>
@@ -9863,10 +9861,10 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C85" t="n">
-        <v>6.421183661400263</v>
+        <v>6.423199616917777</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9891,10 +9889,10 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>16.26294183277037</v>
+        <v>16.20338496372404</v>
       </c>
       <c r="K85" t="n">
-        <v>0.9892827699917506</v>
+        <v>0.9491899781412183</v>
       </c>
       <c r="L85" t="n">
         <v>49</v>
@@ -9909,7 +9907,7 @@
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>6.942040816326545</v>
+        <v>6.984513717629159</v>
       </c>
       <c r="Q85" t="n">
         <v>34</v>
@@ -9918,10 +9916,10 @@
         <v>61.76470588235294</v>
       </c>
       <c r="S85" t="n">
-        <v>66.70612387044612</v>
+        <v>67.25189890227841</v>
       </c>
       <c r="T85" t="n">
-        <v>-4.941417988093178</v>
+        <v>-5.487193019925471</v>
       </c>
       <c r="U85" t="n">
         <v>45.0410173444307</v>
@@ -9950,10 +9948,10 @@
         <v>41.93548387096774</v>
       </c>
       <c r="AG85" t="n">
-        <v>22.89308091846042</v>
+        <v>22.96943404035434</v>
       </c>
       <c r="AH85" t="n">
-        <v>19.04240295250732</v>
+        <v>18.9660498306134</v>
       </c>
       <c r="AI85" t="n">
         <v>26.41554306731223</v>
@@ -9972,10 +9970,10 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C86" t="n">
-        <v>4.382130237494383</v>
+        <v>4.40298296475022</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10032,13 +10030,13 @@
         <v>69.23076923076923</v>
       </c>
       <c r="X86" t="n">
-        <v>72.0732996584329</v>
+        <v>81.75144481783289</v>
       </c>
       <c r="Y86" t="n">
-        <v>0.2862624439589623</v>
+        <v>5.146724108352152</v>
       </c>
       <c r="Z86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA86" t="inlineStr"/>
       <c r="AB86" t="inlineStr"/>
@@ -10046,7 +10044,7 @@
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>5.730140797129191</v>
+        <v>0.8995745098172026</v>
       </c>
       <c r="AE86" t="n">
         <v>51</v>
@@ -10077,10 +10075,10 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C87" t="n">
-        <v>5.514355274933123</v>
+        <v>5.53254387884598</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10105,25 +10103,25 @@
         <v>10</v>
       </c>
       <c r="J87" t="n">
-        <v>25.68615758407521</v>
+        <v>22.71406725516376</v>
       </c>
       <c r="K87" t="n">
-        <v>2.334630350194544</v>
+        <v>2.599199589567536</v>
       </c>
       <c r="L87" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="M87" t="n">
-        <v>58.8235294117647</v>
+        <v>65.21739130434783</v>
       </c>
       <c r="N87" t="n">
-        <v>12.2966575427839</v>
+        <v>9.483720186663188</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>2.604562737642602</v>
+        <v>2.339979668493042</v>
       </c>
       <c r="Q87" t="n">
         <v>47</v>
@@ -10164,10 +10162,10 @@
         <v>44.18604651162791</v>
       </c>
       <c r="AG87" t="n">
-        <v>41.42703049349428</v>
+        <v>41.57901451222623</v>
       </c>
       <c r="AH87" t="n">
-        <v>2.759016018133629</v>
+        <v>2.607031999401677</v>
       </c>
       <c r="AI87" t="n">
         <v>30.43330983917051</v>
@@ -10186,10 +10184,10 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C88" t="n">
-        <v>1.093435878421011</v>
+        <v>1.099173979735625</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10217,7 +10215,7 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>22.49937063691769</v>
+        <v>23.14221930647673</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -10252,25 +10250,25 @@
         <v>68.35443037974683</v>
       </c>
       <c r="X88" t="n">
-        <v>23.43895771829143</v>
+        <v>24.31612033147337</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.7611754819884631</v>
+        <v>0.9442870497137434</v>
       </c>
       <c r="Z88" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="AA88" t="n">
-        <v>52.63157894736842</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB88" t="n">
-        <v>13.93247104962249</v>
+        <v>12.34111706543424</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>5.279007025179661</v>
+        <v>5.103908497255083</v>
       </c>
       <c r="AE88" t="n">
         <v>31</v>
@@ -10301,10 +10299,10 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C89" t="n">
-        <v>2.178484872633137</v>
+        <v>2.192060913873096</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10323,7 +10321,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -10336,13 +10334,13 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>18.33171517007224</v>
+        <v>19.06914340073158</v>
       </c>
       <c r="L89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M89" t="n">
-        <v>83.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="N89" t="n">
         <v>12.23354717638958</v>
@@ -10378,22 +10376,22 @@
         <v>28.7873334490923</v>
       </c>
       <c r="Y89" t="n">
-        <v>4.996376782045764</v>
+        <v>4.40432625970566</v>
       </c>
       <c r="Z89" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA89" t="n">
-        <v>45</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB89" t="n">
-        <v>12.07316893631934</v>
+        <v>12.29381673502749</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>5.266770938277887</v>
+        <v>5.853480101511865</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10411,10 +10409,10 @@
         <v>28.34400610153417</v>
       </c>
       <c r="AJ89" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AK89" t="n">
-        <v>47.72727272727273</v>
+        <v>48.31460674157304</v>
       </c>
     </row>
     <row r="90">
@@ -10424,10 +10422,10 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C90" t="n">
-        <v>2.924914680050079</v>
+        <v>2.942307298641886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10444,7 +10442,11 @@
           <t>SATMA_BEKLE</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H90" t="n">
         <v>5</v>
       </c>
@@ -10455,16 +10457,16 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>15.30086485782711</v>
+        <v>15.98648621268435</v>
       </c>
       <c r="L90" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M90" t="n">
-        <v>66.66666666666667</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N90" t="n">
-        <v>12.26477270856481</v>
+        <v>13.22566581997007</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
@@ -10497,16 +10499,16 @@
         <v>33.24184775233741</v>
       </c>
       <c r="Y90" t="n">
-        <v>3.823762096722905</v>
+        <v>3.251862808563832</v>
       </c>
       <c r="Z90" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA90" t="n">
-        <v>42.85714285714285</v>
+        <v>40</v>
       </c>
       <c r="AB90" t="n">
-        <v>11.48286031783636</v>
+        <v>12.42826150152315</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
@@ -10543,10 +10545,10 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2331544868847044</v>
+        <v>0.2334565935280649</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10574,37 +10576,37 @@
         <v>14.07074278425192</v>
       </c>
       <c r="K91" t="n">
-        <v>2.833463954871096</v>
+        <v>2.966708967804976</v>
       </c>
       <c r="L91" t="n">
         <v>56</v>
       </c>
       <c r="M91" t="n">
-        <v>58.92857142857143</v>
+        <v>62.5</v>
       </c>
       <c r="N91" t="n">
-        <v>14.44970221801777</v>
+        <v>14.01795401988059</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>0.1619473260202398</v>
+        <v>0.03233184058104577</v>
       </c>
       <c r="Q91" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R91" t="n">
-        <v>61.70212765957447</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="S91" t="n">
-        <v>33.28085897378712</v>
+        <v>34.36399083141525</v>
       </c>
       <c r="T91" t="n">
-        <v>28.42126868578735</v>
+        <v>26.50557438597605</v>
       </c>
       <c r="U91" t="n">
-        <v>47.42656695641357</v>
+        <v>46.45684323162075</v>
       </c>
       <c r="V91" t="n">
         <v>81</v>
@@ -10652,10 +10654,10 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C92" t="n">
-        <v>1.14270860260021</v>
+        <v>1.143182819645132</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10683,7 +10685,7 @@
         <v>22.28274626067631</v>
       </c>
       <c r="K92" t="n">
-        <v>8.452066390334135</v>
+        <v>8.497073331143268</v>
       </c>
       <c r="L92" t="n">
         <v>14</v>
@@ -10739,10 +10741,10 @@
         <v>52.94117647058823</v>
       </c>
       <c r="AG92" t="n">
-        <v>40.2686375998766</v>
+        <v>40.23772433366922</v>
       </c>
       <c r="AH92" t="n">
-        <v>12.67253887071163</v>
+        <v>12.70345213691901</v>
       </c>
       <c r="AI92" t="n">
         <v>39.52330421009647</v>
@@ -10761,10 +10763,10 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04214393173943735</v>
+        <v>0.04254190874273115</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10789,25 +10791,25 @@
         <v>10</v>
       </c>
       <c r="J93" t="n">
-        <v>17.21421071359344</v>
+        <v>16.78996521390855</v>
       </c>
       <c r="K93" t="n">
-        <v>2.207847301632593</v>
+        <v>3.173024756685994</v>
       </c>
       <c r="L93" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M93" t="n">
-        <v>56.86274509803921</v>
+        <v>54</v>
       </c>
       <c r="N93" t="n">
-        <v>17.01166850852463</v>
+        <v>19.80117075707787</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>3.710236345332785</v>
+        <v>2.740033308106349</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10825,10 +10827,10 @@
         <v>56.7538641905662</v>
       </c>
       <c r="V93" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="W93" t="n">
-        <v>77.90697674418605</v>
+        <v>78.82352941176471</v>
       </c>
       <c r="X93" t="inlineStr"/>
       <c r="Y93" t="inlineStr"/>
@@ -10870,10 +10872,10 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C94" t="n">
-        <v>6.782866659470971</v>
+        <v>6.863288334553252</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10930,46 +10932,46 @@
         <v>70.90909090909091</v>
       </c>
       <c r="X94" t="n">
-        <v>49.33245658591723</v>
+        <v>49.43866730977011</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.560240963855409</v>
+        <v>1.475012191322944</v>
       </c>
       <c r="Z94" t="n">
         <v>8</v>
       </c>
       <c r="AA94" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="AB94" t="n">
-        <v>11.50265433776413</v>
+        <v>9.960569015483692</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>3.530139103554886</v>
+        <v>4.592731153099971</v>
       </c>
       <c r="AE94" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AF94" t="n">
-        <v>54.05405405405406</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="AG94" t="n">
-        <v>21.23956780603786</v>
+        <v>22.02234817100731</v>
       </c>
       <c r="AH94" t="n">
-        <v>32.81448624801619</v>
+        <v>30.60923077636111</v>
       </c>
       <c r="AI94" t="n">
-        <v>38.38404689217949</v>
+        <v>37.25897138449667</v>
       </c>
       <c r="AJ94" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AK94" t="n">
-        <v>58.18181818181818</v>
+        <v>57.14285714285715</v>
       </c>
     </row>
     <row r="95">
@@ -10979,10 +10981,10 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1383830580346886</v>
+        <v>0.1389422974444268</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11007,25 +11009,25 @@
         <v>10</v>
       </c>
       <c r="J95" t="n">
-        <v>23.88806899577756</v>
+        <v>23.83393539702336</v>
       </c>
       <c r="K95" t="n">
-        <v>0.456616883162142</v>
+        <v>0.7909001831348794</v>
       </c>
       <c r="L95" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M95" t="n">
-        <v>60</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N95" t="n">
-        <v>18.64216108458992</v>
+        <v>19.03389603309782</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>5.518186147245219</v>
+        <v>5.168224321243597</v>
       </c>
       <c r="Q95" t="n">
         <v>23</v>
@@ -11075,10 +11077,10 @@
         <v>43.43546988238708</v>
       </c>
       <c r="AJ95" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AK95" t="n">
-        <v>42.85714285714285</v>
+        <v>44.18604651162791</v>
       </c>
     </row>
     <row r="96">
@@ -11088,10 +11090,10 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1318832488926051</v>
+        <v>0.1322361800892633</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11119,22 +11121,22 @@
         <v>12.85874206974231</v>
       </c>
       <c r="K96" t="n">
-        <v>2.007293450146252</v>
+        <v>2.280273957128909</v>
       </c>
       <c r="L96" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M96" t="n">
-        <v>61.42857142857143</v>
+        <v>59.72222222222222</v>
       </c>
       <c r="N96" t="n">
-        <v>12.92956115569449</v>
+        <v>13.57776283679153</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>7.835426546004776</v>
+        <v>7.547619637885261</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11161,16 +11163,16 @@
         <v>16.74415231729489</v>
       </c>
       <c r="Y96" t="n">
-        <v>11.1095613069332</v>
+        <v>10.87168265924412</v>
       </c>
       <c r="Z96" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AA96" t="n">
-        <v>40</v>
+        <v>36.8421052631579</v>
       </c>
       <c r="AB96" t="n">
-        <v>16.42948776937994</v>
+        <v>18.11843988336842</v>
       </c>
       <c r="AC96" t="n">
         <v>8</v>
@@ -11179,25 +11181,25 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AF96" t="n">
-        <v>47.22222222222222</v>
+        <v>48.64864864864865</v>
       </c>
       <c r="AG96" t="n">
-        <v>28.8948868694483</v>
+        <v>28.92475479189564</v>
       </c>
       <c r="AH96" t="n">
-        <v>18.32733535277392</v>
+        <v>19.723893856753</v>
       </c>
       <c r="AI96" t="n">
-        <v>31.98604151517905</v>
+        <v>33.44640430301664</v>
       </c>
       <c r="AJ96" t="n">
         <v>69</v>
       </c>
       <c r="AK96" t="n">
-        <v>47.82608695652174</v>
+        <v>49.27536231884058</v>
       </c>
     </row>
     <row r="97">
@@ -11207,10 +11209,10 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C97" t="n">
-        <v>1.870267960856468</v>
+        <v>1.875616201351194</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11238,16 +11240,16 @@
         <v>19.26562870655475</v>
       </c>
       <c r="K97" t="n">
-        <v>4.641160066095407</v>
+        <v>4.940393171400981</v>
       </c>
       <c r="L97" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="M97" t="n">
-        <v>43.33333333333334</v>
+        <v>48.14814814814815</v>
       </c>
       <c r="N97" t="n">
-        <v>12.42621476522564</v>
+        <v>12.27530152555119</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11262,10 +11264,10 @@
         <v>56</v>
       </c>
       <c r="S97" t="n">
-        <v>35.11462284392235</v>
+        <v>35.21462284392235</v>
       </c>
       <c r="T97" t="n">
-        <v>20.88537715607765</v>
+        <v>20.78537715607765</v>
       </c>
       <c r="U97" t="n">
         <v>42.30602802165686</v>
@@ -11294,10 +11296,10 @@
         <v>55</v>
       </c>
       <c r="AG97" t="n">
-        <v>58.32067290383721</v>
+        <v>58.09243545501151</v>
       </c>
       <c r="AH97" t="n">
-        <v>-3.320672903837206</v>
+        <v>-3.092435455011511</v>
       </c>
       <c r="AI97" t="n">
         <v>39.82909179893205</v>
@@ -11316,10 +11318,10 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6445295813047244</v>
+        <v>0.6316320800513867</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11347,22 +11349,22 @@
         <v>17.47600423199651</v>
       </c>
       <c r="K98" t="n">
-        <v>7.349428306926975</v>
+        <v>5.201288909925306</v>
       </c>
       <c r="L98" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="M98" t="n">
-        <v>57.14285714285715</v>
+        <v>51.61290322580645</v>
       </c>
       <c r="N98" t="n">
-        <v>16.71038564991307</v>
+        <v>18.16434795474966</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>2.469106482332339</v>
+        <v>4.561456556091636</v>
       </c>
       <c r="Q98" t="n">
         <v>48</v>
@@ -11389,22 +11391,22 @@
         <v>11.17514685780745</v>
       </c>
       <c r="Y98" t="n">
-        <v>3.441163478536746</v>
+        <v>5.373375360162713</v>
       </c>
       <c r="Z98" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="AA98" t="n">
-        <v>44.44444444444444</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB98" t="n">
-        <v>11.75714725586849</v>
+        <v>11.56208130746633</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>4.721304321484765</v>
+        <v>2.775777588849437</v>
       </c>
       <c r="AE98" t="n">
         <v>50</v>
@@ -11435,10 +11437,10 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C99" t="n">
-        <v>0.477211890972546</v>
+        <v>0.4803254020672477</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11466,22 +11468,22 @@
         <v>28.77817890954801</v>
       </c>
       <c r="K99" t="n">
-        <v>2.664098710156071</v>
+        <v>3.333918168573557</v>
       </c>
       <c r="L99" t="n">
         <v>20</v>
       </c>
       <c r="M99" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="N99" t="n">
-        <v>13.34926119412081</v>
+        <v>12.81653281024479</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>1.301235102268294</v>
+        <v>0.6445916725424494</v>
       </c>
       <c r="Q99" t="n">
         <v>35</v>
@@ -11522,19 +11524,19 @@
         <v>51.28205128205128</v>
       </c>
       <c r="AG99" t="n">
-        <v>36.8637115774028</v>
+        <v>37.3032783032783</v>
       </c>
       <c r="AH99" t="n">
-        <v>14.41833970464849</v>
+        <v>13.97877297877299</v>
       </c>
       <c r="AI99" t="n">
         <v>36.19936288445796</v>
       </c>
       <c r="AJ99" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK99" t="n">
-        <v>49.35064935064935</v>
+        <v>48.71794871794872</v>
       </c>
     </row>
     <row r="100">
@@ -11544,10 +11546,10 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C100" t="n">
-        <v>324.7766511811801</v>
+        <v>324.1701803070112</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11564,7 +11566,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H100" t="n">
         <v>5</v>
       </c>
@@ -11572,19 +11578,19 @@
         <v>10</v>
       </c>
       <c r="J100" t="n">
-        <v>25.15478290083538</v>
+        <v>22.53558813827499</v>
       </c>
       <c r="K100" t="n">
-        <v>5.967961089191509</v>
+        <v>5.770082079841754</v>
       </c>
       <c r="L100" t="n">
         <v>15</v>
       </c>
       <c r="M100" t="n">
-        <v>73.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="N100" t="n">
-        <v>11.35281488036559</v>
+        <v>9.113096994515034</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11653,10 +11659,10 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C101" t="n">
-        <v>326.9991669954117</v>
+        <v>327.2024005761539</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11684,7 +11690,7 @@
         <v>13.42090796247281</v>
       </c>
       <c r="K101" t="n">
-        <v>3.550513545740297</v>
+        <v>3.614871329428149</v>
       </c>
       <c r="L101" t="n">
         <v>35</v>
@@ -11693,7 +11699,7 @@
         <v>34.28571428571428</v>
       </c>
       <c r="N101" t="n">
-        <v>8.303444048838744</v>
+        <v>8.220045130496679</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11762,10 +11768,10 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C102" t="n">
-        <v>398.731917351343</v>
+        <v>399.8840837517943</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11861,10 +11867,10 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7133017832312862</v>
+        <v>0.7121054487053645</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11889,25 +11895,25 @@
         <v>10</v>
       </c>
       <c r="J103" t="n">
-        <v>26.3831854858525</v>
+        <v>26.15665886206818</v>
       </c>
       <c r="K103" t="n">
-        <v>9.704631937483965</v>
+        <v>9.520637670364929</v>
       </c>
       <c r="L103" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M103" t="n">
-        <v>53.84615384615385</v>
+        <v>60</v>
       </c>
       <c r="N103" t="n">
-        <v>13.56527573110525</v>
+        <v>12.86523953581864</v>
       </c>
       <c r="O103" t="n">
         <v>10</v>
       </c>
       <c r="P103" t="n">
-        <v>0.2692393723943809</v>
+        <v>0.4376913245135228</v>
       </c>
       <c r="Q103" t="n">
         <v>43</v>
@@ -11934,22 +11940,22 @@
         <v>14.26498323563516</v>
       </c>
       <c r="Y103" t="n">
-        <v>3.991031345750884</v>
+        <v>4.152055538735377</v>
       </c>
       <c r="Z103" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AA103" t="n">
-        <v>44.18604651162791</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB103" t="n">
-        <v>11.36992378833388</v>
+        <v>11.09941705691624</v>
       </c>
       <c r="AC103" t="n">
         <v>10</v>
       </c>
       <c r="AD103" t="n">
-        <v>6.258757633246558</v>
+        <v>6.101272692006421</v>
       </c>
       <c r="AE103" t="n">
         <v>41</v>
@@ -11958,10 +11964,10 @@
         <v>60.97560975609756</v>
       </c>
       <c r="AG103" t="n">
-        <v>36.58483847917071</v>
+        <v>36.06323477357972</v>
       </c>
       <c r="AH103" t="n">
-        <v>24.39077127692686</v>
+        <v>24.91237498251784</v>
       </c>
       <c r="AI103" t="n">
         <v>45.72685693412379</v>
@@ -11980,10 +11986,10 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04843406978796273</v>
+        <v>0.04882888937540767</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12002,7 +12008,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -12012,25 +12018,25 @@
         <v>10</v>
       </c>
       <c r="J104" t="n">
-        <v>28.26076284576177</v>
+        <v>28.20973926735822</v>
       </c>
       <c r="K104" t="n">
-        <v>0.8733615873076195</v>
+        <v>1.623371824024433</v>
       </c>
       <c r="L104" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M104" t="n">
-        <v>80</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N104" t="n">
-        <v>15.48542247307857</v>
+        <v>14.62100600668919</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>3.099567976612172</v>
+        <v>2.338662980097772</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>
@@ -12071,10 +12077,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="AG104" t="n">
-        <v>35.28413789334237</v>
+        <v>35.64217807685518</v>
       </c>
       <c r="AH104" t="n">
-        <v>26.4179897662321</v>
+        <v>26.05994958271928</v>
       </c>
       <c r="AI104" t="n">
         <v>47.42656695641357</v>

--- a/TDA_Result.xlsx
+++ b/TDA_Result.xlsx
@@ -453,7 +453,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -679,7 +679,7 @@
         <v>46244</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4526626889599994</v>
+        <v>0.4580498435553736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -739,22 +739,22 @@
         <v>14.94856954517825</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.961572694682037</v>
+        <v>3.830517025898572</v>
       </c>
       <c r="Z2" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="AA2" t="n">
-        <v>44.11764705882353</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.73616807324932</v>
+        <v>12.6613735935216</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.197051331201839</v>
+        <v>4.335557232042387</v>
       </c>
       <c r="AE2" t="n">
         <v>42</v>
@@ -788,7 +788,7 @@
         <v>46244</v>
       </c>
       <c r="C3" t="n">
-        <v>0.738929878308468</v>
+        <v>0.7424434547303098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,22 +848,22 @@
         <v>12.13279917920569</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.877289370518632</v>
+        <v>2.415475501421493</v>
       </c>
       <c r="Z3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AA3" t="n">
-        <v>43.10344827586207</v>
+        <v>45</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.88608479467795</v>
+        <v>10.52716613075928</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>7.333723063655196</v>
+        <v>7.772261572775285</v>
       </c>
       <c r="AE3" t="n">
         <v>38</v>
@@ -897,7 +897,7 @@
         <v>46244</v>
       </c>
       <c r="C4" t="n">
-        <v>1.413522983916297</v>
+        <v>1.414627304879296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         <v>23.54405567752772</v>
       </c>
       <c r="K4" t="n">
-        <v>9.44469817207867</v>
+        <v>9.530202317292936</v>
       </c>
       <c r="L4" t="n">
         <v>15</v>
       </c>
       <c r="M4" t="n">
-        <v>46.66666666666666</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N4" t="n">
-        <v>11.66216497550878</v>
+        <v>13.32021955243562</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -967,22 +967,22 @@
         <v>12.1087988317258</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.376352870969478</v>
+        <v>2.300083973161904</v>
       </c>
       <c r="Z4" t="n">
         <v>57</v>
       </c>
       <c r="AA4" t="n">
-        <v>31.57894736842105</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.8808641691881</v>
+        <v>11.55139178328925</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>7.809221795365051</v>
+        <v>7.881190015273843</v>
       </c>
       <c r="AE4" t="n">
         <v>45</v>
@@ -1016,7 +1016,7 @@
         <v>46244</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2646819310545627</v>
+        <v>0.2653081642454355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,22 +1076,22 @@
         <v>16.70172291026088</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.260410214072486</v>
+        <v>5.036257868737726</v>
       </c>
       <c r="Z5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA5" t="n">
-        <v>36.36363636363637</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.12502756887595</v>
+        <v>17.15732167421072</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.002755233199796</v>
+        <v>5.226986658130228</v>
       </c>
       <c r="AE5" t="n">
         <v>44</v>
@@ -1125,7 +1125,7 @@
         <v>46244</v>
       </c>
       <c r="C6" t="n">
-        <v>1.956299100854092</v>
+        <v>1.940000468767032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %89.47: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %88.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1157,16 +1157,16 @@
         <v>23.73506360720576</v>
       </c>
       <c r="K6" t="n">
-        <v>3.037026336025317</v>
+        <v>2.178587775754903</v>
       </c>
       <c r="L6" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M6" t="n">
-        <v>89.47368421052632</v>
+        <v>88</v>
       </c>
       <c r="N6" t="n">
-        <v>12.18640485162359</v>
+        <v>13.17071203308601</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
@@ -1199,7 +1199,7 @@
         <v>44.49622708587002</v>
       </c>
       <c r="Y6" t="n">
-        <v>21.41887740380365</v>
+        <v>22.07356502576511</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1244,21 +1244,21 @@
         <v>46244</v>
       </c>
       <c r="C7" t="n">
-        <v>2.129191097068028</v>
+        <v>2.158119472479225</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1272,22 +1272,22 @@
         <v>11.64775322580256</v>
       </c>
       <c r="K7" t="n">
-        <v>2.34677098672722</v>
+        <v>3.737311186385606</v>
       </c>
       <c r="L7" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M7" t="n">
-        <v>58.57142857142857</v>
+        <v>51.66666666666666</v>
       </c>
       <c r="N7" t="n">
-        <v>12.60717207997788</v>
+        <v>12.43698426543203</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6382507303112739</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1314,16 +1314,16 @@
         <v>13.79329344082609</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.574328332384063</v>
+        <v>8.345754823687468</v>
       </c>
       <c r="Z7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
-        <v>61.11111111111111</v>
+        <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.482902640383853</v>
+        <v>8.645933329578495</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
@@ -1363,7 +1363,7 @@
         <v>46244</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3315334941221773</v>
+        <v>0.3345189957646927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,22 +1391,22 @@
         <v>22.10694516187944</v>
       </c>
       <c r="K8" t="n">
-        <v>5.41034509439966</v>
+        <v>6.359578773641328</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>50</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N8" t="n">
-        <v>17.20097034198387</v>
+        <v>16.4609408474371</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.456736958105199</v>
+        <v>1.54233520410032</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1472,21 +1472,21 @@
         <v>46244</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6102563727247416</v>
+        <v>0.6103136689548196</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>BAND</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>BAND</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1528,17 +1528,27 @@
       <c r="W9" t="n">
         <v>56.60377358490566</v>
       </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
+      <c r="X9" t="n">
+        <v>10.56818998714018</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.6825899835756988</v>
+      </c>
       <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>45</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>11.59898270408642</v>
+      </c>
       <c r="AC9" t="n">
         <v>4</v>
       </c>
-      <c r="AD9" t="inlineStr"/>
+      <c r="AD9" t="n">
+        <v>3.340209955007589</v>
+      </c>
       <c r="AE9" t="n">
         <v>34</v>
       </c>
@@ -1571,7 +1581,7 @@
         <v>46244</v>
       </c>
       <c r="C10" t="n">
-        <v>2.057938606168244</v>
+        <v>2.062692358216615</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,28 +1680,24 @@
         <v>46244</v>
       </c>
       <c r="C11" t="n">
-        <v>7.334811960591262</v>
+        <v>7.513569383089614</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>5</v>
       </c>
@@ -1702,16 +1708,16 @@
         <v>20.56423081971027</v>
       </c>
       <c r="K11" t="n">
-        <v>5.095307350510958</v>
+        <v>7.656595405281341</v>
       </c>
       <c r="L11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M11" t="n">
-        <v>76.47058823529412</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N11" t="n">
-        <v>14.83018974219779</v>
+        <v>13.35789015794225</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1744,22 +1750,22 @@
         <v>10.78465339552526</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.135500153348948</v>
+        <v>2.82354811282034</v>
       </c>
       <c r="Z11" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="AA11" t="n">
-        <v>54.54545454545455</v>
+        <v>44</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.83553485163747</v>
+        <v>11.17460533107513</v>
       </c>
       <c r="AC11" t="n">
         <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>0.1815788534700991</v>
       </c>
       <c r="AE11" t="n">
         <v>46</v>
@@ -1793,7 +1799,7 @@
         <v>46244</v>
       </c>
       <c r="C12" t="n">
-        <v>6.507026039324534</v>
+        <v>6.517352926155192</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,7 +1827,7 @@
         <v>20.08266526523165</v>
       </c>
       <c r="K12" t="n">
-        <v>13.28541102059415</v>
+        <v>13.46519908538817</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -1859,7 +1865,7 @@
         <v>18.9022858703151</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.723941855791725</v>
+        <v>4.572735288585705</v>
       </c>
       <c r="Z12" t="n">
         <v>12</v>
@@ -1868,7 +1874,7 @@
         <v>50</v>
       </c>
       <c r="AB12" t="n">
-        <v>12.53915470955308</v>
+        <v>12.46718403715016</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
@@ -1908,7 +1914,7 @@
         <v>46244</v>
       </c>
       <c r="C13" t="n">
-        <v>0.279141980117954</v>
+        <v>0.2818768160586889</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1936,7 +1942,7 @@
         <v>35.3274613290198</v>
       </c>
       <c r="K13" t="n">
-        <v>1.016334672306196</v>
+        <v>2.00602136345307</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -1947,7 +1953,7 @@
         <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>3.943585302928176</v>
+        <v>2.935099905405814</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -2001,7 +2007,7 @@
         <v>46244</v>
       </c>
       <c r="C14" t="n">
-        <v>8.104967216453344</v>
+        <v>8.12178574627063</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,16 +2067,16 @@
         <v>14.33662537827827</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.332587911898468</v>
+        <v>6.138219678068513</v>
       </c>
       <c r="Z14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA14" t="n">
-        <v>39.28571428571428</v>
+        <v>40.74074074074074</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.75804611379783</v>
+        <v>10.98487553716564</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2110,7 +2116,7 @@
         <v>46244</v>
       </c>
       <c r="C15" t="n">
-        <v>12.80448602263217</v>
+        <v>13.10811127545292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,10 +2173,10 @@
         <v>79.56989247311827</v>
       </c>
       <c r="X15" t="n">
-        <v>21.6463997632442</v>
+        <v>23.91362762258735</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.8921330089213253</v>
+        <v>0.3984063745020028</v>
       </c>
       <c r="Z15" t="n">
         <v>38</v>
@@ -2179,13 +2185,13 @@
         <v>34.21052631578947</v>
       </c>
       <c r="AB15" t="n">
-        <v>12.71812976763059</v>
+        <v>14.22094249277022</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>9.189852700490997</v>
+        <v>9.639999999999993</v>
       </c>
       <c r="AE15" t="n">
         <v>31</v>
@@ -2219,7 +2225,7 @@
         <v>46244</v>
       </c>
       <c r="C16" t="n">
-        <v>38.56015430710835</v>
+        <v>39.30336084831804</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,11 +2242,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>5</v>
       </c>
@@ -2251,16 +2253,16 @@
         <v>17.40096492560246</v>
       </c>
       <c r="K16" t="n">
-        <v>11.14449717342687</v>
+        <v>13.28669081354736</v>
       </c>
       <c r="L16" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="M16" t="n">
-        <v>85.71428571428571</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N16" t="n">
-        <v>21.57061637385742</v>
+        <v>18.71491459123237</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
@@ -2290,25 +2292,25 @@
         <v>77.35849056603773</v>
       </c>
       <c r="X16" t="n">
-        <v>12.29218491597857</v>
+        <v>13.52849805114298</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.02205486820871</v>
+        <v>0.2129925452609149</v>
       </c>
       <c r="Z16" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="AA16" t="n">
-        <v>36.98630136986301</v>
+        <v>35.48387096774194</v>
       </c>
       <c r="AB16" t="n">
-        <v>14.289170281546</v>
+        <v>13.80423727901993</v>
       </c>
       <c r="AC16" t="n">
         <v>5</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.019021739130446</v>
+        <v>4.797225186766285</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -2342,7 +2344,7 @@
         <v>46244</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7657543879658049</v>
+        <v>0.7722250449578594</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2370,16 +2372,16 @@
         <v>14.16674936134154</v>
       </c>
       <c r="K17" t="n">
-        <v>8.755917047497498</v>
+        <v>9.674909150095946</v>
       </c>
       <c r="L17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M17" t="n">
-        <v>65.78947368421052</v>
+        <v>69.44444444444444</v>
       </c>
       <c r="N17" t="n">
-        <v>14.81983602063213</v>
+        <v>14.15831234101636</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
@@ -2412,22 +2414,22 @@
         <v>15.7396793517258</v>
       </c>
       <c r="Y17" t="n">
-        <v>6.034025965291534</v>
+        <v>5.240009507197074</v>
       </c>
       <c r="Z17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA17" t="n">
-        <v>47.22222222222222</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="AB17" t="n">
-        <v>12.18320241180209</v>
+        <v>10.43971091706255</v>
       </c>
       <c r="AC17" t="n">
         <v>8</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.092219077069624</v>
+        <v>2.912611618521155</v>
       </c>
       <c r="AE17" t="n">
         <v>41</v>
@@ -2461,7 +2463,7 @@
         <v>46244</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1045734571324104</v>
+        <v>0.1038162373167213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2489,22 +2491,22 @@
         <v>24.37863714425642</v>
       </c>
       <c r="K18" t="n">
-        <v>4.648528942249652</v>
+        <v>3.890765529135631</v>
       </c>
       <c r="L18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M18" t="n">
-        <v>60</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="N18" t="n">
-        <v>16.1263886239993</v>
+        <v>16.99147144679783</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>5.113756602067077</v>
+        <v>5.880440325710246</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2570,7 +2572,7 @@
         <v>46244</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02556705946275914</v>
+        <v>0.02516757469751851</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2598,22 +2600,22 @@
         <v>18.34152851742537</v>
       </c>
       <c r="K19" t="n">
-        <v>3.51357201465452</v>
+        <v>1.896174633632808</v>
       </c>
       <c r="L19" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="M19" t="n">
-        <v>57.14285714285715</v>
+        <v>62.85714285714285</v>
       </c>
       <c r="N19" t="n">
-        <v>25.37572101645628</v>
+        <v>22.46278047041083</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>6.266258480991449</v>
+        <v>7.95302217723528</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2679,7 +2681,7 @@
         <v>46244</v>
       </c>
       <c r="C20" t="n">
-        <v>1.876664095548926</v>
+        <v>1.867643758494115</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2739,16 +2741,16 @@
         <v>16.29942815131207</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.268203293238949</v>
+        <v>5.723539300428248</v>
       </c>
       <c r="Z20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA20" t="n">
-        <v>45.83333333333334</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB20" t="n">
-        <v>13.92148976383984</v>
+        <v>13.1471808178665</v>
       </c>
       <c r="AC20" t="n">
         <v>4</v>
@@ -2788,7 +2790,7 @@
         <v>46244</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9518489880781407</v>
+        <v>0.9605623783257267</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2816,22 +2818,22 @@
         <v>13.9566823466854</v>
       </c>
       <c r="K21" t="n">
-        <v>1.976893411934677</v>
+        <v>2.910407529892356</v>
       </c>
       <c r="L21" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M21" t="n">
-        <v>55.73770491803279</v>
+        <v>50.87719298245614</v>
       </c>
       <c r="N21" t="n">
-        <v>17.73370807604084</v>
+        <v>16.90554560239201</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>5.906344453674461</v>
+        <v>4.945653789806714</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2897,7 +2899,7 @@
         <v>46244</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3390778851318809</v>
+        <v>0.3397622601992031</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2927,7 @@
         <v>20.35908649698318</v>
       </c>
       <c r="K22" t="n">
-        <v>14.31117310030576</v>
+        <v>14.54189211860968</v>
       </c>
       <c r="L22" t="n">
         <v>2</v>
@@ -2963,22 +2965,22 @@
         <v>19.40139685595055</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.263119100512524</v>
+        <v>4.069889352470069</v>
       </c>
       <c r="Z22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA22" t="n">
-        <v>47.05882352941177</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="AB22" t="n">
-        <v>11.56018940523159</v>
+        <v>11.64897406082421</v>
       </c>
       <c r="AC22" t="n">
         <v>5</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.7696938656912344</v>
+        <v>0.9695711192780565</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3004,16 +3006,16 @@
         <v>46244</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8311389750195075</v>
+        <v>0.8640867112173198</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3029,25 +3031,25 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>18.91837442883233</v>
+        <v>19.72222345813771</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9160321042286146</v>
+        <v>5.967077227757911</v>
       </c>
       <c r="L23" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>68.18181818181819</v>
+        <v>70</v>
       </c>
       <c r="N23" t="n">
-        <v>19.28490917746859</v>
+        <v>18.8115330499001</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.046897019844553</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3074,10 +3076,10 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>18.17564070797</v>
+        <v>14.93198653515787</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
@@ -3119,7 +3121,7 @@
         <v>46244</v>
       </c>
       <c r="C24" t="n">
-        <v>0.18881902129124</v>
+        <v>0.1883373331581377</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3147,7 +3149,7 @@
         <v>22.66030863734194</v>
       </c>
       <c r="K24" t="n">
-        <v>7.876712681174936</v>
+        <v>7.601513011240901</v>
       </c>
       <c r="L24" t="n">
         <v>7</v>
@@ -3156,13 +3158,13 @@
         <v>57.14285714285715</v>
       </c>
       <c r="N24" t="n">
-        <v>10.20060895618112</v>
+        <v>10.47568893942637</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>1.968253635147699</v>
+        <v>2.22904578349985</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3189,7 +3191,7 @@
         <v>12.68278405422394</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.265133678926746</v>
+        <v>4.509358803681929</v>
       </c>
       <c r="Z24" t="n">
         <v>29</v>
@@ -3198,7 +3200,7 @@
         <v>51.72413793103448</v>
       </c>
       <c r="AB24" t="n">
-        <v>15.01891149573349</v>
+        <v>14.95215384139686</v>
       </c>
       <c r="AC24" t="n">
         <v>2</v>
@@ -3238,7 +3240,7 @@
         <v>46244</v>
       </c>
       <c r="C25" t="n">
-        <v>4.149407909134485</v>
+        <v>4.081341654660188</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3337,7 +3339,7 @@
         <v>46244</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4379930491117967</v>
+        <v>0.4437882121957873</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3436,7 +3438,7 @@
         <v>46244</v>
       </c>
       <c r="C27" t="n">
-        <v>38.37154485669314</v>
+        <v>37.54163069289717</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3464,7 +3466,7 @@
         <v>61.00029220182797</v>
       </c>
       <c r="K27" t="n">
-        <v>16.40722498852378</v>
+        <v>13.88952586676666</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3489,25 +3491,25 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>17.80589180979497</v>
+        <v>17.89792817380926</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.187263896384239</v>
+        <v>3.399892066918508</v>
       </c>
       <c r="Z27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA27" t="n">
-        <v>20</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AB27" t="n">
-        <v>10.10968013007894</v>
+        <v>10.01602907091211</v>
       </c>
       <c r="AC27" t="n">
         <v>5</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.858547241944299</v>
+        <v>1.656424581005589</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3531,7 +3533,7 @@
         <v>46244</v>
       </c>
       <c r="C28" t="n">
-        <v>1.477440694919097</v>
+        <v>1.485935462096687</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3559,16 +3561,16 @@
         <v>16.53966926125512</v>
       </c>
       <c r="K28" t="n">
-        <v>5.95942084966552</v>
+        <v>6.568650454268665</v>
       </c>
       <c r="L28" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="M28" t="n">
-        <v>46.42857142857143</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="N28" t="n">
-        <v>17.29337785004663</v>
+        <v>14.74519198998796</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
@@ -3640,7 +3642,7 @@
         <v>46244</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4216469223095378</v>
+        <v>0.4244930707204824</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3668,7 +3670,7 @@
         <v>20.65475273479386</v>
       </c>
       <c r="K29" t="n">
-        <v>16.00337598837525</v>
+        <v>16.7864074935623</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3706,7 +3708,7 @@
         <v>55.05052857749912</v>
       </c>
       <c r="Y29" t="n">
-        <v>7.95683448603689</v>
+        <v>7.33553620208176</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
@@ -3717,7 +3719,7 @@
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.219790576034841</v>
+        <v>2.8753889988819</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3751,7 +3753,7 @@
         <v>46244</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3761710864773436</v>
+        <v>0.3770941355246598</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3779,22 +3781,22 @@
         <v>21.6314445059014</v>
       </c>
       <c r="K30" t="n">
-        <v>1.75770946895808</v>
+        <v>2.007402654210511</v>
       </c>
       <c r="L30" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M30" t="n">
-        <v>52.94117647058823</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="N30" t="n">
-        <v>13.60925753485135</v>
+        <v>10.81922057035711</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>3.186284899652736</v>
+        <v>2.93370605262242</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3860,7 +3862,7 @@
         <v>46244</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1783407184903954</v>
+        <v>0.1858205783100081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3877,11 +3879,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>5</v>
       </c>
@@ -3892,22 +3890,18 @@
         <v>31.09418993049242</v>
       </c>
       <c r="K31" t="n">
-        <v>2.417997046684506</v>
+        <v>6.713551462968659</v>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
-      </c>
-      <c r="M31" t="n">
-        <v>75</v>
-      </c>
-      <c r="N31" t="n">
-        <v>16.18915332817012</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>7.402998664247895</v>
+        <v>3.079691840423671</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3973,7 +3967,7 @@
         <v>46244</v>
       </c>
       <c r="C32" t="n">
-        <v>2.376479107295175</v>
+        <v>2.384627539262812</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4033,22 +4027,22 @@
         <v>15.25475988862757</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.161878588931077</v>
+        <v>1.826412868356375</v>
       </c>
       <c r="Z32" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AA32" t="n">
-        <v>31.11111111111111</v>
+        <v>30.43478260869565</v>
       </c>
       <c r="AB32" t="n">
-        <v>12.64953902913536</v>
+        <v>13.02274589842517</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>5.967123373659156</v>
+        <v>6.288440009190344</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4082,7 +4076,7 @@
         <v>46244</v>
       </c>
       <c r="C33" t="n">
-        <v>1.806459338947972</v>
+        <v>1.819405845032865</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4110,22 +4104,22 @@
         <v>12.57251846431013</v>
       </c>
       <c r="K33" t="n">
-        <v>1.249967699160615</v>
+        <v>1.975604470855585</v>
       </c>
       <c r="L33" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="M33" t="n">
-        <v>61.81818181818182</v>
+        <v>59.32203389830509</v>
       </c>
       <c r="N33" t="n">
-        <v>12.0757370060047</v>
+        <v>12.20835416664673</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>2.716082151265908</v>
+        <v>1.985176297457492</v>
       </c>
       <c r="Q33" t="n">
         <v>39</v>
@@ -4191,7 +4185,7 @@
         <v>46244</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7825196563105701</v>
+        <v>0.7864866765271752</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4216,25 +4210,25 @@
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>18.21448986654661</v>
+        <v>19.24836024850346</v>
       </c>
       <c r="K34" t="n">
-        <v>0.1609478861683611</v>
+        <v>1.957589026325679</v>
       </c>
       <c r="L34" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M34" t="n">
-        <v>64.70588235294117</v>
+        <v>63.88888888888889</v>
       </c>
       <c r="N34" t="n">
-        <v>11.06621659967589</v>
+        <v>11.36426027875977</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>3.83288316939121</v>
+        <v>2.003196616533343</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4300,7 +4294,7 @@
         <v>46244</v>
       </c>
       <c r="C35" t="n">
-        <v>1.925912086858855</v>
+        <v>1.915881511931543</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4319,7 +4313,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %81.82: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4332,16 +4326,16 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>8.573776785164998</v>
+        <v>8.008300608647968</v>
       </c>
       <c r="L35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M35" t="n">
-        <v>80</v>
+        <v>81.81818181818181</v>
       </c>
       <c r="N35" t="n">
-        <v>14.18470627803493</v>
+        <v>13.27568040215743</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4374,7 +4368,7 @@
         <v>38.58137734187126</v>
       </c>
       <c r="Y35" t="n">
-        <v>16.29961036325028</v>
+        <v>16.73554045342692</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -4419,7 +4413,7 @@
         <v>46244</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08382642240675728</v>
+        <v>0.08368218259222122</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4447,7 +4441,7 @@
         <v>17.66670693852417</v>
       </c>
       <c r="K36" t="n">
-        <v>4.77172318584862</v>
+        <v>4.591442869844919</v>
       </c>
       <c r="L36" t="n">
         <v>14</v>
@@ -4456,7 +4450,7 @@
         <v>57.14285714285715</v>
       </c>
       <c r="N36" t="n">
-        <v>13.7664191568117</v>
+        <v>14.09899135848872</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4528,7 +4522,7 @@
         <v>46244</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06601330974098192</v>
+        <v>0.06627461249625799</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4556,22 +4550,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>7.458522772889276</v>
+        <v>7.883879540920269</v>
       </c>
       <c r="L37" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M37" t="n">
-        <v>62.85714285714285</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N37" t="n">
-        <v>18.87520782182908</v>
+        <v>15.0620484694513</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>0.5038941659891716</v>
+        <v>0.1076346712538312</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4637,7 +4631,7 @@
         <v>46244</v>
       </c>
       <c r="C38" t="n">
-        <v>1.630423979729076</v>
+        <v>1.632746308381759</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4665,22 +4659,22 @@
         <v>14.71604491689452</v>
       </c>
       <c r="K38" t="n">
-        <v>2.908725754824659</v>
+        <v>3.05530596058885</v>
       </c>
       <c r="L38" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M38" t="n">
-        <v>56.36363636363637</v>
+        <v>56.60377358490566</v>
       </c>
       <c r="N38" t="n">
-        <v>13.56277763441883</v>
+        <v>13.20718576230645</v>
       </c>
       <c r="O38" t="n">
         <v>6</v>
       </c>
       <c r="P38" t="n">
-        <v>3.003899059580406</v>
+        <v>2.857391972168122</v>
       </c>
       <c r="Q38" t="n">
         <v>34</v>
@@ -4746,7 +4740,7 @@
         <v>46244</v>
       </c>
       <c r="C39" t="n">
-        <v>2.671967214215388</v>
+        <v>2.682443923497342</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4774,16 +4768,16 @@
         <v>16.13238434452433</v>
       </c>
       <c r="K39" t="n">
-        <v>5.768486168842646</v>
+        <v>6.183201467326827</v>
       </c>
       <c r="L39" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="M39" t="n">
-        <v>70</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N39" t="n">
-        <v>12.24070780756101</v>
+        <v>12.27545027216149</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4816,22 +4810,22 @@
         <v>10.2437411865161</v>
       </c>
       <c r="Y39" t="n">
-        <v>4.059418674935921</v>
+        <v>3.683238318554016</v>
       </c>
       <c r="Z39" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AA39" t="n">
-        <v>45.45454545454545</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB39" t="n">
-        <v>14.00849739507054</v>
+        <v>13.51254539176915</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.022690813691286</v>
+        <v>2.405356701161065</v>
       </c>
       <c r="AE39" t="n">
         <v>46</v>
@@ -4865,7 +4859,7 @@
         <v>46244</v>
       </c>
       <c r="C40" t="n">
-        <v>0.208937363507126</v>
+        <v>0.2181189636538049</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4922,25 +4916,25 @@
         <v>76.47058823529412</v>
       </c>
       <c r="X40" t="n">
-        <v>18.14352984100791</v>
+        <v>19.81060928895926</v>
       </c>
       <c r="Y40" t="n">
-        <v>3.415006199347725</v>
+        <v>0.5736177798332132</v>
       </c>
       <c r="Z40" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA40" t="n">
-        <v>38.09523809523809</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="AB40" t="n">
-        <v>12.40472491959226</v>
+        <v>12.20092311358603</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.641035256391532</v>
+        <v>4.45191922035858</v>
       </c>
       <c r="AE40" t="n">
         <v>14</v>
@@ -4974,7 +4968,7 @@
         <v>46244</v>
       </c>
       <c r="C41" t="n">
-        <v>1.710058985034242</v>
+        <v>1.712443689113826</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5006,7 +5000,7 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>13.01033792173563</v>
+        <v>13.16793261071165</v>
       </c>
       <c r="L41" t="n">
         <v>5</v>
@@ -5048,7 +5042,7 @@
         <v>36.58819281794096</v>
       </c>
       <c r="Y41" t="n">
-        <v>12.30260043656527</v>
+        <v>12.18030503720299</v>
       </c>
       <c r="Z41" t="n">
         <v>3</v>
@@ -5097,7 +5091,7 @@
         <v>46244</v>
       </c>
       <c r="C42" t="n">
-        <v>3.589866603487027</v>
+        <v>3.657687242367217</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5125,7 +5119,7 @@
         <v>18.35939977786119</v>
       </c>
       <c r="K42" t="n">
-        <v>16.79704756368494</v>
+        <v>19.00360598493511</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5158,25 +5152,25 @@
       </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="n">
-        <v>18.29706591648155</v>
+        <v>20.0953863872158</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.268009769452461</v>
+        <v>0.9090943749999969</v>
       </c>
       <c r="Z42" t="n">
         <v>6</v>
       </c>
       <c r="AA42" t="n">
-        <v>66.66666666666667</v>
+        <v>50</v>
       </c>
       <c r="AB42" t="n">
-        <v>12.42836034283877</v>
+        <v>13.05682117011112</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>8.8441347228569</v>
+        <v>9.174308749789473</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5208,7 +5202,7 @@
         <v>46244</v>
       </c>
       <c r="C43" t="n">
-        <v>7.209072326981126</v>
+        <v>7.22519093502965</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5268,7 +5262,7 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>6.950149605501988</v>
+        <v>6.742101468452599</v>
       </c>
       <c r="Z43" t="n">
         <v>10</v>
@@ -5317,7 +5311,7 @@
         <v>46244</v>
       </c>
       <c r="C44" t="n">
-        <v>5.086168115612351</v>
+        <v>5.060779665194446</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5336,7 +5330,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.95: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %78.26: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -5349,22 +5343,22 @@
         <v>13.03201987649729</v>
       </c>
       <c r="K44" t="n">
-        <v>4.100361258976193</v>
+        <v>3.580727066744771</v>
       </c>
       <c r="L44" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M44" t="n">
-        <v>80.95238095238095</v>
+        <v>78.26086956521739</v>
       </c>
       <c r="N44" t="n">
-        <v>20.49521452087832</v>
+        <v>19.86668303814072</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>5.667260583608313</v>
+        <v>6.197362303818177</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5391,22 +5385,22 @@
         <v>12.1234692799834</v>
       </c>
       <c r="Y44" t="n">
-        <v>7.155600939329398</v>
+        <v>7.619049132262001</v>
       </c>
       <c r="Z44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA44" t="n">
-        <v>18.18181818181818</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="AB44" t="n">
-        <v>8.772956734278921</v>
+        <v>9.691917834769438</v>
       </c>
       <c r="AC44" t="n">
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>3.063619442258314</v>
+        <v>2.577317991830164</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5432,7 +5426,7 @@
         <v>46244</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02158530314104183</v>
+        <v>0.02139243718207961</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5531,11 +5525,11 @@
         <v>46244</v>
       </c>
       <c r="C46" t="n">
-        <v>9.357124401154282</v>
+        <v>9.1599481592865</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5545,7 +5539,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -5559,16 +5553,16 @@
         <v>20.92024905883424</v>
       </c>
       <c r="K46" t="n">
-        <v>13.32037785144347</v>
+        <v>10.93245552895854</v>
       </c>
       <c r="L46" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M46" t="n">
-        <v>53.84615384615385</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="N46" t="n">
-        <v>12.63146762234659</v>
+        <v>14.41348684240534</v>
       </c>
       <c r="O46" t="n">
         <v>10</v>
@@ -5601,22 +5595,22 @@
         <v>16.0625044063383</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.362629144460437</v>
+        <v>4.420074255350626</v>
       </c>
       <c r="Z46" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AA46" t="n">
-        <v>37.5</v>
+        <v>32.35294117647059</v>
       </c>
       <c r="AB46" t="n">
-        <v>12.1758723098851</v>
+        <v>13.91659552208615</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.6527939557923967</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
         <v>37</v>
@@ -5650,7 +5644,7 @@
         <v>46244</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7494081811093126</v>
+        <v>0.7382488429729719</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,25 +5669,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>25.22913744871184</v>
+        <v>25.80558454936143</v>
       </c>
       <c r="K47" t="n">
-        <v>1.131215223697923</v>
+        <v>0.3993137037347605</v>
       </c>
       <c r="L47" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M47" t="n">
-        <v>57.69230769230769</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N47" t="n">
-        <v>13.24296250924603</v>
+        <v>13.51380842266347</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>8.769581930450165</v>
+        <v>9.562501915695965</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5759,7 +5753,7 @@
         <v>46244</v>
       </c>
       <c r="C48" t="n">
-        <v>0.06182198757281377</v>
+        <v>0.06040217906431464</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5787,22 +5781,22 @@
         <v>20.70237270975156</v>
       </c>
       <c r="K48" t="n">
-        <v>5.341751008234596</v>
+        <v>2.922464274602321</v>
       </c>
       <c r="L48" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="M48" t="n">
-        <v>55.17241379310344</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N48" t="n">
-        <v>14.23814929331134</v>
+        <v>16.2937831569074</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>4.422034898016158</v>
+        <v>6.876570411795102</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5868,7 +5862,7 @@
         <v>46244</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2590236381116341</v>
+        <v>0.2571287156030694</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5896,22 +5890,22 @@
         <v>21.9393534200744</v>
       </c>
       <c r="K49" t="n">
-        <v>2.505601756331188</v>
+        <v>1.755708142612722</v>
       </c>
       <c r="L49" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M49" t="n">
-        <v>60.8695652173913</v>
+        <v>60</v>
       </c>
       <c r="N49" t="n">
-        <v>10.2084549776116</v>
+        <v>10.66615203453425</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>2.433426272252248</v>
+        <v>3.188314362512568</v>
       </c>
       <c r="Q49" t="n">
         <v>53</v>
@@ -5977,7 +5971,7 @@
         <v>46244</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7129437322095092</v>
+        <v>0.7118228459692154</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6002,25 +5996,25 @@
         <v>10</v>
       </c>
       <c r="J50" t="n">
-        <v>10.41400888746848</v>
+        <v>11.29749771777515</v>
       </c>
       <c r="K50" t="n">
-        <v>0.1732269359833394</v>
+        <v>1.011905284173031</v>
       </c>
       <c r="L50" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M50" t="n">
-        <v>42.5531914893617</v>
+        <v>40.38461538461539</v>
       </c>
       <c r="N50" t="n">
-        <v>13.684937882731</v>
+        <v>13.72535370926058</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>3.820155525649782</v>
+        <v>2.958160929071352</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6086,7 +6080,7 @@
         <v>46244</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1904955480628467</v>
+        <v>0.1900151898576163</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6118,7 +6112,7 @@
         <v>27.11346359280836</v>
       </c>
       <c r="K51" t="n">
-        <v>10.41145083301693</v>
+        <v>10.13303463432689</v>
       </c>
       <c r="L51" t="n">
         <v>5</v>
@@ -6127,7 +6121,7 @@
         <v>80</v>
       </c>
       <c r="N51" t="n">
-        <v>22.187736672458</v>
+        <v>22.72871476502574</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
@@ -6160,17 +6154,13 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>13.52161478892544</v>
+        <v>13.73968078749415</v>
       </c>
       <c r="Z51" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>11.13314894388493</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
         <v>10</v>
       </c>
@@ -6209,7 +6199,7 @@
         <v>46244</v>
       </c>
       <c r="C52" t="n">
-        <v>4.21018193754409</v>
+        <v>4.286876583588957</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6269,22 +6259,22 @@
         <v>12.1710603868542</v>
       </c>
       <c r="Y52" t="n">
-        <v>3.397710702437784</v>
+        <v>1.637958156180319</v>
       </c>
       <c r="Z52" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="AA52" t="n">
-        <v>35</v>
+        <v>37.5</v>
       </c>
       <c r="AB52" t="n">
-        <v>13.31268153984237</v>
+        <v>12.06351788347552</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>4.764161730562999</v>
+        <v>6.467984727199338</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6318,7 +6308,7 @@
         <v>46244</v>
       </c>
       <c r="C53" t="n">
-        <v>1.628328191333613</v>
+        <v>1.588703086584894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6337,7 +6327,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -6350,22 +6340,22 @@
         <v>28.17598592067425</v>
       </c>
       <c r="K53" t="n">
-        <v>7.352449428939978</v>
+        <v>4.740044831209977</v>
       </c>
       <c r="L53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M53" t="n">
-        <v>100</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N53" t="n">
-        <v>12.63443633390716</v>
+        <v>14.26016933944701</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>0.6032005552781161</v>
+        <v>3.112424836215699</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6423,7 +6413,7 @@
         <v>46244</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08382642240675728</v>
+        <v>0.08389191216289869</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6451,7 +6441,7 @@
         <v>42.39442432818535</v>
       </c>
       <c r="K54" t="n">
-        <v>3.707075276264904</v>
+        <v>3.788096878702207</v>
       </c>
       <c r="L54" t="n">
         <v>5</v>
@@ -6466,7 +6456,7 @@
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>6.067980132475448</v>
+        <v>5.985178751815523</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6493,7 +6483,7 @@
         <v>114.7400208810756</v>
       </c>
       <c r="Y54" t="n">
-        <v>40.25894227470545</v>
+        <v>40.21226931420291</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -6538,7 +6528,7 @@
         <v>46244</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8181459019700281</v>
+        <v>0.8456304681003957</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6566,22 +6556,22 @@
         <v>15.124509340431</v>
       </c>
       <c r="K55" t="n">
-        <v>0.7562545318334557</v>
+        <v>4.141032154089119</v>
       </c>
       <c r="L55" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="M55" t="n">
-        <v>70</v>
+        <v>71.15384615384616</v>
       </c>
       <c r="N55" t="n">
-        <v>14.00276981247055</v>
+        <v>13.38061250851474</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>5.204387055207382</v>
+        <v>1.785048416996982</v>
       </c>
       <c r="Q55" t="n">
         <v>44</v>
@@ -6608,16 +6598,16 @@
         <v>25.41488056506582</v>
       </c>
       <c r="Y55" t="n">
-        <v>14.48263459590213</v>
+        <v>11.60978798127735</v>
       </c>
       <c r="Z55" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AA55" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AB55" t="n">
-        <v>12.49559209226058</v>
+        <v>9.686169325397467</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6657,7 +6647,7 @@
         <v>46244</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9049062363774925</v>
+        <v>0.8984823824105918</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6685,7 +6675,7 @@
         <v>34.38683570496719</v>
       </c>
       <c r="K56" t="n">
-        <v>15.39496973636898</v>
+        <v>14.57579046198487</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6715,13 +6705,13 @@
         <v>21.95662732854271</v>
       </c>
       <c r="Y56" t="n">
-        <v>5.38032064013797</v>
+        <v>6.052017859328274</v>
       </c>
       <c r="Z56" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA56" t="n">
-        <v>33.33333333333334</v>
+        <v>37.5</v>
       </c>
       <c r="AB56" t="n">
         <v>14.70795307963829</v>
@@ -6730,7 +6720,7 @@
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>4.882366322857901</v>
+        <v>4.202306479302842</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6756,7 +6746,7 @@
         <v>46244</v>
       </c>
       <c r="C57" t="n">
-        <v>1.476392800721365</v>
+        <v>1.453427442189803</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6773,7 +6763,11 @@
           <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>5</v>
       </c>
@@ -6784,10 +6778,10 @@
         <v>32.76213282665623</v>
       </c>
       <c r="K57" t="n">
-        <v>26.4194173168443</v>
+        <v>24.45295741361664</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -6822,16 +6816,16 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>8.979567904882412</v>
+        <v>10.39539495019229</v>
       </c>
       <c r="Z57" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AA57" t="n">
-        <v>63.63636363636363</v>
+        <v>75</v>
       </c>
       <c r="AB57" t="n">
-        <v>13.83153316962987</v>
+        <v>13.51506266023374</v>
       </c>
       <c r="AC57" t="n">
         <v>6</v>
@@ -6871,16 +6865,16 @@
         <v>46244</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7850344265592049</v>
+        <v>0.7625774943542657</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6890,7 +6884,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.26: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -6903,22 +6897,22 @@
         <v>16.33691982084211</v>
       </c>
       <c r="K58" t="n">
-        <v>5.830704434910028</v>
+        <v>2.803279300050043</v>
       </c>
       <c r="L58" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M58" t="n">
-        <v>78.26086956521739</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N58" t="n">
-        <v>16.33740473192407</v>
+        <v>20.15533012800163</v>
       </c>
       <c r="O58" t="n">
         <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.136819676285251</v>
       </c>
       <c r="Q58" t="n">
         <v>24</v>
@@ -6945,10 +6939,10 @@
         <v>41.32985472592288</v>
       </c>
       <c r="Y58" t="n">
-        <v>11.45877289445363</v>
+        <v>13.9916100123955</v>
       </c>
       <c r="Z58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="inlineStr"/>
       <c r="AB58" t="inlineStr"/>
@@ -6990,7 +6984,7 @@
         <v>46244</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8194032469624459</v>
+        <v>0.8263353668932085</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7050,22 +7044,22 @@
         <v>10.2478061424703</v>
       </c>
       <c r="Y59" t="n">
-        <v>6.960098725981679</v>
+        <v>6.172984742276211</v>
       </c>
       <c r="Z59" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AA59" t="n">
         <v>50</v>
       </c>
       <c r="AB59" t="n">
-        <v>15.44866820059028</v>
+        <v>15.12318601205643</v>
       </c>
       <c r="AC59" t="n">
         <v>10</v>
       </c>
       <c r="AD59" t="n">
-        <v>3.267309221519155</v>
+        <v>4.078798890928958</v>
       </c>
       <c r="AE59" t="n">
         <v>43</v>
@@ -7099,16 +7093,16 @@
         <v>46244</v>
       </c>
       <c r="C60" t="n">
-        <v>13.57988042989468</v>
+        <v>13.82119252883756</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -7127,22 +7121,22 @@
         <v>14.21636055978318</v>
       </c>
       <c r="K60" t="n">
-        <v>6.872177742187846</v>
+        <v>8.771277639473475</v>
       </c>
       <c r="L60" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M60" t="n">
-        <v>51.35135135135135</v>
+        <v>58.06451612903226</v>
       </c>
       <c r="N60" t="n">
-        <v>12.90110247085263</v>
+        <v>11.95211381735988</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>1.055300155418237</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7208,7 +7202,7 @@
         <v>46244</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6236685875262934</v>
+        <v>0.6505817884708492</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7236,22 +7230,22 @@
         <v>30.3360843704085</v>
       </c>
       <c r="K61" t="n">
-        <v>1.491520257703671</v>
+        <v>5.871188776360436</v>
       </c>
       <c r="L61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M61" t="n">
-        <v>66.66666666666667</v>
+        <v>50</v>
       </c>
       <c r="N61" t="n">
-        <v>12.22538449547143</v>
+        <v>15.2992064867625</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>8.383439050564911</v>
+        <v>3.899844019283827</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7309,7 +7303,7 @@
         <v>46244</v>
       </c>
       <c r="C62" t="n">
-        <v>9.142319193736965</v>
+        <v>8.960704867899617</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7323,10 +7317,14 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>BAND</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>SATMA_BEKLE</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H62" t="n">
         <v>5</v>
       </c>
@@ -7337,16 +7335,16 @@
         <v>10.67683828611802</v>
       </c>
       <c r="K62" t="n">
-        <v>9.872581738648334</v>
+        <v>7.689937002929237</v>
       </c>
       <c r="L62" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M62" t="n">
-        <v>70.37037037037037</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="N62" t="n">
-        <v>11.75173400008662</v>
+        <v>12.65658828717897</v>
       </c>
       <c r="O62" t="n">
         <v>6</v>
@@ -7375,17 +7373,27 @@
       <c r="W62" t="n">
         <v>73.13432835820896</v>
       </c>
-      <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
+      <c r="X62" t="n">
+        <v>10.71458122536377</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>2.731929425156521</v>
+      </c>
       <c r="Z62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" t="inlineStr"/>
-      <c r="AB62" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>39.58333333333334</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>16.61073097776234</v>
+      </c>
       <c r="AC62" t="n">
         <v>2</v>
       </c>
-      <c r="AD62" t="inlineStr"/>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
       <c r="AE62" t="n">
         <v>30</v>
       </c>
@@ -7418,7 +7426,7 @@
         <v>46244</v>
       </c>
       <c r="C63" t="n">
-        <v>0.102477798667902</v>
+        <v>0.1029773190340114</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7435,7 +7443,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H63" t="n">
         <v>5</v>
       </c>
@@ -7446,22 +7458,22 @@
         <v>28.76464722640304</v>
       </c>
       <c r="K63" t="n">
-        <v>2.697028287381209</v>
+        <v>3.19761727187633</v>
       </c>
       <c r="L63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M63" t="n">
-        <v>60</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N63" t="n">
-        <v>13.09147462811611</v>
+        <v>12.56793181945185</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>2.242491093485488</v>
+        <v>1.746535216385148</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7488,22 +7500,22 @@
         <v>10.24796802016521</v>
       </c>
       <c r="Y63" t="n">
-        <v>6.84905116020178</v>
+        <v>6.39499382609875</v>
       </c>
       <c r="Z63" t="n">
         <v>11</v>
       </c>
       <c r="AA63" t="n">
-        <v>54.54545454545455</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="AB63" t="n">
-        <v>12.44107905981065</v>
+        <v>12.49876729611108</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>3.382626671057587</v>
+        <v>3.85129633686877</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7537,7 +7549,7 @@
         <v>46244</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1594797713532145</v>
+        <v>0.1596043656164019</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7562,25 +7574,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>20.58679888238519</v>
+        <v>21.47552816415833</v>
       </c>
       <c r="K64" t="n">
-        <v>2.616515270915243</v>
+        <v>3.858991966646474</v>
       </c>
       <c r="L64" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M64" t="n">
-        <v>59.52380952380953</v>
+        <v>64.86486486486487</v>
       </c>
       <c r="N64" t="n">
-        <v>12.54705725435966</v>
+        <v>14.10469386361876</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>2.322710650222515</v>
+        <v>1.098612659094522</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7646,7 +7658,7 @@
         <v>46244</v>
       </c>
       <c r="C65" t="n">
-        <v>5.825936357269631</v>
+        <v>6.029731186708344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7678,7 +7690,7 @@
         <v>32.91027483217498</v>
       </c>
       <c r="K65" t="n">
-        <v>2.838137119475914</v>
+        <v>6.435478272697948</v>
       </c>
       <c r="L65" t="n">
         <v>5</v>
@@ -7687,13 +7699,13 @@
         <v>80</v>
       </c>
       <c r="N65" t="n">
-        <v>20.04918278117306</v>
+        <v>19.15715795420472</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>6.964209077614414</v>
+        <v>3.348997707483781</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7759,7 +7771,7 @@
         <v>46244</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4367356638826963</v>
+        <v>0.443368742987403</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7858,7 +7870,7 @@
         <v>46244</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02808185213496186</v>
+        <v>0.0281037912037604</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7886,7 +7898,7 @@
         <v>18.49825117353735</v>
       </c>
       <c r="K67" t="n">
-        <v>4.29775840786859</v>
+        <v>4.379241484064833</v>
       </c>
       <c r="L67" t="n">
         <v>1</v>
@@ -7914,7 +7926,7 @@
         <v>10.87173616493582</v>
       </c>
       <c r="Y67" t="n">
-        <v>5.929354030577805</v>
+        <v>5.855860930338974</v>
       </c>
       <c r="Z67" t="n">
         <v>3</v>
@@ -7951,7 +7963,7 @@
         <v>46244</v>
       </c>
       <c r="C68" t="n">
-        <v>3.453648667076047</v>
+        <v>3.403914399977197</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7970,7 +7982,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %94.12: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %92.86: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -7980,25 +7992,25 @@
         <v>10</v>
       </c>
       <c r="J68" t="n">
-        <v>16.5796986006275</v>
+        <v>17.33552180626085</v>
       </c>
       <c r="K68" t="n">
-        <v>1.290722888363272</v>
+        <v>0.7448770357308954</v>
       </c>
       <c r="L68" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M68" t="n">
-        <v>94.11764705882354</v>
+        <v>92.85714285714286</v>
       </c>
       <c r="N68" t="n">
-        <v>15.24835904859901</v>
+        <v>16.59375163464654</v>
       </c>
       <c r="O68" t="n">
         <v>2</v>
       </c>
       <c r="P68" t="n">
-        <v>0.700238967016209</v>
+        <v>1.245842966113253</v>
       </c>
       <c r="Q68" t="n">
         <v>5</v>
@@ -8025,7 +8037,7 @@
         <v>128.0325939207301</v>
       </c>
       <c r="Y68" t="n">
-        <v>15.50297367692418</v>
+        <v>16.71977309148891</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -8070,7 +8082,7 @@
         <v>46244</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4241616925581725</v>
+        <v>0.4202984992312623</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8089,7 +8101,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H69" t="n">
@@ -8102,16 +8114,16 @@
         <v>29.4573350207784</v>
       </c>
       <c r="K69" t="n">
-        <v>8.499055223415365</v>
+        <v>7.510864084354218</v>
       </c>
       <c r="L69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M69" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N69" t="n">
-        <v>21.5371107368305</v>
+        <v>21.84733273523247</v>
       </c>
       <c r="O69" t="n">
         <v>3</v>
@@ -8167,7 +8179,7 @@
         <v>46244</v>
       </c>
       <c r="C70" t="n">
-        <v>0.3900024430309676</v>
+        <v>0.3997449503405339</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8195,22 +8207,22 @@
         <v>21.94656073986526</v>
       </c>
       <c r="K70" t="n">
-        <v>1.681828829137344</v>
+        <v>4.221905124349878</v>
       </c>
       <c r="L70" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M70" t="n">
-        <v>66.66666666666667</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N70" t="n">
-        <v>13.69136707203828</v>
+        <v>11.56447238634469</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>6.213667912562326</v>
+        <v>3.62504875644174</v>
       </c>
       <c r="Q70" t="n">
         <v>30</v>
@@ -8276,7 +8288,7 @@
         <v>46244</v>
       </c>
       <c r="C71" t="n">
-        <v>3.223126005457464</v>
+        <v>3.204671108590313</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8304,22 +8316,22 @@
         <v>18.95735500740921</v>
       </c>
       <c r="K71" t="n">
-        <v>2.883507522554241</v>
+        <v>2.294419625449184</v>
       </c>
       <c r="L71" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M71" t="n">
-        <v>66.66666666666667</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N71" t="n">
-        <v>14.5090794565403</v>
+        <v>14.30912419081266</v>
       </c>
       <c r="O71" t="n">
         <v>6</v>
       </c>
       <c r="P71" t="n">
-        <v>3.02914680155375</v>
+        <v>3.622465808124042</v>
       </c>
       <c r="Q71" t="n">
         <v>43</v>
@@ -8385,7 +8397,7 @@
         <v>46244</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07753944177408076</v>
+        <v>0.07739029022865272</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8413,7 +8425,7 @@
         <v>20.36571476939619</v>
       </c>
       <c r="K72" t="n">
-        <v>8.404924654760059</v>
+        <v>8.196401589925827</v>
       </c>
       <c r="L72" t="n">
         <v>13</v>
@@ -8455,7 +8467,7 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>13.67251309640721</v>
+        <v>13.8385689486289</v>
       </c>
       <c r="Z72" t="n">
         <v>1</v>
@@ -8500,7 +8512,7 @@
         <v>46244</v>
       </c>
       <c r="C73" t="n">
-        <v>0.06999506082354782</v>
+        <v>0.06900109691506505</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8525,25 +8537,25 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>22.14049070857409</v>
+        <v>22.88332385411211</v>
       </c>
       <c r="K73" t="n">
-        <v>1.783114091909765</v>
+        <v>1.304256487155864</v>
       </c>
       <c r="L73" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M73" t="n">
-        <v>72.72727272727273</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N73" t="n">
-        <v>15.63995587073383</v>
+        <v>16.2002307703648</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>8.072936244287465</v>
+        <v>8.583788889410249</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8609,7 +8621,7 @@
         <v>46244</v>
       </c>
       <c r="C74" t="n">
-        <v>5.037967858810818</v>
+        <v>5.07755811159461</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8637,22 +8649,22 @@
         <v>18.35970785011217</v>
       </c>
       <c r="K74" t="n">
-        <v>6.588784999445751</v>
+        <v>7.426399899005953</v>
       </c>
       <c r="L74" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="M74" t="n">
-        <v>56</v>
+        <v>72.22222222222223</v>
       </c>
       <c r="N74" t="n">
-        <v>18.9315259078591</v>
+        <v>21.71559040851504</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>1.323980755162557</v>
+        <v>0.533947057272055</v>
       </c>
       <c r="Q74" t="n">
         <v>35</v>
@@ -8679,10 +8691,10 @@
         <v>59.69432739383429</v>
       </c>
       <c r="Y74" t="n">
-        <v>12.98060452743668</v>
+        <v>12.29677327634475</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA74" t="inlineStr"/>
       <c r="AB74" t="inlineStr"/>
@@ -8724,7 +8736,7 @@
         <v>46244</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1297213899318532</v>
+        <v>0.1289838170477546</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8741,11 +8753,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>5</v>
       </c>
@@ -8756,22 +8764,22 @@
         <v>21.52133760858017</v>
       </c>
       <c r="K75" t="n">
-        <v>2.528946543134447</v>
+        <v>1.94598508361612</v>
       </c>
       <c r="L75" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M75" t="n">
-        <v>83.33333333333333</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N75" t="n">
-        <v>17.14542780110784</v>
+        <v>14.07085928325531</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>3.385437550950821</v>
+        <v>3.976630284222349</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8837,7 +8845,7 @@
         <v>46244</v>
       </c>
       <c r="C76" t="n">
-        <v>1.852563967252942</v>
+        <v>1.872887003004296</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8865,22 +8873,22 @@
         <v>18.36583782901725</v>
       </c>
       <c r="K76" t="n">
-        <v>6.888854873692885</v>
+        <v>8.061449211820126</v>
       </c>
       <c r="L76" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M76" t="n">
-        <v>38.09523809523809</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="N76" t="n">
-        <v>14.44637822264828</v>
+        <v>13.37029545732525</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>2.910635659801453</v>
+        <v>1.793933731519703</v>
       </c>
       <c r="Q76" t="n">
         <v>40</v>
@@ -8946,7 +8954,7 @@
         <v>46244</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5318786325673263</v>
+        <v>0.5272606551503016</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8974,16 +8982,16 @@
         <v>20.36657537342047</v>
       </c>
       <c r="K77" t="n">
-        <v>9.543614866042493</v>
+        <v>8.592514542292239</v>
       </c>
       <c r="L77" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M77" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N77" t="n">
-        <v>15.91559869114716</v>
+        <v>10.35289348072587</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -9016,22 +9024,22 @@
         <v>14.86223722874125</v>
       </c>
       <c r="Y77" t="n">
-        <v>4.630435982286352</v>
+        <v>5.458471676782017</v>
       </c>
       <c r="Z77" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="AA77" t="n">
-        <v>48.07692307692308</v>
+        <v>46.80851063829788</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.71375424262182</v>
+        <v>12.48273666248703</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>5.630270068883103</v>
+        <v>4.803739059190404</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9065,21 +9073,21 @@
         <v>46244</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05469673852474857</v>
+        <v>0.05222271553113422</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -9093,22 +9101,22 @@
         <v>12.76206508896208</v>
       </c>
       <c r="K78" t="n">
-        <v>7.957428620049378</v>
+        <v>3.074337453349707</v>
       </c>
       <c r="L78" t="n">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="M78" t="n">
-        <v>60.97560975609756</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="N78" t="n">
-        <v>16.82932389301555</v>
+        <v>16.24530698554662</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>0.8980533559764581</v>
       </c>
       <c r="Q78" t="n">
         <v>45</v>
@@ -9135,22 +9143,22 @@
         <v>23.16536029857119</v>
       </c>
       <c r="Y78" t="n">
-        <v>5.820168688811112</v>
+        <v>10.08007658246322</v>
       </c>
       <c r="Z78" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AA78" t="n">
-        <v>58.33333333333334</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB78" t="n">
-        <v>13.72480224961067</v>
+        <v>14.37178883655818</v>
       </c>
       <c r="AC78" t="n">
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>4.438138455969298</v>
+        <v>0</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9184,7 +9192,7 @@
         <v>46244</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8701182742221791</v>
+        <v>0.8716369961054974</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9209,25 +9217,25 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>11.87218353498292</v>
+        <v>12.03872531442141</v>
       </c>
       <c r="K79" t="n">
-        <v>0.8013243277523951</v>
+        <v>1.168450629545648</v>
       </c>
       <c r="L79" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M79" t="n">
-        <v>55.93220338983051</v>
+        <v>60</v>
       </c>
       <c r="N79" t="n">
-        <v>11.30416543619934</v>
+        <v>10.88225231662067</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>4.165298125048178</v>
+        <v>3.787296678570828</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9293,7 +9301,7 @@
         <v>46244</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1278352920746443</v>
+        <v>0.1268865211312501</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9321,7 +9329,7 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>4.662559309483361</v>
+        <v>3.885772292983058</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9332,7 +9340,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>5.099665750322457</v>
+        <v>5.885529434938741</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9359,22 +9367,22 @@
         <v>11.74527658842108</v>
       </c>
       <c r="Y80" t="n">
-        <v>6.338269943189367</v>
+        <v>7.033410749329527</v>
       </c>
       <c r="Z80" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA80" t="n">
-        <v>34.375</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="AB80" t="n">
-        <v>12.14812307065434</v>
+        <v>11.68474670222619</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.77418253517494</v>
+        <v>1.039716804135093</v>
       </c>
       <c r="AE80" t="n">
         <v>26</v>
@@ -9408,7 +9416,7 @@
         <v>46244</v>
       </c>
       <c r="C81" t="n">
-        <v>1.087647862791282</v>
+        <v>1.098984081422629</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9436,22 +9444,22 @@
         <v>12.04277302023445</v>
       </c>
       <c r="K81" t="n">
-        <v>3.848756473575299</v>
+        <v>4.931140072396256</v>
       </c>
       <c r="L81" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="M81" t="n">
-        <v>43.47826086956522</v>
+        <v>55.88235294117647</v>
       </c>
       <c r="N81" t="n">
-        <v>14.77634724828385</v>
+        <v>14.21779494451872</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>5.923271241085981</v>
+        <v>4.83065363066344</v>
       </c>
       <c r="Q81" t="n">
         <v>31</v>
@@ -9478,22 +9486,22 @@
         <v>27.31228182970742</v>
       </c>
       <c r="Y81" t="n">
-        <v>8.65751355287342</v>
+        <v>7.705478954066702</v>
       </c>
       <c r="Z81" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA81" t="n">
-        <v>22.22222222222222</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB81" t="n">
-        <v>14.43690406407305</v>
+        <v>13.07901409604973</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.469728380892799</v>
+        <v>2.486085869378263</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9527,7 +9535,7 @@
         <v>46244</v>
       </c>
       <c r="C82" t="n">
-        <v>5.459195759240068</v>
+        <v>5.500163491180046</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9584,10 +9592,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="X82" t="n">
-        <v>21.7292569078541</v>
+        <v>21.79199953349134</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.351967345653282</v>
+        <v>0.6628787878787845</v>
       </c>
       <c r="Z82" t="n">
         <v>9</v>
@@ -9596,13 +9604,13 @@
         <v>44.44444444444444</v>
       </c>
       <c r="AB82" t="n">
-        <v>11.75788225422557</v>
+        <v>12.19745974005039</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>2.684323836061864</v>
+        <v>3.359389895138232</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9636,7 +9644,7 @@
         <v>46244</v>
       </c>
       <c r="C83" t="n">
-        <v>5.736870783462451</v>
+        <v>5.694163538056749</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9664,22 +9672,22 @@
         <v>12.20482860933025</v>
       </c>
       <c r="K83" t="n">
-        <v>5.997080619903739</v>
+        <v>5.208001781424132</v>
       </c>
       <c r="L83" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M83" t="n">
-        <v>45.45454545454545</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N83" t="n">
-        <v>13.64942371105745</v>
+        <v>13.18166684752475</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>3.776443046059352</v>
+        <v>4.554784937871492</v>
       </c>
       <c r="Q83" t="n">
         <v>43</v>
@@ -9706,22 +9714,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>4.639565621074826</v>
+        <v>5.349461595157945</v>
       </c>
       <c r="Z83" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="AA83" t="n">
-        <v>48.93617021276596</v>
+        <v>48.78048780487805</v>
       </c>
       <c r="AB83" t="n">
-        <v>12.77433850361352</v>
+        <v>12.17803308178011</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.426623512975356</v>
+        <v>0.687305551353079</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9755,7 +9763,7 @@
         <v>46244</v>
       </c>
       <c r="C84" t="n">
-        <v>2.208826262481661</v>
+        <v>2.221038406601399</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9783,16 +9791,16 @@
         <v>13.05747170375323</v>
       </c>
       <c r="K84" t="n">
-        <v>5.742149141067787</v>
+        <v>6.326775640116544</v>
       </c>
       <c r="L84" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M84" t="n">
-        <v>59.09090909090909</v>
+        <v>55.81395348837209</v>
       </c>
       <c r="N84" t="n">
-        <v>11.02609612234209</v>
+        <v>9.866960283458381</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
@@ -9864,7 +9872,7 @@
         <v>46244</v>
       </c>
       <c r="C85" t="n">
-        <v>6.423199616917777</v>
+        <v>6.402001546931206</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9889,25 +9897,25 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>16.20338496372404</v>
+        <v>16.44674445852348</v>
       </c>
       <c r="K85" t="n">
-        <v>0.9491899781412183</v>
+        <v>0.9090909090909038</v>
       </c>
       <c r="L85" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M85" t="n">
-        <v>61.22448979591837</v>
+        <v>60.41666666666666</v>
       </c>
       <c r="N85" t="n">
-        <v>15.21855013264566</v>
+        <v>14.86137547388601</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>6.984513717629159</v>
+        <v>7.027027027027044</v>
       </c>
       <c r="Q85" t="n">
         <v>34</v>
@@ -9973,7 +9981,7 @@
         <v>46244</v>
       </c>
       <c r="C86" t="n">
-        <v>4.40298296475022</v>
+        <v>4.643417210281276</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10030,10 +10038,10 @@
         <v>69.23076923076923</v>
       </c>
       <c r="X86" t="n">
-        <v>81.75144481783289</v>
+        <v>82.30403359278233</v>
       </c>
       <c r="Y86" t="n">
-        <v>5.146724108352152</v>
+        <v>0.2702730180180191</v>
       </c>
       <c r="Z86" t="n">
         <v>1</v>
@@ -10044,7 +10052,7 @@
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.8995745098172026</v>
+        <v>5.745254855673243</v>
       </c>
       <c r="AE86" t="n">
         <v>51</v>
@@ -10078,7 +10086,7 @@
         <v>46244</v>
       </c>
       <c r="C87" t="n">
-        <v>5.53254387884598</v>
+        <v>5.552595936281858</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10106,22 +10114,22 @@
         <v>22.71406725516376</v>
       </c>
       <c r="K87" t="n">
-        <v>2.599199589567536</v>
+        <v>2.971058374259949</v>
       </c>
       <c r="L87" t="n">
         <v>23</v>
       </c>
       <c r="M87" t="n">
-        <v>65.21739130434783</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="N87" t="n">
-        <v>9.483720186663188</v>
+        <v>9.85562399953966</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>2.339979668493042</v>
+        <v>1.970399894663255</v>
       </c>
       <c r="Q87" t="n">
         <v>47</v>
@@ -10187,7 +10195,7 @@
         <v>46244</v>
       </c>
       <c r="C88" t="n">
-        <v>1.099173979735625</v>
+        <v>1.107373224610799</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10215,7 +10223,7 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>23.14221930647673</v>
+        <v>24.06079382623481</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -10250,25 +10258,25 @@
         <v>68.35443037974683</v>
       </c>
       <c r="X88" t="n">
-        <v>24.31612033147337</v>
+        <v>26.64539911548436</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.9442870497137434</v>
+        <v>2.040820517208619</v>
       </c>
       <c r="Z88" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AA88" t="n">
-        <v>54.54545454545455</v>
+        <v>50</v>
       </c>
       <c r="AB88" t="n">
-        <v>12.34111706543424</v>
+        <v>14.33759883640497</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>5.103908497255083</v>
+        <v>4.041662561584547</v>
       </c>
       <c r="AE88" t="n">
         <v>31</v>
@@ -10302,7 +10310,7 @@
         <v>46244</v>
       </c>
       <c r="C89" t="n">
-        <v>2.192060913873096</v>
+        <v>2.174897758855566</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10321,7 +10329,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -10334,13 +10342,13 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>19.06914340073158</v>
+        <v>18.13686904965957</v>
       </c>
       <c r="L89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M89" t="n">
-        <v>100</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N89" t="n">
         <v>12.23354717638958</v>
@@ -10376,22 +10384,22 @@
         <v>28.7873334490923</v>
       </c>
       <c r="Y89" t="n">
-        <v>4.40432625970566</v>
+        <v>5.152810645803774</v>
       </c>
       <c r="Z89" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA89" t="n">
-        <v>57.14285714285715</v>
+        <v>45</v>
       </c>
       <c r="AB89" t="n">
-        <v>12.29381673502749</v>
+        <v>13.85472601812689</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>5.853480101511865</v>
+        <v>5.110525032107105</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10425,7 +10433,7 @@
         <v>46244</v>
       </c>
       <c r="C90" t="n">
-        <v>2.942307298641886</v>
+        <v>2.936216925701454</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10457,7 +10465,7 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>15.98648621268435</v>
+        <v>15.74640219514762</v>
       </c>
       <c r="L90" t="n">
         <v>6</v>
@@ -10499,16 +10507,16 @@
         <v>33.24184775233741</v>
       </c>
       <c r="Y90" t="n">
-        <v>3.251862808563832</v>
+        <v>3.452124772043963</v>
       </c>
       <c r="Z90" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA90" t="n">
-        <v>40</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="AB90" t="n">
-        <v>12.42826150152315</v>
+        <v>12.47307528162469</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
@@ -10548,7 +10556,7 @@
         <v>46244</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2334565935280649</v>
+        <v>0.2330097789016386</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10576,22 +10584,22 @@
         <v>14.07074278425192</v>
       </c>
       <c r="K91" t="n">
-        <v>2.966708967804976</v>
+        <v>2.76964007843874</v>
       </c>
       <c r="L91" t="n">
         <v>56</v>
       </c>
       <c r="M91" t="n">
-        <v>62.5</v>
+        <v>58.92857142857143</v>
       </c>
       <c r="N91" t="n">
-        <v>14.01795401988059</v>
+        <v>14.44970221801777</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>0.03233184058104577</v>
+        <v>0.2241517255343606</v>
       </c>
       <c r="Q91" t="n">
         <v>46</v>
@@ -10657,7 +10665,7 @@
         <v>46244</v>
       </c>
       <c r="C92" t="n">
-        <v>1.143182819645132</v>
+        <v>1.156659771034622</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10671,7 +10679,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -10685,16 +10693,16 @@
         <v>22.28274626067631</v>
       </c>
       <c r="K92" t="n">
-        <v>8.497073331143268</v>
+        <v>9.77614239871345</v>
       </c>
       <c r="L92" t="n">
         <v>14</v>
       </c>
       <c r="M92" t="n">
-        <v>50</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N92" t="n">
-        <v>14.60018434921859</v>
+        <v>12.51924294417875</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
@@ -10723,17 +10731,27 @@
       <c r="W92" t="n">
         <v>65.71428571428571</v>
       </c>
-      <c r="X92" t="inlineStr"/>
-      <c r="Y92" t="inlineStr"/>
+      <c r="X92" t="n">
+        <v>10.77139298215177</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>0.8984725718838682</v>
+      </c>
       <c r="Z92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA92" t="inlineStr"/>
-      <c r="AB92" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>41.66666666666666</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>11.65304168423076</v>
+      </c>
       <c r="AC92" t="n">
         <v>4</v>
       </c>
-      <c r="AD92" t="inlineStr"/>
+      <c r="AD92" t="n">
+        <v>3.129646443003464</v>
+      </c>
       <c r="AE92" t="n">
         <v>51</v>
       </c>
@@ -10766,7 +10784,7 @@
         <v>46244</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04254190874273115</v>
+        <v>0.04215568565212681</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10794,22 +10812,22 @@
         <v>16.78996521390855</v>
       </c>
       <c r="K93" t="n">
-        <v>3.173024756685994</v>
+        <v>2.236352997797542</v>
       </c>
       <c r="L93" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M93" t="n">
-        <v>54</v>
+        <v>58.49056603773585</v>
       </c>
       <c r="N93" t="n">
-        <v>19.80117075707787</v>
+        <v>17.05996837608867</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>2.740033308106349</v>
+        <v>3.68131969876071</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10875,7 +10893,7 @@
         <v>46244</v>
       </c>
       <c r="C94" t="n">
-        <v>6.863288334553252</v>
+        <v>7.036434132663127</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10932,25 +10950,25 @@
         <v>70.90909090909091</v>
       </c>
       <c r="X94" t="n">
-        <v>49.43866730977011</v>
+        <v>51.28627381887829</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.475012191322944</v>
+        <v>0.2230483271375538</v>
       </c>
       <c r="Z94" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA94" t="n">
-        <v>50</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB94" t="n">
-        <v>9.960569015483692</v>
+        <v>14.2160206715065</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>4.592731153099971</v>
+        <v>5.789865871833088</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -10984,7 +11002,7 @@
         <v>46244</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1389422974444268</v>
+        <v>0.1388411123225697</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11012,7 +11030,7 @@
         <v>23.83393539702336</v>
       </c>
       <c r="K95" t="n">
-        <v>0.7909001831348794</v>
+        <v>0.7174989244491226</v>
       </c>
       <c r="L95" t="n">
         <v>21</v>
@@ -11027,7 +11045,7 @@
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>5.168224321243597</v>
+        <v>5.244869195484525</v>
       </c>
       <c r="Q95" t="n">
         <v>23</v>
@@ -11093,7 +11111,7 @@
         <v>46244</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1322361800892633</v>
+        <v>0.1325492247827862</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11121,22 +11139,22 @@
         <v>12.85874206974231</v>
       </c>
       <c r="K96" t="n">
-        <v>2.280273957128909</v>
+        <v>2.522403584532995</v>
       </c>
       <c r="L96" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M96" t="n">
-        <v>59.72222222222222</v>
+        <v>61.42857142857143</v>
       </c>
       <c r="N96" t="n">
-        <v>13.57776283679153</v>
+        <v>14.04225157753042</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>7.547619637885261</v>
+        <v>7.293621836812969</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11163,13 +11181,13 @@
         <v>16.74415231729489</v>
       </c>
       <c r="Y96" t="n">
-        <v>10.87168265924412</v>
+        <v>10.66068785610236</v>
       </c>
       <c r="Z96" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA96" t="n">
-        <v>36.8421052631579</v>
+        <v>35</v>
       </c>
       <c r="AB96" t="n">
         <v>18.11843988336842</v>
@@ -11212,7 +11230,7 @@
         <v>46244</v>
       </c>
       <c r="C97" t="n">
-        <v>1.875616201351194</v>
+        <v>1.908541001705945</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11240,16 +11258,16 @@
         <v>19.26562870655475</v>
       </c>
       <c r="K97" t="n">
-        <v>4.940393171400981</v>
+        <v>6.782529900561451</v>
       </c>
       <c r="L97" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M97" t="n">
-        <v>48.14814814814815</v>
+        <v>38.09523809523809</v>
       </c>
       <c r="N97" t="n">
-        <v>12.27530152555119</v>
+        <v>10.31500308322226</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11321,7 +11339,7 @@
         <v>46244</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6316320800513867</v>
+        <v>0.6224779947503315</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11349,22 +11367,22 @@
         <v>17.47600423199651</v>
       </c>
       <c r="K98" t="n">
-        <v>5.201288909925306</v>
+        <v>3.676633017868558</v>
       </c>
       <c r="L98" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="M98" t="n">
-        <v>51.61290322580645</v>
+        <v>51.21951219512195</v>
       </c>
       <c r="N98" t="n">
-        <v>18.16434795474966</v>
+        <v>14.74335546348866</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>4.561456556091636</v>
+        <v>6.09912455494348</v>
       </c>
       <c r="Q98" t="n">
         <v>48</v>
@@ -11391,22 +11409,22 @@
         <v>11.17514685780745</v>
       </c>
       <c r="Y98" t="n">
-        <v>5.373375360162713</v>
+        <v>6.744775295443917</v>
       </c>
       <c r="Z98" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AA98" t="n">
-        <v>41.66666666666666</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="AB98" t="n">
-        <v>11.56208130746633</v>
+        <v>10.54852534432984</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>2.775777588849437</v>
+        <v>1.346010058452796</v>
       </c>
       <c r="AE98" t="n">
         <v>50</v>
@@ -11440,7 +11458,7 @@
         <v>46244</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4803254020672477</v>
+        <v>0.4786033523877138</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11468,22 +11486,22 @@
         <v>28.77817890954801</v>
       </c>
       <c r="K99" t="n">
-        <v>3.333918168573557</v>
+        <v>2.963448191551077</v>
       </c>
       <c r="L99" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M99" t="n">
-        <v>60</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N99" t="n">
-        <v>12.81653281024479</v>
+        <v>12.70566279278295</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>0.6445916725424494</v>
+        <v>1.006718235116355</v>
       </c>
       <c r="Q99" t="n">
         <v>35</v>
@@ -11549,7 +11567,7 @@
         <v>46244</v>
       </c>
       <c r="C100" t="n">
-        <v>324.1701803070112</v>
+        <v>324.3401826786446</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11581,7 +11599,7 @@
         <v>22.53558813827499</v>
       </c>
       <c r="K100" t="n">
-        <v>5.770082079841754</v>
+        <v>5.825550367468946</v>
       </c>
       <c r="L100" t="n">
         <v>15</v>
@@ -11662,7 +11680,7 @@
         <v>46244</v>
       </c>
       <c r="C101" t="n">
-        <v>327.2024005761539</v>
+        <v>329.3281876844792</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11690,16 +11708,16 @@
         <v>13.42090796247281</v>
       </c>
       <c r="K101" t="n">
-        <v>3.614871329428149</v>
+        <v>4.28804230040829</v>
       </c>
       <c r="L101" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="M101" t="n">
-        <v>34.28571428571428</v>
+        <v>44.82758620689656</v>
       </c>
       <c r="N101" t="n">
-        <v>8.220045130496679</v>
+        <v>8.189774946696966</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11771,7 +11789,7 @@
         <v>46244</v>
       </c>
       <c r="C102" t="n">
-        <v>399.8840837517943</v>
+        <v>402.5666462596445</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11870,16 +11888,16 @@
         <v>46244</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7121054487053645</v>
+        <v>0.7197925998560476</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -11898,7 +11916,7 @@
         <v>26.15665886206818</v>
       </c>
       <c r="K103" t="n">
-        <v>9.520637670364929</v>
+        <v>10.70290877560911</v>
       </c>
       <c r="L103" t="n">
         <v>15</v>
@@ -11907,13 +11925,13 @@
         <v>60</v>
       </c>
       <c r="N103" t="n">
-        <v>12.86523953581864</v>
+        <v>11.35999402515668</v>
       </c>
       <c r="O103" t="n">
         <v>10</v>
       </c>
       <c r="P103" t="n">
-        <v>0.4376913245135228</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
         <v>43</v>
@@ -11940,22 +11958,22 @@
         <v>14.26498323563516</v>
       </c>
       <c r="Y103" t="n">
-        <v>4.152055538735377</v>
+        <v>3.117380635045841</v>
       </c>
       <c r="Z103" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA103" t="n">
         <v>42</v>
       </c>
-      <c r="AA103" t="n">
-        <v>42.85714285714285</v>
-      </c>
       <c r="AB103" t="n">
-        <v>11.09941705691624</v>
+        <v>11.54806676105423</v>
       </c>
       <c r="AC103" t="n">
         <v>10</v>
       </c>
       <c r="AD103" t="n">
-        <v>6.101272692006421</v>
+        <v>7.104080597808283</v>
       </c>
       <c r="AE103" t="n">
         <v>41</v>
@@ -11989,7 +12007,7 @@
         <v>46244</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04882888937540767</v>
+        <v>0.04844757801569531</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12008,7 +12026,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -12021,22 +12039,22 @@
         <v>28.20973926735822</v>
       </c>
       <c r="K104" t="n">
-        <v>1.623371824024433</v>
+        <v>0.8297812553171857</v>
       </c>
       <c r="L104" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M104" t="n">
-        <v>85.71428571428571</v>
+        <v>80</v>
       </c>
       <c r="N104" t="n">
-        <v>14.62100600668919</v>
+        <v>13.89980778935865</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>2.338662980097772</v>
+        <v>3.144129348704339</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>

--- a/TDA_Result.xlsx
+++ b/TDA_Result.xlsx
@@ -453,7 +453,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -679,7 +679,7 @@
         <v>46244</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4580498435553736</v>
+        <v>0.4565435010502994</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -739,22 +739,22 @@
         <v>14.94856954517825</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.830517025898572</v>
+        <v>4.146779943424017</v>
       </c>
       <c r="Z2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AA2" t="n">
-        <v>38.46153846153846</v>
+        <v>44.73684210526316</v>
       </c>
       <c r="AB2" t="n">
-        <v>12.6613735935216</v>
+        <v>11.48762678747732</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.335557232042387</v>
+        <v>4.019917175762766</v>
       </c>
       <c r="AE2" t="n">
         <v>42</v>
@@ -788,7 +788,7 @@
         <v>46244</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7424434547303098</v>
+        <v>0.7466519055886273</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,22 +848,22 @@
         <v>12.13279917920569</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.415475501421493</v>
+        <v>1.862329435861898</v>
       </c>
       <c r="Z3" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AA3" t="n">
-        <v>45</v>
+        <v>43.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.52716613075928</v>
+        <v>10.59198096757892</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>7.772261572775285</v>
+        <v>8.292096722246633</v>
       </c>
       <c r="AE3" t="n">
         <v>38</v>
@@ -897,7 +897,7 @@
         <v>46244</v>
       </c>
       <c r="C4" t="n">
-        <v>1.414627304879296</v>
+        <v>1.402330576270362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         <v>23.54405567752772</v>
       </c>
       <c r="K4" t="n">
-        <v>9.530202317292936</v>
+        <v>8.578104780555297</v>
       </c>
       <c r="L4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M4" t="n">
-        <v>53.33333333333334</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N4" t="n">
-        <v>13.32021955243562</v>
+        <v>10.0938172922653</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -967,22 +967,22 @@
         <v>12.1087988317258</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.300083973161904</v>
+        <v>3.149346070927084</v>
       </c>
       <c r="Z4" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="AA4" t="n">
-        <v>33.33333333333334</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.55139178328925</v>
+        <v>13.96399592938681</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>7.881190015273843</v>
+        <v>7.073420417057674</v>
       </c>
       <c r="AE4" t="n">
         <v>45</v>
@@ -1016,7 +1016,7 @@
         <v>46244</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2653081642454355</v>
+        <v>0.2561506670963014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,22 +1076,22 @@
         <v>16.70172291026088</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.036257868737726</v>
+        <v>8.314069542236203</v>
       </c>
       <c r="Z5" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="AA5" t="n">
-        <v>35.29411764705883</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.15732167421072</v>
+        <v>14.68591940771668</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.226986658130228</v>
+        <v>1.838810436177485</v>
       </c>
       <c r="AE5" t="n">
         <v>44</v>
@@ -1125,16 +1125,16 @@
         <v>46244</v>
       </c>
       <c r="C6" t="n">
-        <v>1.940000468767032</v>
+        <v>1.725139134001438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %88.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1154,25 +1154,25 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>23.73506360720576</v>
+        <v>30.70417007027299</v>
       </c>
       <c r="K6" t="n">
-        <v>2.178587775754903</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="N6" t="n">
-        <v>13.17071203308601</v>
+        <v>10.89796730947936</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.000000000000002</v>
       </c>
       <c r="Q6" t="n">
         <v>41</v>
@@ -1199,7 +1199,7 @@
         <v>44.49622708587002</v>
       </c>
       <c r="Y6" t="n">
-        <v>22.07356502576511</v>
+        <v>30.70417007027299</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1244,7 +1244,7 @@
         <v>46244</v>
       </c>
       <c r="C7" t="n">
-        <v>2.158119472479225</v>
+        <v>2.234505737908237</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,16 +1272,16 @@
         <v>11.64775322580256</v>
       </c>
       <c r="K7" t="n">
-        <v>3.737311186385606</v>
+        <v>7.409075371930007</v>
       </c>
       <c r="L7" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="M7" t="n">
-        <v>51.66666666666666</v>
+        <v>53.125</v>
       </c>
       <c r="N7" t="n">
-        <v>12.43698426543203</v>
+        <v>14.12399808663098</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1314,16 +1314,16 @@
         <v>13.79329344082609</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.345754823687468</v>
+        <v>5.101668669508664</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AA7" t="n">
-        <v>60</v>
+        <v>48.57142857142857</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.645933329578495</v>
+        <v>10.37115075502094</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
@@ -1363,7 +1363,7 @@
         <v>46244</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3345189957646927</v>
+        <v>0.3351758606757547</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,22 +1391,18 @@
         <v>22.10694516187944</v>
       </c>
       <c r="K8" t="n">
-        <v>6.359578773641328</v>
+        <v>6.568427527034371</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N8" t="n">
-        <v>16.4609408474371</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>1.54233520410032</v>
+        <v>1.343336395390149</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1472,7 +1468,7 @@
         <v>46244</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6103136689548196</v>
+        <v>0.6166900556431197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,25 +1525,25 @@
         <v>56.60377358490566</v>
       </c>
       <c r="X9" t="n">
-        <v>10.56818998714018</v>
+        <v>11.26249146068097</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.6825899835756988</v>
+        <v>0.2711861694915219</v>
       </c>
       <c r="Z9" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AA9" t="n">
-        <v>45</v>
+        <v>41.86046511627907</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.59898270408642</v>
+        <v>11.77020234024376</v>
       </c>
       <c r="AC9" t="n">
         <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.340209955007589</v>
+        <v>3.738953354890684</v>
       </c>
       <c r="AE9" t="n">
         <v>34</v>
@@ -1581,7 +1577,7 @@
         <v>46244</v>
       </c>
       <c r="C10" t="n">
-        <v>2.062692358216615</v>
+        <v>2.047947532005178</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,21 +1676,21 @@
         <v>46244</v>
       </c>
       <c r="C11" t="n">
-        <v>7.513569383089614</v>
+        <v>7.493769350540917</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1708,16 +1704,16 @@
         <v>20.56423081971027</v>
       </c>
       <c r="K11" t="n">
-        <v>7.656595405281341</v>
+        <v>7.372894811805231</v>
       </c>
       <c r="L11" t="n">
         <v>15</v>
       </c>
       <c r="M11" t="n">
-        <v>73.33333333333333</v>
+        <v>60</v>
       </c>
       <c r="N11" t="n">
-        <v>13.35789015794225</v>
+        <v>14.33116666007836</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1750,22 +1746,22 @@
         <v>10.78465339552526</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.82354811282034</v>
+        <v>3.079631049202547</v>
       </c>
       <c r="Z11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA11" t="n">
-        <v>44</v>
+        <v>43.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.17460533107513</v>
+        <v>11.1724031141323</v>
       </c>
       <c r="AC11" t="n">
         <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.1815788534700991</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>46</v>
@@ -1799,7 +1795,7 @@
         <v>46244</v>
       </c>
       <c r="C12" t="n">
-        <v>6.517352926155192</v>
+        <v>6.419487730358478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,13 +1823,17 @@
         <v>20.08266526523165</v>
       </c>
       <c r="K12" t="n">
-        <v>13.46519908538817</v>
+        <v>11.76139478778118</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="N12" t="n">
+        <v>22.33927009741701</v>
+      </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
@@ -1865,16 +1865,16 @@
         <v>18.9022858703151</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.572735288585705</v>
+        <v>6.005680235889155</v>
       </c>
       <c r="Z12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA12" t="n">
-        <v>50</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="AB12" t="n">
-        <v>12.46718403715016</v>
+        <v>11.33349134838182</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
@@ -1914,7 +1914,7 @@
         <v>46244</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2818768160586889</v>
+        <v>0.2494429438428099</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>35.3274613290198</v>
+        <v>41.62087466615226</v>
       </c>
       <c r="K13" t="n">
-        <v>2.00602136345307</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1953,7 +1953,7 @@
         <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.935099905405814</v>
+        <v>5.000000000000004</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -2007,7 +2007,7 @@
         <v>46244</v>
       </c>
       <c r="C14" t="n">
-        <v>8.12178574627063</v>
+        <v>8.054491952294677</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,16 +2067,16 @@
         <v>14.33662537827827</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.138219678068513</v>
+        <v>6.915919989862696</v>
       </c>
       <c r="Z14" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA14" t="n">
-        <v>40.74074074074074</v>
+        <v>36</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.98487553716564</v>
+        <v>11.58494518108551</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2116,7 +2116,7 @@
         <v>46244</v>
       </c>
       <c r="C15" t="n">
-        <v>13.10811127545292</v>
+        <v>13.18484173843423</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,25 +2173,25 @@
         <v>79.56989247311827</v>
       </c>
       <c r="X15" t="n">
-        <v>23.91362762258735</v>
+        <v>24.14240658517568</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.3984063745020028</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="AA15" t="n">
-        <v>34.21052631578947</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB15" t="n">
-        <v>14.22094249277022</v>
+        <v>14.33550558807397</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>9.639999999999993</v>
+        <v>9.999999999999998</v>
       </c>
       <c r="AE15" t="n">
         <v>31</v>
@@ -2225,7 +2225,7 @@
         <v>46244</v>
       </c>
       <c r="C16" t="n">
-        <v>39.30336084831804</v>
+        <v>39.95279547449227</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,16 +2253,16 @@
         <v>17.40096492560246</v>
       </c>
       <c r="K16" t="n">
-        <v>13.28669081354736</v>
+        <v>15.15859942673052</v>
       </c>
       <c r="L16" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="M16" t="n">
-        <v>66.66666666666667</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="N16" t="n">
-        <v>18.71491459123237</v>
+        <v>15.68786907301461</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
@@ -2292,25 +2292,25 @@
         <v>77.35849056603773</v>
       </c>
       <c r="X16" t="n">
-        <v>13.52849805114298</v>
+        <v>16.60865524322663</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.2129925452609149</v>
+        <v>1.243523316062189</v>
       </c>
       <c r="Z16" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="AA16" t="n">
-        <v>35.48387096774194</v>
+        <v>29.82456140350877</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.80423727901993</v>
+        <v>13.93082575472769</v>
       </c>
       <c r="AC16" t="n">
         <v>5</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.797225186766285</v>
+        <v>3.803777544595999</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -2344,16 +2344,16 @@
         <v>46244</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7722250449578594</v>
+        <v>0.756713460388979</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2361,7 +2361,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %79.07: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>5</v>
       </c>
@@ -2372,22 +2376,22 @@
         <v>14.16674936134154</v>
       </c>
       <c r="K17" t="n">
-        <v>9.674909150095946</v>
+        <v>7.471883439554761</v>
       </c>
       <c r="L17" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="M17" t="n">
-        <v>69.44444444444444</v>
+        <v>79.06976744186046</v>
       </c>
       <c r="N17" t="n">
-        <v>14.15831234101636</v>
+        <v>15.64776226365078</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.4913997443268814</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2414,22 +2418,22 @@
         <v>15.7396793517258</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.240009507197074</v>
+        <v>7.143441176336507</v>
       </c>
       <c r="Z17" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="AA17" t="n">
-        <v>47.36842105263158</v>
+        <v>51.61290322580645</v>
       </c>
       <c r="AB17" t="n">
-        <v>10.43971091706255</v>
+        <v>11.53769482586445</v>
       </c>
       <c r="AC17" t="n">
         <v>8</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.912611618521155</v>
+        <v>0.9224537658024889</v>
       </c>
       <c r="AE17" t="n">
         <v>41</v>
@@ -2463,7 +2467,7 @@
         <v>46244</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1038162373167213</v>
+        <v>0.101454111274639</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,22 +2495,22 @@
         <v>24.37863714425642</v>
       </c>
       <c r="K18" t="n">
-        <v>3.890765529135631</v>
+        <v>1.526943750086129</v>
       </c>
       <c r="L18" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="M18" t="n">
-        <v>57.89473684210526</v>
+        <v>67.85714285714286</v>
       </c>
       <c r="N18" t="n">
-        <v>16.99147144679783</v>
+        <v>17.55197681791838</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>5.880440325710246</v>
+        <v>8.345623276881797</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2572,7 +2576,7 @@
         <v>46244</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02516757469751851</v>
+        <v>0.02536352787106373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2600,22 +2604,22 @@
         <v>18.34152851742537</v>
       </c>
       <c r="K19" t="n">
-        <v>1.896174633632808</v>
+        <v>2.689531920997745</v>
       </c>
       <c r="L19" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="M19" t="n">
-        <v>62.85714285714285</v>
+        <v>58.62068965517241</v>
       </c>
       <c r="N19" t="n">
-        <v>22.46278047041083</v>
+        <v>23.82410481760151</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>7.95302217723528</v>
+        <v>7.11900029364867</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2681,7 +2685,7 @@
         <v>46244</v>
       </c>
       <c r="C20" t="n">
-        <v>1.867643758494115</v>
+        <v>1.884447205815652</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2741,16 +2745,16 @@
         <v>16.29942815131207</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.723539300428248</v>
+        <v>4.875321039412839</v>
       </c>
       <c r="Z20" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AA20" t="n">
-        <v>54.54545454545455</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="AB20" t="n">
-        <v>13.1471808178665</v>
+        <v>12.98065252867794</v>
       </c>
       <c r="AC20" t="n">
         <v>4</v>
@@ -2790,7 +2794,7 @@
         <v>46244</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9605623783257267</v>
+        <v>0.946206276677532</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,22 +2822,22 @@
         <v>13.9566823466854</v>
       </c>
       <c r="K21" t="n">
-        <v>2.910407529892356</v>
+        <v>1.372358253247352</v>
       </c>
       <c r="L21" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M21" t="n">
-        <v>50.87719298245614</v>
+        <v>54.23728813559322</v>
       </c>
       <c r="N21" t="n">
-        <v>16.90554560239201</v>
+        <v>17.7832466742535</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>4.945653789806714</v>
+        <v>6.537918088277617</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2899,7 +2903,7 @@
         <v>46244</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3397622601992031</v>
+        <v>0.3395778158714058</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2927,7 +2931,7 @@
         <v>20.35908649698318</v>
       </c>
       <c r="K22" t="n">
-        <v>14.54189211860968</v>
+        <v>14.47971157423711</v>
       </c>
       <c r="L22" t="n">
         <v>2</v>
@@ -2965,7 +2969,7 @@
         <v>19.40139685595055</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.069889352470069</v>
+        <v>4.121966251074205</v>
       </c>
       <c r="Z22" t="n">
         <v>19</v>
@@ -2980,7 +2984,7 @@
         <v>5</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.9695711192780565</v>
+        <v>0.9157819727770966</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3006,16 +3010,16 @@
         <v>46244</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8640867112173198</v>
+        <v>0.8271444242743407</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3031,25 +3035,25 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>19.72222345813771</v>
+        <v>19.76580328516925</v>
       </c>
       <c r="K23" t="n">
-        <v>5.967077227757911</v>
+        <v>1.49176438795815</v>
       </c>
       <c r="L23" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="M23" t="n">
-        <v>70</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N23" t="n">
-        <v>18.8115330499001</v>
+        <v>21.65624672905748</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.456670236445403</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3076,10 +3080,10 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>14.93198653515787</v>
+        <v>18.56889811161312</v>
       </c>
       <c r="Z23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
@@ -3121,7 +3125,7 @@
         <v>46244</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1883373331581377</v>
+        <v>0.1802697042301657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3149,22 +3153,22 @@
         <v>22.66030863734194</v>
       </c>
       <c r="K24" t="n">
-        <v>7.601513011240901</v>
+        <v>2.992288358292527</v>
       </c>
       <c r="L24" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M24" t="n">
-        <v>57.14285714285715</v>
+        <v>50</v>
       </c>
       <c r="N24" t="n">
-        <v>10.47568893942637</v>
+        <v>11.39307587315487</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>2.22904578349985</v>
+        <v>6.804112961670339</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3191,16 +3195,16 @@
         <v>12.68278405422394</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.509358803681929</v>
+        <v>8.599801449055644</v>
       </c>
       <c r="Z24" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA24" t="n">
-        <v>51.72413793103448</v>
+        <v>48.14814814814815</v>
       </c>
       <c r="AB24" t="n">
-        <v>14.95215384139686</v>
+        <v>10.97274027872045</v>
       </c>
       <c r="AC24" t="n">
         <v>2</v>
@@ -3240,7 +3244,7 @@
         <v>46244</v>
       </c>
       <c r="C25" t="n">
-        <v>4.081341654660188</v>
+        <v>4.068645249376182</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3339,7 +3343,7 @@
         <v>46244</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4437882121957873</v>
+        <v>0.4422896115917362</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3438,11 +3442,11 @@
         <v>46244</v>
       </c>
       <c r="C27" t="n">
-        <v>37.54163069289717</v>
+        <v>36.7875949935645</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3452,7 +3456,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3466,7 +3470,7 @@
         <v>61.00029220182797</v>
       </c>
       <c r="K27" t="n">
-        <v>13.88952586676666</v>
+        <v>11.60201819332238</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3491,25 +3495,25 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>17.89792817380926</v>
+        <v>17.83392576195235</v>
       </c>
       <c r="Y27" t="n">
-        <v>3.399892066918508</v>
+        <v>5.288720992984352</v>
       </c>
       <c r="Z27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AA27" t="n">
-        <v>28.57142857142857</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB27" t="n">
-        <v>10.01602907091211</v>
+        <v>9.939327383614815</v>
       </c>
       <c r="AC27" t="n">
         <v>5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.656424581005589</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3533,7 +3537,7 @@
         <v>46244</v>
       </c>
       <c r="C28" t="n">
-        <v>1.485935462096687</v>
+        <v>1.475696150331602</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3561,16 +3565,16 @@
         <v>16.53966926125512</v>
       </c>
       <c r="K28" t="n">
-        <v>6.568650454268665</v>
+        <v>5.83430521235222</v>
       </c>
       <c r="L28" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M28" t="n">
-        <v>52.17391304347826</v>
+        <v>48.27586206896552</v>
       </c>
       <c r="N28" t="n">
-        <v>14.74519198998796</v>
+        <v>16.50031882445172</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
@@ -3642,7 +3646,7 @@
         <v>46244</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4244930707204824</v>
+        <v>0.4288741650847534</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3670,7 +3674,7 @@
         <v>20.65475273479386</v>
       </c>
       <c r="K29" t="n">
-        <v>16.7864074935623</v>
+        <v>17.99173287337377</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3708,10 +3712,10 @@
         <v>55.05052857749912</v>
       </c>
       <c r="Y29" t="n">
-        <v>7.33553620208176</v>
+        <v>6.379167799120077</v>
       </c>
       <c r="Z29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
@@ -3719,7 +3723,7 @@
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.8753889988819</v>
+        <v>3.867549685000438</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3753,7 +3757,7 @@
         <v>46244</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3770941355246598</v>
+        <v>0.3743740564247834</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,22 +3785,22 @@
         <v>21.6314445059014</v>
       </c>
       <c r="K30" t="n">
-        <v>2.007402654210511</v>
+        <v>1.271596451320778</v>
       </c>
       <c r="L30" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="M30" t="n">
-        <v>46.42857142857143</v>
+        <v>55.88235294117647</v>
       </c>
       <c r="N30" t="n">
-        <v>10.81922057035711</v>
+        <v>13.03151287049459</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>2.93370605262242</v>
+        <v>3.681588598705843</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3862,7 +3866,7 @@
         <v>46244</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1858205783100081</v>
+        <v>0.1817370094229127</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3879,7 +3883,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H31" t="n">
         <v>5</v>
       </c>
@@ -3890,18 +3898,22 @@
         <v>31.09418993049242</v>
       </c>
       <c r="K31" t="n">
-        <v>6.713551462968659</v>
+        <v>4.368428320263651</v>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M31" t="n">
+        <v>75</v>
+      </c>
+      <c r="N31" t="n">
+        <v>15.54180404115201</v>
+      </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>3.079691840423671</v>
+        <v>5.395857512058511</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3967,7 +3979,7 @@
         <v>46244</v>
       </c>
       <c r="C32" t="n">
-        <v>2.384627539262812</v>
+        <v>2.385429300552595</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4027,7 +4039,7 @@
         <v>15.25475988862757</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.826412868356375</v>
+        <v>1.793404870023163</v>
       </c>
       <c r="Z32" t="n">
         <v>46</v>
@@ -4036,13 +4048,13 @@
         <v>30.43478260869565</v>
       </c>
       <c r="AB32" t="n">
-        <v>13.02274589842517</v>
+        <v>13.04824395145401</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>6.288440009190344</v>
+        <v>6.31993719134889</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4076,7 +4088,7 @@
         <v>46244</v>
       </c>
       <c r="C33" t="n">
-        <v>1.819405845032865</v>
+        <v>1.810033487982492</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4104,22 +4116,22 @@
         <v>12.57251846431013</v>
       </c>
       <c r="K33" t="n">
-        <v>1.975604470855585</v>
+        <v>1.450294640650429</v>
       </c>
       <c r="L33" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="M33" t="n">
-        <v>59.32203389830509</v>
+        <v>62.5</v>
       </c>
       <c r="N33" t="n">
-        <v>12.20835416664673</v>
+        <v>12.14923460513611</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>1.985176297457492</v>
+        <v>2.513255745960086</v>
       </c>
       <c r="Q33" t="n">
         <v>39</v>
@@ -4185,7 +4197,7 @@
         <v>46244</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7864866765271752</v>
+        <v>0.7751596842961377</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4210,25 +4222,25 @@
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>19.24836024850346</v>
+        <v>19.29219731829385</v>
       </c>
       <c r="K34" t="n">
-        <v>1.957589026325679</v>
+        <v>0.5437758744808896</v>
       </c>
       <c r="L34" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M34" t="n">
-        <v>63.88888888888889</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N34" t="n">
-        <v>11.36426027875977</v>
+        <v>11.79230815170657</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>2.003196616533343</v>
+        <v>3.437531657686965</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4294,7 +4306,7 @@
         <v>46244</v>
       </c>
       <c r="C35" t="n">
-        <v>1.915881511931543</v>
+        <v>1.901216383882698</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4326,7 +4338,7 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>8.008300608647968</v>
+        <v>7.181550337872089</v>
       </c>
       <c r="L35" t="n">
         <v>11</v>
@@ -4335,7 +4347,7 @@
         <v>81.81818181818181</v>
       </c>
       <c r="N35" t="n">
-        <v>13.27568040215743</v>
+        <v>13.64608558513277</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4368,7 +4380,7 @@
         <v>38.58137734187126</v>
       </c>
       <c r="Y35" t="n">
-        <v>16.73554045342692</v>
+        <v>17.37288882469298</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -4413,7 +4425,7 @@
         <v>46244</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08368218259222122</v>
+        <v>0.08258867605806258</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4441,16 +4453,16 @@
         <v>17.66670693852417</v>
       </c>
       <c r="K36" t="n">
-        <v>4.591442869844919</v>
+        <v>3.224707172323971</v>
       </c>
       <c r="L36" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M36" t="n">
-        <v>57.14285714285715</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="N36" t="n">
-        <v>14.09899135848872</v>
+        <v>12.44154056901678</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4522,7 +4534,7 @@
         <v>46244</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06627461249625799</v>
+        <v>0.06560978710911244</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4550,22 +4562,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>7.883879540920269</v>
+        <v>6.801656057733463</v>
       </c>
       <c r="L37" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M37" t="n">
-        <v>66.66666666666667</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N37" t="n">
-        <v>15.0620484694513</v>
+        <v>19.51196754959671</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>0.1076346712538312</v>
+        <v>1.122027491426492</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4631,7 +4643,7 @@
         <v>46244</v>
       </c>
       <c r="C38" t="n">
-        <v>1.632746308381759</v>
+        <v>1.624523425641737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4659,22 +4671,22 @@
         <v>14.71604491689452</v>
       </c>
       <c r="K38" t="n">
-        <v>3.05530596058885</v>
+        <v>2.536295939068167</v>
       </c>
       <c r="L38" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M38" t="n">
-        <v>56.60377358490566</v>
+        <v>62.5</v>
       </c>
       <c r="N38" t="n">
-        <v>13.20718576230645</v>
+        <v>12.35251913188087</v>
       </c>
       <c r="O38" t="n">
         <v>6</v>
       </c>
       <c r="P38" t="n">
-        <v>2.857391972168122</v>
+        <v>3.378027291906593</v>
       </c>
       <c r="Q38" t="n">
         <v>34</v>
@@ -4740,7 +4752,7 @@
         <v>46244</v>
       </c>
       <c r="C39" t="n">
-        <v>2.682443923497342</v>
+        <v>2.664218385981212</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4768,16 +4780,16 @@
         <v>16.13238434452433</v>
       </c>
       <c r="K39" t="n">
-        <v>6.183201467326827</v>
+        <v>5.461752677671483</v>
       </c>
       <c r="L39" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M39" t="n">
-        <v>66.66666666666667</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N39" t="n">
-        <v>12.27545027216149</v>
+        <v>12.47459691849123</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4810,22 +4822,22 @@
         <v>10.2437411865161</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.683238318554016</v>
+        <v>4.337650788496195</v>
       </c>
       <c r="Z39" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AA39" t="n">
-        <v>41.66666666666666</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="AB39" t="n">
-        <v>13.51254539176915</v>
+        <v>13.61225224484199</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.405356701161065</v>
+        <v>1.737725683307711</v>
       </c>
       <c r="AE39" t="n">
         <v>46</v>
@@ -4859,7 +4871,7 @@
         <v>46244</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2181189636538049</v>
+        <v>0.2196774806896081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4916,25 +4928,25 @@
         <v>76.47058823529412</v>
       </c>
       <c r="X40" t="n">
-        <v>19.81060928895926</v>
+        <v>20.89036800977206</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.5736177798332132</v>
+        <v>0.757584060777905</v>
       </c>
       <c r="Z40" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA40" t="n">
-        <v>29.16666666666667</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="AB40" t="n">
-        <v>12.20092311358603</v>
+        <v>11.46802597456556</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.45191922035858</v>
+        <v>4.274801151374863</v>
       </c>
       <c r="AE40" t="n">
         <v>14</v>
@@ -4968,7 +4980,7 @@
         <v>46244</v>
       </c>
       <c r="C41" t="n">
-        <v>1.712443689113826</v>
+        <v>1.691600457993442</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4987,7 +4999,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -5000,16 +5012,16 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>13.16793261071165</v>
+        <v>11.79049439781381</v>
       </c>
       <c r="L41" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M41" t="n">
-        <v>80</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N41" t="n">
-        <v>12.17975430538131</v>
+        <v>13.38516228592029</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
@@ -5042,17 +5054,13 @@
         <v>36.58819281794096</v>
       </c>
       <c r="Y41" t="n">
-        <v>12.18030503720299</v>
+        <v>13.24921387821629</v>
       </c>
       <c r="Z41" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>22.49011102054075</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
         <v>3</v>
       </c>
@@ -5091,7 +5099,7 @@
         <v>46244</v>
       </c>
       <c r="C42" t="n">
-        <v>3.657687242367217</v>
+        <v>3.716490429949373</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5100,7 +5108,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5115,12 +5123,8 @@
       <c r="I42" t="n">
         <v>10</v>
       </c>
-      <c r="J42" t="n">
-        <v>18.35939977786119</v>
-      </c>
-      <c r="K42" t="n">
-        <v>19.00360598493511</v>
-      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
         <v>0</v>
       </c>
@@ -5129,9 +5133,7 @@
       <c r="O42" t="n">
         <v>2</v>
       </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="n">
         <v>2</v>
       </c>
@@ -5152,25 +5154,25 @@
       </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="n">
-        <v>20.0953863872158</v>
+        <v>23.37193653404788</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.9090943749999969</v>
+        <v>1.990044760305554</v>
       </c>
       <c r="Z42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA42" t="n">
         <v>50</v>
       </c>
       <c r="AB42" t="n">
-        <v>13.05682117011112</v>
+        <v>7.017580456707584</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>9.174308749789473</v>
+        <v>8.172593508593273</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5202,7 +5204,7 @@
         <v>46244</v>
       </c>
       <c r="C43" t="n">
-        <v>7.22519093502965</v>
+        <v>7.21078785059042</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5262,7 +5264,7 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>6.742101468452599</v>
+        <v>6.928006782132656</v>
       </c>
       <c r="Z43" t="n">
         <v>10</v>
@@ -5311,7 +5313,7 @@
         <v>46244</v>
       </c>
       <c r="C44" t="n">
-        <v>5.060779665194446</v>
+        <v>5.001436119583373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5328,11 +5330,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.26: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>5</v>
       </c>
@@ -5343,22 +5341,22 @@
         <v>13.03201987649729</v>
       </c>
       <c r="K44" t="n">
-        <v>3.580727066744771</v>
+        <v>2.36612220192749</v>
       </c>
       <c r="L44" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M44" t="n">
-        <v>78.26086956521739</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N44" t="n">
-        <v>19.86668303814072</v>
+        <v>18.6118219603867</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>6.197362303818177</v>
+        <v>7.457425986122557</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5385,22 +5383,22 @@
         <v>12.1234692799834</v>
       </c>
       <c r="Y44" t="n">
-        <v>7.619049132262001</v>
+        <v>8.702323555196855</v>
       </c>
       <c r="Z44" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA44" t="n">
-        <v>11.11111111111111</v>
+        <v>14.28571428571429</v>
       </c>
       <c r="AB44" t="n">
-        <v>9.691917834769438</v>
+        <v>9.672387522044957</v>
       </c>
       <c r="AC44" t="n">
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.577317991830164</v>
+        <v>1.421368533500078</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5426,7 +5424,7 @@
         <v>46244</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02139243718207961</v>
+        <v>0.0213808240214723</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5525,7 +5523,7 @@
         <v>46244</v>
       </c>
       <c r="C46" t="n">
-        <v>9.1599481592865</v>
+        <v>9.270264322452364</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5553,16 +5551,16 @@
         <v>20.92024905883424</v>
       </c>
       <c r="K46" t="n">
-        <v>10.93245552895854</v>
+        <v>12.26845030226038</v>
       </c>
       <c r="L46" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M46" t="n">
-        <v>42.10526315789474</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N46" t="n">
-        <v>14.41348684240534</v>
+        <v>11.92048283778781</v>
       </c>
       <c r="O46" t="n">
         <v>10</v>
@@ -5595,16 +5593,16 @@
         <v>16.0625044063383</v>
       </c>
       <c r="Y46" t="n">
-        <v>4.420074255350626</v>
+        <v>3.268974871328645</v>
       </c>
       <c r="Z46" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AA46" t="n">
-        <v>32.35294117647059</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB46" t="n">
-        <v>13.91659552208615</v>
+        <v>12.00915435520501</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
@@ -5644,7 +5642,7 @@
         <v>46244</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7382488429729719</v>
+        <v>0.7143711137903003</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5669,25 +5667,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>25.80558454936143</v>
+        <v>28.04553017245678</v>
       </c>
       <c r="K47" t="n">
-        <v>0.3993137037347605</v>
+        <v>0.1763708676916442</v>
       </c>
       <c r="L47" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M47" t="n">
-        <v>58.33333333333334</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N47" t="n">
-        <v>13.51380842266347</v>
+        <v>14.52806188384168</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>9.562501915695965</v>
+        <v>9.80633361662</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5753,7 +5751,7 @@
         <v>46244</v>
       </c>
       <c r="C48" t="n">
-        <v>0.06040217906431464</v>
+        <v>0.05953092106600549</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5781,22 +5779,22 @@
         <v>20.70237270975156</v>
       </c>
       <c r="K48" t="n">
-        <v>2.922464274602321</v>
+        <v>1.437881738110458</v>
       </c>
       <c r="L48" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M48" t="n">
-        <v>53.84615384615385</v>
+        <v>62.7906976744186</v>
       </c>
       <c r="N48" t="n">
-        <v>16.2937831569074</v>
+        <v>14.17452541850965</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>6.876570411795102</v>
+        <v>8.440750255407536</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5862,7 +5860,7 @@
         <v>46244</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2571287156030694</v>
+        <v>0.2542641204094432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5890,22 +5888,22 @@
         <v>21.9393534200744</v>
       </c>
       <c r="K49" t="n">
-        <v>1.755708142612722</v>
+        <v>0.6220778058154242</v>
       </c>
       <c r="L49" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M49" t="n">
-        <v>60</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N49" t="n">
-        <v>10.66615203453425</v>
+        <v>10.35730392418133</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>3.188314362512568</v>
+        <v>4.350856481649368</v>
       </c>
       <c r="Q49" t="n">
         <v>53</v>
@@ -5971,7 +5969,7 @@
         <v>46244</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7118228459692154</v>
+        <v>0.702213351729009</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5996,25 +5994,25 @@
         <v>10</v>
       </c>
       <c r="J50" t="n">
-        <v>11.29749771777515</v>
+        <v>11.66227088204316</v>
       </c>
       <c r="K50" t="n">
-        <v>1.011905284173031</v>
+        <v>0.0597385312867349</v>
       </c>
       <c r="L50" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M50" t="n">
-        <v>40.38461538461539</v>
+        <v>38.77551020408163</v>
       </c>
       <c r="N50" t="n">
-        <v>13.72535370926058</v>
+        <v>14.60985324555625</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>2.958160929071352</v>
+        <v>3.937909019701502</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6080,7 +6078,7 @@
         <v>46244</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1900151898576163</v>
+        <v>0.181108167095259</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6099,7 +6097,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -6112,16 +6110,16 @@
         <v>27.11346359280836</v>
       </c>
       <c r="K51" t="n">
-        <v>10.13303463432689</v>
+        <v>4.970513432150914</v>
       </c>
       <c r="L51" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M51" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="N51" t="n">
-        <v>22.72871476502574</v>
+        <v>17.95969937536291</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
@@ -6154,10 +6152,10 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>13.73968078749415</v>
+        <v>17.78316082343087</v>
       </c>
       <c r="Z51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="inlineStr"/>
@@ -6199,7 +6197,7 @@
         <v>46244</v>
       </c>
       <c r="C52" t="n">
-        <v>4.286876583588957</v>
+        <v>4.282453429850365</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6259,22 +6257,22 @@
         <v>12.1710603868542</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.637958156180319</v>
+        <v>1.739447066493849</v>
       </c>
       <c r="Z52" t="n">
         <v>56</v>
       </c>
       <c r="AA52" t="n">
-        <v>37.5</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="AB52" t="n">
-        <v>12.06351788347552</v>
+        <v>12.40921988117128</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>6.467984727199338</v>
+        <v>6.371379710984049</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6308,7 +6306,7 @@
         <v>46244</v>
       </c>
       <c r="C53" t="n">
-        <v>1.588703086584894</v>
+        <v>1.563734775062616</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6325,11 +6323,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>5</v>
       </c>
@@ -6340,22 +6334,22 @@
         <v>28.17598592067425</v>
       </c>
       <c r="K53" t="n">
-        <v>4.740044831209977</v>
+        <v>3.093933553221206</v>
       </c>
       <c r="L53" t="n">
         <v>7</v>
       </c>
       <c r="M53" t="n">
-        <v>85.71428571428571</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N53" t="n">
-        <v>14.26016933944701</v>
+        <v>17.02235577422501</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>3.112424836215699</v>
+        <v>4.758831366392768</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6413,7 +6407,7 @@
         <v>46244</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08389191216289869</v>
+        <v>0.08384637035570257</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6441,7 +6435,7 @@
         <v>42.39442432818535</v>
       </c>
       <c r="K54" t="n">
-        <v>3.788096878702207</v>
+        <v>3.731754170860202</v>
       </c>
       <c r="L54" t="n">
         <v>5</v>
@@ -6456,7 +6450,7 @@
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>5.985178751815523</v>
+        <v>6.04274542471841</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6483,7 +6477,7 @@
         <v>114.7400208810756</v>
       </c>
       <c r="Y54" t="n">
-        <v>40.21226931420291</v>
+        <v>40.2447258554044</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -6528,7 +6522,7 @@
         <v>46244</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8456304681003957</v>
+        <v>0.8451714066873882</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6556,13 +6550,13 @@
         <v>15.124509340431</v>
       </c>
       <c r="K55" t="n">
-        <v>4.141032154089119</v>
+        <v>4.084497850778002</v>
       </c>
       <c r="L55" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M55" t="n">
-        <v>71.15384615384616</v>
+        <v>69.81132075471699</v>
       </c>
       <c r="N55" t="n">
         <v>13.38061250851474</v>
@@ -6571,7 +6565,7 @@
         <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>1.785048416996982</v>
+        <v>1.840333756490997</v>
       </c>
       <c r="Q55" t="n">
         <v>44</v>
@@ -6598,7 +6592,7 @@
         <v>25.41488056506582</v>
       </c>
       <c r="Y55" t="n">
-        <v>11.60978798127735</v>
+        <v>11.65777174860363</v>
       </c>
       <c r="Z55" t="n">
         <v>12</v>
@@ -6647,7 +6641,7 @@
         <v>46244</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8984823824105918</v>
+        <v>0.8992523541361466</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6675,7 +6669,7 @@
         <v>34.38683570496719</v>
       </c>
       <c r="K56" t="n">
-        <v>14.57579046198487</v>
+        <v>14.67397838510489</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6705,13 +6699,13 @@
         <v>21.95662732854271</v>
       </c>
       <c r="Y56" t="n">
-        <v>6.052017859328274</v>
+        <v>5.97150733253623</v>
       </c>
       <c r="Z56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA56" t="n">
-        <v>37.5</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB56" t="n">
         <v>14.70795307963829</v>
@@ -6720,7 +6714,7 @@
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>4.202306479302842</v>
+        <v>4.284331858547096</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6746,7 +6740,7 @@
         <v>46244</v>
       </c>
       <c r="C57" t="n">
-        <v>1.453427442189803</v>
+        <v>1.406522830645674</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6765,7 +6759,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
+          <t>SAT_Güncel_Benzer_Başarı_% %80.00: SAT yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -6778,10 +6772,10 @@
         <v>32.76213282665623</v>
       </c>
       <c r="K57" t="n">
-        <v>24.45295741361664</v>
+        <v>20.43664572611419</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -6816,16 +6810,16 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>10.39539495019229</v>
+        <v>13.28709017379017</v>
       </c>
       <c r="Z57" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA57" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB57" t="n">
-        <v>13.51506266023374</v>
+        <v>12.75692533836235</v>
       </c>
       <c r="AC57" t="n">
         <v>6</v>
@@ -6865,7 +6859,7 @@
         <v>46244</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7625774943542657</v>
+        <v>0.7143711137903003</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6884,7 +6878,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %79.17: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -6894,25 +6888,25 @@
         <v>10</v>
       </c>
       <c r="J58" t="n">
-        <v>16.33691982084211</v>
+        <v>20.18518226981877</v>
       </c>
       <c r="K58" t="n">
-        <v>2.803279300050043</v>
+        <v>0.9478777426668916</v>
       </c>
       <c r="L58" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M58" t="n">
-        <v>85.71428571428571</v>
+        <v>79.16666666666667</v>
       </c>
       <c r="N58" t="n">
-        <v>20.15533012800163</v>
+        <v>22.87838130409069</v>
       </c>
       <c r="O58" t="n">
         <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>2.136819676285251</v>
+        <v>4.014073745723157</v>
       </c>
       <c r="Q58" t="n">
         <v>24</v>
@@ -6939,7 +6933,7 @@
         <v>41.32985472592288</v>
       </c>
       <c r="Y58" t="n">
-        <v>13.9916100123955</v>
+        <v>19.42863537720422</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -6984,7 +6978,7 @@
         <v>46244</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8263353668932085</v>
+        <v>0.8187598352408174</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7044,22 +7038,22 @@
         <v>10.2478061424703</v>
       </c>
       <c r="Y59" t="n">
-        <v>6.172984742276211</v>
+        <v>7.033155506365175</v>
       </c>
       <c r="Z59" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AA59" t="n">
         <v>50</v>
       </c>
       <c r="AB59" t="n">
-        <v>15.12318601205643</v>
+        <v>14.91469059929055</v>
       </c>
       <c r="AC59" t="n">
         <v>10</v>
       </c>
       <c r="AD59" t="n">
-        <v>4.078798890928958</v>
+        <v>3.191293100023374</v>
       </c>
       <c r="AE59" t="n">
         <v>43</v>
@@ -7093,7 +7087,7 @@
         <v>46244</v>
       </c>
       <c r="C60" t="n">
-        <v>13.82119252883756</v>
+        <v>13.84513190498539</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7107,7 +7101,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -7121,16 +7115,16 @@
         <v>14.21636055978318</v>
       </c>
       <c r="K60" t="n">
-        <v>8.771277639473475</v>
+        <v>8.959677918541864</v>
       </c>
       <c r="L60" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M60" t="n">
-        <v>58.06451612903226</v>
+        <v>58.62068965517241</v>
       </c>
       <c r="N60" t="n">
-        <v>11.95211381735988</v>
+        <v>11.65899024327127</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
@@ -7159,17 +7153,27 @@
       <c r="W60" t="n">
         <v>69.84126984126983</v>
       </c>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
+      <c r="X60" t="n">
+        <v>10.69181511482451</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1.56482861400894</v>
+      </c>
       <c r="Z60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA60" t="inlineStr"/>
-      <c r="AB60" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>32.55813953488372</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>10.29154464375254</v>
+      </c>
       <c r="AC60" t="n">
         <v>5</v>
       </c>
-      <c r="AD60" t="inlineStr"/>
+      <c r="AD60" t="n">
+        <v>3.489780469341419</v>
+      </c>
       <c r="AE60" t="n">
         <v>33</v>
       </c>
@@ -7202,7 +7206,7 @@
         <v>46244</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6505817884708492</v>
+        <v>0.6422631841381101</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7230,22 +7234,22 @@
         <v>30.3360843704085</v>
       </c>
       <c r="K61" t="n">
-        <v>5.871188776360436</v>
+        <v>4.517476537139431</v>
       </c>
       <c r="L61" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M61" t="n">
-        <v>50</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N61" t="n">
-        <v>15.2992064867625</v>
+        <v>13.3246998255089</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>3.899844019283827</v>
+        <v>5.245556671005547</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7303,7 +7307,7 @@
         <v>46244</v>
       </c>
       <c r="C62" t="n">
-        <v>8.960704867899617</v>
+        <v>9.003004016943562</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7320,11 +7324,7 @@
           <t>SATMA_BEKLE</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>5</v>
       </c>
@@ -7335,16 +7335,16 @@
         <v>10.67683828611802</v>
       </c>
       <c r="K62" t="n">
-        <v>7.689937002929237</v>
+        <v>8.198289053685691</v>
       </c>
       <c r="L62" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M62" t="n">
-        <v>76.92307692307692</v>
+        <v>72</v>
       </c>
       <c r="N62" t="n">
-        <v>12.65658828717897</v>
+        <v>12.48664095804736</v>
       </c>
       <c r="O62" t="n">
         <v>6</v>
@@ -7374,19 +7374,19 @@
         <v>73.13432835820896</v>
       </c>
       <c r="X62" t="n">
-        <v>10.71458122536377</v>
+        <v>10.65447838610345</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.731929425156521</v>
+        <v>2.219692657939665</v>
       </c>
       <c r="Z62" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA62" t="n">
-        <v>39.58333333333334</v>
+        <v>44</v>
       </c>
       <c r="AB62" t="n">
-        <v>16.61073097776234</v>
+        <v>15.04433619819926</v>
       </c>
       <c r="AC62" t="n">
         <v>2</v>
@@ -7426,28 +7426,24 @@
         <v>46244</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1029773190340114</v>
+        <v>0.1004060276624901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AL_BEKLE_EŞİK</t>
-        </is>
-      </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>5</v>
       </c>
@@ -7458,22 +7454,22 @@
         <v>28.76464722640304</v>
       </c>
       <c r="K63" t="n">
-        <v>3.19761727187633</v>
+        <v>0.620825165207739</v>
       </c>
       <c r="L63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M63" t="n">
-        <v>83.33333333333333</v>
+        <v>40</v>
       </c>
       <c r="N63" t="n">
-        <v>12.56793181945185</v>
+        <v>16.7494976320711</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>1.746535216385148</v>
+        <v>4.352155557860082</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7500,22 +7496,22 @@
         <v>10.24796802016521</v>
       </c>
       <c r="Y63" t="n">
-        <v>6.39499382609875</v>
+        <v>8.73226330411514</v>
       </c>
       <c r="Z63" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AA63" t="n">
-        <v>63.63636363636363</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="AB63" t="n">
-        <v>12.49876729611108</v>
+        <v>10.93819437215829</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>3.85129633686877</v>
+        <v>1.389030496186305</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7549,7 +7545,7 @@
         <v>46244</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1596043656164019</v>
+        <v>0.1536484719998975</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7574,25 +7570,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>21.47552816415833</v>
+        <v>21.70283994296762</v>
       </c>
       <c r="K64" t="n">
-        <v>3.858991966646474</v>
+        <v>0.2735975398653778</v>
       </c>
       <c r="L64" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M64" t="n">
-        <v>64.86486486486487</v>
+        <v>62.5</v>
       </c>
       <c r="N64" t="n">
-        <v>14.10469386361876</v>
+        <v>15.34020976304821</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>1.098612659094522</v>
+        <v>4.713506422521219</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7658,7 +7654,7 @@
         <v>46244</v>
       </c>
       <c r="C65" t="n">
-        <v>6.029731186708344</v>
+        <v>6.084102248935667</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7677,7 +7673,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -7690,22 +7686,22 @@
         <v>32.91027483217498</v>
       </c>
       <c r="K65" t="n">
-        <v>6.435478272697948</v>
+        <v>7.3952242104798</v>
       </c>
       <c r="L65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M65" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="N65" t="n">
-        <v>19.15715795420472</v>
+        <v>16.67238679599688</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>3.348997707483781</v>
+        <v>2.425411193718641</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7771,7 +7767,7 @@
         <v>46244</v>
       </c>
       <c r="C66" t="n">
-        <v>0.443368742987403</v>
+        <v>0.4355819084613737</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7870,16 +7866,16 @@
         <v>46244</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0281037912037604</v>
+        <v>0.02766930326546147</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7898,18 +7894,22 @@
         <v>18.49825117353735</v>
       </c>
       <c r="K67" t="n">
-        <v>4.379241484064833</v>
+        <v>2.765526056676193</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
-      </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M67" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="N67" t="n">
+        <v>12.94041349650492</v>
+      </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.201252979178036</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7926,14 +7926,12 @@
         <v>10.87173616493582</v>
       </c>
       <c r="Y67" t="n">
-        <v>5.855860930338974</v>
+        <v>7.311340463001859</v>
       </c>
       <c r="Z67" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA67" t="inlineStr"/>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
         <v>3</v>
@@ -7963,16 +7961,16 @@
         <v>46244</v>
       </c>
       <c r="C68" t="n">
-        <v>3.403914399977197</v>
+        <v>3.542509147528433</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7982,7 +7980,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %92.86: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -7992,25 +7990,25 @@
         <v>10</v>
       </c>
       <c r="J68" t="n">
-        <v>17.33552180626085</v>
+        <v>17.380397285086</v>
       </c>
       <c r="K68" t="n">
-        <v>0.7448770357308954</v>
+        <v>4.903782495884079</v>
       </c>
       <c r="L68" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M68" t="n">
-        <v>92.85714285714286</v>
+        <v>100</v>
       </c>
       <c r="N68" t="n">
-        <v>16.59375163464654</v>
+        <v>15.57963927239859</v>
       </c>
       <c r="O68" t="n">
         <v>2</v>
       </c>
       <c r="P68" t="n">
-        <v>1.245842966113253</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>5</v>
@@ -8037,7 +8035,7 @@
         <v>128.0325939207301</v>
       </c>
       <c r="Y68" t="n">
-        <v>16.71977309148891</v>
+        <v>13.32891166898307</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -8082,7 +8080,7 @@
         <v>46244</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4202984992312623</v>
+        <v>0.4112664642024588</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8099,11 +8097,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>5</v>
       </c>
@@ -8114,16 +8108,16 @@
         <v>29.4573350207784</v>
       </c>
       <c r="K69" t="n">
-        <v>7.510864084354218</v>
+        <v>5.20050158683667</v>
       </c>
       <c r="L69" t="n">
         <v>5</v>
       </c>
       <c r="M69" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="N69" t="n">
-        <v>21.84733273523247</v>
+        <v>14.20304940810647</v>
       </c>
       <c r="O69" t="n">
         <v>3</v>
@@ -8179,7 +8173,7 @@
         <v>46244</v>
       </c>
       <c r="C70" t="n">
-        <v>0.3997449503405339</v>
+        <v>0.3957548504711783</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8207,22 +8201,22 @@
         <v>21.94656073986526</v>
       </c>
       <c r="K70" t="n">
-        <v>4.221905124349878</v>
+        <v>3.181602277080886</v>
       </c>
       <c r="L70" t="n">
         <v>22</v>
       </c>
       <c r="M70" t="n">
-        <v>54.54545454545455</v>
+        <v>50</v>
       </c>
       <c r="N70" t="n">
-        <v>11.56447238634469</v>
+        <v>11.16826164139007</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>3.62504875644174</v>
+        <v>4.669822542569113</v>
       </c>
       <c r="Q70" t="n">
         <v>30</v>
@@ -8288,7 +8282,7 @@
         <v>46244</v>
       </c>
       <c r="C71" t="n">
-        <v>3.204671108590313</v>
+        <v>3.171489022637306</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8305,7 +8299,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %78.72: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H71" t="n">
         <v>5</v>
       </c>
@@ -8316,22 +8314,22 @@
         <v>18.95735500740921</v>
       </c>
       <c r="K71" t="n">
-        <v>2.294419625449184</v>
+        <v>1.235233796542801</v>
       </c>
       <c r="L71" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M71" t="n">
-        <v>73.33333333333333</v>
+        <v>78.72340425531915</v>
       </c>
       <c r="N71" t="n">
-        <v>14.30912419081266</v>
+        <v>13.83375454675616</v>
       </c>
       <c r="O71" t="n">
         <v>6</v>
       </c>
       <c r="P71" t="n">
-        <v>3.622465808124042</v>
+        <v>4.706628339529684</v>
       </c>
       <c r="Q71" t="n">
         <v>43</v>
@@ -8397,16 +8395,16 @@
         <v>46244</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07739029022865272</v>
+        <v>0.07420403692633307</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8425,22 +8423,22 @@
         <v>20.36571476939619</v>
       </c>
       <c r="K72" t="n">
-        <v>8.196401589925827</v>
+        <v>3.741822845661491</v>
       </c>
       <c r="L72" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M72" t="n">
-        <v>61.53846153846154</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="N72" t="n">
-        <v>14.52327366036347</v>
+        <v>16.00115835593591</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1.212796459351129</v>
       </c>
       <c r="Q72" t="n">
         <v>12</v>
@@ -8467,10 +8465,10 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>13.8385689486289</v>
+        <v>17.38594089165823</v>
       </c>
       <c r="Z72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr"/>
@@ -8512,7 +8510,7 @@
         <v>46244</v>
       </c>
       <c r="C73" t="n">
-        <v>0.06900109691506505</v>
+        <v>0.06854440734655499</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8540,22 +8538,22 @@
         <v>22.88332385411211</v>
       </c>
       <c r="K73" t="n">
-        <v>1.304256487155864</v>
+        <v>0.6337657377073702</v>
       </c>
       <c r="L73" t="n">
         <v>21</v>
       </c>
       <c r="M73" t="n">
-        <v>71.42857142857143</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N73" t="n">
-        <v>16.2002307703648</v>
+        <v>16.97617006151214</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>8.583788889410249</v>
+        <v>9.307248112631372</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8621,7 +8619,7 @@
         <v>46244</v>
       </c>
       <c r="C74" t="n">
-        <v>5.07755811159461</v>
+        <v>5.072705406520005</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8649,22 +8647,22 @@
         <v>18.35970785011217</v>
       </c>
       <c r="K74" t="n">
-        <v>7.426399899005953</v>
+        <v>7.323730737082235</v>
       </c>
       <c r="L74" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M74" t="n">
-        <v>72.22222222222223</v>
+        <v>73.68421052631579</v>
       </c>
       <c r="N74" t="n">
-        <v>21.71559040851504</v>
+        <v>21.41006206684089</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>0.533947057272055</v>
+        <v>0.6301209045504352</v>
       </c>
       <c r="Q74" t="n">
         <v>35</v>
@@ -8691,7 +8689,7 @@
         <v>59.69432739383429</v>
       </c>
       <c r="Y74" t="n">
-        <v>12.29677327634475</v>
+        <v>12.38059268008711</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
@@ -8736,7 +8734,7 @@
         <v>46244</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1289838170477546</v>
+        <v>0.1270272498311938</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8764,22 +8762,22 @@
         <v>21.52133760858017</v>
       </c>
       <c r="K75" t="n">
-        <v>1.94598508361612</v>
+        <v>0.3995571918074647</v>
       </c>
       <c r="L75" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M75" t="n">
-        <v>66.66666666666667</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N75" t="n">
-        <v>14.07085928325531</v>
+        <v>20.09443459697961</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>3.976630284222349</v>
+        <v>5.578154889162734</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8845,7 +8843,7 @@
         <v>46244</v>
       </c>
       <c r="C76" t="n">
-        <v>1.872887003004296</v>
+        <v>1.860341342267151</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8873,22 +8871,22 @@
         <v>18.36583782901725</v>
       </c>
       <c r="K76" t="n">
-        <v>8.061449211820126</v>
+        <v>7.337592258143211</v>
       </c>
       <c r="L76" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M76" t="n">
-        <v>47.05882352941177</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N76" t="n">
-        <v>13.37029545732525</v>
+        <v>13.73160595198125</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>1.793933731519703</v>
+        <v>2.48040568625183</v>
       </c>
       <c r="Q76" t="n">
         <v>40</v>
@@ -8954,7 +8952,7 @@
         <v>46244</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5272606551503016</v>
+        <v>0.5164936286045563</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8982,16 +8980,16 @@
         <v>20.36657537342047</v>
       </c>
       <c r="K77" t="n">
-        <v>8.592514542292239</v>
+        <v>6.374980434019362</v>
       </c>
       <c r="L77" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M77" t="n">
-        <v>40</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N77" t="n">
-        <v>10.35289348072587</v>
+        <v>10.34206919233464</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -9024,22 +9022,22 @@
         <v>14.86223722874125</v>
       </c>
       <c r="Y77" t="n">
-        <v>5.458471676782017</v>
+        <v>7.389074947077711</v>
       </c>
       <c r="Z77" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AA77" t="n">
-        <v>46.80851063829788</v>
+        <v>50</v>
       </c>
       <c r="AB77" t="n">
-        <v>12.48273666248703</v>
+        <v>12.07817505029321</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>4.803739059190404</v>
+        <v>2.819240874044049</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9073,7 +9071,7 @@
         <v>46244</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05222271553113422</v>
+        <v>0.04905012477154266</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9090,7 +9088,11 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %100.00: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H78" t="n">
         <v>5</v>
       </c>
@@ -9098,25 +9100,25 @@
         <v>10</v>
       </c>
       <c r="J78" t="n">
-        <v>12.76206508896208</v>
+        <v>15.5428166034715</v>
       </c>
       <c r="K78" t="n">
-        <v>3.074337453349707</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="M78" t="n">
-        <v>58.22784810126582</v>
+        <v>67.69230769230769</v>
       </c>
       <c r="N78" t="n">
-        <v>16.24530698554662</v>
+        <v>16.72800252790132</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>0.8980533559764581</v>
+        <v>4.000000000000004</v>
       </c>
       <c r="Q78" t="n">
         <v>45</v>
@@ -9143,16 +9145,16 @@
         <v>23.16536029857119</v>
       </c>
       <c r="Y78" t="n">
-        <v>10.08007658246322</v>
+        <v>15.5428166034715</v>
       </c>
       <c r="Z78" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AA78" t="n">
-        <v>42.85714285714285</v>
+        <v>100</v>
       </c>
       <c r="AB78" t="n">
-        <v>14.37178883655818</v>
+        <v>22.78846965271385</v>
       </c>
       <c r="AC78" t="n">
         <v>10</v>
@@ -9192,7 +9194,7 @@
         <v>46244</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8716369961054974</v>
+        <v>0.8707445754286363</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9217,25 +9219,25 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>12.03872531442141</v>
+        <v>12.08647622758069</v>
       </c>
       <c r="K79" t="n">
-        <v>1.168450629545648</v>
+        <v>1.119764044567484</v>
       </c>
       <c r="L79" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M79" t="n">
-        <v>60</v>
+        <v>59.32203389830509</v>
       </c>
       <c r="N79" t="n">
-        <v>10.88225231662067</v>
+        <v>11.04081635513927</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>3.787296678570828</v>
+        <v>3.837267612414874</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9301,11 +9303,11 @@
         <v>46244</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1268865211312501</v>
+        <v>0.1249310926684605</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -9315,7 +9317,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -9329,7 +9331,7 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>3.885772292983058</v>
+        <v>2.284804796912709</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9340,7 +9342,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>5.885529434938741</v>
+        <v>7.542855674805149</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9367,22 +9369,22 @@
         <v>11.74527658842108</v>
       </c>
       <c r="Y80" t="n">
-        <v>7.033410749329527</v>
+        <v>8.466104412048736</v>
       </c>
       <c r="Z80" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AA80" t="n">
-        <v>46.42857142857143</v>
+        <v>59.09090909090909</v>
     